--- a/resultats.xlsx
+++ b/resultats.xlsx
@@ -1,124 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mathis/Documents_Disque/A_Universite/Python_L3/Code/Projet/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F7E3B2-E7EB-8842-AC64-B6C10E528E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
-  <si>
-    <t>start_date</t>
-  </si>
-  <si>
-    <t>end_date</t>
-  </si>
-  <si>
-    <t>ticker</t>
-  </si>
-  <si>
-    <t>Rendement Moyen Journalier</t>
-  </si>
-  <si>
-    <t>Volatilité Annualisée</t>
-  </si>
-  <si>
-    <t>Sharpe Ratio</t>
-  </si>
-  <si>
-    <t>Max Drawdown</t>
-  </si>
-  <si>
-    <t>20/01/2023</t>
-  </si>
-  <si>
-    <t>30/01/2024</t>
-  </si>
-  <si>
-    <t>^GSPC</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>DSY</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>cours</t>
-  </si>
-  <si>
-    <t>cours 100</t>
-  </si>
-  <si>
-    <t>rendements</t>
-  </si>
-  <si>
-    <t>Matrice corrélations</t>
-  </si>
-  <si>
-    <t>Ticker1</t>
-  </si>
-  <si>
-    <t>Ticker2</t>
-  </si>
-  <si>
-    <t>…</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -133,28 +43,84 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -442,163 +408,139 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rendement Moyen Journalier</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Volatilité Annualisée</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Max Drawdown</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20/01/2023</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>30/01/2024</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>^GSPC</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0008361668887198723</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1255604735857343</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.868098160294477</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.1027661709329137</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20/01/2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30/01/2024</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.001229250692756845</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2013360642749</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.80351773936188</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.1493237070407019</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>8.3616688871987227E-4</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1.229250373731541E-3</v>
-      </c>
-      <c r="E5">
-        <v>2.2389955028307039E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.1255604735857343</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.20133592924251759</v>
-      </c>
-      <c r="E6">
-        <v>5.6722431046152551E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1.8680981602944771</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1.803518404651324</v>
-      </c>
-      <c r="E7">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20/01/2023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30/01/2024</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DSY</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0002238995502830704</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.05672243104615255</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.02331316908072</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>-0.10276617093291369</v>
-      </c>
-      <c r="D8">
-        <v>-0.14932341578477221</v>
-      </c>
-      <c r="E8">
-        <v>-2.9741174682687069E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>19</v>
+      <c r="G4" t="n">
+        <v>-0.02974117468268707</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8756CD-8B6A-4D43-994E-01856BDA2105}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/resultats.xlsx
+++ b/resultats.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="31">
   <si>
     <t>Date début</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>Monte Carlo Defaite 100</t>
+  </si>
+  <si>
+    <t>Matrice de corrélation</t>
   </si>
   <si>
     <t>Date</t>
@@ -454,17 +457,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,7 +480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -492,331 +494,334 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="B4" t="s">
+    <row r="4" spans="1:7" s="1" customFormat="1">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H4" t="s">
+      <c r="G4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="B5" t="s">
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
+      <c r="B5">
+        <v>4019.81005859375</v>
+      </c>
       <c r="C5">
-        <v>4019.81005859375</v>
+        <v>138.8828735351562</v>
       </c>
       <c r="D5">
-        <v>138.8828430175781</v>
+        <v>202</v>
       </c>
       <c r="E5">
-        <v>202</v>
+        <v>236.3760528564453</v>
       </c>
       <c r="F5">
-        <v>236.3760986328125</v>
+        <v>97.51999664306641</v>
       </c>
       <c r="G5">
-        <v>97.51999664306641</v>
-      </c>
-      <c r="H5">
         <v>98.97200012207031</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="B6" t="s">
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
         <v>14</v>
       </c>
+      <c r="B6">
+        <v>4924.97021484375</v>
+      </c>
       <c r="C6">
-        <v>4924.97021484375</v>
+        <v>186.1066284179688</v>
       </c>
       <c r="D6">
-        <v>186.1066284179688</v>
+        <v>214.6000061035156</v>
       </c>
       <c r="E6">
-        <v>214.6000061035156</v>
+        <v>401.6705932617188</v>
       </c>
       <c r="F6">
-        <v>401.6706848144531</v>
+        <v>159</v>
       </c>
       <c r="G6">
-        <v>159</v>
-      </c>
-      <c r="H6">
-        <v>150.2184448242188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="B7" t="s">
+        <v>150.2184295654297</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
         <v>15</v>
       </c>
+      <c r="B7">
+        <v>0.2251748572833444</v>
+      </c>
       <c r="C7">
-        <v>0.2251748572833444</v>
+        <v>0.3400257618579476</v>
       </c>
       <c r="D7">
-        <v>0.3400260563100195</v>
+        <v>0.06237626783918626</v>
       </c>
       <c r="E7">
-        <v>0.06237626783918626</v>
+        <v>0.6992863211302511</v>
       </c>
       <c r="F7">
-        <v>0.6992863793661721</v>
+        <v>0.6304348387331982</v>
       </c>
       <c r="G7">
-        <v>0.6304348387331982</v>
-      </c>
-      <c r="H7">
-        <v>0.5177872998316896</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="B8" t="s">
+        <v>0.5177871456589029</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
+      <c r="B8">
+        <v>0.2212933175580829</v>
+      </c>
       <c r="C8">
-        <v>0.2212933175580829</v>
+        <v>0.3339114632793261</v>
       </c>
       <c r="D8">
-        <v>0.3339117518080437</v>
+        <v>0.06137232945653404</v>
       </c>
       <c r="E8">
-        <v>0.06137232945653404</v>
+        <v>0.6852667271471848</v>
       </c>
       <c r="F8">
-        <v>0.6852667840002158</v>
+        <v>0.6180286426432327</v>
       </c>
       <c r="G8">
-        <v>0.6180286426432327</v>
-      </c>
-      <c r="H8">
-        <v>0.507924140695529</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="B9" t="s">
+        <v>0.5079239899179095</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
         <v>17</v>
       </c>
+      <c r="B9">
+        <v>0.0007932952126940571</v>
+      </c>
       <c r="C9">
-        <v>0.0007932952126940571</v>
+        <v>0.001143315777520085</v>
       </c>
       <c r="D9">
-        <v>0.001143316635864237</v>
+        <v>0.0002363600048310617</v>
       </c>
       <c r="E9">
-        <v>0.0002363600048310617</v>
+        <v>0.002071126374285025</v>
       </c>
       <c r="F9">
-        <v>0.002071126508155384</v>
+        <v>0.001909557622930636</v>
       </c>
       <c r="G9">
-        <v>0.001909557622930636</v>
-      </c>
-      <c r="H9">
-        <v>0.001629896681515416</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10" t="s">
+        <v>0.001629896284728933</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
+      <c r="B10">
+        <v>0.1253305867413214</v>
+      </c>
       <c r="C10">
-        <v>0.1253305867413214</v>
+        <v>0.2005366433319599</v>
       </c>
       <c r="D10">
-        <v>0.2005368292209826</v>
+        <v>0.0567447014935399</v>
       </c>
       <c r="E10">
-        <v>0.0567447014935399</v>
+        <v>0.2370180227174989</v>
       </c>
       <c r="F10">
-        <v>0.2370179323011436</v>
+        <v>0.3161577817349202</v>
       </c>
       <c r="G10">
-        <v>0.3161577817349202</v>
-      </c>
-      <c r="H10">
-        <v>0.2958240455127624</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="B11" t="s">
+        <v>0.2958242952702997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
         <v>19</v>
       </c>
+      <c r="B11">
+        <v>0.007895084861603466</v>
+      </c>
       <c r="C11">
-        <v>0.007895084861603466</v>
+        <v>0.01263262111933393</v>
       </c>
       <c r="D11">
-        <v>0.01263263282924168</v>
+        <v>0.003574580199345286</v>
       </c>
       <c r="E11">
-        <v>0.003574580199345286</v>
+        <v>0.01493073200835142</v>
       </c>
       <c r="F11">
-        <v>0.0149307263126564</v>
+        <v>0.01991606822686756</v>
       </c>
       <c r="G11">
-        <v>0.01991606822686756</v>
-      </c>
-      <c r="H11">
-        <v>0.01863516324428148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12" t="s">
+        <v>0.01863517897752747</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
         <v>20</v>
       </c>
+      <c r="B12">
+        <v>1.765676865574927</v>
+      </c>
       <c r="C12">
-        <v>1.765676865574927</v>
+        <v>1.665089520455288</v>
       </c>
       <c r="D12">
-        <v>1.665089415770546</v>
+        <v>1.081551719212427</v>
       </c>
       <c r="E12">
-        <v>1.081551719212427</v>
+        <v>2.891200927635584</v>
       </c>
       <c r="F12">
-        <v>2.891202270423779</v>
+        <v>1.954810788625198</v>
       </c>
       <c r="G12">
-        <v>1.954810788625198</v>
-      </c>
-      <c r="H12">
-        <v>1.716980578151198</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="B13" t="s">
+        <v>1.716978618858234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
         <v>21</v>
       </c>
+      <c r="B13">
+        <v>-0.1027661709329137</v>
+      </c>
       <c r="C13">
-        <v>-0.1027661709329137</v>
+        <v>-0.1493237857297425</v>
       </c>
       <c r="D13">
-        <v>-0.1493236401017953</v>
+        <v>-0.02974119167021968</v>
       </c>
       <c r="E13">
-        <v>-0.02974119167021968</v>
+        <v>-0.1298761377824637</v>
       </c>
       <c r="F13">
-        <v>-0.1298759868818388</v>
+        <v>-0.1964396385244207</v>
       </c>
       <c r="G13">
-        <v>-0.1964396385244207</v>
-      </c>
-      <c r="H13">
-        <v>-0.17273046423099</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="B14" t="s">
+        <v>-0.1727306660931956</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
         <v>22</v>
       </c>
+      <c r="B14">
+        <v>274.1995309382647</v>
+      </c>
       <c r="C14">
-        <v>289.3292519417429</v>
+        <v>479.964087388934</v>
       </c>
       <c r="D14">
-        <v>508.3534102408851</v>
+        <v>138.6704348944934</v>
       </c>
       <c r="E14">
-        <v>133.3426923463996</v>
+        <v>1590.279683081065</v>
       </c>
       <c r="F14">
-        <v>1560.769980754259</v>
+        <v>1364.921439838779</v>
       </c>
       <c r="G14">
-        <v>1519.729500678265</v>
-      </c>
-      <c r="H14">
-        <v>842.99210660827</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="B15" t="s">
+        <v>892.1121122483803</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
         <v>23</v>
       </c>
+      <c r="B15">
+        <v>177.0349118677307</v>
+      </c>
       <c r="C15">
-        <v>168.0301417946522</v>
+        <v>224.9015932403583</v>
       </c>
       <c r="D15">
-        <v>201.3978305339896</v>
+        <v>113.9666853474681</v>
       </c>
       <c r="E15">
-        <v>108.5500493751687</v>
+        <v>667.2677551551882</v>
       </c>
       <c r="F15">
-        <v>578.7087156414925</v>
+        <v>433.3823542035859</v>
       </c>
       <c r="G15">
-        <v>377.4366988691864</v>
-      </c>
-      <c r="H15">
-        <v>256.5079138038383</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="B16" t="s">
+        <v>256.0116347936635</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
         <v>24</v>
       </c>
+      <c r="B16">
+        <v>264.5725192511479</v>
+      </c>
       <c r="C16">
-        <v>275.6529133100057</v>
+        <v>458.6721137253695</v>
       </c>
       <c r="D16">
-        <v>457.6851227679837</v>
+        <v>136.1337182292322</v>
       </c>
       <c r="E16">
-        <v>131.561905822322</v>
+        <v>1339.407532540178</v>
       </c>
       <c r="F16">
-        <v>1455.508177932308</v>
+        <v>1180.279196810079</v>
       </c>
       <c r="G16">
-        <v>1070.013726878973</v>
-      </c>
-      <c r="H16">
-        <v>648.8716396722762</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" t="s">
+        <v>739.9746896359595</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
         <v>25</v>
       </c>
+      <c r="B17">
+        <v>412.5905649865982</v>
+      </c>
       <c r="C17">
-        <v>446.4992184022089</v>
+        <v>871.260465421851</v>
       </c>
       <c r="D17">
-        <v>954.7323923252362</v>
+        <v>168.0762084020885</v>
       </c>
       <c r="E17">
-        <v>161.1167824863733</v>
+        <v>3598.37871901956</v>
       </c>
       <c r="F17">
-        <v>2556.740558548078</v>
+        <v>2941.517207789171</v>
       </c>
       <c r="G17">
-        <v>3643.382202838813</v>
-      </c>
-      <c r="H17">
-        <v>1953.030047478935</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" t="s">
+        <v>2089.163034403638</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
         <v>26</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -825,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -833,8 +838,166 @@
       <c r="G18">
         <v>0</v>
       </c>
-      <c r="H18">
-        <v>0</v>
+    </row>
+    <row r="20" spans="1:7" s="1" customFormat="1">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>0.7060176093430282</v>
+      </c>
+      <c r="D21">
+        <v>0.004456046337864243</v>
+      </c>
+      <c r="E21">
+        <v>0.6246276333363374</v>
+      </c>
+      <c r="F21">
+        <v>0.6045950866477746</v>
+      </c>
+      <c r="G21">
+        <v>0.6008768067263587</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22">
+        <v>0.7060176093430282</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>-0.05612614144459695</v>
+      </c>
+      <c r="E22">
+        <v>0.5536242390676874</v>
+      </c>
+      <c r="F22">
+        <v>0.4276415487281028</v>
+      </c>
+      <c r="G22">
+        <v>0.5177403248417024</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23">
+        <v>0.004456046337864243</v>
+      </c>
+      <c r="C23">
+        <v>-0.05612614144459695</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>-0.04384003116167206</v>
+      </c>
+      <c r="F23">
+        <v>-0.005269283798744161</v>
+      </c>
+      <c r="G23">
+        <v>-0.01599779840453273</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24">
+        <v>0.6246276333363374</v>
+      </c>
+      <c r="C24">
+        <v>0.5536242390676874</v>
+      </c>
+      <c r="D24">
+        <v>-0.04384003116167206</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0.5709355713557122</v>
+      </c>
+      <c r="G24">
+        <v>0.5011052583023157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25">
+        <v>0.6045950866477746</v>
+      </c>
+      <c r="C25">
+        <v>0.4276415487281028</v>
+      </c>
+      <c r="D25">
+        <v>-0.005269283798744161</v>
+      </c>
+      <c r="E25">
+        <v>0.5709355713557122</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>0.6003312066063872</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>0.6008768067263587</v>
+      </c>
+      <c r="C26">
+        <v>0.5177403248417024</v>
+      </c>
+      <c r="D26">
+        <v>-0.01599779840453273</v>
+      </c>
+      <c r="E26">
+        <v>0.5011052583023157</v>
+      </c>
+      <c r="F26">
+        <v>0.6003312066063872</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -854,13 +1017,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3706,13 +3869,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3720,7 +3883,7 @@
         <v>44949</v>
       </c>
       <c r="B2">
-        <v>138.8828430175781</v>
+        <v>138.8828735351562</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -3731,10 +3894,10 @@
         <v>44950</v>
       </c>
       <c r="B3">
-        <v>140.2804412841797</v>
+        <v>140.2804565429688</v>
       </c>
       <c r="C3">
-        <v>101.006314557101</v>
+        <v>101.0063033491734</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3742,10 +3905,10 @@
         <v>44951</v>
       </c>
       <c r="B4">
-        <v>139.6210327148438</v>
+        <v>139.6210021972656</v>
       </c>
       <c r="C4">
-        <v>100.53151971923</v>
+        <v>100.53147565522</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3756,7 +3919,7 @@
         <v>141.6878967285156</v>
       </c>
       <c r="C5">
-        <v>102.0197265911258</v>
+        <v>102.019704173711</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3767,7 +3930,7 @@
         <v>143.6267852783203</v>
       </c>
       <c r="C6">
-        <v>103.4157871178816</v>
+        <v>103.415764393702</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3775,10 +3938,10 @@
         <v>44956</v>
       </c>
       <c r="B7">
-        <v>140.7430114746094</v>
+        <v>140.7430267333984</v>
       </c>
       <c r="C7">
-        <v>101.3393795926224</v>
+        <v>101.3393683115084</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3786,10 +3949,10 @@
         <v>44957</v>
       </c>
       <c r="B8">
-        <v>142.0126953125</v>
+        <v>142.0126647949219</v>
       </c>
       <c r="C8">
-        <v>102.2535917518089</v>
+        <v>102.2535473093976</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3797,10 +3960,10 @@
         <v>44958</v>
       </c>
       <c r="B9">
-        <v>143.1347198486328</v>
+        <v>143.1346893310547</v>
       </c>
       <c r="C9">
-        <v>103.0614845856205</v>
+        <v>103.061439965686</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3811,7 +3974,7 @@
         <v>148.4396209716797</v>
       </c>
       <c r="C10">
-        <v>106.8811796665856</v>
+        <v>106.8811561809342</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3819,10 +3982,10 @@
         <v>44960</v>
       </c>
       <c r="B11">
-        <v>152.0615386962891</v>
+        <v>152.0615081787109</v>
       </c>
       <c r="C11">
-        <v>109.4890739506556</v>
+        <v>109.4890279183478</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3830,10 +3993,10 @@
         <v>44963</v>
       </c>
       <c r="B12">
-        <v>149.3352355957031</v>
+        <v>149.3352661132812</v>
       </c>
       <c r="C12">
-        <v>107.526050267276</v>
+        <v>107.5260486135313</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3841,10 +4004,10 @@
         <v>44964</v>
       </c>
       <c r="B13">
-        <v>152.2091522216797</v>
+        <v>152.2091674804688</v>
       </c>
       <c r="C13">
-        <v>109.5953603156114</v>
+        <v>109.5953472203606</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3852,10 +4015,10 @@
         <v>44965</v>
       </c>
       <c r="B14">
-        <v>149.5222320556641</v>
+        <v>149.5222473144531</v>
       </c>
       <c r="C14">
-        <v>107.6606935795081</v>
+        <v>107.6606809093734</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3866,7 +4029,7 @@
         <v>148.4888153076172</v>
       </c>
       <c r="C15">
-        <v>106.9166011303666</v>
+        <v>106.9165776369318</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3877,7 +4040,7 @@
         <v>148.8535308837891</v>
       </c>
       <c r="C16">
-        <v>107.1792077765495</v>
+        <v>107.1791842254106</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3888,7 +4051,7 @@
         <v>151.6529998779297</v>
       </c>
       <c r="C17">
-        <v>109.1949131965388</v>
+        <v>109.1948892024767</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3896,10 +4059,10 @@
         <v>44971</v>
       </c>
       <c r="B18">
-        <v>151.0122528076172</v>
+        <v>151.0122680664062</v>
       </c>
       <c r="C18">
-        <v>108.7335552228751</v>
+        <v>108.7335423169939</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3907,10 +4070,10 @@
         <v>44972</v>
       </c>
       <c r="B19">
-        <v>153.1118316650391</v>
+        <v>153.1118621826172</v>
       </c>
       <c r="C19">
-        <v>110.2453178076575</v>
+        <v>110.2453155563915</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3918,10 +4081,10 @@
         <v>44973</v>
       </c>
       <c r="B20">
-        <v>151.5149993896484</v>
+        <v>151.5149841308594</v>
       </c>
       <c r="C20">
-        <v>109.0955485196047</v>
+        <v>109.0955135605727</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3932,7 +4095,7 @@
         <v>150.3715667724609</v>
       </c>
       <c r="C21">
-        <v>108.2722411964368</v>
+        <v>108.2722174051191</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -3943,7 +4106,7 @@
         <v>146.3596801757812</v>
       </c>
       <c r="C22">
-        <v>105.3835571016189</v>
+        <v>105.3835339450493</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3954,7 +4117,7 @@
         <v>146.7835388183594</v>
       </c>
       <c r="C23">
-        <v>105.688748609345</v>
+        <v>105.6887253857137</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3962,10 +4125,10 @@
         <v>44980</v>
       </c>
       <c r="B24">
-        <v>147.2665557861328</v>
+        <v>147.2665252685547</v>
       </c>
       <c r="C24">
-        <v>106.0365359654206</v>
+        <v>106.0364906917599</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3976,7 +4139,7 @@
         <v>144.6149444580078</v>
       </c>
       <c r="C25">
-        <v>104.1272926992891</v>
+        <v>104.1272698187661</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3984,10 +4147,10 @@
         <v>44984</v>
       </c>
       <c r="B26">
-        <v>145.8076629638672</v>
+        <v>145.8076477050781</v>
       </c>
       <c r="C26">
-        <v>104.9860874070763</v>
+        <v>104.9860533510411</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3998,7 +4161,7 @@
         <v>145.3049468994141</v>
       </c>
       <c r="C27">
-        <v>104.6241160839594</v>
+        <v>104.6240930942663</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4006,10 +4169,10 @@
         <v>44986</v>
       </c>
       <c r="B28">
-        <v>143.2349243164062</v>
+        <v>143.2349395751953</v>
       </c>
       <c r="C28">
-        <v>103.1336349431422</v>
+        <v>103.1336232677656</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -4017,10 +4180,10 @@
         <v>44987</v>
       </c>
       <c r="B29">
-        <v>143.8263549804688</v>
+        <v>143.8263854980469</v>
       </c>
       <c r="C29">
-        <v>103.5594835585738</v>
+        <v>103.5594827764269</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -4031,7 +4194,7 @@
         <v>148.8732604980469</v>
       </c>
       <c r="C30">
-        <v>107.1934137172036</v>
+        <v>107.1933901629431</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -4042,7 +4205,7 @@
         <v>151.6332702636719</v>
       </c>
       <c r="C31">
-        <v>109.1807072558847</v>
+        <v>109.1806832649442</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -4053,7 +4216,7 @@
         <v>149.4351196289062</v>
       </c>
       <c r="C32">
-        <v>107.5979699018636</v>
+        <v>107.5979462587076</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -4064,7 +4227,7 @@
         <v>150.6869659423828</v>
       </c>
       <c r="C33">
-        <v>108.4993384843876</v>
+        <v>108.4993146431684</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -4072,10 +4235,10 @@
         <v>44994</v>
       </c>
       <c r="B34">
-        <v>148.4395141601562</v>
+        <v>148.4395446777344</v>
       </c>
       <c r="C34">
-        <v>106.8811027589409</v>
+        <v>106.8811012469143</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -4086,7 +4249,7 @@
         <v>146.37939453125</v>
       </c>
       <c r="C35">
-        <v>105.3977520554667</v>
+        <v>105.3977288957779</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -4097,7 +4260,7 @@
         <v>148.3212432861328</v>
       </c>
       <c r="C36">
-        <v>106.7959440226609</v>
+        <v>106.7959205557389</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -4108,7 +4271,7 @@
         <v>150.4109954833984</v>
       </c>
       <c r="C37">
-        <v>108.3006311041323</v>
+        <v>108.3006073065762</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -4116,10 +4279,10 @@
         <v>45000</v>
       </c>
       <c r="B38">
-        <v>150.8052673339844</v>
+        <v>150.8052520751953</v>
       </c>
       <c r="C38">
-        <v>108.5845191942804</v>
+        <v>108.5844843475399</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -4130,7 +4293,7 @@
         <v>153.6244354248047</v>
       </c>
       <c r="C39">
-        <v>110.614408581311</v>
+        <v>110.6143842753346</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -4141,7 +4304,7 @@
         <v>152.7865447998047</v>
       </c>
       <c r="C40">
-        <v>110.0111010691701</v>
+        <v>110.011076895762</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -4149,10 +4312,10 @@
         <v>45005</v>
       </c>
       <c r="B41">
-        <v>155.1522979736328</v>
+        <v>155.1522827148438</v>
       </c>
       <c r="C41">
-        <v>111.7145175045095</v>
+        <v>111.7144819699955</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -4163,7 +4326,7 @@
         <v>157.0054626464844</v>
       </c>
       <c r="C42">
-        <v>113.0488541530018</v>
+        <v>113.0488293120898</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -4171,10 +4334,10 @@
         <v>45007</v>
       </c>
       <c r="B43">
-        <v>155.576171875</v>
+        <v>155.5761566162109</v>
       </c>
       <c r="C43">
-        <v>112.0197199990419</v>
+        <v>112.0196843974639</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -4185,7 +4348,7 @@
         <v>156.6604461669922</v>
       </c>
       <c r="C44">
-        <v>112.8004314738603</v>
+        <v>112.8004066875357</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -4193,10 +4356,10 @@
         <v>45009</v>
       </c>
       <c r="B45">
-        <v>157.9616088867188</v>
+        <v>157.9615783691406</v>
       </c>
       <c r="C45">
-        <v>113.7373094146164</v>
+        <v>113.737262448818</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -4204,10 +4367,10 @@
         <v>45012</v>
       </c>
       <c r="B46">
-        <v>156.0197143554688</v>
+        <v>156.0197296142578</v>
       </c>
       <c r="C46">
-        <v>112.3390844870029</v>
+        <v>112.3390707888569</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -4218,7 +4381,7 @@
         <v>155.3987121582031</v>
       </c>
       <c r="C47">
-        <v>111.8919434407997</v>
+        <v>111.8919188541027</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -4229,7 +4392,7 @@
         <v>158.4741821289062</v>
       </c>
       <c r="C48">
-        <v>114.1063782146571</v>
+        <v>114.106353141369</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -4237,10 +4400,10 @@
         <v>45015</v>
       </c>
       <c r="B49">
-        <v>160.0414428710938</v>
+        <v>160.0414581298828</v>
       </c>
       <c r="C49">
-        <v>115.2348550719383</v>
+        <v>115.234840737487</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -4248,10 +4411,10 @@
         <v>45016</v>
       </c>
       <c r="B50">
-        <v>162.5451812744141</v>
+        <v>162.545166015625</v>
       </c>
       <c r="C50">
-        <v>117.0376251974054</v>
+        <v>117.0375884932126</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -4262,7 +4425,7 @@
         <v>163.7970581054688</v>
       </c>
       <c r="C51">
-        <v>117.9390157535422</v>
+        <v>117.9389898380853</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -4270,10 +4433,10 @@
         <v>45020</v>
       </c>
       <c r="B52">
-        <v>163.2647399902344</v>
+        <v>163.2647705078125</v>
       </c>
       <c r="C52">
-        <v>117.5557300260409</v>
+        <v>117.5557261684136</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -4281,10 +4444,10 @@
         <v>45021</v>
       </c>
       <c r="B53">
-        <v>161.4214935302734</v>
+        <v>161.4214477539062</v>
       </c>
       <c r="C53">
-        <v>116.228534801698</v>
+        <v>116.2284763016836</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -4292,10 +4455,10 @@
         <v>45022</v>
       </c>
       <c r="B54">
-        <v>162.3086242675781</v>
+        <v>162.3086090087891</v>
       </c>
       <c r="C54">
-        <v>116.8672967380391</v>
+        <v>116.8672600712736</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -4303,10 +4466,10 @@
         <v>45026</v>
       </c>
       <c r="B55">
-        <v>159.7161560058594</v>
+        <v>159.7161865234375</v>
       </c>
       <c r="C55">
-        <v>115.0006383334509</v>
+        <v>115.0006350372694</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -4317,7 +4480,7 @@
         <v>158.5037536621094</v>
       </c>
       <c r="C56">
-        <v>114.1276706454287</v>
+        <v>114.1276455674618</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -4325,10 +4488,10 @@
         <v>45028</v>
       </c>
       <c r="B57">
-        <v>157.8137359619141</v>
+        <v>157.8137512207031</v>
       </c>
       <c r="C57">
-        <v>113.6308362739521</v>
+        <v>113.6308222919616</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -4336,10 +4499,10 @@
         <v>45029</v>
       </c>
       <c r="B58">
-        <v>163.1957550048828</v>
+        <v>163.1957702636719</v>
       </c>
       <c r="C58">
-        <v>117.5060586743803</v>
+        <v>117.5060438408636</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -4347,10 +4510,10 @@
         <v>45030</v>
       </c>
       <c r="B59">
-        <v>162.8507690429688</v>
+        <v>162.8507843017578</v>
       </c>
       <c r="C59">
-        <v>117.2576579688515</v>
+        <v>117.2576431899174</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -4361,7 +4524,7 @@
         <v>162.8704681396484</v>
       </c>
       <c r="C60">
-        <v>117.2718419358929</v>
+        <v>117.2718161670381</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -4372,7 +4535,7 @@
         <v>164.0927734375</v>
       </c>
       <c r="C61">
-        <v>118.151940061258</v>
+        <v>118.151914099014</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -4380,10 +4543,10 @@
         <v>45035</v>
       </c>
       <c r="B62">
-        <v>165.2361907958984</v>
+        <v>165.2362213134766</v>
       </c>
       <c r="C62">
-        <v>118.9752363976196</v>
+        <v>118.9752322280755</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -4391,10 +4554,10 @@
         <v>45036</v>
       </c>
       <c r="B63">
-        <v>164.2701873779297</v>
+        <v>164.2702178955078</v>
       </c>
       <c r="C63">
-        <v>118.2796836590811</v>
+        <v>118.2796796423751</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -4402,10 +4565,10 @@
         <v>45037</v>
       </c>
       <c r="B64">
-        <v>162.6634674072266</v>
+        <v>162.6634979248047</v>
       </c>
       <c r="C64">
-        <v>117.1227949204918</v>
+        <v>117.1227911579959</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -4413,10 +4576,10 @@
         <v>45040</v>
       </c>
       <c r="B65">
-        <v>162.9690399169922</v>
+        <v>162.9690551757812</v>
       </c>
       <c r="C65">
-        <v>117.3428167051315</v>
+        <v>117.342801907485</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -4424,10 +4587,10 @@
         <v>45041</v>
       </c>
       <c r="B66">
-        <v>161.4313201904297</v>
+        <v>161.4313354492188</v>
       </c>
       <c r="C66">
-        <v>116.2356103050091</v>
+        <v>116.2355957506558</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -4435,10 +4598,10 @@
         <v>45042</v>
       </c>
       <c r="B67">
-        <v>161.4214935302734</v>
+        <v>161.4214477539062</v>
       </c>
       <c r="C67">
-        <v>116.228534801698</v>
+        <v>116.2284763016836</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -4449,7 +4612,7 @@
         <v>166.0050506591797</v>
       </c>
       <c r="C68">
-        <v>119.5288395976807</v>
+        <v>119.5288133328822</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -4457,10 +4620,10 @@
         <v>45044</v>
       </c>
       <c r="B69">
-        <v>167.2569122314453</v>
+        <v>167.2569274902344</v>
       </c>
       <c r="C69">
-        <v>120.4302191670111</v>
+        <v>120.4302036909509</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -4468,10 +4631,10 @@
         <v>45047</v>
       </c>
       <c r="B70">
-        <v>167.1682281494141</v>
+        <v>167.1681823730469</v>
       </c>
       <c r="C70">
-        <v>120.3663638483091</v>
+        <v>120.3663044390643</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -4479,10 +4642,10 @@
         <v>45048</v>
       </c>
       <c r="B71">
-        <v>166.1332092285156</v>
+        <v>166.1331939697266</v>
       </c>
       <c r="C71">
-        <v>119.6211177844973</v>
+        <v>119.6210805126179</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -4493,7 +4656,7 @@
         <v>165.0587768554688</v>
       </c>
       <c r="C72">
-        <v>118.8474927997964</v>
+        <v>118.8474666847143</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -4501,10 +4664,10 @@
         <v>45050</v>
       </c>
       <c r="B73">
-        <v>163.4224700927734</v>
+        <v>163.4224395751953</v>
       </c>
       <c r="C73">
-        <v>117.6693006436291</v>
+        <v>117.6692528138304</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -4515,7 +4678,7 @@
         <v>171.0914001464844</v>
       </c>
       <c r="C74">
-        <v>123.1911706508123</v>
+        <v>123.1911435812674</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -4523,10 +4686,10 @@
         <v>45054</v>
       </c>
       <c r="B75">
-        <v>171.0223846435547</v>
+        <v>171.0223693847656</v>
       </c>
       <c r="C75">
-        <v>123.1414773255389</v>
+        <v>123.1414392801095</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -4534,10 +4697,10 @@
         <v>45055</v>
       </c>
       <c r="B76">
-        <v>169.3170623779297</v>
+        <v>169.3170928955078</v>
       </c>
       <c r="C76">
-        <v>121.9135918440981</v>
+        <v>121.9135870288913</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -4545,10 +4708,10 @@
         <v>45056</v>
       </c>
       <c r="B77">
-        <v>171.08154296875</v>
+        <v>171.0815277099609</v>
       </c>
       <c r="C77">
-        <v>123.1840731738884</v>
+        <v>123.1840351190991</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -4559,7 +4722,7 @@
         <v>171.268798828125</v>
       </c>
       <c r="C78">
-        <v>123.318903261829</v>
+        <v>123.3188761642167</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -4567,10 +4730,10 @@
         <v>45058</v>
       </c>
       <c r="B79">
-        <v>170.3409118652344</v>
+        <v>170.3409423828125</v>
       </c>
       <c r="C79">
-        <v>122.6507955656371</v>
+        <v>122.65079058844</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -4581,7 +4744,7 @@
         <v>169.847412109375</v>
       </c>
       <c r="C80">
-        <v>122.2954602735759</v>
+        <v>122.2954334008509</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -4592,7 +4755,7 @@
         <v>169.847412109375</v>
       </c>
       <c r="C81">
-        <v>122.2954602735759</v>
+        <v>122.2954334008509</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -4600,10 +4763,10 @@
         <v>45063</v>
       </c>
       <c r="B82">
-        <v>170.4593963623047</v>
+        <v>170.4594268798828</v>
       </c>
       <c r="C82">
-        <v>122.7361081172064</v>
+        <v>122.7361031212631</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -4611,10 +4774,10 @@
         <v>45064</v>
       </c>
       <c r="B83">
-        <v>172.7889251708984</v>
+        <v>172.7889099121094</v>
       </c>
       <c r="C83">
-        <v>124.413441874191</v>
+        <v>124.413403549265</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -4622,10 +4785,10 @@
         <v>45065</v>
       </c>
       <c r="B84">
-        <v>172.8975219726562</v>
+        <v>172.8974914550781</v>
       </c>
       <c r="C84">
-        <v>124.4916349752237</v>
+        <v>124.4915856463119</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -4633,10 +4796,10 @@
         <v>45068</v>
       </c>
       <c r="B85">
-        <v>171.9498901367188</v>
+        <v>171.9499053955078</v>
       </c>
       <c r="C85">
-        <v>123.8093103515712</v>
+        <v>123.8092941330027</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -4647,7 +4810,7 @@
         <v>169.3439788818359</v>
       </c>
       <c r="C86">
-        <v>121.9329725705589</v>
+        <v>121.9329457774856</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -4658,7 +4821,7 @@
         <v>169.6203765869141</v>
       </c>
       <c r="C87">
-        <v>122.131987581393</v>
+        <v>122.1319607445889</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -4666,10 +4829,10 @@
         <v>45071</v>
       </c>
       <c r="B88">
-        <v>170.7555389404297</v>
+        <v>170.7555236816406</v>
       </c>
       <c r="C88">
-        <v>122.949340055501</v>
+        <v>122.949302052291</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -4677,10 +4840,10 @@
         <v>45072</v>
       </c>
       <c r="B89">
-        <v>173.1640014648438</v>
+        <v>173.1639709472656</v>
       </c>
       <c r="C89">
-        <v>124.6835085619084</v>
+        <v>124.6834591908351</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -4691,7 +4854,7 @@
         <v>175.0098571777344</v>
       </c>
       <c r="C90">
-        <v>126.0125825301429</v>
+        <v>126.012554840632</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -4702,7 +4865,7 @@
         <v>174.9604949951172</v>
       </c>
       <c r="C91">
-        <v>125.9770402114916</v>
+        <v>125.9770125297907</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -4710,10 +4873,10 @@
         <v>45078</v>
       </c>
       <c r="B92">
-        <v>177.7638549804688</v>
+        <v>177.7638244628906</v>
       </c>
       <c r="C92">
-        <v>127.9955472671088</v>
+        <v>127.9954971682612</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -4724,7 +4887,7 @@
         <v>178.6127014160156</v>
       </c>
       <c r="C93">
-        <v>128.6067433062333</v>
+        <v>128.6067150466917</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -4732,10 +4895,10 @@
         <v>45082</v>
       </c>
       <c r="B94">
-        <v>177.2603759765625</v>
+        <v>177.2604064941406</v>
       </c>
       <c r="C94">
-        <v>127.6330266036727</v>
+        <v>127.6330205316998</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -4743,10 +4906,10 @@
         <v>45083</v>
       </c>
       <c r="B95">
-        <v>176.8952178955078</v>
+        <v>176.8952026367188</v>
       </c>
       <c r="C95">
-        <v>127.3701013401047</v>
+        <v>127.3700623654941</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -4757,7 +4920,7 @@
         <v>175.5231323242188</v>
       </c>
       <c r="C96">
-        <v>126.3821567232773</v>
+        <v>126.3821289525577</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -4768,7 +4931,7 @@
         <v>178.2376098632812</v>
       </c>
       <c r="C97">
-        <v>128.3366656317095</v>
+        <v>128.3366374315138</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -4779,7 +4942,7 @@
         <v>178.6225738525391</v>
       </c>
       <c r="C98">
-        <v>128.6138517699635</v>
+        <v>128.61382350886</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -4790,7 +4953,7 @@
         <v>181.4160308837891</v>
       </c>
       <c r="C99">
-        <v>130.6252283882377</v>
+        <v>130.6251996851622</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -4798,10 +4961,10 @@
         <v>45090</v>
       </c>
       <c r="B100">
-        <v>180.9422149658203</v>
+        <v>180.9422302246094</v>
       </c>
       <c r="C100">
-        <v>130.2840660764115</v>
+        <v>130.2840484351056</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -4812,7 +4975,7 @@
         <v>181.5739440917969</v>
       </c>
       <c r="C101">
-        <v>130.7389308475025</v>
+        <v>130.7389021194424</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -4823,7 +4986,7 @@
         <v>183.6073455810547</v>
       </c>
       <c r="C102">
-        <v>132.2030436529989</v>
+        <v>132.2030146032204</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -4831,10 +4994,10 @@
         <v>45093</v>
       </c>
       <c r="B103">
-        <v>182.5314483642578</v>
+        <v>182.5314331054688</v>
       </c>
       <c r="C103">
-        <v>131.4283639348851</v>
+        <v>131.4283240685278</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -4845,7 +5008,7 @@
         <v>182.6202392578125</v>
       </c>
       <c r="C104">
-        <v>131.4922961612318</v>
+        <v>131.4922672676302</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -4853,10 +5016,10 @@
         <v>45098</v>
       </c>
       <c r="B105">
-        <v>181.5838165283203</v>
+        <v>181.5838470458984</v>
       </c>
       <c r="C105">
-        <v>130.7460393112327</v>
+        <v>130.7460325552186</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -4864,10 +5027,10 @@
         <v>45099</v>
       </c>
       <c r="B106">
-        <v>184.5845642089844</v>
+        <v>184.5845489501953</v>
       </c>
       <c r="C106">
-        <v>132.9066716942293</v>
+        <v>132.9066315030343</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -4878,7 +5041,7 @@
         <v>184.2686920166016</v>
       </c>
       <c r="C107">
-        <v>132.6792338152806</v>
+        <v>132.6792046608659</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -4886,10 +5049,10 @@
         <v>45103</v>
       </c>
       <c r="B108">
-        <v>182.8768920898438</v>
+        <v>182.8769073486328</v>
       </c>
       <c r="C108">
-        <v>131.6770942446054</v>
+        <v>131.677076297201</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -4897,10 +5060,10 @@
         <v>45104</v>
       </c>
       <c r="B109">
-        <v>185.6308898925781</v>
+        <v>185.630859375</v>
       </c>
       <c r="C109">
-        <v>133.6600589815714</v>
+        <v>133.6600076380261</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -4911,7 +5074,7 @@
         <v>186.8054962158203</v>
       </c>
       <c r="C110">
-        <v>134.5058123501811</v>
+        <v>134.5057827944013</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -4919,10 +5082,10 @@
         <v>45106</v>
       </c>
       <c r="B111">
-        <v>187.14111328125</v>
+        <v>187.1410980224609</v>
       </c>
       <c r="C111">
-        <v>134.7474671565903</v>
+        <v>134.7474265609062</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -4930,10 +5093,10 @@
         <v>45107</v>
       </c>
       <c r="B112">
-        <v>191.4645080566406</v>
+        <v>191.4645233154297</v>
       </c>
       <c r="C112">
-        <v>137.8604469037312</v>
+        <v>137.8604275976211</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -4941,10 +5104,10 @@
         <v>45110</v>
       </c>
       <c r="B113">
-        <v>189.9740600585938</v>
+        <v>189.9740295410156</v>
       </c>
       <c r="C113">
-        <v>136.7872776297855</v>
+        <v>136.7872255990775</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -4952,10 +5115,10 @@
         <v>45112</v>
       </c>
       <c r="B114">
-        <v>188.858642578125</v>
+        <v>188.8586120605469</v>
       </c>
       <c r="C114">
-        <v>135.984142083138</v>
+        <v>135.9840902289079</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -4963,10 +5126,10 @@
         <v>45113</v>
       </c>
       <c r="B115">
-        <v>189.3324432373047</v>
+        <v>189.3324279785156</v>
       </c>
       <c r="C115">
-        <v>136.3252934081579</v>
+        <v>136.3252524657684</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -4974,10 +5137,10 @@
         <v>45114</v>
       </c>
       <c r="B116">
-        <v>188.2170257568359</v>
+        <v>188.2170104980469</v>
       </c>
       <c r="C116">
-        <v>135.5221578615104</v>
+        <v>135.5221170955988</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -4988,7 +5151,7 @@
         <v>186.1737670898438</v>
       </c>
       <c r="C117">
-        <v>134.0509475790902</v>
+        <v>134.0509181232605</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -4999,7 +5162,7 @@
         <v>185.6506195068359</v>
       </c>
       <c r="C118">
-        <v>133.6742649222255</v>
+        <v>133.6742355491666</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -5007,10 +5170,10 @@
         <v>45119</v>
       </c>
       <c r="B119">
-        <v>187.3187866210938</v>
+        <v>187.3187713623047</v>
       </c>
       <c r="C119">
-        <v>134.875397530122</v>
+        <v>134.8753569063269</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -5018,10 +5181,10 @@
         <v>45120</v>
       </c>
       <c r="B120">
-        <v>188.0788269042969</v>
+        <v>188.0788421630859</v>
       </c>
       <c r="C120">
-        <v>135.4226503560934</v>
+        <v>135.4226315856551</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -5029,10 +5192,10 @@
         <v>45121</v>
       </c>
       <c r="B121">
-        <v>188.2269134521484</v>
+        <v>188.2268829345703</v>
       </c>
       <c r="C121">
-        <v>135.529277312047</v>
+        <v>135.5292255577671</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -5040,10 +5203,10 @@
         <v>45124</v>
       </c>
       <c r="B122">
-        <v>191.4842834472656</v>
+        <v>191.4842681884766</v>
       </c>
       <c r="C122">
-        <v>137.8746858048044</v>
+        <v>137.8746445219576</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -5051,10 +5214,10 @@
         <v>45125</v>
       </c>
       <c r="B123">
-        <v>191.2276306152344</v>
+        <v>191.2276458740234</v>
       </c>
       <c r="C123">
-        <v>137.6898877214308</v>
+        <v>137.6898684527987</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -5062,10 +5225,10 @@
         <v>45126</v>
       </c>
       <c r="B124">
-        <v>192.5799407958984</v>
+        <v>192.5799560546875</v>
       </c>
       <c r="C124">
-        <v>138.663593437185</v>
+        <v>138.6635739545946</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -5076,7 +5239,7 @@
         <v>190.6353759765625</v>
       </c>
       <c r="C125">
-        <v>137.2634458184544</v>
+        <v>137.263415656723</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -5084,10 +5247,10 @@
         <v>45128</v>
       </c>
       <c r="B126">
-        <v>189.4607543945312</v>
+        <v>189.4607391357422</v>
       </c>
       <c r="C126">
-        <v>136.4176814630383</v>
+        <v>136.4176405003478</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -5095,10 +5258,10 @@
         <v>45131</v>
       </c>
       <c r="B127">
-        <v>190.2602844238281</v>
+        <v>190.2602691650391</v>
       </c>
       <c r="C127">
-        <v>136.9933681439307</v>
+        <v>136.9933270547411</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -5106,10 +5269,10 @@
         <v>45132</v>
       </c>
       <c r="B128">
-        <v>191.1190185546875</v>
+        <v>191.1190490722656</v>
       </c>
       <c r="C128">
-        <v>137.6116836335918</v>
+        <v>137.6116753689479</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -5120,7 +5283,7 @@
         <v>191.9876861572266</v>
       </c>
       <c r="C129">
-        <v>138.2371515342086</v>
+        <v>138.2371211585189</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -5128,10 +5291,10 @@
         <v>45134</v>
       </c>
       <c r="B130">
-        <v>190.7242126464844</v>
+        <v>190.7242279052734</v>
       </c>
       <c r="C130">
-        <v>137.3274110052203</v>
+        <v>137.3273918162373</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -5139,10 +5302,10 @@
         <v>45135</v>
       </c>
       <c r="B131">
-        <v>193.3005218505859</v>
+        <v>193.3005065917969</v>
       </c>
       <c r="C131">
-        <v>139.1824343818482</v>
+        <v>139.1823928116418</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -5150,10 +5313,10 @@
         <v>45138</v>
       </c>
       <c r="B132">
-        <v>193.9124908447266</v>
+        <v>193.9125061035156</v>
       </c>
       <c r="C132">
-        <v>139.6230712386723</v>
+        <v>139.62305154525</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -5164,7 +5327,7 @@
         <v>193.0833435058594</v>
       </c>
       <c r="C133">
-        <v>139.0260591665892</v>
+        <v>139.026028617548</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -5172,10 +5335,10 @@
         <v>45140</v>
       </c>
       <c r="B134">
-        <v>190.0924987792969</v>
+        <v>190.0925140380859</v>
       </c>
       <c r="C134">
-        <v>136.8725572209357</v>
+        <v>136.8725381319005</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -5186,7 +5349,7 @@
         <v>188.70068359375</v>
       </c>
       <c r="C135">
-        <v>135.8704066634541</v>
+        <v>135.8703768078236</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -5197,7 +5360,7 @@
         <v>179.6392822265625</v>
       </c>
       <c r="C136">
-        <v>129.3459136661149</v>
+        <v>129.345885244151</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -5205,10 +5368,10 @@
         <v>45145</v>
       </c>
       <c r="B137">
-        <v>176.5398559570312</v>
+        <v>176.5398406982422</v>
       </c>
       <c r="C137">
-        <v>127.1142296062351</v>
+        <v>127.1141906878486</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -5216,10 +5379,10 @@
         <v>45146</v>
       </c>
       <c r="B138">
-        <v>177.4775085449219</v>
+        <v>177.4775543212891</v>
       </c>
       <c r="C138">
-        <v>127.7893688585126</v>
+        <v>127.7893737389896</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -5227,10 +5390,10 @@
         <v>45147</v>
       </c>
       <c r="B139">
-        <v>175.8883666992188</v>
+        <v>175.8883514404297</v>
       </c>
       <c r="C139">
-        <v>126.6451369208772</v>
+        <v>126.6450981055674</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -5238,10 +5401,10 @@
         <v>45148</v>
       </c>
       <c r="B140">
-        <v>175.6712341308594</v>
+        <v>175.6712188720703</v>
       </c>
       <c r="C140">
-        <v>126.4887946660374</v>
+        <v>126.4887558850815</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -5252,7 +5415,7 @@
         <v>175.7305145263672</v>
       </c>
       <c r="C141">
-        <v>126.531478408838</v>
+        <v>126.531450605307</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -5260,10 +5423,10 @@
         <v>45152</v>
       </c>
       <c r="B142">
-        <v>177.3811645507812</v>
+        <v>177.3811798095703</v>
       </c>
       <c r="C142">
-        <v>127.719998163006</v>
+        <v>127.7199810851183</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -5271,10 +5434,10 @@
         <v>45153</v>
       </c>
       <c r="B143">
-        <v>175.3944549560547</v>
+        <v>175.3944396972656</v>
       </c>
       <c r="C143">
-        <v>126.2895049850436</v>
+        <v>126.289466247879</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -5282,10 +5445,10 @@
         <v>45154</v>
       </c>
       <c r="B144">
-        <v>174.5246429443359</v>
+        <v>174.524658203125</v>
       </c>
       <c r="C144">
-        <v>125.663213073948</v>
+        <v>125.6631964480102</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -5293,10 +5456,10 @@
         <v>45155</v>
       </c>
       <c r="B145">
-        <v>171.9844055175781</v>
+        <v>171.9844207763672</v>
       </c>
       <c r="C145">
-        <v>123.8341625076111</v>
+        <v>123.8341462835817</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -5304,10 +5467,10 @@
         <v>45156</v>
       </c>
       <c r="B146">
-        <v>172.4687347412109</v>
+        <v>172.46875</v>
       </c>
       <c r="C146">
-        <v>124.1828947290357</v>
+        <v>124.1828784283773</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -5315,10 +5478,10 @@
         <v>45159</v>
       </c>
       <c r="B147">
-        <v>173.8030700683594</v>
+        <v>173.8031005859375</v>
       </c>
       <c r="C147">
-        <v>125.1436579868699</v>
+        <v>125.1436524619011</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -5326,10 +5489,10 @@
         <v>45160</v>
       </c>
       <c r="B148">
-        <v>175.1769866943359</v>
+        <v>175.1770172119141</v>
       </c>
       <c r="C148">
-        <v>126.1329210204634</v>
+        <v>126.1329152781178</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -5337,10 +5500,10 @@
         <v>45161</v>
       </c>
       <c r="B149">
-        <v>179.0219421386719</v>
+        <v>179.0219268798828</v>
       </c>
       <c r="C149">
-        <v>128.9014094534437</v>
+        <v>128.9013701423494</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -5348,10 +5511,10 @@
         <v>45162</v>
       </c>
       <c r="B150">
-        <v>174.3368377685547</v>
+        <v>174.3368530273438</v>
       </c>
       <c r="C150">
-        <v>125.5279874609776</v>
+        <v>125.5279708647538</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -5359,10 +5522,10 @@
         <v>45163</v>
       </c>
       <c r="B151">
-        <v>176.541015625</v>
+        <v>176.5410003662109</v>
       </c>
       <c r="C151">
-        <v>127.1150646035202</v>
+        <v>127.1150256849503</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -5370,10 +5533,10 @@
         <v>45166</v>
       </c>
       <c r="B152">
-        <v>178.1027221679688</v>
+        <v>178.1026916503906</v>
       </c>
       <c r="C152">
-        <v>128.2395422632777</v>
+        <v>128.2394921108155</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -5384,7 +5547,7 @@
         <v>181.9871673583984</v>
       </c>
       <c r="C153">
-        <v>131.0364645511791</v>
+        <v>131.0364357577401</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -5392,10 +5555,10 @@
         <v>45168</v>
       </c>
       <c r="B154">
-        <v>185.4762878417969</v>
+        <v>185.4762725830078</v>
       </c>
       <c r="C154">
-        <v>133.5487406592919</v>
+        <v>133.5487003270112</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -5403,10 +5566,10 @@
         <v>45169</v>
       </c>
       <c r="B155">
-        <v>185.6937255859375</v>
+        <v>185.6937408447266</v>
       </c>
       <c r="C155">
-        <v>133.7053026502594</v>
+        <v>133.7052842571844</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -5414,10 +5577,10 @@
         <v>45170</v>
       </c>
       <c r="B156">
-        <v>187.2653045654297</v>
+        <v>187.2653198242188</v>
       </c>
       <c r="C156">
-        <v>134.8368887737471</v>
+        <v>134.8368701320218</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -5425,10 +5588,10 @@
         <v>45174</v>
       </c>
       <c r="B157">
-        <v>187.5025634765625</v>
+        <v>187.5025329589844</v>
       </c>
       <c r="C157">
-        <v>135.0077226262071</v>
+        <v>135.0076709865315</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -5436,10 +5599,10 @@
         <v>45175</v>
       </c>
       <c r="B158">
-        <v>180.7912139892578</v>
+        <v>180.7911834716797</v>
       </c>
       <c r="C158">
-        <v>130.1753406404385</v>
+        <v>130.1752900626116</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -5447,10 +5610,10 @@
         <v>45176</v>
       </c>
       <c r="B159">
-        <v>175.503173828125</v>
+        <v>175.5031585693359</v>
       </c>
       <c r="C159">
-        <v>126.3677859805274</v>
+        <v>126.3677472261616</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -5458,10 +5621,10 @@
         <v>45177</v>
       </c>
       <c r="B160">
-        <v>176.1159820556641</v>
+        <v>176.115966796875</v>
       </c>
       <c r="C160">
-        <v>126.8090271117026</v>
+        <v>126.8089882603802</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -5472,7 +5635,7 @@
         <v>177.2823181152344</v>
       </c>
       <c r="C161">
-        <v>127.6488256312525</v>
+        <v>127.6487975822</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -5480,10 +5643,10 @@
         <v>45181</v>
       </c>
       <c r="B162">
-        <v>174.2577667236328</v>
+        <v>174.2577514648438</v>
       </c>
       <c r="C162">
-        <v>125.4710538302974</v>
+        <v>125.4710152729759</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -5491,10 +5654,10 @@
         <v>45182</v>
       </c>
       <c r="B163">
-        <v>172.1919708251953</v>
+        <v>172.1920013427734</v>
       </c>
       <c r="C163">
-        <v>123.9836160348484</v>
+        <v>123.9836107647826</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -5502,10 +5665,10 @@
         <v>45183</v>
       </c>
       <c r="B164">
-        <v>173.7042541503906</v>
+        <v>173.7042388916016</v>
       </c>
       <c r="C164">
-        <v>125.0725074287291</v>
+        <v>125.0724689589827</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -5513,10 +5676,10 @@
         <v>45184</v>
       </c>
       <c r="B165">
-        <v>172.9827117919922</v>
+        <v>172.9826965332031</v>
       </c>
       <c r="C165">
-        <v>124.5529743152638</v>
+        <v>124.5529359596776</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -5524,10 +5687,10 @@
         <v>45187</v>
       </c>
       <c r="B166">
-        <v>175.9084320068359</v>
+        <v>175.9084167480469</v>
       </c>
       <c r="C166">
-        <v>126.6595845712717</v>
+        <v>126.6595457527872</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -5538,7 +5701,7 @@
         <v>176.9956817626953</v>
       </c>
       <c r="C167">
-        <v>127.4424384733349</v>
+        <v>127.4424104696331</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -5549,7 +5712,7 @@
         <v>173.4571380615234</v>
       </c>
       <c r="C168">
-        <v>124.8945760993453</v>
+        <v>124.8945486555008</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -5557,10 +5720,10 @@
         <v>45190</v>
       </c>
       <c r="B169">
-        <v>171.9151916503906</v>
+        <v>171.9152069091797</v>
       </c>
       <c r="C169">
-        <v>123.7843263538547</v>
+        <v>123.7843101407761</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -5568,10 +5731,10 @@
         <v>45191</v>
       </c>
       <c r="B170">
-        <v>172.7652282714844</v>
+        <v>172.7652587890625</v>
       </c>
       <c r="C170">
-        <v>124.3963793638771</v>
+        <v>124.3963740031123</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -5582,7 +5745,7 @@
         <v>174.0403137207031</v>
       </c>
       <c r="C171">
-        <v>125.3144808525234</v>
+        <v>125.3144533164107</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -5590,10 +5753,10 @@
         <v>45195</v>
       </c>
       <c r="B172">
-        <v>169.9680480957031</v>
+        <v>169.9680633544922</v>
       </c>
       <c r="C172">
-        <v>122.3823219648453</v>
+        <v>122.3823060598376</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -5601,10 +5764,10 @@
         <v>45196</v>
       </c>
       <c r="B173">
-        <v>168.4557495117188</v>
+        <v>168.4557647705078</v>
       </c>
       <c r="C173">
-        <v>121.2934195841582</v>
+        <v>121.2934039184217</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -5612,10 +5775,10 @@
         <v>45197</v>
       </c>
       <c r="B174">
-        <v>168.7127532958984</v>
+        <v>168.7127380371094</v>
       </c>
       <c r="C174">
-        <v>121.4784703640786</v>
+        <v>121.4784326840718</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -5623,10 +5786,10 @@
         <v>45198</v>
       </c>
       <c r="B175">
-        <v>169.2267456054688</v>
+        <v>169.2267303466797</v>
       </c>
       <c r="C175">
-        <v>121.848560937113</v>
+        <v>121.848523175784</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -5637,7 +5800,7 @@
         <v>171.7373046875</v>
       </c>
       <c r="C176">
-        <v>123.6562421650337</v>
+        <v>123.6562149932958</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -5645,10 +5808,10 @@
         <v>45202</v>
       </c>
       <c r="B177">
-        <v>170.4029235839844</v>
+        <v>170.4029388427734</v>
       </c>
       <c r="C177">
-        <v>122.6954459467804</v>
+        <v>122.6954299729681</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -5656,10 +5819,10 @@
         <v>45203</v>
       </c>
       <c r="B178">
-        <v>171.6483459472656</v>
+        <v>171.6483612060547</v>
       </c>
       <c r="C178">
-        <v>123.5921890838168</v>
+        <v>123.5921729129577</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -5667,10 +5830,10 @@
         <v>45204</v>
       </c>
       <c r="B179">
-        <v>172.8838653564453</v>
+        <v>172.8838806152344</v>
       </c>
       <c r="C179">
-        <v>124.4818017835102</v>
+        <v>124.4817854171711</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -5681,7 +5844,7 @@
         <v>175.4339904785156</v>
       </c>
       <c r="C180">
-        <v>126.3179718003838</v>
+        <v>126.3179440437679</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -5689,10 +5852,10 @@
         <v>45208</v>
       </c>
       <c r="B181">
-        <v>176.9166259765625</v>
+        <v>176.9166107177734</v>
       </c>
       <c r="C181">
-        <v>127.385515829461</v>
+        <v>127.3854768514632</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -5703,7 +5866,7 @@
         <v>176.3235473632812</v>
       </c>
       <c r="C182">
-        <v>126.9584806389399</v>
+        <v>126.9584527415812</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -5711,10 +5874,10 @@
         <v>45210</v>
       </c>
       <c r="B183">
-        <v>177.7171936035156</v>
+        <v>177.7172241210938</v>
       </c>
       <c r="C183">
-        <v>127.9619496131875</v>
+        <v>127.9619434689383</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -5722,10 +5885,10 @@
         <v>45211</v>
       </c>
       <c r="B184">
-        <v>178.6167144775391</v>
+        <v>178.6166687011719</v>
       </c>
       <c r="C184">
-        <v>128.6096328363122</v>
+        <v>128.6095716157238</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -5733,10 +5896,10 @@
         <v>45212</v>
       </c>
       <c r="B185">
-        <v>176.7782592773438</v>
+        <v>176.7782440185547</v>
       </c>
       <c r="C185">
-        <v>127.2858874691738</v>
+        <v>127.2858485130679</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -5744,10 +5907,10 @@
         <v>45215</v>
       </c>
       <c r="B186">
-        <v>176.6497497558594</v>
+        <v>176.6497344970703</v>
       </c>
       <c r="C186">
-        <v>127.1933565858104</v>
+        <v>127.1933176500369</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -5755,10 +5918,10 @@
         <v>45216</v>
       </c>
       <c r="B187">
-        <v>175.097900390625</v>
+        <v>175.0979309082031</v>
       </c>
       <c r="C187">
-        <v>126.0759764029767</v>
+        <v>126.0759706731439</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -5766,10 +5929,10 @@
         <v>45217</v>
       </c>
       <c r="B188">
-        <v>173.8030700683594</v>
+        <v>173.8031005859375</v>
       </c>
       <c r="C188">
-        <v>125.1436579868699</v>
+        <v>125.1436524619011</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -5777,10 +5940,10 @@
         <v>45218</v>
       </c>
       <c r="B189">
-        <v>173.4275054931641</v>
+        <v>173.427490234375</v>
       </c>
       <c r="C189">
-        <v>124.8732397213482</v>
+        <v>124.8732012953881</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -5788,10 +5951,10 @@
         <v>45219</v>
       </c>
       <c r="B190">
-        <v>170.8773956298828</v>
+        <v>170.8773803710938</v>
       </c>
       <c r="C190">
-        <v>123.0370806912811</v>
+        <v>123.0370426687914</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -5802,7 +5965,7 @@
         <v>170.9959869384766</v>
       </c>
       <c r="C191">
-        <v>123.1224701504951</v>
+        <v>123.1224430960462</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -5810,10 +5973,10 @@
         <v>45223</v>
       </c>
       <c r="B192">
-        <v>171.4308776855469</v>
+        <v>171.430908203125</v>
       </c>
       <c r="C192">
-        <v>123.4356051192365</v>
+        <v>123.4355999695885</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -5824,7 +5987,7 @@
         <v>169.1179962158203</v>
       </c>
       <c r="C193">
-        <v>121.7702579680165</v>
+        <v>121.7702312106975</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -5832,10 +5995,10 @@
         <v>45225</v>
       </c>
       <c r="B194">
-        <v>164.9567718505859</v>
+        <v>164.9567565917969</v>
       </c>
       <c r="C194">
-        <v>118.7740459991215</v>
+        <v>118.7740089133743</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -5843,10 +6006,10 @@
         <v>45226</v>
       </c>
       <c r="B195">
-        <v>166.2713623046875</v>
+        <v>166.2713470458984</v>
       </c>
       <c r="C195">
-        <v>119.7205923294952</v>
+        <v>119.7205550357576</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -5854,10 +6017,10 @@
         <v>45229</v>
       </c>
       <c r="B196">
-        <v>168.3173980712891</v>
+        <v>168.3173675537109</v>
       </c>
       <c r="C196">
-        <v>121.1938022106773</v>
+        <v>121.1937536064184</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -5865,10 +6028,10 @@
         <v>45230</v>
       </c>
       <c r="B197">
-        <v>168.7918090820312</v>
+        <v>168.7918243408203</v>
       </c>
       <c r="C197">
-        <v>121.5353930079525</v>
+        <v>121.5353772890457</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -5879,7 +6042,7 @@
         <v>171.9547424316406</v>
       </c>
       <c r="C198">
-        <v>123.8128041560012</v>
+        <v>123.8127769498611</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -5890,7 +6053,7 @@
         <v>175.5130615234375</v>
       </c>
       <c r="C199">
-        <v>126.3749054310641</v>
+        <v>126.3748776619378</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -5901,7 +6064,7 @@
         <v>174.6036987304688</v>
       </c>
       <c r="C200">
-        <v>125.7201357178219</v>
+        <v>125.7201080925722</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -5909,10 +6072,10 @@
         <v>45236</v>
       </c>
       <c r="B201">
-        <v>177.1537780761719</v>
+        <v>177.15380859375</v>
       </c>
       <c r="C201">
-        <v>127.5562727742763</v>
+        <v>127.5562667191689</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -5923,7 +6086,7 @@
         <v>179.7138061523438</v>
       </c>
       <c r="C202">
-        <v>129.3995732284928</v>
+        <v>129.3995447947379</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -5931,10 +6094,10 @@
         <v>45238</v>
       </c>
       <c r="B203">
-        <v>180.7714233398438</v>
+        <v>180.7714080810547</v>
       </c>
       <c r="C203">
-        <v>130.1610907525589</v>
+        <v>130.1610511646671</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -5942,10 +6105,10 @@
         <v>45239</v>
       </c>
       <c r="B204">
-        <v>180.2969818115234</v>
+        <v>180.2969970703125</v>
       </c>
       <c r="C204">
-        <v>129.8194779816709</v>
+        <v>129.8194604424518</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -5953,10 +6116,10 @@
         <v>45240</v>
       </c>
       <c r="B205">
-        <v>184.4834899902344</v>
+        <v>184.4834747314453</v>
       </c>
       <c r="C205">
-        <v>132.8338950887437</v>
+        <v>132.8338549135404</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -5967,7 +6130,7 @@
         <v>182.8999481201172</v>
       </c>
       <c r="C206">
-        <v>131.6936953090512</v>
+        <v>131.6936663711949</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -5975,10 +6138,10 @@
         <v>45244</v>
       </c>
       <c r="B207">
-        <v>185.5128021240234</v>
+        <v>185.5127868652344</v>
       </c>
       <c r="C207">
-        <v>133.575032086968</v>
+        <v>133.5749917489102</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -5989,7 +6152,7 @@
         <v>186.0769348144531</v>
       </c>
       <c r="C208">
-        <v>133.9812253057793</v>
+        <v>133.9811958652701</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -5997,10 +6160,10 @@
         <v>45246</v>
       </c>
       <c r="B209">
-        <v>187.7594604492188</v>
+        <v>187.7594909667969</v>
       </c>
       <c r="C209">
-        <v>135.1926964984828</v>
+        <v>135.1926887653777</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -6011,7 +6174,7 @@
         <v>187.7396545410156</v>
       </c>
       <c r="C210">
-        <v>135.1784356237968</v>
+        <v>135.1784059202174</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -6022,7 +6185,7 @@
         <v>189.4815673828125</v>
       </c>
       <c r="C211">
-        <v>136.4326674669456</v>
+        <v>136.4326374877662</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -6030,10 +6193,10 @@
         <v>45251</v>
       </c>
       <c r="B212">
-        <v>188.679931640625</v>
+        <v>188.6798858642578</v>
       </c>
       <c r="C212">
-        <v>135.8554646067723</v>
+        <v>135.8554017940133</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -6041,10 +6204,10 @@
         <v>45252</v>
       </c>
       <c r="B213">
-        <v>189.3430023193359</v>
+        <v>189.343017578125</v>
       </c>
       <c r="C213">
-        <v>136.3328962781754</v>
+        <v>136.3328773077232</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -6052,10 +6215,10 @@
         <v>45254</v>
       </c>
       <c r="B214">
-        <v>188.0167999267578</v>
+        <v>188.0167846679688</v>
       </c>
       <c r="C214">
-        <v>135.3779889881437</v>
+        <v>135.3779482539112</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -6066,7 +6229,7 @@
         <v>187.8386383056641</v>
       </c>
       <c r="C215">
-        <v>135.2497070368078</v>
+        <v>135.2496773175674</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -6074,10 +6237,10 @@
         <v>45258</v>
       </c>
       <c r="B216">
-        <v>188.4423675537109</v>
+        <v>188.4423522949219</v>
       </c>
       <c r="C216">
-        <v>135.6844110181847</v>
+        <v>135.6843702166202</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -6085,10 +6248,10 @@
         <v>45259</v>
       </c>
       <c r="B217">
-        <v>187.4229583740234</v>
+        <v>187.4229431152344</v>
       </c>
       <c r="C217">
-        <v>134.9504044573034</v>
+        <v>134.9503638170266</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -6099,7 +6262,7 @@
         <v>187.9969787597656</v>
       </c>
       <c r="C218">
-        <v>135.3637171266513</v>
+        <v>135.3636873823588</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -6110,7 +6273,7 @@
         <v>189.2737426757812</v>
       </c>
       <c r="C219">
-        <v>136.2830271639999</v>
+        <v>136.2829972177018</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -6121,7 +6284,7 @@
         <v>187.4823303222656</v>
       </c>
       <c r="C220">
-        <v>134.9931541209423</v>
+        <v>134.9931244580759</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -6129,10 +6292,10 @@
         <v>45265</v>
       </c>
       <c r="B221">
-        <v>191.4313049316406</v>
+        <v>191.4313201904297</v>
       </c>
       <c r="C221">
-        <v>137.8365396130403</v>
+        <v>137.8365203121834</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -6140,10 +6303,10 @@
         <v>45266</v>
       </c>
       <c r="B222">
-        <v>190.3426208496094</v>
+        <v>190.3426361083984</v>
       </c>
       <c r="C222">
-        <v>137.0526529511771</v>
+        <v>137.0526338225684</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -6151,10 +6314,10 @@
         <v>45267</v>
       </c>
       <c r="B223">
-        <v>192.2725830078125</v>
+        <v>192.2725982666016</v>
       </c>
       <c r="C223">
-        <v>138.4422861961984</v>
+        <v>138.4422667622372</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -6165,7 +6328,7 @@
         <v>193.6977844238281</v>
       </c>
       <c r="C224">
-        <v>139.4684758860475</v>
+        <v>139.4684452397914</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -6173,10 +6336,10 @@
         <v>45271</v>
       </c>
       <c r="B225">
-        <v>191.1937713623047</v>
+        <v>191.1937866210938</v>
       </c>
       <c r="C225">
-        <v>137.6655079980654</v>
+        <v>137.6654887347904</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -6184,10 +6347,10 @@
         <v>45272</v>
       </c>
       <c r="B226">
-        <v>192.7080383300781</v>
+        <v>192.7080535888672</v>
       </c>
       <c r="C226">
-        <v>138.7558276767761</v>
+        <v>138.7558081739185</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -6195,10 +6358,10 @@
         <v>45273</v>
       </c>
       <c r="B227">
-        <v>195.9246368408203</v>
+        <v>195.9246215820312</v>
       </c>
       <c r="C227">
-        <v>141.0718794228762</v>
+        <v>141.0718374374906</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -6209,7 +6372,7 @@
         <v>196.0731048583984</v>
       </c>
       <c r="C228">
-        <v>141.1787810489895</v>
+        <v>141.1787500269177</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -6220,7 +6383,7 @@
         <v>195.5386505126953</v>
       </c>
       <c r="C229">
-        <v>140.7939571685945</v>
+        <v>140.7939262310824</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -6228,10 +6391,10 @@
         <v>45278</v>
       </c>
       <c r="B230">
-        <v>193.8759307861328</v>
+        <v>193.8758850097656</v>
       </c>
       <c r="C230">
-        <v>139.596746850577</v>
+        <v>139.5966832157233</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -6239,10 +6402,10 @@
         <v>45279</v>
       </c>
       <c r="B231">
-        <v>194.9151306152344</v>
+        <v>194.9151458740234</v>
       </c>
       <c r="C231">
-        <v>140.345003299338</v>
+        <v>140.3449834472812</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -6253,7 +6416,7 @@
         <v>192.8268432617188</v>
       </c>
       <c r="C232">
-        <v>138.8413709512794</v>
+        <v>138.8413404428209</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -6261,10 +6424,10 @@
         <v>45281</v>
       </c>
       <c r="B233">
-        <v>192.6783447265625</v>
+        <v>192.6783599853516</v>
       </c>
       <c r="C233">
-        <v>138.7344473515534</v>
+        <v>138.7344278533938</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -6272,10 +6435,10 @@
         <v>45282</v>
       </c>
       <c r="B234">
-        <v>191.6094818115234</v>
+        <v>191.6094512939453</v>
       </c>
       <c r="C234">
-        <v>137.9648325511826</v>
+        <v>137.9647802617233</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -6283,10 +6446,10 @@
         <v>45286</v>
       </c>
       <c r="B235">
-        <v>191.0651092529297</v>
+        <v>191.0651397705078</v>
       </c>
       <c r="C235">
-        <v>137.5728672466382</v>
+        <v>137.5728589905237</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -6297,7 +6460,7 @@
         <v>191.1640930175781</v>
       </c>
       <c r="C236">
-        <v>137.6441386596492</v>
+        <v>137.6441084142658</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -6305,10 +6468,10 @@
         <v>45288</v>
       </c>
       <c r="B237">
-        <v>191.5896606445312</v>
+        <v>191.5896759033203</v>
       </c>
       <c r="C237">
-        <v>137.9505606896902</v>
+        <v>137.9505413637788</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -6319,7 +6482,7 @@
         <v>190.5504608154297</v>
       </c>
       <c r="C238">
-        <v>137.2023042409292</v>
+        <v>137.2022740926328</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -6330,7 +6493,7 @@
         <v>183.7313079833984</v>
       </c>
       <c r="C239">
-        <v>132.2923004680599</v>
+        <v>132.2922713986685</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -6341,7 +6504,7 @@
         <v>182.3556060791016</v>
       </c>
       <c r="C240">
-        <v>131.3017519781195</v>
+        <v>131.3017231263873</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -6349,10 +6512,10 @@
         <v>45295</v>
       </c>
       <c r="B241">
-        <v>180.0396575927734</v>
+        <v>180.0396728515625</v>
       </c>
       <c r="C241">
-        <v>129.6341964788164</v>
+        <v>129.6341789803103</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -6363,7 +6526,7 @@
         <v>179.3171691894531</v>
       </c>
       <c r="C242">
-        <v>129.1139821833553</v>
+        <v>129.1139538123551</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -6371,10 +6534,10 @@
         <v>45299</v>
       </c>
       <c r="B243">
-        <v>183.6521606445312</v>
+        <v>183.6521301269531</v>
       </c>
       <c r="C243">
-        <v>132.2353119033477</v>
+        <v>132.2352608728708</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -6382,10 +6545,10 @@
         <v>45300</v>
       </c>
       <c r="B244">
-        <v>183.2364501953125</v>
+        <v>183.2364349365234</v>
       </c>
       <c r="C244">
-        <v>131.9359873502306</v>
+        <v>131.93594737233</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -6393,10 +6556,10 @@
         <v>45301</v>
       </c>
       <c r="B245">
-        <v>184.2756500244141</v>
+        <v>184.275634765625</v>
       </c>
       <c r="C245">
-        <v>132.6842437989916</v>
+        <v>132.684203656672</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -6404,10 +6567,10 @@
         <v>45302</v>
       </c>
       <c r="B246">
-        <v>183.6818084716797</v>
+        <v>183.6818389892578</v>
       </c>
       <c r="C246">
-        <v>132.2566592681513</v>
+        <v>132.2566521801994</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -6415,10 +6578,10 @@
         <v>45303</v>
       </c>
       <c r="B247">
-        <v>184.0084228515625</v>
+        <v>184.0084381103516</v>
       </c>
       <c r="C247">
-        <v>132.4918318587941</v>
+        <v>132.4918137323623</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -6426,10 +6589,10 @@
         <v>45307</v>
       </c>
       <c r="B248">
-        <v>181.7419891357422</v>
+        <v>181.7419738769531</v>
       </c>
       <c r="C248">
-        <v>130.859928546206</v>
+        <v>130.8598888047544</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -6437,10 +6600,10 @@
         <v>45308</v>
       </c>
       <c r="B249">
-        <v>180.8017272949219</v>
+        <v>180.8017578125</v>
       </c>
       <c r="C249">
-        <v>130.1829105500369</v>
+        <v>130.1829039177625</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -6448,10 +6611,10 @@
         <v>45309</v>
       </c>
       <c r="B250">
-        <v>186.6905670166016</v>
+        <v>186.6905822753906</v>
       </c>
       <c r="C250">
-        <v>134.4230597244992</v>
+        <v>134.4230411737071</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -6459,10 +6622,10 @@
         <v>45310</v>
       </c>
       <c r="B251">
-        <v>189.5904235839844</v>
+        <v>189.5904541015625</v>
       </c>
       <c r="C251">
-        <v>136.5110473436869</v>
+        <v>136.5110393208925</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -6470,10 +6633,10 @@
         <v>45313</v>
       </c>
       <c r="B252">
-        <v>191.8964691162109</v>
+        <v>191.896484375</v>
       </c>
       <c r="C252">
-        <v>138.171472405647</v>
+        <v>138.1714530311933</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -6484,7 +6647,7 @@
         <v>193.1732177734375</v>
       </c>
       <c r="C253">
-        <v>139.0907714561891</v>
+        <v>139.0907408929283</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -6495,7 +6658,7 @@
         <v>192.5002136230469</v>
       </c>
       <c r="C254">
-        <v>138.6061873738303</v>
+        <v>138.6061569170501</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -6506,7 +6669,7 @@
         <v>192.1735992431641</v>
       </c>
       <c r="C255">
-        <v>138.3710147831875</v>
+        <v>138.3709843780832</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -6514,10 +6677,10 @@
         <v>45317</v>
       </c>
       <c r="B256">
-        <v>190.4415893554688</v>
+        <v>190.4416046142578</v>
       </c>
       <c r="C256">
-        <v>137.1239133773816</v>
+        <v>137.1238942331145</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -6528,7 +6691,7 @@
         <v>189.7586975097656</v>
       </c>
       <c r="C257">
-        <v>136.6322098444861</v>
+        <v>136.63217982146</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -6539,7 +6702,7 @@
         <v>186.1066284179688</v>
       </c>
       <c r="C258">
-        <v>134.002605631002</v>
+        <v>134.0025761857948</v>
       </c>
     </row>
   </sheetData>
@@ -6558,13 +6721,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -9410,13 +9573,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -9424,7 +9587,7 @@
         <v>44949</v>
       </c>
       <c r="B2">
-        <v>236.3760986328125</v>
+        <v>236.3760528564453</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -9435,10 +9598,10 @@
         <v>44950</v>
       </c>
       <c r="B3">
-        <v>235.8498840332031</v>
+        <v>235.8498992919922</v>
       </c>
       <c r="C3">
-        <v>99.77738248382431</v>
+        <v>99.77740826192209</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9446,10 +9609,10 @@
         <v>44951</v>
       </c>
       <c r="B4">
-        <v>234.4564514160156</v>
+        <v>234.4564666748047</v>
       </c>
       <c r="C4">
-        <v>99.18788438090822</v>
+        <v>99.18791004484434</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9457,10 +9620,10 @@
         <v>44952</v>
       </c>
       <c r="B5">
-        <v>241.6574554443359</v>
+        <v>241.657470703125</v>
       </c>
       <c r="C5">
-        <v>102.234302385931</v>
+        <v>102.2343286398336</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -9468,10 +9631,10 @@
         <v>44953</v>
       </c>
       <c r="B6">
-        <v>241.8133697509766</v>
+        <v>241.8133850097656</v>
       </c>
       <c r="C6">
-        <v>102.300262653294</v>
+        <v>102.3002889199705</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -9479,10 +9642,10 @@
         <v>44956</v>
       </c>
       <c r="B7">
-        <v>236.5027465820312</v>
+        <v>236.5027618408203</v>
       </c>
       <c r="C7">
-        <v>100.0535789997175</v>
+        <v>100.0536048313033</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9490,10 +9653,10 @@
         <v>44957</v>
       </c>
       <c r="B8">
-        <v>241.4723358154297</v>
+        <v>241.4723205566406</v>
       </c>
       <c r="C8">
-        <v>102.155986672127</v>
+        <v>102.1560000002582</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -9501,10 +9664,10 @@
         <v>44958</v>
       </c>
       <c r="B9">
-        <v>246.2859954833984</v>
+        <v>246.2859802246094</v>
       </c>
       <c r="C9">
-        <v>104.1924276218722</v>
+        <v>104.1924413443787</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9515,7 +9678,7 @@
         <v>257.8329467773438</v>
       </c>
       <c r="C10">
-        <v>109.0774186851533</v>
+        <v>109.077439808985</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9523,10 +9686,10 @@
         <v>44960</v>
       </c>
       <c r="B11">
-        <v>251.7427673339844</v>
+        <v>251.7427978515625</v>
       </c>
       <c r="C11">
-        <v>106.5009401500625</v>
+        <v>106.5009736855407</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9534,10 +9697,10 @@
         <v>44963</v>
       </c>
       <c r="B12">
-        <v>250.2031402587891</v>
+        <v>250.2031860351562</v>
       </c>
       <c r="C12">
-        <v>105.8495938066291</v>
+        <v>105.8496336712706</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9548,7 +9711,7 @@
         <v>260.7172546386719</v>
       </c>
       <c r="C13">
-        <v>110.2976384442621</v>
+        <v>110.2976598044005</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9556,10 +9719,10 @@
         <v>44965</v>
       </c>
       <c r="B14">
-        <v>259.9084167480469</v>
+        <v>259.908447265625</v>
       </c>
       <c r="C14">
-        <v>109.9554558398011</v>
+        <v>109.9554900442776</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9567,10 +9730,10 @@
         <v>44966</v>
       </c>
       <c r="B15">
-        <v>256.8779907226562</v>
+        <v>256.8779296875</v>
       </c>
       <c r="C15">
-        <v>108.6734201166809</v>
+        <v>108.6734153410649</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9578,10 +9741,10 @@
         <v>44967</v>
       </c>
       <c r="B16">
-        <v>256.3712768554688</v>
+        <v>256.3713073730469</v>
       </c>
       <c r="C16">
-        <v>108.4590524754014</v>
+        <v>108.4590863900858</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9589,10 +9752,10 @@
         <v>44970</v>
       </c>
       <c r="B17">
-        <v>264.3810424804688</v>
+        <v>264.3810729980469</v>
       </c>
       <c r="C17">
-        <v>111.8476208083793</v>
+        <v>111.8476553792906</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9600,10 +9763,10 @@
         <v>44971</v>
       </c>
       <c r="B18">
-        <v>265.2092895507812</v>
+        <v>265.2093505859375</v>
       </c>
       <c r="C18">
-        <v>112.1980145559295</v>
+        <v>112.1980621053026</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9611,10 +9774,10 @@
         <v>44972</v>
       </c>
       <c r="B19">
-        <v>263.0895080566406</v>
+        <v>263.0895385742188</v>
       </c>
       <c r="C19">
-        <v>111.3012312066817</v>
+        <v>111.3012656717798</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9622,10 +9785,10 @@
         <v>44973</v>
       </c>
       <c r="B20">
-        <v>256.0853881835938</v>
+        <v>256.0853576660156</v>
       </c>
       <c r="C20">
-        <v>108.3381059526656</v>
+        <v>108.3381140227179</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9633,10 +9796,10 @@
         <v>44974</v>
       </c>
       <c r="B21">
-        <v>252.0900421142578</v>
+        <v>252.0899963378906</v>
       </c>
       <c r="C21">
-        <v>106.6478563494084</v>
+        <v>106.6478576368261</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9644,10 +9807,10 @@
         <v>44978</v>
       </c>
       <c r="B22">
-        <v>246.8247222900391</v>
+        <v>246.8246917724609</v>
       </c>
       <c r="C22">
-        <v>104.420338485008</v>
+        <v>104.420345796349</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9658,7 +9821,7 @@
         <v>245.6915283203125</v>
       </c>
       <c r="C23">
-        <v>103.9409355435596</v>
+        <v>103.9409556726648</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9669,7 +9832,7 @@
         <v>248.8761291503906</v>
       </c>
       <c r="C24">
-        <v>105.2881956297095</v>
+        <v>105.2882160197238</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9680,7 +9843,7 @@
         <v>243.4545135498047</v>
       </c>
       <c r="C25">
-        <v>102.9945561154167</v>
+        <v>102.9945760612469</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9691,7 +9854,7 @@
         <v>244.3727874755859</v>
       </c>
       <c r="C26">
-        <v>103.3830361398745</v>
+        <v>103.3830561609374</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9699,10 +9862,10 @@
         <v>44985</v>
       </c>
       <c r="B27">
-        <v>243.64990234375</v>
+        <v>243.6498870849609</v>
       </c>
       <c r="C27">
-        <v>103.0772162469085</v>
+        <v>103.0772297534442</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9710,10 +9873,10 @@
         <v>44986</v>
       </c>
       <c r="B28">
-        <v>240.57275390625</v>
+        <v>240.5727691650391</v>
       </c>
       <c r="C28">
-        <v>101.7754143916034</v>
+        <v>101.7754405566381</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9721,10 +9884,10 @@
         <v>44987</v>
       </c>
       <c r="B29">
-        <v>245.3008117675781</v>
+        <v>245.3007659912109</v>
       </c>
       <c r="C29">
-        <v>103.7756411017805</v>
+        <v>103.7756418329676</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -9732,10 +9895,10 @@
         <v>44988</v>
       </c>
       <c r="B30">
-        <v>249.3840789794922</v>
+        <v>249.3840942382812</v>
       </c>
       <c r="C30">
-        <v>105.5030861503837</v>
+        <v>105.503113037316</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9743,10 +9906,10 @@
         <v>44991</v>
       </c>
       <c r="B31">
-        <v>250.9275207519531</v>
+        <v>250.9275360107422</v>
       </c>
       <c r="C31">
-        <v>106.1560463191098</v>
+        <v>106.1560733324937</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -9757,7 +9920,7 @@
         <v>248.2704620361328</v>
       </c>
       <c r="C32">
-        <v>105.0319653603375</v>
+        <v>105.0319857007305</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9768,7 +9931,7 @@
         <v>247.8308715820312</v>
       </c>
       <c r="C33">
-        <v>104.8459945889084</v>
+        <v>104.8460148932864</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -9776,10 +9939,10 @@
         <v>44994</v>
       </c>
       <c r="B34">
-        <v>246.4828033447266</v>
+        <v>246.4828186035156</v>
       </c>
       <c r="C34">
-        <v>104.275688096373</v>
+        <v>104.2757147456085</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9787,10 +9950,10 @@
         <v>44995</v>
       </c>
       <c r="B35">
-        <v>242.839111328125</v>
+        <v>242.8390960693359</v>
       </c>
       <c r="C35">
-        <v>102.7342073638977</v>
+        <v>102.7342208040066</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -9798,10 +9961,10 @@
         <v>44998</v>
       </c>
       <c r="B36">
-        <v>248.0457763671875</v>
+        <v>248.0457916259766</v>
       </c>
       <c r="C36">
-        <v>104.9369110505977</v>
+        <v>104.936937827885</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9812,7 +9975,7 @@
         <v>254.7568511962891</v>
       </c>
       <c r="C37">
-        <v>107.7760622456289</v>
+        <v>107.7760831174411</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9820,10 +9983,10 @@
         <v>45000</v>
       </c>
       <c r="B38">
-        <v>259.29931640625</v>
+        <v>259.2992858886719</v>
       </c>
       <c r="C38">
-        <v>109.6977731276657</v>
+        <v>109.6977814610299</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -9831,10 +9994,10 @@
         <v>45001</v>
       </c>
       <c r="B39">
-        <v>269.8103637695312</v>
+        <v>269.8103942871094</v>
       </c>
       <c r="C39">
-        <v>114.1445202497634</v>
+        <v>114.1445552654901</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -9845,7 +10008,7 @@
         <v>272.9656677246094</v>
       </c>
       <c r="C40">
-        <v>115.4793861576653</v>
+        <v>115.4794085212962</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -9853,10 +10016,10 @@
         <v>45005</v>
       </c>
       <c r="B41">
-        <v>265.9322814941406</v>
+        <v>265.9322509765625</v>
       </c>
       <c r="C41">
-        <v>112.5038796360036</v>
+        <v>112.5038885127958</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9864,10 +10027,10 @@
         <v>45006</v>
       </c>
       <c r="B42">
-        <v>267.4463195800781</v>
+        <v>267.4462890625</v>
       </c>
       <c r="C42">
-        <v>113.1444004393736</v>
+        <v>113.1444094402084</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -9875,10 +10038,10 @@
         <v>45007</v>
       </c>
       <c r="B43">
-        <v>265.9907531738281</v>
+        <v>265.9908447265625</v>
       </c>
       <c r="C43">
-        <v>112.5286163500901</v>
+        <v>112.5286768740921</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -9889,7 +10052,7 @@
         <v>271.2366027832031</v>
       </c>
       <c r="C44">
-        <v>114.7478972501966</v>
+        <v>114.747919472168</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -9897,10 +10060,10 @@
         <v>45009</v>
       </c>
       <c r="B45">
-        <v>274.0792236328125</v>
+        <v>274.0792846679688</v>
       </c>
       <c r="C45">
-        <v>115.9504811265069</v>
+        <v>115.9505294025792</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9908,10 +10071,10 @@
         <v>45012</v>
       </c>
       <c r="B46">
-        <v>269.9862060546875</v>
+        <v>269.9861450195312</v>
       </c>
       <c r="C46">
-        <v>114.2189111404555</v>
+        <v>114.2189074387742</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -9919,10 +10082,10 @@
         <v>45013</v>
       </c>
       <c r="B47">
-        <v>268.8628540039062</v>
+        <v>268.86279296875</v>
       </c>
       <c r="C47">
-        <v>113.7436718682623</v>
+        <v>113.7436680745466</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -9930,10 +10093,10 @@
         <v>45014</v>
       </c>
       <c r="B48">
-        <v>274.0207214355469</v>
+        <v>274.0205993652344</v>
       </c>
       <c r="C48">
-        <v>115.9257315018181</v>
+        <v>115.9257023094684</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -9941,10 +10104,10 @@
         <v>45015</v>
       </c>
       <c r="B49">
-        <v>277.4787292480469</v>
+        <v>277.4787902832031</v>
       </c>
       <c r="C49">
-        <v>117.3886576743461</v>
+        <v>117.3887062289343</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9952,10 +10115,10 @@
         <v>45016</v>
       </c>
       <c r="B50">
-        <v>281.6304321289062</v>
+        <v>281.63037109375</v>
       </c>
       <c r="C50">
-        <v>119.1450547487003</v>
+        <v>119.1450520010114</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -9963,10 +10126,10 @@
         <v>45019</v>
       </c>
       <c r="B51">
-        <v>280.585205078125</v>
+        <v>280.5852355957031</v>
       </c>
       <c r="C51">
-        <v>118.7028666185015</v>
+        <v>118.7029025169934</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -9974,10 +10137,10 @@
         <v>45020</v>
       </c>
       <c r="B52">
-        <v>280.5363159179688</v>
+        <v>280.5363464355469</v>
       </c>
       <c r="C52">
-        <v>118.6821838335503</v>
+        <v>118.6822197280368</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -9985,10 +10148,10 @@
         <v>45021</v>
       </c>
       <c r="B53">
-        <v>277.7619934082031</v>
+        <v>277.7620849609375</v>
       </c>
       <c r="C53">
-        <v>117.5084938852805</v>
+        <v>117.508555373681</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -9999,7 +10162,7 @@
         <v>284.8541564941406</v>
       </c>
       <c r="C54">
-        <v>120.5088662270521</v>
+        <v>120.5088895646873</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -10010,7 +10173,7 @@
         <v>282.6951904296875</v>
       </c>
       <c r="C55">
-        <v>119.5955056643977</v>
+        <v>119.5955288251524</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -10018,10 +10181,10 @@
         <v>45027</v>
       </c>
       <c r="B56">
-        <v>276.2870178222656</v>
+        <v>276.2869567871094</v>
       </c>
       <c r="C56">
-        <v>116.8844986529078</v>
+        <v>116.8844954674417</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -10032,7 +10195,7 @@
         <v>276.9316711425781</v>
       </c>
       <c r="C57">
-        <v>117.1572222167711</v>
+        <v>117.1572449053301</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -10040,10 +10203,10 @@
         <v>45029</v>
       </c>
       <c r="B58">
-        <v>283.134765625</v>
+        <v>283.1347961425781</v>
       </c>
       <c r="C58">
-        <v>119.7814699805257</v>
+        <v>119.7815060878989</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -10051,10 +10214,10 @@
         <v>45030</v>
       </c>
       <c r="B59">
-        <v>279.5204467773438</v>
+        <v>279.5203857421875</v>
       </c>
       <c r="C59">
-        <v>118.2524157028041</v>
+        <v>118.2524127822476</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -10062,10 +10225,10 @@
         <v>45033</v>
       </c>
       <c r="B60">
-        <v>282.1188659667969</v>
+        <v>282.1188354492188</v>
       </c>
       <c r="C60">
-        <v>119.3516889391771</v>
+        <v>119.3516991421097</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -10073,10 +10236,10 @@
         <v>45034</v>
       </c>
       <c r="B61">
-        <v>281.6987915039062</v>
+        <v>281.6987609863281</v>
       </c>
       <c r="C61">
-        <v>119.1739744979454</v>
+        <v>119.1739846664619</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -10084,10 +10247,10 @@
         <v>45035</v>
       </c>
       <c r="B62">
-        <v>281.7769470214844</v>
+        <v>281.7770080566406</v>
       </c>
       <c r="C62">
-        <v>119.2070385505422</v>
+        <v>119.2070874572764</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -10095,10 +10258,10 @@
         <v>45036</v>
       </c>
       <c r="B63">
-        <v>279.4910583496094</v>
+        <v>279.4910888671875</v>
       </c>
       <c r="C63">
-        <v>118.2399827927492</v>
+        <v>118.2400186015994</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -10106,10 +10269,10 @@
         <v>45037</v>
       </c>
       <c r="B64">
-        <v>279.1492309570312</v>
+        <v>279.149169921875</v>
       </c>
       <c r="C64">
-        <v>118.0953711359213</v>
+        <v>118.0953681849517</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -10117,10 +10280,10 @@
         <v>45040</v>
       </c>
       <c r="B65">
-        <v>275.25146484375</v>
+        <v>275.2514953613281</v>
       </c>
       <c r="C65">
-        <v>116.4464031836512</v>
+        <v>116.4464386451586</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -10131,7 +10294,7 @@
         <v>269.0484313964844</v>
       </c>
       <c r="C66">
-        <v>113.8221812411014</v>
+        <v>113.8222032837994</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -10139,10 +10302,10 @@
         <v>45042</v>
       </c>
       <c r="B67">
-        <v>288.5368957519531</v>
+        <v>288.5369262695312</v>
       </c>
       <c r="C67">
-        <v>122.0668660752234</v>
+        <v>122.0669026251843</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -10150,10 +10313,10 @@
         <v>45043</v>
       </c>
       <c r="B68">
-        <v>297.7779846191406</v>
+        <v>297.7780456542969</v>
       </c>
       <c r="C68">
-        <v>125.9763513914789</v>
+        <v>125.9764016091519</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -10161,10 +10324,10 @@
         <v>45044</v>
       </c>
       <c r="B69">
-        <v>300.1518249511719</v>
+        <v>300.15185546875</v>
       </c>
       <c r="C69">
-        <v>126.9806155052203</v>
+        <v>126.9806530067734</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -10175,7 +10338,7 @@
         <v>298.4911804199219</v>
       </c>
       <c r="C70">
-        <v>126.2780721682014</v>
+        <v>126.2780966230957</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -10186,7 +10349,7 @@
         <v>298.3446350097656</v>
       </c>
       <c r="C71">
-        <v>126.2160754557572</v>
+        <v>126.2160998986453</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -10194,10 +10357,10 @@
         <v>45049</v>
       </c>
       <c r="B72">
-        <v>297.3580017089844</v>
+        <v>297.3579711914062</v>
       </c>
       <c r="C72">
-        <v>125.7986756820542</v>
+        <v>125.7986871335042</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -10208,7 +10371,7 @@
         <v>298.3446350097656</v>
       </c>
       <c r="C73">
-        <v>126.2160754557572</v>
+        <v>126.2160998986453</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -10216,10 +10379,10 @@
         <v>45051</v>
       </c>
       <c r="B74">
-        <v>303.4633483886719</v>
+        <v>303.46337890625</v>
       </c>
       <c r="C74">
-        <v>128.3815707865087</v>
+        <v>128.3816085593695</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -10227,10 +10390,10 @@
         <v>45054</v>
       </c>
       <c r="B75">
-        <v>301.5096435546875</v>
+        <v>301.5096130371094</v>
       </c>
       <c r="C75">
-        <v>127.5550469352037</v>
+        <v>127.555058726791</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -10238,10 +10401,10 @@
         <v>45055</v>
       </c>
       <c r="B76">
-        <v>299.8977966308594</v>
+        <v>299.8978576660156</v>
       </c>
       <c r="C76">
-        <v>126.873147651329</v>
+        <v>126.8731980426749</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -10249,10 +10412,10 @@
         <v>45056</v>
       </c>
       <c r="B77">
-        <v>305.0850830078125</v>
+        <v>305.0849609375</v>
       </c>
       <c r="C77">
-        <v>129.0676531055421</v>
+        <v>129.0676264582447</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -10260,10 +10423,10 @@
         <v>45057</v>
       </c>
       <c r="B78">
-        <v>302.9359130859375</v>
+        <v>302.9358825683594</v>
       </c>
       <c r="C78">
-        <v>128.1584368462394</v>
+        <v>128.1584487546786</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -10271,10 +10434,10 @@
         <v>45058</v>
       </c>
       <c r="B79">
-        <v>301.8222961425781</v>
+        <v>301.8222351074219</v>
       </c>
       <c r="C79">
-        <v>127.6873160561931</v>
+        <v>127.6873149627907</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -10282,10 +10445,10 @@
         <v>45061</v>
       </c>
       <c r="B80">
-        <v>302.3009033203125</v>
+        <v>302.3009338378906</v>
       </c>
       <c r="C80">
-        <v>127.889793032716</v>
+        <v>127.8898307103396</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -10293,10 +10456,10 @@
         <v>45062</v>
       </c>
       <c r="B81">
-        <v>304.5281066894531</v>
+        <v>304.5281982421875</v>
       </c>
       <c r="C81">
-        <v>128.8320217022061</v>
+        <v>128.8320853835105</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -10304,10 +10467,10 @@
         <v>45063</v>
       </c>
       <c r="B82">
-        <v>307.4064331054688</v>
+        <v>307.4065246582031</v>
       </c>
       <c r="C82">
-        <v>130.049710983256</v>
+        <v>130.0497749003769</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -10315,10 +10478,10 @@
         <v>45064</v>
       </c>
       <c r="B83">
-        <v>311.8315124511719</v>
+        <v>311.8314819335938</v>
       </c>
       <c r="C83">
-        <v>131.921761233386</v>
+        <v>131.9217738706271</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -10329,7 +10492,7 @@
         <v>311.6553344726562</v>
       </c>
       <c r="C84">
-        <v>131.8472283260681</v>
+        <v>131.8472538594801</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -10340,7 +10503,7 @@
         <v>314.4356689453125</v>
       </c>
       <c r="C85">
-        <v>133.0234616629992</v>
+        <v>133.0234874241994</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -10348,10 +10511,10 @@
         <v>45069</v>
       </c>
       <c r="B86">
-        <v>308.6399536132812</v>
+        <v>308.6399841308594</v>
       </c>
       <c r="C86">
-        <v>130.5715575299022</v>
+        <v>130.5715957268738</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -10359,10 +10522,10 @@
         <v>45070</v>
       </c>
       <c r="B87">
-        <v>307.2595825195312</v>
+        <v>307.2596435546875</v>
       </c>
       <c r="C87">
-        <v>129.9875851647884</v>
+        <v>129.9876361592732</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -10370,10 +10533,10 @@
         <v>45071</v>
       </c>
       <c r="B88">
-        <v>319.076171875</v>
+        <v>319.0761413574219</v>
       </c>
       <c r="C88">
-        <v>134.9866478550584</v>
+        <v>134.9866610858425</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -10381,10 +10544,10 @@
         <v>45072</v>
       </c>
       <c r="B89">
-        <v>325.8997497558594</v>
+        <v>325.8998107910156</v>
       </c>
       <c r="C89">
-        <v>137.8733939856217</v>
+        <v>137.873446507265</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -10395,7 +10558,7 @@
         <v>324.2550354003906</v>
       </c>
       <c r="C90">
-        <v>137.1775899830251</v>
+        <v>137.17761654871</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -10403,10 +10566,10 @@
         <v>45077</v>
       </c>
       <c r="B91">
-        <v>321.4943237304688</v>
+        <v>321.4942626953125</v>
       </c>
       <c r="C91">
-        <v>136.0096581633997</v>
+        <v>136.0096586816942</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -10414,10 +10577,10 @@
         <v>45078</v>
       </c>
       <c r="B92">
-        <v>325.5962829589844</v>
+        <v>325.5962524414062</v>
       </c>
       <c r="C92">
-        <v>137.7450109559371</v>
+        <v>137.7450247209034</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -10428,7 +10591,7 @@
         <v>328.3570861816406</v>
       </c>
       <c r="C93">
-        <v>138.9129815073696</v>
+        <v>138.9130084091288</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -10436,10 +10599,10 @@
         <v>45082</v>
       </c>
       <c r="B94">
-        <v>328.8857727050781</v>
+        <v>328.8857116699219</v>
       </c>
       <c r="C94">
-        <v>139.136644782335</v>
+        <v>139.1366459061989</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -10447,10 +10610,10 @@
         <v>45083</v>
       </c>
       <c r="B95">
-        <v>326.6732177734375</v>
+        <v>326.6731567382812</v>
       </c>
       <c r="C95">
-        <v>138.2006132019688</v>
+        <v>138.2006141445617</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -10458,10 +10621,10 @@
         <v>45084</v>
       </c>
       <c r="B96">
-        <v>316.5895080566406</v>
+        <v>316.5894470214844</v>
       </c>
       <c r="C96">
-        <v>133.9346532444602</v>
+        <v>133.9346533609112</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -10469,10 +10632,10 @@
         <v>45085</v>
       </c>
       <c r="B97">
-        <v>318.4300231933594</v>
+        <v>318.4299926757812</v>
       </c>
       <c r="C97">
-        <v>134.7132916716803</v>
+        <v>134.7133048495266</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -10480,10 +10643,10 @@
         <v>45086</v>
       </c>
       <c r="B98">
-        <v>319.9278869628906</v>
+        <v>319.9279174804688</v>
       </c>
       <c r="C98">
-        <v>135.3469698558092</v>
+        <v>135.3470089775827</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -10491,10 +10654,10 @@
         <v>45089</v>
       </c>
       <c r="B99">
-        <v>324.8816223144531</v>
+        <v>324.881591796875</v>
       </c>
       <c r="C99">
-        <v>137.4426704703023</v>
+        <v>137.4426841767175</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -10502,10 +10665,10 @@
         <v>45090</v>
       </c>
       <c r="B100">
-        <v>327.2703857421875</v>
+        <v>327.2703552246094</v>
       </c>
       <c r="C100">
-        <v>138.4532478685886</v>
+        <v>138.4532617707114</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -10513,10 +10676,10 @@
         <v>45091</v>
       </c>
       <c r="B101">
-        <v>330.2563171386719</v>
+        <v>330.25634765625</v>
       </c>
       <c r="C101">
-        <v>139.7164599334949</v>
+        <v>139.7164999014598</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -10527,7 +10690,7 @@
         <v>340.7904052734375</v>
       </c>
       <c r="C102">
-        <v>144.1729545603604</v>
+        <v>144.1729824807611</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -10535,10 +10698,10 @@
         <v>45093</v>
       </c>
       <c r="B103">
-        <v>335.1415405273438</v>
+        <v>335.1414794921875</v>
       </c>
       <c r="C103">
-        <v>141.7831762457311</v>
+        <v>141.7831778821198</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -10546,10 +10709,10 @@
         <v>45097</v>
       </c>
       <c r="B104">
-        <v>330.951416015625</v>
+        <v>330.9513854980469</v>
       </c>
       <c r="C104">
-        <v>140.0105247230289</v>
+        <v>140.0105389267324</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -10560,7 +10723,7 @@
         <v>326.5556640625</v>
       </c>
       <c r="C105">
-        <v>138.1508815617491</v>
+        <v>138.1509083159207</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -10568,10 +10731,10 @@
         <v>45099</v>
       </c>
       <c r="B106">
-        <v>332.5765075683594</v>
+        <v>332.5765380859375</v>
       </c>
       <c r="C106">
-        <v>140.6980272083198</v>
+        <v>140.6980673663741</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -10579,10 +10742,10 @@
         <v>45100</v>
       </c>
       <c r="B107">
-        <v>327.9850158691406</v>
+        <v>327.9850463867188</v>
       </c>
       <c r="C107">
-        <v>138.7555754436212</v>
+        <v>138.7556152255021</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -10590,10 +10753,10 @@
         <v>45103</v>
       </c>
       <c r="B108">
-        <v>321.6998291015625</v>
+        <v>321.6998596191406</v>
       </c>
       <c r="C108">
-        <v>136.0965981595678</v>
+        <v>136.0966374265136</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -10601,10 +10764,10 @@
         <v>45104</v>
       </c>
       <c r="B109">
-        <v>327.54443359375</v>
+        <v>327.5445861816406</v>
       </c>
       <c r="C109">
-        <v>138.5691850776159</v>
+        <v>138.5692764658201</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -10615,7 +10778,7 @@
         <v>328.7976379394531</v>
       </c>
       <c r="C110">
-        <v>139.0993589627726</v>
+        <v>139.0993859006254</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -10626,7 +10789,7 @@
         <v>328.014404296875</v>
       </c>
       <c r="C111">
-        <v>138.7680083536761</v>
+        <v>138.7680352273599</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -10634,10 +10797,10 @@
         <v>45107</v>
       </c>
       <c r="B112">
-        <v>333.3891296386719</v>
+        <v>333.3891906738281</v>
       </c>
       <c r="C112">
-        <v>141.0418107274711</v>
+        <v>141.0418638627071</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -10645,10 +10808,10 @@
         <v>45110</v>
       </c>
       <c r="B113">
-        <v>330.8926696777344</v>
+        <v>330.8926391601562</v>
       </c>
       <c r="C113">
-        <v>139.9856718135213</v>
+        <v>139.9856860124119</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -10659,7 +10822,7 @@
         <v>331.0493469238281</v>
       </c>
       <c r="C114">
-        <v>140.051954845943</v>
+        <v>140.0519819682746</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -10667,10 +10830,10 @@
         <v>45113</v>
       </c>
       <c r="B115">
-        <v>334.103759765625</v>
+        <v>334.1038513183594</v>
       </c>
       <c r="C115">
-        <v>141.3441383025037</v>
+        <v>141.3442044068929</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -10678,10 +10841,10 @@
         <v>45114</v>
       </c>
       <c r="B116">
-        <v>330.1388549804688</v>
+        <v>330.1387939453125</v>
       </c>
       <c r="C116">
-        <v>139.6667670250822</v>
+        <v>139.6667682516091</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -10689,10 +10852,10 @@
         <v>45117</v>
       </c>
       <c r="B117">
-        <v>324.8620300292969</v>
+        <v>324.8619995117188</v>
       </c>
       <c r="C117">
-        <v>137.434381863599</v>
+        <v>137.4343955684091</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -10700,10 +10863,10 @@
         <v>45118</v>
       </c>
       <c r="B118">
-        <v>325.4885559082031</v>
+        <v>325.4885864257812</v>
       </c>
       <c r="C118">
-        <v>137.6994365296714</v>
+        <v>137.6994761070214</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -10714,7 +10877,7 @@
         <v>330.1192626953125</v>
       </c>
       <c r="C119">
-        <v>139.6584784183789</v>
+        <v>139.6585054645103</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -10722,10 +10885,10 @@
         <v>45120</v>
       </c>
       <c r="B120">
-        <v>335.464599609375</v>
+        <v>335.4646301269531</v>
       </c>
       <c r="C120">
-        <v>141.919847882119</v>
+        <v>141.9198882767899</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -10733,10 +10896,10 @@
         <v>45121</v>
       </c>
       <c r="B121">
-        <v>337.9904479980469</v>
+        <v>337.9904174804688</v>
       </c>
       <c r="C121">
-        <v>142.9884197061237</v>
+        <v>142.9884344865236</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -10744,10 +10907,10 @@
         <v>45124</v>
       </c>
       <c r="B122">
-        <v>338.4701232910156</v>
+        <v>338.4701538085938</v>
       </c>
       <c r="C122">
-        <v>143.1913485537285</v>
+        <v>143.1913891946371</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -10755,10 +10918,10 @@
         <v>45125</v>
       </c>
       <c r="B123">
-        <v>351.9411926269531</v>
+        <v>351.9412536621094</v>
       </c>
       <c r="C123">
-        <v>148.8903466393444</v>
+        <v>148.8904012945205</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -10769,7 +10932,7 @@
         <v>347.6238098144531</v>
       </c>
       <c r="C124">
-        <v>147.0638579048778</v>
+        <v>147.0638863851281</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -10777,10 +10940,10 @@
         <v>45127</v>
       </c>
       <c r="B125">
-        <v>339.586181640625</v>
+        <v>339.5862426757812</v>
       </c>
       <c r="C125">
-        <v>143.6635021919621</v>
+        <v>143.6635558349124</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -10788,10 +10951,10 @@
         <v>45128</v>
       </c>
       <c r="B126">
-        <v>336.5512084960938</v>
+        <v>336.55126953125</v>
       </c>
       <c r="C126">
-        <v>142.3795427890929</v>
+        <v>142.3795961833928</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -10799,10 +10962,10 @@
         <v>45131</v>
       </c>
       <c r="B127">
-        <v>337.8631286621094</v>
+        <v>337.8631896972656</v>
       </c>
       <c r="C127">
-        <v>142.9345566731547</v>
+        <v>142.9346101749381</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -10810,10 +10973,10 @@
         <v>45132</v>
       </c>
       <c r="B128">
-        <v>343.6098937988281</v>
+        <v>343.6099548339844</v>
       </c>
       <c r="C128">
-        <v>145.3657522000958</v>
+        <v>145.3658061727022</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -10821,10 +10984,10 @@
         <v>45133</v>
       </c>
       <c r="B129">
-        <v>330.6773071289062</v>
+        <v>330.67724609375</v>
       </c>
       <c r="C129">
-        <v>139.8945616927969</v>
+        <v>139.8945629634383</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -10832,10 +10995,10 @@
         <v>45134</v>
       </c>
       <c r="B130">
-        <v>323.7753295898438</v>
+        <v>323.7753601074219</v>
       </c>
       <c r="C130">
-        <v>136.974648224818</v>
+        <v>136.9746876618062</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -10843,10 +11006,10 @@
         <v>45135</v>
       </c>
       <c r="B131">
-        <v>331.2647399902344</v>
+        <v>331.2646484375</v>
       </c>
       <c r="C131">
-        <v>140.1430778772697</v>
+        <v>140.1430662854337</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -10854,10 +11017,10 @@
         <v>45138</v>
       </c>
       <c r="B132">
-        <v>328.8661804199219</v>
+        <v>328.8661499023438</v>
       </c>
       <c r="C132">
-        <v>139.1283561756317</v>
+        <v>139.1283702084953</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -10865,10 +11028,10 @@
         <v>45139</v>
       </c>
       <c r="B133">
-        <v>329.2773132324219</v>
+        <v>329.27734375</v>
       </c>
       <c r="C133">
-        <v>139.3022878103774</v>
+        <v>139.302327698134</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -10879,7 +11042,7 @@
         <v>320.6229553222656</v>
       </c>
       <c r="C134">
-        <v>135.6410217347408</v>
+        <v>135.6410480028553</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -10887,10 +11050,10 @@
         <v>45141</v>
       </c>
       <c r="B135">
-        <v>319.8006286621094</v>
+        <v>319.8005676269531</v>
       </c>
       <c r="C135">
-        <v>135.2931326440449</v>
+        <v>135.2931330235778</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -10901,7 +11064,7 @@
         <v>320.8970642089844</v>
       </c>
       <c r="C136">
-        <v>135.7569847649728</v>
+        <v>135.7570110555446</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -10909,10 +11072,10 @@
         <v>45145</v>
       </c>
       <c r="B137">
-        <v>323.1781311035156</v>
+        <v>323.1781005859375</v>
       </c>
       <c r="C137">
-        <v>136.7220006475958</v>
+        <v>136.7220142144468</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -10920,10 +11083,10 @@
         <v>45146</v>
       </c>
       <c r="B138">
-        <v>319.2034301757812</v>
+        <v>319.203369140625</v>
       </c>
       <c r="C138">
-        <v>135.0404850668227</v>
+        <v>135.0404853974281</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -10931,10 +11094,10 @@
         <v>45147</v>
       </c>
       <c r="B139">
-        <v>315.4636840820312</v>
+        <v>315.463623046875</v>
       </c>
       <c r="C139">
-        <v>133.4583682134773</v>
+        <v>133.4583682376915</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -10945,7 +11108,7 @@
         <v>316.14892578125</v>
       </c>
       <c r="C140">
-        <v>133.7482628784549</v>
+        <v>133.7482887800195</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -10953,10 +11116,10 @@
         <v>45149</v>
       </c>
       <c r="B141">
-        <v>314.2692260742188</v>
+        <v>314.2692565917969</v>
       </c>
       <c r="C141">
-        <v>132.9530472378283</v>
+        <v>132.9530858959969</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -10967,7 +11130,7 @@
         <v>317.235595703125</v>
       </c>
       <c r="C142">
-        <v>134.2079836066336</v>
+        <v>134.2080095972272</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -10975,10 +11138,10 @@
         <v>45153</v>
       </c>
       <c r="B143">
-        <v>315.1014099121094</v>
+        <v>315.1013793945312</v>
       </c>
       <c r="C143">
-        <v>133.3051064530806</v>
+        <v>133.305119358219</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -10986,10 +11149,10 @@
         <v>45154</v>
       </c>
       <c r="B144">
-        <v>314.3361511230469</v>
+        <v>314.3360900878906</v>
       </c>
       <c r="C144">
-        <v>132.9813601887633</v>
+        <v>132.9813601206005</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -10997,10 +11160,10 @@
         <v>45155</v>
       </c>
       <c r="B145">
-        <v>310.8827819824219</v>
+        <v>310.8827209472656</v>
       </c>
       <c r="C145">
-        <v>131.5203964277912</v>
+        <v>131.5203960766996</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -11008,10 +11171,10 @@
         <v>45156</v>
       </c>
       <c r="B146">
-        <v>310.4903869628906</v>
+        <v>310.4903564453125</v>
       </c>
       <c r="C146">
-        <v>131.3543919028833</v>
+        <v>131.3544044302483</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -11019,10 +11182,10 @@
         <v>45159</v>
       </c>
       <c r="B147">
-        <v>315.7881774902344</v>
+        <v>315.7882080078125</v>
       </c>
       <c r="C147">
-        <v>133.5956466481753</v>
+        <v>133.5956854307891</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -11030,10 +11193,10 @@
         <v>45160</v>
       </c>
       <c r="B148">
-        <v>316.3571166992188</v>
+        <v>316.3571472167969</v>
       </c>
       <c r="C148">
-        <v>133.8363390076291</v>
+        <v>133.8363778368553</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -11041,10 +11204,10 @@
         <v>45161</v>
       </c>
       <c r="B149">
-        <v>320.8112487792969</v>
+        <v>320.8112182617188</v>
       </c>
       <c r="C149">
-        <v>135.7206801511883</v>
+        <v>135.7206935241245</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -11052,10 +11215,10 @@
         <v>45162</v>
       </c>
       <c r="B150">
-        <v>313.9143371582031</v>
+        <v>313.9142761230469</v>
       </c>
       <c r="C150">
-        <v>132.8029098431982</v>
+        <v>132.8029097404768</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -11063,10 +11226,10 @@
         <v>45163</v>
       </c>
       <c r="B151">
-        <v>316.8674011230469</v>
+        <v>316.8673706054688</v>
       </c>
       <c r="C151">
-        <v>134.0522171893825</v>
+        <v>134.0522302392058</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -11077,7 +11240,7 @@
         <v>317.5736999511719</v>
       </c>
       <c r="C152">
-        <v>134.3510201699758</v>
+        <v>134.3510461882698</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -11085,10 +11248,10 @@
         <v>45167</v>
       </c>
       <c r="B153">
-        <v>322.194580078125</v>
+        <v>322.1945495605469</v>
       </c>
       <c r="C153">
-        <v>136.3059048447294</v>
+        <v>136.3059183309996</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -11099,7 +11262,7 @@
         <v>322.5673522949219</v>
       </c>
       <c r="C154">
-        <v>136.4636078523316</v>
+        <v>136.4636342797474</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -11107,10 +11270,10 @@
         <v>45169</v>
       </c>
       <c r="B155">
-        <v>321.556884765625</v>
+        <v>321.5569152832031</v>
       </c>
       <c r="C155">
-        <v>136.0361248981999</v>
+        <v>136.0361641534345</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -11121,7 +11284,7 @@
         <v>322.4398193359375</v>
       </c>
       <c r="C156">
-        <v>136.4096544451462</v>
+        <v>136.4096808621134</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -11129,10 +11292,10 @@
         <v>45174</v>
       </c>
       <c r="B157">
-        <v>327.2372436523438</v>
+        <v>327.2372741699219</v>
       </c>
       <c r="C157">
-        <v>138.4392269544457</v>
+        <v>138.4392666750629</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -11140,10 +11303,10 @@
         <v>45175</v>
       </c>
       <c r="B158">
-        <v>326.5799560546875</v>
+        <v>326.5799865722656</v>
       </c>
       <c r="C158">
-        <v>138.161158401213</v>
+        <v>138.1611980679796</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -11151,10 +11314,10 @@
         <v>45176</v>
       </c>
       <c r="B159">
-        <v>323.6661682128906</v>
+        <v>323.6661987304688</v>
       </c>
       <c r="C159">
-        <v>136.9284670002422</v>
+        <v>136.928506428287</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -11162,10 +11325,10 @@
         <v>45177</v>
       </c>
       <c r="B160">
-        <v>327.9436645507812</v>
+        <v>327.943603515625</v>
       </c>
       <c r="C160">
-        <v>138.7380815774484</v>
+        <v>138.7380826241269</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -11173,10 +11336,10 @@
         <v>45180</v>
       </c>
       <c r="B161">
-        <v>331.5442199707031</v>
+        <v>331.544189453125</v>
       </c>
       <c r="C161">
-        <v>140.2613131735139</v>
+        <v>140.2613274257848</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -11184,10 +11347,10 @@
         <v>45181</v>
       </c>
       <c r="B162">
-        <v>325.4909362792969</v>
+        <v>325.490966796875</v>
       </c>
       <c r="C162">
-        <v>137.7004435566541</v>
+        <v>137.7004831341991</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -11198,7 +11361,7 @@
         <v>329.6997680664062</v>
       </c>
       <c r="C163">
-        <v>139.4810092785917</v>
+        <v>139.4810362903546</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -11206,10 +11369,10 @@
         <v>45183</v>
       </c>
       <c r="B164">
-        <v>332.2898254394531</v>
+        <v>332.289794921875</v>
       </c>
       <c r="C164">
-        <v>140.5767450099231</v>
+        <v>140.5767593232803</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -11217,10 +11380,10 @@
         <v>45184</v>
       </c>
       <c r="B165">
-        <v>323.9703063964844</v>
+        <v>323.9702758789062</v>
       </c>
       <c r="C165">
-        <v>137.0571340631783</v>
+        <v>137.0571476949309</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -11231,7 +11394,7 @@
         <v>322.832275390625</v>
       </c>
       <c r="C166">
-        <v>136.5756847912588</v>
+        <v>136.5757112403793</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -11239,10 +11402,10 @@
         <v>45188</v>
       </c>
       <c r="B167">
-        <v>322.4299926757812</v>
+        <v>322.4300231933594</v>
       </c>
       <c r="C167">
-        <v>136.4054972311922</v>
+        <v>136.4055365579592</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -11253,7 +11416,7 @@
         <v>314.6991271972656</v>
       </c>
       <c r="C168">
-        <v>133.134918893014</v>
+        <v>133.1349446757989</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -11264,7 +11427,7 @@
         <v>313.4826049804688</v>
       </c>
       <c r="C169">
-        <v>132.6202635518719</v>
+        <v>132.6202892349892</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -11272,10 +11435,10 @@
         <v>45191</v>
       </c>
       <c r="B170">
-        <v>311.0103149414062</v>
+        <v>311.0103454589844</v>
       </c>
       <c r="C170">
-        <v>131.5743498349767</v>
+        <v>131.5743882261481</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -11283,10 +11446,10 @@
         <v>45194</v>
       </c>
       <c r="B171">
-        <v>311.5302429199219</v>
+        <v>311.5303344726562</v>
       </c>
       <c r="C171">
-        <v>131.79430776707</v>
+        <v>131.794372022048</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -11297,7 +11460,7 @@
         <v>306.2324829101562</v>
       </c>
       <c r="C172">
-        <v>129.5530659323805</v>
+        <v>129.5530910215071</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -11305,10 +11468,10 @@
         <v>45196</v>
       </c>
       <c r="B173">
-        <v>306.8701477050781</v>
+        <v>306.8702392578125</v>
       </c>
       <c r="C173">
-        <v>129.8228329683076</v>
+        <v>129.8228968414915</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -11316,10 +11479,10 @@
         <v>45197</v>
       </c>
       <c r="B174">
-        <v>307.7040710449219</v>
+        <v>307.7041015625</v>
       </c>
       <c r="C174">
-        <v>130.1756280878933</v>
+        <v>130.1756662081896</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -11327,10 +11490,10 @@
         <v>45198</v>
       </c>
       <c r="B175">
-        <v>309.7742004394531</v>
+        <v>309.774169921875</v>
       </c>
       <c r="C175">
-        <v>131.0514058871314</v>
+        <v>131.0514183558203</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -11338,10 +11501,10 @@
         <v>45201</v>
       </c>
       <c r="B176">
-        <v>315.7096862792969</v>
+        <v>315.7096557617188</v>
       </c>
       <c r="C176">
-        <v>133.5624405789527</v>
+        <v>133.5624535339263</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -11352,7 +11515,7 @@
         <v>307.4588317871094</v>
       </c>
       <c r="C177">
-        <v>130.0718784874765</v>
+        <v>130.0719036770758</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -11363,7 +11526,7 @@
         <v>312.9234008789062</v>
       </c>
       <c r="C178">
-        <v>132.383689674565</v>
+        <v>132.3837153118676</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -11374,7 +11537,7 @@
         <v>313.3158264160156</v>
       </c>
       <c r="C179">
-        <v>132.5497071100753</v>
+        <v>132.5497327795287</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -11385,7 +11548,7 @@
         <v>321.0663452148438</v>
       </c>
       <c r="C180">
-        <v>135.8285998761615</v>
+        <v>135.8286261806022</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -11393,10 +11556,10 @@
         <v>45208</v>
       </c>
       <c r="B181">
-        <v>323.577880859375</v>
+        <v>323.5778198242188</v>
       </c>
       <c r="C181">
-        <v>136.8911166276681</v>
+        <v>136.8911173166651</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -11404,10 +11567,10 @@
         <v>45209</v>
       </c>
       <c r="B182">
-        <v>322.1750183105469</v>
+        <v>322.1749572753906</v>
       </c>
       <c r="C182">
-        <v>136.2976291486284</v>
+        <v>136.2976297226912</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -11415,10 +11578,10 @@
         <v>45210</v>
       </c>
       <c r="B183">
-        <v>326.128662109375</v>
+        <v>326.1287231445312</v>
       </c>
       <c r="C183">
-        <v>137.9702364137858</v>
+        <v>137.9702889541836</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -11426,10 +11589,10 @@
         <v>45211</v>
       </c>
       <c r="B184">
-        <v>324.8925170898438</v>
+        <v>324.8924865722656</v>
       </c>
       <c r="C184">
-        <v>137.4472795553382</v>
+        <v>137.447293262646</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -11437,10 +11600,10 @@
         <v>45212</v>
       </c>
       <c r="B185">
-        <v>321.5274047851562</v>
+        <v>321.5274353027344</v>
       </c>
       <c r="C185">
-        <v>136.023653256338</v>
+        <v>136.0236925091573</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -11448,10 +11611,10 @@
         <v>45215</v>
       </c>
       <c r="B186">
-        <v>326.3445129394531</v>
+        <v>326.3445434570312</v>
       </c>
       <c r="C186">
-        <v>138.0615531041477</v>
+        <v>138.0615927516249</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -11459,10 +11622,10 @@
         <v>45216</v>
       </c>
       <c r="B187">
-        <v>325.7754821777344</v>
+        <v>325.7754516601562</v>
       </c>
       <c r="C187">
-        <v>137.8208220128869</v>
+        <v>137.8208357925346</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -11470,10 +11633,10 @@
         <v>45217</v>
       </c>
       <c r="B188">
-        <v>323.8623657226562</v>
+        <v>323.8623352050781</v>
       </c>
       <c r="C188">
-        <v>137.0114692626962</v>
+        <v>137.0114828856054</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -11481,10 +11644,10 @@
         <v>45218</v>
       </c>
       <c r="B189">
-        <v>325.0494384765625</v>
+        <v>325.0494995117188</v>
       </c>
       <c r="C189">
-        <v>137.5136658725786</v>
+        <v>137.5137183245572</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -11492,10 +11655,10 @@
         <v>45219</v>
       </c>
       <c r="B190">
-        <v>320.4874877929688</v>
+        <v>320.4875183105469</v>
       </c>
       <c r="C190">
-        <v>135.5837115709466</v>
+        <v>135.5837507385673</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -11503,10 +11666,10 @@
         <v>45222</v>
       </c>
       <c r="B191">
-        <v>323.0873107910156</v>
+        <v>323.0873413085938</v>
       </c>
       <c r="C191">
-        <v>136.6835786950273</v>
+        <v>136.6836180756472</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -11514,10 +11677,10 @@
         <v>45223</v>
       </c>
       <c r="B192">
-        <v>324.2744140625</v>
+        <v>324.2744750976562</v>
       </c>
       <c r="C192">
-        <v>137.185788215512</v>
+        <v>137.1858406039942</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -11528,7 +11691,7 @@
         <v>334.2225341796875</v>
       </c>
       <c r="C193">
-        <v>141.3943863668171</v>
+        <v>141.3944137491228</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -11536,10 +11699,10 @@
         <v>45225</v>
       </c>
       <c r="B194">
-        <v>321.6843872070312</v>
+        <v>321.6844177246094</v>
       </c>
       <c r="C194">
-        <v>136.090065394783</v>
+        <v>136.0901046604637</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -11547,10 +11710,10 @@
         <v>45226</v>
       </c>
       <c r="B195">
-        <v>323.5680236816406</v>
+        <v>323.5680847167969</v>
       </c>
       <c r="C195">
-        <v>136.8869465031117</v>
+        <v>136.8869988337205</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -11558,10 +11721,10 @@
         <v>45229</v>
       </c>
       <c r="B196">
-        <v>330.9260864257812</v>
+        <v>330.9261169433594</v>
       </c>
       <c r="C196">
-        <v>139.9998089230853</v>
+        <v>139.9998489459233</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -11569,10 +11732,10 @@
         <v>45230</v>
       </c>
       <c r="B197">
-        <v>331.7109375</v>
+        <v>331.7109680175781</v>
       </c>
       <c r="C197">
-        <v>140.3318437941059</v>
+        <v>140.3318838812454</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -11580,10 +11743,10 @@
         <v>45231</v>
       </c>
       <c r="B198">
-        <v>339.5203247070312</v>
+        <v>339.5203552246094</v>
       </c>
       <c r="C198">
-        <v>143.635641112109</v>
+        <v>143.6356818390589</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -11591,10 +11754,10 @@
         <v>45232</v>
       </c>
       <c r="B199">
-        <v>341.7277526855469</v>
+        <v>341.7277221679688</v>
       </c>
       <c r="C199">
-        <v>144.5695037112818</v>
+        <v>144.5695187978729</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -11602,10 +11765,10 @@
         <v>45233</v>
       </c>
       <c r="B200">
-        <v>346.1229553222656</v>
+        <v>346.1229248046875</v>
       </c>
       <c r="C200">
-        <v>146.4289144817193</v>
+        <v>146.4289299284023</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -11616,7 +11779,7 @@
         <v>349.7823486328125</v>
       </c>
       <c r="C201">
-        <v>147.9770377190994</v>
+        <v>147.9770663761953</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -11624,10 +11787,10 @@
         <v>45237</v>
       </c>
       <c r="B202">
-        <v>353.7066955566406</v>
+        <v>353.7066345214844</v>
       </c>
       <c r="C202">
-        <v>149.6372508060089</v>
+        <v>149.6372539634104</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -11635,10 +11798,10 @@
         <v>45238</v>
       </c>
       <c r="B203">
-        <v>356.3261413574219</v>
+        <v>356.326171875</v>
       </c>
       <c r="C203">
-        <v>150.7454194473952</v>
+        <v>150.7454615512182</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -11646,10 +11809,10 @@
         <v>45239</v>
       </c>
       <c r="B204">
-        <v>353.8636169433594</v>
+        <v>353.8636779785156</v>
       </c>
       <c r="C204">
-        <v>149.7036371232493</v>
+        <v>149.7036919359265</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -11660,7 +11823,7 @@
         <v>362.6736755371094</v>
       </c>
       <c r="C205">
-        <v>153.4307730920325</v>
+        <v>153.4308028052937</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -11668,10 +11831,10 @@
         <v>45243</v>
       </c>
       <c r="B206">
-        <v>359.740234375</v>
+        <v>359.7402038574219</v>
       </c>
       <c r="C206">
-        <v>152.1897672631537</v>
+        <v>152.1897838254781</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -11679,10 +11842,10 @@
         <v>45244</v>
       </c>
       <c r="B207">
-        <v>363.2623291015625</v>
+        <v>363.2622680664062</v>
       </c>
       <c r="C207">
-        <v>153.679805700599</v>
+        <v>153.679809640878</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -11690,10 +11853,10 @@
         <v>45245</v>
       </c>
       <c r="B208">
-        <v>363.4098205566406</v>
+        <v>363.4097595214844</v>
       </c>
       <c r="C208">
-        <v>153.7422026417158</v>
+        <v>153.7422065940785</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -11701,10 +11864,10 @@
         <v>45246</v>
       </c>
       <c r="B209">
-        <v>369.7997436523438</v>
+        <v>369.7996826171875</v>
       </c>
       <c r="C209">
-        <v>156.4454891130055</v>
+        <v>156.4454935888841</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -11715,7 +11878,7 @@
         <v>363.5867309570312</v>
       </c>
       <c r="C210">
-        <v>153.8170454034899</v>
+        <v>153.8170751915563</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -11726,7 +11889,7 @@
         <v>371.0481872558594</v>
       </c>
       <c r="C211">
-        <v>156.9736489441968</v>
+        <v>156.9736793435681</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -11734,10 +11897,10 @@
         <v>45251</v>
       </c>
       <c r="B212">
-        <v>366.752197265625</v>
+        <v>366.7522277832031</v>
       </c>
       <c r="C212">
-        <v>155.1562105419716</v>
+        <v>155.1562534999843</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -11748,7 +11911,7 @@
         <v>371.4512939453125</v>
       </c>
       <c r="C213">
-        <v>157.1441850905266</v>
+        <v>157.1442155229237</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -11759,7 +11922,7 @@
         <v>371.0383605957031</v>
       </c>
       <c r="C214">
-        <v>156.9694917302428</v>
+        <v>156.969522128809</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -11770,7 +11933,7 @@
         <v>372.1983642578125</v>
       </c>
       <c r="C215">
-        <v>157.4602366358482</v>
+        <v>157.4602671294516</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -11778,10 +11941,10 @@
         <v>45258</v>
       </c>
       <c r="B216">
-        <v>376.2191467285156</v>
+        <v>376.2191772460938</v>
       </c>
       <c r="C216">
-        <v>159.1612472261571</v>
+        <v>159.1612909597815</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -11792,7 +11955,7 @@
         <v>372.4342956542969</v>
       </c>
       <c r="C217">
-        <v>157.5600485025509</v>
+        <v>157.5600790154838</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -11803,7 +11966,7 @@
         <v>372.4933166503906</v>
       </c>
       <c r="C218">
-        <v>157.5850176074795</v>
+        <v>157.5850481252479</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -11811,10 +11974,10 @@
         <v>45261</v>
       </c>
       <c r="B219">
-        <v>368.1678771972656</v>
+        <v>368.1678466796875</v>
       </c>
       <c r="C219">
-        <v>155.7551204739947</v>
+        <v>155.755137726782</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -11822,10 +11985,10 @@
         <v>45264</v>
       </c>
       <c r="B220">
-        <v>362.8887939453125</v>
+        <v>362.8887634277344</v>
       </c>
       <c r="C220">
-        <v>153.5217799279382</v>
+        <v>153.5217967482189</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -11833,10 +11996,10 @@
         <v>45265</v>
       </c>
       <c r="B221">
-        <v>366.2115173339844</v>
+        <v>366.2114868164062</v>
       </c>
       <c r="C221">
-        <v>154.927473400286</v>
+        <v>154.927490492792</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -11847,7 +12010,7 @@
         <v>362.5545043945312</v>
       </c>
       <c r="C222">
-        <v>153.3803571898886</v>
+        <v>153.3803868933863</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -11855,10 +12018,10 @@
         <v>45267</v>
       </c>
       <c r="B223">
-        <v>364.6681213378906</v>
+        <v>364.6680908203125</v>
       </c>
       <c r="C223">
-        <v>154.2745325974634</v>
+        <v>154.2745495635215</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -11866,10 +12029,10 @@
         <v>45268</v>
       </c>
       <c r="B224">
-        <v>367.892578125</v>
+        <v>367.8926086425781</v>
       </c>
       <c r="C224">
-        <v>155.6386539302714</v>
+        <v>155.6386969817136</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -11877,10 +12040,10 @@
         <v>45271</v>
       </c>
       <c r="B225">
-        <v>365.0121459960938</v>
+        <v>365.0121765136719</v>
       </c>
       <c r="C225">
-        <v>154.42007381766</v>
+        <v>154.4201166331131</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -11891,7 +12054,7 @@
         <v>368.0400390625</v>
       </c>
       <c r="C226">
-        <v>155.7010379607858</v>
+        <v>155.7010681137045</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -11899,10 +12062,10 @@
         <v>45273</v>
       </c>
       <c r="B227">
-        <v>368.0301513671875</v>
+        <v>368.0302124023438</v>
       </c>
       <c r="C227">
-        <v>155.6968549256272</v>
+        <v>155.6969108989454</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -11910,10 +12073,10 @@
         <v>45274</v>
       </c>
       <c r="B228">
-        <v>359.7331237792969</v>
+        <v>359.7330932617188</v>
       </c>
       <c r="C228">
-        <v>152.1867590928081</v>
+        <v>152.1867756545499</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -11924,7 +12087,7 @@
         <v>364.4518432617188</v>
       </c>
       <c r="C229">
-        <v>154.1830351586687</v>
+        <v>154.1830650176123</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -11935,7 +12098,7 @@
         <v>366.3393249511719</v>
       </c>
       <c r="C230">
-        <v>154.9815430028925</v>
+        <v>154.9815730164744</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -11943,10 +12106,10 @@
         <v>45279</v>
       </c>
       <c r="B231">
-        <v>366.93896484375</v>
+        <v>366.9389953613281</v>
       </c>
       <c r="C231">
-        <v>155.235223428302</v>
+        <v>155.2352664016163</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -11957,7 +12120,7 @@
         <v>364.3436889648438</v>
       </c>
       <c r="C232">
-        <v>154.1372799839702</v>
+        <v>154.1373098340529</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -11965,10 +12128,10 @@
         <v>45281</v>
       </c>
       <c r="B233">
-        <v>367.2142639160156</v>
+        <v>367.2142028808594</v>
       </c>
       <c r="C233">
-        <v>155.3516899720253</v>
+        <v>155.3516942360799</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -11976,10 +12139,10 @@
         <v>45282</v>
       </c>
       <c r="B234">
-        <v>368.2366027832031</v>
+        <v>368.2366638183594</v>
       </c>
       <c r="C234">
-        <v>155.7841951504679</v>
+        <v>155.7842511407003</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -11987,10 +12150,10 @@
         <v>45286</v>
       </c>
       <c r="B235">
-        <v>368.3153381347656</v>
+        <v>368.3153076171875</v>
       </c>
       <c r="C235">
-        <v>155.8175045045091</v>
+        <v>155.8175217693777</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -12001,7 +12164,7 @@
         <v>367.7352600097656</v>
       </c>
       <c r="C236">
-        <v>155.5720997752006</v>
+        <v>155.5721299031492</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -12009,10 +12172,10 @@
         <v>45288</v>
       </c>
       <c r="B237">
-        <v>368.9247436523438</v>
+        <v>368.9248046875</v>
       </c>
       <c r="C237">
-        <v>156.075316322668</v>
+        <v>156.0753723692787</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -12020,10 +12183,10 @@
         <v>45289</v>
       </c>
       <c r="B238">
-        <v>369.6719360351562</v>
+        <v>369.6719055175781</v>
       </c>
       <c r="C238">
-        <v>156.391419510399</v>
+        <v>156.3914368864114</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -12031,10 +12194,10 @@
         <v>45293</v>
       </c>
       <c r="B239">
-        <v>364.5894775390625</v>
+        <v>364.5894165039062</v>
       </c>
       <c r="C239">
-        <v>154.2412619752292</v>
+        <v>154.2412660242393</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -12042,10 +12205,10 @@
         <v>45294</v>
       </c>
       <c r="B240">
-        <v>364.3240356445312</v>
+        <v>364.3240661621094</v>
       </c>
       <c r="C240">
-        <v>154.1289655560622</v>
+        <v>154.1290083151396</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -12056,7 +12219,7 @@
         <v>361.7090759277344</v>
       </c>
       <c r="C241">
-        <v>153.0226947732201</v>
+        <v>153.0227244074533</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -12067,7 +12230,7 @@
         <v>361.5223083496094</v>
       </c>
       <c r="C242">
-        <v>152.9436818868897</v>
+        <v>152.9437115058213</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -12075,10 +12238,10 @@
         <v>45299</v>
       </c>
       <c r="B243">
-        <v>368.3447875976562</v>
+        <v>368.3447570800781</v>
       </c>
       <c r="C243">
-        <v>155.8299632357688</v>
+        <v>155.8299805030501</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -12089,7 +12252,7 @@
         <v>369.4261169433594</v>
       </c>
       <c r="C244">
-        <v>156.2874246085376</v>
+        <v>156.2874548750153</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -12097,10 +12260,10 @@
         <v>45301</v>
       </c>
       <c r="B245">
-        <v>376.2878723144531</v>
+        <v>376.2879943847656</v>
       </c>
       <c r="C245">
-        <v>159.1903219026303</v>
+        <v>159.1904043736998</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -12108,10 +12271,10 @@
         <v>45302</v>
       </c>
       <c r="B246">
-        <v>378.1164245605469</v>
+        <v>378.1164855957031</v>
       </c>
       <c r="C246">
-        <v>159.9638993737325</v>
+        <v>159.9639561734026</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -12119,10 +12282,10 @@
         <v>45303</v>
       </c>
       <c r="B247">
-        <v>381.8914489746094</v>
+        <v>381.8915100097656</v>
       </c>
       <c r="C247">
-        <v>161.5609408833847</v>
+        <v>161.5609979923364</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -12133,7 +12296,7 @@
         <v>383.6609497070312</v>
       </c>
       <c r="C248">
-        <v>162.309536338956</v>
+        <v>162.3095677716703</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -12141,10 +12304,10 @@
         <v>45308</v>
       </c>
       <c r="B249">
-        <v>382.8744812011719</v>
+        <v>382.8744506835938</v>
       </c>
       <c r="C249">
-        <v>161.9768172060114</v>
+        <v>161.9768356636868</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -12152,10 +12315,10 @@
         <v>45309</v>
       </c>
       <c r="B250">
-        <v>387.2000122070312</v>
+        <v>387.1999816894531</v>
       </c>
       <c r="C250">
-        <v>163.8067530713032</v>
+        <v>163.8067718833622</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -12163,10 +12326,10 @@
         <v>45310</v>
       </c>
       <c r="B251">
-        <v>391.9186401367188</v>
+        <v>391.918701171875</v>
       </c>
       <c r="C251">
-        <v>165.8029904053568</v>
+        <v>165.8030483358198</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -12174,10 +12337,10 @@
         <v>45313</v>
       </c>
       <c r="B252">
-        <v>389.7952270507812</v>
+        <v>389.7951965332031</v>
       </c>
       <c r="C252">
-        <v>164.9046706944303</v>
+        <v>164.9046897191111</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -12185,10 +12348,10 @@
         <v>45314</v>
       </c>
       <c r="B253">
-        <v>392.144775390625</v>
+        <v>392.1447448730469</v>
       </c>
       <c r="C253">
-        <v>165.8986579687078</v>
+        <v>165.8986771858832</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -12199,7 +12362,7 @@
         <v>395.7427978515625</v>
       </c>
       <c r="C254">
-        <v>167.4208179847789</v>
+        <v>167.4208504073393</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -12207,10 +12370,10 @@
         <v>45316</v>
       </c>
       <c r="B255">
-        <v>398.013671875</v>
+        <v>398.0137023925781</v>
       </c>
       <c r="C255">
-        <v>168.3815217262198</v>
+        <v>168.381567245434</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -12221,7 +12384,7 @@
         <v>397.089599609375</v>
       </c>
       <c r="C256">
-        <v>167.9905886873171</v>
+        <v>167.9906212202187</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -12232,7 +12395,7 @@
         <v>402.7815551757812</v>
       </c>
       <c r="C257">
-        <v>170.3985967724527</v>
+        <v>170.3986297716869</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -12240,10 +12403,10 @@
         <v>45321</v>
       </c>
       <c r="B258">
-        <v>401.6706848144531</v>
+        <v>401.6705932617188</v>
       </c>
       <c r="C258">
-        <v>169.9286379366172</v>
+        <v>169.9286321130251</v>
       </c>
     </row>
   </sheetData>
@@ -12262,13 +12425,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -15114,13 +15277,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -15150,10 +15313,10 @@
         <v>44951</v>
       </c>
       <c r="B4">
-        <v>94.43946075439453</v>
+        <v>94.43944549560547</v>
       </c>
       <c r="C4">
-        <v>95.42038216658709</v>
+        <v>95.42036674930841</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -15161,10 +15324,10 @@
         <v>44952</v>
       </c>
       <c r="B5">
-        <v>96.72060394287109</v>
+        <v>96.72059631347656</v>
       </c>
       <c r="C5">
-        <v>97.72521907567557</v>
+        <v>97.72521136703622</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -15172,10 +15335,10 @@
         <v>44953</v>
       </c>
       <c r="B6">
-        <v>98.55544281005859</v>
+        <v>98.55545043945312</v>
       </c>
       <c r="C6">
-        <v>99.57911600099226</v>
+        <v>99.57912370963159</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -15216,10 +15379,10 @@
         <v>44959</v>
       </c>
       <c r="B10">
-        <v>106.856819152832</v>
+        <v>106.8568267822266</v>
       </c>
       <c r="C10">
-        <v>107.9667168704651</v>
+        <v>107.9667245791044</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -15238,10 +15401,10 @@
         <v>44963</v>
       </c>
       <c r="B12">
-        <v>102.0565185546875</v>
+        <v>102.0565032958984</v>
       </c>
       <c r="C12">
-        <v>103.1165566309793</v>
+        <v>103.1165412137006</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -15249,10 +15412,10 @@
         <v>44964</v>
       </c>
       <c r="B13">
-        <v>106.7576370239258</v>
+        <v>106.7576599121094</v>
       </c>
       <c r="C13">
-        <v>107.8665045591206</v>
+        <v>107.8665276850386</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -15260,10 +15423,10 @@
         <v>44965</v>
       </c>
       <c r="B14">
-        <v>98.55544281005859</v>
+        <v>98.55545043945312</v>
       </c>
       <c r="C14">
-        <v>99.57911600099226</v>
+        <v>99.57912370963159</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -15271,10 +15434,10 @@
         <v>44966</v>
       </c>
       <c r="B15">
-        <v>94.23117065429688</v>
+        <v>94.23119354248047</v>
       </c>
       <c r="C15">
-        <v>95.20992860412422</v>
+        <v>95.20995173004222</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -15293,10 +15456,10 @@
         <v>44970</v>
       </c>
       <c r="B17">
-        <v>93.83444976806641</v>
+        <v>93.83446502685547</v>
       </c>
       <c r="C17">
-        <v>94.80908706738538</v>
+        <v>94.80910248466404</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -15304,10 +15467,10 @@
         <v>44971</v>
       </c>
       <c r="B18">
-        <v>93.90389251708984</v>
+        <v>93.90387725830078</v>
       </c>
       <c r="C18">
-        <v>94.87925110260522</v>
+        <v>94.87923568532656</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -15326,10 +15489,10 @@
         <v>44973</v>
       </c>
       <c r="B20">
-        <v>94.72707366943359</v>
+        <v>94.72708892822266</v>
       </c>
       <c r="C20">
-        <v>95.71098245220759</v>
+        <v>95.71099786948626</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -15337,10 +15500,10 @@
         <v>44974</v>
       </c>
       <c r="B21">
-        <v>93.57657623291016</v>
+        <v>93.57659149169922</v>
       </c>
       <c r="C21">
-        <v>94.54853505788957</v>
+        <v>94.54855047516824</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -15348,10 +15511,10 @@
         <v>44978</v>
       </c>
       <c r="B22">
-        <v>91.03757476806641</v>
+        <v>91.03758239746094</v>
       </c>
       <c r="C22">
-        <v>91.98316155658397</v>
+        <v>91.98316926522328</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -15359,10 +15522,10 @@
         <v>44979</v>
       </c>
       <c r="B23">
-        <v>90.89871978759766</v>
+        <v>90.89872741699219</v>
       </c>
       <c r="C23">
-        <v>91.84286432070159</v>
+        <v>91.84287202934092</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -15370,10 +15533,10 @@
         <v>44980</v>
       </c>
       <c r="B24">
-        <v>90.14495086669922</v>
+        <v>90.14495849609375</v>
       </c>
       <c r="C24">
-        <v>91.08126617176174</v>
+        <v>91.08127388040108</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -15381,10 +15544,10 @@
         <v>44981</v>
       </c>
       <c r="B25">
-        <v>88.39939117431641</v>
+        <v>88.39937591552734</v>
       </c>
       <c r="C25">
-        <v>89.3175757439338</v>
+        <v>89.31756032665513</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -15392,10 +15555,10 @@
         <v>44984</v>
       </c>
       <c r="B26">
-        <v>89.13332366943359</v>
+        <v>89.13330841064453</v>
       </c>
       <c r="C26">
-        <v>90.05913143060475</v>
+        <v>90.05911601332608</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -15403,10 +15566,10 @@
         <v>44985</v>
       </c>
       <c r="B27">
-        <v>89.32175445556641</v>
+        <v>89.32174682617188</v>
       </c>
       <c r="C27">
-        <v>90.2495194048807</v>
+        <v>90.24951169624138</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -15425,10 +15588,10 @@
         <v>44987</v>
       </c>
       <c r="B29">
-        <v>91.24585723876953</v>
+        <v>91.24584197998047</v>
       </c>
       <c r="C29">
-        <v>92.19360741040749</v>
+        <v>92.19359199312883</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -15436,10 +15599,10 @@
         <v>44988</v>
       </c>
       <c r="B30">
-        <v>92.88232421875</v>
+        <v>92.88233184814453</v>
       </c>
       <c r="C30">
-        <v>93.84707200439577</v>
+        <v>93.84707971303511</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -15447,10 +15610,10 @@
         <v>44991</v>
       </c>
       <c r="B31">
-        <v>94.35017395019531</v>
+        <v>94.35021209716797</v>
       </c>
       <c r="C31">
-        <v>95.33016796045899</v>
+        <v>95.33020650365567</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -15458,10 +15621,10 @@
         <v>44992</v>
       </c>
       <c r="B32">
-        <v>93.09061431884766</v>
+        <v>93.09060668945312</v>
       </c>
       <c r="C32">
-        <v>94.05752556685864</v>
+        <v>94.05751785821931</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -15469,10 +15632,10 @@
         <v>44993</v>
       </c>
       <c r="B33">
-        <v>93.47740936279297</v>
+        <v>93.4774169921875</v>
       </c>
       <c r="C33">
-        <v>94.44833816382369</v>
+        <v>94.44834587246302</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -15502,10 +15665,10 @@
         <v>44998</v>
       </c>
       <c r="B36">
-        <v>90.3631591796875</v>
+        <v>90.36315155029297</v>
       </c>
       <c r="C36">
-        <v>91.30174096535907</v>
+        <v>91.30173325671974</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -15513,10 +15676,10 @@
         <v>44999</v>
       </c>
       <c r="B37">
-        <v>93.19969177246094</v>
+        <v>93.19971466064453</v>
       </c>
       <c r="C37">
-        <v>94.16773598341965</v>
+        <v>94.16775910933765</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -15524,10 +15687,10 @@
         <v>45000</v>
       </c>
       <c r="B38">
-        <v>95.32215881347656</v>
+        <v>95.32216644287109</v>
       </c>
       <c r="C38">
-        <v>96.31224861163551</v>
+        <v>96.31225632027484</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -15535,10 +15698,10 @@
         <v>45001</v>
       </c>
       <c r="B39">
-        <v>99.49766540527344</v>
+        <v>99.49765014648438</v>
       </c>
       <c r="C39">
-        <v>100.5311252501261</v>
+        <v>100.5311098328474</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -15546,10 +15709,10 @@
         <v>45002</v>
       </c>
       <c r="B40">
-        <v>100.7870025634766</v>
+        <v>100.786994934082</v>
       </c>
       <c r="C40">
-        <v>101.8338544630478</v>
+        <v>101.8338467544085</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -15557,10 +15720,10 @@
         <v>45005</v>
       </c>
       <c r="B41">
-        <v>100.3902816772461</v>
+        <v>100.390266418457</v>
       </c>
       <c r="C41">
-        <v>101.4330129263089</v>
+        <v>101.4329975090303</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -15568,10 +15731,10 @@
         <v>45006</v>
       </c>
       <c r="B42">
-        <v>104.059944152832</v>
+        <v>104.0599365234375</v>
       </c>
       <c r="C42">
-        <v>105.1407913596637</v>
+        <v>105.1407836510243</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -15579,10 +15742,10 @@
         <v>45007</v>
       </c>
       <c r="B43">
-        <v>102.5226440429688</v>
+        <v>102.5226516723633</v>
       </c>
       <c r="C43">
-        <v>103.5875236597413</v>
+        <v>103.5875313683806</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -15590,10 +15753,10 @@
         <v>45008</v>
       </c>
       <c r="B44">
-        <v>104.734375</v>
+        <v>104.7343597412109</v>
       </c>
       <c r="C44">
-        <v>105.8222273681672</v>
+        <v>105.8222119508886</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -15601,10 +15764,10 @@
         <v>45009</v>
       </c>
       <c r="B45">
-        <v>104.5756912231445</v>
+        <v>104.57568359375</v>
       </c>
       <c r="C45">
-        <v>105.6618953786553</v>
+        <v>105.661887670016</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -15623,10 +15786,10 @@
         <v>45013</v>
       </c>
       <c r="B47">
-        <v>100.2018203735352</v>
+        <v>100.2018356323242</v>
       </c>
       <c r="C47">
-        <v>101.2425941174756</v>
+        <v>101.2426095347543</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -15634,10 +15797,10 @@
         <v>45014</v>
       </c>
       <c r="B48">
-        <v>100.5588684082031</v>
+        <v>100.5588912963867</v>
       </c>
       <c r="C48">
-        <v>101.6033507296767</v>
+        <v>101.6033738555947</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -15645,10 +15808,10 @@
         <v>45015</v>
       </c>
       <c r="B49">
-        <v>100.0629730224609</v>
+        <v>100.06298828125</v>
       </c>
       <c r="C49">
-        <v>101.1023045902326</v>
+        <v>101.1023200075113</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -15733,10 +15896,10 @@
         <v>45028</v>
       </c>
       <c r="B57">
-        <v>103.7822418212891</v>
+        <v>103.7822494506836</v>
       </c>
       <c r="C57">
-        <v>104.8602045965383</v>
+        <v>104.8602123051776</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -15744,10 +15907,10 @@
         <v>45029</v>
       </c>
       <c r="B58">
-        <v>106.5493698120117</v>
+        <v>106.5493774414062</v>
       </c>
       <c r="C58">
-        <v>107.6560741225757</v>
+        <v>107.656081831215</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -15755,10 +15918,10 @@
         <v>45030</v>
       </c>
       <c r="B59">
-        <v>107.9775619506836</v>
+        <v>107.9775772094727</v>
       </c>
       <c r="C59">
-        <v>109.0991005713798</v>
+        <v>109.0991159886584</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -15766,10 +15929,10 @@
         <v>45033</v>
       </c>
       <c r="B60">
-        <v>105.1013488769531</v>
+        <v>105.1013412475586</v>
       </c>
       <c r="C60">
-        <v>106.1930129201421</v>
+        <v>106.1930052115027</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -15799,10 +15962,10 @@
         <v>45036</v>
       </c>
       <c r="B63">
-        <v>104.4269104003906</v>
+        <v>104.4269256591797</v>
       </c>
       <c r="C63">
-        <v>105.5115692029992</v>
+        <v>105.5115846202778</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -15810,10 +15973,10 @@
         <v>45037</v>
       </c>
       <c r="B64">
-        <v>104.5459289550781</v>
+        <v>104.5459365844727</v>
       </c>
       <c r="C64">
-        <v>105.6318239766126</v>
+        <v>105.6318316852519</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -15821,10 +15984,10 @@
         <v>45040</v>
       </c>
       <c r="B65">
-        <v>105.1013488769531</v>
+        <v>105.1013412475586</v>
       </c>
       <c r="C65">
-        <v>106.1930129201421</v>
+        <v>106.1930052115027</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -15832,10 +15995,10 @@
         <v>45041</v>
       </c>
       <c r="B66">
-        <v>102.9987106323242</v>
+        <v>102.9987258911133</v>
       </c>
       <c r="C66">
-        <v>104.0685350455557</v>
+        <v>104.0685504628344</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -15843,10 +16006,10 @@
         <v>45042</v>
       </c>
       <c r="B67">
-        <v>102.8598556518555</v>
+        <v>102.8598785400391</v>
       </c>
       <c r="C67">
-        <v>103.9282378096734</v>
+        <v>103.9282609355914</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -15854,10 +16017,10 @@
         <v>45043</v>
       </c>
       <c r="B68">
-        <v>106.7080612182617</v>
+        <v>106.7080459594727</v>
       </c>
       <c r="C68">
-        <v>107.816413820727</v>
+        <v>107.8163984034483</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -15865,10 +16028,10 @@
         <v>45044</v>
       </c>
       <c r="B69">
-        <v>106.4600982666016</v>
+        <v>106.4601058959961</v>
       </c>
       <c r="C69">
-        <v>107.5658753337263</v>
+        <v>107.5658830423656</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -15876,10 +16039,10 @@
         <v>45047</v>
       </c>
       <c r="B70">
-        <v>106.3212509155273</v>
+        <v>106.3212585449219</v>
       </c>
       <c r="C70">
-        <v>107.4255858064832</v>
+        <v>107.4255935151226</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -15898,10 +16061,10 @@
         <v>45049</v>
       </c>
       <c r="B72">
-        <v>104.5459289550781</v>
+        <v>104.5459365844727</v>
       </c>
       <c r="C72">
-        <v>105.6318239766126</v>
+        <v>105.6318316852519</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -15931,10 +16094,10 @@
         <v>45054</v>
       </c>
       <c r="B75">
-        <v>106.8865814208984</v>
+        <v>106.8865737915039</v>
       </c>
       <c r="C75">
-        <v>107.9967882725078</v>
+        <v>107.9967805638685</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -15942,10 +16105,10 @@
         <v>45055</v>
       </c>
       <c r="B76">
-        <v>106.4700393676758</v>
+        <v>106.4700241088867</v>
       </c>
       <c r="C76">
-        <v>107.5759196907787</v>
+        <v>107.5759042735001</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -15953,10 +16116,10 @@
         <v>45056</v>
       </c>
       <c r="B77">
-        <v>110.8339691162109</v>
+        <v>110.8339538574219</v>
       </c>
       <c r="C77">
-        <v>111.9851765949059</v>
+        <v>111.9851611776272</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -15964,10 +16127,10 @@
         <v>45057</v>
       </c>
       <c r="B78">
-        <v>115.6144485473633</v>
+        <v>115.6144409179688</v>
       </c>
       <c r="C78">
-        <v>116.8153097894015</v>
+        <v>116.8153020807622</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -15986,10 +16149,10 @@
         <v>45061</v>
       </c>
       <c r="B80">
-        <v>115.5549468994141</v>
+        <v>115.554931640625</v>
       </c>
       <c r="C80">
-        <v>116.7551901112341</v>
+        <v>116.7551746939555</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -15997,10 +16160,10 @@
         <v>45062</v>
       </c>
       <c r="B81">
-        <v>118.5303573608398</v>
+        <v>118.5303421020508</v>
       </c>
       <c r="C81">
-        <v>119.7615054910951</v>
+        <v>119.7614900738164</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -16008,10 +16171,10 @@
         <v>45063</v>
       </c>
       <c r="B82">
-        <v>119.8494415283203</v>
+        <v>119.8494491577148</v>
       </c>
       <c r="C82">
-        <v>121.0942906887808</v>
+        <v>121.0942983974201</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -16019,10 +16182,10 @@
         <v>45064</v>
       </c>
       <c r="B83">
-        <v>121.8231353759766</v>
+        <v>121.8231430053711</v>
       </c>
       <c r="C83">
-        <v>123.0884848499798</v>
+        <v>123.0884925586192</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -16030,10 +16193,10 @@
         <v>45065</v>
       </c>
       <c r="B84">
-        <v>121.7537002563477</v>
+        <v>121.7537078857422</v>
       </c>
       <c r="C84">
-        <v>123.0183285233993</v>
+        <v>123.0183362320387</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -16041,10 +16204,10 @@
         <v>45068</v>
       </c>
       <c r="B85">
-        <v>124.0249404907227</v>
+        <v>124.0249328613281</v>
       </c>
       <c r="C85">
-        <v>125.313159618632</v>
+        <v>125.3131519099927</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -16063,10 +16226,10 @@
         <v>45070</v>
       </c>
       <c r="B87">
-        <v>119.9089508056641</v>
+        <v>119.9089584350586</v>
       </c>
       <c r="C87">
-        <v>121.1544180755875</v>
+        <v>121.1544257842269</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -16074,10 +16237,10 @@
         <v>45071</v>
       </c>
       <c r="B88">
-        <v>122.4678039550781</v>
+        <v>122.4678115844727</v>
       </c>
       <c r="C88">
-        <v>123.7398494564407</v>
+        <v>123.7398571650801</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -16096,10 +16259,10 @@
         <v>45076</v>
       </c>
       <c r="B90">
-        <v>122.6562423706055</v>
+        <v>122.6562347412109</v>
       </c>
       <c r="C90">
-        <v>123.930245139356</v>
+        <v>123.9302374307167</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -16118,10 +16281,10 @@
         <v>45078</v>
       </c>
       <c r="B92">
-        <v>122.7058334350586</v>
+        <v>122.7058410644531</v>
       </c>
       <c r="C92">
-        <v>123.9803512950283</v>
+        <v>123.9803590036676</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -16129,10 +16292,10 @@
         <v>45079</v>
       </c>
       <c r="B93">
-        <v>123.6480407714844</v>
+        <v>123.6480484008789</v>
       </c>
       <c r="C93">
-        <v>124.9323451268834</v>
+        <v>124.9323528355228</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -16162,10 +16325,10 @@
         <v>45084</v>
       </c>
       <c r="B96">
-        <v>121.4958343505859</v>
+        <v>121.4958419799805</v>
       </c>
       <c r="C96">
-        <v>122.7577842225429</v>
+        <v>122.7577919311822</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -16195,10 +16358,10 @@
         <v>45089</v>
       </c>
       <c r="B99">
-        <v>122.6264877319336</v>
+        <v>122.6264953613281</v>
       </c>
       <c r="C99">
-        <v>123.9001814459527</v>
+        <v>123.900189154592</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -16206,10 +16369,10 @@
         <v>45090</v>
       </c>
       <c r="B100">
-        <v>122.81494140625</v>
+        <v>122.8149337768555</v>
       </c>
       <c r="C100">
-        <v>124.0905925461466</v>
+        <v>124.0905848375073</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -16217,10 +16380,10 @@
         <v>45091</v>
       </c>
       <c r="B101">
-        <v>122.6562423706055</v>
+        <v>122.6562347412109</v>
       </c>
       <c r="C101">
-        <v>123.930245139356</v>
+        <v>123.9302374307167</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -16239,10 +16402,10 @@
         <v>45093</v>
       </c>
       <c r="B103">
-        <v>122.5173950195312</v>
+        <v>122.5174026489258</v>
       </c>
       <c r="C103">
-        <v>123.789955612113</v>
+        <v>123.7899633207523</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -16250,10 +16413,10 @@
         <v>45097</v>
       </c>
       <c r="B104">
-        <v>122.0909118652344</v>
+        <v>122.0909194946289</v>
       </c>
       <c r="C104">
-        <v>123.3590426733314</v>
+        <v>123.3590503819708</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -16261,10 +16424,10 @@
         <v>45098</v>
       </c>
       <c r="B105">
-        <v>119.5618286132812</v>
+        <v>119.5618362426758</v>
       </c>
       <c r="C105">
-        <v>120.8036904031603</v>
+        <v>120.8036981117996</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -16294,10 +16457,10 @@
         <v>45103</v>
       </c>
       <c r="B108">
-        <v>117.3699340820312</v>
+        <v>117.3699417114258</v>
       </c>
       <c r="C108">
-        <v>118.5890291570032</v>
+        <v>118.5890368656426</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -16305,10 +16468,10 @@
         <v>45104</v>
       </c>
       <c r="B109">
-        <v>117.3600234985352</v>
+        <v>117.3600158691406</v>
       </c>
       <c r="C109">
-        <v>118.5790156345081</v>
+        <v>118.5790079258688</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -16316,10 +16479,10 @@
         <v>45105</v>
       </c>
       <c r="B110">
-        <v>119.1948547363281</v>
+        <v>119.1948699951172</v>
       </c>
       <c r="C110">
-        <v>120.4329048511855</v>
+        <v>120.4329202684641</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -16327,10 +16490,10 @@
         <v>45106</v>
       </c>
       <c r="B111">
-        <v>118.1237030029297</v>
+        <v>118.1237106323242</v>
       </c>
       <c r="C111">
-        <v>119.3506273059431</v>
+        <v>119.3506350145824</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -16338,10 +16501,10 @@
         <v>45107</v>
       </c>
       <c r="B112">
-        <v>118.7187805175781</v>
+        <v>118.7187881469727</v>
       </c>
       <c r="C112">
-        <v>119.9518857567317</v>
+        <v>119.951893465371</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -16349,10 +16512,10 @@
         <v>45110</v>
       </c>
       <c r="B113">
-        <v>118.9171524047852</v>
+        <v>118.9171600341797</v>
       </c>
       <c r="C113">
-        <v>120.1523180880601</v>
+        <v>120.1523257966994</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -16360,10 +16523,10 @@
         <v>45112</v>
       </c>
       <c r="B114">
-        <v>120.7519836425781</v>
+        <v>120.7519760131836</v>
       </c>
       <c r="C114">
-        <v>122.0062073047375</v>
+        <v>122.0061995960981</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -16371,10 +16534,10 @@
         <v>45113</v>
       </c>
       <c r="B115">
-        <v>119.1254348754883</v>
+        <v>119.1254272460938</v>
       </c>
       <c r="C115">
-        <v>120.3627639418836</v>
+        <v>120.3627562332443</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -16382,10 +16545,10 @@
         <v>45114</v>
       </c>
       <c r="B116">
-        <v>118.5005874633789</v>
+        <v>118.5006103515625</v>
       </c>
       <c r="C116">
-        <v>119.731426380413</v>
+        <v>119.731449506331</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -16415,10 +16578,10 @@
         <v>45119</v>
       </c>
       <c r="B119">
-        <v>117.9551086425781</v>
+        <v>117.9550933837891</v>
       </c>
       <c r="C119">
-        <v>119.180281793936</v>
+        <v>119.1802663766574</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -16448,10 +16611,10 @@
         <v>45124</v>
       </c>
       <c r="B122">
-        <v>123.6282043457031</v>
+        <v>123.6282119750977</v>
       </c>
       <c r="C122">
-        <v>124.9123026646145</v>
+        <v>124.9123103732539</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -16492,10 +16655,10 @@
         <v>45128</v>
       </c>
       <c r="B126">
-        <v>119.0361633300781</v>
+        <v>119.0361785888672</v>
       </c>
       <c r="C126">
-        <v>120.2725651530342</v>
+        <v>120.2725805703129</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -16525,10 +16688,10 @@
         <v>45133</v>
       </c>
       <c r="B129">
-        <v>128.2103576660156</v>
+        <v>128.2103424072266</v>
       </c>
       <c r="C129">
-        <v>129.5420497796177</v>
+        <v>129.5420343623391</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -16569,10 +16732,10 @@
         <v>45139</v>
       </c>
       <c r="B133">
-        <v>130.4716491699219</v>
+        <v>130.4716644287109</v>
       </c>
       <c r="C133">
-        <v>131.8268288091586</v>
+        <v>131.8268442264373</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -16580,10 +16743,10 @@
         <v>45140</v>
       </c>
       <c r="B134">
-        <v>127.3276519775391</v>
+        <v>127.32763671875</v>
       </c>
       <c r="C134">
-        <v>128.65017562593</v>
+        <v>128.6501602086513</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -16602,10 +16765,10 @@
         <v>45142</v>
       </c>
       <c r="B136">
-        <v>127.0598602294922</v>
+        <v>127.0598526000977</v>
       </c>
       <c r="C136">
-        <v>128.3796023852997</v>
+        <v>128.3795946766604</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -16624,10 +16787,10 @@
         <v>45146</v>
       </c>
       <c r="B138">
-        <v>130.3228607177734</v>
+        <v>130.3228759765625</v>
       </c>
       <c r="C138">
-        <v>131.6764949248631</v>
+        <v>131.6765103421418</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -16646,10 +16809,10 @@
         <v>45148</v>
       </c>
       <c r="B140">
-        <v>128.6269226074219</v>
+        <v>128.6268920898438</v>
       </c>
       <c r="C140">
-        <v>129.9629414872648</v>
+        <v>129.9629106527074</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -16668,10 +16831,10 @@
         <v>45152</v>
       </c>
       <c r="B142">
-        <v>130.2534332275391</v>
+        <v>130.2534484863281</v>
       </c>
       <c r="C142">
-        <v>131.6063463069219</v>
+        <v>131.6063617242006</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -16679,10 +16842,10 @@
         <v>45153</v>
       </c>
       <c r="B143">
-        <v>128.7161712646484</v>
+        <v>128.7161407470703</v>
       </c>
       <c r="C143">
-        <v>130.0531171501962</v>
+        <v>130.0530863156389</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -16690,10 +16853,10 @@
         <v>45154</v>
       </c>
       <c r="B144">
-        <v>127.6450119018555</v>
+        <v>127.6450042724609</v>
       </c>
       <c r="C144">
-        <v>128.9708318963145</v>
+        <v>128.9708241876752</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -16712,10 +16875,10 @@
         <v>45156</v>
       </c>
       <c r="B146">
-        <v>126.415168762207</v>
+        <v>126.4151840209961</v>
       </c>
       <c r="C146">
-        <v>127.7282146529208</v>
+        <v>127.7282300701995</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -16723,10 +16886,10 @@
         <v>45159</v>
       </c>
       <c r="B147">
-        <v>127.3177261352539</v>
+        <v>127.3177185058594</v>
       </c>
       <c r="C147">
-        <v>128.6401466861562</v>
+        <v>128.6401389775168</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -16756,10 +16919,10 @@
         <v>45162</v>
       </c>
       <c r="B150">
-        <v>128.7161712646484</v>
+        <v>128.7161407470703</v>
       </c>
       <c r="C150">
-        <v>130.0531171501962</v>
+        <v>130.0530863156389</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -16778,10 +16941,10 @@
         <v>45166</v>
       </c>
       <c r="B152">
-        <v>129.9360656738281</v>
+        <v>129.9360809326172</v>
       </c>
       <c r="C152">
-        <v>131.2856823278981</v>
+        <v>131.2856977451767</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -16789,10 +16952,10 @@
         <v>45167</v>
       </c>
       <c r="B153">
-        <v>133.4669342041016</v>
+        <v>133.4669036865234</v>
       </c>
       <c r="C153">
-        <v>134.8532251944851</v>
+        <v>134.8531943599278</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -16811,10 +16974,10 @@
         <v>45169</v>
       </c>
       <c r="B155">
-        <v>135.0538024902344</v>
+        <v>135.0537719726562</v>
       </c>
       <c r="C155">
-        <v>136.4565759241618</v>
+        <v>136.4565450896044</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -16822,10 +16985,10 @@
         <v>45170</v>
       </c>
       <c r="B156">
-        <v>134.5479431152344</v>
+        <v>134.5479583740234</v>
       </c>
       <c r="C156">
-        <v>135.9454623017473</v>
+        <v>135.945477719026</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -16833,10 +16996,10 @@
         <v>45174</v>
       </c>
       <c r="B157">
-        <v>134.6570739746094</v>
+        <v>134.6570892333984</v>
       </c>
       <c r="C157">
-        <v>136.0557266787836</v>
+        <v>136.0557420960623</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -16866,10 +17029,10 @@
         <v>45177</v>
       </c>
       <c r="B160">
-        <v>135.2620697021484</v>
+        <v>135.2620849609375</v>
       </c>
       <c r="C160">
-        <v>136.6670063607067</v>
+        <v>136.6670217779853</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -16877,10 +17040,10 @@
         <v>45180</v>
       </c>
       <c r="B161">
-        <v>135.7976379394531</v>
+        <v>135.7976226806641</v>
       </c>
       <c r="C161">
-        <v>137.2081374246885</v>
+        <v>137.2081220074099</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -16888,10 +17051,10 @@
         <v>45181</v>
       </c>
       <c r="B162">
-        <v>134.2305755615234</v>
+        <v>134.2305908203125</v>
       </c>
       <c r="C162">
-        <v>135.6247983227234</v>
+        <v>135.6248137400021</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -16899,10 +17062,10 @@
         <v>45182</v>
       </c>
       <c r="B163">
-        <v>135.58935546875</v>
+        <v>135.5893707275391</v>
       </c>
       <c r="C163">
-        <v>136.997691570865</v>
+        <v>136.9977069881436</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -16910,10 +17073,10 @@
         <v>45183</v>
       </c>
       <c r="B164">
-        <v>136.9679718017578</v>
+        <v>136.9679565429688</v>
       </c>
       <c r="C164">
-        <v>138.3906272812754</v>
+        <v>138.3906118639968</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -16921,10 +17084,10 @@
         <v>45184</v>
       </c>
       <c r="B165">
-        <v>136.2736968994141</v>
+        <v>136.2737121582031</v>
       </c>
       <c r="C165">
-        <v>137.6891411018636</v>
+        <v>137.6891565191423</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -16954,10 +17117,10 @@
         <v>45189</v>
       </c>
       <c r="B168">
-        <v>132.6437072753906</v>
+        <v>132.6436767578125</v>
       </c>
       <c r="C168">
-        <v>134.0214475930468</v>
+        <v>134.0214167584894</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -16976,10 +17139,10 @@
         <v>45191</v>
       </c>
       <c r="B170">
-        <v>129.1822967529297</v>
+        <v>129.1823120117188</v>
       </c>
       <c r="C170">
-        <v>130.5240841789582</v>
+        <v>130.5240995962369</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -16987,10 +17150,10 @@
         <v>45194</v>
       </c>
       <c r="B171">
-        <v>130.0352478027344</v>
+        <v>130.0352630615234</v>
       </c>
       <c r="C171">
-        <v>131.3858946392426</v>
+        <v>131.3859100565213</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -16998,10 +17161,10 @@
         <v>45195</v>
       </c>
       <c r="B172">
-        <v>127.5160903930664</v>
+        <v>127.5161056518555</v>
       </c>
       <c r="C172">
-        <v>128.8405713088453</v>
+        <v>128.8405867261239</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -17031,10 +17194,10 @@
         <v>45198</v>
       </c>
       <c r="B175">
-        <v>129.7873229980469</v>
+        <v>129.7873077392578</v>
       </c>
       <c r="C175">
-        <v>131.1353946954386</v>
+        <v>131.1353792781599</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -17064,10 +17227,10 @@
         <v>45203</v>
       </c>
       <c r="B178">
-        <v>134.1314239501953</v>
+        <v>134.1314086914062</v>
       </c>
       <c r="C178">
-        <v>135.5246168459362</v>
+        <v>135.5246014286575</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -17119,10 +17282,10 @@
         <v>45210</v>
       </c>
       <c r="B183">
-        <v>139.3979034423828</v>
+        <v>139.3978729248047</v>
       </c>
       <c r="C183">
-        <v>140.8457980746594</v>
+        <v>140.8457672401021</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -17130,10 +17293,10 @@
         <v>45211</v>
       </c>
       <c r="B184">
-        <v>137.830810546875</v>
+        <v>137.8308258056641</v>
       </c>
       <c r="C184">
-        <v>139.262428138137</v>
+        <v>139.2624435554156</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -17141,10 +17304,10 @@
         <v>45212</v>
       </c>
       <c r="B185">
-        <v>136.2340393066406</v>
+        <v>136.2340240478516</v>
       </c>
       <c r="C185">
-        <v>137.6490715946045</v>
+        <v>137.6490561773258</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -17163,10 +17326,10 @@
         <v>45216</v>
       </c>
       <c r="B187">
-        <v>138.5746765136719</v>
+        <v>138.5746917724609</v>
       </c>
       <c r="C187">
-        <v>140.0140204732211</v>
+        <v>140.0140358904997</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -17185,10 +17348,10 @@
         <v>45218</v>
       </c>
       <c r="B189">
-        <v>136.6208038330078</v>
+        <v>136.620849609375</v>
       </c>
       <c r="C189">
-        <v>138.0398533570122</v>
+        <v>138.0398996088482</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -17196,10 +17359,10 @@
         <v>45219</v>
       </c>
       <c r="B190">
-        <v>134.4884490966797</v>
+        <v>134.4884643554688</v>
       </c>
       <c r="C190">
-        <v>135.8853503322192</v>
+        <v>135.8853657494979</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -17218,10 +17381,10 @@
         <v>45223</v>
       </c>
       <c r="B192">
-        <v>137.6721343994141</v>
+        <v>137.6721649169922</v>
       </c>
       <c r="C192">
-        <v>139.1021038572644</v>
+        <v>139.1021346918217</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -17229,10 +17392,10 @@
         <v>45224</v>
       </c>
       <c r="B193">
-        <v>124.5803298950195</v>
+        <v>124.5803375244141</v>
       </c>
       <c r="C193">
-        <v>125.8743177276041</v>
+        <v>125.8743254362435</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -17240,10 +17403,10 @@
         <v>45225</v>
       </c>
       <c r="B194">
-        <v>121.2776336669922</v>
+        <v>121.2776412963867</v>
       </c>
       <c r="C194">
-        <v>122.5373171375849</v>
+        <v>122.5373248462242</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -17251,10 +17414,10 @@
         <v>45226</v>
       </c>
       <c r="B195">
-        <v>121.1685333251953</v>
+        <v>121.1685485839844</v>
       </c>
       <c r="C195">
-        <v>122.4270835951059</v>
+        <v>122.4270990123846</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -17295,10 +17458,10 @@
         <v>45232</v>
       </c>
       <c r="B199">
-        <v>126.4449234008789</v>
+        <v>126.4449310302734</v>
       </c>
       <c r="C199">
-        <v>127.7582783463242</v>
+        <v>127.7582860549635</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -17306,10 +17469,10 @@
         <v>45233</v>
       </c>
       <c r="B200">
-        <v>128.041748046875</v>
+        <v>128.0417327880859</v>
       </c>
       <c r="C200">
-        <v>129.371688850332</v>
+        <v>129.3716734330533</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -17317,10 +17480,10 @@
         <v>45236</v>
       </c>
       <c r="B201">
-        <v>129.1822967529297</v>
+        <v>129.1823120117188</v>
       </c>
       <c r="C201">
-        <v>130.5240841789582</v>
+        <v>130.5240995962369</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -17361,10 +17524,10 @@
         <v>45240</v>
       </c>
       <c r="B205">
-        <v>131.5031127929688</v>
+        <v>131.5031280517578</v>
       </c>
       <c r="C205">
-        <v>132.8690060125845</v>
+        <v>132.8690214298632</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -17383,10 +17546,10 @@
         <v>45244</v>
       </c>
       <c r="B207">
-        <v>132.524658203125</v>
+        <v>132.5246734619141</v>
       </c>
       <c r="C207">
-        <v>133.901161984876</v>
+        <v>133.9011774021546</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -17394,10 +17557,10 @@
         <v>45245</v>
       </c>
       <c r="B208">
-        <v>133.5164794921875</v>
+        <v>133.5164947509766</v>
       </c>
       <c r="C208">
-        <v>134.9032850983214</v>
+        <v>134.9033005156001</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -17405,10 +17568,10 @@
         <v>45246</v>
       </c>
       <c r="B209">
-        <v>135.8075561523438</v>
+        <v>135.8075714111328</v>
       </c>
       <c r="C209">
-        <v>137.218158655823</v>
+        <v>137.2181740731016</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -17416,10 +17579,10 @@
         <v>45247</v>
       </c>
       <c r="B210">
-        <v>134.2008361816406</v>
+        <v>134.2008209228516</v>
       </c>
       <c r="C210">
-        <v>135.5947500465987</v>
+        <v>135.59473462932</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -17449,10 +17612,10 @@
         <v>45252</v>
       </c>
       <c r="B213">
-        <v>137.3547668457031</v>
+        <v>137.3547515869141</v>
       </c>
       <c r="C213">
-        <v>138.7814398782405</v>
+        <v>138.7814244609618</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -17460,10 +17623,10 @@
         <v>45254</v>
       </c>
       <c r="B214">
-        <v>135.5695343017578</v>
+        <v>135.5695190429688</v>
       </c>
       <c r="C214">
-        <v>136.9776645258747</v>
+        <v>136.9776491085961</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -17471,10 +17634,10 @@
         <v>45257</v>
       </c>
       <c r="B215">
-        <v>135.2918243408203</v>
+        <v>135.2918090820312</v>
       </c>
       <c r="C215">
-        <v>136.69707005411</v>
+        <v>136.6970546368314</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -17482,10 +17645,10 @@
         <v>45258</v>
       </c>
       <c r="B216">
-        <v>136.0753479003906</v>
+        <v>136.0753326416016</v>
       </c>
       <c r="C216">
-        <v>137.4887318964532</v>
+        <v>137.4887164791746</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -17493,10 +17656,10 @@
         <v>45259</v>
       </c>
       <c r="B217">
-        <v>133.8834381103516</v>
+        <v>133.8834533691406</v>
       </c>
       <c r="C217">
-        <v>135.2740552330175</v>
+        <v>135.2740706502962</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -17504,10 +17667,10 @@
         <v>45260</v>
       </c>
       <c r="B218">
-        <v>131.443603515625</v>
+        <v>131.4436187744141</v>
       </c>
       <c r="C218">
-        <v>132.8088786257778</v>
+        <v>132.8088940430565</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -17515,10 +17678,10 @@
         <v>45261</v>
       </c>
       <c r="B219">
-        <v>130.7791137695312</v>
+        <v>130.7790985107422</v>
       </c>
       <c r="C219">
-        <v>132.1374869743267</v>
+        <v>132.137471557048</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -17526,10 +17689,10 @@
         <v>45264</v>
       </c>
       <c r="B220">
-        <v>128.2103576660156</v>
+        <v>128.2103424072266</v>
       </c>
       <c r="C220">
-        <v>129.5420497796177</v>
+        <v>129.5420343623391</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -17548,10 +17711,10 @@
         <v>45266</v>
       </c>
       <c r="B222">
-        <v>128.9542083740234</v>
+        <v>128.9541931152344</v>
       </c>
       <c r="C222">
-        <v>130.2936266974231</v>
+        <v>130.2936112801445</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -17559,10 +17722,10 @@
         <v>45267</v>
       </c>
       <c r="B223">
-        <v>135.8075561523438</v>
+        <v>135.8075714111328</v>
       </c>
       <c r="C223">
-        <v>137.218158655823</v>
+        <v>137.2181740731016</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -17570,10 +17733,10 @@
         <v>45268</v>
       </c>
       <c r="B224">
-        <v>133.8834381103516</v>
+        <v>133.8834533691406</v>
       </c>
       <c r="C224">
-        <v>135.2740552330175</v>
+        <v>135.2740706502962</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -17592,10 +17755,10 @@
         <v>45272</v>
       </c>
       <c r="B226">
-        <v>131.4337005615234</v>
+        <v>131.4337310791016</v>
       </c>
       <c r="C226">
-        <v>132.798872811922</v>
+        <v>132.7989036464793</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -17614,10 +17777,10 @@
         <v>45274</v>
       </c>
       <c r="B228">
-        <v>130.8584594726562</v>
+        <v>130.8584442138672</v>
       </c>
       <c r="C228">
-        <v>132.2176568234023</v>
+        <v>132.2176414061236</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -17625,10 +17788,10 @@
         <v>45275</v>
       </c>
       <c r="B229">
-        <v>131.5130462646484</v>
+        <v>131.5130615234375</v>
       </c>
       <c r="C229">
-        <v>132.8790426609976</v>
+        <v>132.8790580782763</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -17636,10 +17799,10 @@
         <v>45278</v>
       </c>
       <c r="B230">
-        <v>134.6867980957031</v>
+        <v>134.6868133544922</v>
       </c>
       <c r="C230">
-        <v>136.0857595376297</v>
+        <v>136.0857749549083</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -17647,10 +17810,10 @@
         <v>45279</v>
       </c>
       <c r="B231">
-        <v>135.5298461914062</v>
+        <v>135.5298309326172</v>
       </c>
       <c r="C231">
-        <v>136.9375641840583</v>
+        <v>136.9375487667796</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -17658,10 +17821,10 @@
         <v>45280</v>
       </c>
       <c r="B232">
-        <v>137.2059936523438</v>
+        <v>137.2060089111328</v>
       </c>
       <c r="C232">
-        <v>138.6311214112237</v>
+        <v>138.6311368285023</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -17669,10 +17832,10 @@
         <v>45281</v>
       </c>
       <c r="B233">
-        <v>139.2689361572266</v>
+        <v>139.2689208984375</v>
       </c>
       <c r="C233">
-        <v>140.7154912353542</v>
+        <v>140.7154758180755</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -17680,10 +17843,10 @@
         <v>45282</v>
       </c>
       <c r="B234">
-        <v>140.3302001953125</v>
+        <v>140.3301849365234</v>
       </c>
       <c r="C234">
-        <v>141.7877783840194</v>
+        <v>141.7877629667408</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -17691,10 +17854,10 @@
         <v>45286</v>
       </c>
       <c r="B235">
-        <v>140.3599243164062</v>
+        <v>140.3599395751953</v>
       </c>
       <c r="C235">
-        <v>141.8178112428654</v>
+        <v>141.8178266601441</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -17702,10 +17865,10 @@
         <v>45287</v>
       </c>
       <c r="B236">
-        <v>139.2193603515625</v>
+        <v>139.2193298339844</v>
       </c>
       <c r="C236">
-        <v>140.6654004969606</v>
+        <v>140.6653696624032</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -17713,10 +17876,10 @@
         <v>45288</v>
       </c>
       <c r="B237">
-        <v>139.0805053710938</v>
+        <v>139.0804901123047</v>
       </c>
       <c r="C237">
-        <v>140.5251032610782</v>
+        <v>140.5250878437995</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -17735,10 +17898,10 @@
         <v>45293</v>
       </c>
       <c r="B239">
-        <v>137.0373840332031</v>
+        <v>137.0373687744141</v>
       </c>
       <c r="C239">
-        <v>138.460760481938</v>
+        <v>138.4607450646593</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -17757,10 +17920,10 @@
         <v>45295</v>
       </c>
       <c r="B241">
-        <v>135.27197265625</v>
+        <v>135.2719879150391</v>
       </c>
       <c r="C241">
-        <v>136.6770121745625</v>
+        <v>136.6770275918411</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -17768,10 +17931,10 @@
         <v>45296</v>
       </c>
       <c r="B242">
-        <v>134.6173706054688</v>
+        <v>134.6174011230469</v>
       </c>
       <c r="C242">
-        <v>136.0156109196885</v>
+        <v>136.0156417542458</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -17779,10 +17942,10 @@
         <v>45299</v>
       </c>
       <c r="B243">
-        <v>137.701904296875</v>
+        <v>137.7018737792969</v>
       </c>
       <c r="C243">
-        <v>139.1321829679464</v>
+        <v>139.132152133389</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -17790,10 +17953,10 @@
         <v>45300</v>
       </c>
       <c r="B244">
-        <v>139.7946014404297</v>
+        <v>139.7945709228516</v>
       </c>
       <c r="C244">
-        <v>141.2466164854802</v>
+        <v>141.2465856509229</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -17812,10 +17975,10 @@
         <v>45302</v>
       </c>
       <c r="B246">
-        <v>140.9153594970703</v>
+        <v>140.9153442382812</v>
       </c>
       <c r="C246">
-        <v>142.3790156036736</v>
+        <v>142.3790001863949</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -17845,10 +18008,10 @@
         <v>45308</v>
       </c>
       <c r="B249">
-        <v>140.3103637695312</v>
+        <v>140.3103179931641</v>
       </c>
       <c r="C249">
-        <v>141.7677359217505</v>
+        <v>141.7676896699145</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -17856,10 +18019,10 @@
         <v>45309</v>
       </c>
       <c r="B250">
-        <v>142.3038787841797</v>
+        <v>142.3038635253906</v>
       </c>
       <c r="C250">
-        <v>143.7819571279398</v>
+        <v>143.7819417106612</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -17867,10 +18030,10 @@
         <v>45310</v>
       </c>
       <c r="B251">
-        <v>145.1800842285156</v>
+        <v>145.1800994873047</v>
       </c>
       <c r="C251">
-        <v>146.6880370705382</v>
+        <v>146.6880524878169</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -17889,10 +18052,10 @@
         <v>45314</v>
       </c>
       <c r="B253">
-        <v>145.8346710205078</v>
+        <v>145.8346557617188</v>
       </c>
       <c r="C253">
-        <v>147.3494229081335</v>
+        <v>147.3494074908548</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -17900,10 +18063,10 @@
         <v>45315</v>
       </c>
       <c r="B254">
-        <v>147.4810485839844</v>
+        <v>147.4810943603516</v>
       </c>
       <c r="C254">
-        <v>149.0129010246169</v>
+        <v>149.0129472764529</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -17911,10 +18074,10 @@
         <v>45316</v>
       </c>
       <c r="B255">
-        <v>150.6250762939453</v>
+        <v>150.6250915527344</v>
       </c>
       <c r="C255">
-        <v>152.1895850424029</v>
+        <v>152.1896004596816</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -17922,10 +18085,10 @@
         <v>45317</v>
       </c>
       <c r="B256">
-        <v>150.9424591064453</v>
+        <v>150.9424743652344</v>
       </c>
       <c r="C256">
-        <v>152.5102644387055</v>
+        <v>152.5102798559841</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -17933,10 +18096,10 @@
         <v>45320</v>
       </c>
       <c r="B257">
-        <v>152.2516479492188</v>
+        <v>152.2516174316406</v>
       </c>
       <c r="C257">
-        <v>153.8330515311748</v>
+        <v>153.8330206966174</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -17944,10 +18107,10 @@
         <v>45321</v>
       </c>
       <c r="B258">
-        <v>150.2184448242188</v>
+        <v>150.2184295654297</v>
       </c>
       <c r="C258">
-        <v>151.7787299831689</v>
+        <v>151.7787145658903</v>
       </c>
     </row>
   </sheetData>

--- a/resultats.xlsx
+++ b/resultats.xlsx
@@ -473,7 +473,8 @@
     <col min="1" max="1" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1">
@@ -535,19 +536,19 @@
         <v>4019.81005859375</v>
       </c>
       <c r="C5" s="1">
-        <v>138.8828735351562</v>
+        <v>138.8828582763672</v>
       </c>
       <c r="D5" s="1">
         <v>202</v>
       </c>
       <c r="E5" s="1">
-        <v>236.3760833740234</v>
+        <v>236.3760528564453</v>
       </c>
       <c r="F5" s="1">
         <v>97.51999664306641</v>
       </c>
       <c r="G5" s="1">
-        <v>98.97200775146484</v>
+        <v>98.97200012207031</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -564,7 +565,7 @@
         <v>214.6000061035156</v>
       </c>
       <c r="E6" s="1">
-        <v>401.670654296875</v>
+        <v>401.6706848144531</v>
       </c>
       <c r="F6" s="1">
         <v>159</v>
@@ -581,19 +582,19 @@
         <v>0.2251748572833444</v>
       </c>
       <c r="C7" s="3">
-        <v>0.3400257618579476</v>
+        <v>0.3400259090839674</v>
       </c>
       <c r="D7" s="3">
         <v>0.06237626783918626</v>
       </c>
       <c r="E7" s="3">
-        <v>0.699286359954201</v>
+        <v>0.6992867084483964</v>
       </c>
       <c r="F7" s="3">
         <v>0.6304348387331982</v>
       </c>
       <c r="G7" s="3">
-        <v>0.5177871828309498</v>
+        <v>0.5177872998316896</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="3" customFormat="1">
@@ -604,19 +605,19 @@
         <v>0.2212933175580829</v>
       </c>
       <c r="C8" s="3">
-        <v>0.3339114632793265</v>
+        <v>0.333911607543669</v>
       </c>
       <c r="D8" s="3">
         <v>0.06137232945653404</v>
       </c>
       <c r="E8" s="3">
-        <v>0.6852667650492092</v>
+        <v>0.6852671052679291</v>
       </c>
       <c r="F8" s="3">
         <v>0.6180286426432327</v>
       </c>
       <c r="G8" s="3">
-        <v>0.5079240262713609</v>
+        <v>0.5079241406955293</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="3" customFormat="1">
@@ -627,19 +628,19 @@
         <v>0.0007932952126940571</v>
       </c>
       <c r="C9" s="3">
-        <v>0.001143315777520086</v>
+        <v>0.001143316206692137</v>
       </c>
       <c r="D9" s="3">
         <v>0.0002363600048310617</v>
       </c>
       <c r="E9" s="3">
-        <v>0.002071126463531941</v>
+        <v>0.002071127264636061</v>
       </c>
       <c r="F9" s="3">
         <v>0.001909557622930636</v>
       </c>
       <c r="G9" s="3">
-        <v>0.001629896380396704</v>
+        <v>0.001629896681515417</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="3" customFormat="1">
@@ -650,19 +651,19 @@
         <v>0.1253305867413214</v>
       </c>
       <c r="C10" s="3">
-        <v>0.2005366250449454</v>
+        <v>0.2005366690122959</v>
       </c>
       <c r="D10" s="3">
         <v>0.0567447014935399</v>
       </c>
       <c r="E10" s="3">
-        <v>0.2370178833315305</v>
+        <v>0.2370178639279349</v>
       </c>
       <c r="F10" s="3">
         <v>0.3161577817349202</v>
       </c>
       <c r="G10" s="3">
-        <v>0.295824282479715</v>
+        <v>0.2958241860927493</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="3" customFormat="1">
@@ -673,19 +674,19 @@
         <v>0.007895084861603466</v>
       </c>
       <c r="C11" s="3">
-        <v>0.0126326199673603</v>
+        <v>0.01263262273704304</v>
       </c>
       <c r="D11" s="3">
         <v>0.003574580199345286</v>
       </c>
       <c r="E11" s="3">
-        <v>0.01493072322786074</v>
+        <v>0.01493072200554911</v>
       </c>
       <c r="F11" s="3">
         <v>0.01991606822686756</v>
       </c>
       <c r="G11" s="3">
-        <v>0.01863517817179637</v>
+        <v>0.01863517209998826</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -696,19 +697,19 @@
         <v>1.765676865574927</v>
       </c>
       <c r="C12" s="1">
-        <v>1.665089672295464</v>
+        <v>1.6650900266185</v>
       </c>
       <c r="D12" s="1">
         <v>1.081551719212427</v>
       </c>
       <c r="E12" s="1">
-        <v>2.891202787811109</v>
+        <v>2.891204459914819</v>
       </c>
       <c r="F12" s="1">
         <v>1.954810788625198</v>
       </c>
       <c r="G12" s="1">
-        <v>1.71697881598408</v>
+        <v>1.716979762216875</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="3" customFormat="1">
@@ -719,19 +720,19 @@
         <v>-0.1027661709329137</v>
       </c>
       <c r="C13" s="3">
-        <v>-0.1493237974798889</v>
+        <v>-0.1493236401017953</v>
       </c>
       <c r="D13" s="3">
         <v>-0.02974119167021968</v>
       </c>
       <c r="E13" s="3">
-        <v>-0.129875900169687</v>
+        <v>-0.1298759756200135</v>
       </c>
       <c r="F13" s="3">
         <v>-0.1964396385244207</v>
       </c>
       <c r="G13" s="3">
-        <v>-0.1727305232966189</v>
+        <v>-0.1727306660931956</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -739,22 +740,22 @@
         <v>22</v>
       </c>
       <c r="B14" s="1">
-        <v>291.2596969394553</v>
+        <v>281.8065128365591</v>
       </c>
       <c r="C14" s="1">
-        <v>463.1816923937729</v>
+        <v>477.3226911640876</v>
       </c>
       <c r="D14" s="1">
-        <v>135.9096651624703</v>
+        <v>136.368050303444</v>
       </c>
       <c r="E14" s="1">
-        <v>1623.325089552892</v>
+        <v>1640.707354991571</v>
       </c>
       <c r="F14" s="1">
-        <v>1592.366790028111</v>
+        <v>1347.676699482176</v>
       </c>
       <c r="G14" s="1">
-        <v>958.0454020042548</v>
+        <v>953.2319921016054</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -762,22 +763,22 @@
         <v>23</v>
       </c>
       <c r="B15" s="1">
-        <v>180.9055570008025</v>
+        <v>172.4089108020503</v>
       </c>
       <c r="C15" s="1">
-        <v>217.8374081283564</v>
+        <v>226.1296221361287</v>
       </c>
       <c r="D15" s="1">
-        <v>107.1628274839205</v>
+        <v>112.4875905927913</v>
       </c>
       <c r="E15" s="1">
-        <v>604.4691100543741</v>
+        <v>585.7725499788321</v>
       </c>
       <c r="F15" s="1">
-        <v>348.4489522193817</v>
+        <v>368.9152057443455</v>
       </c>
       <c r="G15" s="1">
-        <v>221.9091605405716</v>
+        <v>247.6704918040359</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -785,22 +786,22 @@
         <v>24</v>
       </c>
       <c r="B16" s="1">
-        <v>280.1007288216953</v>
+        <v>269.280615281568</v>
       </c>
       <c r="C16" s="1">
-        <v>395.7445344071994</v>
+        <v>442.2350825204397</v>
       </c>
       <c r="D16" s="1">
-        <v>132.7218588148095</v>
+        <v>135.5645468315637</v>
       </c>
       <c r="E16" s="1">
-        <v>1346.969171970037</v>
+        <v>1345.84104139986</v>
       </c>
       <c r="F16" s="1">
-        <v>1305.313901741338</v>
+        <v>1063.070311669332</v>
       </c>
       <c r="G16" s="1">
-        <v>885.101385054207</v>
+        <v>735.5035177628083</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -808,22 +809,22 @@
         <v>25</v>
       </c>
       <c r="B17" s="1">
-        <v>430.1776992587394</v>
+        <v>413.1424048339946</v>
       </c>
       <c r="C17" s="1">
-        <v>1017.137410973331</v>
+        <v>903.1246609120141</v>
       </c>
       <c r="D17" s="1">
-        <v>167.3250936442868</v>
+        <v>166.0721244291448</v>
       </c>
       <c r="E17" s="1">
-        <v>3347.418118195292</v>
+        <v>3400.707016549626</v>
       </c>
       <c r="F17" s="1">
-        <v>4084.292467457472</v>
+        <v>3258.446295319865</v>
       </c>
       <c r="G17" s="1">
-        <v>2106.930737225002</v>
+        <v>2214.917181848391</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="3" customFormat="1">
@@ -834,10 +835,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
         <v>0.01</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0.02</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
@@ -880,19 +881,19 @@
         <v>1</v>
       </c>
       <c r="C21" s="1">
-        <v>0.7060169733035652</v>
+        <v>0.7060165381290121</v>
       </c>
       <c r="D21" s="1">
         <v>0.004456046337864243</v>
       </c>
       <c r="E21" s="1">
-        <v>0.6246280571108986</v>
+        <v>0.6246277619651215</v>
       </c>
       <c r="F21" s="1">
         <v>0.6045950866477746</v>
       </c>
       <c r="G21" s="1">
-        <v>0.6008777233826612</v>
+        <v>0.6008778074911151</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -900,22 +901,22 @@
         <v>7</v>
       </c>
       <c r="B22" s="1">
-        <v>0.7060169733035652</v>
+        <v>0.7060165381290121</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>-0.05612589111334376</v>
+        <v>-0.05612555099858751</v>
       </c>
       <c r="E22" s="1">
-        <v>0.5536242649868754</v>
+        <v>0.5536231956682565</v>
       </c>
       <c r="F22" s="1">
-        <v>0.4276409112506135</v>
+        <v>0.4276403029312523</v>
       </c>
       <c r="G22" s="1">
-        <v>0.5177388014684229</v>
+        <v>0.5177398601059796</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -926,19 +927,19 @@
         <v>0.004456046337864243</v>
       </c>
       <c r="C23" s="1">
-        <v>-0.05612589111334376</v>
+        <v>-0.05612555099858751</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="E23" s="1">
-        <v>-0.04384083030588472</v>
+        <v>-0.04384018829302527</v>
       </c>
       <c r="F23" s="1">
         <v>-0.005269283798744161</v>
       </c>
       <c r="G23" s="1">
-        <v>-0.01599708220043846</v>
+        <v>-0.01599638681897387</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -946,22 +947,22 @@
         <v>9</v>
       </c>
       <c r="B24" s="1">
-        <v>0.6246280571108986</v>
+        <v>0.6246277619651215</v>
       </c>
       <c r="C24" s="1">
-        <v>0.5536242649868754</v>
+        <v>0.5536231956682565</v>
       </c>
       <c r="D24" s="1">
-        <v>-0.04384083030588472</v>
+        <v>-0.04384018829302527</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1">
-        <v>0.5709354222714931</v>
+        <v>0.5709347819284806</v>
       </c>
       <c r="G24" s="1">
-        <v>0.5011058975187479</v>
+        <v>0.5011048421180136</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -972,19 +973,19 @@
         <v>0.6045950866477746</v>
       </c>
       <c r="C25" s="1">
-        <v>0.4276409112506135</v>
+        <v>0.4276403029312523</v>
       </c>
       <c r="D25" s="1">
         <v>-0.005269283798744161</v>
       </c>
       <c r="E25" s="1">
-        <v>0.5709354222714931</v>
+        <v>0.5709347819284806</v>
       </c>
       <c r="F25" s="1">
         <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>0.6003321806866373</v>
+        <v>0.600332078067905</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -992,19 +993,19 @@
         <v>11</v>
       </c>
       <c r="B26" s="1">
-        <v>0.6008777233826612</v>
+        <v>0.6008778074911151</v>
       </c>
       <c r="C26" s="1">
-        <v>0.5177388014684229</v>
+        <v>0.5177398601059796</v>
       </c>
       <c r="D26" s="1">
-        <v>-0.01599708220043846</v>
+        <v>-0.01599638681897387</v>
       </c>
       <c r="E26" s="1">
-        <v>0.5011058975187479</v>
+        <v>0.5011048421180136</v>
       </c>
       <c r="F26" s="1">
-        <v>0.6003321806866373</v>
+        <v>0.600332078067905</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -3895,7 +3896,7 @@
         <v>44949</v>
       </c>
       <c r="B2" s="1">
-        <v>138.8828735351562</v>
+        <v>138.8828582763672</v>
       </c>
       <c r="C2" s="1">
         <v>100</v>
@@ -3906,10 +3907,10 @@
         <v>44950</v>
       </c>
       <c r="B3" s="1">
-        <v>140.2804718017578</v>
+        <v>140.2804412841797</v>
       </c>
       <c r="C3" s="1">
-        <v>101.0063143359774</v>
+        <v>101.006303459734</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3920,7 +3921,7 @@
         <v>139.6210174560547</v>
       </c>
       <c r="C4" s="1">
-        <v>100.531486642024</v>
+        <v>100.5314976872226</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3931,7 +3932,7 @@
         <v>141.6878967285156</v>
       </c>
       <c r="C5" s="1">
-        <v>102.019704173711</v>
+        <v>102.0197153824172</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3939,10 +3940,10 @@
         <v>44953</v>
       </c>
       <c r="B6" s="1">
-        <v>143.6267700195312</v>
+        <v>143.6268005371094</v>
       </c>
       <c r="C6" s="1">
-        <v>103.415753406898</v>
+        <v>103.4157867425958</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3950,10 +3951,10 @@
         <v>44956</v>
       </c>
       <c r="B7" s="1">
-        <v>140.7430267333984</v>
+        <v>140.7430419921875</v>
       </c>
       <c r="C7" s="1">
-        <v>101.3393683115084</v>
+        <v>101.3393904322726</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3961,10 +3962,10 @@
         <v>44957</v>
       </c>
       <c r="B8" s="1">
-        <v>142.0126647949219</v>
+        <v>142.0126495361328</v>
       </c>
       <c r="C8" s="1">
-        <v>102.2535473093976</v>
+        <v>102.2535475569905</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3972,10 +3973,10 @@
         <v>44958</v>
       </c>
       <c r="B9" s="1">
-        <v>143.1347045898438</v>
+        <v>143.1346740722656</v>
       </c>
       <c r="C9" s="1">
-        <v>103.06145095249</v>
+        <v>103.0614403020405</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3983,10 +3984,10 @@
         <v>44959</v>
       </c>
       <c r="B10" s="1">
-        <v>148.4396209716797</v>
+        <v>148.4395751953125</v>
       </c>
       <c r="C10" s="1">
-        <v>106.8811561809342</v>
+        <v>106.8811349633431</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3994,10 +3995,10 @@
         <v>44960</v>
       </c>
       <c r="B11" s="1">
-        <v>152.0615386962891</v>
+        <v>152.0615692138672</v>
       </c>
       <c r="C11" s="1">
-        <v>109.4890498919558</v>
+        <v>109.4890838949147</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4005,10 +4006,10 @@
         <v>44963</v>
       </c>
       <c r="B12" s="1">
-        <v>149.3352813720703</v>
+        <v>149.3352508544922</v>
       </c>
       <c r="C12" s="1">
-        <v>107.5260596003352</v>
+        <v>107.5260494404036</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4016,10 +4017,10 @@
         <v>44964</v>
       </c>
       <c r="B13" s="1">
-        <v>152.2091369628906</v>
+        <v>152.2091674804688</v>
       </c>
       <c r="C13" s="1">
-        <v>109.5953252467526</v>
+        <v>109.5953592613879</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4030,7 +4031,7 @@
         <v>149.5222473144531</v>
       </c>
       <c r="C14" s="1">
-        <v>107.6606809093734</v>
+        <v>107.6606927378426</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4038,10 +4039,10 @@
         <v>44966</v>
       </c>
       <c r="B15" s="1">
-        <v>148.4888153076172</v>
+        <v>148.4888458251953</v>
       </c>
       <c r="C15" s="1">
-        <v>106.9165776369318</v>
+        <v>106.9166113572583</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4049,10 +4050,10 @@
         <v>44967</v>
       </c>
       <c r="B16" s="1">
-        <v>148.8535614013672</v>
+        <v>148.8535308837891</v>
       </c>
       <c r="C16" s="1">
-        <v>107.1792061990185</v>
+        <v>107.1791960009787</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4063,7 +4064,7 @@
         <v>151.6529998779297</v>
       </c>
       <c r="C17" s="1">
-        <v>109.1948892024767</v>
+        <v>109.1949011995064</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4071,10 +4072,10 @@
         <v>44971</v>
       </c>
       <c r="B18" s="1">
-        <v>151.0122833251953</v>
+        <v>151.0122528076172</v>
       </c>
       <c r="C18" s="1">
-        <v>108.7335533037979</v>
+        <v>108.7335432765312</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4082,10 +4083,10 @@
         <v>44972</v>
       </c>
       <c r="B19" s="1">
-        <v>153.1118469238281</v>
+        <v>153.1118621826172</v>
       </c>
       <c r="C19" s="1">
-        <v>110.2453045695876</v>
+        <v>110.2453276688296</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4096,7 +4097,7 @@
         <v>151.5149993896484</v>
       </c>
       <c r="C20" s="1">
-        <v>109.0955245473766</v>
+        <v>109.0955365334894</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4107,7 +4108,7 @@
         <v>150.3715515136719</v>
       </c>
       <c r="C21" s="1">
-        <v>108.2722064183151</v>
+        <v>108.2722183139715</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4115,10 +4116,10 @@
         <v>44978</v>
       </c>
       <c r="B22" s="1">
-        <v>146.3596496582031</v>
+        <v>146.3596649169922</v>
       </c>
       <c r="C22" s="1">
-        <v>105.3835119714413</v>
+        <v>105.3835345365277</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4126,10 +4127,10 @@
         <v>44979</v>
       </c>
       <c r="B23" s="1">
-        <v>146.7835388183594</v>
+        <v>146.7835235595703</v>
       </c>
       <c r="C23" s="1">
-        <v>105.6887253857137</v>
+        <v>105.6887260107229</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4137,10 +4138,10 @@
         <v>44980</v>
       </c>
       <c r="B24" s="1">
-        <v>147.2665252685547</v>
+        <v>147.2665710449219</v>
       </c>
       <c r="C24" s="1">
-        <v>106.0364906917599</v>
+        <v>106.0365353021981</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4148,10 +4149,10 @@
         <v>44981</v>
       </c>
       <c r="B25" s="1">
-        <v>144.6149749755859</v>
+        <v>144.6149444580078</v>
       </c>
       <c r="C25" s="1">
-        <v>104.127291792374</v>
+        <v>104.1272812590263</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4159,10 +4160,10 @@
         <v>44984</v>
       </c>
       <c r="B26" s="1">
-        <v>145.8076782226562</v>
+        <v>145.8076934814453</v>
       </c>
       <c r="C26" s="1">
-        <v>104.9860753246491</v>
+        <v>104.9860978460698</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4173,7 +4174,7 @@
         <v>145.3049468994141</v>
       </c>
       <c r="C27" s="1">
-        <v>104.6240930942663</v>
+        <v>104.6241045891116</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4181,10 +4182,10 @@
         <v>44986</v>
       </c>
       <c r="B28" s="1">
-        <v>143.2349090576172</v>
+        <v>143.2349395751953</v>
       </c>
       <c r="C28" s="1">
-        <v>103.1336012941576</v>
+        <v>103.1336345988558</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -4192,10 +4193,10 @@
         <v>44987</v>
       </c>
       <c r="B29" s="1">
-        <v>143.8264007568359</v>
+        <v>143.8263854980469</v>
       </c>
       <c r="C29" s="1">
-        <v>103.5594937632309</v>
+        <v>103.5594941543055</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -4203,10 +4204,10 @@
         <v>44988</v>
       </c>
       <c r="B30" s="1">
-        <v>148.8732604980469</v>
+        <v>148.8732452392578</v>
       </c>
       <c r="C30" s="1">
-        <v>107.1933901629431</v>
+        <v>107.1933909532669</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -4214,10 +4215,10 @@
         <v>44991</v>
       </c>
       <c r="B31" s="1">
-        <v>151.6332550048828</v>
+        <v>151.6332855224609</v>
       </c>
       <c r="C31" s="1">
-        <v>109.1806722781402</v>
+        <v>109.1807062472183</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -4228,7 +4229,7 @@
         <v>149.4351196289062</v>
       </c>
       <c r="C32" s="1">
-        <v>107.5979462587076</v>
+        <v>107.5979580802843</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -4236,10 +4237,10 @@
         <v>44993</v>
       </c>
       <c r="B33" s="1">
-        <v>150.6869964599609</v>
+        <v>150.6869659423828</v>
       </c>
       <c r="C33" s="1">
-        <v>108.4993366167763</v>
+        <v>108.4993265637767</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -4247,10 +4248,10 @@
         <v>44994</v>
       </c>
       <c r="B34" s="1">
-        <v>148.4395446777344</v>
+        <v>148.4395141601562</v>
       </c>
       <c r="C34" s="1">
-        <v>106.8811012469143</v>
+        <v>106.8810910161224</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -4258,10 +4259,10 @@
         <v>44995</v>
       </c>
       <c r="B35" s="1">
-        <v>146.3793792724609</v>
+        <v>146.3793640136719</v>
       </c>
       <c r="C35" s="1">
-        <v>105.3977179089739</v>
+        <v>105.3977185020106</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -4269,10 +4270,10 @@
         <v>44998</v>
       </c>
       <c r="B36" s="1">
-        <v>148.3212432861328</v>
+        <v>148.3212585449219</v>
       </c>
       <c r="C36" s="1">
-        <v>106.7959205557389</v>
+        <v>106.7959432760038</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -4280,10 +4281,10 @@
         <v>44999</v>
       </c>
       <c r="B37" s="1">
-        <v>150.4109802246094</v>
+        <v>150.4109649658203</v>
       </c>
       <c r="C37" s="1">
-        <v>108.3005963197722</v>
+        <v>108.3005972317426</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -4291,10 +4292,10 @@
         <v>45000</v>
       </c>
       <c r="B38" s="1">
-        <v>150.8052673339844</v>
+        <v>150.8052825927734</v>
       </c>
       <c r="C38" s="1">
-        <v>108.5844953343438</v>
+        <v>108.584518251116</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -4302,10 +4303,10 @@
         <v>45001</v>
       </c>
       <c r="B39" s="1">
-        <v>153.6244049072266</v>
+        <v>153.6244354248047</v>
       </c>
       <c r="C39" s="1">
-        <v>110.6143623017266</v>
+        <v>110.6143964283215</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -4316,7 +4317,7 @@
         <v>152.7865447998047</v>
       </c>
       <c r="C40" s="1">
-        <v>110.011076895762</v>
+        <v>110.0110889824647</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -4324,10 +4325,10 @@
         <v>45005</v>
       </c>
       <c r="B41" s="1">
-        <v>155.1522674560547</v>
+        <v>155.1522979736328</v>
       </c>
       <c r="C41" s="1">
-        <v>111.7144709831915</v>
+        <v>111.7145052306531</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -4338,7 +4339,7 @@
         <v>157.0054168701172</v>
       </c>
       <c r="C42" s="1">
-        <v>113.0487963516779</v>
+        <v>113.0488087721289</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -4346,10 +4347,10 @@
         <v>45007</v>
       </c>
       <c r="B43" s="1">
-        <v>155.5761566162109</v>
+        <v>155.576171875</v>
       </c>
       <c r="C43" s="1">
-        <v>112.0196843974639</v>
+        <v>112.0197076916536</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -4357,10 +4358,10 @@
         <v>45008</v>
       </c>
       <c r="B44" s="1">
-        <v>156.660400390625</v>
+        <v>156.6604156494141</v>
       </c>
       <c r="C44" s="1">
-        <v>112.8003737271238</v>
+        <v>112.8003971070863</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -4368,10 +4369,10 @@
         <v>45009</v>
       </c>
       <c r="B45" s="1">
-        <v>157.9615783691406</v>
+        <v>157.9616088867188</v>
       </c>
       <c r="C45" s="1">
-        <v>113.737262448818</v>
+        <v>113.7372969185198</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -4379,10 +4380,10 @@
         <v>45012</v>
       </c>
       <c r="B46" s="1">
-        <v>156.0197143554688</v>
+        <v>156.0197296142578</v>
       </c>
       <c r="C46" s="1">
-        <v>112.3390598020529</v>
+        <v>112.3390831313318</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -4390,10 +4391,10 @@
         <v>45013</v>
       </c>
       <c r="B47" s="1">
-        <v>155.3986968994141</v>
+        <v>155.3987274169922</v>
       </c>
       <c r="C47" s="1">
-        <v>111.8919078672987</v>
+        <v>111.891942134255</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -4401,10 +4402,10 @@
         <v>45014</v>
       </c>
       <c r="B48" s="1">
-        <v>158.4741821289062</v>
+        <v>158.4741668701172</v>
       </c>
       <c r="C48" s="1">
-        <v>114.106353141369</v>
+        <v>114.1063546912065</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -4412,10 +4413,10 @@
         <v>45015</v>
       </c>
       <c r="B49" s="1">
-        <v>160.0414581298828</v>
+        <v>160.0414886474609</v>
       </c>
       <c r="C49" s="1">
-        <v>115.234840737487</v>
+        <v>115.2348753717248</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -4423,10 +4424,10 @@
         <v>45016</v>
       </c>
       <c r="B50" s="1">
-        <v>162.5451812744141</v>
+        <v>162.5451507568359</v>
       </c>
       <c r="C50" s="1">
-        <v>117.0375994800166</v>
+        <v>117.0375903650992</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -4434,10 +4435,10 @@
         <v>45019</v>
       </c>
       <c r="B51" s="1">
-        <v>163.7970733642578</v>
+        <v>163.7970581054688</v>
       </c>
       <c r="C51" s="1">
-        <v>117.9390008248892</v>
+        <v>117.9390027958123</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -4448,7 +4449,7 @@
         <v>163.2647857666016</v>
       </c>
       <c r="C52" s="1">
-        <v>117.5557371552176</v>
+        <v>117.5557500708374</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -4456,10 +4457,10 @@
         <v>45021</v>
       </c>
       <c r="B53" s="1">
-        <v>161.4214630126953</v>
+        <v>161.4214477539062</v>
       </c>
       <c r="C53" s="1">
-        <v>116.2284872884875</v>
+        <v>116.2284890714798</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -4470,7 +4471,7 @@
         <v>162.3086090087891</v>
       </c>
       <c r="C54" s="1">
-        <v>116.8672600712736</v>
+        <v>116.8672729112518</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -4478,10 +4479,10 @@
         <v>45026</v>
       </c>
       <c r="B55" s="1">
-        <v>159.7161560058594</v>
+        <v>159.7161865234375</v>
       </c>
       <c r="C55" s="1">
-        <v>115.0006130636615</v>
+        <v>115.0006476721652</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -4489,10 +4490,10 @@
         <v>45027</v>
       </c>
       <c r="B56" s="1">
-        <v>158.5037536621094</v>
+        <v>158.5037384033203</v>
       </c>
       <c r="C56" s="1">
-        <v>114.1276455674618</v>
+        <v>114.1276471196387</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -4503,7 +4504,7 @@
         <v>157.8137359619141</v>
       </c>
       <c r="C57" s="1">
-        <v>113.6308113051576</v>
+        <v>113.6308237895535</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -4514,7 +4515,7 @@
         <v>163.1957702636719</v>
       </c>
       <c r="C58" s="1">
-        <v>117.5060438408636</v>
+        <v>117.5060567510237</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -4525,7 +4526,7 @@
         <v>162.8507843017578</v>
       </c>
       <c r="C59" s="1">
-        <v>117.2576431899174</v>
+        <v>117.2576560727863</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -4533,10 +4534,10 @@
         <v>45033</v>
       </c>
       <c r="B60" s="1">
-        <v>162.8704681396484</v>
+        <v>162.8704833984375</v>
       </c>
       <c r="C60" s="1">
-        <v>117.2718161670381</v>
+        <v>117.2718400382692</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -4544,10 +4545,10 @@
         <v>45034</v>
       </c>
       <c r="B61" s="1">
-        <v>164.0927581787109</v>
+        <v>164.0927886962891</v>
       </c>
       <c r="C61" s="1">
-        <v>118.15190311221</v>
+        <v>118.1519380669397</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -4555,10 +4556,10 @@
         <v>45035</v>
       </c>
       <c r="B62" s="1">
-        <v>165.2362213134766</v>
+        <v>165.2362060546875</v>
       </c>
       <c r="C62" s="1">
-        <v>118.9752322280755</v>
+        <v>118.9752343128473</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -4569,7 +4570,7 @@
         <v>164.2701873779297</v>
       </c>
       <c r="C63" s="1">
-        <v>118.2796576687672</v>
+        <v>118.2796706639228</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -4577,10 +4578,10 @@
         <v>45037</v>
       </c>
       <c r="B64" s="1">
-        <v>162.6634979248047</v>
+        <v>162.6634674072266</v>
       </c>
       <c r="C64" s="1">
-        <v>117.1227911579959</v>
+        <v>117.1227820524385</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -4588,10 +4589,10 @@
         <v>45040</v>
       </c>
       <c r="B65" s="1">
-        <v>162.9690551757812</v>
+        <v>162.9690399169922</v>
       </c>
       <c r="C65" s="1">
-        <v>117.342801907485</v>
+        <v>117.3428038129048</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -4599,10 +4600,10 @@
         <v>45041</v>
       </c>
       <c r="B66" s="1">
-        <v>161.4313507080078</v>
+        <v>161.4313201904297</v>
       </c>
       <c r="C66" s="1">
-        <v>116.2356067374598</v>
+        <v>116.2355975344291</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -4610,10 +4611,10 @@
         <v>45042</v>
       </c>
       <c r="B67" s="1">
-        <v>161.4214630126953</v>
+        <v>161.4214477539062</v>
       </c>
       <c r="C67" s="1">
-        <v>116.2284872884875</v>
+        <v>116.2284890714798</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -4621,10 +4622,10 @@
         <v>45043</v>
       </c>
       <c r="B68" s="1">
-        <v>166.0050506591797</v>
+        <v>166.0050659179688</v>
       </c>
       <c r="C68" s="1">
-        <v>119.5288133328822</v>
+        <v>119.5288374520852</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -4635,7 +4636,7 @@
         <v>167.2569274902344</v>
       </c>
       <c r="C69" s="1">
-        <v>120.4302036909509</v>
+        <v>120.4302169223827</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -4646,7 +4647,7 @@
         <v>167.1681976318359</v>
       </c>
       <c r="C70" s="1">
-        <v>120.3663154258683</v>
+        <v>120.3663286502809</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -4654,10 +4655,10 @@
         <v>45048</v>
       </c>
       <c r="B71" s="1">
-        <v>166.1332244873047</v>
+        <v>166.1331939697266</v>
       </c>
       <c r="C71" s="1">
-        <v>119.6211024862258</v>
+        <v>119.621093655153</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -4665,10 +4666,10 @@
         <v>45049</v>
       </c>
       <c r="B72" s="1">
-        <v>165.0587768554688</v>
+        <v>165.0587463378906</v>
       </c>
       <c r="C72" s="1">
-        <v>118.8474666847143</v>
+        <v>118.8474577686436</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -4676,10 +4677,10 @@
         <v>45050</v>
       </c>
       <c r="B73" s="1">
-        <v>163.4224700927734</v>
+        <v>163.4224548339844</v>
       </c>
       <c r="C73" s="1">
-        <v>117.6692747874383</v>
+        <v>117.6692767287271</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -4687,10 +4688,10 @@
         <v>45051</v>
       </c>
       <c r="B74" s="1">
-        <v>171.0913848876953</v>
+        <v>171.0913696289062</v>
       </c>
       <c r="C74" s="1">
-        <v>123.1911325944634</v>
+        <v>123.191135142428</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -4701,7 +4702,7 @@
         <v>171.0223846435547</v>
       </c>
       <c r="C75" s="1">
-        <v>123.1414502669134</v>
+        <v>123.1414637962246</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -4709,10 +4710,10 @@
         <v>45055</v>
       </c>
       <c r="B76" s="1">
-        <v>169.3171081542969</v>
+        <v>169.3170776367188</v>
       </c>
       <c r="C76" s="1">
-        <v>121.9135980156953</v>
+        <v>121.9135894364945</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -4720,10 +4721,10 @@
         <v>45056</v>
       </c>
       <c r="B77" s="1">
-        <v>171.0815277099609</v>
+        <v>171.0814971923828</v>
       </c>
       <c r="C77" s="1">
-        <v>123.1840351190991</v>
+        <v>123.1840266794787</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -4734,7 +4735,7 @@
         <v>171.2687835693359</v>
       </c>
       <c r="C78" s="1">
-        <v>123.3188651774127</v>
+        <v>123.3188787262162</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -4745,7 +4746,7 @@
         <v>170.3409423828125</v>
       </c>
       <c r="C79" s="1">
-        <v>122.65079058844</v>
+        <v>122.6508040638435</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -4756,7 +4757,7 @@
         <v>169.847412109375</v>
       </c>
       <c r="C80" s="1">
-        <v>122.2954334008509</v>
+        <v>122.2954468372119</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -4767,7 +4768,7 @@
         <v>169.847412109375</v>
       </c>
       <c r="C81" s="1">
-        <v>122.2954334008509</v>
+        <v>122.2954468372119</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -4775,10 +4776,10 @@
         <v>45063</v>
       </c>
       <c r="B82" s="1">
-        <v>170.4594268798828</v>
+        <v>170.4594116210938</v>
       </c>
       <c r="C82" s="1">
-        <v>122.7361031212631</v>
+        <v>122.7361056192345</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -4789,7 +4790,7 @@
         <v>172.7889099121094</v>
       </c>
       <c r="C83" s="1">
-        <v>124.413403549265</v>
+        <v>124.4134172183233</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -4797,10 +4798,10 @@
         <v>45065</v>
       </c>
       <c r="B84" s="1">
-        <v>172.8975219726562</v>
+        <v>172.8974914550781</v>
       </c>
       <c r="C84" s="1">
-        <v>124.4916076199199</v>
+        <v>124.4915993239599</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -4808,10 +4809,10 @@
         <v>45068</v>
       </c>
       <c r="B85" s="1">
-        <v>171.9499053955078</v>
+        <v>171.9498901367188</v>
       </c>
       <c r="C85" s="1">
-        <v>123.8092941330027</v>
+        <v>123.8092967488835</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -4819,10 +4820,10 @@
         <v>45069</v>
       </c>
       <c r="B86" s="1">
-        <v>169.3439788818359</v>
+        <v>169.3440093994141</v>
       </c>
       <c r="C86" s="1">
-        <v>121.9329457774856</v>
+        <v>121.9329811476311</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -4830,10 +4831,10 @@
         <v>45070</v>
       </c>
       <c r="B87" s="1">
-        <v>169.620361328125</v>
+        <v>169.6203765869141</v>
       </c>
       <c r="C87" s="1">
-        <v>122.1319497577849</v>
+        <v>122.1319741629895</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -4841,10 +4842,10 @@
         <v>45071</v>
       </c>
       <c r="B88" s="1">
-        <v>170.7555389404297</v>
+        <v>170.7555084228516</v>
       </c>
       <c r="C88" s="1">
-        <v>122.949313039095</v>
+        <v>122.9493045736861</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -4852,10 +4853,10 @@
         <v>45072</v>
       </c>
       <c r="B89" s="1">
-        <v>173.1639862060547</v>
+        <v>173.1640014648438</v>
       </c>
       <c r="C89" s="1">
-        <v>124.683470177639</v>
+        <v>124.6834948631742</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -4863,10 +4864,10 @@
         <v>45076</v>
       </c>
       <c r="B90" s="1">
-        <v>175.0098724365234</v>
+        <v>175.0098571777344</v>
       </c>
       <c r="C90" s="1">
-        <v>126.012565827436</v>
+        <v>126.0125686853859</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -4877,7 +4878,7 @@
         <v>174.9604949951172</v>
       </c>
       <c r="C91" s="1">
-        <v>125.9770125297907</v>
+        <v>125.9770263706396</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -4885,10 +4886,10 @@
         <v>45078</v>
       </c>
       <c r="B92" s="1">
-        <v>177.7637786865234</v>
+        <v>177.7638244628906</v>
       </c>
       <c r="C92" s="1">
-        <v>127.9954642078492</v>
+        <v>127.995511230877</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -4899,7 +4900,7 @@
         <v>178.6126861572266</v>
       </c>
       <c r="C93" s="1">
-        <v>128.6067040598877</v>
+        <v>128.6067181896558</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -4907,10 +4908,10 @@
         <v>45082</v>
       </c>
       <c r="B94" s="1">
-        <v>177.2604064941406</v>
+        <v>177.2603912353516</v>
       </c>
       <c r="C94" s="1">
-        <v>127.6330205316998</v>
+        <v>127.6330235676859</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -4918,10 +4919,10 @@
         <v>45083</v>
       </c>
       <c r="B95" s="1">
-        <v>176.8951721191406</v>
+        <v>176.8951873779297</v>
       </c>
       <c r="C95" s="1">
-        <v>127.3700403918861</v>
+        <v>127.3700653725895</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -4929,10 +4930,10 @@
         <v>45084</v>
       </c>
       <c r="B96" s="1">
-        <v>175.5231475830078</v>
+        <v>175.5231323242188</v>
       </c>
       <c r="C96" s="1">
-        <v>126.3821399393616</v>
+        <v>126.3821428379159</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -4940,10 +4941,10 @@
         <v>45085</v>
       </c>
       <c r="B97" s="1">
-        <v>178.2376403808594</v>
+        <v>178.2376251220703</v>
       </c>
       <c r="C97" s="1">
-        <v>128.3366594051217</v>
+        <v>128.3366625184153</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -4954,7 +4955,7 @@
         <v>178.6225738525391</v>
       </c>
       <c r="C98" s="1">
-        <v>128.61382350886</v>
+        <v>128.6138376394102</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -4962,10 +4963,10 @@
         <v>45089</v>
       </c>
       <c r="B99" s="1">
-        <v>181.416015625</v>
+        <v>181.4160308837891</v>
       </c>
       <c r="C99" s="1">
-        <v>130.6251886983582</v>
+        <v>130.6252140366984</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -4973,10 +4974,10 @@
         <v>45090</v>
       </c>
       <c r="B100" s="1">
-        <v>180.9422454833984</v>
+        <v>180.9422302246094</v>
       </c>
       <c r="C100" s="1">
-        <v>130.2840594219095</v>
+        <v>130.2840627491601</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -4987,7 +4988,7 @@
         <v>181.5739593505859</v>
       </c>
       <c r="C101" s="1">
-        <v>130.7389131062463</v>
+        <v>130.738927470276</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -4995,10 +4996,10 @@
         <v>45092</v>
       </c>
       <c r="B102" s="1">
-        <v>183.6073608398438</v>
+        <v>183.6073303222656</v>
       </c>
       <c r="C102" s="1">
-        <v>132.2030255900243</v>
+        <v>132.2030181413028</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -5006,10 +5007,10 @@
         <v>45093</v>
       </c>
       <c r="B103" s="1">
-        <v>182.5314331054688</v>
+        <v>182.5314178466797</v>
       </c>
       <c r="C103" s="1">
-        <v>131.4283240685278</v>
+        <v>131.4283275214965</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -5017,10 +5018,10 @@
         <v>45097</v>
       </c>
       <c r="B104" s="1">
-        <v>182.6202850341797</v>
+        <v>182.6202545166016</v>
       </c>
       <c r="C104" s="1">
-        <v>131.4923002280421</v>
+        <v>131.4922927012346</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -5028,10 +5029,10 @@
         <v>45098</v>
       </c>
       <c r="B105" s="1">
-        <v>181.5838012695312</v>
+        <v>181.5838317871094</v>
       </c>
       <c r="C105" s="1">
-        <v>130.7459995948066</v>
+        <v>130.7460359332253</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -5039,10 +5040,10 @@
         <v>45099</v>
       </c>
       <c r="B106" s="1">
-        <v>184.5845642089844</v>
+        <v>184.5845947265625</v>
       </c>
       <c r="C106" s="1">
-        <v>132.9066424898383</v>
+        <v>132.9066790656425</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -5050,10 +5051,10 @@
         <v>45100</v>
       </c>
       <c r="B107" s="1">
-        <v>184.2687072753906</v>
+        <v>184.2686920166016</v>
       </c>
       <c r="C107" s="1">
-        <v>132.6792156476699</v>
+        <v>132.6792192380717</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -5061,10 +5062,10 @@
         <v>45103</v>
       </c>
       <c r="B108" s="1">
-        <v>182.8769073486328</v>
+        <v>182.8769378662109</v>
       </c>
       <c r="C108" s="1">
-        <v>131.677076297201</v>
+        <v>131.6771127379151</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -5072,10 +5073,10 @@
         <v>45104</v>
       </c>
       <c r="B109" s="1">
-        <v>185.6308746337891</v>
+        <v>185.630859375</v>
       </c>
       <c r="C109" s="1">
-        <v>133.6600186248301</v>
+        <v>133.6600223229908</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -5086,7 +5087,7 @@
         <v>186.8054809570312</v>
       </c>
       <c r="C110" s="1">
-        <v>134.5057718075973</v>
+        <v>134.5057865854844</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -5094,10 +5095,10 @@
         <v>45106</v>
       </c>
       <c r="B111" s="1">
-        <v>187.1410980224609</v>
+        <v>187.1410827636719</v>
       </c>
       <c r="C111" s="1">
-        <v>134.7474265609062</v>
+        <v>134.7474303785383</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -5105,10 +5106,10 @@
         <v>45107</v>
       </c>
       <c r="B112" s="1">
-        <v>191.4645538330078</v>
+        <v>191.4644927978516</v>
       </c>
       <c r="C112" s="1">
-        <v>137.860449571229</v>
+        <v>137.8604207704673</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -5116,10 +5117,10 @@
         <v>45110</v>
       </c>
       <c r="B113" s="1">
-        <v>189.9740295410156</v>
+        <v>189.9740142822266</v>
       </c>
       <c r="C113" s="1">
-        <v>136.7872255990775</v>
+        <v>136.7872296408183</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -5130,7 +5131,7 @@
         <v>188.8586273193359</v>
       </c>
       <c r="C114" s="1">
-        <v>135.9841012157118</v>
+        <v>135.9841161560201</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -5138,10 +5139,10 @@
         <v>45113</v>
       </c>
       <c r="B115" s="1">
-        <v>189.3324432373047</v>
+        <v>189.3324127197266</v>
       </c>
       <c r="C115" s="1">
-        <v>136.3252634525724</v>
+        <v>136.3252564567531</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -5149,10 +5150,10 @@
         <v>45114</v>
       </c>
       <c r="B116" s="1">
-        <v>188.2169952392578</v>
+        <v>188.2170104980469</v>
       </c>
       <c r="C116" s="1">
-        <v>135.5221061087948</v>
+        <v>135.5221319851498</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -5160,10 +5161,10 @@
         <v>45117</v>
       </c>
       <c r="B117" s="1">
-        <v>186.1737670898438</v>
+        <v>186.1737823486328</v>
       </c>
       <c r="C117" s="1">
-        <v>134.0509181232605</v>
+        <v>134.0509438379789</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -5171,10 +5172,10 @@
         <v>45118</v>
       </c>
       <c r="B118" s="1">
-        <v>185.6506195068359</v>
+        <v>185.6506042480469</v>
       </c>
       <c r="C118" s="1">
-        <v>133.6742355491666</v>
+        <v>133.6742392488893</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -5182,10 +5183,10 @@
         <v>45119</v>
       </c>
       <c r="B119" s="1">
-        <v>187.3187713623047</v>
+        <v>187.3187561035156</v>
       </c>
       <c r="C119" s="1">
-        <v>134.8753569063269</v>
+        <v>134.8753607380145</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -5193,10 +5194,10 @@
         <v>45120</v>
       </c>
       <c r="B120" s="1">
-        <v>188.0788116455078</v>
+        <v>188.0788269042969</v>
       </c>
       <c r="C120" s="1">
-        <v>135.4226096120472</v>
+        <v>135.4226354774706</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -5204,10 +5205,10 @@
         <v>45121</v>
       </c>
       <c r="B121" s="1">
-        <v>188.2269134521484</v>
+        <v>188.2268981933594</v>
       </c>
       <c r="C121" s="1">
-        <v>135.529247531375</v>
+        <v>135.5292514349042</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -5218,7 +5219,7 @@
         <v>191.4842681884766</v>
       </c>
       <c r="C122" s="1">
-        <v>137.8746445219576</v>
+        <v>137.8746596699762</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -5226,10 +5227,10 @@
         <v>45125</v>
       </c>
       <c r="B123" s="1">
-        <v>191.2276306152344</v>
+        <v>191.2276153564453</v>
       </c>
       <c r="C123" s="1">
-        <v>137.6898574659947</v>
+        <v>137.6898616069059</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -5237,10 +5238,10 @@
         <v>45126</v>
       </c>
       <c r="B124" s="1">
-        <v>192.5799255371094</v>
+        <v>192.5799102783203</v>
       </c>
       <c r="C124" s="1">
-        <v>138.6635519809867</v>
+        <v>138.6635562288758</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -5248,10 +5249,10 @@
         <v>45127</v>
       </c>
       <c r="B125" s="1">
-        <v>190.6353912353516</v>
+        <v>190.6353607177734</v>
       </c>
       <c r="C125" s="1">
-        <v>137.263426643527</v>
+        <v>137.2634197507819</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -5259,10 +5260,10 @@
         <v>45128</v>
       </c>
       <c r="B126" s="1">
-        <v>189.4607543945312</v>
+        <v>189.4607391357422</v>
       </c>
       <c r="C126" s="1">
-        <v>136.4176514871518</v>
+        <v>136.4176554882882</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -5270,10 +5271,10 @@
         <v>45131</v>
       </c>
       <c r="B127" s="1">
-        <v>190.2602996826172</v>
+        <v>190.2603149414062</v>
       </c>
       <c r="C127" s="1">
-        <v>136.993349028349</v>
+        <v>136.9933750663466</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -5281,10 +5282,10 @@
         <v>45132</v>
       </c>
       <c r="B128" s="1">
-        <v>191.1190490722656</v>
+        <v>191.1190338134766</v>
       </c>
       <c r="C128" s="1">
-        <v>137.6116753689479</v>
+        <v>137.6116795012694</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -5292,10 +5293,10 @@
         <v>45133</v>
       </c>
       <c r="B129" s="1">
-        <v>191.9876556396484</v>
+        <v>191.9876861572266</v>
       </c>
       <c r="C129" s="1">
-        <v>138.237099184911</v>
+        <v>138.2371363463621</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -5303,10 +5304,10 @@
         <v>45134</v>
       </c>
       <c r="B130" s="1">
-        <v>190.7242126464844</v>
+        <v>190.7241973876953</v>
       </c>
       <c r="C130" s="1">
-        <v>137.3273808294334</v>
+        <v>137.32738493052</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -5314,10 +5315,10 @@
         <v>45135</v>
       </c>
       <c r="B131" s="1">
-        <v>193.3005065917969</v>
+        <v>193.3005218505859</v>
       </c>
       <c r="C131" s="1">
-        <v>139.1823928116418</v>
+        <v>139.1824190901453</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -5328,7 +5329,7 @@
         <v>193.9124908447266</v>
       </c>
       <c r="C132" s="1">
-        <v>139.6230405584461</v>
+        <v>139.6230558985575</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -5339,7 +5340,7 @@
         <v>193.0833435058594</v>
       </c>
       <c r="C133" s="1">
-        <v>139.026028617548</v>
+        <v>139.026043892067</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -5347,10 +5348,10 @@
         <v>45140</v>
       </c>
       <c r="B134" s="1">
-        <v>190.0924987792969</v>
+        <v>190.0924835205078</v>
       </c>
       <c r="C134" s="1">
-        <v>136.8725271450966</v>
+        <v>136.8725311962093</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -5358,10 +5359,10 @@
         <v>45141</v>
       </c>
       <c r="B135" s="1">
-        <v>188.7006683349609</v>
+        <v>188.7006988525391</v>
       </c>
       <c r="C135" s="1">
-        <v>135.8703658210197</v>
+        <v>135.8704027224424</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -5369,10 +5370,10 @@
         <v>45142</v>
       </c>
       <c r="B136" s="1">
-        <v>179.6392822265625</v>
+        <v>179.6392974853516</v>
       </c>
       <c r="C136" s="1">
-        <v>129.345885244151</v>
+        <v>129.3459104419366</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -5383,7 +5384,7 @@
         <v>176.5398406982422</v>
       </c>
       <c r="C137" s="1">
-        <v>127.1141906878486</v>
+        <v>127.1142046536371</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -5391,10 +5392,10 @@
         <v>45146</v>
       </c>
       <c r="B138" s="1">
-        <v>177.4775543212891</v>
+        <v>177.4775848388672</v>
       </c>
       <c r="C138" s="1">
-        <v>127.7893737389896</v>
+        <v>127.7894097525695</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -5405,7 +5406,7 @@
         <v>175.8883666992188</v>
       </c>
       <c r="C139" s="1">
-        <v>126.6451090923713</v>
+        <v>126.6451230066227</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -5413,10 +5414,10 @@
         <v>45148</v>
       </c>
       <c r="B140" s="1">
-        <v>175.6712036132812</v>
+        <v>175.6711883544922</v>
       </c>
       <c r="C140" s="1">
-        <v>126.4887448982776</v>
+        <v>126.4887478085444</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -5424,10 +5425,10 @@
         <v>45149</v>
       </c>
       <c r="B141" s="1">
-        <v>175.7304840087891</v>
+        <v>175.7305145263672</v>
       </c>
       <c r="C141" s="1">
-        <v>126.531428631699</v>
+        <v>126.5314645070709</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -5435,10 +5436,10 @@
         <v>45152</v>
       </c>
       <c r="B142" s="1">
-        <v>177.3811950683594</v>
+        <v>177.3811492919922</v>
       </c>
       <c r="C142" s="1">
-        <v>127.7199920719223</v>
+        <v>127.7199731438534</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -5446,10 +5447,10 @@
         <v>45153</v>
       </c>
       <c r="B143" s="1">
-        <v>175.3944396972656</v>
+        <v>175.3944549560547</v>
       </c>
       <c r="C143" s="1">
-        <v>126.289466247879</v>
+        <v>126.2894911098618</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -5460,7 +5461,7 @@
         <v>174.5246276855469</v>
       </c>
       <c r="C144" s="1">
-        <v>125.6631744744023</v>
+        <v>125.6631882807704</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -5471,7 +5472,7 @@
         <v>171.9844055175781</v>
       </c>
       <c r="C145" s="1">
-        <v>123.8341352967777</v>
+        <v>123.8341489021929</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -5482,7 +5483,7 @@
         <v>172.46875</v>
       </c>
       <c r="C146" s="1">
-        <v>124.1828784283773</v>
+        <v>124.1828920721082</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -5490,10 +5491,10 @@
         <v>45159</v>
       </c>
       <c r="B147" s="1">
-        <v>173.8030700683594</v>
+        <v>173.8031005859375</v>
       </c>
       <c r="C147" s="1">
-        <v>125.1436304882931</v>
+        <v>125.1436662111904</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -5501,10 +5502,10 @@
         <v>45160</v>
       </c>
       <c r="B148" s="1">
-        <v>175.1769866943359</v>
+        <v>175.1770172119141</v>
       </c>
       <c r="C148" s="1">
-        <v>126.1328933045098</v>
+        <v>126.1329291360954</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -5512,10 +5513,10 @@
         <v>45161</v>
       </c>
       <c r="B149" s="1">
-        <v>179.0219421386719</v>
+        <v>179.0219573974609</v>
       </c>
       <c r="C149" s="1">
-        <v>128.9013811291534</v>
+        <v>128.9014062781022</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -5523,10 +5524,10 @@
         <v>45162</v>
       </c>
       <c r="B150" s="1">
-        <v>174.3368530273438</v>
+        <v>174.3368682861328</v>
       </c>
       <c r="C150" s="1">
-        <v>125.5279708647538</v>
+        <v>125.5279956430725</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -5534,10 +5535,10 @@
         <v>45163</v>
       </c>
       <c r="B151" s="1">
-        <v>176.541015625</v>
+        <v>176.5409851074219</v>
       </c>
       <c r="C151" s="1">
-        <v>127.1150366717543</v>
+        <v>127.1150286640254</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -5545,10 +5546,10 @@
         <v>45166</v>
       </c>
       <c r="B152" s="1">
-        <v>178.1027374267578</v>
+        <v>178.1026916503906</v>
       </c>
       <c r="C152" s="1">
-        <v>128.2395250712274</v>
+        <v>128.2395062002387</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -5559,7 +5560,7 @@
         <v>181.9871826171875</v>
       </c>
       <c r="C153" s="1">
-        <v>131.0364467445441</v>
+        <v>131.0364611412632</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -5570,7 +5571,7 @@
         <v>185.4762878417969</v>
       </c>
       <c r="C154" s="1">
-        <v>133.5487113138152</v>
+        <v>133.5487259865519</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -5578,10 +5579,10 @@
         <v>45169</v>
       </c>
       <c r="B155" s="1">
-        <v>185.6937255859375</v>
+        <v>185.6937561035156</v>
       </c>
       <c r="C155" s="1">
-        <v>133.7052732703804</v>
+        <v>133.7053099339286</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -5592,7 +5593,7 @@
         <v>187.2653198242188</v>
       </c>
       <c r="C156" s="1">
-        <v>134.8368701320218</v>
+        <v>134.8368849462861</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -5600,10 +5601,10 @@
         <v>45174</v>
       </c>
       <c r="B157" s="1">
-        <v>187.5025482177734</v>
+        <v>187.5025329589844</v>
       </c>
       <c r="C157" s="1">
-        <v>135.0076819733355</v>
+        <v>135.0076858195613</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -5611,10 +5612,10 @@
         <v>45175</v>
       </c>
       <c r="B158" s="1">
-        <v>180.7911987304688</v>
+        <v>180.7911834716797</v>
       </c>
       <c r="C158" s="1">
-        <v>130.1753010494156</v>
+        <v>130.1753043647171</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -5622,10 +5623,10 @@
         <v>45176</v>
       </c>
       <c r="B159" s="1">
-        <v>175.5031585693359</v>
+        <v>175.503173828125</v>
       </c>
       <c r="C159" s="1">
-        <v>126.3677472261616</v>
+        <v>126.367772096745</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -5636,7 +5637,7 @@
         <v>176.1159820556641</v>
       </c>
       <c r="C160" s="1">
-        <v>126.8089992471842</v>
+        <v>126.8090131794419</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -5647,7 +5648,7 @@
         <v>177.2823181152344</v>
       </c>
       <c r="C161" s="1">
-        <v>127.6487975822</v>
+        <v>127.6488116067247</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -5655,10 +5656,10 @@
         <v>45181</v>
       </c>
       <c r="B162" s="1">
-        <v>174.2577819824219</v>
+        <v>174.2577667236328</v>
       </c>
       <c r="C162" s="1">
-        <v>125.4710372465839</v>
+        <v>125.4710400450371</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -5666,10 +5667,10 @@
         <v>45182</v>
       </c>
       <c r="B163" s="1">
-        <v>172.1919860839844</v>
+        <v>172.1920013427734</v>
       </c>
       <c r="C163" s="1">
-        <v>123.9835997779787</v>
+        <v>123.9836243866204</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -5677,10 +5678,10 @@
         <v>45183</v>
       </c>
       <c r="B164" s="1">
-        <v>173.7042694091797</v>
+        <v>173.7042388916016</v>
       </c>
       <c r="C164" s="1">
-        <v>125.0724909325907</v>
+        <v>125.0724827004512</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -5688,10 +5689,10 @@
         <v>45184</v>
       </c>
       <c r="B165" s="1">
-        <v>172.9827117919922</v>
+        <v>172.9826965332031</v>
       </c>
       <c r="C165" s="1">
-        <v>124.5529469464815</v>
+        <v>124.552949644066</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -5702,7 +5703,7 @@
         <v>175.9084167480469</v>
       </c>
       <c r="C166" s="1">
-        <v>126.6595457527872</v>
+        <v>126.6595596686248</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -5710,10 +5711,10 @@
         <v>45188</v>
       </c>
       <c r="B167" s="1">
-        <v>176.9956817626953</v>
+        <v>176.9956970214844</v>
       </c>
       <c r="C167" s="1">
-        <v>127.4424104696331</v>
+        <v>127.4424354582877</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -5721,10 +5722,10 @@
         <v>45189</v>
       </c>
       <c r="B168" s="1">
-        <v>173.4571380615234</v>
+        <v>173.4571685791016</v>
       </c>
       <c r="C168" s="1">
-        <v>124.8945486555008</v>
+        <v>124.8945843510319</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -5732,10 +5733,10 @@
         <v>45190</v>
       </c>
       <c r="B169" s="1">
-        <v>171.9152221679688</v>
+        <v>171.9152069091797</v>
       </c>
       <c r="C169" s="1">
-        <v>123.7843211275801</v>
+        <v>123.7843237407171</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -5743,10 +5744,10 @@
         <v>45191</v>
       </c>
       <c r="B170" s="1">
-        <v>172.7652740478516</v>
+        <v>172.7652282714844</v>
       </c>
       <c r="C170" s="1">
-        <v>124.3963849899163</v>
+        <v>124.3963656966892</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -5754,10 +5755,10 @@
         <v>45194</v>
       </c>
       <c r="B171" s="1">
-        <v>174.0403137207031</v>
+        <v>174.0402984619141</v>
       </c>
       <c r="C171" s="1">
-        <v>125.3144533164107</v>
+        <v>125.3144560976604</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -5765,10 +5766,10 @@
         <v>45195</v>
       </c>
       <c r="B172" s="1">
-        <v>169.9680480957031</v>
+        <v>169.9680328369141</v>
       </c>
       <c r="C172" s="1">
-        <v>122.3822950730337</v>
+        <v>122.3822975321328</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -5776,10 +5777,10 @@
         <v>45196</v>
       </c>
       <c r="B173" s="1">
-        <v>168.4557495117188</v>
+        <v>168.4557647705078</v>
       </c>
       <c r="C173" s="1">
-        <v>121.2933929316177</v>
+        <v>121.2934172446917</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -5787,10 +5788,10 @@
         <v>45197</v>
       </c>
       <c r="B174" s="1">
-        <v>168.7127380371094</v>
+        <v>168.7127532958984</v>
       </c>
       <c r="C174" s="1">
-        <v>121.4784326840718</v>
+        <v>121.4784570174757</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -5798,10 +5799,10 @@
         <v>45198</v>
       </c>
       <c r="B175" s="1">
-        <v>169.2267456054688</v>
+        <v>169.2267303466797</v>
       </c>
       <c r="C175" s="1">
-        <v>121.848534162588</v>
+        <v>121.8485365630439</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -5809,10 +5810,10 @@
         <v>45201</v>
       </c>
       <c r="B176" s="1">
-        <v>171.7372741699219</v>
+        <v>171.7373199462891</v>
       </c>
       <c r="C176" s="1">
-        <v>123.6561930196879</v>
+        <v>123.6562395659684</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -5820,10 +5821,10 @@
         <v>45202</v>
       </c>
       <c r="B177" s="1">
-        <v>170.4028930664062</v>
+        <v>170.4029235839844</v>
       </c>
       <c r="C177" s="1">
-        <v>122.6953970125562</v>
+        <v>122.6954324664707</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -5831,10 +5832,10 @@
         <v>45203</v>
       </c>
       <c r="B178" s="1">
-        <v>171.6483764648438</v>
+        <v>171.6483306884766</v>
       </c>
       <c r="C178" s="1">
-        <v>123.5921838997617</v>
+        <v>123.5921645181786</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -5842,10 +5843,10 @@
         <v>45204</v>
       </c>
       <c r="B179" s="1">
-        <v>172.8838806152344</v>
+        <v>172.8838653564453</v>
       </c>
       <c r="C179" s="1">
-        <v>124.4817854171711</v>
+        <v>124.4817881069372</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -5853,10 +5854,10 @@
         <v>45205</v>
       </c>
       <c r="B180" s="1">
-        <v>175.4339752197266</v>
+        <v>175.4339904785156</v>
       </c>
       <c r="C180" s="1">
-        <v>126.317933056964</v>
+        <v>126.3179579220743</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -5864,10 +5865,10 @@
         <v>45208</v>
       </c>
       <c r="B181" s="1">
-        <v>176.9165954589844</v>
+        <v>176.9165802001953</v>
       </c>
       <c r="C181" s="1">
-        <v>127.3854658646593</v>
+        <v>127.3854688734471</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -5875,10 +5876,10 @@
         <v>45209</v>
       </c>
       <c r="B182" s="1">
-        <v>176.3235473632812</v>
+        <v>176.3235626220703</v>
       </c>
       <c r="C182" s="1">
-        <v>126.9584527415812</v>
+        <v>126.9584776770642</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -5886,10 +5887,10 @@
         <v>45210</v>
       </c>
       <c r="B183" s="1">
-        <v>177.7172241210938</v>
+        <v>177.7172393798828</v>
       </c>
       <c r="C183" s="1">
-        <v>127.9619434689383</v>
+        <v>127.9619685146729</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -5897,10 +5898,10 @@
         <v>45211</v>
       </c>
       <c r="B184" s="1">
-        <v>178.61669921875</v>
+        <v>178.6166839599609</v>
       </c>
       <c r="C184" s="1">
-        <v>128.6095935893317</v>
+        <v>128.609596732612</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -5911,7 +5912,7 @@
         <v>176.7782287597656</v>
       </c>
       <c r="C185" s="1">
-        <v>127.2858375262639</v>
+        <v>127.2858515109109</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -5919,10 +5920,10 @@
         <v>45215</v>
       </c>
       <c r="B186" s="1">
-        <v>176.6497192382812</v>
+        <v>176.6497344970703</v>
       </c>
       <c r="C186" s="1">
-        <v>127.1933066632329</v>
+        <v>127.1933316245189</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -5933,7 +5934,7 @@
         <v>175.0979156494141</v>
       </c>
       <c r="C187" s="1">
-        <v>126.0759596863399</v>
+        <v>126.07597353806</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -5941,10 +5942,10 @@
         <v>45217</v>
       </c>
       <c r="B188" s="1">
-        <v>173.8030700683594</v>
+        <v>173.8031005859375</v>
       </c>
       <c r="C188" s="1">
-        <v>125.1436304882931</v>
+        <v>125.1436662111904</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -5952,10 +5953,10 @@
         <v>45218</v>
       </c>
       <c r="B189" s="1">
-        <v>173.4274749755859</v>
+        <v>173.427490234375</v>
       </c>
       <c r="C189" s="1">
-        <v>124.8731903085842</v>
+        <v>124.8732150149635</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -5963,10 +5964,10 @@
         <v>45219</v>
       </c>
       <c r="B190" s="1">
-        <v>170.8773651123047</v>
+        <v>170.8773803710938</v>
       </c>
       <c r="C190" s="1">
-        <v>123.0370316819874</v>
+        <v>123.0370561866315</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -5977,7 +5978,7 @@
         <v>170.9960021972656</v>
       </c>
       <c r="C191" s="1">
-        <v>123.1224540828502</v>
+        <v>123.1224676100743</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -5988,7 +5989,7 @@
         <v>171.4308929443359</v>
       </c>
       <c r="C192" s="1">
-        <v>123.4355889827846</v>
+        <v>123.4356025444122</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -5996,10 +5997,10 @@
         <v>45224</v>
       </c>
       <c r="B193" s="1">
-        <v>169.1179962158203</v>
+        <v>169.1180114746094</v>
       </c>
       <c r="C193" s="1">
-        <v>121.7702312106975</v>
+        <v>121.7702555761607</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -6007,10 +6008,10 @@
         <v>45225</v>
       </c>
       <c r="B194" s="1">
-        <v>164.9567413330078</v>
+        <v>164.9567718505859</v>
       </c>
       <c r="C194" s="1">
-        <v>118.7739979265703</v>
+        <v>118.7740329496485</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -6018,10 +6019,10 @@
         <v>45226</v>
       </c>
       <c r="B195" s="1">
-        <v>166.2713317871094</v>
+        <v>166.2713623046875</v>
       </c>
       <c r="C195" s="1">
-        <v>119.7205440489537</v>
+        <v>119.720579176027</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -6029,10 +6030,10 @@
         <v>45229</v>
       </c>
       <c r="B196" s="1">
-        <v>168.3173675537109</v>
+        <v>168.3173828125</v>
       </c>
       <c r="C196" s="1">
-        <v>121.1937536064184</v>
+        <v>121.1937779085452</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -6040,10 +6041,10 @@
         <v>45230</v>
       </c>
       <c r="B197" s="1">
-        <v>168.7918243408203</v>
+        <v>168.7918395996094</v>
       </c>
       <c r="C197" s="1">
-        <v>121.5353772890457</v>
+        <v>121.535401628706</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -6051,10 +6052,10 @@
         <v>45231</v>
       </c>
       <c r="B198" s="1">
-        <v>171.9547729492188</v>
+        <v>171.9547576904297</v>
       </c>
       <c r="C198" s="1">
-        <v>123.812798923469</v>
+        <v>123.8128015397348</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -6062,10 +6063,10 @@
         <v>45232</v>
       </c>
       <c r="B199" s="1">
-        <v>175.5130462646484</v>
+        <v>175.5130615234375</v>
       </c>
       <c r="C199" s="1">
-        <v>126.3748666751338</v>
+        <v>126.3748915464994</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -6076,7 +6077,7 @@
         <v>174.6036834716797</v>
       </c>
       <c r="C200" s="1">
-        <v>125.7200971057682</v>
+        <v>125.7201109183903</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -6087,7 +6088,7 @@
         <v>177.1538238525391</v>
       </c>
       <c r="C201" s="1">
-        <v>127.5562777059729</v>
+        <v>127.5562917203326</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -6098,7 +6099,7 @@
         <v>179.7138061523438</v>
       </c>
       <c r="C202" s="1">
-        <v>129.3995447947379</v>
+        <v>129.3995590116138</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -6109,7 +6110,7 @@
         <v>180.7714233398438</v>
       </c>
       <c r="C203" s="1">
-        <v>130.1610621514711</v>
+        <v>130.1610764520134</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -6117,10 +6118,10 @@
         <v>45239</v>
       </c>
       <c r="B204" s="1">
-        <v>180.2969665527344</v>
+        <v>180.2969970703125</v>
       </c>
       <c r="C204" s="1">
-        <v>129.8194384688439</v>
+        <v>129.819474705463</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -6128,10 +6129,10 @@
         <v>45240</v>
       </c>
       <c r="B205" s="1">
-        <v>184.4834747314453</v>
+        <v>184.4835052490234</v>
       </c>
       <c r="C205" s="1">
-        <v>132.8338549135404</v>
+        <v>132.8338914813476</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -6139,10 +6140,10 @@
         <v>45243</v>
       </c>
       <c r="B206" s="1">
-        <v>182.8999328613281</v>
+        <v>182.8999633789062</v>
       </c>
       <c r="C206" s="1">
-        <v>131.6936553843909</v>
+        <v>131.6936918269266</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -6150,10 +6151,10 @@
         <v>45244</v>
       </c>
       <c r="B207" s="1">
-        <v>185.5128021240234</v>
+        <v>185.5128173828125</v>
       </c>
       <c r="C207" s="1">
-        <v>133.5750027357142</v>
+        <v>133.5750283981447</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -6164,7 +6165,7 @@
         <v>186.0769348144531</v>
       </c>
       <c r="C208" s="1">
-        <v>133.9811958652701</v>
+        <v>133.9812105855231</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -6175,7 +6176,7 @@
         <v>187.7594604492188</v>
       </c>
       <c r="C209" s="1">
-        <v>135.1926667917697</v>
+        <v>135.1926816451247</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -6183,10 +6184,10 @@
         <v>45247</v>
       </c>
       <c r="B210" s="1">
-        <v>187.7396697998047</v>
+        <v>187.7396545410156</v>
       </c>
       <c r="C210" s="1">
-        <v>135.1784169070213</v>
+        <v>135.1784207720054</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -6197,7 +6198,7 @@
         <v>189.4815826416016</v>
       </c>
       <c r="C211" s="1">
-        <v>136.4326484745702</v>
+        <v>136.4326634641594</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -6205,10 +6206,10 @@
         <v>45251</v>
       </c>
       <c r="B212" s="1">
-        <v>188.679931640625</v>
+        <v>188.6799011230469</v>
       </c>
       <c r="C212" s="1">
-        <v>135.8554347544252</v>
+        <v>135.8554277069867</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -6216,10 +6217,10 @@
         <v>45252</v>
       </c>
       <c r="B213" s="1">
-        <v>189.3430023193359</v>
+        <v>189.3429870605469</v>
       </c>
       <c r="C213" s="1">
-        <v>136.3328663209193</v>
+        <v>136.3328703127405</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -6227,10 +6228,10 @@
         <v>45254</v>
       </c>
       <c r="B214" s="1">
-        <v>188.0167999267578</v>
+        <v>188.0167846679688</v>
       </c>
       <c r="C214" s="1">
-        <v>135.3779592407152</v>
+        <v>135.3779631276226</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -6241,7 +6242,7 @@
         <v>187.8386383056641</v>
       </c>
       <c r="C215" s="1">
-        <v>135.2496773175674</v>
+        <v>135.249692177186</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -6249,10 +6250,10 @@
         <v>45258</v>
       </c>
       <c r="B216" s="1">
-        <v>188.4423828125</v>
+        <v>188.4423522949219</v>
       </c>
       <c r="C216" s="1">
-        <v>135.6843921902282</v>
+        <v>135.6843851239976</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -6263,7 +6264,7 @@
         <v>187.4229431152344</v>
       </c>
       <c r="C217" s="1">
-        <v>134.9503638170266</v>
+        <v>134.9503786437602</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -6271,10 +6272,10 @@
         <v>45260</v>
       </c>
       <c r="B218" s="1">
-        <v>187.9969787597656</v>
+        <v>187.9969940185547</v>
       </c>
       <c r="C218" s="1">
-        <v>135.3636873823588</v>
+        <v>135.3637132413086</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -6282,10 +6283,10 @@
         <v>45261</v>
       </c>
       <c r="B219" s="1">
-        <v>189.2737426757812</v>
+        <v>189.2737121582031</v>
       </c>
       <c r="C219" s="1">
-        <v>136.2829972177018</v>
+        <v>136.2829902172388</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -6293,10 +6294,10 @@
         <v>45264</v>
       </c>
       <c r="B220" s="1">
-        <v>187.4823150634766</v>
+        <v>187.4823303222656</v>
       </c>
       <c r="C220" s="1">
-        <v>134.9931134712719</v>
+        <v>134.9931392895075</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -6304,10 +6305,10 @@
         <v>45265</v>
       </c>
       <c r="B221" s="1">
-        <v>191.4313354492188</v>
+        <v>191.4312896728516</v>
       </c>
       <c r="C221" s="1">
-        <v>137.8365312989874</v>
+        <v>137.836513482403</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -6315,10 +6316,10 @@
         <v>45266</v>
       </c>
       <c r="B222" s="1">
-        <v>190.3426361083984</v>
+        <v>190.3426208496094</v>
       </c>
       <c r="C222" s="1">
-        <v>137.0526338225684</v>
+        <v>137.0526378934691</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -6329,7 +6330,7 @@
         <v>192.2725830078125</v>
       </c>
       <c r="C223" s="1">
-        <v>138.4422557754332</v>
+        <v>138.4422709858142</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -6337,10 +6338,10 @@
         <v>45268</v>
       </c>
       <c r="B224" s="1">
-        <v>193.6977691650391</v>
+        <v>193.6977844238281</v>
       </c>
       <c r="C224" s="1">
-        <v>139.4684342529874</v>
+        <v>139.4684605629178</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -6348,10 +6349,10 @@
         <v>45271</v>
       </c>
       <c r="B225" s="1">
-        <v>191.1937713623047</v>
+        <v>191.1938018798828</v>
       </c>
       <c r="C225" s="1">
-        <v>137.6654777479864</v>
+        <v>137.6655148466346</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -6359,10 +6360,10 @@
         <v>45272</v>
       </c>
       <c r="B226" s="1">
-        <v>192.7080535888672</v>
+        <v>192.7080688476562</v>
       </c>
       <c r="C226" s="1">
-        <v>138.7558081739185</v>
+        <v>138.755834405554</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -6370,10 +6371,10 @@
         <v>45273</v>
       </c>
       <c r="B227" s="1">
-        <v>195.9246368408203</v>
+        <v>195.9246673583984</v>
       </c>
       <c r="C227" s="1">
-        <v>141.0718484242946</v>
+        <v>141.0718858971941</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -6384,7 +6385,7 @@
         <v>196.0731048583984</v>
       </c>
       <c r="C228" s="1">
-        <v>141.1787500269177</v>
+        <v>141.1787655379519</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -6395,7 +6396,7 @@
         <v>195.5386657714844</v>
       </c>
       <c r="C229" s="1">
-        <v>140.7939372178863</v>
+        <v>140.7939526866419</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -6406,7 +6407,7 @@
         <v>193.8759307861328</v>
       </c>
       <c r="C230" s="1">
-        <v>139.5967161761351</v>
+        <v>139.5967315133544</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -6417,7 +6418,7 @@
         <v>194.9151306152344</v>
       </c>
       <c r="C231" s="1">
-        <v>140.3449724604772</v>
+        <v>140.3449878799059</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -6425,10 +6426,10 @@
         <v>45280</v>
       </c>
       <c r="B232" s="1">
-        <v>192.8268432617188</v>
+        <v>192.8268127441406</v>
       </c>
       <c r="C232" s="1">
-        <v>138.8413404428209</v>
+        <v>138.8413337234382</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -6439,7 +6440,7 @@
         <v>192.6783447265625</v>
       </c>
       <c r="C233" s="1">
-        <v>138.7344168665899</v>
+        <v>138.73443210907</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -6447,10 +6448,10 @@
         <v>45282</v>
       </c>
       <c r="B234" s="1">
-        <v>191.6094665527344</v>
+        <v>191.6094818115234</v>
       </c>
       <c r="C234" s="1">
-        <v>137.9647912485272</v>
+        <v>137.9648173932552</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -6461,7 +6462,7 @@
         <v>191.0651245117188</v>
       </c>
       <c r="C235" s="1">
-        <v>137.5728480037197</v>
+        <v>137.5728631185805</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -6469,10 +6470,10 @@
         <v>45287</v>
       </c>
       <c r="B236" s="1">
-        <v>191.1640930175781</v>
+        <v>191.1641082763672</v>
       </c>
       <c r="C236" s="1">
-        <v>137.6441084142658</v>
+        <v>137.644134523761</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -6480,10 +6481,10 @@
         <v>45288</v>
       </c>
       <c r="B237" s="1">
-        <v>191.5896911621094</v>
+        <v>191.5896453857422</v>
       </c>
       <c r="C237" s="1">
-        <v>137.9505523505828</v>
+        <v>137.9505345465257</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -6491,10 +6492,10 @@
         <v>45289</v>
       </c>
       <c r="B238" s="1">
-        <v>190.5504760742188</v>
+        <v>190.5504608154297</v>
       </c>
       <c r="C238" s="1">
-        <v>137.2022850794368</v>
+        <v>137.2022891667794</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -6502,10 +6503,10 @@
         <v>45293</v>
       </c>
       <c r="B239" s="1">
-        <v>183.7312774658203</v>
+        <v>183.7313232421875</v>
       </c>
       <c r="C239" s="1">
-        <v>132.2922494250606</v>
+        <v>132.2922969201678</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -6513,10 +6514,10 @@
         <v>45294</v>
       </c>
       <c r="B240" s="1">
-        <v>182.3556365966797</v>
+        <v>182.3555908203125</v>
       </c>
       <c r="C240" s="1">
-        <v>131.3017450999953</v>
+        <v>131.3017265654467</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -6524,10 +6525,10 @@
         <v>45295</v>
       </c>
       <c r="B241" s="1">
-        <v>180.0396881103516</v>
+        <v>180.0396728515625</v>
       </c>
       <c r="C241" s="1">
-        <v>129.6341899671143</v>
+        <v>129.634193222965</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -6538,7 +6539,7 @@
         <v>179.3171691894531</v>
       </c>
       <c r="C242" s="1">
-        <v>129.1139538123551</v>
+        <v>129.1139679978536</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -6549,7 +6550,7 @@
         <v>183.6521301269531</v>
       </c>
       <c r="C243" s="1">
-        <v>132.2352608728708</v>
+        <v>132.2352754013013</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -6557,10 +6558,10 @@
         <v>45300</v>
       </c>
       <c r="B244" s="1">
-        <v>183.2364654541016</v>
+        <v>183.2364501953125</v>
       </c>
       <c r="C244" s="1">
-        <v>131.935969345938</v>
+        <v>131.9359728546807</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -6568,10 +6569,10 @@
         <v>45301</v>
       </c>
       <c r="B245" s="1">
-        <v>184.2756500244141</v>
+        <v>184.275634765625</v>
       </c>
       <c r="C245" s="1">
-        <v>132.684214643476</v>
+        <v>132.684218234427</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -6579,10 +6580,10 @@
         <v>45302</v>
       </c>
       <c r="B246" s="1">
-        <v>183.6818237304688</v>
+        <v>183.6818084716797</v>
       </c>
       <c r="C246" s="1">
-        <v>132.2566411933954</v>
+        <v>132.2566447373698</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -6593,7 +6594,7 @@
         <v>184.0084228515625</v>
       </c>
       <c r="C247" s="1">
-        <v>132.4918027455584</v>
+        <v>132.4918173021746</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -6604,7 +6605,7 @@
         <v>181.7419738769531</v>
       </c>
       <c r="C248" s="1">
-        <v>130.8598888047544</v>
+        <v>130.8599031820754</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -6612,10 +6613,10 @@
         <v>45308</v>
       </c>
       <c r="B249" s="1">
-        <v>180.8017425537109</v>
+        <v>180.8017272949219</v>
       </c>
       <c r="C249" s="1">
-        <v>130.1828929309585</v>
+        <v>130.1828962470941</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -6623,10 +6624,10 @@
         <v>45309</v>
       </c>
       <c r="B250" s="1">
-        <v>186.6905822753906</v>
+        <v>186.6905670166016</v>
       </c>
       <c r="C250" s="1">
-        <v>134.4230411737071</v>
+        <v>134.4230449556995</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -6637,7 +6638,7 @@
         <v>189.5904388427734</v>
       </c>
       <c r="C251" s="1">
-        <v>136.5110283340885</v>
+        <v>136.5110433322892</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -6645,10 +6646,10 @@
         <v>45313</v>
       </c>
       <c r="B252" s="1">
-        <v>191.896484375</v>
+        <v>191.8964691162109</v>
       </c>
       <c r="C252" s="1">
-        <v>138.1714530311933</v>
+        <v>138.1714572250165</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -6656,10 +6657,10 @@
         <v>45314</v>
       </c>
       <c r="B253" s="1">
-        <v>193.1732177734375</v>
+        <v>193.1732025146484</v>
       </c>
       <c r="C253" s="1">
-        <v>139.0907408929283</v>
+        <v>139.0907451877518</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -6667,10 +6668,10 @@
         <v>45315</v>
       </c>
       <c r="B254" s="1">
-        <v>192.5001983642578</v>
+        <v>192.5002136230469</v>
       </c>
       <c r="C254" s="1">
-        <v>138.6061459302461</v>
+        <v>138.6061721454385</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -6678,10 +6679,10 @@
         <v>45316</v>
       </c>
       <c r="B255" s="1">
-        <v>192.1736145019531</v>
+        <v>192.1735992431641</v>
       </c>
       <c r="C255" s="1">
-        <v>138.3709953648872</v>
+        <v>138.3709995806336</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -6689,10 +6690,10 @@
         <v>45317</v>
       </c>
       <c r="B256" s="1">
-        <v>190.4416046142578</v>
+        <v>190.4415893554688</v>
       </c>
       <c r="C256" s="1">
-        <v>137.1238942331145</v>
+        <v>137.1238983118444</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -6700,10 +6701,10 @@
         <v>45320</v>
       </c>
       <c r="B257" s="1">
-        <v>189.7586975097656</v>
+        <v>189.7586822509766</v>
       </c>
       <c r="C257" s="1">
-        <v>136.63217982146</v>
+        <v>136.6321838461663</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -6714,7 +6715,7 @@
         <v>186.1066284179688</v>
       </c>
       <c r="C258" s="1">
-        <v>134.0025761857948</v>
+        <v>134.0025909083967</v>
       </c>
     </row>
   </sheetData>
@@ -9601,7 +9602,7 @@
         <v>44949</v>
       </c>
       <c r="B2" s="1">
-        <v>236.3760833740234</v>
+        <v>236.3760528564453</v>
       </c>
       <c r="C2" s="1">
         <v>100</v>
@@ -9612,10 +9613,10 @@
         <v>44950</v>
       </c>
       <c r="B3" s="1">
-        <v>235.8498992919922</v>
+        <v>235.8498687744141</v>
       </c>
       <c r="C3" s="1">
-        <v>99.77739538005686</v>
+        <v>99.77739535131724</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9623,10 +9624,10 @@
         <v>44951</v>
       </c>
       <c r="B4" s="1">
-        <v>234.4564971923828</v>
+        <v>234.4564514160156</v>
       </c>
       <c r="C4" s="1">
-        <v>99.18791014969005</v>
+        <v>99.18790358954192</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9634,10 +9635,10 @@
         <v>44952</v>
       </c>
       <c r="B5" s="1">
-        <v>241.6574554443359</v>
+        <v>241.657470703125</v>
       </c>
       <c r="C5" s="1">
-        <v>102.2343089854635</v>
+        <v>102.2343286398336</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -9645,10 +9646,10 @@
         <v>44953</v>
       </c>
       <c r="B6" s="1">
-        <v>241.8133544921875</v>
+        <v>241.8133850097656</v>
       </c>
       <c r="C6" s="1">
-        <v>102.3002628017829</v>
+        <v>102.3002889199705</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -9656,10 +9657,10 @@
         <v>44956</v>
       </c>
       <c r="B7" s="1">
-        <v>236.5027313232422</v>
+        <v>236.5027770996094</v>
       </c>
       <c r="C7" s="1">
-        <v>100.0535790031762</v>
+        <v>100.0536112866057</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9667,10 +9668,10 @@
         <v>44957</v>
       </c>
       <c r="B8" s="1">
-        <v>241.4723205566406</v>
+        <v>241.4723052978516</v>
       </c>
       <c r="C8" s="1">
-        <v>102.1559868113024</v>
+        <v>102.1559935449558</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -9678,10 +9679,10 @@
         <v>44958</v>
       </c>
       <c r="B9" s="1">
-        <v>246.2859344482422</v>
+        <v>246.2859802246094</v>
       </c>
       <c r="C9" s="1">
-        <v>104.1924085266013</v>
+        <v>104.1924413443787</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9689,10 +9690,10 @@
         <v>44959</v>
       </c>
       <c r="B10" s="1">
-        <v>257.8329772949219</v>
+        <v>257.8328857421875</v>
       </c>
       <c r="C10" s="1">
-        <v>109.0774386370328</v>
+        <v>109.0774139877753</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9700,10 +9701,10 @@
         <v>44960</v>
       </c>
       <c r="B11" s="1">
-        <v>251.7427520751953</v>
+        <v>251.7427978515625</v>
       </c>
       <c r="C11" s="1">
-        <v>106.5009405697178</v>
+        <v>106.5009736855407</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9711,10 +9712,10 @@
         <v>44963</v>
       </c>
       <c r="B12" s="1">
-        <v>250.2031402587891</v>
+        <v>250.2031555175781</v>
       </c>
       <c r="C12" s="1">
-        <v>105.8496006395396</v>
+        <v>105.8496207606657</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9722,10 +9723,10 @@
         <v>44964</v>
       </c>
       <c r="B13" s="1">
-        <v>260.7172546386719</v>
+        <v>260.7171936035156</v>
       </c>
       <c r="C13" s="1">
-        <v>110.2976455643073</v>
+        <v>110.2976339831908</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9733,10 +9734,10 @@
         <v>44965</v>
       </c>
       <c r="B14" s="1">
-        <v>259.9083862304688</v>
+        <v>259.9084777832031</v>
       </c>
       <c r="C14" s="1">
-        <v>109.9554500271542</v>
+        <v>109.9555029548824</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9747,7 +9748,7 @@
         <v>256.8780212402344</v>
       </c>
       <c r="C15" s="1">
-        <v>108.673440042481</v>
+        <v>108.6734540728795</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9755,10 +9756,10 @@
         <v>44967</v>
       </c>
       <c r="B16" s="1">
-        <v>256.3713073730469</v>
+        <v>256.3712768554688</v>
       </c>
       <c r="C16" s="1">
-        <v>108.4590723873635</v>
+        <v>108.459073479481</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9766,10 +9767,10 @@
         <v>44970</v>
       </c>
       <c r="B17" s="1">
-        <v>264.3810424804688</v>
+        <v>264.381103515625</v>
       </c>
       <c r="C17" s="1">
-        <v>111.8476280284805</v>
+        <v>111.8476682898955</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9777,10 +9778,10 @@
         <v>44971</v>
       </c>
       <c r="B18" s="1">
-        <v>265.2093200683594</v>
+        <v>265.2093811035156</v>
       </c>
       <c r="C18" s="1">
-        <v>112.1980347092529</v>
+        <v>112.1980750159075</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9791,7 +9792,7 @@
         <v>263.0895385742188</v>
       </c>
       <c r="C19" s="1">
-        <v>111.301251302115</v>
+        <v>111.3012656717798</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9799,10 +9800,10 @@
         <v>44973</v>
       </c>
       <c r="B20" s="1">
-        <v>256.0853576660156</v>
+        <v>256.0853881835938</v>
       </c>
       <c r="C20" s="1">
-        <v>108.3381000356139</v>
+        <v>108.3381269333227</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9810,10 +9811,10 @@
         <v>44974</v>
       </c>
       <c r="B21" s="1">
-        <v>252.0900115966797</v>
+        <v>252.0899963378906</v>
       </c>
       <c r="C21" s="1">
-        <v>106.647850323246</v>
+        <v>106.6478576368261</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9821,10 +9822,10 @@
         <v>44978</v>
       </c>
       <c r="B22" s="1">
-        <v>246.82470703125</v>
+        <v>246.8246917724609</v>
       </c>
       <c r="C22" s="1">
-        <v>104.4203387703541</v>
+        <v>104.420345796349</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9835,7 +9836,7 @@
         <v>245.6915283203125</v>
       </c>
       <c r="C23" s="1">
-        <v>103.9409422532604</v>
+        <v>103.9409556726648</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9846,7 +9847,7 @@
         <v>248.8761138916016</v>
       </c>
       <c r="C24" s="1">
-        <v>105.2881959710784</v>
+        <v>105.2882095644214</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9854,10 +9855,10 @@
         <v>44981</v>
       </c>
       <c r="B25" s="1">
-        <v>243.4545593261719</v>
+        <v>243.4544982910156</v>
       </c>
       <c r="C25" s="1">
-        <v>102.9945821299306</v>
+        <v>102.9945696059445</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9865,10 +9866,10 @@
         <v>44984</v>
       </c>
       <c r="B26" s="1">
-        <v>244.3727569580078</v>
+        <v>244.3727874755859</v>
       </c>
       <c r="C26" s="1">
-        <v>103.3830299029581</v>
+        <v>103.3830561609374</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9879,7 +9880,7 @@
         <v>243.6498718261719</v>
       </c>
       <c r="C27" s="1">
-        <v>103.0772099902506</v>
+        <v>103.0772232981418</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9890,7 +9891,7 @@
         <v>240.5727691650391</v>
       </c>
       <c r="C28" s="1">
-        <v>101.7754274168149</v>
+        <v>101.7754405566381</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9898,10 +9899,10 @@
         <v>44987</v>
       </c>
       <c r="B29" s="1">
-        <v>245.3007965087891</v>
+        <v>245.3008117675781</v>
       </c>
       <c r="C29" s="1">
-        <v>103.7756413455095</v>
+        <v>103.7756611988749</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -9909,10 +9910,10 @@
         <v>44988</v>
       </c>
       <c r="B30" s="1">
-        <v>249.3840789794922</v>
+        <v>249.3840942382812</v>
       </c>
       <c r="C30" s="1">
-        <v>105.5030929609261</v>
+        <v>105.503113037316</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9920,10 +9921,10 @@
         <v>44991</v>
       </c>
       <c r="B31" s="1">
-        <v>250.9275665283203</v>
+        <v>250.9275512695312</v>
       </c>
       <c r="C31" s="1">
-        <v>106.1560725377075</v>
+        <v>106.1560797877961</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -9934,7 +9935,7 @@
         <v>248.2704315185547</v>
       </c>
       <c r="C32" s="1">
-        <v>105.0319592298644</v>
+        <v>105.0319727901257</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9942,10 +9943,10 @@
         <v>44993</v>
       </c>
       <c r="B33" s="1">
-        <v>247.8308715820312</v>
+        <v>247.8308410644531</v>
       </c>
       <c r="C33" s="1">
-        <v>104.8460013570335</v>
+        <v>104.8460019826816</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -9953,10 +9954,10 @@
         <v>44994</v>
       </c>
       <c r="B34" s="1">
-        <v>246.4828186035156</v>
+        <v>246.4828033447266</v>
       </c>
       <c r="C34" s="1">
-        <v>104.2757012829847</v>
+        <v>104.2757082903061</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9964,10 +9965,10 @@
         <v>44995</v>
       </c>
       <c r="B35" s="1">
-        <v>242.839111328125</v>
+        <v>242.8390960693359</v>
       </c>
       <c r="C35" s="1">
-        <v>102.7342139957006</v>
+        <v>102.7342208040066</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -9978,7 +9979,7 @@
         <v>248.0457916259766</v>
       </c>
       <c r="C36" s="1">
-        <v>104.9369242798934</v>
+        <v>104.936937827885</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9989,7 +9990,7 @@
         <v>254.7568511962891</v>
       </c>
       <c r="C37" s="1">
-        <v>107.7760692028987</v>
+        <v>107.7760831174411</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9997,10 +9998,10 @@
         <v>45000</v>
       </c>
       <c r="B38" s="1">
-        <v>259.2992858886719</v>
+        <v>259.2992553710938</v>
       </c>
       <c r="C38" s="1">
-        <v>109.6977672983846</v>
+        <v>109.6977685504251</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -10008,10 +10009,10 @@
         <v>45001</v>
       </c>
       <c r="B39" s="1">
-        <v>269.8103332519531</v>
+        <v>269.8103637695312</v>
       </c>
       <c r="C39" s="1">
-        <v>114.1445147075332</v>
+        <v>114.1445423548853</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -10019,10 +10020,10 @@
         <v>45002</v>
       </c>
       <c r="B40" s="1">
-        <v>272.9656677246094</v>
+        <v>272.9656066894531</v>
       </c>
       <c r="C40" s="1">
-        <v>115.479393612208</v>
+        <v>115.4793827000865</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -10030,10 +10031,10 @@
         <v>45005</v>
       </c>
       <c r="B41" s="1">
-        <v>265.9322814941406</v>
+        <v>265.9322509765625</v>
       </c>
       <c r="C41" s="1">
-        <v>112.5038868984684</v>
+        <v>112.5038885127958</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -10041,10 +10042,10 @@
         <v>45006</v>
       </c>
       <c r="B42" s="1">
-        <v>267.4463500976562</v>
+        <v>267.4463195800781</v>
       </c>
       <c r="C42" s="1">
-        <v>113.1444206537891</v>
+        <v>113.1444223508133</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -10055,7 +10056,7 @@
         <v>265.9908142089844</v>
       </c>
       <c r="C43" s="1">
-        <v>112.528649435358</v>
+        <v>112.5286639634873</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -10063,10 +10064,10 @@
         <v>45008</v>
       </c>
       <c r="B44" s="1">
-        <v>271.236572265625</v>
+        <v>271.2366027832031</v>
       </c>
       <c r="C44" s="1">
-        <v>114.7478917469163</v>
+        <v>114.747919472168</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -10074,10 +10075,10 @@
         <v>45009</v>
       </c>
       <c r="B45" s="1">
-        <v>274.0792541503906</v>
+        <v>274.0792846679688</v>
       </c>
       <c r="C45" s="1">
-        <v>115.9505015220633</v>
+        <v>115.9505294025792</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -10088,7 +10089,7 @@
         <v>269.9861755371094</v>
       </c>
       <c r="C46" s="1">
-        <v>114.2189056030275</v>
+        <v>114.218920349379</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -10096,10 +10097,10 @@
         <v>45013</v>
       </c>
       <c r="B47" s="1">
-        <v>268.8627624511719</v>
+        <v>268.8628234863281</v>
       </c>
       <c r="C47" s="1">
-        <v>113.7436404789498</v>
+        <v>113.7436809851514</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -10107,10 +10108,10 @@
         <v>45014</v>
       </c>
       <c r="B48" s="1">
-        <v>274.0207214355469</v>
+        <v>274.0206604003906</v>
       </c>
       <c r="C48" s="1">
-        <v>115.9257389851737</v>
+        <v>115.9257281306781</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -10118,10 +10119,10 @@
         <v>45015</v>
       </c>
       <c r="B49" s="1">
-        <v>277.478759765625</v>
+        <v>277.4787292480469</v>
       </c>
       <c r="C49" s="1">
-        <v>117.3886781627411</v>
+        <v>117.3886804077246</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -10132,7 +10133,7 @@
         <v>281.6304016113281</v>
       </c>
       <c r="C50" s="1">
-        <v>119.1450495292697</v>
+        <v>119.1450649116162</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -10140,10 +10141,10 @@
         <v>45019</v>
       </c>
       <c r="B51" s="1">
-        <v>280.5852355957031</v>
+        <v>280.585205078125</v>
       </c>
       <c r="C51" s="1">
-        <v>118.7028871917327</v>
+        <v>118.7028896063886</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -10151,10 +10152,10 @@
         <v>45020</v>
       </c>
       <c r="B52" s="1">
-        <v>280.5362854003906</v>
+        <v>280.5363464355469</v>
       </c>
       <c r="C52" s="1">
-        <v>118.68217858424</v>
+        <v>118.6822197280368</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -10165,7 +10166,7 @@
         <v>277.7620544433594</v>
       </c>
       <c r="C53" s="1">
-        <v>117.5085272920145</v>
+        <v>117.5085424630762</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -10173,10 +10174,10 @@
         <v>45022</v>
       </c>
       <c r="B54" s="1">
-        <v>284.8540954589844</v>
+        <v>284.8540649414062</v>
       </c>
       <c r="C54" s="1">
-        <v>120.5088481850565</v>
+        <v>120.5088508328728</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -10184,10 +10185,10 @@
         <v>45026</v>
       </c>
       <c r="B55" s="1">
-        <v>282.6952209472656</v>
+        <v>282.6951599121094</v>
       </c>
       <c r="C55" s="1">
-        <v>119.5955262952514</v>
+        <v>119.5955159145476</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -10198,7 +10199,7 @@
         <v>276.2869567871094</v>
       </c>
       <c r="C56" s="1">
-        <v>116.8844803769483</v>
+        <v>116.8844954674417</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -10206,10 +10207,10 @@
         <v>45028</v>
       </c>
       <c r="B57" s="1">
-        <v>276.9316711425781</v>
+        <v>276.9317016601562</v>
       </c>
       <c r="C57" s="1">
-        <v>117.1572297796231</v>
+        <v>117.1572578159349</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -10217,10 +10218,10 @@
         <v>45029</v>
       </c>
       <c r="B58" s="1">
-        <v>283.1347961425781</v>
+        <v>283.1348266601562</v>
       </c>
       <c r="C58" s="1">
-        <v>119.7814906233839</v>
+        <v>119.7815189985037</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -10228,10 +10229,10 @@
         <v>45030</v>
       </c>
       <c r="B59" s="1">
-        <v>279.5204162597656</v>
+        <v>279.5204467773438</v>
       </c>
       <c r="C59" s="1">
-        <v>118.252410425751</v>
+        <v>118.2524386034573</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -10239,10 +10240,10 @@
         <v>45033</v>
       </c>
       <c r="B60" s="1">
-        <v>282.1188354492188</v>
+        <v>282.1188049316406</v>
       </c>
       <c r="C60" s="1">
-        <v>119.3516837330854</v>
+        <v>119.3516862315048</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -10250,10 +10251,10 @@
         <v>45034</v>
       </c>
       <c r="B61" s="1">
-        <v>281.6988220214844</v>
+        <v>281.6987915039062</v>
       </c>
       <c r="C61" s="1">
-        <v>119.1739951015881</v>
+        <v>119.1739975770668</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -10264,7 +10265,7 @@
         <v>281.7769470214844</v>
       </c>
       <c r="C62" s="1">
-        <v>119.207046245716</v>
+        <v>119.2070616360667</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -10272,10 +10273,10 @@
         <v>45036</v>
       </c>
       <c r="B63" s="1">
-        <v>279.4910583496094</v>
+        <v>279.4910888671875</v>
       </c>
       <c r="C63" s="1">
-        <v>118.2399904254967</v>
+        <v>118.2400186015994</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -10286,7 +10287,7 @@
         <v>279.1492004394531</v>
       </c>
       <c r="C64" s="1">
-        <v>118.0953658487305</v>
+        <v>118.0953810955565</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -10297,7 +10298,7 @@
         <v>275.2514953613281</v>
       </c>
       <c r="C65" s="1">
-        <v>116.446423611221</v>
+        <v>116.4464386451586</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -10308,7 +10309,7 @@
         <v>269.0484008789062</v>
       </c>
       <c r="C66" s="1">
-        <v>113.8221756780633</v>
+        <v>113.8221903731946</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -10316,10 +10317,10 @@
         <v>45042</v>
       </c>
       <c r="B67" s="1">
-        <v>288.5368957519531</v>
+        <v>288.536865234375</v>
       </c>
       <c r="C67" s="1">
-        <v>122.0668739550077</v>
+        <v>122.0668768039746</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -10327,10 +10328,10 @@
         <v>45043</v>
       </c>
       <c r="B68" s="1">
-        <v>297.7779846191406</v>
+        <v>297.7780151367188</v>
       </c>
       <c r="C68" s="1">
-        <v>125.9763595236323</v>
+        <v>125.9763886985471</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -10341,7 +10342,7 @@
         <v>300.1517944335938</v>
       </c>
       <c r="C69" s="1">
-        <v>126.9806107915988</v>
+        <v>126.9806271855637</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -10352,7 +10353,7 @@
         <v>298.4911804199219</v>
       </c>
       <c r="C70" s="1">
-        <v>126.2780803198318</v>
+        <v>126.2780966230957</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -10360,10 +10361,10 @@
         <v>45048</v>
       </c>
       <c r="B71" s="1">
-        <v>298.3446044921875</v>
+        <v>298.3446655273438</v>
       </c>
       <c r="C71" s="1">
-        <v>126.2160706927823</v>
+        <v>126.2161128092501</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -10371,10 +10372,10 @@
         <v>45049</v>
       </c>
       <c r="B72" s="1">
-        <v>297.3579711914062</v>
+        <v>297.3580322265625</v>
       </c>
       <c r="C72" s="1">
-        <v>125.798670892135</v>
+        <v>125.7987129547139</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -10382,10 +10383,10 @@
         <v>45050</v>
       </c>
       <c r="B73" s="1">
-        <v>298.3446044921875</v>
+        <v>298.3446655273438</v>
       </c>
       <c r="C73" s="1">
-        <v>126.2160706927823</v>
+        <v>126.2161128092501</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -10393,10 +10394,10 @@
         <v>45051</v>
       </c>
       <c r="B74" s="1">
-        <v>303.4634094238281</v>
+        <v>303.4633483886719</v>
       </c>
       <c r="C74" s="1">
-        <v>128.3816048951327</v>
+        <v>128.3815956487647</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -10407,7 +10408,7 @@
         <v>301.5096740722656</v>
       </c>
       <c r="C75" s="1">
-        <v>127.5550680798699</v>
+        <v>127.5550845480007</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -10415,10 +10416,10 @@
         <v>45055</v>
       </c>
       <c r="B76" s="1">
-        <v>299.8977966308594</v>
+        <v>299.8978271484375</v>
       </c>
       <c r="C76" s="1">
-        <v>126.8731558413733</v>
+        <v>126.87318513207</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -10429,7 +10430,7 @@
         <v>305.0849914550781</v>
       </c>
       <c r="C77" s="1">
-        <v>129.0676227054388</v>
+        <v>129.0676393688496</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -10437,10 +10438,10 @@
         <v>45057</v>
       </c>
       <c r="B78" s="1">
-        <v>302.9359130859375</v>
+        <v>302.9358520507812</v>
       </c>
       <c r="C78" s="1">
-        <v>128.158445119253</v>
+        <v>128.1584358440737</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -10451,7 +10452,7 @@
         <v>301.8222351074219</v>
       </c>
       <c r="C79" s="1">
-        <v>127.6872984775881</v>
+        <v>127.6873149627907</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -10459,10 +10460,10 @@
         <v>45061</v>
       </c>
       <c r="B80" s="1">
-        <v>302.3009643554688</v>
+        <v>302.3008728027344</v>
       </c>
       <c r="C80" s="1">
-        <v>127.8898271095942</v>
+        <v>127.8898048891299</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -10473,7 +10474,7 @@
         <v>304.5281677246094</v>
       </c>
       <c r="C81" s="1">
-        <v>128.832055839908</v>
+        <v>128.8320724729057</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -10484,7 +10485,7 @@
         <v>307.4064636230469</v>
       </c>
       <c r="C82" s="1">
-        <v>130.0497322889602</v>
+        <v>130.0497490791672</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -10492,10 +10493,10 @@
         <v>45064</v>
       </c>
       <c r="B83" s="1">
-        <v>311.8315124511719</v>
+        <v>311.83154296875</v>
       </c>
       <c r="C83" s="1">
-        <v>131.9217697493335</v>
+        <v>131.9217996918368</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -10503,10 +10504,10 @@
         <v>45065</v>
       </c>
       <c r="B84" s="1">
-        <v>311.6553344726562</v>
+        <v>311.6553039550781</v>
       </c>
       <c r="C84" s="1">
-        <v>131.8472368372043</v>
+        <v>131.8472409488752</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -10517,7 +10518,7 @@
         <v>314.4356384277344</v>
       </c>
       <c r="C85" s="1">
-        <v>133.0234573394617</v>
+        <v>133.0234745135946</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -10525,10 +10526,10 @@
         <v>45069</v>
       </c>
       <c r="B86" s="1">
-        <v>308.6399536132812</v>
+        <v>308.6399841308594</v>
       </c>
       <c r="C86" s="1">
-        <v>130.5715659586901</v>
+        <v>130.5715957268738</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -10536,10 +10537,10 @@
         <v>45070</v>
       </c>
       <c r="B87" s="1">
-        <v>307.2596130371094</v>
+        <v>307.2595825195312</v>
       </c>
       <c r="C87" s="1">
-        <v>129.9876064664822</v>
+        <v>129.9876103380635</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -10547,10 +10548,10 @@
         <v>45071</v>
       </c>
       <c r="B88" s="1">
-        <v>319.076171875</v>
+        <v>319.0761413574219</v>
       </c>
       <c r="C88" s="1">
-        <v>134.9866565688536</v>
+        <v>134.9866610858425</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -10561,7 +10562,7 @@
         <v>325.8997802734375</v>
       </c>
       <c r="C89" s="1">
-        <v>137.8734157963683</v>
+        <v>137.8734335966602</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -10569,10 +10570,10 @@
         <v>45076</v>
       </c>
       <c r="B90" s="1">
-        <v>324.2550354003906</v>
+        <v>324.2550048828125</v>
       </c>
       <c r="C90" s="1">
-        <v>137.1775988382523</v>
+        <v>137.1776036381052</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -10580,10 +10581,10 @@
         <v>45077</v>
       </c>
       <c r="B91" s="1">
-        <v>321.4942932128906</v>
+        <v>321.4942016601562</v>
       </c>
       <c r="C91" s="1">
-        <v>136.0096540326301</v>
+        <v>136.0096328604846</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -10594,7 +10595,7 @@
         <v>325.5962829589844</v>
       </c>
       <c r="C92" s="1">
-        <v>137.745019847793</v>
+        <v>137.7450376315082</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -10602,10 +10603,10 @@
         <v>45079</v>
       </c>
       <c r="B93" s="1">
-        <v>328.3570556640625</v>
+        <v>328.3570251464844</v>
       </c>
       <c r="C93" s="1">
-        <v>138.9129775640183</v>
+        <v>138.9129825879191</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -10613,10 +10614,10 @@
         <v>45082</v>
       </c>
       <c r="B94" s="1">
-        <v>328.8858032226562</v>
+        <v>328.8857727050781</v>
       </c>
       <c r="C94" s="1">
-        <v>139.1366666746282</v>
+        <v>139.1366717274086</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -10624,10 +10625,10 @@
         <v>45083</v>
       </c>
       <c r="B95" s="1">
-        <v>326.6731567382812</v>
+        <v>326.6731872558594</v>
       </c>
       <c r="C95" s="1">
-        <v>138.2005963020288</v>
+        <v>138.2006270551666</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -10635,10 +10636,10 @@
         <v>45084</v>
       </c>
       <c r="B96" s="1">
-        <v>316.5894165039062</v>
+        <v>316.5894775390625</v>
       </c>
       <c r="C96" s="1">
-        <v>133.9346231585365</v>
+        <v>133.9346662715161</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -10646,10 +10647,10 @@
         <v>45085</v>
       </c>
       <c r="B97" s="1">
-        <v>318.4300537109375</v>
+        <v>318.4299621582031</v>
       </c>
       <c r="C97" s="1">
-        <v>134.7133132784327</v>
+        <v>134.7132919389217</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -10657,10 +10658,10 @@
         <v>45086</v>
       </c>
       <c r="B98" s="1">
-        <v>319.9278869628906</v>
+        <v>319.9278259277344</v>
       </c>
       <c r="C98" s="1">
-        <v>135.3469785928643</v>
+        <v>135.3469702457682</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -10668,10 +10669,10 @@
         <v>45089</v>
       </c>
       <c r="B99" s="1">
-        <v>324.8816223144531</v>
+        <v>324.8816528320312</v>
       </c>
       <c r="C99" s="1">
-        <v>137.4426793426411</v>
+        <v>137.4427099979272</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -10679,10 +10680,10 @@
         <v>45090</v>
       </c>
       <c r="B100" s="1">
-        <v>327.2703857421875</v>
+        <v>327.2704162597656</v>
       </c>
       <c r="C100" s="1">
-        <v>138.4532568061634</v>
+        <v>138.4532875919211</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -10690,10 +10691,10 @@
         <v>45091</v>
       </c>
       <c r="B101" s="1">
-        <v>330.2563171386719</v>
+        <v>330.2563781738281</v>
       </c>
       <c r="C101" s="1">
-        <v>139.7164689526138</v>
+        <v>139.7165128120647</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -10701,10 +10702,10 @@
         <v>45092</v>
       </c>
       <c r="B102" s="1">
-        <v>340.7903747558594</v>
+        <v>340.7903442382812</v>
       </c>
       <c r="C102" s="1">
-        <v>144.1729509565563</v>
+        <v>144.1729566595514</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -10712,10 +10713,10 @@
         <v>45093</v>
       </c>
       <c r="B103" s="1">
-        <v>335.1415405273438</v>
+        <v>335.1415100097656</v>
       </c>
       <c r="C103" s="1">
-        <v>141.7831853982627</v>
+        <v>141.7831907927247</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -10726,7 +10727,7 @@
         <v>330.951416015625</v>
       </c>
       <c r="C104" s="1">
-        <v>140.0105337611305</v>
+        <v>140.0105518373372</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -10737,7 +10738,7 @@
         <v>326.5557250976562</v>
       </c>
       <c r="C105" s="1">
-        <v>138.1509163010115</v>
+        <v>138.1509341371304</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -10745,10 +10746,10 @@
         <v>45099</v>
       </c>
       <c r="B106" s="1">
-        <v>332.5765686035156</v>
+        <v>332.5765380859375</v>
       </c>
       <c r="C106" s="1">
-        <v>140.6980621120081</v>
+        <v>140.6980673663741</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -10756,10 +10757,10 @@
         <v>45100</v>
       </c>
       <c r="B107" s="1">
-        <v>327.9849853515625</v>
+        <v>327.9850158691406</v>
       </c>
       <c r="C107" s="1">
-        <v>138.7555714901089</v>
+        <v>138.7556023148973</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -10770,7 +10771,7 @@
         <v>321.6998291015625</v>
       </c>
       <c r="C108" s="1">
-        <v>136.0966069450137</v>
+        <v>136.0966245159088</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -10778,10 +10779,10 @@
         <v>45104</v>
       </c>
       <c r="B109" s="1">
-        <v>327.5444946289062</v>
+        <v>327.5445251464844</v>
       </c>
       <c r="C109" s="1">
-        <v>138.5692198438811</v>
+        <v>138.5692506446104</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -10792,7 +10793,7 @@
         <v>328.797607421875</v>
       </c>
       <c r="C110" s="1">
-        <v>139.0993550314525</v>
+        <v>139.0993729900206</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -10800,10 +10801,10 @@
         <v>45106</v>
       </c>
       <c r="B111" s="1">
-        <v>328.0144348144531</v>
+        <v>328.0143737792969</v>
       </c>
       <c r="C111" s="1">
-        <v>138.7680302221728</v>
+        <v>138.7680223167551</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -10814,7 +10815,7 @@
         <v>333.3891296386719</v>
       </c>
       <c r="C112" s="1">
-        <v>141.0418198321454</v>
+        <v>141.0418380414974</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -10822,10 +10823,10 @@
         <v>45110</v>
       </c>
       <c r="B113" s="1">
-        <v>330.8927001953125</v>
+        <v>330.8926696777344</v>
       </c>
       <c r="C113" s="1">
-        <v>139.9856937606218</v>
+        <v>139.9856989230167</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -10836,7 +10837,7 @@
         <v>331.04931640625</v>
       </c>
       <c r="C114" s="1">
-        <v>140.0519509761158</v>
+        <v>140.0519690576698</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -10844,10 +10845,10 @@
         <v>45113</v>
       </c>
       <c r="B115" s="1">
-        <v>334.1038208007812</v>
+        <v>334.103759765625</v>
       </c>
       <c r="C115" s="1">
-        <v>141.3441732479004</v>
+        <v>141.3441656750784</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -10855,10 +10856,10 @@
         <v>45114</v>
       </c>
       <c r="B116" s="1">
-        <v>330.1388244628906</v>
+        <v>330.1388854980469</v>
       </c>
       <c r="C116" s="1">
-        <v>139.6667631303901</v>
+        <v>139.6668069834236</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -10866,10 +10867,10 @@
         <v>45117</v>
       </c>
       <c r="B117" s="1">
-        <v>324.8620300292969</v>
+        <v>324.862060546875</v>
       </c>
       <c r="C117" s="1">
-        <v>137.4343907354028</v>
+        <v>137.4344213896187</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -10877,10 +10878,10 @@
         <v>45118</v>
       </c>
       <c r="B118" s="1">
-        <v>325.4886169433594</v>
+        <v>325.4885559082031</v>
       </c>
       <c r="C118" s="1">
-        <v>137.6994712397917</v>
+        <v>137.6994631964166</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -10891,7 +10892,7 @@
         <v>330.1192932128906</v>
       </c>
       <c r="C119" s="1">
-        <v>139.6585003443581</v>
+        <v>139.6585183751152</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -10902,7 +10903,7 @@
         <v>335.464599609375</v>
       </c>
       <c r="C120" s="1">
-        <v>141.9198570434732</v>
+        <v>141.9198753661851</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -10910,10 +10911,10 @@
         <v>45121</v>
       </c>
       <c r="B121" s="1">
-        <v>337.9904479980469</v>
+        <v>337.9904174804688</v>
       </c>
       <c r="C121" s="1">
-        <v>142.9884289364574</v>
+        <v>142.9884344865236</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -10924,7 +10925,7 @@
         <v>338.4701538085938</v>
       </c>
       <c r="C122" s="1">
-        <v>143.1913707077651</v>
+        <v>143.1913891946371</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -10932,10 +10933,10 @@
         <v>45125</v>
       </c>
       <c r="B123" s="1">
-        <v>351.9411926269531</v>
+        <v>351.9412231445312</v>
       </c>
       <c r="C123" s="1">
-        <v>148.8903562506653</v>
+        <v>148.8903883839157</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -10946,7 +10947,7 @@
         <v>347.623779296875</v>
       </c>
       <c r="C124" s="1">
-        <v>147.0638544876902</v>
+        <v>147.0638734745233</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -10954,10 +10955,10 @@
         <v>45127</v>
       </c>
       <c r="B125" s="1">
-        <v>339.586181640625</v>
+        <v>339.5862121582031</v>
       </c>
       <c r="C125" s="1">
-        <v>143.6635114658744</v>
+        <v>143.6635429243075</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -10965,10 +10966,10 @@
         <v>45128</v>
       </c>
       <c r="B126" s="1">
-        <v>336.55126953125</v>
+        <v>336.5513000488281</v>
       </c>
       <c r="C126" s="1">
-        <v>142.3795778013281</v>
+        <v>142.3796090939977</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -10976,10 +10977,10 @@
         <v>45131</v>
       </c>
       <c r="B127" s="1">
-        <v>337.8631286621094</v>
+        <v>337.8631591796875</v>
       </c>
       <c r="C127" s="1">
-        <v>142.9345659000114</v>
+        <v>142.9345972643332</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -10987,10 +10988,10 @@
         <v>45132</v>
       </c>
       <c r="B128" s="1">
-        <v>343.6099243164062</v>
+        <v>343.6099853515625</v>
       </c>
       <c r="C128" s="1">
-        <v>145.3657744944966</v>
+        <v>145.365819083307</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -11001,7 +11002,7 @@
         <v>330.6773071289062</v>
       </c>
       <c r="C129" s="1">
-        <v>139.8945707234127</v>
+        <v>139.894588784648</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -11009,10 +11010,10 @@
         <v>45134</v>
       </c>
       <c r="B130" s="1">
-        <v>323.7753601074219</v>
+        <v>323.7752990722656</v>
       </c>
       <c r="C130" s="1">
-        <v>136.9746699775478</v>
+        <v>136.9746618405965</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -11020,10 +11021,10 @@
         <v>45135</v>
       </c>
       <c r="B131" s="1">
-        <v>331.2647399902344</v>
+        <v>331.2647094726562</v>
       </c>
       <c r="C131" s="1">
-        <v>140.1430869239281</v>
+        <v>140.1430921066434</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -11031,10 +11032,10 @@
         <v>45138</v>
       </c>
       <c r="B132" s="1">
-        <v>328.8661499023438</v>
+        <v>328.8661193847656</v>
       </c>
       <c r="C132" s="1">
-        <v>139.1283522461835</v>
+        <v>139.1283572978905</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -11045,7 +11046,7 @@
         <v>329.2773132324219</v>
       </c>
       <c r="C133" s="1">
-        <v>139.3022968027601</v>
+        <v>139.3023147875292</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -11053,10 +11054,10 @@
         <v>45140</v>
       </c>
       <c r="B134" s="1">
-        <v>320.6229858398438</v>
+        <v>320.6229553222656</v>
       </c>
       <c r="C134" s="1">
-        <v>135.641043401381</v>
+        <v>135.6410480028553</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -11064,10 +11065,10 @@
         <v>45141</v>
       </c>
       <c r="B135" s="1">
-        <v>319.8005676269531</v>
+        <v>319.8006286621094</v>
       </c>
       <c r="C135" s="1">
-        <v>135.2931155564183</v>
+        <v>135.2931588447875</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -11075,10 +11076,10 @@
         <v>45142</v>
       </c>
       <c r="B136" s="1">
-        <v>320.8970642089844</v>
+        <v>320.8970947265625</v>
       </c>
       <c r="C136" s="1">
-        <v>135.7569935284956</v>
+        <v>135.7570239661494</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -11086,10 +11087,10 @@
         <v>45145</v>
       </c>
       <c r="B137" s="1">
-        <v>323.1781005859375</v>
+        <v>323.1781616210938</v>
       </c>
       <c r="C137" s="1">
-        <v>136.7219965628101</v>
+        <v>136.7220400356565</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -11097,10 +11098,10 @@
         <v>45146</v>
       </c>
       <c r="B138" s="1">
-        <v>319.2033996582031</v>
+        <v>319.203369140625</v>
       </c>
       <c r="C138" s="1">
-        <v>135.0404808734901</v>
+        <v>135.0404853974281</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -11108,10 +11109,10 @@
         <v>45147</v>
       </c>
       <c r="B139" s="1">
-        <v>315.463623046875</v>
+        <v>315.4636535644531</v>
       </c>
       <c r="C139" s="1">
-        <v>133.4583510074112</v>
+        <v>133.4583811482963</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -11119,10 +11120,10 @@
         <v>45148</v>
       </c>
       <c r="B140" s="1">
-        <v>316.14892578125</v>
+        <v>316.1489562988281</v>
       </c>
       <c r="C140" s="1">
-        <v>133.7482715123087</v>
+        <v>133.7483016906243</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -11130,10 +11131,10 @@
         <v>45149</v>
       </c>
       <c r="B141" s="1">
-        <v>314.269287109375</v>
+        <v>314.2692260742188</v>
       </c>
       <c r="C141" s="1">
-        <v>132.9530816415548</v>
+        <v>132.9530729853921</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -11144,7 +11145,7 @@
         <v>317.235595703125</v>
       </c>
       <c r="C142" s="1">
-        <v>134.2079922701637</v>
+        <v>134.2080095972272</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -11155,7 +11156,7 @@
         <v>315.101318359375</v>
       </c>
       <c r="C143" s="1">
-        <v>133.3050763265177</v>
+        <v>133.3050935370093</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -11163,10 +11164,10 @@
         <v>45154</v>
       </c>
       <c r="B144" s="1">
-        <v>314.3361511230469</v>
+        <v>314.336181640625</v>
       </c>
       <c r="C144" s="1">
-        <v>132.9813687731112</v>
+        <v>132.9813988524151</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -11174,10 +11175,10 @@
         <v>45155</v>
       </c>
       <c r="B145" s="1">
-        <v>310.8827514648438</v>
+        <v>310.8828125</v>
       </c>
       <c r="C145" s="1">
-        <v>131.5203920072263</v>
+        <v>131.5204348085141</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -11185,10 +11186,10 @@
         <v>45156</v>
       </c>
       <c r="B146" s="1">
-        <v>310.4904174804688</v>
+        <v>310.4903259277344</v>
       </c>
       <c r="C146" s="1">
-        <v>131.3544132928087</v>
+        <v>131.3543915196434</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -11196,10 +11197,10 @@
         <v>45159</v>
       </c>
       <c r="B147" s="1">
-        <v>315.7881469726562</v>
+        <v>315.7881164550781</v>
       </c>
       <c r="C147" s="1">
-        <v>133.595642361574</v>
+        <v>133.5956466989746</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -11207,10 +11208,10 @@
         <v>45160</v>
       </c>
       <c r="B148" s="1">
-        <v>316.3571166992188</v>
+        <v>316.3571472167969</v>
       </c>
       <c r="C148" s="1">
-        <v>133.8363476471685</v>
+        <v>133.8363778368553</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -11221,7 +11222,7 @@
         <v>320.811279296875</v>
       </c>
       <c r="C149" s="1">
-        <v>135.7207018229707</v>
+        <v>135.7207193453342</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -11229,10 +11230,10 @@
         <v>45162</v>
       </c>
       <c r="B150" s="1">
-        <v>313.9142761230469</v>
+        <v>313.914306640625</v>
       </c>
       <c r="C150" s="1">
-        <v>132.8028925948202</v>
+        <v>132.8029226510817</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -11243,7 +11244,7 @@
         <v>316.8673400878906</v>
       </c>
       <c r="C151" s="1">
-        <v>134.0522000216511</v>
+        <v>134.0522173286009</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -11254,7 +11255,7 @@
         <v>317.5736999511719</v>
       </c>
       <c r="C152" s="1">
-        <v>134.3510288427394</v>
+        <v>134.3510461882698</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -11265,7 +11266,7 @@
         <v>322.194580078125</v>
       </c>
       <c r="C153" s="1">
-        <v>136.3059136436866</v>
+        <v>136.3059312416045</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -11276,7 +11277,7 @@
         <v>322.5674133300781</v>
       </c>
       <c r="C154" s="1">
-        <v>136.4636424826754</v>
+        <v>136.463660100957</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -11284,10 +11285,10 @@
         <v>45169</v>
       </c>
       <c r="B155" s="1">
-        <v>321.5568542480469</v>
+        <v>321.556884765625</v>
       </c>
       <c r="C155" s="1">
-        <v>136.0361207691388</v>
+        <v>136.0361512428297</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -11295,10 +11296,10 @@
         <v>45170</v>
       </c>
       <c r="B156" s="1">
-        <v>322.4397888183594</v>
+        <v>322.4398193359375</v>
       </c>
       <c r="C156" s="1">
-        <v>136.4096503401976</v>
+        <v>136.4096808621134</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -11309,7 +11310,7 @@
         <v>327.2372436523438</v>
       </c>
       <c r="C157" s="1">
-        <v>138.4392358911153</v>
+        <v>138.439253764458</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -11317,10 +11318,10 @@
         <v>45175</v>
       </c>
       <c r="B158" s="1">
-        <v>326.5799255371094</v>
+        <v>326.5800170898438</v>
       </c>
       <c r="C158" s="1">
-        <v>138.1611544093292</v>
+        <v>138.1612109785845</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -11331,7 +11332,7 @@
         <v>323.6661682128906</v>
       </c>
       <c r="C159" s="1">
-        <v>136.9284758393877</v>
+        <v>136.9284935176821</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -11339,10 +11340,10 @@
         <v>45177</v>
       </c>
       <c r="B160" s="1">
-        <v>327.9436340332031</v>
+        <v>327.943603515625</v>
       </c>
       <c r="C160" s="1">
-        <v>138.7380776228068</v>
+        <v>138.7380826241269</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -11353,7 +11354,7 @@
         <v>331.544189453125</v>
       </c>
       <c r="C161" s="1">
-        <v>140.2613093172014</v>
+        <v>140.2613274257848</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -11361,10 +11362,10 @@
         <v>45181</v>
       </c>
       <c r="B162" s="1">
-        <v>325.490966796875</v>
+        <v>325.4909362792969</v>
       </c>
       <c r="C162" s="1">
-        <v>137.7004653562362</v>
+        <v>137.7004702235942</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -11372,10 +11373,10 @@
         <v>45182</v>
       </c>
       <c r="B163" s="1">
-        <v>329.6997985839844</v>
+        <v>329.6998291015625</v>
       </c>
       <c r="C163" s="1">
-        <v>139.4810311931147</v>
+        <v>139.4810621115643</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -11386,7 +11387,7 @@
         <v>332.2898559570312</v>
       </c>
       <c r="C164" s="1">
-        <v>140.5767669951791</v>
+        <v>140.57678514449</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -11394,10 +11395,10 @@
         <v>45184</v>
       </c>
       <c r="B165" s="1">
-        <v>323.9703063964844</v>
+        <v>323.9703369140625</v>
       </c>
       <c r="C165" s="1">
-        <v>137.0571429106296</v>
+        <v>137.0571735161406</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -11408,7 +11409,7 @@
         <v>322.8322448730469</v>
       </c>
       <c r="C166" s="1">
-        <v>136.575680697028</v>
+        <v>136.5756983297744</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -11416,10 +11417,10 @@
         <v>45188</v>
       </c>
       <c r="B167" s="1">
-        <v>322.4299926757812</v>
+        <v>322.4300231933594</v>
       </c>
       <c r="C167" s="1">
-        <v>136.4055060365785</v>
+        <v>136.4055365579592</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -11427,10 +11428,10 @@
         <v>45189</v>
       </c>
       <c r="B168" s="1">
-        <v>314.6991577148438</v>
+        <v>314.6991882324219</v>
       </c>
       <c r="C168" s="1">
-        <v>133.1349403978777</v>
+        <v>133.1349704970086</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -11438,10 +11439,10 @@
         <v>45190</v>
       </c>
       <c r="B169" s="1">
-        <v>313.4826049804688</v>
+        <v>313.4826354980469</v>
       </c>
       <c r="C169" s="1">
-        <v>132.6202721129099</v>
+        <v>132.6203021455941</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -11449,10 +11450,10 @@
         <v>45191</v>
       </c>
       <c r="B170" s="1">
-        <v>311.0103759765625</v>
+        <v>311.0102844238281</v>
       </c>
       <c r="C170" s="1">
-        <v>131.5743841497041</v>
+        <v>131.5743624049384</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -11463,7 +11464,7 @@
         <v>311.5303039550781</v>
       </c>
       <c r="C171" s="1">
-        <v>131.7943420959964</v>
+        <v>131.7943591114431</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -11474,7 +11475,7 @@
         <v>306.2325134277344</v>
       </c>
       <c r="C172" s="1">
-        <v>129.5530872060248</v>
+        <v>129.5531039321119</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -11485,7 +11486,7 @@
         <v>306.8702087402344</v>
       </c>
       <c r="C173" s="1">
-        <v>129.8228671699693</v>
+        <v>129.8228839308867</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -11496,7 +11497,7 @@
         <v>307.7041320800781</v>
       </c>
       <c r="C174" s="1">
-        <v>130.1756623123291</v>
+        <v>130.1756791187944</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -11507,7 +11508,7 @@
         <v>309.774169921875</v>
       </c>
       <c r="C175" s="1">
-        <v>131.0514014362917</v>
+        <v>131.0514183558203</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -11515,10 +11516,10 @@
         <v>45201</v>
       </c>
       <c r="B176" s="1">
-        <v>315.7096252441406</v>
+        <v>315.7096557617188</v>
       </c>
       <c r="C176" s="1">
-        <v>133.5624233796047</v>
+        <v>133.5624535339263</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -11526,10 +11527,10 @@
         <v>45202</v>
       </c>
       <c r="B177" s="1">
-        <v>307.4588623046875</v>
+        <v>307.4588928222656</v>
       </c>
       <c r="C177" s="1">
-        <v>130.0718997946117</v>
+        <v>130.0719294982855</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -11540,7 +11541,7 @@
         <v>312.9234313964844</v>
       </c>
       <c r="C178" s="1">
-        <v>132.3837111309346</v>
+        <v>132.3837282224724</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -11548,10 +11549,10 @@
         <v>45204</v>
       </c>
       <c r="B179" s="1">
-        <v>313.3157653808594</v>
+        <v>313.3158264160156</v>
       </c>
       <c r="C179" s="1">
-        <v>132.5496898453523</v>
+        <v>132.5497327795287</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -11562,7 +11563,7 @@
         <v>321.0663757324219</v>
       </c>
       <c r="C180" s="1">
-        <v>135.8286215549105</v>
+        <v>135.828639091207</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -11573,7 +11574,7 @@
         <v>323.5778503417969</v>
       </c>
       <c r="C181" s="1">
-        <v>136.8911125537993</v>
+        <v>136.8911302272699</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -11584,7 +11585,7 @@
         <v>322.1749267578125</v>
       </c>
       <c r="C182" s="1">
-        <v>136.2975992152419</v>
+        <v>136.2976168120863</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -11595,7 +11596,7 @@
         <v>326.1286926269531</v>
       </c>
       <c r="C183" s="1">
-        <v>137.9702582307839</v>
+        <v>137.9702760435787</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -11606,7 +11607,7 @@
         <v>324.8925170898438</v>
       </c>
       <c r="C184" s="1">
-        <v>137.4472884279746</v>
+        <v>137.4473061732509</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -11614,10 +11615,10 @@
         <v>45212</v>
       </c>
       <c r="B185" s="1">
-        <v>321.5274658203125</v>
+        <v>321.5274353027344</v>
       </c>
       <c r="C185" s="1">
-        <v>136.0236878582813</v>
+        <v>136.0236925091573</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -11625,10 +11626,10 @@
         <v>45215</v>
       </c>
       <c r="B186" s="1">
-        <v>326.3445739746094</v>
+        <v>326.344482421875</v>
       </c>
       <c r="C186" s="1">
-        <v>138.0615878376437</v>
+        <v>138.0615669304153</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -11639,7 +11640,7 @@
         <v>325.7754821777344</v>
       </c>
       <c r="C187" s="1">
-        <v>137.8208309096366</v>
+        <v>137.8208487031394</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -11647,10 +11648,10 @@
         <v>45217</v>
       </c>
       <c r="B188" s="1">
-        <v>323.8623657226562</v>
+        <v>323.8623962402344</v>
       </c>
       <c r="C188" s="1">
-        <v>137.0114781071997</v>
+        <v>137.0115087068151</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -11658,10 +11659,10 @@
         <v>45218</v>
       </c>
       <c r="B189" s="1">
-        <v>325.0494384765625</v>
+        <v>325.0494995117188</v>
       </c>
       <c r="C189" s="1">
-        <v>137.5136747495004</v>
+        <v>137.5137183245572</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -11669,10 +11670,10 @@
         <v>45219</v>
       </c>
       <c r="B190" s="1">
-        <v>320.487548828125</v>
+        <v>320.4874877929688</v>
       </c>
       <c r="C190" s="1">
-        <v>135.5837461444904</v>
+        <v>135.5837378279624</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -11680,10 +11681,10 @@
         <v>45222</v>
       </c>
       <c r="B191" s="1">
-        <v>323.0873718261719</v>
+        <v>323.0872802734375</v>
       </c>
       <c r="C191" s="1">
-        <v>136.6836133395709</v>
+        <v>136.6835922544376</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -11694,7 +11695,7 @@
         <v>324.2744140625</v>
       </c>
       <c r="C192" s="1">
-        <v>137.1857970712684</v>
+        <v>137.1858147827845</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -11702,10 +11703,10 @@
         <v>45224</v>
       </c>
       <c r="B193" s="1">
-        <v>334.2225341796875</v>
+        <v>334.2225646972656</v>
       </c>
       <c r="C193" s="1">
-        <v>141.3943954942511</v>
+        <v>141.3944266597277</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -11716,7 +11717,7 @@
         <v>321.6844177246094</v>
       </c>
       <c r="C194" s="1">
-        <v>136.0900870904103</v>
+        <v>136.0901046604637</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -11727,7 +11728,7 @@
         <v>323.5680847167969</v>
       </c>
       <c r="C195" s="1">
-        <v>136.8869811607833</v>
+        <v>136.8869988337205</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -11735,10 +11736,10 @@
         <v>45229</v>
       </c>
       <c r="B196" s="1">
-        <v>330.9261169433594</v>
+        <v>330.9260864257812</v>
       </c>
       <c r="C196" s="1">
-        <v>139.9998308710984</v>
+        <v>139.9998360353185</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -11746,10 +11747,10 @@
         <v>45230</v>
       </c>
       <c r="B197" s="1">
-        <v>331.7109375</v>
+        <v>331.7109680175781</v>
       </c>
       <c r="C197" s="1">
-        <v>140.3318528529496</v>
+        <v>140.3318838812454</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -11757,10 +11758,10 @@
         <v>45231</v>
       </c>
       <c r="B198" s="1">
-        <v>339.5204162597656</v>
+        <v>339.5203552246094</v>
       </c>
       <c r="C198" s="1">
-        <v>143.6356891160323</v>
+        <v>143.6356818390589</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -11768,10 +11769,10 @@
         <v>45232</v>
       </c>
       <c r="B199" s="1">
-        <v>341.7277221679688</v>
+        <v>341.7276916503906</v>
       </c>
       <c r="C199" s="1">
-        <v>144.569500133076</v>
+        <v>144.5695058872681</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -11782,7 +11783,7 @@
         <v>346.1229248046875</v>
       </c>
       <c r="C200" s="1">
-        <v>146.4289110235442</v>
+        <v>146.4289299284023</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -11790,10 +11791,10 @@
         <v>45236</v>
       </c>
       <c r="B201" s="1">
-        <v>349.7823486328125</v>
+        <v>349.7823181152344</v>
       </c>
       <c r="C201" s="1">
-        <v>147.9770472714634</v>
+        <v>147.9770534655904</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -11804,7 +11805,7 @@
         <v>353.7066345214844</v>
       </c>
       <c r="C202" s="1">
-        <v>149.6372346443384</v>
+        <v>149.6372539634104</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -11812,10 +11813,10 @@
         <v>45238</v>
       </c>
       <c r="B203" s="1">
-        <v>356.3261413574219</v>
+        <v>356.326171875</v>
       </c>
       <c r="C203" s="1">
-        <v>150.7454291784667</v>
+        <v>150.7454615512182</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -11826,7 +11827,7 @@
         <v>353.8636779785156</v>
       </c>
       <c r="C204" s="1">
-        <v>149.7036726082769</v>
+        <v>149.7036919359265</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -11834,10 +11835,10 @@
         <v>45240</v>
       </c>
       <c r="B205" s="1">
-        <v>362.6737365722656</v>
+        <v>362.6737060546875</v>
       </c>
       <c r="C205" s="1">
-        <v>153.4308088176579</v>
+        <v>153.4308157158985</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -11845,10 +11846,10 @@
         <v>45243</v>
       </c>
       <c r="B206" s="1">
-        <v>359.7402954101562</v>
+        <v>359.740234375</v>
       </c>
       <c r="C206" s="1">
-        <v>152.1898029086685</v>
+        <v>152.1897967360829</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -11856,10 +11857,10 @@
         <v>45244</v>
       </c>
       <c r="B207" s="1">
-        <v>363.2622985839844</v>
+        <v>363.2623291015625</v>
       </c>
       <c r="C207" s="1">
-        <v>153.6798027104907</v>
+        <v>153.6798354620877</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -11867,10 +11868,10 @@
         <v>45245</v>
       </c>
       <c r="B208" s="1">
-        <v>363.4098510742188</v>
+        <v>363.4097595214844</v>
       </c>
       <c r="C208" s="1">
-        <v>153.7422254768418</v>
+        <v>153.7422065940785</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -11878,10 +11879,10 @@
         <v>45246</v>
       </c>
       <c r="B209" s="1">
-        <v>369.7997131347656</v>
+        <v>369.7996826171875</v>
       </c>
       <c r="C209" s="1">
-        <v>156.4454863014304</v>
+        <v>156.4454935888841</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -11889,10 +11890,10 @@
         <v>45247</v>
       </c>
       <c r="B210" s="1">
-        <v>363.5867309570312</v>
+        <v>363.5867004394531</v>
       </c>
       <c r="C210" s="1">
-        <v>153.8170553328441</v>
+        <v>153.8170622809514</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -11903,7 +11904,7 @@
         <v>371.0481872558594</v>
       </c>
       <c r="C211" s="1">
-        <v>156.9736590773192</v>
+        <v>156.9736793435681</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -11911,10 +11912,10 @@
         <v>45251</v>
       </c>
       <c r="B212" s="1">
-        <v>366.7522583007812</v>
+        <v>366.752197265625</v>
       </c>
       <c r="C212" s="1">
-        <v>155.1562463789793</v>
+        <v>155.1562405893795</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -11925,7 +11926,7 @@
         <v>371.4512634277344</v>
       </c>
       <c r="C213" s="1">
-        <v>157.1441823240545</v>
+        <v>157.1442026123189</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -11933,10 +11934,10 @@
         <v>45254</v>
       </c>
       <c r="B214" s="1">
-        <v>371.0383605957031</v>
+        <v>371.0383911132812</v>
       </c>
       <c r="C214" s="1">
-        <v>156.9695018630969</v>
+        <v>156.9695350394138</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -11944,10 +11945,10 @@
         <v>45257</v>
       </c>
       <c r="B215" s="1">
-        <v>372.1983947753906</v>
+        <v>372.1983642578125</v>
       </c>
       <c r="C215" s="1">
-        <v>157.4602597109845</v>
+        <v>157.4602671294516</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -11955,10 +11956,10 @@
         <v>45258</v>
       </c>
       <c r="B216" s="1">
-        <v>376.2191772460938</v>
+        <v>376.2191467285156</v>
       </c>
       <c r="C216" s="1">
-        <v>159.1612704110988</v>
+        <v>159.1612780491766</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -11966,10 +11967,10 @@
         <v>45259</v>
       </c>
       <c r="B217" s="1">
-        <v>372.4342956542969</v>
+        <v>372.434326171875</v>
       </c>
       <c r="C217" s="1">
-        <v>157.5600586735272</v>
+        <v>157.5600919260886</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -11977,10 +11978,10 @@
         <v>45260</v>
       </c>
       <c r="B218" s="1">
-        <v>372.4933471679688</v>
+        <v>372.4933166503906</v>
       </c>
       <c r="C218" s="1">
-        <v>157.5850406906708</v>
+        <v>157.5850481252479</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -11991,7 +11992,7 @@
         <v>368.1678466796875</v>
       </c>
       <c r="C219" s="1">
-        <v>155.7551176178543</v>
+        <v>155.755137726782</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -12002,7 +12003,7 @@
         <v>362.8887634277344</v>
       </c>
       <c r="C220" s="1">
-        <v>153.5217769276289</v>
+        <v>153.5217967482189</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -12013,7 +12014,7 @@
         <v>366.2114868164062</v>
       </c>
       <c r="C221" s="1">
-        <v>154.9274704907185</v>
+        <v>154.927490492792</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -12021,10 +12022,10 @@
         <v>45266</v>
       </c>
       <c r="B222" s="1">
-        <v>362.5544738769531</v>
+        <v>362.5545349121094</v>
       </c>
       <c r="C222" s="1">
-        <v>153.3803541804501</v>
+        <v>153.3803998039912</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -12032,10 +12033,10 @@
         <v>45267</v>
       </c>
       <c r="B223" s="1">
-        <v>364.6680908203125</v>
+        <v>364.6681213378906</v>
       </c>
       <c r="C223" s="1">
-        <v>154.2745296457466</v>
+        <v>154.2745624741264</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -12043,10 +12044,10 @@
         <v>45268</v>
       </c>
       <c r="B224" s="1">
-        <v>367.8925476074219</v>
+        <v>367.892578125</v>
       </c>
       <c r="C224" s="1">
-        <v>155.6386510666127</v>
+        <v>155.6386840711088</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -12057,7 +12058,7 @@
         <v>365.0121459960938</v>
       </c>
       <c r="C225" s="1">
-        <v>154.4200837859414</v>
+        <v>154.4201037225082</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -12068,7 +12069,7 @@
         <v>368.0400085449219</v>
       </c>
       <c r="C226" s="1">
-        <v>155.7010351011542</v>
+        <v>155.7010552030996</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -12079,7 +12080,7 @@
         <v>368.0301818847656</v>
       </c>
       <c r="C227" s="1">
-        <v>155.6968778869319</v>
+        <v>155.6968979883406</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -12087,10 +12088,10 @@
         <v>45274</v>
       </c>
       <c r="B228" s="1">
-        <v>359.7331237792969</v>
+        <v>359.7330932617188</v>
       </c>
       <c r="C228" s="1">
-        <v>152.1867689169224</v>
+        <v>152.1867756545499</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -12101,7 +12102,7 @@
         <v>364.4518432617188</v>
       </c>
       <c r="C229" s="1">
-        <v>154.1830451116487</v>
+        <v>154.1830650176123</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -12109,10 +12110,10 @@
         <v>45278</v>
       </c>
       <c r="B230" s="1">
-        <v>366.3393249511719</v>
+        <v>366.33935546875</v>
       </c>
       <c r="C230" s="1">
-        <v>154.9815530074185</v>
+        <v>154.9815859270792</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -12120,10 +12121,10 @@
         <v>45279</v>
       </c>
       <c r="B231" s="1">
-        <v>366.93896484375</v>
+        <v>366.9390258789062</v>
       </c>
       <c r="C231" s="1">
-        <v>155.2352334492039</v>
+        <v>155.2352793122211</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -12131,10 +12132,10 @@
         <v>45280</v>
       </c>
       <c r="B232" s="1">
-        <v>364.3436889648438</v>
+        <v>364.3436584472656</v>
       </c>
       <c r="C232" s="1">
-        <v>154.1372899339965</v>
+        <v>154.1372969234481</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -12142,10 +12143,10 @@
         <v>45281</v>
       </c>
       <c r="B233" s="1">
-        <v>367.2142028808594</v>
+        <v>367.2142639160156</v>
       </c>
       <c r="C233" s="1">
-        <v>155.3516741792391</v>
+        <v>155.3517200572895</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -12153,10 +12154,10 @@
         <v>45282</v>
       </c>
       <c r="B234" s="1">
-        <v>368.2366027832031</v>
+        <v>368.2366333007812</v>
       </c>
       <c r="C234" s="1">
-        <v>155.7842052068075</v>
+        <v>155.7842382300955</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -12164,10 +12165,10 @@
         <v>45286</v>
       </c>
       <c r="B235" s="1">
-        <v>368.3153076171875</v>
+        <v>368.3152770996094</v>
       </c>
       <c r="C235" s="1">
-        <v>155.8175016523958</v>
+        <v>155.8175088587729</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -12178,7 +12179,7 @@
         <v>367.7352600097656</v>
       </c>
       <c r="C236" s="1">
-        <v>155.5721098178488</v>
+        <v>155.5721299031492</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -12186,10 +12187,10 @@
         <v>45288</v>
       </c>
       <c r="B237" s="1">
-        <v>368.9248046875</v>
+        <v>368.9248352050781</v>
       </c>
       <c r="C237" s="1">
-        <v>156.0753522190067</v>
+        <v>156.0753852798835</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -12197,10 +12198,10 @@
         <v>45289</v>
       </c>
       <c r="B238" s="1">
-        <v>369.6719360351562</v>
+        <v>369.671875</v>
       </c>
       <c r="C238" s="1">
-        <v>156.3914296059367</v>
+        <v>156.3914239758066</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -12211,7 +12212,7 @@
         <v>364.5894165039062</v>
       </c>
       <c r="C239" s="1">
-        <v>154.2412461107615</v>
+        <v>154.2412660242393</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -12222,7 +12223,7 @@
         <v>364.3240356445312</v>
       </c>
       <c r="C240" s="1">
-        <v>154.1289755055518</v>
+        <v>154.1289954045347</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -12230,10 +12231,10 @@
         <v>45295</v>
       </c>
       <c r="B241" s="1">
-        <v>361.7091369628906</v>
+        <v>361.7090759277344</v>
       </c>
       <c r="C241" s="1">
-        <v>153.0227304725029</v>
+        <v>153.0227244074533</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -12244,7 +12245,7 @@
         <v>361.5222778320312</v>
       </c>
       <c r="C242" s="1">
-        <v>152.9436788492625</v>
+        <v>152.9436985952165</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -12252,10 +12253,10 @@
         <v>45299</v>
       </c>
       <c r="B243" s="1">
-        <v>368.3447570800781</v>
+        <v>368.3447875976562</v>
       </c>
       <c r="C243" s="1">
-        <v>155.8299603844597</v>
+        <v>155.8299934136549</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -12263,10 +12264,10 @@
         <v>45300</v>
       </c>
       <c r="B244" s="1">
-        <v>369.4261474609375</v>
+        <v>369.4261779785156</v>
       </c>
       <c r="C244" s="1">
-        <v>156.2874476079654</v>
+        <v>156.287480696225</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -12274,10 +12275,10 @@
         <v>45301</v>
       </c>
       <c r="B245" s="1">
-        <v>376.2878723144531</v>
+        <v>376.2879028320312</v>
       </c>
       <c r="C245" s="1">
-        <v>159.1903321788457</v>
+        <v>159.1903656418853</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -12285,10 +12286,10 @@
         <v>45302</v>
       </c>
       <c r="B246" s="1">
-        <v>378.1164855957031</v>
+        <v>378.1164245605469</v>
       </c>
       <c r="C246" s="1">
-        <v>159.963935521091</v>
+        <v>159.9639303521929</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -12296,10 +12297,10 @@
         <v>45303</v>
       </c>
       <c r="B247" s="1">
-        <v>381.8914184570312</v>
+        <v>381.8914489746094</v>
       </c>
       <c r="C247" s="1">
-        <v>161.5609384020275</v>
+        <v>161.5609721711267</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -12307,10 +12308,10 @@
         <v>45307</v>
       </c>
       <c r="B248" s="1">
-        <v>383.660888671875</v>
+        <v>383.6609191894531</v>
       </c>
       <c r="C248" s="1">
-        <v>162.3095209953197</v>
+        <v>162.3095548610654</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -12318,10 +12319,10 @@
         <v>45308</v>
       </c>
       <c r="B249" s="1">
-        <v>382.8744812011719</v>
+        <v>382.87451171875</v>
       </c>
       <c r="C249" s="1">
-        <v>161.9768276621034</v>
+        <v>161.9768614848964</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -12332,7 +12333,7 @@
         <v>387.199951171875</v>
       </c>
       <c r="C250" s="1">
-        <v>163.8067378243168</v>
+        <v>163.8067589727574</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -12343,7 +12344,7 @@
         <v>391.9186706542969</v>
       </c>
       <c r="C251" s="1">
-        <v>165.803014019043</v>
+        <v>165.803035425215</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -12354,7 +12355,7 @@
         <v>389.7952575683594</v>
       </c>
       <c r="C252" s="1">
-        <v>164.9046942501273</v>
+        <v>164.9047155403208</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -12362,10 +12363,10 @@
         <v>45314</v>
       </c>
       <c r="B253" s="1">
-        <v>392.1447448730469</v>
+        <v>392.144775390625</v>
       </c>
       <c r="C253" s="1">
-        <v>165.8986557673633</v>
+        <v>165.8986900964881</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -12376,7 +12377,7 @@
         <v>395.7427978515625</v>
       </c>
       <c r="C254" s="1">
-        <v>167.4208287922976</v>
+        <v>167.4208504073393</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -12387,7 +12388,7 @@
         <v>398.0137023925781</v>
       </c>
       <c r="C255" s="1">
-        <v>168.381545506358</v>
+        <v>168.381567245434</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -12398,7 +12399,7 @@
         <v>397.089599609375</v>
       </c>
       <c r="C256" s="1">
-        <v>167.9905995316162</v>
+        <v>167.9906212202187</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -12406,10 +12407,10 @@
         <v>45320</v>
       </c>
       <c r="B257" s="1">
-        <v>402.7815551757812</v>
+        <v>402.7815246582031</v>
       </c>
       <c r="C257" s="1">
-        <v>170.398607772196</v>
+        <v>170.3986168610821</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -12417,10 +12418,10 @@
         <v>45321</v>
       </c>
       <c r="B258" s="1">
-        <v>401.670654296875</v>
+        <v>401.6706848144531</v>
       </c>
       <c r="C258" s="1">
-        <v>169.9286359954201</v>
+        <v>169.9286708448396</v>
       </c>
     </row>
   </sheetData>
@@ -15307,7 +15308,7 @@
         <v>44949</v>
       </c>
       <c r="B2" s="1">
-        <v>98.97200775146484</v>
+        <v>98.97200012207031</v>
       </c>
       <c r="C2" s="1">
         <v>100</v>
@@ -15318,10 +15319,10 @@
         <v>44950</v>
       </c>
       <c r="B3" s="1">
-        <v>96.89911651611328</v>
+        <v>96.89912414550781</v>
       </c>
       <c r="C3" s="1">
-        <v>97.90557827162914</v>
+        <v>97.9055935274564</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -15332,7 +15333,7 @@
         <v>94.43946075439453</v>
       </c>
       <c r="C4" s="1">
-        <v>95.42037481097454</v>
+        <v>95.42038216658709</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -15340,10 +15341,10 @@
         <v>44952</v>
       </c>
       <c r="B5" s="1">
-        <v>96.72060394287109</v>
+        <v>96.72058868408203</v>
       </c>
       <c r="C5" s="1">
-        <v>97.72521154239146</v>
+        <v>97.72520365839689</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -15351,10 +15352,10 @@
         <v>44953</v>
       </c>
       <c r="B6" s="1">
-        <v>98.55544281005859</v>
+        <v>98.55545043945312</v>
       </c>
       <c r="C6" s="1">
-        <v>99.57910832479794</v>
+        <v>99.57912370963159</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -15365,7 +15366,7 @@
         <v>96.14536285400391</v>
       </c>
       <c r="C7" s="1">
-        <v>97.14399559867563</v>
+        <v>97.14400308715588</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -15373,10 +15374,10 @@
         <v>44957</v>
       </c>
       <c r="B8" s="1">
-        <v>98.02977752685547</v>
+        <v>98.02978515625</v>
       </c>
       <c r="C8" s="1">
-        <v>99.04798311561439</v>
+        <v>99.04799845950552</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -15387,7 +15388,7 @@
         <v>99.60674285888672</v>
       </c>
       <c r="C9" s="1">
-        <v>100.6413279086101</v>
+        <v>100.6413356666871</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -15398,7 +15399,7 @@
         <v>106.8568267822266</v>
       </c>
       <c r="C10" s="1">
-        <v>107.9667162563397</v>
+        <v>107.9667245791044</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -15409,7 +15410,7 @@
         <v>103.9210891723633</v>
       </c>
       <c r="C11" s="1">
-        <v>105.0004860296726</v>
+        <v>105.0004941237813</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -15420,7 +15421,7 @@
         <v>102.056510925293</v>
       </c>
       <c r="C12" s="1">
-        <v>103.1165409734577</v>
+        <v>103.1165489223399</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -15431,7 +15432,7 @@
         <v>106.7576522827148</v>
       </c>
       <c r="C13" s="1">
-        <v>107.8665116613589</v>
+        <v>107.8665199763992</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -15439,10 +15440,10 @@
         <v>44965</v>
       </c>
       <c r="B14" s="1">
-        <v>98.55544281005859</v>
+        <v>98.55545043945312</v>
       </c>
       <c r="C14" s="1">
-        <v>99.57910832479794</v>
+        <v>99.57912370963159</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -15450,10 +15451,10 @@
         <v>44966</v>
       </c>
       <c r="B15" s="1">
-        <v>94.23117065429688</v>
+        <v>94.23118591308594</v>
       </c>
       <c r="C15" s="1">
-        <v>95.20992126473477</v>
+        <v>95.20994402140288</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -15464,7 +15465,7 @@
         <v>93.79479217529297</v>
       </c>
       <c r="C16" s="1">
-        <v>94.76901025472503</v>
+        <v>94.76901756012623</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -15472,10 +15473,10 @@
         <v>44970</v>
       </c>
       <c r="B17" s="1">
-        <v>93.83445739746094</v>
+        <v>93.83446502685547</v>
       </c>
       <c r="C17" s="1">
-        <v>94.8090874675341</v>
+        <v>94.80910248466404</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -15483,10 +15484,10 @@
         <v>44971</v>
       </c>
       <c r="B18" s="1">
-        <v>93.90388488769531</v>
+        <v>93.90387725830078</v>
       </c>
       <c r="C18" s="1">
-        <v>94.87923608006778</v>
+        <v>94.87923568532656</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -15497,7 +15498,7 @@
         <v>96.14536285400391</v>
       </c>
       <c r="C19" s="1">
-        <v>97.14399559867563</v>
+        <v>97.14400308715588</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -15508,7 +15509,7 @@
         <v>94.72708129882812</v>
       </c>
       <c r="C20" s="1">
-        <v>95.71098278283246</v>
+        <v>95.71099016084693</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -15516,10 +15517,10 @@
         <v>44974</v>
       </c>
       <c r="B21" s="1">
-        <v>93.57658386230469</v>
+        <v>93.57659149169922</v>
       </c>
       <c r="C21" s="1">
-        <v>94.54853547812331</v>
+        <v>94.54855047516824</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -15527,10 +15528,10 @@
         <v>44978</v>
       </c>
       <c r="B22" s="1">
-        <v>91.03757476806641</v>
+        <v>91.03758239746094</v>
       </c>
       <c r="C22" s="1">
-        <v>91.98315446593433</v>
+        <v>91.98316926522328</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -15538,10 +15539,10 @@
         <v>44979</v>
       </c>
       <c r="B23" s="1">
-        <v>90.89871978759766</v>
+        <v>90.89872741699219</v>
       </c>
       <c r="C23" s="1">
-        <v>91.84285724086698</v>
+        <v>91.84287202934092</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -15549,10 +15550,10 @@
         <v>44980</v>
       </c>
       <c r="B24" s="1">
-        <v>90.14495849609375</v>
+        <v>90.14493560791016</v>
       </c>
       <c r="C24" s="1">
-        <v>91.08126685927471</v>
+        <v>91.08125075448308</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -15560,10 +15561,10 @@
         <v>44981</v>
       </c>
       <c r="B25" s="1">
-        <v>88.39939117431641</v>
+        <v>88.39937591552734</v>
       </c>
       <c r="C25" s="1">
-        <v>89.31756885876455</v>
+        <v>89.31756032665513</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -15574,7 +15575,7 @@
         <v>89.13332366943359</v>
       </c>
       <c r="C26" s="1">
-        <v>90.05912448827166</v>
+        <v>90.05913143060475</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -15585,7 +15586,7 @@
         <v>89.32176208496094</v>
       </c>
       <c r="C27" s="1">
-        <v>90.24952015651003</v>
+        <v>90.24952711352005</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -15593,10 +15594,10 @@
         <v>44986</v>
       </c>
       <c r="B28" s="1">
-        <v>89.61929321289062</v>
+        <v>89.61930084228516</v>
       </c>
       <c r="C28" s="1">
-        <v>90.55014165009116</v>
+        <v>90.55015633891433</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -15604,10 +15605,10 @@
         <v>44987</v>
       </c>
       <c r="B29" s="1">
-        <v>91.245849609375</v>
+        <v>91.24586486816406</v>
       </c>
       <c r="C29" s="1">
-        <v>92.19359259489663</v>
+        <v>92.19361511904684</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -15615,10 +15616,10 @@
         <v>44988</v>
       </c>
       <c r="B30" s="1">
-        <v>92.88233184814453</v>
+        <v>92.88232421875</v>
       </c>
       <c r="C30" s="1">
-        <v>93.84707247870277</v>
+        <v>93.84707200439577</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -15626,10 +15627,10 @@
         <v>44991</v>
       </c>
       <c r="B31" s="1">
-        <v>94.35018157958984</v>
+        <v>94.35019683837891</v>
       </c>
       <c r="C31" s="1">
-        <v>95.33016832043948</v>
+        <v>95.330191086377</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -15637,10 +15638,10 @@
         <v>44992</v>
       </c>
       <c r="B32" s="1">
-        <v>93.09061431884766</v>
+        <v>93.09060668945312</v>
       </c>
       <c r="C32" s="1">
-        <v>94.05751831630378</v>
+        <v>94.05751785821931</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -15648,10 +15649,10 @@
         <v>44993</v>
       </c>
       <c r="B33" s="1">
-        <v>93.47740936279297</v>
+        <v>93.4774169921875</v>
       </c>
       <c r="C33" s="1">
-        <v>94.4483308831425</v>
+        <v>94.44834587246302</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -15659,10 +15660,10 @@
         <v>44994</v>
       </c>
       <c r="B34" s="1">
-        <v>91.563232421875</v>
+        <v>91.56322479248047</v>
       </c>
       <c r="C34" s="1">
-        <v>92.51427196647913</v>
+        <v>92.51427138943137</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -15670,10 +15671,10 @@
         <v>44995</v>
       </c>
       <c r="B35" s="1">
-        <v>89.88707733154297</v>
+        <v>89.88706970214844</v>
       </c>
       <c r="C35" s="1">
-        <v>90.82070716122517</v>
+        <v>90.8207064536266</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -15681,10 +15682,10 @@
         <v>44998</v>
       </c>
       <c r="B36" s="1">
-        <v>90.36314392089844</v>
+        <v>90.36315155029297</v>
       </c>
       <c r="C36" s="1">
-        <v>91.30171850996021</v>
+        <v>91.30173325671974</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -15692,10 +15693,10 @@
         <v>44999</v>
       </c>
       <c r="B37" s="1">
-        <v>93.19970703125</v>
+        <v>93.19971466064453</v>
       </c>
       <c r="C37" s="1">
-        <v>94.16774414164655</v>
+        <v>94.16775910933765</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -15703,10 +15704,10 @@
         <v>45000</v>
       </c>
       <c r="B38" s="1">
-        <v>95.32215881347656</v>
+        <v>95.32216644287109</v>
       </c>
       <c r="C38" s="1">
-        <v>96.31224118727221</v>
+        <v>96.31225632027484</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -15714,10 +15715,10 @@
         <v>45001</v>
       </c>
       <c r="B39" s="1">
-        <v>99.49765014648438</v>
+        <v>99.49767303466797</v>
       </c>
       <c r="C39" s="1">
-        <v>100.5311020832673</v>
+        <v>100.5311329587654</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -15728,7 +15729,7 @@
         <v>100.7870025634766</v>
       </c>
       <c r="C40" s="1">
-        <v>101.8338466130438</v>
+        <v>101.8338544630478</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -15736,10 +15737,10 @@
         <v>45005</v>
       </c>
       <c r="B41" s="1">
-        <v>100.3902816772461</v>
+        <v>100.3902740478516</v>
       </c>
       <c r="C41" s="1">
-        <v>101.4330051072044</v>
+        <v>101.4330052176696</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -15747,10 +15748,10 @@
         <v>45006</v>
       </c>
       <c r="B42" s="1">
-        <v>104.0599517822266</v>
+        <v>104.059944152832</v>
       </c>
       <c r="C42" s="1">
-        <v>105.1407909633786</v>
+        <v>105.1407913596637</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -15761,7 +15762,7 @@
         <v>102.5226516723633</v>
       </c>
       <c r="C43" s="1">
-        <v>103.587523383192</v>
+        <v>103.5875313683806</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -15769,10 +15770,10 @@
         <v>45008</v>
       </c>
       <c r="B44" s="1">
-        <v>104.7343673706055</v>
+        <v>104.7343826293945</v>
       </c>
       <c r="C44" s="1">
-        <v>105.8222115020753</v>
+        <v>105.8222350768066</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -15783,7 +15784,7 @@
         <v>104.5756912231445</v>
       </c>
       <c r="C45" s="1">
-        <v>105.6618872335615</v>
+        <v>105.6618953786553</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -15791,10 +15792,10 @@
         <v>45012</v>
       </c>
       <c r="B46" s="1">
-        <v>101.6201171875</v>
+        <v>101.6201019287109</v>
       </c>
       <c r="C46" s="1">
-        <v>102.6756145461705</v>
+        <v>102.6756070437846</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -15802,10 +15803,10 @@
         <v>45013</v>
       </c>
       <c r="B47" s="1">
-        <v>100.2018432617188</v>
+        <v>100.2018280029297</v>
       </c>
       <c r="C47" s="1">
-        <v>101.242609438966</v>
+        <v>101.242601826115</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -15816,7 +15817,7 @@
         <v>100.5588760375977</v>
       </c>
       <c r="C48" s="1">
-        <v>101.6033506060802</v>
+        <v>101.603358438316</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -15824,10 +15825,10 @@
         <v>45015</v>
       </c>
       <c r="B49" s="1">
-        <v>100.06298828125</v>
+        <v>100.0629806518555</v>
       </c>
       <c r="C49" s="1">
-        <v>101.1023122138987</v>
+        <v>101.102312298872</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -15835,10 +15836,10 @@
         <v>45016</v>
       </c>
       <c r="B50" s="1">
-        <v>102.8796920776367</v>
+        <v>102.8796997070312</v>
       </c>
       <c r="C50" s="1">
-        <v>103.9482722589449</v>
+        <v>103.9482879805816</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -15846,10 +15847,10 @@
         <v>45019</v>
       </c>
       <c r="B51" s="1">
-        <v>103.5045394897461</v>
+        <v>103.5045318603516</v>
       </c>
       <c r="C51" s="1">
-        <v>104.579609771748</v>
+        <v>104.5796101247736</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -15857,10 +15858,10 @@
         <v>45020</v>
       </c>
       <c r="B52" s="1">
-        <v>103.8615875244141</v>
+        <v>103.8615798950195</v>
       </c>
       <c r="C52" s="1">
-        <v>104.9403663561396</v>
+        <v>104.9403667369746</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -15871,7 +15872,7 @@
         <v>103.6136322021484</v>
       </c>
       <c r="C53" s="1">
-        <v>104.6898355970907</v>
+        <v>104.6898436672526</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -15882,7 +15883,7 @@
         <v>107.53125</v>
       </c>
       <c r="C54" s="1">
-        <v>108.6481445036751</v>
+        <v>108.6481528789686</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -15893,7 +15894,7 @@
         <v>105.5674896240234</v>
       </c>
       <c r="C55" s="1">
-        <v>106.6639871438406</v>
+        <v>106.6639953661827</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -15901,10 +15902,10 @@
         <v>45027</v>
       </c>
       <c r="B56" s="1">
-        <v>104.4864120483398</v>
+        <v>104.4864196777344</v>
       </c>
       <c r="C56" s="1">
-        <v>105.5716807430264</v>
+        <v>105.5716965898059</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -15912,10 +15913,10 @@
         <v>45028</v>
       </c>
       <c r="B57" s="1">
-        <v>103.7822341918945</v>
+        <v>103.7822418212891</v>
       </c>
       <c r="C57" s="1">
-        <v>104.8601888046052</v>
+        <v>104.8602045965383</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -15923,10 +15924,10 @@
         <v>45029</v>
       </c>
       <c r="B58" s="1">
-        <v>106.5493698120117</v>
+        <v>106.5493774414062</v>
       </c>
       <c r="C58" s="1">
-        <v>107.6560658237579</v>
+        <v>107.656081831215</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -15937,7 +15938,7 @@
         <v>107.9775695800781</v>
       </c>
       <c r="C59" s="1">
-        <v>109.099099869963</v>
+        <v>109.0991082800191</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -15945,10 +15946,10 @@
         <v>45033</v>
       </c>
       <c r="B60" s="1">
-        <v>105.1013488769531</v>
+        <v>105.1013412475586</v>
       </c>
       <c r="C60" s="1">
-        <v>106.1930047341063</v>
+        <v>106.1930052115027</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -15959,7 +15960,7 @@
         <v>103.6433868408203</v>
       </c>
       <c r="C61" s="1">
-        <v>104.7198992881766</v>
+        <v>104.7199073606559</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -15967,10 +15968,10 @@
         <v>45035</v>
       </c>
       <c r="B62" s="1">
-        <v>103.3260192871094</v>
+        <v>103.3260116577148</v>
       </c>
       <c r="C62" s="1">
-        <v>104.3992353338715</v>
+        <v>104.3992356729927</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -15978,10 +15979,10 @@
         <v>45036</v>
       </c>
       <c r="B63" s="1">
-        <v>104.4269180297852</v>
+        <v>104.4269104003906</v>
       </c>
       <c r="C63" s="1">
-        <v>105.5115687781322</v>
+        <v>105.5115692029992</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -15989,10 +15990,10 @@
         <v>45037</v>
       </c>
       <c r="B64" s="1">
-        <v>104.5459365844727</v>
+        <v>104.5459289550781</v>
       </c>
       <c r="C64" s="1">
-        <v>105.6318235424756</v>
+        <v>105.6318239766126</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -16000,10 +16001,10 @@
         <v>45040</v>
       </c>
       <c r="B65" s="1">
-        <v>105.1013488769531</v>
+        <v>105.1013412475586</v>
       </c>
       <c r="C65" s="1">
-        <v>106.1930047341063</v>
+        <v>106.1930052115027</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -16014,7 +16015,7 @@
         <v>102.9987106323242</v>
       </c>
       <c r="C66" s="1">
-        <v>104.0685270232883</v>
+        <v>104.0685350455557</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -16022,10 +16023,10 @@
         <v>45042</v>
       </c>
       <c r="B67" s="1">
-        <v>102.8598556518555</v>
+        <v>102.8598480224609</v>
       </c>
       <c r="C67" s="1">
-        <v>103.928229798221</v>
+        <v>103.928230101034</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -16033,10 +16034,10 @@
         <v>45043</v>
       </c>
       <c r="B68" s="1">
-        <v>106.7080612182617</v>
+        <v>106.7080459594727</v>
       </c>
       <c r="C68" s="1">
-        <v>107.8164055095491</v>
+        <v>107.8163984034483</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -16044,10 +16045,10 @@
         <v>45044</v>
       </c>
       <c r="B69" s="1">
-        <v>106.4600982666016</v>
+        <v>106.4601058959961</v>
       </c>
       <c r="C69" s="1">
-        <v>107.5658670418615</v>
+        <v>107.5658830423656</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -16055,10 +16056,10 @@
         <v>45047</v>
       </c>
       <c r="B70" s="1">
-        <v>106.3212432861328</v>
+        <v>106.3212509155273</v>
       </c>
       <c r="C70" s="1">
-        <v>107.4255698167942</v>
+        <v>107.4255858064832</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -16066,10 +16067,10 @@
         <v>45048</v>
       </c>
       <c r="B71" s="1">
-        <v>104.4566650390625</v>
+        <v>104.456672668457</v>
       </c>
       <c r="C71" s="1">
-        <v>105.5416247605793</v>
+        <v>105.5416406050418</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -16077,10 +16078,10 @@
         <v>45049</v>
       </c>
       <c r="B72" s="1">
-        <v>104.5459365844727</v>
+        <v>104.5459289550781</v>
       </c>
       <c r="C72" s="1">
-        <v>105.6318235424756</v>
+        <v>105.6318239766126</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -16088,10 +16089,10 @@
         <v>45050</v>
       </c>
       <c r="B73" s="1">
-        <v>103.8318328857422</v>
+        <v>103.8318405151367</v>
       </c>
       <c r="C73" s="1">
-        <v>104.9103026650537</v>
+        <v>104.9103184608499</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -16099,10 +16100,10 @@
         <v>45051</v>
       </c>
       <c r="B74" s="1">
-        <v>104.7046203613281</v>
+        <v>104.7046127319336</v>
       </c>
       <c r="C74" s="1">
-        <v>105.7921555196282</v>
+        <v>105.7921559661245</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -16113,7 +16114,7 @@
         <v>106.8865814208984</v>
       </c>
       <c r="C75" s="1">
-        <v>107.9967799474255</v>
+        <v>107.9967882725078</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -16124,7 +16125,7 @@
         <v>106.4700317382812</v>
       </c>
       <c r="C76" s="1">
-        <v>107.575903689501</v>
+        <v>107.5759119821394</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -16132,10 +16133,10 @@
         <v>45056</v>
       </c>
       <c r="B77" s="1">
-        <v>110.8339614868164</v>
+        <v>110.8339538574219</v>
       </c>
       <c r="C77" s="1">
-        <v>111.9851602537345</v>
+        <v>111.9851611776272</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -16143,10 +16144,10 @@
         <v>45057</v>
       </c>
       <c r="B78" s="1">
-        <v>115.6144409179688</v>
+        <v>115.6144561767578</v>
       </c>
       <c r="C78" s="1">
-        <v>116.8152930758926</v>
+        <v>116.8153174980409</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -16154,10 +16155,10 @@
         <v>45058</v>
       </c>
       <c r="B79" s="1">
-        <v>116.5467529296875</v>
+        <v>116.5467376708984</v>
       </c>
       <c r="C79" s="1">
-        <v>117.7572887299162</v>
+        <v>117.7572823901222</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -16168,7 +16169,7 @@
         <v>115.5549392700195</v>
       </c>
       <c r="C80" s="1">
-        <v>116.7551734023596</v>
+        <v>116.7551824025948</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -16176,10 +16177,10 @@
         <v>45062</v>
       </c>
       <c r="B81" s="1">
-        <v>118.5303573608398</v>
+        <v>118.5303497314453</v>
       </c>
       <c r="C81" s="1">
-        <v>119.7614962591133</v>
+        <v>119.7614977824557</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -16187,10 +16188,10 @@
         <v>45063</v>
       </c>
       <c r="B82" s="1">
-        <v>119.8494491577148</v>
+        <v>119.8494338989258</v>
       </c>
       <c r="C82" s="1">
-        <v>121.0942890626982</v>
+        <v>121.0942829801415</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -16198,10 +16199,10 @@
         <v>45064</v>
       </c>
       <c r="B83" s="1">
-        <v>121.8231353759766</v>
+        <v>121.823127746582</v>
       </c>
       <c r="C83" s="1">
-        <v>123.0884753615332</v>
+        <v>123.0884771413405</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -16209,10 +16210,10 @@
         <v>45065</v>
       </c>
       <c r="B84" s="1">
-        <v>121.7537078857422</v>
+        <v>121.7537155151367</v>
       </c>
       <c r="C84" s="1">
-        <v>123.0183267489996</v>
+        <v>123.018343940678</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -16223,7 +16224,7 @@
         <v>124.0249404907227</v>
       </c>
       <c r="C85" s="1">
-        <v>125.3131499586932</v>
+        <v>125.313159618632</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -16231,10 +16232,10 @@
         <v>45069</v>
       </c>
       <c r="B86" s="1">
-        <v>121.5553436279297</v>
+        <v>121.5553359985352</v>
       </c>
       <c r="C86" s="1">
-        <v>122.8179021417605</v>
+        <v>122.8179039007103</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -16242,10 +16243,10 @@
         <v>45070</v>
       </c>
       <c r="B87" s="1">
-        <v>119.9089508056641</v>
+        <v>119.9089584350586</v>
       </c>
       <c r="C87" s="1">
-        <v>121.1544087362311</v>
+        <v>121.1544257842269</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -16256,7 +16257,7 @@
         <v>122.4678115844727</v>
       </c>
       <c r="C88" s="1">
-        <v>123.7398476264215</v>
+        <v>123.7398571650801</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -16267,7 +16268,7 @@
         <v>123.5885467529297</v>
       </c>
       <c r="C89" s="1">
-        <v>124.872223531406</v>
+        <v>124.8722331573554</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -16275,10 +16276,10 @@
         <v>45076</v>
       </c>
       <c r="B90" s="1">
-        <v>122.6562576293945</v>
+        <v>122.65625</v>
       </c>
       <c r="C90" s="1">
-        <v>123.9302510032986</v>
+        <v>123.9302528479953</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -16289,7 +16290,7 @@
         <v>121.8628158569336</v>
       </c>
       <c r="C91" s="1">
-        <v>123.1285679916198</v>
+        <v>123.128577483157</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -16297,10 +16298,10 @@
         <v>45078</v>
       </c>
       <c r="B92" s="1">
-        <v>122.7058334350586</v>
+        <v>122.7058410644531</v>
       </c>
       <c r="C92" s="1">
-        <v>123.9803417378309</v>
+        <v>123.9803590036676</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -16308,10 +16309,10 @@
         <v>45079</v>
       </c>
       <c r="B93" s="1">
-        <v>123.6480407714844</v>
+        <v>123.6480560302734</v>
       </c>
       <c r="C93" s="1">
-        <v>124.9323354963003</v>
+        <v>124.9323605441621</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -16319,10 +16320,10 @@
         <v>45082</v>
       </c>
       <c r="B94" s="1">
-        <v>124.9770660400391</v>
+        <v>124.9770736694336</v>
       </c>
       <c r="C94" s="1">
-        <v>126.2751649475246</v>
+        <v>126.275182390261</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -16333,7 +16334,7 @@
         <v>126.2664108276367</v>
       </c>
       <c r="C95" s="1">
-        <v>127.5779017686624</v>
+        <v>127.5779116031827</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -16341,10 +16342,10 @@
         <v>45084</v>
       </c>
       <c r="B96" s="1">
-        <v>121.4958419799805</v>
+        <v>121.4958343505859</v>
       </c>
       <c r="C96" s="1">
-        <v>122.7577824682275</v>
+        <v>122.7577842225429</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -16352,10 +16353,10 @@
         <v>45085</v>
       </c>
       <c r="B97" s="1">
-        <v>121.138801574707</v>
+        <v>121.1387939453125</v>
       </c>
       <c r="C97" s="1">
-        <v>122.3970335924746</v>
+        <v>122.3970353189812</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -16363,10 +16364,10 @@
         <v>45086</v>
       </c>
       <c r="B98" s="1">
-        <v>121.2280578613281</v>
+        <v>121.2280502319336</v>
       </c>
       <c r="C98" s="1">
-        <v>122.4872169570935</v>
+        <v>122.4872186905519</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -16374,10 +16375,10 @@
         <v>45089</v>
       </c>
       <c r="B99" s="1">
-        <v>122.6264801025391</v>
+        <v>122.6264877319336</v>
       </c>
       <c r="C99" s="1">
-        <v>123.9001641862965</v>
+        <v>123.9001814459527</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -16388,7 +16389,7 @@
         <v>122.81494140625</v>
       </c>
       <c r="C100" s="1">
-        <v>124.0905829804511</v>
+        <v>124.0905925461466</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -16396,10 +16397,10 @@
         <v>45091</v>
       </c>
       <c r="B101" s="1">
-        <v>122.6562576293945</v>
+        <v>122.65625</v>
       </c>
       <c r="C101" s="1">
-        <v>123.9302510032986</v>
+        <v>123.9302528479953</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -16407,10 +16408,10 @@
         <v>45092</v>
       </c>
       <c r="B102" s="1">
-        <v>124.0646133422852</v>
+        <v>124.0646057128906</v>
       </c>
       <c r="C102" s="1">
-        <v>125.3532348801411</v>
+        <v>125.3532368345305</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -16421,7 +16422,7 @@
         <v>122.5174026489258</v>
       </c>
       <c r="C103" s="1">
-        <v>123.7899537782313</v>
+        <v>123.7899633207523</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -16429,10 +16430,10 @@
         <v>45097</v>
       </c>
       <c r="B104" s="1">
-        <v>122.0909194946289</v>
+        <v>122.0909271240234</v>
       </c>
       <c r="C104" s="1">
-        <v>123.3590408726673</v>
+        <v>123.3590580906101</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -16440,10 +16441,10 @@
         <v>45098</v>
       </c>
       <c r="B105" s="1">
-        <v>119.5618209838867</v>
+        <v>119.5618133544922</v>
       </c>
       <c r="C105" s="1">
-        <v>120.8036733822015</v>
+        <v>120.8036749858816</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -16451,10 +16452,10 @@
         <v>45099</v>
       </c>
       <c r="B106" s="1">
-        <v>122.1405181884766</v>
+        <v>122.1405029296875</v>
       </c>
       <c r="C106" s="1">
-        <v>123.4091547331158</v>
+        <v>123.4091488290037</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -16465,7 +16466,7 @@
         <v>121.3371429443359</v>
       </c>
       <c r="C107" s="1">
-        <v>122.5974350737975</v>
+        <v>122.5974445243916</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -16476,7 +16477,7 @@
         <v>117.3699417114258</v>
       </c>
       <c r="C108" s="1">
-        <v>118.5890277240421</v>
+        <v>118.5890368656426</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -16484,10 +16485,10 @@
         <v>45104</v>
       </c>
       <c r="B109" s="1">
-        <v>117.3600158691406</v>
+        <v>117.3600234985352</v>
       </c>
       <c r="C109" s="1">
-        <v>118.5789987850414</v>
+        <v>118.5790156345081</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -16495,10 +16496,10 @@
         <v>45105</v>
       </c>
       <c r="B110" s="1">
-        <v>119.1948623657227</v>
+        <v>119.1948547363281</v>
       </c>
       <c r="C110" s="1">
-        <v>120.4329032760867</v>
+        <v>120.4329048511855</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -16509,7 +16510,7 @@
         <v>118.1237106323242</v>
       </c>
       <c r="C111" s="1">
-        <v>119.3506258142731</v>
+        <v>119.3506350145824</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -16517,10 +16518,10 @@
         <v>45107</v>
       </c>
       <c r="B112" s="1">
-        <v>118.7187881469727</v>
+        <v>118.7187805175781</v>
       </c>
       <c r="C112" s="1">
-        <v>119.9518842187129</v>
+        <v>119.9518857567317</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -16528,10 +16529,10 @@
         <v>45110</v>
       </c>
       <c r="B113" s="1">
-        <v>118.9171447753906</v>
+        <v>118.9171600341797</v>
       </c>
       <c r="C113" s="1">
-        <v>120.1523011173132</v>
+        <v>120.1523257966994</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -16542,7 +16543,7 @@
         <v>120.7519760131836</v>
       </c>
       <c r="C114" s="1">
-        <v>122.006190191081</v>
+        <v>122.0061995960981</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -16550,10 +16551,10 @@
         <v>45113</v>
       </c>
       <c r="B115" s="1">
-        <v>119.1254348754883</v>
+        <v>119.1254272460938</v>
       </c>
       <c r="C115" s="1">
-        <v>120.362754663553</v>
+        <v>120.3627562332443</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -16564,7 +16565,7 @@
         <v>118.5005950927734</v>
       </c>
       <c r="C116" s="1">
-        <v>119.7314248593887</v>
+        <v>119.7314340890524</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -16572,10 +16573,10 @@
         <v>45117</v>
       </c>
       <c r="B117" s="1">
-        <v>115.4954223632812</v>
+        <v>115.4954376220703</v>
       </c>
       <c r="C117" s="1">
-        <v>116.6950383115491</v>
+        <v>116.6950627244274</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -16583,10 +16584,10 @@
         <v>45118</v>
       </c>
       <c r="B118" s="1">
-        <v>116.1797637939453</v>
+        <v>116.1797714233398</v>
       </c>
       <c r="C118" s="1">
-        <v>117.3864877892464</v>
+        <v>117.3865045467867</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -16594,10 +16595,10 @@
         <v>45119</v>
       </c>
       <c r="B119" s="1">
-        <v>117.9551010131836</v>
+        <v>117.9551086425781</v>
       </c>
       <c r="C119" s="1">
-        <v>119.1802648981199</v>
+        <v>119.180281793936</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -16608,7 +16609,7 @@
         <v>123.5191192626953</v>
       </c>
       <c r="C120" s="1">
-        <v>124.8020749188724</v>
+        <v>124.8020845394142</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -16619,7 +16620,7 @@
         <v>124.3918991088867</v>
       </c>
       <c r="C121" s="1">
-        <v>125.6839200648081</v>
+        <v>125.6839297533282</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -16627,10 +16628,10 @@
         <v>45124</v>
       </c>
       <c r="B122" s="1">
-        <v>123.6282119750977</v>
+        <v>123.6282196044922</v>
       </c>
       <c r="C122" s="1">
-        <v>124.9123007442151</v>
+        <v>124.9123180818932</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -16638,10 +16639,10 @@
         <v>45125</v>
       </c>
       <c r="B123" s="1">
-        <v>122.7455062866211</v>
+        <v>122.7454986572266</v>
       </c>
       <c r="C123" s="1">
-        <v>124.0204266592787</v>
+        <v>124.0204285109268</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -16649,10 +16650,10 @@
         <v>45126</v>
       </c>
       <c r="B124" s="1">
-        <v>121.0296783447266</v>
+        <v>121.0296936035156</v>
       </c>
       <c r="C124" s="1">
-        <v>122.2867769325769</v>
+        <v>122.2868017765022</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -16660,10 +16661,10 @@
         <v>45127</v>
       </c>
       <c r="B125" s="1">
-        <v>118.2228927612305</v>
+        <v>118.2228851318359</v>
       </c>
       <c r="C125" s="1">
-        <v>119.4508381178927</v>
+        <v>119.4508396172876</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -16671,10 +16672,10 @@
         <v>45128</v>
       </c>
       <c r="B126" s="1">
-        <v>119.0361633300781</v>
+        <v>119.0361709594727</v>
       </c>
       <c r="C126" s="1">
-        <v>120.2725558816567</v>
+        <v>120.2725728616736</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -16682,10 +16683,10 @@
         <v>45131</v>
       </c>
       <c r="B127" s="1">
-        <v>120.5337982177734</v>
+        <v>120.5337905883789</v>
       </c>
       <c r="C127" s="1">
-        <v>121.7857462490342</v>
+        <v>121.7857479284188</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -16693,10 +16694,10 @@
         <v>45132</v>
       </c>
       <c r="B128" s="1">
-        <v>121.2082061767578</v>
+        <v>121.2082290649414</v>
       </c>
       <c r="C128" s="1">
-        <v>122.4671590790921</v>
+        <v>122.4671916455617</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -16707,7 +16708,7 @@
         <v>128.2103424072266</v>
       </c>
       <c r="C129" s="1">
-        <v>129.5420243764116</v>
+        <v>129.5420343623391</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -16715,10 +16716,10 @@
         <v>45134</v>
       </c>
       <c r="B130" s="1">
-        <v>128.3392486572266</v>
+        <v>128.3392639160156</v>
       </c>
       <c r="C130" s="1">
-        <v>129.672269536562</v>
+        <v>129.6722949498083</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -16729,7 +16730,7 @@
         <v>131.4932098388672</v>
       </c>
       <c r="C131" s="1">
-        <v>132.8589899571084</v>
+        <v>132.8590001987287</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -16740,7 +16741,7 @@
         <v>131.6320648193359</v>
       </c>
       <c r="C132" s="1">
-        <v>132.9992871821757</v>
+        <v>132.9992974346111</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -16748,10 +16749,10 @@
         <v>45139</v>
       </c>
       <c r="B133" s="1">
-        <v>130.4716339111328</v>
+        <v>130.4716491699219</v>
       </c>
       <c r="C133" s="1">
-        <v>131.8268032298271</v>
+        <v>131.8268288091586</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -16759,10 +16760,10 @@
         <v>45140</v>
       </c>
       <c r="B134" s="1">
-        <v>127.3276443481445</v>
+        <v>127.32763671875</v>
       </c>
       <c r="C134" s="1">
-        <v>128.6501580001139</v>
+        <v>128.6501602086513</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -16770,10 +16771,10 @@
         <v>45141</v>
       </c>
       <c r="B135" s="1">
-        <v>127.3970565795898</v>
+        <v>127.3970718383789</v>
       </c>
       <c r="C135" s="1">
-        <v>128.7202911953702</v>
+        <v>128.7203165352318</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -16784,7 +16785,7 @@
         <v>127.0598449707031</v>
       </c>
       <c r="C136" s="1">
-        <v>128.3795770717024</v>
+        <v>128.379586968021</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -16795,7 +16796,7 @@
         <v>130.4518280029297</v>
       </c>
       <c r="C137" s="1">
-        <v>131.8067916036582</v>
+        <v>131.8068017641684</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -16806,7 +16807,7 @@
         <v>130.3228759765625</v>
       </c>
       <c r="C138" s="1">
-        <v>131.6765001916753</v>
+        <v>131.6765103421418</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -16814,10 +16815,10 @@
         <v>45147</v>
       </c>
       <c r="B139" s="1">
-        <v>128.5971374511719</v>
+        <v>128.59716796875</v>
       </c>
       <c r="C139" s="1">
-        <v>129.9328369432503</v>
+        <v>129.9328777938614</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -16825,10 +16826,10 @@
         <v>45148</v>
       </c>
       <c r="B140" s="1">
-        <v>128.6269073486328</v>
+        <v>128.6268920898438</v>
       </c>
       <c r="C140" s="1">
-        <v>129.9629160516137</v>
+        <v>129.9629106527074</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -16839,7 +16840,7 @@
         <v>128.4979553222656</v>
       </c>
       <c r="C141" s="1">
-        <v>129.8326246396308</v>
+        <v>129.8326346479596</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -16850,7 +16851,7 @@
         <v>130.2534637451172</v>
       </c>
       <c r="C142" s="1">
-        <v>131.6063669964191</v>
+        <v>131.6063771414793</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -16858,10 +16859,10 @@
         <v>45153</v>
       </c>
       <c r="B143" s="1">
-        <v>128.7161712646484</v>
+        <v>128.7161865234375</v>
       </c>
       <c r="C143" s="1">
-        <v>130.0531071248712</v>
+        <v>130.0531325674749</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -16872,7 +16873,7 @@
         <v>127.6450119018555</v>
       </c>
       <c r="C144" s="1">
-        <v>128.970821954419</v>
+        <v>128.9708318963145</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -16883,7 +16884,7 @@
         <v>128.8549957275391</v>
       </c>
       <c r="C145" s="1">
-        <v>130.1933735153836</v>
+        <v>130.1933835515212</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -16891,10 +16892,10 @@
         <v>45156</v>
       </c>
       <c r="B146" s="1">
-        <v>126.4151763916016</v>
+        <v>126.4151840209961</v>
       </c>
       <c r="C146" s="1">
-        <v>127.7282125154529</v>
+        <v>127.7282300701995</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -16902,10 +16903,10 @@
         <v>45159</v>
       </c>
       <c r="B147" s="1">
-        <v>127.3177108764648</v>
+        <v>127.3177185058594</v>
       </c>
       <c r="C147" s="1">
-        <v>128.6401213524745</v>
+        <v>128.6401389775168</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -16916,7 +16917,7 @@
         <v>128.0219116210938</v>
       </c>
       <c r="C148" s="1">
-        <v>129.3516364168119</v>
+        <v>129.3516463880631</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -16924,10 +16925,10 @@
         <v>45161</v>
       </c>
       <c r="B149" s="1">
-        <v>131.2849273681641</v>
+        <v>131.2849426269531</v>
       </c>
       <c r="C149" s="1">
-        <v>132.6485441195073</v>
+        <v>132.6485697621839</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -16935,10 +16936,10 @@
         <v>45162</v>
       </c>
       <c r="B150" s="1">
-        <v>128.7161712646484</v>
+        <v>128.7161865234375</v>
       </c>
       <c r="C150" s="1">
-        <v>130.0531071248712</v>
+        <v>130.0531325674749</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -16946,10 +16947,10 @@
         <v>45163</v>
       </c>
       <c r="B151" s="1">
-        <v>128.8153228759766</v>
+        <v>128.8153381347656</v>
       </c>
       <c r="C151" s="1">
-        <v>130.1532885939358</v>
+        <v>130.1533140442621</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -16957,10 +16958,10 @@
         <v>45166</v>
       </c>
       <c r="B152" s="1">
-        <v>129.9360809326172</v>
+        <v>129.9360656738281</v>
       </c>
       <c r="C152" s="1">
-        <v>131.2856876248366</v>
+        <v>131.2856823278981</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -16968,10 +16969,10 @@
         <v>45167</v>
       </c>
       <c r="B153" s="1">
-        <v>133.4669189453125</v>
+        <v>133.4669036865234</v>
       </c>
       <c r="C153" s="1">
-        <v>134.8531993818597</v>
+        <v>134.8531943599278</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -16982,7 +16983,7 @@
         <v>134.7661895751953</v>
       </c>
       <c r="C154" s="1">
-        <v>136.1659651419982</v>
+        <v>136.1659756385413</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -16993,7 +16994,7 @@
         <v>135.0537719726562</v>
       </c>
       <c r="C155" s="1">
-        <v>136.4565345706624</v>
+        <v>136.4565450896044</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -17004,7 +17005,7 @@
         <v>134.5479736328125</v>
       </c>
       <c r="C156" s="1">
-        <v>135.9454826567577</v>
+        <v>135.9454931363046</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -17012,10 +17013,10 @@
         <v>45174</v>
       </c>
       <c r="B157" s="1">
-        <v>134.6570434570312</v>
+        <v>134.6570739746094</v>
       </c>
       <c r="C157" s="1">
-        <v>136.0556853561842</v>
+        <v>136.0557266787836</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -17023,10 +17024,10 @@
         <v>45175</v>
       </c>
       <c r="B158" s="1">
-        <v>133.3578186035156</v>
+        <v>133.3578033447266</v>
       </c>
       <c r="C158" s="1">
-        <v>134.7429658478782</v>
+        <v>134.7429608174488</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -17037,7 +17038,7 @@
         <v>134.1512298583984</v>
       </c>
       <c r="C159" s="1">
-        <v>135.5446180250021</v>
+        <v>135.5446284736478</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -17048,7 +17049,7 @@
         <v>135.2620544433594</v>
       </c>
       <c r="C160" s="1">
-        <v>136.6669804082634</v>
+        <v>136.666990943428</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -17056,10 +17057,10 @@
         <v>45180</v>
       </c>
       <c r="B161" s="1">
-        <v>135.7976379394531</v>
+        <v>135.7976531982422</v>
       </c>
       <c r="C161" s="1">
-        <v>137.2081268478089</v>
+        <v>137.2081528419672</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -17067,10 +17068,10 @@
         <v>45181</v>
       </c>
       <c r="B162" s="1">
-        <v>134.2305755615234</v>
+        <v>134.2306213378906</v>
       </c>
       <c r="C162" s="1">
-        <v>135.6247878678977</v>
+        <v>135.6248445745594</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -17078,10 +17079,10 @@
         <v>45182</v>
       </c>
       <c r="B163" s="1">
-        <v>135.5893707275391</v>
+        <v>135.58935546875</v>
       </c>
       <c r="C163" s="1">
-        <v>136.9976964274854</v>
+        <v>136.997691570865</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -17092,7 +17093,7 @@
         <v>136.9679718017578</v>
       </c>
       <c r="C164" s="1">
-        <v>138.3906166132419</v>
+        <v>138.3906272812754</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -17100,10 +17101,10 @@
         <v>45184</v>
       </c>
       <c r="B165" s="1">
-        <v>136.273681640625</v>
+        <v>136.2737121582031</v>
       </c>
       <c r="C165" s="1">
-        <v>137.6891150706277</v>
+        <v>137.6891565191423</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -17114,7 +17115,7 @@
         <v>137.0770721435547</v>
       </c>
       <c r="C166" s="1">
-        <v>138.5008501472234</v>
+        <v>138.5008608237545</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -17125,7 +17126,7 @@
         <v>136.9084320068359</v>
       </c>
       <c r="C167" s="1">
-        <v>138.3304583965153</v>
+        <v>138.3304690599114</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -17133,10 +17134,10 @@
         <v>45189</v>
       </c>
       <c r="B168" s="1">
-        <v>132.6437225341797</v>
+        <v>132.6437072753906</v>
       </c>
       <c r="C168" s="1">
-        <v>134.021452679095</v>
+        <v>134.0214475930468</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -17144,10 +17145,10 @@
         <v>45190</v>
       </c>
       <c r="B169" s="1">
-        <v>129.3707580566406</v>
+        <v>129.3707275390625</v>
       </c>
       <c r="C169" s="1">
-        <v>130.7144929114827</v>
+        <v>130.7144721532342</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -17158,7 +17159,7 @@
         <v>129.1823120117188</v>
       </c>
       <c r="C170" s="1">
-        <v>130.5240895346056</v>
+        <v>130.5240995962369</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -17166,10 +17167,10 @@
         <v>45194</v>
       </c>
       <c r="B171" s="1">
-        <v>130.0352783203125</v>
+        <v>130.0352630615234</v>
       </c>
       <c r="C171" s="1">
-        <v>131.3859153457336</v>
+        <v>131.3859100565213</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -17177,10 +17178,10 @@
         <v>45195</v>
       </c>
       <c r="B172" s="1">
-        <v>127.5160980224609</v>
+        <v>127.5160751342773</v>
       </c>
       <c r="C172" s="1">
-        <v>128.8405690856298</v>
+        <v>128.8405558915666</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -17188,10 +17189,10 @@
         <v>45196</v>
       </c>
       <c r="B173" s="1">
-        <v>129.4699401855469</v>
+        <v>129.4699249267578</v>
       </c>
       <c r="C173" s="1">
-        <v>130.8147052151022</v>
+        <v>130.8146998818574</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -17202,7 +17203,7 @@
         <v>131.2254180908203</v>
       </c>
       <c r="C174" s="1">
-        <v>132.5884167373356</v>
+        <v>132.5884269580984</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -17213,7 +17214,7 @@
         <v>129.7872924804688</v>
       </c>
       <c r="C175" s="1">
-        <v>131.1353537521298</v>
+        <v>131.1353638608813</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -17221,10 +17222,10 @@
         <v>45201</v>
       </c>
       <c r="B176" s="1">
-        <v>133.0702056884766</v>
+        <v>133.0701751708984</v>
       </c>
       <c r="C176" s="1">
-        <v>134.452365584659</v>
+        <v>134.4523451145496</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -17232,10 +17233,10 @@
         <v>45202</v>
       </c>
       <c r="B177" s="1">
-        <v>131.3444519042969</v>
+        <v>131.3444366455078</v>
       </c>
       <c r="C177" s="1">
-        <v>132.7086869189565</v>
+        <v>132.7086817317119</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -17243,10 +17244,10 @@
         <v>45203</v>
       </c>
       <c r="B178" s="1">
-        <v>134.1314086914062</v>
+        <v>134.1313934326172</v>
       </c>
       <c r="C178" s="1">
-        <v>135.5245909815556</v>
+        <v>135.5245860113789</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -17257,7 +17258,7 @@
         <v>133.9627990722656</v>
       </c>
       <c r="C179" s="1">
-        <v>135.3542300654024</v>
+        <v>135.3542404993718</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -17265,10 +17266,10 @@
         <v>45205</v>
       </c>
       <c r="B180" s="1">
-        <v>136.4522247314453</v>
+        <v>136.4522399902344</v>
       </c>
       <c r="C180" s="1">
-        <v>137.8695126344203</v>
+        <v>137.8695386795625</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -17276,10 +17277,10 @@
         <v>45208</v>
       </c>
       <c r="B181" s="1">
-        <v>137.2853088378906</v>
+        <v>137.2853393554688</v>
       </c>
       <c r="C181" s="1">
-        <v>138.711249732992</v>
+        <v>138.7112912602993</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -17290,7 +17291,7 @@
         <v>136.9282989501953</v>
       </c>
       <c r="C182" s="1">
-        <v>138.3505316917941</v>
+        <v>138.3505423567376</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -17298,10 +17299,10 @@
         <v>45210</v>
       </c>
       <c r="B183" s="1">
-        <v>139.3979034423828</v>
+        <v>139.3978881835938</v>
       </c>
       <c r="C183" s="1">
-        <v>140.8457872173657</v>
+        <v>140.8457826573807</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -17312,7 +17313,7 @@
         <v>137.8308258056641</v>
       </c>
       <c r="C184" s="1">
-        <v>139.262432820177</v>
+        <v>139.2624435554156</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -17323,7 +17324,7 @@
         <v>136.2340240478516</v>
       </c>
       <c r="C185" s="1">
-        <v>137.6490455664574</v>
+        <v>137.6490561773258</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -17334,7 +17335,7 @@
         <v>137.9597625732422</v>
       </c>
       <c r="C186" s="1">
-        <v>139.3927088148824</v>
+        <v>139.3927195601636</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -17342,10 +17343,10 @@
         <v>45216</v>
       </c>
       <c r="B187" s="1">
-        <v>138.5746765136719</v>
+        <v>138.5746459960938</v>
       </c>
       <c r="C187" s="1">
-        <v>140.014009680046</v>
+        <v>140.0139896386637</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -17353,10 +17354,10 @@
         <v>45217</v>
       </c>
       <c r="B188" s="1">
-        <v>136.8291168212891</v>
+        <v>136.8291015625</v>
       </c>
       <c r="C188" s="1">
-        <v>138.2503193881746</v>
+        <v>138.2503146281144</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -17364,10 +17365,10 @@
         <v>45218</v>
       </c>
       <c r="B189" s="1">
-        <v>136.6208190917969</v>
+        <v>136.6208343505859</v>
       </c>
       <c r="C189" s="1">
-        <v>138.0398581332961</v>
+        <v>138.0398841915696</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -17375,10 +17376,10 @@
         <v>45219</v>
       </c>
       <c r="B190" s="1">
-        <v>134.4884796142578</v>
+        <v>134.4884490966797</v>
       </c>
       <c r="C190" s="1">
-        <v>135.8853706918634</v>
+        <v>135.8853503322192</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -17389,7 +17390,7 @@
         <v>135.3810577392578</v>
       </c>
       <c r="C191" s="1">
-        <v>136.7872197553293</v>
+        <v>136.7872302997628</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -17397,10 +17398,10 @@
         <v>45223</v>
       </c>
       <c r="B192" s="1">
-        <v>137.6721496582031</v>
+        <v>137.672119140625</v>
       </c>
       <c r="C192" s="1">
-        <v>139.1021085516632</v>
+        <v>139.1020884399857</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -17408,10 +17409,10 @@
         <v>45224</v>
       </c>
       <c r="B193" s="1">
-        <v>124.5803451538086</v>
+        <v>124.5803298950195</v>
       </c>
       <c r="C193" s="1">
-        <v>125.8743234416852</v>
+        <v>125.8743177276041</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -17419,10 +17420,10 @@
         <v>45225</v>
       </c>
       <c r="B194" s="1">
-        <v>121.2776412963867</v>
+        <v>121.2776260375977</v>
       </c>
       <c r="C194" s="1">
-        <v>122.5373154002645</v>
+        <v>122.5373094289455</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -17430,10 +17431,10 @@
         <v>45226</v>
       </c>
       <c r="B195" s="1">
-        <v>121.1685333251953</v>
+        <v>121.1685409545898</v>
       </c>
       <c r="C195" s="1">
-        <v>122.4270741576443</v>
+        <v>122.4270913037452</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -17444,7 +17445,7 @@
         <v>123.4397735595703</v>
       </c>
       <c r="C196" s="1">
-        <v>124.7219050759767</v>
+        <v>124.7219146903386</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -17455,7 +17456,7 @@
         <v>123.0628967285156</v>
       </c>
       <c r="C197" s="1">
-        <v>124.3411137395</v>
+        <v>124.341123324508</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -17466,7 +17467,7 @@
         <v>125.4134521484375</v>
       </c>
       <c r="C198" s="1">
-        <v>126.7160836661731</v>
+        <v>126.716093434259</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -17474,10 +17475,10 @@
         <v>45232</v>
       </c>
       <c r="B199" s="1">
-        <v>126.444938659668</v>
+        <v>126.4449310302734</v>
       </c>
       <c r="C199" s="1">
-        <v>127.7582839151775</v>
+        <v>127.7582860549635</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -17485,10 +17486,10 @@
         <v>45233</v>
       </c>
       <c r="B200" s="1">
-        <v>128.0417633056641</v>
+        <v>128.0417327880859</v>
       </c>
       <c r="C200" s="1">
-        <v>129.3716942948134</v>
+        <v>129.3716734330533</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -17499,7 +17500,7 @@
         <v>129.1823120117188</v>
       </c>
       <c r="C201" s="1">
-        <v>130.5240895346056</v>
+        <v>130.5240995962369</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -17507,10 +17508,10 @@
         <v>45237</v>
       </c>
       <c r="B202" s="1">
-        <v>129.8964233398438</v>
+        <v>129.8964080810547</v>
       </c>
       <c r="C202" s="1">
-        <v>131.2456181206663</v>
+        <v>131.2456128206389</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -17521,7 +17522,7 @@
         <v>130.7592926025391</v>
       </c>
       <c r="C203" s="1">
-        <v>132.1174497448788</v>
+        <v>132.1174599293365</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -17532,7 +17533,7 @@
         <v>129.1723937988281</v>
       </c>
       <c r="C204" s="1">
-        <v>130.5140683042436</v>
+        <v>130.5140783651024</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -17540,10 +17541,10 @@
         <v>45240</v>
       </c>
       <c r="B205" s="1">
-        <v>131.5031127929688</v>
+        <v>131.5031280517578</v>
       </c>
       <c r="C205" s="1">
-        <v>132.8689957701928</v>
+        <v>132.8690214298632</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -17554,7 +17555,7 @@
         <v>131.0072326660156</v>
       </c>
       <c r="C206" s="1">
-        <v>132.3679650866501</v>
+        <v>132.3679752904191</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -17562,10 +17563,10 @@
         <v>45244</v>
       </c>
       <c r="B207" s="1">
-        <v>132.5246887207031</v>
+        <v>132.5246734619141</v>
       </c>
       <c r="C207" s="1">
-        <v>133.9011824974741</v>
+        <v>133.9011774021546</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -17573,10 +17574,10 @@
         <v>45245</v>
       </c>
       <c r="B208" s="1">
-        <v>133.5164642333984</v>
+        <v>133.5165252685547</v>
       </c>
       <c r="C208" s="1">
-        <v>134.903259281837</v>
+        <v>134.9033313501574</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -17587,7 +17588,7 @@
         <v>135.8075561523438</v>
       </c>
       <c r="C209" s="1">
-        <v>137.2181480781708</v>
+        <v>137.218158655823</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -17598,7 +17599,7 @@
         <v>134.2008209228516</v>
       </c>
       <c r="C210" s="1">
-        <v>135.5947241768118</v>
+        <v>135.59473462932</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -17606,10 +17607,10 @@
         <v>45250</v>
       </c>
       <c r="B211" s="1">
-        <v>135.1331329345703</v>
+        <v>135.1331481933594</v>
       </c>
       <c r="C211" s="1">
-        <v>136.5367198308355</v>
+        <v>136.5367457732374</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -17617,10 +17618,10 @@
         <v>45251</v>
       </c>
       <c r="B212" s="1">
-        <v>135.8472290039062</v>
+        <v>135.8472442626953</v>
       </c>
       <c r="C212" s="1">
-        <v>137.2582329996187</v>
+        <v>137.2582589976395</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -17628,10 +17629,10 @@
         <v>45252</v>
       </c>
       <c r="B213" s="1">
-        <v>137.3547668457031</v>
+        <v>137.3547821044922</v>
       </c>
       <c r="C213" s="1">
-        <v>138.7814291800807</v>
+        <v>138.7814552955192</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -17639,10 +17640,10 @@
         <v>45254</v>
       </c>
       <c r="B214" s="1">
-        <v>135.5695190429688</v>
+        <v>135.5695343017578</v>
       </c>
       <c r="C214" s="1">
-        <v>136.9776385494839</v>
+        <v>136.9776645258747</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -17653,7 +17654,7 @@
         <v>135.2918090820312</v>
       </c>
       <c r="C215" s="1">
-        <v>136.6970440993492</v>
+        <v>136.6970546368314</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -17664,7 +17665,7 @@
         <v>136.0753326416016</v>
       </c>
       <c r="C216" s="1">
-        <v>137.4887058806661</v>
+        <v>137.4887164791746</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -17672,10 +17673,10 @@
         <v>45259</v>
       </c>
       <c r="B217" s="1">
-        <v>133.8834533691406</v>
+        <v>133.8834686279297</v>
       </c>
       <c r="C217" s="1">
-        <v>135.2740602225068</v>
+        <v>135.2740860675748</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -17686,7 +17687,7 @@
         <v>131.443603515625</v>
       </c>
       <c r="C218" s="1">
-        <v>132.8088683880211</v>
+        <v>132.8088786257778</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -17694,10 +17695,10 @@
         <v>45261</v>
       </c>
       <c r="B219" s="1">
-        <v>130.7791137695312</v>
+        <v>130.7790985107422</v>
       </c>
       <c r="C219" s="1">
-        <v>132.1374767883252</v>
+        <v>132.137471557048</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -17708,7 +17709,7 @@
         <v>128.2103424072266</v>
       </c>
       <c r="C220" s="1">
-        <v>129.5420243764116</v>
+        <v>129.5420343623391</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -17719,7 +17720,7 @@
         <v>129.9162445068359</v>
       </c>
       <c r="C221" s="1">
-        <v>131.2656451641127</v>
+        <v>131.2656552829078</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -17727,10 +17728,10 @@
         <v>45266</v>
       </c>
       <c r="B222" s="1">
-        <v>128.9542083740234</v>
+        <v>128.9542236328125</v>
       </c>
       <c r="C222" s="1">
-        <v>130.2936166535581</v>
+        <v>130.2936421147018</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -17741,7 +17742,7 @@
         <v>135.8075561523438</v>
       </c>
       <c r="C223" s="1">
-        <v>137.2181480781708</v>
+        <v>137.218158655823</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -17749,10 +17750,10 @@
         <v>45268</v>
       </c>
       <c r="B224" s="1">
-        <v>133.8834533691406</v>
+        <v>133.8834686279297</v>
       </c>
       <c r="C224" s="1">
-        <v>135.2740602225068</v>
+        <v>135.2740860675748</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -17760,10 +17761,10 @@
         <v>45271</v>
       </c>
       <c r="B225" s="1">
-        <v>132.1973724365234</v>
+        <v>132.1973876953125</v>
       </c>
       <c r="C225" s="1">
-        <v>133.5704664782521</v>
+        <v>133.5704921919963</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -17771,10 +17772,10 @@
         <v>45272</v>
       </c>
       <c r="B226" s="1">
-        <v>131.4337158203125</v>
+        <v>131.4337005615234</v>
       </c>
       <c r="C226" s="1">
-        <v>132.7988779922141</v>
+        <v>132.798872811922</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -17782,10 +17783,10 @@
         <v>45273</v>
       </c>
       <c r="B227" s="1">
-        <v>131.4833068847656</v>
+        <v>131.4832916259766</v>
       </c>
       <c r="C227" s="1">
-        <v>132.8489841440239</v>
+        <v>132.8489789675943</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -17796,7 +17797,7 @@
         <v>130.8584594726562</v>
       </c>
       <c r="C228" s="1">
-        <v>132.2176466312208</v>
+        <v>132.2176568234023</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -17804,10 +17805,10 @@
         <v>45275</v>
       </c>
       <c r="B229" s="1">
-        <v>131.5130462646484</v>
+        <v>131.5130310058594</v>
       </c>
       <c r="C229" s="1">
-        <v>132.8790324178323</v>
+        <v>132.879027243719</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -17815,10 +17816,10 @@
         <v>45278</v>
       </c>
       <c r="B230" s="1">
-        <v>134.6868286132812</v>
+        <v>134.6868133544922</v>
       </c>
       <c r="C230" s="1">
-        <v>136.085779881825</v>
+        <v>136.0857749549083</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -17829,7 +17830,7 @@
         <v>135.5298309326172</v>
       </c>
       <c r="C231" s="1">
-        <v>136.9375382107586</v>
+        <v>136.9375487667796</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -17840,7 +17841,7 @@
         <v>137.2059783935547</v>
       </c>
       <c r="C232" s="1">
-        <v>138.6310953073739</v>
+        <v>138.631105993945</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -17851,7 +17852,7 @@
         <v>139.2689514160156</v>
       </c>
       <c r="C233" s="1">
-        <v>140.7154958053828</v>
+        <v>140.7155066526328</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -17859,10 +17860,10 @@
         <v>45282</v>
       </c>
       <c r="B234" s="1">
-        <v>140.3301544189453</v>
+        <v>140.3301696777344</v>
       </c>
       <c r="C234" s="1">
-        <v>141.7877212022794</v>
+        <v>141.7877475494621</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -17873,7 +17874,7 @@
         <v>140.3599395751953</v>
       </c>
       <c r="C235" s="1">
-        <v>141.8178157279202</v>
+        <v>141.8178266601441</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -17884,7 +17885,7 @@
         <v>139.2193450927734</v>
       </c>
       <c r="C236" s="1">
-        <v>140.6653742362955</v>
+        <v>140.6653850796819</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -17892,10 +17893,10 @@
         <v>45288</v>
       </c>
       <c r="B237" s="1">
-        <v>139.0805206298828</v>
+        <v>139.0804901123047</v>
       </c>
       <c r="C237" s="1">
-        <v>140.5251078457831</v>
+        <v>140.5250878437995</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -17903,10 +17904,10 @@
         <v>45289</v>
       </c>
       <c r="B238" s="1">
-        <v>138.544921875</v>
+        <v>138.5449523925781</v>
       </c>
       <c r="C238" s="1">
-        <v>139.9839459889602</v>
+        <v>139.983987614375</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -17914,10 +17915,10 @@
         <v>45293</v>
       </c>
       <c r="B239" s="1">
-        <v>137.0373840332031</v>
+        <v>137.0373992919922</v>
       </c>
       <c r="C239" s="1">
-        <v>138.4607498084982</v>
+        <v>138.4607758992166</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -17925,10 +17926,10 @@
         <v>45294</v>
       </c>
       <c r="B240" s="1">
-        <v>137.7812347412109</v>
+        <v>137.78125</v>
       </c>
       <c r="C240" s="1">
-        <v>139.2123266683672</v>
+        <v>139.212352817022</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -17939,7 +17940,7 @@
         <v>135.27197265625</v>
       </c>
       <c r="C241" s="1">
-        <v>136.6770016386253</v>
+        <v>136.6770121745625</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -17950,7 +17951,7 @@
         <v>134.6174011230469</v>
       </c>
       <c r="C242" s="1">
-        <v>136.0156312692914</v>
+        <v>136.0156417542458</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -17958,10 +17959,10 @@
         <v>45299</v>
       </c>
       <c r="B243" s="1">
-        <v>137.7018890380859</v>
+        <v>137.701904296875</v>
       </c>
       <c r="C243" s="1">
-        <v>139.1321568254716</v>
+        <v>139.1321829679464</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -17969,10 +17970,10 @@
         <v>45300</v>
       </c>
       <c r="B244" s="1">
-        <v>139.7946166992188</v>
+        <v>139.7946014404297</v>
       </c>
       <c r="C244" s="1">
-        <v>141.2466210145663</v>
+        <v>141.2466164854802</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -17980,10 +17981,10 @@
         <v>45301</v>
       </c>
       <c r="B245" s="1">
-        <v>141.1136779785156</v>
+        <v>141.1136932373047</v>
       </c>
       <c r="C245" s="1">
-        <v>142.5793829835962</v>
+        <v>142.5794093918053</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -17991,10 +17992,10 @@
         <v>45302</v>
       </c>
       <c r="B246" s="1">
-        <v>140.9153289794922</v>
+        <v>140.9153442382812</v>
       </c>
       <c r="C246" s="1">
-        <v>142.3789737936347</v>
+        <v>142.3790001863949</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -18005,7 +18006,7 @@
         <v>141.4806671142578</v>
       </c>
       <c r="C247" s="1">
-        <v>142.950183924266</v>
+        <v>142.9501949437801</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -18013,10 +18014,10 @@
         <v>45307</v>
       </c>
       <c r="B248" s="1">
-        <v>141.3219909667969</v>
+        <v>141.3219757080078</v>
       </c>
       <c r="C248" s="1">
-        <v>142.7898596557523</v>
+        <v>142.7898552456289</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -18024,10 +18025,10 @@
         <v>45308</v>
       </c>
       <c r="B249" s="1">
-        <v>140.3103485107422</v>
+        <v>140.3103179931641</v>
       </c>
       <c r="C249" s="1">
-        <v>141.7677095761104</v>
+        <v>141.7676896699145</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -18035,10 +18036,10 @@
         <v>45309</v>
       </c>
       <c r="B250" s="1">
-        <v>142.3038482666016</v>
+        <v>142.3038635253906</v>
       </c>
       <c r="C250" s="1">
-        <v>143.7819152097532</v>
+        <v>143.7819417106612</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -18046,10 +18047,10 @@
         <v>45310</v>
       </c>
       <c r="B251" s="1">
-        <v>145.1800994873047</v>
+        <v>145.1800689697266</v>
       </c>
       <c r="C251" s="1">
-        <v>146.6880411801648</v>
+        <v>146.6880216532595</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -18060,7 +18061,7 @@
         <v>144.7932891845703</v>
       </c>
       <c r="C252" s="1">
-        <v>146.2972131960487</v>
+        <v>146.2972244735732</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -18071,7 +18072,7 @@
         <v>145.8346710205078</v>
       </c>
       <c r="C253" s="1">
-        <v>147.3494115494988</v>
+        <v>147.3494229081335</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -18082,7 +18083,7 @@
         <v>147.4810638427734</v>
       </c>
       <c r="C254" s="1">
-        <v>149.0129049550282</v>
+        <v>149.0129164418956</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -18093,7 +18094,7 @@
         <v>150.6250610351562</v>
       </c>
       <c r="C255" s="1">
-        <v>152.1895578933801</v>
+        <v>152.1895696251242</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -18101,10 +18102,10 @@
         <v>45317</v>
       </c>
       <c r="B256" s="1">
-        <v>150.9424591064453</v>
+        <v>150.9424896240234</v>
       </c>
       <c r="C256" s="1">
-        <v>152.5102526822401</v>
+        <v>152.5102952732628</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -18115,7 +18116,7 @@
         <v>152.2516326904297</v>
       </c>
       <c r="C257" s="1">
-        <v>153.833024255463</v>
+        <v>153.8330361138961</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -18126,7 +18127,7 @@
         <v>150.2184448242188</v>
       </c>
       <c r="C258" s="1">
-        <v>151.778718283095</v>
+        <v>151.7787299831689</v>
       </c>
     </row>
   </sheetData>

--- a/resultats.xlsx
+++ b/resultats.xlsx
@@ -473,8 +473,7 @@
     <col min="1" max="1" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1">
@@ -536,19 +535,19 @@
         <v>4019.81005859375</v>
       </c>
       <c r="C5" s="1">
-        <v>138.8828582763672</v>
+        <v>138.8828430175781</v>
       </c>
       <c r="D5" s="1">
         <v>202</v>
       </c>
       <c r="E5" s="1">
-        <v>236.3760528564453</v>
+        <v>236.3760986328125</v>
       </c>
       <c r="F5" s="1">
         <v>97.51999664306641</v>
       </c>
       <c r="G5" s="1">
-        <v>98.97200012207031</v>
+        <v>98.97199249267578</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -571,7 +570,7 @@
         <v>159</v>
       </c>
       <c r="G6" s="1">
-        <v>150.2184448242188</v>
+        <v>150.2184600830078</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="3" customFormat="1">
@@ -582,19 +581,19 @@
         <v>0.2251748572833444</v>
       </c>
       <c r="C7" s="3">
-        <v>0.3400259090839674</v>
+        <v>0.3400260563100195</v>
       </c>
       <c r="D7" s="3">
         <v>0.06237626783918626</v>
       </c>
       <c r="E7" s="3">
-        <v>0.6992867084483964</v>
+        <v>0.6992863793661721</v>
       </c>
       <c r="F7" s="3">
         <v>0.6304348387331982</v>
       </c>
       <c r="G7" s="3">
-        <v>0.5177872998316896</v>
+        <v>0.517787571005246</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="3" customFormat="1">
@@ -605,19 +604,19 @@
         <v>0.2212933175580829</v>
       </c>
       <c r="C8" s="3">
-        <v>0.333911607543669</v>
+        <v>0.3339117518080452</v>
       </c>
       <c r="D8" s="3">
         <v>0.06137232945653404</v>
       </c>
       <c r="E8" s="3">
-        <v>0.6852671052679291</v>
+        <v>0.6852667840002153</v>
       </c>
       <c r="F8" s="3">
         <v>0.6180286426432327</v>
       </c>
       <c r="G8" s="3">
-        <v>0.5079241406955293</v>
+        <v>0.5079244058973418</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="3" customFormat="1">
@@ -628,19 +627,19 @@
         <v>0.0007932952126940571</v>
       </c>
       <c r="C9" s="3">
-        <v>0.001143316206692137</v>
+        <v>0.001143316635864242</v>
       </c>
       <c r="D9" s="3">
         <v>0.0002363600048310617</v>
       </c>
       <c r="E9" s="3">
-        <v>0.002071127264636061</v>
+        <v>0.002071126508155384</v>
       </c>
       <c r="F9" s="3">
         <v>0.001909557622930636</v>
       </c>
       <c r="G9" s="3">
-        <v>0.001629896681515417</v>
+        <v>0.001629897379420586</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="3" customFormat="1">
@@ -651,19 +650,19 @@
         <v>0.1253305867413214</v>
       </c>
       <c r="C10" s="3">
-        <v>0.2005366690122959</v>
+        <v>0.2005365867859033</v>
       </c>
       <c r="D10" s="3">
         <v>0.0567447014935399</v>
       </c>
       <c r="E10" s="3">
-        <v>0.2370178639279349</v>
+        <v>0.237017821350406</v>
       </c>
       <c r="F10" s="3">
         <v>0.3161577817349202</v>
       </c>
       <c r="G10" s="3">
-        <v>0.2958241860927493</v>
+        <v>0.295824069544639</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="3" customFormat="1">
@@ -674,19 +673,19 @@
         <v>0.007895084861603466</v>
       </c>
       <c r="C11" s="3">
-        <v>0.01263262273704304</v>
+        <v>0.01263261755726718</v>
       </c>
       <c r="D11" s="3">
         <v>0.003574580199345286</v>
       </c>
       <c r="E11" s="3">
-        <v>0.01493072200554911</v>
+        <v>0.01493071932341689</v>
       </c>
       <c r="F11" s="3">
         <v>0.01991606822686756</v>
       </c>
       <c r="G11" s="3">
-        <v>0.01863517209998826</v>
+        <v>0.01863516475814741</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -697,19 +696,19 @@
         <v>1.765676865574927</v>
       </c>
       <c r="C12" s="1">
-        <v>1.6650900266185</v>
+        <v>1.665091428750285</v>
       </c>
       <c r="D12" s="1">
         <v>1.081551719212427</v>
       </c>
       <c r="E12" s="1">
-        <v>2.891204459914819</v>
+        <v>2.891203623828439</v>
       </c>
       <c r="F12" s="1">
         <v>1.954810788625198</v>
       </c>
       <c r="G12" s="1">
-        <v>1.716979762216875</v>
+        <v>1.716981335153654</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="3" customFormat="1">
@@ -726,7 +725,7 @@
         <v>-0.02974119167021968</v>
       </c>
       <c r="E13" s="3">
-        <v>-0.1298759756200135</v>
+        <v>-0.129875900169687</v>
       </c>
       <c r="F13" s="3">
         <v>-0.1964396385244207</v>
@@ -740,22 +739,22 @@
         <v>22</v>
       </c>
       <c r="B14" s="1">
-        <v>281.8065128365591</v>
+        <v>276.1600664370077</v>
       </c>
       <c r="C14" s="1">
-        <v>477.3226911640876</v>
+        <v>477.4879464885985</v>
       </c>
       <c r="D14" s="1">
-        <v>136.368050303444</v>
+        <v>135.4241270416449</v>
       </c>
       <c r="E14" s="1">
-        <v>1640.707354991571</v>
+        <v>1459.405947235744</v>
       </c>
       <c r="F14" s="1">
-        <v>1347.676699482176</v>
+        <v>1492.239514073</v>
       </c>
       <c r="G14" s="1">
-        <v>953.2319921016054</v>
+        <v>1010.627389295891</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -763,22 +762,22 @@
         <v>23</v>
       </c>
       <c r="B15" s="1">
-        <v>172.4089108020503</v>
+        <v>178.2326878503416</v>
       </c>
       <c r="C15" s="1">
-        <v>226.1296221361287</v>
+        <v>218.8578667831883</v>
       </c>
       <c r="D15" s="1">
-        <v>112.4875905927913</v>
+        <v>113.6232836619716</v>
       </c>
       <c r="E15" s="1">
-        <v>585.7725499788321</v>
+        <v>494.7682914898266</v>
       </c>
       <c r="F15" s="1">
-        <v>368.9152057443455</v>
+        <v>401.3814220466234</v>
       </c>
       <c r="G15" s="1">
-        <v>247.6704918040359</v>
+        <v>254.3858357059047</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -786,22 +785,22 @@
         <v>24</v>
       </c>
       <c r="B16" s="1">
-        <v>269.280615281568</v>
+        <v>264.5203265010251</v>
       </c>
       <c r="C16" s="1">
-        <v>442.2350825204397</v>
+        <v>441.9585686873706</v>
       </c>
       <c r="D16" s="1">
-        <v>135.5645468315637</v>
+        <v>132.3152773411375</v>
       </c>
       <c r="E16" s="1">
-        <v>1345.84104139986</v>
+        <v>1316.297161203467</v>
       </c>
       <c r="F16" s="1">
-        <v>1063.070311669332</v>
+        <v>1128.278748252805</v>
       </c>
       <c r="G16" s="1">
-        <v>735.5035177628083</v>
+        <v>828.0935053534004</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -809,22 +808,22 @@
         <v>25</v>
       </c>
       <c r="B17" s="1">
-        <v>413.1424048339946</v>
+        <v>404.2569374336622</v>
       </c>
       <c r="C17" s="1">
-        <v>903.1246609120141</v>
+        <v>892.8068078558273</v>
       </c>
       <c r="D17" s="1">
-        <v>166.0721244291448</v>
+        <v>162.5229752818519</v>
       </c>
       <c r="E17" s="1">
-        <v>3400.707016549626</v>
+        <v>3044.628573842618</v>
       </c>
       <c r="F17" s="1">
-        <v>3258.446295319865</v>
+        <v>3602.879418452111</v>
       </c>
       <c r="G17" s="1">
-        <v>2214.917181848391</v>
+        <v>2210.390721627754</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="3" customFormat="1">
@@ -838,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="3">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
@@ -881,19 +880,19 @@
         <v>1</v>
       </c>
       <c r="C21" s="1">
-        <v>0.7060165381290121</v>
+        <v>0.7060172465660103</v>
       </c>
       <c r="D21" s="1">
         <v>0.004456046337864243</v>
       </c>
       <c r="E21" s="1">
-        <v>0.6246277619651215</v>
+        <v>0.6246286916963628</v>
       </c>
       <c r="F21" s="1">
         <v>0.6045950866477746</v>
       </c>
       <c r="G21" s="1">
-        <v>0.6008778074911151</v>
+        <v>0.6008773229065343</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -901,22 +900,22 @@
         <v>7</v>
       </c>
       <c r="B22" s="1">
-        <v>0.7060165381290121</v>
+        <v>0.7060172465660103</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>-0.05612555099858751</v>
+        <v>-0.0561253848466664</v>
       </c>
       <c r="E22" s="1">
-        <v>0.5536231956682565</v>
+        <v>0.5536257816599395</v>
       </c>
       <c r="F22" s="1">
-        <v>0.4276403029312523</v>
+        <v>0.4276414333842711</v>
       </c>
       <c r="G22" s="1">
-        <v>0.5177398601059796</v>
+        <v>0.5177399329107535</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -927,19 +926,19 @@
         <v>0.004456046337864243</v>
       </c>
       <c r="C23" s="1">
-        <v>-0.05612555099858751</v>
+        <v>-0.0561253848466664</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="E23" s="1">
-        <v>-0.04384018829302527</v>
+        <v>-0.04384078424626962</v>
       </c>
       <c r="F23" s="1">
         <v>-0.005269283798744161</v>
       </c>
       <c r="G23" s="1">
-        <v>-0.01599638681897387</v>
+        <v>-0.01599772152909821</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -947,22 +946,22 @@
         <v>9</v>
       </c>
       <c r="B24" s="1">
-        <v>0.6246277619651215</v>
+        <v>0.6246286916963628</v>
       </c>
       <c r="C24" s="1">
-        <v>0.5536231956682565</v>
+        <v>0.5536257816599395</v>
       </c>
       <c r="D24" s="1">
-        <v>-0.04384018829302527</v>
+        <v>-0.04384078424626962</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1">
-        <v>0.5709347819284806</v>
+        <v>0.5709360806035841</v>
       </c>
       <c r="G24" s="1">
-        <v>0.5011048421180136</v>
+        <v>0.5011065761627947</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -973,19 +972,19 @@
         <v>0.6045950866477746</v>
       </c>
       <c r="C25" s="1">
-        <v>0.4276403029312523</v>
+        <v>0.4276414333842711</v>
       </c>
       <c r="D25" s="1">
         <v>-0.005269283798744161</v>
       </c>
       <c r="E25" s="1">
-        <v>0.5709347819284806</v>
+        <v>0.5709360806035841</v>
       </c>
       <c r="F25" s="1">
         <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>0.600332078067905</v>
+        <v>0.6003319856823502</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -993,19 +992,19 @@
         <v>11</v>
       </c>
       <c r="B26" s="1">
-        <v>0.6008778074911151</v>
+        <v>0.6008773229065343</v>
       </c>
       <c r="C26" s="1">
-        <v>0.5177398601059796</v>
+        <v>0.5177399329107535</v>
       </c>
       <c r="D26" s="1">
-        <v>-0.01599638681897387</v>
+        <v>-0.01599772152909821</v>
       </c>
       <c r="E26" s="1">
-        <v>0.5011048421180136</v>
+        <v>0.5011065761627947</v>
       </c>
       <c r="F26" s="1">
-        <v>0.600332078067905</v>
+        <v>0.6003319856823502</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -3896,7 +3895,7 @@
         <v>44949</v>
       </c>
       <c r="B2" s="1">
-        <v>138.8828582763672</v>
+        <v>138.8828430175781</v>
       </c>
       <c r="C2" s="1">
         <v>100</v>
@@ -3907,10 +3906,10 @@
         <v>44950</v>
       </c>
       <c r="B3" s="1">
-        <v>140.2804412841797</v>
+        <v>140.2804565429688</v>
       </c>
       <c r="C3" s="1">
-        <v>101.006303459734</v>
+        <v>101.0063255439073</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3921,7 +3920,7 @@
         <v>139.6210174560547</v>
       </c>
       <c r="C4" s="1">
-        <v>100.5314976872226</v>
+        <v>100.5315087324236</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3929,10 +3928,10 @@
         <v>44952</v>
       </c>
       <c r="B5" s="1">
-        <v>141.6878967285156</v>
+        <v>141.6878509521484</v>
       </c>
       <c r="C5" s="1">
-        <v>102.0197153824172</v>
+        <v>102.0196936307066</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3943,7 +3942,7 @@
         <v>143.6268005371094</v>
       </c>
       <c r="C6" s="1">
-        <v>103.4157867425958</v>
+        <v>103.415798104688</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3951,10 +3950,10 @@
         <v>44956</v>
       </c>
       <c r="B7" s="1">
-        <v>140.7430419921875</v>
+        <v>140.7430267333984</v>
       </c>
       <c r="C7" s="1">
-        <v>101.3393904322726</v>
+        <v>101.3393905794288</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3962,10 +3961,10 @@
         <v>44957</v>
       </c>
       <c r="B8" s="1">
-        <v>142.0126495361328</v>
+        <v>142.0126800537109</v>
       </c>
       <c r="C8" s="1">
-        <v>102.2535475569905</v>
+        <v>102.2535807650026</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3976,7 +3975,7 @@
         <v>143.1346740722656</v>
       </c>
       <c r="C9" s="1">
-        <v>103.0614403020405</v>
+        <v>103.0614516252014</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3984,10 +3983,10 @@
         <v>44959</v>
       </c>
       <c r="B10" s="1">
-        <v>148.4395751953125</v>
+        <v>148.4396362304688</v>
       </c>
       <c r="C10" s="1">
-        <v>106.8811349633431</v>
+        <v>106.881190653392</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3995,10 +3994,10 @@
         <v>44960</v>
       </c>
       <c r="B11" s="1">
-        <v>152.0615692138672</v>
+        <v>152.0615234375</v>
       </c>
       <c r="C11" s="1">
-        <v>109.4890838949147</v>
+        <v>109.4890629638492</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4006,10 +4005,10 @@
         <v>44963</v>
       </c>
       <c r="B12" s="1">
-        <v>149.3352508544922</v>
+        <v>149.3352661132812</v>
       </c>
       <c r="C12" s="1">
-        <v>107.5260494404036</v>
+        <v>107.5260722408888</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4017,10 +4016,10 @@
         <v>44964</v>
       </c>
       <c r="B13" s="1">
-        <v>152.2091674804688</v>
+        <v>152.2091522216797</v>
       </c>
       <c r="C13" s="1">
-        <v>109.5953592613879</v>
+        <v>109.5953603156114</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4031,7 +4030,7 @@
         <v>149.5222473144531</v>
       </c>
       <c r="C14" s="1">
-        <v>107.6606927378426</v>
+        <v>107.6607045663145</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4039,10 +4038,10 @@
         <v>44966</v>
       </c>
       <c r="B15" s="1">
-        <v>148.4888458251953</v>
+        <v>148.4888153076172</v>
       </c>
       <c r="C15" s="1">
-        <v>106.9166113572583</v>
+        <v>106.9166011303666</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4050,10 +4049,10 @@
         <v>44967</v>
       </c>
       <c r="B16" s="1">
-        <v>148.8535308837891</v>
+        <v>148.8535461425781</v>
       </c>
       <c r="C16" s="1">
-        <v>107.1791960009787</v>
+        <v>107.1792187633558</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4064,7 +4063,7 @@
         <v>151.6529998779297</v>
       </c>
       <c r="C17" s="1">
-        <v>109.1949011995064</v>
+        <v>109.1949131965388</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4072,10 +4071,10 @@
         <v>44971</v>
       </c>
       <c r="B18" s="1">
-        <v>151.0122528076172</v>
+        <v>151.0122680664062</v>
       </c>
       <c r="C18" s="1">
-        <v>108.7335432765312</v>
+        <v>108.7335662096814</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4083,10 +4082,10 @@
         <v>44972</v>
       </c>
       <c r="B19" s="1">
-        <v>153.1118621826172</v>
+        <v>153.1118316650391</v>
       </c>
       <c r="C19" s="1">
-        <v>110.2453276688296</v>
+        <v>110.2453178076575</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4097,7 +4096,7 @@
         <v>151.5149993896484</v>
       </c>
       <c r="C20" s="1">
-        <v>109.0955365334894</v>
+        <v>109.0955485196047</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4105,10 +4104,10 @@
         <v>44974</v>
       </c>
       <c r="B21" s="1">
-        <v>150.3715515136719</v>
+        <v>150.3715972900391</v>
       </c>
       <c r="C21" s="1">
-        <v>108.2722183139715</v>
+        <v>108.2722631700496</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4119,7 +4118,7 @@
         <v>146.3596649169922</v>
       </c>
       <c r="C22" s="1">
-        <v>105.3835345365277</v>
+        <v>105.3835461148126</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4130,7 +4129,7 @@
         <v>146.7835235595703</v>
       </c>
       <c r="C23" s="1">
-        <v>105.6887260107229</v>
+        <v>105.6887376225386</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4138,10 +4137,10 @@
         <v>44980</v>
       </c>
       <c r="B24" s="1">
-        <v>147.2665710449219</v>
+        <v>147.2665405273438</v>
       </c>
       <c r="C24" s="1">
-        <v>106.0365353021981</v>
+        <v>106.0365249786142</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4152,7 +4151,7 @@
         <v>144.6149444580078</v>
       </c>
       <c r="C25" s="1">
-        <v>104.1272812590263</v>
+        <v>104.1272926992891</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4160,10 +4159,10 @@
         <v>44984</v>
       </c>
       <c r="B26" s="1">
-        <v>145.8076934814453</v>
+        <v>145.8076629638672</v>
       </c>
       <c r="C26" s="1">
-        <v>104.9860978460698</v>
+        <v>104.9860874070763</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4171,10 +4170,10 @@
         <v>44985</v>
       </c>
       <c r="B27" s="1">
-        <v>145.3049468994141</v>
+        <v>145.3049621582031</v>
       </c>
       <c r="C27" s="1">
-        <v>104.6241045891116</v>
+        <v>104.6241270707658</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4182,10 +4181,10 @@
         <v>44986</v>
       </c>
       <c r="B28" s="1">
-        <v>143.2349395751953</v>
+        <v>143.2349090576172</v>
       </c>
       <c r="C28" s="1">
-        <v>103.1336345988558</v>
+        <v>103.1336239563358</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -4196,7 +4195,7 @@
         <v>143.8263854980469</v>
       </c>
       <c r="C29" s="1">
-        <v>103.5594941543055</v>
+        <v>103.5595055321866</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -4207,7 +4206,7 @@
         <v>148.8732452392578</v>
       </c>
       <c r="C30" s="1">
-        <v>107.1933909532669</v>
+        <v>107.1934027303972</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -4215,10 +4214,10 @@
         <v>44991</v>
       </c>
       <c r="B31" s="1">
-        <v>151.6332855224609</v>
+        <v>151.6332550048828</v>
       </c>
       <c r="C31" s="1">
-        <v>109.1807062472183</v>
+        <v>109.1806962690783</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -4229,7 +4228,7 @@
         <v>149.4351196289062</v>
       </c>
       <c r="C32" s="1">
-        <v>107.5979580802843</v>
+        <v>107.5979699018636</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -4237,10 +4236,10 @@
         <v>44993</v>
       </c>
       <c r="B33" s="1">
-        <v>150.6869659423828</v>
+        <v>150.6869812011719</v>
       </c>
       <c r="C33" s="1">
-        <v>108.4993265637767</v>
+        <v>108.499349471194</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -4248,10 +4247,10 @@
         <v>44994</v>
       </c>
       <c r="B34" s="1">
-        <v>148.4395141601562</v>
+        <v>148.4395599365234</v>
       </c>
       <c r="C34" s="1">
-        <v>106.8810910161224</v>
+        <v>106.88113571936</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -4259,10 +4258,10 @@
         <v>44995</v>
       </c>
       <c r="B35" s="1">
-        <v>146.3793640136719</v>
+        <v>146.37939453125</v>
       </c>
       <c r="C35" s="1">
-        <v>105.3977185020106</v>
+        <v>105.3977520554667</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -4273,7 +4272,7 @@
         <v>148.3212585449219</v>
       </c>
       <c r="C36" s="1">
-        <v>106.7959432760038</v>
+        <v>106.7959550094673</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -4281,10 +4280,10 @@
         <v>44999</v>
       </c>
       <c r="B37" s="1">
-        <v>150.4109649658203</v>
+        <v>150.4109802246094</v>
       </c>
       <c r="C37" s="1">
-        <v>108.3005972317426</v>
+        <v>108.3006201173259</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -4292,10 +4291,10 @@
         <v>45000</v>
       </c>
       <c r="B38" s="1">
-        <v>150.8052825927734</v>
+        <v>150.8052673339844</v>
       </c>
       <c r="C38" s="1">
-        <v>108.584518251116</v>
+        <v>108.5845191942804</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -4306,7 +4305,7 @@
         <v>153.6244354248047</v>
       </c>
       <c r="C39" s="1">
-        <v>110.6143964283215</v>
+        <v>110.614408581311</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -4314,10 +4313,10 @@
         <v>45002</v>
       </c>
       <c r="B40" s="1">
-        <v>152.7865447998047</v>
+        <v>152.7865600585938</v>
       </c>
       <c r="C40" s="1">
-        <v>110.0110889824647</v>
+        <v>110.0111120559765</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -4325,10 +4324,10 @@
         <v>45005</v>
       </c>
       <c r="B41" s="1">
-        <v>155.1522979736328</v>
+        <v>155.1522827148438</v>
       </c>
       <c r="C41" s="1">
-        <v>111.7145052306531</v>
+        <v>111.7145065177032</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -4339,7 +4338,7 @@
         <v>157.0054168701172</v>
       </c>
       <c r="C42" s="1">
-        <v>113.0488087721289</v>
+        <v>113.0488211925827</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -4347,10 +4346,10 @@
         <v>45007</v>
       </c>
       <c r="B43" s="1">
-        <v>155.576171875</v>
+        <v>155.5761566162109</v>
       </c>
       <c r="C43" s="1">
-        <v>112.0197076916536</v>
+        <v>112.0197090122356</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -4358,10 +4357,10 @@
         <v>45008</v>
       </c>
       <c r="B44" s="1">
-        <v>156.6604156494141</v>
+        <v>156.6604309082031</v>
       </c>
       <c r="C44" s="1">
-        <v>112.8003971070863</v>
+        <v>112.8004204870539</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -4372,7 +4371,7 @@
         <v>157.9616088867188</v>
       </c>
       <c r="C45" s="1">
-        <v>113.7372969185198</v>
+        <v>113.7373094146164</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -4383,7 +4382,7 @@
         <v>156.0197296142578</v>
       </c>
       <c r="C46" s="1">
-        <v>112.3390831313318</v>
+        <v>112.3390954738093</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -4391,10 +4390,10 @@
         <v>45013</v>
       </c>
       <c r="B47" s="1">
-        <v>155.3987274169922</v>
+        <v>155.3987121582031</v>
       </c>
       <c r="C47" s="1">
-        <v>111.891942134255</v>
+        <v>111.8919434407997</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -4402,10 +4401,10 @@
         <v>45014</v>
       </c>
       <c r="B48" s="1">
-        <v>158.4741668701172</v>
+        <v>158.4741821289062</v>
       </c>
       <c r="C48" s="1">
-        <v>114.1063546912065</v>
+        <v>114.1063782146571</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -4413,10 +4412,10 @@
         <v>45015</v>
       </c>
       <c r="B49" s="1">
-        <v>160.0414886474609</v>
+        <v>160.0414733886719</v>
       </c>
       <c r="C49" s="1">
-        <v>115.2348753717248</v>
+        <v>115.2348770455511</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -4424,10 +4423,10 @@
         <v>45016</v>
       </c>
       <c r="B50" s="1">
-        <v>162.5451507568359</v>
+        <v>162.5451812744141</v>
       </c>
       <c r="C50" s="1">
-        <v>117.0375903650992</v>
+        <v>117.0376251974054</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -4438,7 +4437,7 @@
         <v>163.7970581054688</v>
       </c>
       <c r="C51" s="1">
-        <v>117.9390027958123</v>
+        <v>117.9390157535422</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -4446,10 +4445,10 @@
         <v>45020</v>
       </c>
       <c r="B52" s="1">
-        <v>163.2647857666016</v>
+        <v>163.2647705078125</v>
       </c>
       <c r="C52" s="1">
-        <v>117.5557500708374</v>
+        <v>117.5557519996537</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -4457,10 +4456,10 @@
         <v>45021</v>
       </c>
       <c r="B53" s="1">
-        <v>161.4214477539062</v>
+        <v>161.4214782714844</v>
       </c>
       <c r="C53" s="1">
-        <v>116.2284890714798</v>
+        <v>116.2285238148917</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -4468,10 +4467,10 @@
         <v>45022</v>
       </c>
       <c r="B54" s="1">
-        <v>162.3086090087891</v>
+        <v>162.30859375</v>
       </c>
       <c r="C54" s="1">
-        <v>116.8672729112518</v>
+        <v>116.8672747644264</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -4479,10 +4478,10 @@
         <v>45026</v>
       </c>
       <c r="B55" s="1">
-        <v>159.7161865234375</v>
+        <v>159.7161560058594</v>
       </c>
       <c r="C55" s="1">
-        <v>115.0006476721652</v>
+        <v>115.0006383334509</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -4493,7 +4492,7 @@
         <v>158.5037384033203</v>
       </c>
       <c r="C56" s="1">
-        <v>114.1276471196387</v>
+        <v>114.1276596586223</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -4504,7 +4503,7 @@
         <v>157.8137359619141</v>
       </c>
       <c r="C57" s="1">
-        <v>113.6308237895535</v>
+        <v>113.6308362739521</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -4512,10 +4511,10 @@
         <v>45029</v>
       </c>
       <c r="B58" s="1">
-        <v>163.1957702636719</v>
+        <v>163.1957550048828</v>
       </c>
       <c r="C58" s="1">
-        <v>117.5060567510237</v>
+        <v>117.5060586743803</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -4523,10 +4522,10 @@
         <v>45030</v>
       </c>
       <c r="B59" s="1">
-        <v>162.8507843017578</v>
+        <v>162.8507537841797</v>
       </c>
       <c r="C59" s="1">
-        <v>117.2576560727863</v>
+        <v>117.2576469820451</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -4537,7 +4536,7 @@
         <v>162.8704833984375</v>
       </c>
       <c r="C60" s="1">
-        <v>117.2718400382692</v>
+        <v>117.2718529226992</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -4545,10 +4544,10 @@
         <v>45034</v>
       </c>
       <c r="B61" s="1">
-        <v>164.0927886962891</v>
+        <v>164.0927734375</v>
       </c>
       <c r="C61" s="1">
-        <v>118.1519380669397</v>
+        <v>118.151940061258</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -4556,10 +4555,10 @@
         <v>45035</v>
       </c>
       <c r="B62" s="1">
-        <v>165.2362060546875</v>
+        <v>165.2362213134766</v>
       </c>
       <c r="C62" s="1">
-        <v>118.9752343128473</v>
+        <v>118.9752583712323</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -4570,7 +4569,7 @@
         <v>164.2701873779297</v>
       </c>
       <c r="C63" s="1">
-        <v>118.2796706639228</v>
+        <v>118.2796836590811</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -4578,10 +4577,10 @@
         <v>45037</v>
       </c>
       <c r="B64" s="1">
-        <v>162.6634674072266</v>
+        <v>162.6634979248047</v>
       </c>
       <c r="C64" s="1">
-        <v>117.1227820524385</v>
+        <v>117.1228168941046</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -4589,10 +4588,10 @@
         <v>45040</v>
       </c>
       <c r="B65" s="1">
-        <v>162.9690399169922</v>
+        <v>162.9690551757812</v>
       </c>
       <c r="C65" s="1">
-        <v>117.3428038129048</v>
+        <v>117.3428276919379</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -4603,7 +4602,7 @@
         <v>161.4313201904297</v>
       </c>
       <c r="C66" s="1">
-        <v>116.2355975344291</v>
+        <v>116.2356103050091</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -4611,10 +4610,10 @@
         <v>45042</v>
       </c>
       <c r="B67" s="1">
-        <v>161.4214477539062</v>
+        <v>161.4214782714844</v>
       </c>
       <c r="C67" s="1">
-        <v>116.2284890714798</v>
+        <v>116.2285238148917</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -4622,10 +4621,10 @@
         <v>45043</v>
       </c>
       <c r="B68" s="1">
-        <v>166.0050659179688</v>
+        <v>166.0050811767578</v>
       </c>
       <c r="C68" s="1">
-        <v>119.5288374520852</v>
+        <v>119.5288615712935</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -4633,10 +4632,10 @@
         <v>45044</v>
       </c>
       <c r="B69" s="1">
-        <v>167.2569274902344</v>
+        <v>167.2569122314453</v>
       </c>
       <c r="C69" s="1">
-        <v>120.4302169223827</v>
+        <v>120.4302191670111</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -4644,10 +4643,10 @@
         <v>45047</v>
       </c>
       <c r="B70" s="1">
-        <v>167.1681976318359</v>
+        <v>167.168212890625</v>
       </c>
       <c r="C70" s="1">
-        <v>120.3663286502809</v>
+        <v>120.3663528615027</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -4658,7 +4657,7 @@
         <v>166.1331939697266</v>
       </c>
       <c r="C71" s="1">
-        <v>119.621093655153</v>
+        <v>119.6211067976909</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -4666,10 +4665,10 @@
         <v>45049</v>
       </c>
       <c r="B72" s="1">
-        <v>165.0587463378906</v>
+        <v>165.0587768554688</v>
       </c>
       <c r="C72" s="1">
-        <v>118.8474577686436</v>
+        <v>118.8474927997964</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -4677,10 +4676,10 @@
         <v>45050</v>
       </c>
       <c r="B73" s="1">
-        <v>163.4224548339844</v>
+        <v>163.4224853515625</v>
       </c>
       <c r="C73" s="1">
-        <v>117.6692767287271</v>
+        <v>117.6693116304355</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -4688,10 +4687,10 @@
         <v>45051</v>
       </c>
       <c r="B74" s="1">
-        <v>171.0913696289062</v>
+        <v>171.0913848876953</v>
       </c>
       <c r="C74" s="1">
-        <v>123.191135142428</v>
+        <v>123.1911596640059</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -4699,10 +4698,10 @@
         <v>45054</v>
       </c>
       <c r="B75" s="1">
-        <v>171.0223846435547</v>
+        <v>171.0223693847656</v>
       </c>
       <c r="C75" s="1">
-        <v>123.1414637962246</v>
+        <v>123.1414663387325</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -4713,7 +4712,7 @@
         <v>169.3170776367188</v>
       </c>
       <c r="C76" s="1">
-        <v>121.9135894364945</v>
+        <v>121.9136028309045</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -4721,10 +4720,10 @@
         <v>45056</v>
       </c>
       <c r="B77" s="1">
-        <v>171.0814971923828</v>
+        <v>171.0815124511719</v>
       </c>
       <c r="C77" s="1">
-        <v>123.1840266794787</v>
+        <v>123.1840512002756</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -4732,10 +4731,10 @@
         <v>45057</v>
       </c>
       <c r="B78" s="1">
-        <v>171.2687835693359</v>
+        <v>171.268798828125</v>
       </c>
       <c r="C78" s="1">
-        <v>123.3188787262162</v>
+        <v>123.318903261829</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -4743,10 +4742,10 @@
         <v>45058</v>
       </c>
       <c r="B79" s="1">
-        <v>170.3409423828125</v>
+        <v>170.3409881591797</v>
       </c>
       <c r="C79" s="1">
-        <v>122.6508040638435</v>
+        <v>122.650850499669</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -4754,10 +4753,10 @@
         <v>45061</v>
       </c>
       <c r="B80" s="1">
-        <v>169.847412109375</v>
+        <v>169.8473968505859</v>
       </c>
       <c r="C80" s="1">
-        <v>122.2954468372119</v>
+        <v>122.2954492867695</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -4765,10 +4764,10 @@
         <v>45062</v>
       </c>
       <c r="B81" s="1">
-        <v>169.847412109375</v>
+        <v>169.8473968505859</v>
       </c>
       <c r="C81" s="1">
-        <v>122.2954468372119</v>
+        <v>122.2954492867695</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -4776,10 +4775,10 @@
         <v>45063</v>
       </c>
       <c r="B82" s="1">
-        <v>170.4594116210938</v>
+        <v>170.4593963623047</v>
       </c>
       <c r="C82" s="1">
-        <v>122.7361056192345</v>
+        <v>122.7361081172064</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -4787,10 +4786,10 @@
         <v>45064</v>
       </c>
       <c r="B83" s="1">
-        <v>172.7889099121094</v>
+        <v>172.7888946533203</v>
       </c>
       <c r="C83" s="1">
-        <v>124.4134172183233</v>
+        <v>124.4134199005782</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -4798,10 +4797,10 @@
         <v>45065</v>
       </c>
       <c r="B84" s="1">
-        <v>172.8974914550781</v>
+        <v>172.8975372314453</v>
       </c>
       <c r="C84" s="1">
-        <v>124.4915993239599</v>
+        <v>124.49164596203</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -4812,7 +4811,7 @@
         <v>171.9498901367188</v>
       </c>
       <c r="C85" s="1">
-        <v>123.8092967488835</v>
+        <v>123.8093103515712</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -4820,10 +4819,10 @@
         <v>45069</v>
       </c>
       <c r="B86" s="1">
-        <v>169.3440093994141</v>
+        <v>169.343994140625</v>
       </c>
       <c r="C86" s="1">
-        <v>121.9329811476311</v>
+        <v>121.9329835573653</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -4831,10 +4830,10 @@
         <v>45070</v>
       </c>
       <c r="B87" s="1">
-        <v>169.6203765869141</v>
+        <v>169.6203918457031</v>
       </c>
       <c r="C87" s="1">
-        <v>122.1319741629895</v>
+        <v>122.1319985681994</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -4842,10 +4841,10 @@
         <v>45071</v>
       </c>
       <c r="B88" s="1">
-        <v>170.7555084228516</v>
+        <v>170.7555541992188</v>
       </c>
       <c r="C88" s="1">
-        <v>122.9493045736861</v>
+        <v>122.9493510423073</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -4856,7 +4855,7 @@
         <v>173.1640014648438</v>
       </c>
       <c r="C89" s="1">
-        <v>124.6834948631742</v>
+        <v>124.6835085619084</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -4864,10 +4863,10 @@
         <v>45076</v>
       </c>
       <c r="B90" s="1">
-        <v>175.0098571777344</v>
+        <v>175.0098419189453</v>
       </c>
       <c r="C90" s="1">
-        <v>126.0125686853859</v>
+        <v>126.0125715433365</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -4875,10 +4874,10 @@
         <v>45077</v>
       </c>
       <c r="B91" s="1">
-        <v>174.9604949951172</v>
+        <v>174.9605102539062</v>
       </c>
       <c r="C91" s="1">
-        <v>125.9770263706396</v>
+        <v>125.977051198298</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -4889,7 +4888,7 @@
         <v>177.7638244628906</v>
       </c>
       <c r="C92" s="1">
-        <v>127.995511230877</v>
+        <v>127.995525293496</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -4897,10 +4896,10 @@
         <v>45079</v>
       </c>
       <c r="B93" s="1">
-        <v>178.6126861572266</v>
+        <v>178.6127166748047</v>
       </c>
       <c r="C93" s="1">
-        <v>128.6067181896558</v>
+        <v>128.6067542930397</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -4908,10 +4907,10 @@
         <v>45082</v>
       </c>
       <c r="B94" s="1">
-        <v>177.2603912353516</v>
+        <v>177.2604064941406</v>
       </c>
       <c r="C94" s="1">
-        <v>127.6330235676859</v>
+        <v>127.6330485772855</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -4919,10 +4918,10 @@
         <v>45083</v>
       </c>
       <c r="B95" s="1">
-        <v>176.8951873779297</v>
+        <v>176.8951721191406</v>
       </c>
       <c r="C95" s="1">
-        <v>127.3700653725895</v>
+        <v>127.3700683796856</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -4930,10 +4929,10 @@
         <v>45084</v>
       </c>
       <c r="B96" s="1">
-        <v>175.5231323242188</v>
+        <v>175.5231475830078</v>
       </c>
       <c r="C96" s="1">
-        <v>126.3821428379159</v>
+        <v>126.3821677100837</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -4944,7 +4943,7 @@
         <v>178.2376251220703</v>
       </c>
       <c r="C97" s="1">
-        <v>128.3366625184153</v>
+        <v>128.3366766185159</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -4955,7 +4954,7 @@
         <v>178.6225738525391</v>
       </c>
       <c r="C98" s="1">
-        <v>128.6138376394102</v>
+        <v>128.6138517699635</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -4963,10 +4962,10 @@
         <v>45089</v>
       </c>
       <c r="B99" s="1">
-        <v>181.4160308837891</v>
+        <v>181.4160003662109</v>
       </c>
       <c r="C99" s="1">
-        <v>130.6252140366984</v>
+        <v>130.6252064146249</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -4974,10 +4973,10 @@
         <v>45090</v>
       </c>
       <c r="B100" s="1">
-        <v>180.9422302246094</v>
+        <v>180.9422149658203</v>
       </c>
       <c r="C100" s="1">
-        <v>130.2840627491601</v>
+        <v>130.2840660764115</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -4985,10 +4984,10 @@
         <v>45091</v>
       </c>
       <c r="B101" s="1">
-        <v>181.5739593505859</v>
+        <v>181.5739440917969</v>
       </c>
       <c r="C101" s="1">
-        <v>130.738927470276</v>
+        <v>130.7389308475025</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -4999,7 +4998,7 @@
         <v>183.6073303222656</v>
       </c>
       <c r="C102" s="1">
-        <v>132.2030181413028</v>
+        <v>132.2030326661925</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -5007,10 +5006,10 @@
         <v>45093</v>
       </c>
       <c r="B103" s="1">
-        <v>182.5314178466797</v>
+        <v>182.5314331054688</v>
       </c>
       <c r="C103" s="1">
-        <v>131.4283275214965</v>
+        <v>131.4283529480788</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -5018,10 +5017,10 @@
         <v>45097</v>
       </c>
       <c r="B104" s="1">
-        <v>182.6202545166016</v>
+        <v>182.6202697753906</v>
       </c>
       <c r="C104" s="1">
-        <v>131.4922927012346</v>
+        <v>131.4923181348446</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -5032,7 +5031,7 @@
         <v>181.5838317871094</v>
       </c>
       <c r="C105" s="1">
-        <v>130.7460359332253</v>
+        <v>130.7460502980391</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -5040,10 +5039,10 @@
         <v>45099</v>
       </c>
       <c r="B106" s="1">
-        <v>184.5845947265625</v>
+        <v>184.5845489501953</v>
       </c>
       <c r="C106" s="1">
-        <v>132.9066790656425</v>
+        <v>132.9066607074229</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -5054,7 +5053,7 @@
         <v>184.2686920166016</v>
       </c>
       <c r="C107" s="1">
-        <v>132.6792192380717</v>
+        <v>132.6792338152806</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -5062,10 +5061,10 @@
         <v>45103</v>
       </c>
       <c r="B108" s="1">
-        <v>182.8769378662109</v>
+        <v>182.8769073486328</v>
       </c>
       <c r="C108" s="1">
-        <v>131.6771127379151</v>
+        <v>131.6771052314118</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -5073,10 +5072,10 @@
         <v>45104</v>
       </c>
       <c r="B109" s="1">
-        <v>185.630859375</v>
+        <v>185.6308746337891</v>
       </c>
       <c r="C109" s="1">
-        <v>133.6600223229908</v>
+        <v>133.660047994765</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -5084,10 +5083,10 @@
         <v>45105</v>
       </c>
       <c r="B110" s="1">
-        <v>186.8054809570312</v>
+        <v>186.8054656982422</v>
       </c>
       <c r="C110" s="1">
-        <v>134.5057865854844</v>
+        <v>134.5057903765684</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -5095,10 +5094,10 @@
         <v>45106</v>
       </c>
       <c r="B111" s="1">
-        <v>187.1410827636719</v>
+        <v>187.1410980224609</v>
       </c>
       <c r="C111" s="1">
-        <v>134.7474303785383</v>
+        <v>134.747456169784</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -5106,10 +5105,10 @@
         <v>45107</v>
       </c>
       <c r="B112" s="1">
-        <v>191.4644927978516</v>
+        <v>191.4645385742188</v>
       </c>
       <c r="C112" s="1">
-        <v>137.8604207704673</v>
+        <v>137.8604688773439</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -5117,10 +5116,10 @@
         <v>45110</v>
       </c>
       <c r="B113" s="1">
-        <v>189.9740142822266</v>
+        <v>189.9740295410156</v>
       </c>
       <c r="C113" s="1">
-        <v>136.7872296408183</v>
+        <v>136.7872556561727</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -5128,10 +5127,10 @@
         <v>45112</v>
       </c>
       <c r="B114" s="1">
-        <v>188.8586273193359</v>
+        <v>188.858642578125</v>
       </c>
       <c r="C114" s="1">
-        <v>135.9841161560201</v>
+        <v>135.984142083138</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -5139,10 +5138,10 @@
         <v>45113</v>
       </c>
       <c r="B115" s="1">
-        <v>189.3324127197266</v>
+        <v>189.3324432373047</v>
       </c>
       <c r="C115" s="1">
-        <v>136.3252564567531</v>
+        <v>136.3252934081579</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -5150,10 +5149,10 @@
         <v>45114</v>
       </c>
       <c r="B116" s="1">
-        <v>188.2170104980469</v>
+        <v>188.2169952392578</v>
       </c>
       <c r="C116" s="1">
-        <v>135.5221319851498</v>
+        <v>135.5221358878977</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -5161,10 +5160,10 @@
         <v>45117</v>
       </c>
       <c r="B117" s="1">
-        <v>186.1737823486328</v>
+        <v>186.1737518310547</v>
       </c>
       <c r="C117" s="1">
-        <v>134.0509438379789</v>
+        <v>134.0509365922838</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -5175,7 +5174,7 @@
         <v>185.6506042480469</v>
       </c>
       <c r="C118" s="1">
-        <v>133.6742392488893</v>
+        <v>133.6742539354191</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -5183,10 +5182,10 @@
         <v>45119</v>
       </c>
       <c r="B119" s="1">
-        <v>187.3187561035156</v>
+        <v>187.3188018798828</v>
       </c>
       <c r="C119" s="1">
-        <v>134.8753607380145</v>
+        <v>134.8754085169284</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -5194,10 +5193,10 @@
         <v>45120</v>
       </c>
       <c r="B120" s="1">
-        <v>188.0788269042969</v>
+        <v>188.0788116455078</v>
       </c>
       <c r="C120" s="1">
-        <v>135.4226354774706</v>
+        <v>135.422639369287</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -5208,7 +5207,7 @@
         <v>188.2268981933594</v>
       </c>
       <c r="C121" s="1">
-        <v>135.5292514349042</v>
+        <v>135.5292663252407</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -5219,7 +5218,7 @@
         <v>191.4842681884766</v>
       </c>
       <c r="C122" s="1">
-        <v>137.8746596699762</v>
+        <v>137.8746748179981</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -5227,10 +5226,10 @@
         <v>45125</v>
       </c>
       <c r="B123" s="1">
-        <v>191.2276153564453</v>
+        <v>191.2276306152344</v>
       </c>
       <c r="C123" s="1">
-        <v>137.6898616069059</v>
+        <v>137.6898877214308</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -5238,10 +5237,10 @@
         <v>45126</v>
       </c>
       <c r="B124" s="1">
-        <v>192.5799102783203</v>
+        <v>192.5799255371094</v>
       </c>
       <c r="C124" s="1">
-        <v>138.6635562288758</v>
+        <v>138.6635824503786</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -5249,10 +5248,10 @@
         <v>45127</v>
       </c>
       <c r="B125" s="1">
-        <v>190.6353607177734</v>
+        <v>190.6353759765625</v>
       </c>
       <c r="C125" s="1">
-        <v>137.2634197507819</v>
+        <v>137.2634458184544</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -5260,10 +5259,10 @@
         <v>45128</v>
       </c>
       <c r="B126" s="1">
-        <v>189.4607391357422</v>
+        <v>189.4607543945312</v>
       </c>
       <c r="C126" s="1">
-        <v>136.4176554882882</v>
+        <v>136.4176814630383</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -5271,10 +5270,10 @@
         <v>45131</v>
       </c>
       <c r="B127" s="1">
-        <v>190.2603149414062</v>
+        <v>190.2602996826172</v>
       </c>
       <c r="C127" s="1">
-        <v>136.9933750663466</v>
+        <v>136.9933791307371</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -5282,10 +5281,10 @@
         <v>45132</v>
       </c>
       <c r="B128" s="1">
-        <v>191.1190338134766</v>
+        <v>191.1190490722656</v>
       </c>
       <c r="C128" s="1">
-        <v>137.6116795012694</v>
+        <v>137.6117056072045</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -5293,10 +5292,10 @@
         <v>45133</v>
       </c>
       <c r="B129" s="1">
-        <v>191.9876861572266</v>
+        <v>191.9877014160156</v>
       </c>
       <c r="C129" s="1">
-        <v>138.2371363463621</v>
+        <v>138.237162521015</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -5304,10 +5303,10 @@
         <v>45134</v>
       </c>
       <c r="B130" s="1">
-        <v>190.7241973876953</v>
+        <v>190.7242126464844</v>
       </c>
       <c r="C130" s="1">
-        <v>137.32738493052</v>
+        <v>137.3274110052203</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -5315,10 +5314,10 @@
         <v>45135</v>
       </c>
       <c r="B131" s="1">
-        <v>193.3005218505859</v>
+        <v>193.300537109375</v>
       </c>
       <c r="C131" s="1">
-        <v>139.1824190901453</v>
+        <v>139.1824453686546</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -5329,7 +5328,7 @@
         <v>193.9124908447266</v>
       </c>
       <c r="C132" s="1">
-        <v>139.6230558985575</v>
+        <v>139.6230712386723</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -5337,10 +5336,10 @@
         <v>45139</v>
       </c>
       <c r="B133" s="1">
-        <v>193.0833435058594</v>
+        <v>193.0833587646484</v>
       </c>
       <c r="C133" s="1">
-        <v>139.026043892067</v>
+        <v>139.0260701533956</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -5348,10 +5347,10 @@
         <v>45140</v>
       </c>
       <c r="B134" s="1">
-        <v>190.0924835205078</v>
+        <v>190.0924530029297</v>
       </c>
       <c r="C134" s="1">
-        <v>136.8725311962093</v>
+        <v>136.8725242605165</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -5362,7 +5361,7 @@
         <v>188.7006988525391</v>
       </c>
       <c r="C135" s="1">
-        <v>135.8704027224424</v>
+        <v>135.8704176502605</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -5373,7 +5372,7 @@
         <v>179.6392974853516</v>
       </c>
       <c r="C136" s="1">
-        <v>129.3459104419366</v>
+        <v>129.3459246529213</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -5381,10 +5380,10 @@
         <v>45145</v>
       </c>
       <c r="B137" s="1">
-        <v>176.5398406982422</v>
+        <v>176.5398559570312</v>
       </c>
       <c r="C137" s="1">
-        <v>127.1142046536371</v>
+        <v>127.1142296062351</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -5392,10 +5391,10 @@
         <v>45146</v>
       </c>
       <c r="B138" s="1">
-        <v>177.4775848388672</v>
+        <v>177.4775543212891</v>
       </c>
       <c r="C138" s="1">
-        <v>127.7894097525695</v>
+        <v>127.7894018189317</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -5406,7 +5405,7 @@
         <v>175.8883666992188</v>
       </c>
       <c r="C139" s="1">
-        <v>126.6451230066227</v>
+        <v>126.6451369208772</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -5414,10 +5413,10 @@
         <v>45148</v>
       </c>
       <c r="B140" s="1">
-        <v>175.6711883544922</v>
+        <v>175.6712188720703</v>
       </c>
       <c r="C140" s="1">
-        <v>126.4887478085444</v>
+        <v>126.4887836792309</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -5425,10 +5424,10 @@
         <v>45149</v>
       </c>
       <c r="B141" s="1">
-        <v>175.7305145263672</v>
+        <v>175.7304992675781</v>
       </c>
       <c r="C141" s="1">
-        <v>126.5314645070709</v>
+        <v>126.5314674220316</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -5436,10 +5435,10 @@
         <v>45152</v>
       </c>
       <c r="B142" s="1">
-        <v>177.3811492919922</v>
+        <v>177.3811645507812</v>
       </c>
       <c r="C142" s="1">
-        <v>127.7199731438534</v>
+        <v>127.719998163006</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -5450,7 +5449,7 @@
         <v>175.3944549560547</v>
       </c>
       <c r="C143" s="1">
-        <v>126.2894911098618</v>
+        <v>126.2895049850436</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -5458,10 +5457,10 @@
         <v>45154</v>
       </c>
       <c r="B144" s="1">
-        <v>174.5246276855469</v>
+        <v>174.5246429443359</v>
       </c>
       <c r="C144" s="1">
-        <v>125.6631882807704</v>
+        <v>125.663213073948</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -5472,7 +5471,7 @@
         <v>171.9844055175781</v>
       </c>
       <c r="C145" s="1">
-        <v>123.8341489021929</v>
+        <v>123.8341625076111</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -5480,10 +5479,10 @@
         <v>45156</v>
       </c>
       <c r="B146" s="1">
-        <v>172.46875</v>
+        <v>172.4687347412109</v>
       </c>
       <c r="C146" s="1">
-        <v>124.1828920721082</v>
+        <v>124.1828947290357</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -5491,10 +5490,10 @@
         <v>45159</v>
       </c>
       <c r="B147" s="1">
-        <v>173.8031005859375</v>
+        <v>173.8030853271484</v>
       </c>
       <c r="C147" s="1">
-        <v>125.1436662111904</v>
+        <v>125.1436689736763</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -5502,10 +5501,10 @@
         <v>45160</v>
       </c>
       <c r="B148" s="1">
-        <v>175.1770172119141</v>
+        <v>175.1769866943359</v>
       </c>
       <c r="C148" s="1">
-        <v>126.1329291360954</v>
+        <v>126.1329210204634</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -5513,10 +5512,10 @@
         <v>45161</v>
       </c>
       <c r="B149" s="1">
-        <v>179.0219573974609</v>
+        <v>179.0219421386719</v>
       </c>
       <c r="C149" s="1">
-        <v>128.9014062781022</v>
+        <v>128.9014094534437</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -5524,10 +5523,10 @@
         <v>45162</v>
       </c>
       <c r="B150" s="1">
-        <v>174.3368682861328</v>
+        <v>174.3368377685547</v>
       </c>
       <c r="C150" s="1">
-        <v>125.5279956430725</v>
+        <v>125.5279874609776</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -5535,10 +5534,10 @@
         <v>45163</v>
       </c>
       <c r="B151" s="1">
-        <v>176.5409851074219</v>
+        <v>176.5410308837891</v>
       </c>
       <c r="C151" s="1">
-        <v>127.1150286640254</v>
+        <v>127.1150755903266</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -5546,10 +5545,10 @@
         <v>45166</v>
       </c>
       <c r="B152" s="1">
-        <v>178.1026916503906</v>
+        <v>178.1027221679688</v>
       </c>
       <c r="C152" s="1">
-        <v>128.2395062002387</v>
+        <v>128.2395422632777</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -5560,7 +5559,7 @@
         <v>181.9871826171875</v>
       </c>
       <c r="C153" s="1">
-        <v>131.0364611412632</v>
+        <v>131.0364755379854</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -5571,7 +5570,7 @@
         <v>185.4762878417969</v>
       </c>
       <c r="C154" s="1">
-        <v>133.5487259865519</v>
+        <v>133.5487406592919</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -5579,10 +5578,10 @@
         <v>45169</v>
       </c>
       <c r="B155" s="1">
-        <v>185.6937561035156</v>
+        <v>185.6937255859375</v>
       </c>
       <c r="C155" s="1">
-        <v>133.7053099339286</v>
+        <v>133.7053026502594</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -5593,7 +5592,7 @@
         <v>187.2653198242188</v>
       </c>
       <c r="C156" s="1">
-        <v>134.8368849462861</v>
+        <v>134.8368997605536</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -5604,7 +5603,7 @@
         <v>187.5025329589844</v>
       </c>
       <c r="C157" s="1">
-        <v>135.0076858195613</v>
+        <v>135.0077006525943</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -5612,10 +5611,10 @@
         <v>45175</v>
       </c>
       <c r="B158" s="1">
-        <v>180.7911834716797</v>
+        <v>180.7911987304688</v>
       </c>
       <c r="C158" s="1">
-        <v>130.1753043647171</v>
+        <v>130.1753296536321</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -5626,7 +5625,7 @@
         <v>175.503173828125</v>
       </c>
       <c r="C159" s="1">
-        <v>126.367772096745</v>
+        <v>126.3677859805274</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -5637,7 +5636,7 @@
         <v>176.1159820556641</v>
       </c>
       <c r="C160" s="1">
-        <v>126.8090131794419</v>
+        <v>126.8090271117026</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -5645,10 +5644,10 @@
         <v>45180</v>
       </c>
       <c r="B161" s="1">
-        <v>177.2823181152344</v>
+        <v>177.2822875976562</v>
       </c>
       <c r="C161" s="1">
-        <v>127.6488116067247</v>
+        <v>127.6488036576397</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -5656,10 +5655,10 @@
         <v>45181</v>
       </c>
       <c r="B162" s="1">
-        <v>174.2577667236328</v>
+        <v>174.2577972412109</v>
       </c>
       <c r="C162" s="1">
-        <v>125.4710400450371</v>
+        <v>125.4710758039101</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -5667,10 +5666,10 @@
         <v>45182</v>
       </c>
       <c r="B163" s="1">
-        <v>172.1920013427734</v>
+        <v>172.1919708251953</v>
       </c>
       <c r="C163" s="1">
-        <v>123.9836243866204</v>
+        <v>123.9836160348484</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -5681,7 +5680,7 @@
         <v>173.7042388916016</v>
       </c>
       <c r="C164" s="1">
-        <v>125.0724827004512</v>
+        <v>125.0724964419228</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -5692,7 +5691,7 @@
         <v>172.9826965332031</v>
       </c>
       <c r="C165" s="1">
-        <v>124.552949644066</v>
+        <v>124.5529633284574</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -5700,10 +5699,10 @@
         <v>45187</v>
       </c>
       <c r="B166" s="1">
-        <v>175.9084167480469</v>
+        <v>175.9084320068359</v>
       </c>
       <c r="C166" s="1">
-        <v>126.6595596686248</v>
+        <v>126.6595845712717</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -5711,10 +5710,10 @@
         <v>45188</v>
       </c>
       <c r="B167" s="1">
-        <v>176.9956970214844</v>
+        <v>176.9956817626953</v>
       </c>
       <c r="C167" s="1">
-        <v>127.4424354582877</v>
+        <v>127.4424384733349</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -5722,10 +5721,10 @@
         <v>45189</v>
       </c>
       <c r="B168" s="1">
-        <v>173.4571685791016</v>
+        <v>173.4571380615234</v>
       </c>
       <c r="C168" s="1">
-        <v>124.8945843510319</v>
+        <v>124.8945760993453</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -5733,10 +5732,10 @@
         <v>45190</v>
       </c>
       <c r="B169" s="1">
-        <v>171.9152069091797</v>
+        <v>171.9151916503906</v>
       </c>
       <c r="C169" s="1">
-        <v>123.7843237407171</v>
+        <v>123.7843263538547</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -5744,10 +5743,10 @@
         <v>45191</v>
       </c>
       <c r="B170" s="1">
-        <v>172.7652282714844</v>
+        <v>172.7652130126953</v>
       </c>
       <c r="C170" s="1">
-        <v>124.3963656966892</v>
+        <v>124.3963683770707</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -5755,10 +5754,10 @@
         <v>45194</v>
       </c>
       <c r="B171" s="1">
-        <v>174.0402984619141</v>
+        <v>174.0403137207031</v>
       </c>
       <c r="C171" s="1">
-        <v>125.3144560976604</v>
+        <v>125.3144808525234</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -5766,10 +5765,10 @@
         <v>45195</v>
       </c>
       <c r="B172" s="1">
-        <v>169.9680328369141</v>
+        <v>169.9680480957031</v>
       </c>
       <c r="C172" s="1">
-        <v>122.3822975321328</v>
+        <v>122.3823219648453</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -5780,7 +5779,7 @@
         <v>168.4557647705078</v>
       </c>
       <c r="C173" s="1">
-        <v>121.2934172446917</v>
+        <v>121.2934305709646</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -5788,10 +5787,10 @@
         <v>45197</v>
       </c>
       <c r="B174" s="1">
-        <v>168.7127532958984</v>
+        <v>168.7127380371094</v>
       </c>
       <c r="C174" s="1">
-        <v>121.4784570174757</v>
+        <v>121.4784593772722</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -5799,10 +5798,10 @@
         <v>45198</v>
       </c>
       <c r="B175" s="1">
-        <v>169.2267303466797</v>
+        <v>169.2267456054688</v>
       </c>
       <c r="C175" s="1">
-        <v>121.8485365630439</v>
+        <v>121.848560937113</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -5810,10 +5809,10 @@
         <v>45201</v>
       </c>
       <c r="B176" s="1">
-        <v>171.7373199462891</v>
+        <v>171.7373046875</v>
       </c>
       <c r="C176" s="1">
-        <v>123.6562395659684</v>
+        <v>123.6562421650337</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -5821,10 +5820,10 @@
         <v>45202</v>
       </c>
       <c r="B177" s="1">
-        <v>170.4029235839844</v>
+        <v>170.4029083251953</v>
       </c>
       <c r="C177" s="1">
-        <v>122.6954324664707</v>
+        <v>122.695434959974</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -5832,10 +5831,10 @@
         <v>45203</v>
       </c>
       <c r="B178" s="1">
-        <v>171.6483306884766</v>
+        <v>171.6483764648438</v>
       </c>
       <c r="C178" s="1">
-        <v>123.5921645181786</v>
+        <v>123.5922110574296</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -5846,7 +5845,7 @@
         <v>172.8838653564453</v>
       </c>
       <c r="C179" s="1">
-        <v>124.4817881069372</v>
+        <v>124.4818017835102</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -5854,10 +5853,10 @@
         <v>45205</v>
       </c>
       <c r="B180" s="1">
-        <v>175.4339904785156</v>
+        <v>175.4339752197266</v>
       </c>
       <c r="C180" s="1">
-        <v>126.3179579220743</v>
+        <v>126.3179608135774</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -5865,10 +5864,10 @@
         <v>45208</v>
       </c>
       <c r="B181" s="1">
-        <v>176.9165802001953</v>
+        <v>176.9166259765625</v>
       </c>
       <c r="C181" s="1">
-        <v>127.3854688734471</v>
+        <v>127.385515829461</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -5879,7 +5878,7 @@
         <v>176.3235626220703</v>
       </c>
       <c r="C182" s="1">
-        <v>126.9584776770642</v>
+        <v>126.9584916257463</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -5887,10 +5886,10 @@
         <v>45210</v>
       </c>
       <c r="B183" s="1">
-        <v>177.7172393798828</v>
+        <v>177.7172088623047</v>
       </c>
       <c r="C183" s="1">
-        <v>127.9619685146729</v>
+        <v>127.9619605999939</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -5898,10 +5897,10 @@
         <v>45211</v>
       </c>
       <c r="B184" s="1">
-        <v>178.6166839599609</v>
+        <v>178.6166687011719</v>
       </c>
       <c r="C184" s="1">
-        <v>128.609596732612</v>
+        <v>128.6095998758931</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -5909,10 +5908,10 @@
         <v>45212</v>
       </c>
       <c r="B185" s="1">
-        <v>176.7782287597656</v>
+        <v>176.7782440185547</v>
       </c>
       <c r="C185" s="1">
-        <v>127.2858515109109</v>
+        <v>127.2858764823674</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -5920,10 +5919,10 @@
         <v>45215</v>
       </c>
       <c r="B186" s="1">
-        <v>176.6497344970703</v>
+        <v>176.6497192382812</v>
       </c>
       <c r="C186" s="1">
-        <v>127.1933316245189</v>
+        <v>127.1933346121976</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -5931,10 +5930,10 @@
         <v>45216</v>
       </c>
       <c r="B187" s="1">
-        <v>175.0979156494141</v>
+        <v>175.097900390625</v>
       </c>
       <c r="C187" s="1">
-        <v>126.07597353806</v>
+        <v>126.0759764029767</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -5942,10 +5941,10 @@
         <v>45217</v>
       </c>
       <c r="B188" s="1">
-        <v>173.8031005859375</v>
+        <v>173.8030853271484</v>
       </c>
       <c r="C188" s="1">
-        <v>125.1436662111904</v>
+        <v>125.1436689736763</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -5956,7 +5955,7 @@
         <v>173.427490234375</v>
       </c>
       <c r="C189" s="1">
-        <v>124.8732150149635</v>
+        <v>124.8732287345418</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -5967,7 +5966,7 @@
         <v>170.8773803710938</v>
       </c>
       <c r="C190" s="1">
-        <v>123.0370561866315</v>
+        <v>123.0370697044747</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -5975,10 +5974,10 @@
         <v>45222</v>
       </c>
       <c r="B191" s="1">
-        <v>170.9960021972656</v>
+        <v>170.9959869384766</v>
       </c>
       <c r="C191" s="1">
-        <v>123.1224676100743</v>
+        <v>123.1224701504951</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -5986,10 +5985,10 @@
         <v>45223</v>
       </c>
       <c r="B192" s="1">
-        <v>171.4308929443359</v>
+        <v>171.4308776855469</v>
       </c>
       <c r="C192" s="1">
-        <v>123.4356025444122</v>
+        <v>123.4356051192365</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -5997,10 +5996,10 @@
         <v>45224</v>
       </c>
       <c r="B193" s="1">
-        <v>169.1180114746094</v>
+        <v>169.1179962158203</v>
       </c>
       <c r="C193" s="1">
-        <v>121.7702555761607</v>
+        <v>121.7702579680165</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -6011,7 +6010,7 @@
         <v>164.9567718505859</v>
       </c>
       <c r="C194" s="1">
-        <v>118.7740329496485</v>
+        <v>118.7740459991215</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -6019,10 +6018,10 @@
         <v>45226</v>
       </c>
       <c r="B195" s="1">
-        <v>166.2713623046875</v>
+        <v>166.2713470458984</v>
       </c>
       <c r="C195" s="1">
-        <v>119.720579176027</v>
+        <v>119.7205813426888</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -6033,7 +6032,7 @@
         <v>168.3173828125</v>
       </c>
       <c r="C196" s="1">
-        <v>121.1937779085452</v>
+        <v>121.1937912238709</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -6041,10 +6040,10 @@
         <v>45230</v>
       </c>
       <c r="B197" s="1">
-        <v>168.7918395996094</v>
+        <v>168.7918090820312</v>
       </c>
       <c r="C197" s="1">
-        <v>121.535401628706</v>
+        <v>121.5353930079525</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -6052,10 +6051,10 @@
         <v>45231</v>
       </c>
       <c r="B198" s="1">
-        <v>171.9547576904297</v>
+        <v>171.9547729492188</v>
       </c>
       <c r="C198" s="1">
-        <v>123.8128015397348</v>
+        <v>123.812826129614</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -6063,10 +6062,10 @@
         <v>45232</v>
       </c>
       <c r="B199" s="1">
-        <v>175.5130615234375</v>
+        <v>175.5130462646484</v>
       </c>
       <c r="C199" s="1">
-        <v>126.3748915464994</v>
+        <v>126.3748944442577</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -6074,10 +6073,10 @@
         <v>45233</v>
       </c>
       <c r="B200" s="1">
-        <v>174.6036834716797</v>
+        <v>174.6037139892578</v>
       </c>
       <c r="C200" s="1">
-        <v>125.7201109183903</v>
+        <v>125.7201467046283</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -6088,7 +6087,7 @@
         <v>177.1538238525391</v>
       </c>
       <c r="C201" s="1">
-        <v>127.5562917203326</v>
+        <v>127.5563057346954</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -6096,10 +6095,10 @@
         <v>45237</v>
       </c>
       <c r="B202" s="1">
-        <v>179.7138061523438</v>
+        <v>179.7138366699219</v>
       </c>
       <c r="C202" s="1">
-        <v>129.3995590116138</v>
+        <v>129.3995952021056</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -6110,7 +6109,7 @@
         <v>180.7714233398438</v>
       </c>
       <c r="C203" s="1">
-        <v>130.1610764520134</v>
+        <v>130.1610907525589</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -6121,7 +6120,7 @@
         <v>180.2969970703125</v>
       </c>
       <c r="C204" s="1">
-        <v>129.819474705463</v>
+        <v>129.8194889684773</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -6129,10 +6128,10 @@
         <v>45240</v>
       </c>
       <c r="B205" s="1">
-        <v>184.4835052490234</v>
+        <v>184.4834899902344</v>
       </c>
       <c r="C205" s="1">
-        <v>132.8338914813476</v>
+        <v>132.8338950887437</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -6140,10 +6139,10 @@
         <v>45243</v>
       </c>
       <c r="B206" s="1">
-        <v>182.8999633789062</v>
+        <v>182.8999328613281</v>
       </c>
       <c r="C206" s="1">
-        <v>131.6936918269266</v>
+        <v>131.6936843222448</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -6151,10 +6150,10 @@
         <v>45244</v>
       </c>
       <c r="B207" s="1">
-        <v>185.5128173828125</v>
+        <v>185.5128021240234</v>
       </c>
       <c r="C207" s="1">
-        <v>133.5750283981447</v>
+        <v>133.575032086968</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -6162,10 +6161,10 @@
         <v>45245</v>
       </c>
       <c r="B208" s="1">
-        <v>186.0769348144531</v>
+        <v>186.0769195556641</v>
       </c>
       <c r="C208" s="1">
-        <v>133.9812105855231</v>
+        <v>133.9812143189729</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -6173,10 +6172,10 @@
         <v>45246</v>
       </c>
       <c r="B209" s="1">
-        <v>187.7594604492188</v>
+        <v>187.7594909667969</v>
       </c>
       <c r="C209" s="1">
-        <v>135.1926816451247</v>
+        <v>135.1927184720956</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -6184,10 +6183,10 @@
         <v>45247</v>
       </c>
       <c r="B210" s="1">
-        <v>187.7396545410156</v>
+        <v>187.7396697998047</v>
       </c>
       <c r="C210" s="1">
-        <v>135.1784207720054</v>
+        <v>135.1784466106032</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -6195,10 +6194,10 @@
         <v>45250</v>
       </c>
       <c r="B211" s="1">
-        <v>189.4815826416016</v>
+        <v>189.4815673828125</v>
       </c>
       <c r="C211" s="1">
-        <v>136.4326634641594</v>
+        <v>136.4326674669456</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -6206,10 +6205,10 @@
         <v>45251</v>
       </c>
       <c r="B212" s="1">
-        <v>188.6799011230469</v>
+        <v>188.6798858642578</v>
       </c>
       <c r="C212" s="1">
-        <v>135.8554277069867</v>
+        <v>135.8554316463532</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -6217,10 +6216,10 @@
         <v>45252</v>
       </c>
       <c r="B213" s="1">
-        <v>189.3429870605469</v>
+        <v>189.3430023193359</v>
       </c>
       <c r="C213" s="1">
-        <v>136.3328703127405</v>
+        <v>136.3328962781754</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -6228,10 +6227,10 @@
         <v>45254</v>
       </c>
       <c r="B214" s="1">
-        <v>188.0167846679688</v>
+        <v>188.0167694091797</v>
       </c>
       <c r="C214" s="1">
-        <v>135.3779631276226</v>
+        <v>135.3779670145309</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -6242,7 +6241,7 @@
         <v>187.8386383056641</v>
       </c>
       <c r="C215" s="1">
-        <v>135.249692177186</v>
+        <v>135.2497070368078</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -6250,10 +6249,10 @@
         <v>45258</v>
       </c>
       <c r="B216" s="1">
-        <v>188.4423522949219</v>
+        <v>188.4423675537109</v>
       </c>
       <c r="C216" s="1">
-        <v>135.6843851239976</v>
+        <v>135.6844110181847</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -6264,7 +6263,7 @@
         <v>187.4229431152344</v>
       </c>
       <c r="C217" s="1">
-        <v>134.9503786437602</v>
+        <v>134.950393470497</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -6272,10 +6271,10 @@
         <v>45260</v>
       </c>
       <c r="B218" s="1">
-        <v>187.9969940185547</v>
+        <v>187.9969787597656</v>
       </c>
       <c r="C218" s="1">
-        <v>135.3637132413086</v>
+        <v>135.3637171266513</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -6283,10 +6282,10 @@
         <v>45261</v>
       </c>
       <c r="B219" s="1">
-        <v>189.2737121582031</v>
+        <v>189.2737579345703</v>
       </c>
       <c r="C219" s="1">
-        <v>136.2829902172388</v>
+        <v>136.2830381508062</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -6297,7 +6296,7 @@
         <v>187.4823303222656</v>
       </c>
       <c r="C220" s="1">
-        <v>134.9931392895075</v>
+        <v>134.9931541209423</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -6308,7 +6307,7 @@
         <v>191.4312896728516</v>
       </c>
       <c r="C221" s="1">
-        <v>137.836513482403</v>
+        <v>137.8365286262339</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -6316,10 +6315,10 @@
         <v>45266</v>
       </c>
       <c r="B222" s="1">
-        <v>190.3426208496094</v>
+        <v>190.3426361083984</v>
       </c>
       <c r="C222" s="1">
-        <v>137.0526378934691</v>
+        <v>137.0526639379834</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -6327,10 +6326,10 @@
         <v>45267</v>
       </c>
       <c r="B223" s="1">
-        <v>192.2725830078125</v>
+        <v>192.2725982666016</v>
       </c>
       <c r="C223" s="1">
-        <v>138.4422709858142</v>
+        <v>138.4422971830048</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -6341,7 +6340,7 @@
         <v>193.6977844238281</v>
       </c>
       <c r="C224" s="1">
-        <v>139.4684605629178</v>
+        <v>139.4684758860475</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -6349,10 +6348,10 @@
         <v>45271</v>
       </c>
       <c r="B225" s="1">
-        <v>191.1938018798828</v>
+        <v>191.1937866210938</v>
       </c>
       <c r="C225" s="1">
-        <v>137.6655148466346</v>
+        <v>137.6655189848718</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -6360,10 +6359,10 @@
         <v>45272</v>
       </c>
       <c r="B226" s="1">
-        <v>192.7080688476562</v>
+        <v>192.7080535888672</v>
       </c>
       <c r="C226" s="1">
-        <v>138.755834405554</v>
+        <v>138.7558386635825</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -6371,10 +6370,10 @@
         <v>45273</v>
       </c>
       <c r="B227" s="1">
-        <v>195.9246673583984</v>
+        <v>195.9246520996094</v>
       </c>
       <c r="C227" s="1">
-        <v>141.0718858971941</v>
+        <v>141.0718904096826</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -6382,10 +6381,10 @@
         <v>45274</v>
       </c>
       <c r="B228" s="1">
-        <v>196.0731048583984</v>
+        <v>196.0730895996094</v>
       </c>
       <c r="C228" s="1">
-        <v>141.1787655379519</v>
+        <v>141.1787700621831</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -6393,10 +6392,10 @@
         <v>45275</v>
       </c>
       <c r="B229" s="1">
-        <v>195.5386657714844</v>
+        <v>195.5386505126953</v>
       </c>
       <c r="C229" s="1">
-        <v>140.7939526866419</v>
+        <v>140.7939571685945</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -6407,7 +6406,7 @@
         <v>193.8759307861328</v>
       </c>
       <c r="C230" s="1">
-        <v>139.5967315133544</v>
+        <v>139.596746850577</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -6418,7 +6417,7 @@
         <v>194.9151306152344</v>
       </c>
       <c r="C231" s="1">
-        <v>140.3449878799059</v>
+        <v>140.345003299338</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -6426,10 +6425,10 @@
         <v>45280</v>
       </c>
       <c r="B232" s="1">
-        <v>192.8268127441406</v>
+        <v>192.8268280029297</v>
       </c>
       <c r="C232" s="1">
-        <v>138.8413337234382</v>
+        <v>138.8413599644731</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -6440,7 +6439,7 @@
         <v>192.6783447265625</v>
       </c>
       <c r="C233" s="1">
-        <v>138.73443210907</v>
+        <v>138.7344473515534</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -6451,7 +6450,7 @@
         <v>191.6094818115234</v>
       </c>
       <c r="C234" s="1">
-        <v>137.9648173932552</v>
+        <v>137.9648325511826</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -6462,7 +6461,7 @@
         <v>191.0651245117188</v>
       </c>
       <c r="C235" s="1">
-        <v>137.5728631185805</v>
+        <v>137.5728782334446</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -6470,10 +6469,10 @@
         <v>45287</v>
       </c>
       <c r="B236" s="1">
-        <v>191.1641082763672</v>
+        <v>191.1640930175781</v>
       </c>
       <c r="C236" s="1">
-        <v>137.644134523761</v>
+        <v>137.6441386596492</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -6481,10 +6480,10 @@
         <v>45288</v>
       </c>
       <c r="B237" s="1">
-        <v>191.5896453857422</v>
+        <v>191.5896606445312</v>
       </c>
       <c r="C237" s="1">
-        <v>137.9505345465257</v>
+        <v>137.9505606896902</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -6495,7 +6494,7 @@
         <v>190.5504608154297</v>
       </c>
       <c r="C238" s="1">
-        <v>137.2022891667794</v>
+        <v>137.2023042409292</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -6503,10 +6502,10 @@
         <v>45293</v>
       </c>
       <c r="B239" s="1">
-        <v>183.7313232421875</v>
+        <v>183.7313079833984</v>
       </c>
       <c r="C239" s="1">
-        <v>132.2922969201678</v>
+        <v>132.2923004680599</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -6514,10 +6513,10 @@
         <v>45294</v>
       </c>
       <c r="B240" s="1">
-        <v>182.3555908203125</v>
+        <v>182.3556213378906</v>
       </c>
       <c r="C240" s="1">
-        <v>131.3017265654467</v>
+        <v>131.301762964926</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -6525,10 +6524,10 @@
         <v>45295</v>
       </c>
       <c r="B241" s="1">
-        <v>180.0396728515625</v>
+        <v>180.0396575927734</v>
       </c>
       <c r="C241" s="1">
-        <v>129.634193222965</v>
+        <v>129.6341964788164</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -6536,10 +6535,10 @@
         <v>45296</v>
       </c>
       <c r="B242" s="1">
-        <v>179.3171691894531</v>
+        <v>179.3171539306641</v>
       </c>
       <c r="C242" s="1">
-        <v>129.1139679978536</v>
+        <v>129.1139711965489</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -6547,10 +6546,10 @@
         <v>45299</v>
       </c>
       <c r="B243" s="1">
-        <v>183.6521301269531</v>
+        <v>183.6521148681641</v>
       </c>
       <c r="C243" s="1">
-        <v>132.2352754013013</v>
+        <v>132.2352789429286</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -6561,7 +6560,7 @@
         <v>183.2364501953125</v>
       </c>
       <c r="C244" s="1">
-        <v>131.9359728546807</v>
+        <v>131.9359873502306</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -6572,7 +6571,7 @@
         <v>184.275634765625</v>
       </c>
       <c r="C245" s="1">
-        <v>132.684218234427</v>
+        <v>132.6842328121851</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -6580,10 +6579,10 @@
         <v>45302</v>
       </c>
       <c r="B246" s="1">
-        <v>183.6818084716797</v>
+        <v>183.6818237304688</v>
       </c>
       <c r="C246" s="1">
-        <v>132.2566447373698</v>
+        <v>132.2566702549576</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -6591,10 +6590,10 @@
         <v>45303</v>
       </c>
       <c r="B247" s="1">
-        <v>184.0084228515625</v>
+        <v>184.0084075927734</v>
       </c>
       <c r="C247" s="1">
-        <v>132.4918173021746</v>
+        <v>132.4918208719877</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -6605,7 +6604,7 @@
         <v>181.7419738769531</v>
       </c>
       <c r="C248" s="1">
-        <v>130.8599031820754</v>
+        <v>130.8599175593996</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -6613,10 +6612,10 @@
         <v>45308</v>
       </c>
       <c r="B249" s="1">
-        <v>180.8017272949219</v>
+        <v>180.8017425537109</v>
       </c>
       <c r="C249" s="1">
-        <v>130.1828962470941</v>
+        <v>130.1829215368433</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -6627,7 +6626,7 @@
         <v>186.6905670166016</v>
       </c>
       <c r="C250" s="1">
-        <v>134.4230449556995</v>
+        <v>134.4230597244992</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -6635,10 +6634,10 @@
         <v>45310</v>
       </c>
       <c r="B251" s="1">
-        <v>189.5904388427734</v>
+        <v>189.5904235839844</v>
       </c>
       <c r="C251" s="1">
-        <v>136.5110433322892</v>
+        <v>136.5110473436869</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -6646,10 +6645,10 @@
         <v>45313</v>
       </c>
       <c r="B252" s="1">
-        <v>191.8964691162109</v>
+        <v>191.8964996337891</v>
       </c>
       <c r="C252" s="1">
-        <v>138.1714572250165</v>
+        <v>138.1714943792597</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -6660,7 +6659,7 @@
         <v>193.1732025146484</v>
       </c>
       <c r="C253" s="1">
-        <v>139.0907451877518</v>
+        <v>139.0907604693827</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -6668,10 +6667,10 @@
         <v>45315</v>
       </c>
       <c r="B254" s="1">
-        <v>192.5002136230469</v>
+        <v>192.5002288818359</v>
       </c>
       <c r="C254" s="1">
-        <v>138.6061721454385</v>
+        <v>138.6061983606367</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -6679,10 +6678,10 @@
         <v>45316</v>
       </c>
       <c r="B255" s="1">
-        <v>192.1735992431641</v>
+        <v>192.1736297607422</v>
       </c>
       <c r="C255" s="1">
-        <v>138.3709995806336</v>
+        <v>138.3710367568002</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -6693,7 +6692,7 @@
         <v>190.4415893554688</v>
       </c>
       <c r="C256" s="1">
-        <v>137.1238983118444</v>
+        <v>137.1239133773816</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -6701,10 +6700,10 @@
         <v>45320</v>
       </c>
       <c r="B257" s="1">
-        <v>189.7586822509766</v>
+        <v>189.7586975097656</v>
       </c>
       <c r="C257" s="1">
-        <v>136.6321838461663</v>
+        <v>136.6322098444861</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -6715,7 +6714,7 @@
         <v>186.1066284179688</v>
       </c>
       <c r="C258" s="1">
-        <v>134.0025909083967</v>
+        <v>134.002605631002</v>
       </c>
     </row>
   </sheetData>
@@ -9602,7 +9601,7 @@
         <v>44949</v>
       </c>
       <c r="B2" s="1">
-        <v>236.3760528564453</v>
+        <v>236.3760986328125</v>
       </c>
       <c r="C2" s="1">
         <v>100</v>
@@ -9613,10 +9612,10 @@
         <v>44950</v>
       </c>
       <c r="B3" s="1">
-        <v>235.8498687744141</v>
+        <v>235.8498840332031</v>
       </c>
       <c r="C3" s="1">
-        <v>99.77739535131724</v>
+        <v>99.77738248382431</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9627,7 +9626,7 @@
         <v>234.4564514160156</v>
       </c>
       <c r="C4" s="1">
-        <v>99.18790358954192</v>
+        <v>99.18788438090822</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9635,10 +9634,10 @@
         <v>44952</v>
       </c>
       <c r="B5" s="1">
-        <v>241.657470703125</v>
+        <v>241.6574554443359</v>
       </c>
       <c r="C5" s="1">
-        <v>102.2343286398336</v>
+        <v>102.234302385931</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -9646,10 +9645,10 @@
         <v>44953</v>
       </c>
       <c r="B6" s="1">
-        <v>241.8133850097656</v>
+        <v>241.8133697509766</v>
       </c>
       <c r="C6" s="1">
-        <v>102.3002889199705</v>
+        <v>102.300262653294</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -9657,10 +9656,10 @@
         <v>44956</v>
       </c>
       <c r="B7" s="1">
-        <v>236.5027770996094</v>
+        <v>236.5027465820312</v>
       </c>
       <c r="C7" s="1">
-        <v>100.0536112866057</v>
+        <v>100.0535789997175</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9668,10 +9667,10 @@
         <v>44957</v>
       </c>
       <c r="B8" s="1">
-        <v>241.4723052978516</v>
+        <v>241.4723358154297</v>
       </c>
       <c r="C8" s="1">
-        <v>102.1559935449558</v>
+        <v>102.155986672127</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -9682,7 +9681,7 @@
         <v>246.2859802246094</v>
       </c>
       <c r="C9" s="1">
-        <v>104.1924413443787</v>
+        <v>104.192421166571</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9690,10 +9689,10 @@
         <v>44959</v>
       </c>
       <c r="B10" s="1">
-        <v>257.8328857421875</v>
+        <v>257.8329467773438</v>
       </c>
       <c r="C10" s="1">
-        <v>109.0774139877753</v>
+        <v>109.0774186851533</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9704,7 +9703,7 @@
         <v>251.7427978515625</v>
       </c>
       <c r="C11" s="1">
-        <v>106.5009736855407</v>
+        <v>106.5009530606649</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9715,7 +9714,7 @@
         <v>250.2031555175781</v>
       </c>
       <c r="C12" s="1">
-        <v>105.8496207606657</v>
+        <v>105.8496002619303</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9723,10 +9722,10 @@
         <v>44964</v>
       </c>
       <c r="B13" s="1">
-        <v>260.7171936035156</v>
+        <v>260.7172241210938</v>
       </c>
       <c r="C13" s="1">
-        <v>110.2976339831908</v>
+        <v>110.2976255336597</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9737,7 +9736,7 @@
         <v>259.9084777832031</v>
       </c>
       <c r="C14" s="1">
-        <v>109.9555029548824</v>
+        <v>109.9554816610058</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9745,10 +9744,10 @@
         <v>44966</v>
       </c>
       <c r="B15" s="1">
-        <v>256.8780212402344</v>
+        <v>256.8779907226562</v>
       </c>
       <c r="C15" s="1">
-        <v>108.6734540728795</v>
+        <v>108.6734201166809</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9756,10 +9755,10 @@
         <v>44967</v>
       </c>
       <c r="B16" s="1">
-        <v>256.3712768554688</v>
+        <v>256.3713073730469</v>
       </c>
       <c r="C16" s="1">
-        <v>108.459073479481</v>
+        <v>108.4590653860038</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9770,7 +9769,7 @@
         <v>264.381103515625</v>
       </c>
       <c r="C17" s="1">
-        <v>111.8476682898955</v>
+        <v>111.847646629584</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9778,10 +9777,10 @@
         <v>44971</v>
       </c>
       <c r="B18" s="1">
-        <v>265.2093811035156</v>
+        <v>265.2093200683594</v>
       </c>
       <c r="C18" s="1">
-        <v>112.1980750159075</v>
+        <v>112.1980274665318</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9792,7 +9791,7 @@
         <v>263.0895385742188</v>
       </c>
       <c r="C19" s="1">
-        <v>111.3012656717798</v>
+        <v>111.301244117284</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9800,10 +9799,10 @@
         <v>44973</v>
       </c>
       <c r="B20" s="1">
-        <v>256.0853881835938</v>
+        <v>256.0854187011719</v>
       </c>
       <c r="C20" s="1">
-        <v>108.3381269333227</v>
+        <v>108.3381188632679</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9811,10 +9810,10 @@
         <v>44974</v>
       </c>
       <c r="B21" s="1">
-        <v>252.0899963378906</v>
+        <v>252.0900115966797</v>
       </c>
       <c r="C21" s="1">
-        <v>106.6478576368261</v>
+        <v>106.6478434388061</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9822,10 +9821,10 @@
         <v>44978</v>
       </c>
       <c r="B22" s="1">
-        <v>246.8246917724609</v>
+        <v>246.82470703125</v>
       </c>
       <c r="C22" s="1">
-        <v>104.420345796349</v>
+        <v>104.4203320297068</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9833,10 +9832,10 @@
         <v>44979</v>
       </c>
       <c r="B23" s="1">
-        <v>245.6915283203125</v>
+        <v>245.6915435791016</v>
       </c>
       <c r="C23" s="1">
-        <v>103.9409556726648</v>
+        <v>103.9409419988608</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9847,7 +9846,7 @@
         <v>248.8761138916016</v>
       </c>
       <c r="C24" s="1">
-        <v>105.2882095644214</v>
+        <v>105.2881891744083</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9855,10 +9854,10 @@
         <v>44981</v>
       </c>
       <c r="B25" s="1">
-        <v>243.4544982910156</v>
+        <v>243.4545288085938</v>
       </c>
       <c r="C25" s="1">
-        <v>102.9945696059445</v>
+        <v>102.9945625707178</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9866,10 +9865,10 @@
         <v>44984</v>
       </c>
       <c r="B26" s="1">
-        <v>244.3727874755859</v>
+        <v>244.3727722167969</v>
       </c>
       <c r="C26" s="1">
-        <v>103.3830561609374</v>
+        <v>103.3830296845733</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9877,10 +9876,10 @@
         <v>44985</v>
       </c>
       <c r="B27" s="1">
-        <v>243.6498718261719</v>
+        <v>243.6498565673828</v>
       </c>
       <c r="C27" s="1">
-        <v>103.0772232981418</v>
+        <v>103.0771968810051</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9891,7 +9890,7 @@
         <v>240.5727691650391</v>
       </c>
       <c r="C28" s="1">
-        <v>101.7754405566381</v>
+        <v>101.7754208469045</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9899,10 +9898,10 @@
         <v>44987</v>
       </c>
       <c r="B29" s="1">
-        <v>245.3008117675781</v>
+        <v>245.3007965087891</v>
       </c>
       <c r="C29" s="1">
-        <v>103.7756611988749</v>
+        <v>103.7756346464793</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -9910,10 +9909,10 @@
         <v>44988</v>
       </c>
       <c r="B30" s="1">
-        <v>249.3840942382812</v>
+        <v>249.3840789794922</v>
       </c>
       <c r="C30" s="1">
-        <v>105.503113037316</v>
+        <v>105.5030861503837</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9921,10 +9920,10 @@
         <v>44991</v>
       </c>
       <c r="B31" s="1">
-        <v>250.9275512695312</v>
+        <v>250.9275817871094</v>
       </c>
       <c r="C31" s="1">
-        <v>106.1560797877961</v>
+        <v>106.1560721403145</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -9932,10 +9931,10 @@
         <v>44992</v>
       </c>
       <c r="B32" s="1">
-        <v>248.2704315185547</v>
+        <v>248.2704620361328</v>
       </c>
       <c r="C32" s="1">
-        <v>105.0319727901257</v>
+        <v>105.0319653603375</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9943,10 +9942,10 @@
         <v>44993</v>
       </c>
       <c r="B33" s="1">
-        <v>247.8308410644531</v>
+        <v>247.8308563232422</v>
       </c>
       <c r="C33" s="1">
-        <v>104.8460019826816</v>
+        <v>104.8459881336072</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -9954,10 +9953,10 @@
         <v>44994</v>
       </c>
       <c r="B34" s="1">
-        <v>246.4828033447266</v>
+        <v>246.4828186035156</v>
       </c>
       <c r="C34" s="1">
-        <v>104.2757082903061</v>
+        <v>104.2756945516742</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9968,7 +9967,7 @@
         <v>242.8390960693359</v>
       </c>
       <c r="C35" s="1">
-        <v>102.7342208040066</v>
+        <v>102.7342009085965</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -9976,10 +9975,10 @@
         <v>44998</v>
       </c>
       <c r="B36" s="1">
-        <v>248.0457916259766</v>
+        <v>248.0457763671875</v>
       </c>
       <c r="C36" s="1">
-        <v>104.936937827885</v>
+        <v>104.9369110505977</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9987,10 +9986,10 @@
         <v>44999</v>
       </c>
       <c r="B37" s="1">
-        <v>254.7568511962891</v>
+        <v>254.7568817138672</v>
       </c>
       <c r="C37" s="1">
-        <v>107.7760831174411</v>
+        <v>107.7760751562312</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -10001,7 +10000,7 @@
         <v>259.2992553710938</v>
       </c>
       <c r="C38" s="1">
-        <v>109.6977685504251</v>
+        <v>109.697747306461</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -10009,10 +10008,10 @@
         <v>45001</v>
       </c>
       <c r="B39" s="1">
-        <v>269.8103637695312</v>
+        <v>269.8103332519531</v>
       </c>
       <c r="C39" s="1">
-        <v>114.1445423548853</v>
+        <v>114.144507339161</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -10020,10 +10019,10 @@
         <v>45002</v>
       </c>
       <c r="B40" s="1">
-        <v>272.9656066894531</v>
+        <v>272.965576171875</v>
       </c>
       <c r="C40" s="1">
-        <v>115.4793827000865</v>
+        <v>115.4793474258583</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -10031,10 +10030,10 @@
         <v>45005</v>
       </c>
       <c r="B41" s="1">
-        <v>265.9322509765625</v>
+        <v>265.9321899414062</v>
       </c>
       <c r="C41" s="1">
-        <v>112.5038885127958</v>
+        <v>112.5038409041966</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -10042,10 +10041,10 @@
         <v>45006</v>
       </c>
       <c r="B42" s="1">
-        <v>267.4463195800781</v>
+        <v>267.4462890625</v>
       </c>
       <c r="C42" s="1">
-        <v>113.1444223508133</v>
+        <v>113.1443875287713</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -10056,7 +10055,7 @@
         <v>265.9908142089844</v>
       </c>
       <c r="C43" s="1">
-        <v>112.5286639634873</v>
+        <v>112.5286421712948</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -10067,7 +10066,7 @@
         <v>271.2366027832031</v>
       </c>
       <c r="C44" s="1">
-        <v>114.747919472168</v>
+        <v>114.7478972501966</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -10075,10 +10074,10 @@
         <v>45009</v>
       </c>
       <c r="B45" s="1">
-        <v>274.0792846679688</v>
+        <v>274.0792541503906</v>
       </c>
       <c r="C45" s="1">
-        <v>115.9505294025792</v>
+        <v>115.9504940371092</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -10089,7 +10088,7 @@
         <v>269.9861755371094</v>
       </c>
       <c r="C46" s="1">
-        <v>114.218920349379</v>
+        <v>114.2188982298531</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -10097,10 +10096,10 @@
         <v>45013</v>
       </c>
       <c r="B47" s="1">
-        <v>268.8628234863281</v>
+        <v>268.86279296875</v>
       </c>
       <c r="C47" s="1">
-        <v>113.7436809851514</v>
+        <v>113.7436460470576</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -10108,10 +10107,10 @@
         <v>45014</v>
       </c>
       <c r="B48" s="1">
-        <v>274.0206604003906</v>
+        <v>274.0206909179688</v>
       </c>
       <c r="C48" s="1">
-        <v>115.9257281306781</v>
+        <v>115.9257185912157</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -10119,10 +10118,10 @@
         <v>45015</v>
       </c>
       <c r="B49" s="1">
-        <v>277.4787292480469</v>
+        <v>277.478759765625</v>
       </c>
       <c r="C49" s="1">
-        <v>117.3886804077246</v>
+        <v>117.3886705849484</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -10133,7 +10132,7 @@
         <v>281.6304016113281</v>
       </c>
       <c r="C50" s="1">
-        <v>119.1450649116162</v>
+        <v>119.145041838098</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -10141,10 +10140,10 @@
         <v>45019</v>
       </c>
       <c r="B51" s="1">
-        <v>280.585205078125</v>
+        <v>280.5852355957031</v>
       </c>
       <c r="C51" s="1">
-        <v>118.7028896063886</v>
+        <v>118.7028795291039</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -10155,7 +10154,7 @@
         <v>280.5363464355469</v>
       </c>
       <c r="C52" s="1">
-        <v>118.6822197280368</v>
+        <v>118.6821967441527</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -10163,10 +10162,10 @@
         <v>45021</v>
       </c>
       <c r="B53" s="1">
-        <v>277.7620544433594</v>
+        <v>277.7620239257812</v>
       </c>
       <c r="C53" s="1">
-        <v>117.5085424630762</v>
+        <v>117.5085067958829</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -10174,10 +10173,10 @@
         <v>45022</v>
       </c>
       <c r="B54" s="1">
-        <v>284.8540649414062</v>
+        <v>284.8541259765625</v>
       </c>
       <c r="C54" s="1">
-        <v>120.5088508328728</v>
+        <v>120.5088533164497</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -10185,10 +10184,10 @@
         <v>45026</v>
       </c>
       <c r="B55" s="1">
-        <v>282.6951599121094</v>
+        <v>282.6952819824219</v>
       </c>
       <c r="C55" s="1">
-        <v>119.5955159145476</v>
+        <v>119.5955443962047</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -10199,7 +10198,7 @@
         <v>276.2869567871094</v>
       </c>
       <c r="C56" s="1">
-        <v>116.8844954674417</v>
+        <v>116.8844728317031</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -10207,10 +10206,10 @@
         <v>45028</v>
       </c>
       <c r="B57" s="1">
-        <v>276.9317016601562</v>
+        <v>276.931640625</v>
       </c>
       <c r="C57" s="1">
-        <v>117.1572578159349</v>
+        <v>117.1572093061687</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -10218,10 +10217,10 @@
         <v>45029</v>
       </c>
       <c r="B58" s="1">
-        <v>283.1348266601562</v>
+        <v>283.1347961425781</v>
       </c>
       <c r="C58" s="1">
-        <v>119.7815189985037</v>
+        <v>119.781482891128</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -10229,10 +10228,10 @@
         <v>45030</v>
       </c>
       <c r="B59" s="1">
-        <v>279.5204467773438</v>
+        <v>279.5204162597656</v>
       </c>
       <c r="C59" s="1">
-        <v>118.2524386034573</v>
+        <v>118.2524027922018</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -10240,10 +10239,10 @@
         <v>45033</v>
       </c>
       <c r="B60" s="1">
-        <v>282.1188049316406</v>
+        <v>282.1188659667969</v>
       </c>
       <c r="C60" s="1">
-        <v>119.3516862315048</v>
+        <v>119.3516889391771</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -10251,10 +10250,10 @@
         <v>45034</v>
       </c>
       <c r="B61" s="1">
-        <v>281.6987915039062</v>
+        <v>281.6988525390625</v>
       </c>
       <c r="C61" s="1">
-        <v>119.1739975770668</v>
+        <v>119.1740003191501</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -10262,10 +10261,10 @@
         <v>45035</v>
       </c>
       <c r="B62" s="1">
-        <v>281.7769470214844</v>
+        <v>281.7770080566406</v>
       </c>
       <c r="C62" s="1">
-        <v>119.2070616360667</v>
+        <v>119.2070643717468</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -10276,7 +10275,7 @@
         <v>279.4910888671875</v>
       </c>
       <c r="C63" s="1">
-        <v>118.2400186015994</v>
+        <v>118.2399957033515</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -10284,10 +10283,10 @@
         <v>45037</v>
       </c>
       <c r="B64" s="1">
-        <v>279.1492004394531</v>
+        <v>279.1492309570312</v>
       </c>
       <c r="C64" s="1">
-        <v>118.0953810955565</v>
+        <v>118.0953711359213</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -10295,10 +10294,10 @@
         <v>45040</v>
       </c>
       <c r="B65" s="1">
-        <v>275.2514953613281</v>
+        <v>275.2515563964844</v>
       </c>
       <c r="C65" s="1">
-        <v>116.4464386451586</v>
+        <v>116.4464419154583</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -10306,10 +10305,10 @@
         <v>45041</v>
       </c>
       <c r="B66" s="1">
-        <v>269.0484008789062</v>
+        <v>269.0484619140625</v>
       </c>
       <c r="C66" s="1">
-        <v>113.8221903731946</v>
+        <v>113.8221941517037</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -10317,10 +10316,10 @@
         <v>45042</v>
       </c>
       <c r="B67" s="1">
-        <v>288.536865234375</v>
+        <v>288.5368957519531</v>
       </c>
       <c r="C67" s="1">
-        <v>122.0668768039746</v>
+        <v>122.0668660752234</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -10328,10 +10327,10 @@
         <v>45043</v>
       </c>
       <c r="B68" s="1">
-        <v>297.7780151367188</v>
+        <v>297.7780456542969</v>
       </c>
       <c r="C68" s="1">
-        <v>125.9763886985471</v>
+        <v>125.9763772126836</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -10342,7 +10341,7 @@
         <v>300.1517944335938</v>
       </c>
       <c r="C69" s="1">
-        <v>126.9806271855637</v>
+        <v>126.9806025946179</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -10350,10 +10349,10 @@
         <v>45047</v>
       </c>
       <c r="B70" s="1">
-        <v>298.4911804199219</v>
+        <v>298.4911193847656</v>
       </c>
       <c r="C70" s="1">
-        <v>126.2780966230957</v>
+        <v>126.2780463469967</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -10361,10 +10360,10 @@
         <v>45048</v>
       </c>
       <c r="B71" s="1">
-        <v>298.3446655273438</v>
+        <v>298.3446044921875</v>
       </c>
       <c r="C71" s="1">
-        <v>126.2161128092501</v>
+        <v>126.2160625451548</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -10372,10 +10371,10 @@
         <v>45049</v>
       </c>
       <c r="B72" s="1">
-        <v>297.3580322265625</v>
+        <v>297.3579406738281</v>
       </c>
       <c r="C72" s="1">
-        <v>125.7987129547139</v>
+        <v>125.7986498608495</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -10383,10 +10382,10 @@
         <v>45050</v>
       </c>
       <c r="B73" s="1">
-        <v>298.3446655273438</v>
+        <v>298.3446044921875</v>
       </c>
       <c r="C73" s="1">
-        <v>126.2161128092501</v>
+        <v>126.2160625451548</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -10394,10 +10393,10 @@
         <v>45051</v>
       </c>
       <c r="B74" s="1">
-        <v>303.4633483886719</v>
+        <v>303.4634094238281</v>
       </c>
       <c r="C74" s="1">
-        <v>128.3815956487647</v>
+        <v>128.3815966077134</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -10405,10 +10404,10 @@
         <v>45054</v>
       </c>
       <c r="B75" s="1">
-        <v>301.5096740722656</v>
+        <v>301.5096435546875</v>
       </c>
       <c r="C75" s="1">
-        <v>127.5550845480007</v>
+        <v>127.5550469352037</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -10416,10 +10415,10 @@
         <v>45055</v>
       </c>
       <c r="B76" s="1">
-        <v>299.8978271484375</v>
+        <v>299.8977966308594</v>
       </c>
       <c r="C76" s="1">
-        <v>126.87318513207</v>
+        <v>126.873147651329</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -10427,10 +10426,10 @@
         <v>45056</v>
       </c>
       <c r="B77" s="1">
-        <v>305.0849914550781</v>
+        <v>305.0849609375</v>
       </c>
       <c r="C77" s="1">
-        <v>129.0676393688496</v>
+        <v>129.0676014631327</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -10438,10 +10437,10 @@
         <v>45057</v>
       </c>
       <c r="B78" s="1">
-        <v>302.9358520507812</v>
+        <v>302.9359130859375</v>
       </c>
       <c r="C78" s="1">
-        <v>128.1584358440737</v>
+        <v>128.1584368462394</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -10452,7 +10451,7 @@
         <v>301.8222351074219</v>
       </c>
       <c r="C79" s="1">
-        <v>127.6873149627907</v>
+        <v>127.6872902349885</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -10460,10 +10459,10 @@
         <v>45061</v>
       </c>
       <c r="B80" s="1">
-        <v>302.3008728027344</v>
+        <v>302.3009033203125</v>
       </c>
       <c r="C80" s="1">
-        <v>127.8898048891299</v>
+        <v>127.889793032716</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -10474,7 +10473,7 @@
         <v>304.5281677246094</v>
       </c>
       <c r="C81" s="1">
-        <v>128.8320724729057</v>
+        <v>128.8320475234108</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -10482,10 +10481,10 @@
         <v>45063</v>
       </c>
       <c r="B82" s="1">
-        <v>307.4064636230469</v>
+        <v>307.4064331054688</v>
       </c>
       <c r="C82" s="1">
-        <v>130.0497490791672</v>
+        <v>130.049710983256</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -10493,10 +10492,10 @@
         <v>45064</v>
       </c>
       <c r="B83" s="1">
-        <v>311.83154296875</v>
+        <v>311.8314514160156</v>
       </c>
       <c r="C83" s="1">
-        <v>131.9217996918368</v>
+        <v>131.9217354121813</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -10504,10 +10503,10 @@
         <v>45065</v>
       </c>
       <c r="B84" s="1">
-        <v>311.6553039550781</v>
+        <v>311.6553344726562</v>
       </c>
       <c r="C84" s="1">
-        <v>131.8472409488752</v>
+        <v>131.8472283260681</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -10518,7 +10517,7 @@
         <v>314.4356384277344</v>
       </c>
       <c r="C85" s="1">
-        <v>133.0234745135946</v>
+        <v>133.0234487523968</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -10526,10 +10525,10 @@
         <v>45069</v>
       </c>
       <c r="B86" s="1">
-        <v>308.6399841308594</v>
+        <v>308.6399536132812</v>
       </c>
       <c r="C86" s="1">
-        <v>130.5715957268738</v>
+        <v>130.5715575299022</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -10537,10 +10536,10 @@
         <v>45070</v>
       </c>
       <c r="B87" s="1">
-        <v>307.2595825195312</v>
+        <v>307.2596130371094</v>
       </c>
       <c r="C87" s="1">
-        <v>129.9876103380635</v>
+        <v>129.9875980753907</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -10548,10 +10547,10 @@
         <v>45071</v>
       </c>
       <c r="B88" s="1">
-        <v>319.0761413574219</v>
+        <v>319.0761108398438</v>
       </c>
       <c r="C88" s="1">
-        <v>134.9866610858425</v>
+        <v>134.9866220338537</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -10559,10 +10558,10 @@
         <v>45072</v>
       </c>
       <c r="B89" s="1">
-        <v>325.8997802734375</v>
+        <v>325.8997497558594</v>
       </c>
       <c r="C89" s="1">
-        <v>137.8734335966602</v>
+        <v>137.8733939856217</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -10573,7 +10572,7 @@
         <v>324.2550048828125</v>
       </c>
       <c r="C90" s="1">
-        <v>137.1776036381052</v>
+        <v>137.1775770724228</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -10581,10 +10580,10 @@
         <v>45077</v>
       </c>
       <c r="B91" s="1">
-        <v>321.4942016601562</v>
+        <v>321.4943237304688</v>
       </c>
       <c r="C91" s="1">
-        <v>136.0096328604846</v>
+        <v>136.0096581633997</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -10592,10 +10591,10 @@
         <v>45078</v>
       </c>
       <c r="B92" s="1">
-        <v>325.5962829589844</v>
+        <v>325.5963134765625</v>
       </c>
       <c r="C92" s="1">
-        <v>137.7450376315082</v>
+        <v>137.7450238665395</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -10606,7 +10605,7 @@
         <v>328.3570251464844</v>
       </c>
       <c r="C93" s="1">
-        <v>138.9129825879191</v>
+        <v>138.912955686165</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -10614,10 +10613,10 @@
         <v>45082</v>
       </c>
       <c r="B94" s="1">
-        <v>328.8857727050781</v>
+        <v>328.8857421875</v>
       </c>
       <c r="C94" s="1">
-        <v>139.1366717274086</v>
+        <v>139.1366318717326</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -10628,7 +10627,7 @@
         <v>326.6731872558594</v>
       </c>
       <c r="C95" s="1">
-        <v>138.2006270551666</v>
+        <v>138.2006002913665</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -10636,10 +10635,10 @@
         <v>45084</v>
       </c>
       <c r="B96" s="1">
-        <v>316.5894775390625</v>
+        <v>316.5895080566406</v>
       </c>
       <c r="C96" s="1">
-        <v>133.9346662715161</v>
+        <v>133.9346532444602</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -10647,10 +10646,10 @@
         <v>45085</v>
       </c>
       <c r="B97" s="1">
-        <v>318.4299621582031</v>
+        <v>318.4300231933594</v>
       </c>
       <c r="C97" s="1">
-        <v>134.7132919389217</v>
+        <v>134.7132916716803</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -10658,10 +10657,10 @@
         <v>45086</v>
       </c>
       <c r="B98" s="1">
-        <v>319.9278259277344</v>
+        <v>319.9278564453125</v>
       </c>
       <c r="C98" s="1">
-        <v>135.3469702457682</v>
+        <v>135.3469569452069</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -10672,7 +10671,7 @@
         <v>324.8816528320312</v>
       </c>
       <c r="C99" s="1">
-        <v>137.4427099979272</v>
+        <v>137.4426833809046</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -10683,7 +10682,7 @@
         <v>327.2704162597656</v>
       </c>
       <c r="C100" s="1">
-        <v>138.4532875919211</v>
+        <v>138.453260779191</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -10691,10 +10690,10 @@
         <v>45091</v>
       </c>
       <c r="B101" s="1">
-        <v>330.2563781738281</v>
+        <v>330.2563171386719</v>
       </c>
       <c r="C101" s="1">
-        <v>139.7165128120647</v>
+        <v>139.7164599334949</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -10702,10 +10701,10 @@
         <v>45092</v>
       </c>
       <c r="B102" s="1">
-        <v>340.7903442382812</v>
+        <v>340.7904357910156</v>
       </c>
       <c r="C102" s="1">
-        <v>144.1729566595514</v>
+        <v>144.1729674709628</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -10713,10 +10712,10 @@
         <v>45093</v>
       </c>
       <c r="B103" s="1">
-        <v>335.1415100097656</v>
+        <v>335.1415405273438</v>
       </c>
       <c r="C103" s="1">
-        <v>141.7831907927247</v>
+        <v>141.7831762457311</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -10727,7 +10726,7 @@
         <v>330.951416015625</v>
       </c>
       <c r="C104" s="1">
-        <v>140.0105518373372</v>
+        <v>140.0105247230289</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -10738,7 +10737,7 @@
         <v>326.5557250976562</v>
       </c>
       <c r="C105" s="1">
-        <v>138.1509341371304</v>
+        <v>138.1509073829538</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -10746,10 +10745,10 @@
         <v>45099</v>
       </c>
       <c r="B106" s="1">
-        <v>332.5765380859375</v>
+        <v>332.5766296386719</v>
       </c>
       <c r="C106" s="1">
-        <v>140.6980673663741</v>
+        <v>140.6980788507292</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -10760,7 +10759,7 @@
         <v>327.9850158691406</v>
       </c>
       <c r="C107" s="1">
-        <v>138.7556023148973</v>
+        <v>138.7555754436212</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -10768,10 +10767,10 @@
         <v>45103</v>
       </c>
       <c r="B108" s="1">
-        <v>321.6998291015625</v>
+        <v>321.6997985839844</v>
       </c>
       <c r="C108" s="1">
-        <v>136.0966245159088</v>
+        <v>136.0965852489655</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -10782,7 +10781,7 @@
         <v>327.5445251464844</v>
       </c>
       <c r="C109" s="1">
-        <v>138.5692506446104</v>
+        <v>138.569223809423</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -10790,10 +10789,10 @@
         <v>45105</v>
       </c>
       <c r="B110" s="1">
-        <v>328.797607421875</v>
+        <v>328.7976379394531</v>
       </c>
       <c r="C110" s="1">
-        <v>139.0993729900206</v>
+        <v>139.0993589627726</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -10801,10 +10800,10 @@
         <v>45106</v>
       </c>
       <c r="B111" s="1">
-        <v>328.0143737792969</v>
+        <v>328.014404296875</v>
       </c>
       <c r="C111" s="1">
-        <v>138.7680223167551</v>
+        <v>138.7680083536761</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -10812,10 +10811,10 @@
         <v>45107</v>
       </c>
       <c r="B112" s="1">
-        <v>333.3891296386719</v>
+        <v>333.38916015625</v>
       </c>
       <c r="C112" s="1">
-        <v>141.0418380414974</v>
+        <v>141.0418236380735</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -10823,10 +10822,10 @@
         <v>45110</v>
       </c>
       <c r="B113" s="1">
-        <v>330.8926696777344</v>
+        <v>330.8926391601562</v>
       </c>
       <c r="C113" s="1">
-        <v>139.9856989230167</v>
+        <v>139.985658902919</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -10837,7 +10836,7 @@
         <v>331.04931640625</v>
       </c>
       <c r="C114" s="1">
-        <v>140.0519690576698</v>
+        <v>140.0519419353406</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -10845,10 +10844,10 @@
         <v>45113</v>
       </c>
       <c r="B115" s="1">
-        <v>334.103759765625</v>
+        <v>334.1037902832031</v>
       </c>
       <c r="C115" s="1">
-        <v>141.3441656750784</v>
+        <v>141.344151213106</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -10856,10 +10855,10 @@
         <v>45114</v>
       </c>
       <c r="B116" s="1">
-        <v>330.1388854980469</v>
+        <v>330.1388549804688</v>
       </c>
       <c r="C116" s="1">
-        <v>139.6668069834236</v>
+        <v>139.6667670250822</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -10867,10 +10866,10 @@
         <v>45117</v>
       </c>
       <c r="B117" s="1">
-        <v>324.862060546875</v>
+        <v>324.8620300292969</v>
       </c>
       <c r="C117" s="1">
-        <v>137.4344213896187</v>
+        <v>137.434381863599</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -10878,10 +10877,10 @@
         <v>45118</v>
       </c>
       <c r="B118" s="1">
-        <v>325.4885559082031</v>
+        <v>325.4886169433594</v>
       </c>
       <c r="C118" s="1">
-        <v>137.6994631964166</v>
+        <v>137.6994623508761</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -10889,10 +10888,10 @@
         <v>45119</v>
       </c>
       <c r="B119" s="1">
-        <v>330.1192932128906</v>
+        <v>330.1192626953125</v>
       </c>
       <c r="C119" s="1">
-        <v>139.6585183751152</v>
+        <v>139.6584784183789</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -10903,7 +10902,7 @@
         <v>335.464599609375</v>
       </c>
       <c r="C120" s="1">
-        <v>141.9198753661851</v>
+        <v>141.919847882119</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -10911,10 +10910,10 @@
         <v>45121</v>
       </c>
       <c r="B121" s="1">
-        <v>337.9904174804688</v>
+        <v>337.9904479980469</v>
       </c>
       <c r="C121" s="1">
-        <v>142.9884344865236</v>
+        <v>142.9884197061237</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -10925,7 +10924,7 @@
         <v>338.4701538085938</v>
       </c>
       <c r="C122" s="1">
-        <v>143.1913891946371</v>
+        <v>143.1913614643308</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -10933,10 +10932,10 @@
         <v>45125</v>
       </c>
       <c r="B123" s="1">
-        <v>351.9412231445312</v>
+        <v>351.9411926269531</v>
       </c>
       <c r="C123" s="1">
-        <v>148.8903883839157</v>
+        <v>148.8903466393444</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -10944,10 +10943,10 @@
         <v>45126</v>
       </c>
       <c r="B124" s="1">
-        <v>347.623779296875</v>
+        <v>347.6238098144531</v>
       </c>
       <c r="C124" s="1">
-        <v>147.0638734745233</v>
+        <v>147.0638579048778</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -10955,10 +10954,10 @@
         <v>45127</v>
       </c>
       <c r="B125" s="1">
-        <v>339.5862121582031</v>
+        <v>339.586181640625</v>
       </c>
       <c r="C125" s="1">
-        <v>143.6635429243075</v>
+        <v>143.6635021919621</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -10966,10 +10965,10 @@
         <v>45128</v>
       </c>
       <c r="B126" s="1">
-        <v>336.5513000488281</v>
+        <v>336.55126953125</v>
       </c>
       <c r="C126" s="1">
-        <v>142.3796090939977</v>
+        <v>142.3795686102976</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -10977,10 +10976,10 @@
         <v>45131</v>
       </c>
       <c r="B127" s="1">
-        <v>337.8631591796875</v>
+        <v>337.8630981445312</v>
       </c>
       <c r="C127" s="1">
-        <v>142.9345972643332</v>
+        <v>142.9345437625523</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -10988,10 +10987,10 @@
         <v>45132</v>
       </c>
       <c r="B128" s="1">
-        <v>343.6099853515625</v>
+        <v>343.60986328125</v>
       </c>
       <c r="C128" s="1">
-        <v>145.365819083307</v>
+        <v>145.3657392894934</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -11002,7 +11001,7 @@
         <v>330.6773071289062</v>
       </c>
       <c r="C129" s="1">
-        <v>139.894588784648</v>
+        <v>139.8945616927969</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -11010,10 +11009,10 @@
         <v>45134</v>
       </c>
       <c r="B130" s="1">
-        <v>323.7752990722656</v>
+        <v>323.7753295898438</v>
       </c>
       <c r="C130" s="1">
-        <v>136.9746618405965</v>
+        <v>136.974648224818</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -11024,7 +11023,7 @@
         <v>331.2647094726562</v>
       </c>
       <c r="C131" s="1">
-        <v>140.1430921066434</v>
+        <v>140.1430649666674</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -11035,7 +11034,7 @@
         <v>328.8661193847656</v>
       </c>
       <c r="C132" s="1">
-        <v>139.1283572978905</v>
+        <v>139.128330354427</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -11046,7 +11045,7 @@
         <v>329.2773132324219</v>
       </c>
       <c r="C133" s="1">
-        <v>139.3023147875292</v>
+        <v>139.3022878103774</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -11054,10 +11053,10 @@
         <v>45140</v>
       </c>
       <c r="B134" s="1">
-        <v>320.6229553222656</v>
+        <v>320.6228942871094</v>
       </c>
       <c r="C134" s="1">
-        <v>135.6410480028553</v>
+        <v>135.6409959135362</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -11065,10 +11064,10 @@
         <v>45141</v>
       </c>
       <c r="B135" s="1">
-        <v>319.8006286621094</v>
+        <v>319.8005981445312</v>
       </c>
       <c r="C135" s="1">
-        <v>135.2931588447875</v>
+        <v>135.2931197334425</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -11076,10 +11075,10 @@
         <v>45142</v>
       </c>
       <c r="B136" s="1">
-        <v>320.8970947265625</v>
+        <v>320.8970336914062</v>
       </c>
       <c r="C136" s="1">
-        <v>135.7570239661494</v>
+        <v>135.7569718543705</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -11087,10 +11086,10 @@
         <v>45145</v>
       </c>
       <c r="B137" s="1">
-        <v>323.1781616210938</v>
+        <v>323.1781005859375</v>
       </c>
       <c r="C137" s="1">
-        <v>136.7220400356565</v>
+        <v>136.7219877369935</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -11098,10 +11097,10 @@
         <v>45146</v>
       </c>
       <c r="B138" s="1">
-        <v>319.203369140625</v>
+        <v>319.2033996582031</v>
       </c>
       <c r="C138" s="1">
-        <v>135.0404853974281</v>
+        <v>135.0404721562203</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -11109,10 +11108,10 @@
         <v>45147</v>
       </c>
       <c r="B139" s="1">
-        <v>315.4636535644531</v>
+        <v>315.463623046875</v>
       </c>
       <c r="C139" s="1">
-        <v>133.4583811482963</v>
+        <v>133.4583423922726</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -11120,10 +11119,10 @@
         <v>45148</v>
       </c>
       <c r="B140" s="1">
-        <v>316.1489562988281</v>
+        <v>316.14892578125</v>
       </c>
       <c r="C140" s="1">
-        <v>133.7483016906243</v>
+        <v>133.7482628784549</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -11134,7 +11133,7 @@
         <v>314.2692260742188</v>
       </c>
       <c r="C141" s="1">
-        <v>132.9530729853921</v>
+        <v>132.9530472378283</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -11142,10 +11141,10 @@
         <v>45152</v>
       </c>
       <c r="B142" s="1">
-        <v>317.235595703125</v>
+        <v>317.2356567382812</v>
       </c>
       <c r="C142" s="1">
-        <v>134.2080095972272</v>
+        <v>134.2080094278382</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -11156,7 +11155,7 @@
         <v>315.101318359375</v>
       </c>
       <c r="C143" s="1">
-        <v>133.3050935370093</v>
+        <v>133.3050677212735</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -11167,7 +11166,7 @@
         <v>314.336181640625</v>
       </c>
       <c r="C144" s="1">
-        <v>132.9813988524151</v>
+        <v>132.9813730993657</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -11175,10 +11174,10 @@
         <v>45155</v>
       </c>
       <c r="B145" s="1">
-        <v>310.8828125</v>
+        <v>310.8827819824219</v>
       </c>
       <c r="C145" s="1">
-        <v>131.5204348085141</v>
+        <v>131.5203964277912</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -11186,10 +11185,10 @@
         <v>45156</v>
       </c>
       <c r="B146" s="1">
-        <v>310.4903259277344</v>
+        <v>310.4903564453125</v>
       </c>
       <c r="C146" s="1">
-        <v>131.3543915196434</v>
+        <v>131.354378992281</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -11197,10 +11196,10 @@
         <v>45159</v>
       </c>
       <c r="B147" s="1">
-        <v>315.7881164550781</v>
+        <v>315.7881469726562</v>
       </c>
       <c r="C147" s="1">
-        <v>133.5956466989746</v>
+        <v>133.5956337375729</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -11208,10 +11207,10 @@
         <v>45160</v>
       </c>
       <c r="B148" s="1">
-        <v>316.3571472167969</v>
+        <v>316.357177734375</v>
       </c>
       <c r="C148" s="1">
-        <v>133.8363778368553</v>
+        <v>133.8363648288338</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -11222,7 +11221,7 @@
         <v>320.811279296875</v>
       </c>
       <c r="C149" s="1">
-        <v>135.7207193453342</v>
+        <v>135.7206930617907</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -11230,10 +11229,10 @@
         <v>45162</v>
       </c>
       <c r="B150" s="1">
-        <v>313.914306640625</v>
+        <v>313.9143371582031</v>
       </c>
       <c r="C150" s="1">
-        <v>132.8029226510817</v>
+        <v>132.8029098431982</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -11244,7 +11243,7 @@
         <v>316.8673400878906</v>
       </c>
       <c r="C151" s="1">
-        <v>134.0522173286009</v>
+        <v>134.0521913681779</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -11252,10 +11251,10 @@
         <v>45166</v>
       </c>
       <c r="B152" s="1">
-        <v>317.5736999511719</v>
+        <v>317.57373046875</v>
       </c>
       <c r="C152" s="1">
-        <v>134.3510461882698</v>
+        <v>134.3510330805782</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -11266,7 +11265,7 @@
         <v>322.194580078125</v>
       </c>
       <c r="C153" s="1">
-        <v>136.3059312416045</v>
+        <v>136.3059048447294</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -11274,10 +11273,10 @@
         <v>45168</v>
       </c>
       <c r="B154" s="1">
-        <v>322.5674133300781</v>
+        <v>322.5673828125</v>
       </c>
       <c r="C154" s="1">
-        <v>136.463660100957</v>
+        <v>136.463620762934</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -11288,7 +11287,7 @@
         <v>321.556884765625</v>
       </c>
       <c r="C155" s="1">
-        <v>136.0361512428297</v>
+        <v>136.0361248981999</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -11296,10 +11295,10 @@
         <v>45170</v>
       </c>
       <c r="B156" s="1">
-        <v>322.4398193359375</v>
+        <v>322.4397888183594</v>
       </c>
       <c r="C156" s="1">
-        <v>136.4096808621134</v>
+        <v>136.4096415345439</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -11307,10 +11306,10 @@
         <v>45174</v>
       </c>
       <c r="B157" s="1">
-        <v>327.2372436523438</v>
+        <v>327.2372741699219</v>
       </c>
       <c r="C157" s="1">
-        <v>138.439253764458</v>
+        <v>138.4392398650481</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -11318,10 +11317,10 @@
         <v>45175</v>
       </c>
       <c r="B158" s="1">
-        <v>326.5800170898438</v>
+        <v>326.5799865722656</v>
       </c>
       <c r="C158" s="1">
-        <v>138.1612109785845</v>
+        <v>138.1611713118153</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -11332,7 +11331,7 @@
         <v>323.6661682128906</v>
       </c>
       <c r="C159" s="1">
-        <v>136.9284935176821</v>
+        <v>136.9284670002422</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -11340,10 +11339,10 @@
         <v>45177</v>
       </c>
       <c r="B160" s="1">
-        <v>327.943603515625</v>
+        <v>327.9436340332031</v>
       </c>
       <c r="C160" s="1">
-        <v>138.7380826241269</v>
+        <v>138.738068666846</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -11351,10 +11350,10 @@
         <v>45180</v>
       </c>
       <c r="B161" s="1">
-        <v>331.544189453125</v>
+        <v>331.5442199707031</v>
       </c>
       <c r="C161" s="1">
-        <v>140.2613274257848</v>
+        <v>140.2613131735139</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -11362,10 +11361,10 @@
         <v>45181</v>
       </c>
       <c r="B162" s="1">
-        <v>325.4909362792969</v>
+        <v>325.4909057617188</v>
       </c>
       <c r="C162" s="1">
-        <v>137.7004702235942</v>
+        <v>137.7004306460517</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -11373,10 +11372,10 @@
         <v>45182</v>
       </c>
       <c r="B163" s="1">
-        <v>329.6998291015625</v>
+        <v>329.6997680664062</v>
       </c>
       <c r="C163" s="1">
-        <v>139.4810621115643</v>
+        <v>139.4810092785917</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -11384,10 +11383,10 @@
         <v>45183</v>
       </c>
       <c r="B164" s="1">
-        <v>332.2898559570312</v>
+        <v>332.2898254394531</v>
       </c>
       <c r="C164" s="1">
-        <v>140.57678514449</v>
+        <v>140.5767450099231</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -11395,10 +11394,10 @@
         <v>45184</v>
       </c>
       <c r="B165" s="1">
-        <v>323.9703369140625</v>
+        <v>323.9702453613281</v>
       </c>
       <c r="C165" s="1">
-        <v>137.0571735161406</v>
+        <v>137.0571082419736</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -11406,10 +11405,10 @@
         <v>45187</v>
       </c>
       <c r="B166" s="1">
-        <v>322.8322448730469</v>
+        <v>322.8323059082031</v>
       </c>
       <c r="C166" s="1">
-        <v>136.5756983297744</v>
+        <v>136.5756977018611</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -11417,10 +11416,10 @@
         <v>45188</v>
       </c>
       <c r="B167" s="1">
-        <v>322.4300231933594</v>
+        <v>322.4300842285156</v>
       </c>
       <c r="C167" s="1">
-        <v>136.4055365579592</v>
+        <v>136.4055359629992</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -11428,10 +11427,10 @@
         <v>45189</v>
       </c>
       <c r="B168" s="1">
-        <v>314.6991882324219</v>
+        <v>314.6991577148438</v>
       </c>
       <c r="C168" s="1">
-        <v>133.1349704970086</v>
+        <v>133.1349318036163</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -11442,7 +11441,7 @@
         <v>313.4826354980469</v>
       </c>
       <c r="C169" s="1">
-        <v>132.6203021455941</v>
+        <v>132.6202764624743</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -11453,7 +11452,7 @@
         <v>311.0102844238281</v>
       </c>
       <c r="C170" s="1">
-        <v>131.5743624049384</v>
+        <v>131.5743369243743</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -11461,10 +11460,10 @@
         <v>45194</v>
       </c>
       <c r="B171" s="1">
-        <v>311.5303039550781</v>
+        <v>311.5302734375</v>
       </c>
       <c r="C171" s="1">
-        <v>131.7943591114431</v>
+        <v>131.7943206776724</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -11475,7 +11474,7 @@
         <v>306.2325134277344</v>
       </c>
       <c r="C172" s="1">
-        <v>129.5531039321119</v>
+        <v>129.5530788429828</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -11486,7 +11485,7 @@
         <v>306.8702087402344</v>
       </c>
       <c r="C173" s="1">
-        <v>129.8228839308867</v>
+        <v>129.8228587895123</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -11494,10 +11493,10 @@
         <v>45197</v>
       </c>
       <c r="B174" s="1">
-        <v>307.7041320800781</v>
+        <v>307.7040405273438</v>
       </c>
       <c r="C174" s="1">
-        <v>130.1756791187944</v>
+        <v>130.175615177291</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -11505,10 +11504,10 @@
         <v>45198</v>
       </c>
       <c r="B175" s="1">
-        <v>309.774169921875</v>
+        <v>309.7741394042969</v>
       </c>
       <c r="C175" s="1">
-        <v>131.0514183558203</v>
+        <v>131.0513800659267</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -11516,10 +11515,10 @@
         <v>45201</v>
       </c>
       <c r="B176" s="1">
-        <v>315.7096557617188</v>
+        <v>315.7096252441406</v>
       </c>
       <c r="C176" s="1">
-        <v>133.5624535339263</v>
+        <v>133.562414757748</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -11527,10 +11526,10 @@
         <v>45202</v>
       </c>
       <c r="B177" s="1">
-        <v>307.4588928222656</v>
+        <v>307.4588623046875</v>
       </c>
       <c r="C177" s="1">
-        <v>130.0719294982855</v>
+        <v>130.0718913980788</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -11538,10 +11537,10 @@
         <v>45203</v>
       </c>
       <c r="B178" s="1">
-        <v>312.9234313964844</v>
+        <v>312.9234008789062</v>
       </c>
       <c r="C178" s="1">
-        <v>132.3837282224724</v>
+        <v>132.383689674565</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -11552,7 +11551,7 @@
         <v>313.3158264160156</v>
       </c>
       <c r="C179" s="1">
-        <v>132.5497327795287</v>
+        <v>132.5497071100753</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -11560,10 +11559,10 @@
         <v>45205</v>
       </c>
       <c r="B180" s="1">
-        <v>321.0663757324219</v>
+        <v>321.0663452148438</v>
       </c>
       <c r="C180" s="1">
-        <v>135.828639091207</v>
+        <v>135.8285998761615</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -11574,7 +11573,7 @@
         <v>323.5778503417969</v>
       </c>
       <c r="C181" s="1">
-        <v>136.8911302272699</v>
+        <v>136.8911037170657</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -11582,10 +11581,10 @@
         <v>45209</v>
       </c>
       <c r="B182" s="1">
-        <v>322.1749267578125</v>
+        <v>322.1749877929688</v>
       </c>
       <c r="C182" s="1">
-        <v>136.2976168120863</v>
+        <v>136.2976162380261</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -11593,10 +11592,10 @@
         <v>45210</v>
       </c>
       <c r="B183" s="1">
-        <v>326.1286926269531</v>
+        <v>326.128662109375</v>
       </c>
       <c r="C183" s="1">
-        <v>137.9702760435787</v>
+        <v>137.9702364137858</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -11604,10 +11603,10 @@
         <v>45211</v>
       </c>
       <c r="B184" s="1">
-        <v>324.8925170898438</v>
+        <v>324.8924865722656</v>
       </c>
       <c r="C184" s="1">
-        <v>137.4473061732509</v>
+        <v>137.4472666447359</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -11615,10 +11614,10 @@
         <v>45212</v>
       </c>
       <c r="B185" s="1">
-        <v>321.5274353027344</v>
+        <v>321.5274047851562</v>
       </c>
       <c r="C185" s="1">
-        <v>136.0236925091573</v>
+        <v>136.023653256338</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -11626,10 +11625,10 @@
         <v>45215</v>
       </c>
       <c r="B186" s="1">
-        <v>326.344482421875</v>
+        <v>326.3445434570312</v>
       </c>
       <c r="C186" s="1">
-        <v>138.0615669304153</v>
+        <v>138.0615660147501</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -11637,10 +11636,10 @@
         <v>45216</v>
       </c>
       <c r="B187" s="1">
-        <v>325.7754821777344</v>
+        <v>325.7754516601562</v>
       </c>
       <c r="C187" s="1">
-        <v>137.8208487031394</v>
+        <v>137.8208091022845</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -11648,10 +11647,10 @@
         <v>45217</v>
       </c>
       <c r="B188" s="1">
-        <v>323.8623962402344</v>
+        <v>323.8623352050781</v>
       </c>
       <c r="C188" s="1">
-        <v>137.0115087068151</v>
+        <v>137.0114563520938</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -11659,10 +11658,10 @@
         <v>45218</v>
       </c>
       <c r="B189" s="1">
-        <v>325.0494995117188</v>
+        <v>325.0494689941406</v>
       </c>
       <c r="C189" s="1">
-        <v>137.5137183245572</v>
+        <v>137.5136787831809</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -11670,10 +11669,10 @@
         <v>45219</v>
       </c>
       <c r="B190" s="1">
-        <v>320.4874877929688</v>
+        <v>320.4875183105469</v>
       </c>
       <c r="C190" s="1">
-        <v>135.5837378279624</v>
+        <v>135.5837244815489</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -11681,10 +11680,10 @@
         <v>45222</v>
       </c>
       <c r="B191" s="1">
-        <v>323.0872802734375</v>
+        <v>323.0873107910156</v>
       </c>
       <c r="C191" s="1">
-        <v>136.6835922544376</v>
+        <v>136.6835786950273</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -11692,10 +11691,10 @@
         <v>45223</v>
       </c>
       <c r="B192" s="1">
-        <v>324.2744140625</v>
+        <v>324.2744750976562</v>
       </c>
       <c r="C192" s="1">
-        <v>137.1858147827845</v>
+        <v>137.1858140367167</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -11703,10 +11702,10 @@
         <v>45224</v>
       </c>
       <c r="B193" s="1">
-        <v>334.2225646972656</v>
+        <v>334.2225341796875</v>
       </c>
       <c r="C193" s="1">
-        <v>141.3944266597277</v>
+        <v>141.3943863668171</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -11714,10 +11713,10 @@
         <v>45225</v>
       </c>
       <c r="B194" s="1">
-        <v>321.6844177246094</v>
+        <v>321.6844482421875</v>
       </c>
       <c r="C194" s="1">
-        <v>136.0901046604637</v>
+        <v>136.0900912159877</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -11725,10 +11724,10 @@
         <v>45226</v>
       </c>
       <c r="B195" s="1">
-        <v>323.5680847167969</v>
+        <v>323.5680541992188</v>
       </c>
       <c r="C195" s="1">
-        <v>136.8869988337205</v>
+        <v>136.886959413714</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -11739,7 +11738,7 @@
         <v>330.9260864257812</v>
       </c>
       <c r="C196" s="1">
-        <v>139.9998360353185</v>
+        <v>139.9998089230853</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -11747,10 +11746,10 @@
         <v>45230</v>
       </c>
       <c r="B197" s="1">
-        <v>331.7109680175781</v>
+        <v>331.7109375</v>
       </c>
       <c r="C197" s="1">
-        <v>140.3318838812454</v>
+        <v>140.3318437941059</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -11758,10 +11757,10 @@
         <v>45231</v>
       </c>
       <c r="B198" s="1">
-        <v>339.5203552246094</v>
+        <v>339.5203247070312</v>
       </c>
       <c r="C198" s="1">
-        <v>143.6356818390589</v>
+        <v>143.635641112109</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -11769,10 +11768,10 @@
         <v>45232</v>
       </c>
       <c r="B199" s="1">
-        <v>341.7276916503906</v>
+        <v>341.727783203125</v>
       </c>
       <c r="C199" s="1">
-        <v>144.5695058872681</v>
+        <v>144.5695166218841</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -11780,10 +11779,10 @@
         <v>45233</v>
       </c>
       <c r="B200" s="1">
-        <v>346.1229248046875</v>
+        <v>346.1229553222656</v>
       </c>
       <c r="C200" s="1">
-        <v>146.4289299284023</v>
+        <v>146.4289144817193</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -11791,10 +11790,10 @@
         <v>45236</v>
       </c>
       <c r="B201" s="1">
-        <v>349.7823181152344</v>
+        <v>349.7823486328125</v>
       </c>
       <c r="C201" s="1">
-        <v>147.9770534655904</v>
+        <v>147.9770377190994</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -11802,10 +11801,10 @@
         <v>45237</v>
       </c>
       <c r="B202" s="1">
-        <v>353.7066345214844</v>
+        <v>353.7066650390625</v>
       </c>
       <c r="C202" s="1">
-        <v>149.6372539634104</v>
+        <v>149.6372378954066</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -11813,10 +11812,10 @@
         <v>45238</v>
       </c>
       <c r="B203" s="1">
-        <v>356.326171875</v>
+        <v>356.3261108398438</v>
       </c>
       <c r="C203" s="1">
-        <v>150.7454615512182</v>
+        <v>150.7454065367929</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -11824,10 +11823,10 @@
         <v>45239</v>
       </c>
       <c r="B204" s="1">
-        <v>353.8636779785156</v>
+        <v>353.8636474609375</v>
       </c>
       <c r="C204" s="1">
-        <v>149.7036919359265</v>
+        <v>149.7036500338516</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -11835,10 +11834,10 @@
         <v>45240</v>
       </c>
       <c r="B205" s="1">
-        <v>362.6737060546875</v>
+        <v>362.6736755371094</v>
       </c>
       <c r="C205" s="1">
-        <v>153.4308157158985</v>
+        <v>153.4307730920325</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -11849,7 +11848,7 @@
         <v>359.740234375</v>
       </c>
       <c r="C206" s="1">
-        <v>152.1897967360829</v>
+        <v>152.1897672631537</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -11860,7 +11859,7 @@
         <v>363.2623291015625</v>
       </c>
       <c r="C207" s="1">
-        <v>153.6798354620877</v>
+        <v>153.679805700599</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -11868,10 +11867,10 @@
         <v>45245</v>
       </c>
       <c r="B208" s="1">
-        <v>363.4097595214844</v>
+        <v>363.4097900390625</v>
       </c>
       <c r="C208" s="1">
-        <v>153.7422065940785</v>
+        <v>153.7421897311135</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -11882,7 +11881,7 @@
         <v>369.7996826171875</v>
       </c>
       <c r="C209" s="1">
-        <v>156.4454935888841</v>
+        <v>156.4454632918008</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -11890,10 +11889,10 @@
         <v>45247</v>
       </c>
       <c r="B210" s="1">
-        <v>363.5867004394531</v>
+        <v>363.5867614746094</v>
       </c>
       <c r="C210" s="1">
-        <v>153.8170622809514</v>
+        <v>153.8170583140922</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -11901,10 +11900,10 @@
         <v>45250</v>
       </c>
       <c r="B211" s="1">
-        <v>371.0481872558594</v>
+        <v>371.0482177734375</v>
       </c>
       <c r="C211" s="1">
-        <v>156.9736793435681</v>
+        <v>156.9736618547991</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -11912,10 +11911,10 @@
         <v>45251</v>
       </c>
       <c r="B212" s="1">
-        <v>366.752197265625</v>
+        <v>366.7522583007812</v>
       </c>
       <c r="C212" s="1">
-        <v>155.1562405893795</v>
+        <v>155.1562363631763</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -11923,10 +11922,10 @@
         <v>45252</v>
       </c>
       <c r="B213" s="1">
-        <v>371.4512634277344</v>
+        <v>371.4512939453125</v>
       </c>
       <c r="C213" s="1">
-        <v>157.1442026123189</v>
+        <v>157.1441850905266</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -11937,7 +11936,7 @@
         <v>371.0383911132812</v>
       </c>
       <c r="C214" s="1">
-        <v>156.9695350394138</v>
+        <v>156.9695046408451</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -11945,10 +11944,10 @@
         <v>45257</v>
       </c>
       <c r="B215" s="1">
-        <v>372.1983642578125</v>
+        <v>372.1983947753906</v>
       </c>
       <c r="C215" s="1">
-        <v>157.4602671294516</v>
+        <v>157.4602495464505</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -11959,7 +11958,7 @@
         <v>376.2191467285156</v>
       </c>
       <c r="C216" s="1">
-        <v>159.1612780491766</v>
+        <v>159.1612472261571</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -11970,7 +11969,7 @@
         <v>372.434326171875</v>
       </c>
       <c r="C217" s="1">
-        <v>157.5600919260886</v>
+        <v>157.5600614131532</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -11981,7 +11980,7 @@
         <v>372.4933166503906</v>
       </c>
       <c r="C218" s="1">
-        <v>157.5850481252479</v>
+        <v>157.5850176074795</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -11992,7 +11991,7 @@
         <v>368.1678466796875</v>
       </c>
       <c r="C219" s="1">
-        <v>155.755137726782</v>
+        <v>155.7551075633924</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -12000,10 +11999,10 @@
         <v>45264</v>
       </c>
       <c r="B220" s="1">
-        <v>362.8887634277344</v>
+        <v>362.8887939453125</v>
       </c>
       <c r="C220" s="1">
-        <v>153.5217967482189</v>
+        <v>153.5217799279382</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -12014,7 +12013,7 @@
         <v>366.2114868164062</v>
       </c>
       <c r="C221" s="1">
-        <v>154.927490492792</v>
+        <v>154.9274604896837</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -12022,10 +12021,10 @@
         <v>45266</v>
       </c>
       <c r="B222" s="1">
-        <v>362.5545349121094</v>
+        <v>362.5545654296875</v>
       </c>
       <c r="C222" s="1">
-        <v>153.3803998039912</v>
+        <v>153.3803830110933</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -12036,7 +12035,7 @@
         <v>364.6681213378906</v>
       </c>
       <c r="C223" s="1">
-        <v>154.2745624741264</v>
+        <v>154.2745325974634</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -12044,10 +12043,10 @@
         <v>45268</v>
       </c>
       <c r="B224" s="1">
-        <v>367.892578125</v>
+        <v>367.8925170898438</v>
       </c>
       <c r="C224" s="1">
-        <v>155.6386840711088</v>
+        <v>155.6386281090667</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -12055,10 +12054,10 @@
         <v>45271</v>
       </c>
       <c r="B225" s="1">
-        <v>365.0121459960938</v>
+        <v>365.0121765136719</v>
       </c>
       <c r="C225" s="1">
-        <v>154.4201037225082</v>
+        <v>154.4200867282623</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -12069,7 +12068,7 @@
         <v>368.0400085449219</v>
       </c>
       <c r="C226" s="1">
-        <v>155.7010552030996</v>
+        <v>155.7010250501835</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -12077,10 +12076,10 @@
         <v>45273</v>
       </c>
       <c r="B227" s="1">
-        <v>368.0301818847656</v>
+        <v>368.0301513671875</v>
       </c>
       <c r="C227" s="1">
-        <v>155.6968979883406</v>
+        <v>155.6968549256272</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -12088,10 +12087,10 @@
         <v>45274</v>
       </c>
       <c r="B228" s="1">
-        <v>359.7330932617188</v>
+        <v>359.7331237792969</v>
       </c>
       <c r="C228" s="1">
-        <v>152.1867756545499</v>
+        <v>152.1867590928081</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -12099,10 +12098,10 @@
         <v>45275</v>
       </c>
       <c r="B229" s="1">
-        <v>364.4518432617188</v>
+        <v>364.4518127441406</v>
       </c>
       <c r="C229" s="1">
-        <v>154.1830650176123</v>
+        <v>154.1830222480664</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -12110,10 +12109,10 @@
         <v>45278</v>
       </c>
       <c r="B230" s="1">
-        <v>366.33935546875</v>
+        <v>366.3392944335938</v>
       </c>
       <c r="C230" s="1">
-        <v>154.9815859270792</v>
+        <v>154.9815300922901</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -12121,10 +12120,10 @@
         <v>45279</v>
       </c>
       <c r="B231" s="1">
-        <v>366.9390258789062</v>
+        <v>366.93896484375</v>
       </c>
       <c r="C231" s="1">
-        <v>155.2352793122211</v>
+        <v>155.235223428302</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -12132,10 +12131,10 @@
         <v>45280</v>
       </c>
       <c r="B232" s="1">
-        <v>364.3436584472656</v>
+        <v>364.3437194824219</v>
       </c>
       <c r="C232" s="1">
-        <v>154.1372969234481</v>
+        <v>154.1372928945725</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -12143,10 +12142,10 @@
         <v>45281</v>
       </c>
       <c r="B233" s="1">
-        <v>367.2142639160156</v>
+        <v>367.2142028808594</v>
       </c>
       <c r="C233" s="1">
-        <v>155.3517200572895</v>
+        <v>155.3516641508206</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -12157,7 +12156,7 @@
         <v>368.2366333007812</v>
       </c>
       <c r="C234" s="1">
-        <v>155.7842382300955</v>
+        <v>155.7842080610702</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -12165,10 +12164,10 @@
         <v>45286</v>
       </c>
       <c r="B235" s="1">
-        <v>368.3152770996094</v>
+        <v>368.3153076171875</v>
       </c>
       <c r="C235" s="1">
-        <v>155.8175088587729</v>
+        <v>155.8174915939068</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -12176,10 +12175,10 @@
         <v>45287</v>
       </c>
       <c r="B236" s="1">
-        <v>367.7352600097656</v>
+        <v>367.7352905273438</v>
       </c>
       <c r="C236" s="1">
-        <v>155.5721299031492</v>
+        <v>155.5721126858029</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -12187,10 +12186,10 @@
         <v>45288</v>
       </c>
       <c r="B237" s="1">
-        <v>368.9248352050781</v>
+        <v>368.9248046875</v>
       </c>
       <c r="C237" s="1">
-        <v>156.0753852798835</v>
+        <v>156.0753421438727</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -12198,10 +12197,10 @@
         <v>45289</v>
       </c>
       <c r="B238" s="1">
-        <v>369.671875</v>
+        <v>369.6719360351562</v>
       </c>
       <c r="C238" s="1">
-        <v>156.3914239758066</v>
+        <v>156.391419510399</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -12209,10 +12208,10 @@
         <v>45293</v>
       </c>
       <c r="B239" s="1">
-        <v>364.5894165039062</v>
+        <v>364.5894775390625</v>
       </c>
       <c r="C239" s="1">
-        <v>154.2412660242393</v>
+        <v>154.2412619752292</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -12223,7 +12222,7 @@
         <v>364.3240356445312</v>
       </c>
       <c r="C240" s="1">
-        <v>154.1289954045347</v>
+        <v>154.1289655560622</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -12234,7 +12233,7 @@
         <v>361.7090759277344</v>
       </c>
       <c r="C241" s="1">
-        <v>153.0227244074533</v>
+        <v>153.0226947732201</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -12245,7 +12244,7 @@
         <v>361.5222778320312</v>
       </c>
       <c r="C242" s="1">
-        <v>152.9436985952165</v>
+        <v>152.9436689762873</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -12253,10 +12252,10 @@
         <v>45299</v>
       </c>
       <c r="B243" s="1">
-        <v>368.3447875976562</v>
+        <v>368.3447570800781</v>
       </c>
       <c r="C243" s="1">
-        <v>155.8299934136549</v>
+        <v>155.8299503251664</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -12264,10 +12263,10 @@
         <v>45300</v>
       </c>
       <c r="B244" s="1">
-        <v>369.4261779785156</v>
+        <v>369.4261474609375</v>
       </c>
       <c r="C244" s="1">
-        <v>156.287480696225</v>
+        <v>156.28743751914</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -12278,7 +12277,7 @@
         <v>376.2879028320312</v>
       </c>
       <c r="C245" s="1">
-        <v>159.1903656418853</v>
+        <v>159.1903348132326</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -12286,10 +12285,10 @@
         <v>45302</v>
       </c>
       <c r="B246" s="1">
-        <v>378.1164245605469</v>
+        <v>378.116455078125</v>
       </c>
       <c r="C246" s="1">
-        <v>159.9639303521929</v>
+        <v>159.9639122843348</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -12297,10 +12296,10 @@
         <v>45303</v>
       </c>
       <c r="B247" s="1">
-        <v>381.8914489746094</v>
+        <v>381.8914184570312</v>
       </c>
       <c r="C247" s="1">
-        <v>161.5609721711267</v>
+        <v>161.5609279727824</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -12308,10 +12307,10 @@
         <v>45307</v>
       </c>
       <c r="B248" s="1">
-        <v>383.6609191894531</v>
+        <v>383.660888671875</v>
       </c>
       <c r="C248" s="1">
-        <v>162.3095548610654</v>
+        <v>162.3095105177513</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -12319,10 +12318,10 @@
         <v>45308</v>
       </c>
       <c r="B249" s="1">
-        <v>382.87451171875</v>
+        <v>382.8744812011719</v>
       </c>
       <c r="C249" s="1">
-        <v>161.9768614848964</v>
+        <v>161.9768172060114</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -12330,10 +12329,10 @@
         <v>45309</v>
       </c>
       <c r="B250" s="1">
-        <v>387.199951171875</v>
+        <v>387.1999816894531</v>
       </c>
       <c r="C250" s="1">
-        <v>163.8067589727574</v>
+        <v>163.8067401607009</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -12344,7 +12343,7 @@
         <v>391.9186706542969</v>
       </c>
       <c r="C251" s="1">
-        <v>165.803035425215</v>
+        <v>165.8030033159591</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -12355,7 +12354,7 @@
         <v>389.7952575683594</v>
       </c>
       <c r="C252" s="1">
-        <v>164.9047155403208</v>
+        <v>164.9046836050327</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -12363,10 +12362,10 @@
         <v>45314</v>
       </c>
       <c r="B253" s="1">
-        <v>392.144775390625</v>
+        <v>392.1447448730469</v>
       </c>
       <c r="C253" s="1">
-        <v>165.8986900964881</v>
+        <v>165.8986450581054</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -12374,10 +12373,10 @@
         <v>45315</v>
       </c>
       <c r="B254" s="1">
-        <v>395.7427978515625</v>
+        <v>395.7427673339844</v>
       </c>
       <c r="C254" s="1">
-        <v>167.4208504073393</v>
+        <v>167.4208050741766</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -12388,7 +12387,7 @@
         <v>398.0137023925781</v>
       </c>
       <c r="C255" s="1">
-        <v>168.381567245434</v>
+        <v>168.3815346368222</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -12399,7 +12398,7 @@
         <v>397.089599609375</v>
       </c>
       <c r="C256" s="1">
-        <v>167.9906212202187</v>
+        <v>167.9905886873171</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -12407,10 +12406,10 @@
         <v>45320</v>
       </c>
       <c r="B257" s="1">
-        <v>402.7815246582031</v>
+        <v>402.7815551757812</v>
       </c>
       <c r="C257" s="1">
-        <v>170.3986168610821</v>
+        <v>170.3985967724527</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -12421,7 +12420,7 @@
         <v>401.6706848144531</v>
       </c>
       <c r="C258" s="1">
-        <v>169.9286708448396</v>
+        <v>169.9286379366172</v>
       </c>
     </row>
   </sheetData>
@@ -15308,7 +15307,7 @@
         <v>44949</v>
       </c>
       <c r="B2" s="1">
-        <v>98.97200012207031</v>
+        <v>98.97199249267578</v>
       </c>
       <c r="C2" s="1">
         <v>100</v>
@@ -15319,10 +15318,10 @@
         <v>44950</v>
       </c>
       <c r="B3" s="1">
-        <v>96.89912414550781</v>
+        <v>96.89913177490234</v>
       </c>
       <c r="C3" s="1">
-        <v>97.9055935274564</v>
+        <v>97.905608783286</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -15333,7 +15332,7 @@
         <v>94.43946075439453</v>
       </c>
       <c r="C4" s="1">
-        <v>95.42038216658709</v>
+        <v>95.42038952220076</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -15341,10 +15340,10 @@
         <v>44952</v>
       </c>
       <c r="B5" s="1">
-        <v>96.72058868408203</v>
+        <v>96.72059631347656</v>
       </c>
       <c r="C5" s="1">
-        <v>97.72520365839689</v>
+        <v>97.72521890032088</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -15352,10 +15351,10 @@
         <v>44953</v>
       </c>
       <c r="B6" s="1">
-        <v>98.55545043945312</v>
+        <v>98.55544281005859</v>
       </c>
       <c r="C6" s="1">
-        <v>99.57912370963159</v>
+        <v>99.57912367718775</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -15366,7 +15365,7 @@
         <v>96.14536285400391</v>
       </c>
       <c r="C7" s="1">
-        <v>97.14400308715588</v>
+        <v>97.14401057563728</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -15374,10 +15373,10 @@
         <v>44957</v>
       </c>
       <c r="B8" s="1">
-        <v>98.02978515625</v>
+        <v>98.02977752685547</v>
       </c>
       <c r="C8" s="1">
-        <v>99.04799845950552</v>
+        <v>99.04799838611915</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -15385,10 +15384,10 @@
         <v>44958</v>
       </c>
       <c r="B9" s="1">
-        <v>99.60674285888672</v>
+        <v>99.60675811767578</v>
       </c>
       <c r="C9" s="1">
-        <v>100.6413356666871</v>
+        <v>100.6413588420451</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -15399,7 +15398,7 @@
         <v>106.8568267822266</v>
       </c>
       <c r="C10" s="1">
-        <v>107.9667245791044</v>
+        <v>107.9667329018705</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -15407,10 +15406,10 @@
         <v>44960</v>
       </c>
       <c r="B11" s="1">
-        <v>103.9210891723633</v>
+        <v>103.9210968017578</v>
       </c>
       <c r="C11" s="1">
-        <v>105.0004941237813</v>
+        <v>105.0005099265313</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -15418,10 +15417,10 @@
         <v>44963</v>
       </c>
       <c r="B12" s="1">
-        <v>102.056510925293</v>
+        <v>102.0565032958984</v>
       </c>
       <c r="C12" s="1">
-        <v>103.1165489223399</v>
+        <v>103.1165491625835</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -15429,10 +15428,10 @@
         <v>44964</v>
       </c>
       <c r="B13" s="1">
-        <v>106.7576522827148</v>
+        <v>106.7576446533203</v>
       </c>
       <c r="C13" s="1">
-        <v>107.8665199763992</v>
+        <v>107.8665205828009</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -15440,10 +15439,10 @@
         <v>44965</v>
       </c>
       <c r="B14" s="1">
-        <v>98.55545043945312</v>
+        <v>98.55544281005859</v>
       </c>
       <c r="C14" s="1">
-        <v>99.57912370963159</v>
+        <v>99.57912367718775</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -15454,7 +15453,7 @@
         <v>94.23118591308594</v>
       </c>
       <c r="C15" s="1">
-        <v>95.20994402140288</v>
+        <v>95.20995136079465</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -15462,10 +15461,10 @@
         <v>44967</v>
       </c>
       <c r="B16" s="1">
-        <v>93.79479217529297</v>
+        <v>93.79478454589844</v>
       </c>
       <c r="C16" s="1">
-        <v>94.76901756012623</v>
+        <v>94.76901715688862</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -15476,7 +15475,7 @@
         <v>93.83446502685547</v>
       </c>
       <c r="C17" s="1">
-        <v>94.80910248466404</v>
+        <v>94.80910979315638</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -15484,10 +15483,10 @@
         <v>44971</v>
       </c>
       <c r="B18" s="1">
-        <v>93.90387725830078</v>
+        <v>93.90390014648438</v>
       </c>
       <c r="C18" s="1">
-        <v>94.87923568532656</v>
+        <v>94.87926612514499</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -15498,7 +15497,7 @@
         <v>96.14536285400391</v>
       </c>
       <c r="C19" s="1">
-        <v>97.14400308715588</v>
+        <v>97.14401057563728</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -15506,10 +15505,10 @@
         <v>44973</v>
       </c>
       <c r="B20" s="1">
-        <v>94.72708129882812</v>
+        <v>94.72708892822266</v>
       </c>
       <c r="C20" s="1">
-        <v>95.71099016084693</v>
+        <v>95.71100524750246</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -15520,7 +15519,7 @@
         <v>93.57659149169922</v>
       </c>
       <c r="C21" s="1">
-        <v>94.54855047516824</v>
+        <v>94.54855776357554</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -15528,10 +15527,10 @@
         <v>44978</v>
       </c>
       <c r="B22" s="1">
-        <v>91.03758239746094</v>
+        <v>91.03757476806641</v>
       </c>
       <c r="C22" s="1">
-        <v>91.98316926522328</v>
+        <v>91.98316864723468</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -15539,10 +15538,10 @@
         <v>44979</v>
       </c>
       <c r="B23" s="1">
-        <v>90.89872741699219</v>
+        <v>90.89871978759766</v>
       </c>
       <c r="C23" s="1">
-        <v>91.84287202934092</v>
+        <v>91.84287140053731</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -15550,10 +15549,10 @@
         <v>44980</v>
       </c>
       <c r="B24" s="1">
-        <v>90.14493560791016</v>
+        <v>90.14495849609375</v>
       </c>
       <c r="C24" s="1">
-        <v>91.08125075448308</v>
+        <v>91.08128090152853</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -15564,7 +15563,7 @@
         <v>88.39937591552734</v>
       </c>
       <c r="C25" s="1">
-        <v>89.31756032665513</v>
+        <v>89.31756721182425</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -15575,7 +15574,7 @@
         <v>89.13332366943359</v>
       </c>
       <c r="C26" s="1">
-        <v>90.05913143060475</v>
+        <v>90.0591383729389</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -15583,10 +15582,10 @@
         <v>44985</v>
       </c>
       <c r="B27" s="1">
-        <v>89.32176208496094</v>
+        <v>89.32175445556641</v>
       </c>
       <c r="C27" s="1">
-        <v>90.24952711352005</v>
+        <v>90.2495263618912</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -15594,10 +15593,10 @@
         <v>44986</v>
       </c>
       <c r="B28" s="1">
-        <v>89.61930084228516</v>
+        <v>89.61930847167969</v>
       </c>
       <c r="C28" s="1">
-        <v>90.55015633891433</v>
+        <v>90.55017102773976</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -15605,10 +15604,10 @@
         <v>44987</v>
       </c>
       <c r="B29" s="1">
-        <v>91.24586486816406</v>
+        <v>91.245849609375</v>
       </c>
       <c r="C29" s="1">
-        <v>92.19361511904684</v>
+        <v>92.19360680864081</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -15616,10 +15615,10 @@
         <v>44988</v>
       </c>
       <c r="B30" s="1">
-        <v>92.88232421875</v>
+        <v>92.88233184814453</v>
       </c>
       <c r="C30" s="1">
-        <v>93.84707200439577</v>
+        <v>93.84708694736857</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -15630,7 +15629,7 @@
         <v>94.35019683837891</v>
       </c>
       <c r="C31" s="1">
-        <v>95.330191086377</v>
+        <v>95.33019843503817</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -15638,10 +15637,10 @@
         <v>44992</v>
       </c>
       <c r="B32" s="1">
-        <v>93.09060668945312</v>
+        <v>93.09062194824219</v>
       </c>
       <c r="C32" s="1">
-        <v>94.05751785821931</v>
+        <v>94.05754052605455</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -15649,10 +15648,10 @@
         <v>44993</v>
       </c>
       <c r="B33" s="1">
-        <v>93.4774169921875</v>
+        <v>93.47740936279297</v>
       </c>
       <c r="C33" s="1">
-        <v>94.44834587246302</v>
+        <v>94.448345444506</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -15663,7 +15662,7 @@
         <v>91.56322479248047</v>
       </c>
       <c r="C34" s="1">
-        <v>92.51427138943137</v>
+        <v>92.51427852102343</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -15671,10 +15670,10 @@
         <v>44995</v>
       </c>
       <c r="B35" s="1">
-        <v>89.88706970214844</v>
+        <v>89.8870849609375</v>
       </c>
       <c r="C35" s="1">
-        <v>90.8207064536266</v>
+        <v>90.82072887194769</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -15682,10 +15681,10 @@
         <v>44998</v>
       </c>
       <c r="B36" s="1">
-        <v>90.36315155029297</v>
+        <v>90.36316680908203</v>
       </c>
       <c r="C36" s="1">
-        <v>91.30173325671974</v>
+        <v>91.30175571212146</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -15693,10 +15692,10 @@
         <v>44999</v>
       </c>
       <c r="B37" s="1">
-        <v>93.19971466064453</v>
+        <v>93.19970703125</v>
       </c>
       <c r="C37" s="1">
-        <v>94.16775910933765</v>
+        <v>94.1677586597512</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -15704,10 +15703,10 @@
         <v>45000</v>
       </c>
       <c r="B38" s="1">
-        <v>95.32216644287109</v>
+        <v>95.32215881347656</v>
       </c>
       <c r="C38" s="1">
-        <v>96.31225632027484</v>
+        <v>96.31225603599997</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -15715,10 +15714,10 @@
         <v>45001</v>
       </c>
       <c r="B39" s="1">
-        <v>99.49767303466797</v>
+        <v>99.49765014648438</v>
       </c>
       <c r="C39" s="1">
-        <v>100.5311329587654</v>
+        <v>100.5311175824287</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -15726,10 +15725,10 @@
         <v>45002</v>
       </c>
       <c r="B40" s="1">
-        <v>100.7870025634766</v>
+        <v>100.786994934082</v>
       </c>
       <c r="C40" s="1">
-        <v>101.8338544630478</v>
+        <v>101.833854604413</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -15737,10 +15736,10 @@
         <v>45005</v>
       </c>
       <c r="B41" s="1">
-        <v>100.3902740478516</v>
+        <v>100.3902816772461</v>
       </c>
       <c r="C41" s="1">
-        <v>101.4330052176696</v>
+        <v>101.4330207454147</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -15751,7 +15750,7 @@
         <v>104.059944152832</v>
       </c>
       <c r="C42" s="1">
-        <v>105.1407913596637</v>
+        <v>105.1407994645887</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -15762,7 +15761,7 @@
         <v>102.5226516723633</v>
       </c>
       <c r="C43" s="1">
-        <v>103.5875313683806</v>
+        <v>103.5875393535704</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -15770,10 +15769,10 @@
         <v>45008</v>
       </c>
       <c r="B44" s="1">
-        <v>104.7343826293945</v>
+        <v>104.734375</v>
       </c>
       <c r="C44" s="1">
-        <v>105.8222350768066</v>
+        <v>105.8222355256217</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -15781,10 +15780,10 @@
         <v>45009</v>
       </c>
       <c r="B45" s="1">
-        <v>104.5756912231445</v>
+        <v>104.57568359375</v>
       </c>
       <c r="C45" s="1">
-        <v>105.6618953786553</v>
+        <v>105.6618958151104</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -15792,10 +15791,10 @@
         <v>45012</v>
       </c>
       <c r="B46" s="1">
-        <v>101.6201019287109</v>
+        <v>101.6201095581055</v>
       </c>
       <c r="C46" s="1">
-        <v>102.6756070437846</v>
+        <v>102.6756226673174</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -15803,10 +15802,10 @@
         <v>45013</v>
       </c>
       <c r="B47" s="1">
-        <v>100.2018280029297</v>
+        <v>100.2018356323242</v>
       </c>
       <c r="C47" s="1">
-        <v>101.242601826115</v>
+        <v>101.2426173391825</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -15814,10 +15813,10 @@
         <v>45014</v>
       </c>
       <c r="B48" s="1">
-        <v>100.5588760375977</v>
+        <v>100.5588836669922</v>
       </c>
       <c r="C48" s="1">
-        <v>101.603358438316</v>
+        <v>101.603373979193</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -15828,7 +15827,7 @@
         <v>100.0629806518555</v>
       </c>
       <c r="C49" s="1">
-        <v>101.102312298872</v>
+        <v>101.1023200924852</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -15836,10 +15835,10 @@
         <v>45016</v>
       </c>
       <c r="B50" s="1">
-        <v>102.8796997070312</v>
+        <v>102.8796920776367</v>
       </c>
       <c r="C50" s="1">
-        <v>103.9482879805816</v>
+        <v>103.9482882849409</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -15847,10 +15846,10 @@
         <v>45019</v>
       </c>
       <c r="B51" s="1">
-        <v>103.5045318603516</v>
+        <v>103.5045394897461</v>
       </c>
       <c r="C51" s="1">
-        <v>104.5796101247736</v>
+        <v>104.5796258950791</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -15858,10 +15857,10 @@
         <v>45020</v>
       </c>
       <c r="B52" s="1">
-        <v>103.8615798950195</v>
+        <v>103.8615951538086</v>
       </c>
       <c r="C52" s="1">
-        <v>104.9403667369746</v>
+        <v>104.9403902437295</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -15872,7 +15871,7 @@
         <v>103.6136322021484</v>
       </c>
       <c r="C53" s="1">
-        <v>104.6898436672526</v>
+        <v>104.6898517374157</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -15883,7 +15882,7 @@
         <v>107.53125</v>
       </c>
       <c r="C54" s="1">
-        <v>108.6481528789686</v>
+        <v>108.6481612542636</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -15894,7 +15893,7 @@
         <v>105.5674896240234</v>
       </c>
       <c r="C55" s="1">
-        <v>106.6639953661827</v>
+        <v>106.6640035885261</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -15902,10 +15901,10 @@
         <v>45027</v>
       </c>
       <c r="B56" s="1">
-        <v>104.4864196777344</v>
+        <v>104.4864120483398</v>
       </c>
       <c r="C56" s="1">
-        <v>105.5716965898059</v>
+        <v>105.5716970193079</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -15916,7 +15915,7 @@
         <v>103.7822418212891</v>
       </c>
       <c r="C57" s="1">
-        <v>104.8602045965383</v>
+        <v>104.8602126798339</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -15924,10 +15923,10 @@
         <v>45029</v>
       </c>
       <c r="B58" s="1">
-        <v>106.5493774414062</v>
+        <v>106.5493545532227</v>
       </c>
       <c r="C58" s="1">
-        <v>107.656081831215</v>
+        <v>107.6560670041149</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -15935,10 +15934,10 @@
         <v>45030</v>
       </c>
       <c r="B59" s="1">
-        <v>107.9775695800781</v>
+        <v>107.9775772094727</v>
       </c>
       <c r="C59" s="1">
-        <v>109.0991082800191</v>
+        <v>109.0991243987165</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -15946,10 +15945,10 @@
         <v>45033</v>
       </c>
       <c r="B60" s="1">
-        <v>105.1013412475586</v>
+        <v>105.1013336181641</v>
       </c>
       <c r="C60" s="1">
-        <v>106.1930052115027</v>
+        <v>106.1930056888992</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -15960,7 +15959,7 @@
         <v>103.6433868408203</v>
       </c>
       <c r="C61" s="1">
-        <v>104.7199073606559</v>
+        <v>104.7199154331365</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -15968,10 +15967,10 @@
         <v>45035</v>
       </c>
       <c r="B62" s="1">
-        <v>103.3260116577148</v>
+        <v>103.3260192871094</v>
       </c>
       <c r="C62" s="1">
-        <v>104.3992356729927</v>
+        <v>104.3992514293938</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -15979,10 +15978,10 @@
         <v>45036</v>
       </c>
       <c r="B63" s="1">
-        <v>104.4269104003906</v>
+        <v>104.4269180297852</v>
       </c>
       <c r="C63" s="1">
-        <v>105.5115692029992</v>
+        <v>105.511585045146</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -15990,10 +15989,10 @@
         <v>45037</v>
       </c>
       <c r="B64" s="1">
-        <v>104.5459289550781</v>
+        <v>104.5459365844727</v>
       </c>
       <c r="C64" s="1">
-        <v>105.6318239766126</v>
+        <v>105.6318398280295</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -16001,10 +16000,10 @@
         <v>45040</v>
       </c>
       <c r="B65" s="1">
-        <v>105.1013412475586</v>
+        <v>105.1013336181641</v>
       </c>
       <c r="C65" s="1">
-        <v>106.1930052115027</v>
+        <v>106.1930056888992</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -16012,10 +16011,10 @@
         <v>45041</v>
       </c>
       <c r="B66" s="1">
-        <v>102.9987106323242</v>
+        <v>102.9987182617188</v>
       </c>
       <c r="C66" s="1">
-        <v>104.0685350455557</v>
+        <v>104.0685507764643</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -16023,10 +16022,10 @@
         <v>45042</v>
       </c>
       <c r="B67" s="1">
-        <v>102.8598480224609</v>
+        <v>102.85986328125</v>
       </c>
       <c r="C67" s="1">
-        <v>103.928230101034</v>
+        <v>103.928253529767</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -16034,10 +16033,10 @@
         <v>45043</v>
       </c>
       <c r="B68" s="1">
-        <v>106.7080459594727</v>
+        <v>106.7080612182617</v>
       </c>
       <c r="C68" s="1">
-        <v>107.8163984034483</v>
+        <v>107.8164221319061</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -16048,7 +16047,7 @@
         <v>106.4601058959961</v>
       </c>
       <c r="C69" s="1">
-        <v>107.5658830423656</v>
+        <v>107.5658913342322</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -16056,10 +16055,10 @@
         <v>45047</v>
       </c>
       <c r="B70" s="1">
-        <v>106.3212509155273</v>
+        <v>106.3212585449219</v>
       </c>
       <c r="C70" s="1">
-        <v>107.4255858064832</v>
+        <v>107.4256017961748</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -16070,7 +16069,7 @@
         <v>104.456672668457</v>
       </c>
       <c r="C71" s="1">
-        <v>105.5416406050418</v>
+        <v>105.5416487408669</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -16078,10 +16077,10 @@
         <v>45049</v>
       </c>
       <c r="B72" s="1">
-        <v>104.5459289550781</v>
+        <v>104.5459365844727</v>
       </c>
       <c r="C72" s="1">
-        <v>105.6318239766126</v>
+        <v>105.6318398280295</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -16089,10 +16088,10 @@
         <v>45050</v>
       </c>
       <c r="B73" s="1">
-        <v>103.8318405151367</v>
+        <v>103.8318328857422</v>
       </c>
       <c r="C73" s="1">
-        <v>104.9103184608499</v>
+        <v>104.9103188393687</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -16103,7 +16102,7 @@
         <v>104.7046127319336</v>
       </c>
       <c r="C74" s="1">
-        <v>105.7921559661245</v>
+        <v>105.7921641212609</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -16114,7 +16113,7 @@
         <v>106.8865814208984</v>
       </c>
       <c r="C75" s="1">
-        <v>107.9967882725078</v>
+        <v>107.9967965975913</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -16122,10 +16121,10 @@
         <v>45055</v>
       </c>
       <c r="B76" s="1">
-        <v>106.4700317382812</v>
+        <v>106.4700241088867</v>
       </c>
       <c r="C76" s="1">
-        <v>107.5759119821394</v>
+        <v>107.5759125661392</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -16133,10 +16132,10 @@
         <v>45056</v>
       </c>
       <c r="B77" s="1">
-        <v>110.8339538574219</v>
+        <v>110.8339614868164</v>
       </c>
       <c r="C77" s="1">
-        <v>111.9851611776272</v>
+        <v>111.9851775188</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -16144,10 +16143,10 @@
         <v>45057</v>
       </c>
       <c r="B78" s="1">
-        <v>115.6144561767578</v>
+        <v>115.6144409179688</v>
       </c>
       <c r="C78" s="1">
-        <v>116.8153174980409</v>
+        <v>116.8153110856332</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -16155,10 +16154,10 @@
         <v>45058</v>
       </c>
       <c r="B79" s="1">
-        <v>116.5467376708984</v>
+        <v>116.546745300293</v>
       </c>
       <c r="C79" s="1">
-        <v>117.7572823901222</v>
+        <v>117.757299176247</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -16169,7 +16168,7 @@
         <v>115.5549392700195</v>
       </c>
       <c r="C80" s="1">
-        <v>116.7551824025948</v>
+        <v>116.7551914028314</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -16180,7 +16179,7 @@
         <v>118.5303497314453</v>
       </c>
       <c r="C81" s="1">
-        <v>119.7614977824557</v>
+        <v>119.7615070144384</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -16188,10 +16187,10 @@
         <v>45063</v>
       </c>
       <c r="B82" s="1">
-        <v>119.8494338989258</v>
+        <v>119.8494491577148</v>
       </c>
       <c r="C82" s="1">
-        <v>121.0942829801415</v>
+        <v>121.0943077321436</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -16199,10 +16198,10 @@
         <v>45064</v>
       </c>
       <c r="B83" s="1">
-        <v>121.823127746582</v>
+        <v>121.8231506347656</v>
       </c>
       <c r="C83" s="1">
-        <v>123.0884771413405</v>
+        <v>123.0885097557078</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -16210,10 +16209,10 @@
         <v>45065</v>
       </c>
       <c r="B84" s="1">
-        <v>121.7537155151367</v>
+        <v>121.7537078857422</v>
       </c>
       <c r="C84" s="1">
-        <v>123.018343940678</v>
+        <v>123.0183457150793</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -16221,10 +16220,10 @@
         <v>45068</v>
       </c>
       <c r="B85" s="1">
-        <v>124.0249404907227</v>
+        <v>124.0249328613281</v>
       </c>
       <c r="C85" s="1">
-        <v>125.313159618632</v>
+        <v>125.3131615699323</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -16232,10 +16231,10 @@
         <v>45069</v>
       </c>
       <c r="B86" s="1">
-        <v>121.5553359985352</v>
+        <v>121.5553436279297</v>
       </c>
       <c r="C86" s="1">
-        <v>122.8179039007103</v>
+        <v>122.8179210769402</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -16243,10 +16242,10 @@
         <v>45070</v>
       </c>
       <c r="B87" s="1">
-        <v>119.9089584350586</v>
+        <v>119.9089660644531</v>
       </c>
       <c r="C87" s="1">
-        <v>121.1544257842269</v>
+        <v>121.1544428322252</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -16254,10 +16253,10 @@
         <v>45071</v>
       </c>
       <c r="B88" s="1">
-        <v>122.4678115844727</v>
+        <v>122.4678039550781</v>
       </c>
       <c r="C88" s="1">
-        <v>123.7398571650801</v>
+        <v>123.7398589951002</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -16265,10 +16264,10 @@
         <v>45072</v>
       </c>
       <c r="B89" s="1">
-        <v>123.5885467529297</v>
+        <v>123.5885391235352</v>
       </c>
       <c r="C89" s="1">
-        <v>124.8722331573554</v>
+        <v>124.8722350746663</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -16276,10 +16275,10 @@
         <v>45076</v>
       </c>
       <c r="B90" s="1">
-        <v>122.65625</v>
+        <v>122.6562347412109</v>
       </c>
       <c r="C90" s="1">
-        <v>123.9302528479953</v>
+        <v>123.9302469840524</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -16287,10 +16286,10 @@
         <v>45077</v>
       </c>
       <c r="B91" s="1">
-        <v>121.8628158569336</v>
+        <v>121.8628082275391</v>
       </c>
       <c r="C91" s="1">
-        <v>123.128577483157</v>
+        <v>123.1285792660558</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -16301,7 +16300,7 @@
         <v>122.7058410644531</v>
       </c>
       <c r="C92" s="1">
-        <v>123.9803590036676</v>
+        <v>123.9803685608671</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -16309,10 +16308,10 @@
         <v>45079</v>
       </c>
       <c r="B93" s="1">
-        <v>123.6480560302734</v>
+        <v>123.6480407714844</v>
       </c>
       <c r="C93" s="1">
-        <v>124.9323605441621</v>
+        <v>124.9323547574681</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -16323,7 +16322,7 @@
         <v>124.9770736694336</v>
       </c>
       <c r="C94" s="1">
-        <v>126.275182390261</v>
+        <v>126.2751921243601</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -16334,7 +16333,7 @@
         <v>126.2664108276367</v>
       </c>
       <c r="C95" s="1">
-        <v>127.5779116031827</v>
+        <v>127.5779214377045</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -16342,10 +16341,10 @@
         <v>45084</v>
       </c>
       <c r="B96" s="1">
-        <v>121.4958343505859</v>
+        <v>121.4958267211914</v>
       </c>
       <c r="C96" s="1">
-        <v>122.7577842225429</v>
+        <v>122.7577859768585</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -16353,10 +16352,10 @@
         <v>45085</v>
       </c>
       <c r="B97" s="1">
-        <v>121.1387939453125</v>
+        <v>121.138786315918</v>
       </c>
       <c r="C97" s="1">
-        <v>122.3970353189812</v>
+        <v>122.397037045488</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -16364,10 +16363,10 @@
         <v>45086</v>
       </c>
       <c r="B98" s="1">
-        <v>121.2280502319336</v>
+        <v>121.2280578613281</v>
       </c>
       <c r="C98" s="1">
-        <v>122.4872186905519</v>
+        <v>122.4872358412905</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -16375,10 +16374,10 @@
         <v>45089</v>
       </c>
       <c r="B99" s="1">
-        <v>122.6264877319336</v>
+        <v>122.6264953613281</v>
       </c>
       <c r="C99" s="1">
-        <v>123.9001814459527</v>
+        <v>123.9001987056114</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -16386,10 +16385,10 @@
         <v>45090</v>
       </c>
       <c r="B100" s="1">
-        <v>122.81494140625</v>
+        <v>122.8149337768555</v>
       </c>
       <c r="C100" s="1">
-        <v>124.0905925461466</v>
+        <v>124.0905944032037</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -16397,10 +16396,10 @@
         <v>45091</v>
       </c>
       <c r="B101" s="1">
-        <v>122.65625</v>
+        <v>122.6562347412109</v>
       </c>
       <c r="C101" s="1">
-        <v>123.9302528479953</v>
+        <v>123.9302469840524</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -16411,7 +16410,7 @@
         <v>124.0646057128906</v>
       </c>
       <c r="C102" s="1">
-        <v>125.3532368345305</v>
+        <v>125.3532464975602</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -16419,10 +16418,10 @@
         <v>45093</v>
       </c>
       <c r="B103" s="1">
-        <v>122.5174026489258</v>
+        <v>122.5173950195312</v>
       </c>
       <c r="C103" s="1">
-        <v>123.7899633207523</v>
+        <v>123.7899651546349</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -16430,10 +16429,10 @@
         <v>45097</v>
       </c>
       <c r="B104" s="1">
-        <v>122.0909271240234</v>
+        <v>122.0909118652344</v>
       </c>
       <c r="C104" s="1">
-        <v>123.3590580906101</v>
+        <v>123.3590521826359</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -16441,10 +16440,10 @@
         <v>45098</v>
       </c>
       <c r="B105" s="1">
-        <v>119.5618133544922</v>
+        <v>119.5618209838867</v>
       </c>
       <c r="C105" s="1">
-        <v>120.8036749858816</v>
+        <v>120.8036920068419</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -16452,10 +16451,10 @@
         <v>45099</v>
       </c>
       <c r="B106" s="1">
-        <v>122.1405029296875</v>
+        <v>122.140510559082</v>
       </c>
       <c r="C106" s="1">
-        <v>123.4091488290037</v>
+        <v>123.4091660508106</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -16463,10 +16462,10 @@
         <v>45100</v>
       </c>
       <c r="B107" s="1">
-        <v>121.3371429443359</v>
+        <v>121.3371505737305</v>
       </c>
       <c r="C107" s="1">
-        <v>122.5974445243916</v>
+        <v>122.5974616836271</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -16474,10 +16473,10 @@
         <v>45103</v>
       </c>
       <c r="B108" s="1">
-        <v>117.3699417114258</v>
+        <v>117.3699264526367</v>
       </c>
       <c r="C108" s="1">
-        <v>118.5890368656426</v>
+        <v>118.5890305899646</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -16485,10 +16484,10 @@
         <v>45104</v>
       </c>
       <c r="B109" s="1">
-        <v>117.3600234985352</v>
+        <v>117.3600158691406</v>
       </c>
       <c r="C109" s="1">
-        <v>118.5790156345081</v>
+        <v>118.5790170666975</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -16496,10 +16495,10 @@
         <v>45105</v>
       </c>
       <c r="B110" s="1">
-        <v>119.1948547363281</v>
+        <v>119.1948623657227</v>
       </c>
       <c r="C110" s="1">
-        <v>120.4329048511855</v>
+        <v>120.4329218435644</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -16507,10 +16506,10 @@
         <v>45106</v>
       </c>
       <c r="B111" s="1">
-        <v>118.1237106323242</v>
+        <v>118.1237030029297</v>
       </c>
       <c r="C111" s="1">
-        <v>119.3506350145824</v>
+        <v>119.3506365062532</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -16521,7 +16520,7 @@
         <v>118.7187805175781</v>
       </c>
       <c r="C112" s="1">
-        <v>119.9518857567317</v>
+        <v>119.9518950033906</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -16529,10 +16528,10 @@
         <v>45110</v>
       </c>
       <c r="B113" s="1">
-        <v>118.9171600341797</v>
+        <v>118.9171524047852</v>
       </c>
       <c r="C113" s="1">
-        <v>120.1523257966994</v>
+        <v>120.1523273501697</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -16540,10 +16539,10 @@
         <v>45112</v>
       </c>
       <c r="B114" s="1">
-        <v>120.7519760131836</v>
+        <v>120.7519836425781</v>
       </c>
       <c r="C114" s="1">
-        <v>122.0061995960981</v>
+        <v>122.0062167097567</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -16551,10 +16550,10 @@
         <v>45113</v>
       </c>
       <c r="B115" s="1">
-        <v>119.1254272460938</v>
+        <v>119.1254348754883</v>
       </c>
       <c r="C115" s="1">
-        <v>120.3627562332443</v>
+        <v>120.3627732202157</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -16565,7 +16564,7 @@
         <v>118.5005950927734</v>
       </c>
       <c r="C116" s="1">
-        <v>119.7314340890524</v>
+        <v>119.7314433187175</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -16573,10 +16572,10 @@
         <v>45117</v>
       </c>
       <c r="B117" s="1">
-        <v>115.4954376220703</v>
+        <v>115.4954299926758</v>
       </c>
       <c r="C117" s="1">
-        <v>116.6950627244274</v>
+        <v>116.6950640113897</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -16584,10 +16583,10 @@
         <v>45118</v>
       </c>
       <c r="B118" s="1">
-        <v>116.1797714233398</v>
+        <v>116.1797790527344</v>
       </c>
       <c r="C118" s="1">
-        <v>117.3865045467867</v>
+        <v>117.3865213043296</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -16595,10 +16594,10 @@
         <v>45119</v>
       </c>
       <c r="B119" s="1">
-        <v>117.9551086425781</v>
+        <v>117.9551010131836</v>
       </c>
       <c r="C119" s="1">
-        <v>119.180281793936</v>
+        <v>119.1802832724749</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -16609,7 +16608,7 @@
         <v>123.5191192626953</v>
       </c>
       <c r="C120" s="1">
-        <v>124.8020845394142</v>
+        <v>124.8020941599575</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -16620,7 +16619,7 @@
         <v>124.3918991088867</v>
       </c>
       <c r="C121" s="1">
-        <v>125.6839297533282</v>
+        <v>125.6839394418498</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -16628,10 +16627,10 @@
         <v>45124</v>
       </c>
       <c r="B122" s="1">
-        <v>123.6282196044922</v>
+        <v>123.6282043457031</v>
       </c>
       <c r="C122" s="1">
-        <v>124.9123180818932</v>
+        <v>124.9123122936542</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -16639,10 +16638,10 @@
         <v>45125</v>
       </c>
       <c r="B123" s="1">
-        <v>122.7454986572266</v>
+        <v>122.7455215454102</v>
       </c>
       <c r="C123" s="1">
-        <v>124.0204285109268</v>
+        <v>124.0204611971348</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -16653,7 +16652,7 @@
         <v>121.0296936035156</v>
       </c>
       <c r="C124" s="1">
-        <v>122.2868017765022</v>
+        <v>122.2868112031514</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -16661,10 +16660,10 @@
         <v>45127</v>
       </c>
       <c r="B125" s="1">
-        <v>118.2228851318359</v>
+        <v>118.2228927612305</v>
       </c>
       <c r="C125" s="1">
-        <v>119.4508396172876</v>
+        <v>119.4508565339627</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -16672,10 +16671,10 @@
         <v>45128</v>
       </c>
       <c r="B126" s="1">
-        <v>119.0361709594727</v>
+        <v>119.0361633300781</v>
       </c>
       <c r="C126" s="1">
-        <v>120.2725728616736</v>
+        <v>120.2725744244132</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -16683,10 +16682,10 @@
         <v>45131</v>
       </c>
       <c r="B127" s="1">
-        <v>120.5337905883789</v>
+        <v>120.5337982177734</v>
       </c>
       <c r="C127" s="1">
-        <v>121.7857479284188</v>
+        <v>121.7857650250835</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -16694,10 +16693,10 @@
         <v>45132</v>
       </c>
       <c r="B128" s="1">
-        <v>121.2082290649414</v>
+        <v>121.2082214355469</v>
       </c>
       <c r="C128" s="1">
-        <v>122.4671916455617</v>
+        <v>122.4671933774766</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -16708,7 +16707,7 @@
         <v>128.2103424072266</v>
       </c>
       <c r="C129" s="1">
-        <v>129.5420343623391</v>
+        <v>129.542044348268</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -16716,10 +16715,10 @@
         <v>45134</v>
       </c>
       <c r="B130" s="1">
-        <v>128.3392639160156</v>
+        <v>128.3392944335938</v>
       </c>
       <c r="C130" s="1">
-        <v>129.6722949498083</v>
+        <v>129.6723357803383</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -16730,7 +16729,7 @@
         <v>131.4932098388672</v>
       </c>
       <c r="C131" s="1">
-        <v>132.8590001987287</v>
+        <v>132.8590104403507</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -16738,10 +16737,10 @@
         <v>45138</v>
       </c>
       <c r="B132" s="1">
-        <v>131.6320648193359</v>
+        <v>131.6320953369141</v>
       </c>
       <c r="C132" s="1">
-        <v>132.9992974346111</v>
+        <v>132.9993385216077</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -16752,7 +16751,7 @@
         <v>130.4716491699219</v>
       </c>
       <c r="C133" s="1">
-        <v>131.8268288091586</v>
+        <v>131.8268389712142</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -16760,10 +16759,10 @@
         <v>45140</v>
       </c>
       <c r="B134" s="1">
-        <v>127.32763671875</v>
+        <v>127.3276519775391</v>
       </c>
       <c r="C134" s="1">
-        <v>128.6501602086513</v>
+        <v>128.6501855431088</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -16774,7 +16773,7 @@
         <v>127.3970718383789</v>
       </c>
       <c r="C135" s="1">
-        <v>128.7203165352318</v>
+        <v>128.7203264578175</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -16785,7 +16784,7 @@
         <v>127.0598449707031</v>
       </c>
       <c r="C136" s="1">
-        <v>128.379586968021</v>
+        <v>128.3795968643411</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -16796,7 +16795,7 @@
         <v>130.4518280029297</v>
       </c>
       <c r="C137" s="1">
-        <v>131.8068017641684</v>
+        <v>131.8068119246801</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -16804,10 +16803,10 @@
         <v>45146</v>
       </c>
       <c r="B138" s="1">
-        <v>130.3228759765625</v>
+        <v>130.3228607177734</v>
       </c>
       <c r="C138" s="1">
-        <v>131.6765103421418</v>
+        <v>131.67650507533</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -16815,10 +16814,10 @@
         <v>45147</v>
       </c>
       <c r="B139" s="1">
-        <v>128.59716796875</v>
+        <v>128.5971527099609</v>
       </c>
       <c r="C139" s="1">
-        <v>129.9328777938614</v>
+        <v>129.9328723926393</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -16829,7 +16828,7 @@
         <v>128.6268920898438</v>
       </c>
       <c r="C140" s="1">
-        <v>129.9629106527074</v>
+        <v>129.9629206710803</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -16837,10 +16836,10 @@
         <v>45149</v>
       </c>
       <c r="B141" s="1">
-        <v>128.4979553222656</v>
+        <v>128.4979705810547</v>
       </c>
       <c r="C141" s="1">
-        <v>129.8326346479596</v>
+        <v>129.8326600735697</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -16848,10 +16847,10 @@
         <v>45152</v>
       </c>
       <c r="B142" s="1">
-        <v>130.2534637451172</v>
+        <v>130.2534790039062</v>
       </c>
       <c r="C142" s="1">
-        <v>131.6063771414793</v>
+        <v>131.6064027038209</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -16859,10 +16858,10 @@
         <v>45153</v>
       </c>
       <c r="B143" s="1">
-        <v>128.7161865234375</v>
+        <v>128.7161560058594</v>
       </c>
       <c r="C143" s="1">
-        <v>130.0531325674749</v>
+        <v>130.0531117582429</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -16870,10 +16869,10 @@
         <v>45154</v>
       </c>
       <c r="B144" s="1">
-        <v>127.6450119018555</v>
+        <v>127.64501953125</v>
       </c>
       <c r="C144" s="1">
-        <v>128.9708318963145</v>
+        <v>128.9708495468514</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -16881,10 +16880,10 @@
         <v>45155</v>
       </c>
       <c r="B145" s="1">
-        <v>128.8549957275391</v>
+        <v>128.8550262451172</v>
       </c>
       <c r="C145" s="1">
-        <v>130.1933835515212</v>
+        <v>130.1934244222201</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -16892,10 +16891,10 @@
         <v>45156</v>
       </c>
       <c r="B146" s="1">
-        <v>126.4151840209961</v>
+        <v>126.4151763916016</v>
       </c>
       <c r="C146" s="1">
-        <v>127.7282300701995</v>
+        <v>127.7282322076689</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -16903,10 +16902,10 @@
         <v>45159</v>
       </c>
       <c r="B147" s="1">
-        <v>127.3177185058594</v>
+        <v>127.3177032470703</v>
       </c>
       <c r="C147" s="1">
-        <v>128.6401389775168</v>
+        <v>128.6401334766421</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -16914,10 +16913,10 @@
         <v>45160</v>
       </c>
       <c r="B148" s="1">
-        <v>128.0219116210938</v>
+        <v>128.0219268798828</v>
       </c>
       <c r="C148" s="1">
-        <v>129.3516463880631</v>
+        <v>129.3516717765956</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -16925,10 +16924,10 @@
         <v>45161</v>
       </c>
       <c r="B149" s="1">
-        <v>131.2849426269531</v>
+        <v>131.2849273681641</v>
       </c>
       <c r="C149" s="1">
-        <v>132.6485697621839</v>
+        <v>132.6485645703046</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -16936,10 +16935,10 @@
         <v>45162</v>
       </c>
       <c r="B150" s="1">
-        <v>128.7161865234375</v>
+        <v>128.7161560058594</v>
       </c>
       <c r="C150" s="1">
-        <v>130.0531325674749</v>
+        <v>130.0531117582429</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -16947,10 +16946,10 @@
         <v>45163</v>
       </c>
       <c r="B151" s="1">
-        <v>128.8153381347656</v>
+        <v>128.8153533935547</v>
       </c>
       <c r="C151" s="1">
-        <v>130.1533140442621</v>
+        <v>130.1533394945923</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -16958,10 +16957,10 @@
         <v>45166</v>
       </c>
       <c r="B152" s="1">
-        <v>129.9360656738281</v>
+        <v>129.9360961914062</v>
       </c>
       <c r="C152" s="1">
-        <v>131.2856823278981</v>
+        <v>131.2857232827983</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -16969,10 +16968,10 @@
         <v>45167</v>
       </c>
       <c r="B153" s="1">
-        <v>133.4669036865234</v>
+        <v>133.4669189453125</v>
       </c>
       <c r="C153" s="1">
-        <v>134.8531943599278</v>
+        <v>134.8532201725548</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -16980,10 +16979,10 @@
         <v>45168</v>
       </c>
       <c r="B154" s="1">
-        <v>134.7661895751953</v>
+        <v>134.7661743164062</v>
       </c>
       <c r="C154" s="1">
-        <v>136.1659756385413</v>
+        <v>136.1659707178062</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -16991,10 +16990,10 @@
         <v>45169</v>
       </c>
       <c r="B155" s="1">
-        <v>135.0537719726562</v>
+        <v>135.0537872314453</v>
       </c>
       <c r="C155" s="1">
-        <v>136.4565450896044</v>
+        <v>136.456571025828</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -17002,10 +17001,10 @@
         <v>45170</v>
       </c>
       <c r="B156" s="1">
-        <v>134.5479736328125</v>
+        <v>134.5479278564453</v>
       </c>
       <c r="C156" s="1">
-        <v>135.9454931363046</v>
+        <v>135.9454573640136</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -17016,7 +17015,7 @@
         <v>134.6570739746094</v>
       </c>
       <c r="C157" s="1">
-        <v>136.0557266787836</v>
+        <v>136.0557371668297</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -17024,10 +17023,10 @@
         <v>45175</v>
       </c>
       <c r="B158" s="1">
-        <v>133.3578033447266</v>
+        <v>133.3578186035156</v>
       </c>
       <c r="C158" s="1">
-        <v>134.7429608174488</v>
+        <v>134.7429866215783</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -17038,7 +17037,7 @@
         <v>134.1512298583984</v>
       </c>
       <c r="C159" s="1">
-        <v>135.5446284736478</v>
+        <v>135.5446389222951</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -17046,10 +17045,10 @@
         <v>45177</v>
       </c>
       <c r="B160" s="1">
-        <v>135.2620544433594</v>
+        <v>135.2620849609375</v>
       </c>
       <c r="C160" s="1">
-        <v>136.666990943428</v>
+        <v>136.6670323131539</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -17057,10 +17056,10 @@
         <v>45180</v>
       </c>
       <c r="B161" s="1">
-        <v>135.7976531982422</v>
+        <v>135.7976226806641</v>
       </c>
       <c r="C161" s="1">
-        <v>137.2081528419672</v>
+        <v>137.2081325842899</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -17068,10 +17067,10 @@
         <v>45181</v>
       </c>
       <c r="B162" s="1">
-        <v>134.2306213378906</v>
+        <v>134.2305603027344</v>
       </c>
       <c r="C162" s="1">
-        <v>135.6248445745594</v>
+        <v>135.6247933602709</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -17079,10 +17078,10 @@
         <v>45182</v>
       </c>
       <c r="B163" s="1">
-        <v>135.58935546875</v>
+        <v>135.5893707275391</v>
       </c>
       <c r="C163" s="1">
-        <v>136.997691570865</v>
+        <v>136.9977175488036</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -17090,10 +17089,10 @@
         <v>45183</v>
       </c>
       <c r="B164" s="1">
-        <v>136.9679718017578</v>
+        <v>136.9679565429688</v>
       </c>
       <c r="C164" s="1">
-        <v>138.3906272812754</v>
+        <v>138.3906225320307</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -17101,10 +17100,10 @@
         <v>45184</v>
       </c>
       <c r="B165" s="1">
-        <v>136.2737121582031</v>
+        <v>136.273681640625</v>
       </c>
       <c r="C165" s="1">
-        <v>137.6891565191423</v>
+        <v>137.6891362985439</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -17115,7 +17114,7 @@
         <v>137.0770721435547</v>
       </c>
       <c r="C166" s="1">
-        <v>138.5008608237545</v>
+        <v>138.5008715002871</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -17123,10 +17122,10 @@
         <v>45188</v>
       </c>
       <c r="B167" s="1">
-        <v>136.9084320068359</v>
+        <v>136.9084625244141</v>
       </c>
       <c r="C167" s="1">
-        <v>138.3304690599114</v>
+        <v>138.3305105578689</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -17137,7 +17136,7 @@
         <v>132.6437072753906</v>
       </c>
       <c r="C168" s="1">
-        <v>134.0214475930468</v>
+        <v>134.0214579242776</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -17145,10 +17144,10 @@
         <v>45190</v>
       </c>
       <c r="B169" s="1">
-        <v>129.3707275390625</v>
+        <v>129.3707580566406</v>
       </c>
       <c r="C169" s="1">
-        <v>130.7144721532342</v>
+        <v>130.7145130641019</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -17156,10 +17155,10 @@
         <v>45191</v>
       </c>
       <c r="B170" s="1">
-        <v>129.1823120117188</v>
+        <v>129.1822967529297</v>
       </c>
       <c r="C170" s="1">
-        <v>130.5240995962369</v>
+        <v>130.5240942405899</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -17170,7 +17169,7 @@
         <v>130.0352630615234</v>
       </c>
       <c r="C171" s="1">
-        <v>131.3859100565213</v>
+        <v>131.385920184588</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -17178,10 +17177,10 @@
         <v>45195</v>
       </c>
       <c r="B172" s="1">
-        <v>127.5160751342773</v>
+        <v>127.5160903930664</v>
       </c>
       <c r="C172" s="1">
-        <v>128.8405558915666</v>
+        <v>128.840581240701</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -17192,7 +17191,7 @@
         <v>129.4699249267578</v>
       </c>
       <c r="C173" s="1">
-        <v>130.8146998818574</v>
+        <v>130.8147099658916</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -17203,7 +17202,7 @@
         <v>131.2254180908203</v>
       </c>
       <c r="C174" s="1">
-        <v>132.5884269580984</v>
+        <v>132.5884371788629</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -17211,10 +17210,10 @@
         <v>45198</v>
       </c>
       <c r="B175" s="1">
-        <v>129.7872924804688</v>
+        <v>129.7873229980469</v>
       </c>
       <c r="C175" s="1">
-        <v>131.1353638608813</v>
+        <v>131.135404804194</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -17225,7 +17224,7 @@
         <v>133.0701751708984</v>
       </c>
       <c r="C176" s="1">
-        <v>134.4523451145496</v>
+        <v>134.4523554789968</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -17233,10 +17232,10 @@
         <v>45202</v>
       </c>
       <c r="B177" s="1">
-        <v>131.3444366455078</v>
+        <v>131.3444061279297</v>
       </c>
       <c r="C177" s="1">
-        <v>132.7086817317119</v>
+        <v>132.7086611271866</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -17244,10 +17243,10 @@
         <v>45203</v>
       </c>
       <c r="B178" s="1">
-        <v>134.1313934326172</v>
+        <v>134.1314086914062</v>
       </c>
       <c r="C178" s="1">
-        <v>135.5245860113789</v>
+        <v>135.5246118757611</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -17255,10 +17254,10 @@
         <v>45204</v>
       </c>
       <c r="B179" s="1">
-        <v>133.9627990722656</v>
+        <v>133.9628295898438</v>
       </c>
       <c r="C179" s="1">
-        <v>135.3542404993718</v>
+        <v>135.3542817679026</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -17266,10 +17265,10 @@
         <v>45205</v>
       </c>
       <c r="B180" s="1">
-        <v>136.4522399902344</v>
+        <v>136.4522247314453</v>
       </c>
       <c r="C180" s="1">
-        <v>137.8695386795625</v>
+        <v>137.8695338901489</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -17280,7 +17279,7 @@
         <v>137.2853393554688</v>
       </c>
       <c r="C181" s="1">
-        <v>138.7112912602993</v>
+        <v>138.7113019530533</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -17288,10 +17287,10 @@
         <v>45209</v>
       </c>
       <c r="B182" s="1">
-        <v>136.9282989501953</v>
+        <v>136.9282836914062</v>
       </c>
       <c r="C182" s="1">
-        <v>138.3505423567376</v>
+        <v>138.3505376044029</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -17299,10 +17298,10 @@
         <v>45210</v>
       </c>
       <c r="B183" s="1">
-        <v>139.3978881835938</v>
+        <v>139.3978576660156</v>
       </c>
       <c r="C183" s="1">
-        <v>140.8457826573807</v>
+        <v>140.8457626801153</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -17310,10 +17309,10 @@
         <v>45211</v>
       </c>
       <c r="B184" s="1">
-        <v>137.8308258056641</v>
+        <v>137.8308410644531</v>
       </c>
       <c r="C184" s="1">
-        <v>139.2624435554156</v>
+        <v>139.2624697079358</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -17324,7 +17323,7 @@
         <v>136.2340240478516</v>
       </c>
       <c r="C185" s="1">
-        <v>137.6490561773258</v>
+        <v>137.6490667881959</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -17332,10 +17331,10 @@
         <v>45215</v>
       </c>
       <c r="B186" s="1">
-        <v>137.9597625732422</v>
+        <v>137.9597778320312</v>
       </c>
       <c r="C186" s="1">
-        <v>139.3927195601636</v>
+        <v>139.3927457227262</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -17343,10 +17342,10 @@
         <v>45216</v>
       </c>
       <c r="B187" s="1">
-        <v>138.5746459960938</v>
+        <v>138.5746765136719</v>
       </c>
       <c r="C187" s="1">
-        <v>140.0139896386637</v>
+        <v>140.0140312663977</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -17354,10 +17353,10 @@
         <v>45217</v>
       </c>
       <c r="B188" s="1">
-        <v>136.8291015625</v>
+        <v>136.8291320800781</v>
       </c>
       <c r="C188" s="1">
-        <v>138.2503146281144</v>
+        <v>138.2503561198931</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -17368,7 +17367,7 @@
         <v>136.6208343505859</v>
       </c>
       <c r="C189" s="1">
-        <v>138.0398841915696</v>
+        <v>138.0398948325672</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -17376,10 +17375,10 @@
         <v>45219</v>
       </c>
       <c r="B190" s="1">
-        <v>134.4884490966797</v>
+        <v>134.4884643554688</v>
       </c>
       <c r="C190" s="1">
-        <v>135.8853503322192</v>
+        <v>135.8853762244115</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -17387,10 +17386,10 @@
         <v>45222</v>
       </c>
       <c r="B191" s="1">
-        <v>135.3810577392578</v>
+        <v>135.3810729980469</v>
       </c>
       <c r="C191" s="1">
-        <v>136.7872302997628</v>
+        <v>136.7872562614777</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -17398,10 +17397,10 @@
         <v>45223</v>
       </c>
       <c r="B192" s="1">
-        <v>137.672119140625</v>
+        <v>137.6721343994141</v>
       </c>
       <c r="C192" s="1">
-        <v>139.1020884399857</v>
+        <v>139.1021145801447</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -17409,10 +17408,10 @@
         <v>45224</v>
       </c>
       <c r="B193" s="1">
-        <v>124.5803298950195</v>
+        <v>124.5803451538086</v>
       </c>
       <c r="C193" s="1">
-        <v>125.8743177276041</v>
+        <v>125.8743428480819</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -17420,10 +17419,10 @@
         <v>45225</v>
       </c>
       <c r="B194" s="1">
-        <v>121.2776260375977</v>
+        <v>121.2776336669922</v>
       </c>
       <c r="C194" s="1">
-        <v>122.5373094289455</v>
+        <v>122.5373265835454</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -17431,10 +17430,10 @@
         <v>45226</v>
       </c>
       <c r="B195" s="1">
-        <v>121.1685409545898</v>
+        <v>121.1685485839844</v>
       </c>
       <c r="C195" s="1">
-        <v>122.4270913037452</v>
+        <v>122.4271084498488</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -17445,7 +17444,7 @@
         <v>123.4397735595703</v>
       </c>
       <c r="C196" s="1">
-        <v>124.7219146903386</v>
+        <v>124.7219243047019</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -17456,7 +17455,7 @@
         <v>123.0628967285156</v>
       </c>
       <c r="C197" s="1">
-        <v>124.341123324508</v>
+        <v>124.3411329095175</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -17467,7 +17466,7 @@
         <v>125.4134521484375</v>
       </c>
       <c r="C198" s="1">
-        <v>126.716093434259</v>
+        <v>126.7161032023463</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -17475,10 +17474,10 @@
         <v>45232</v>
       </c>
       <c r="B199" s="1">
-        <v>126.4449310302734</v>
+        <v>126.444938659668</v>
       </c>
       <c r="C199" s="1">
-        <v>127.7582860549635</v>
+        <v>127.7583036120297</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -17486,10 +17485,10 @@
         <v>45233</v>
       </c>
       <c r="B200" s="1">
-        <v>128.0417327880859</v>
+        <v>128.041748046875</v>
       </c>
       <c r="C200" s="1">
-        <v>129.3716734330533</v>
+        <v>129.3716988231296</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -17497,10 +17496,10 @@
         <v>45236</v>
       </c>
       <c r="B201" s="1">
-        <v>129.1823120117188</v>
+        <v>129.1822967529297</v>
       </c>
       <c r="C201" s="1">
-        <v>130.5240995962369</v>
+        <v>130.5240942405899</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -17511,7 +17510,7 @@
         <v>129.8964080810547</v>
       </c>
       <c r="C202" s="1">
-        <v>131.2456128206389</v>
+        <v>131.2456229378906</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -17519,10 +17518,10 @@
         <v>45238</v>
       </c>
       <c r="B203" s="1">
-        <v>130.7592926025391</v>
+        <v>130.7592620849609</v>
       </c>
       <c r="C203" s="1">
-        <v>132.1174599293365</v>
+        <v>132.117439279236</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -17530,10 +17529,10 @@
         <v>45239</v>
       </c>
       <c r="B204" s="1">
-        <v>129.1723937988281</v>
+        <v>129.1724090576172</v>
       </c>
       <c r="C204" s="1">
-        <v>130.5140783651024</v>
+        <v>130.5141038432427</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -17541,10 +17540,10 @@
         <v>45240</v>
       </c>
       <c r="B205" s="1">
-        <v>131.5031280517578</v>
+        <v>131.5031127929688</v>
       </c>
       <c r="C205" s="1">
-        <v>132.8690214298632</v>
+        <v>132.8690162549778</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -17555,7 +17554,7 @@
         <v>131.0072326660156</v>
       </c>
       <c r="C206" s="1">
-        <v>132.3679752904191</v>
+        <v>132.3679854941897</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -17566,7 +17565,7 @@
         <v>132.5246734619141</v>
       </c>
       <c r="C207" s="1">
-        <v>133.9011774021546</v>
+        <v>133.9011877241143</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -17574,10 +17573,10 @@
         <v>45245</v>
       </c>
       <c r="B208" s="1">
-        <v>133.5165252685547</v>
+        <v>133.5164642333984</v>
       </c>
       <c r="C208" s="1">
-        <v>134.9033313501574</v>
+        <v>134.90328008025</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -17585,10 +17584,10 @@
         <v>45246</v>
       </c>
       <c r="B209" s="1">
-        <v>135.8075561523438</v>
+        <v>135.8075256347656</v>
       </c>
       <c r="C209" s="1">
-        <v>137.218158655823</v>
+        <v>137.218138398917</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -17596,10 +17595,10 @@
         <v>45247</v>
       </c>
       <c r="B210" s="1">
-        <v>134.2008209228516</v>
+        <v>134.2008361816406</v>
       </c>
       <c r="C210" s="1">
-        <v>135.59473462932</v>
+        <v>135.5947604991098</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -17607,10 +17606,10 @@
         <v>45250</v>
       </c>
       <c r="B211" s="1">
-        <v>135.1331481933594</v>
+        <v>135.1331176757812</v>
       </c>
       <c r="C211" s="1">
-        <v>136.5367457732374</v>
+        <v>136.5367254638038</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -17618,10 +17617,10 @@
         <v>45251</v>
       </c>
       <c r="B212" s="1">
-        <v>135.8472442626953</v>
+        <v>135.8471984863281</v>
       </c>
       <c r="C212" s="1">
-        <v>137.2582589976395</v>
+        <v>137.2582233265449</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -17632,7 +17631,7 @@
         <v>137.3547821044922</v>
       </c>
       <c r="C213" s="1">
-        <v>138.7814552955192</v>
+        <v>138.7814659936818</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -17640,10 +17639,10 @@
         <v>45254</v>
       </c>
       <c r="B214" s="1">
-        <v>135.5695343017578</v>
+        <v>135.5695037841797</v>
       </c>
       <c r="C214" s="1">
-        <v>136.9776645258747</v>
+        <v>136.97764425043</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -17651,10 +17650,10 @@
         <v>45257</v>
       </c>
       <c r="B215" s="1">
-        <v>135.2918090820312</v>
+        <v>135.2917938232422</v>
       </c>
       <c r="C215" s="1">
-        <v>136.6970546368314</v>
+        <v>136.6970497570352</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -17662,10 +17661,10 @@
         <v>45258</v>
       </c>
       <c r="B216" s="1">
-        <v>136.0753326416016</v>
+        <v>136.0753479003906</v>
       </c>
       <c r="C216" s="1">
-        <v>137.4887164791746</v>
+        <v>137.4887424949645</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -17676,7 +17675,7 @@
         <v>133.8834686279297</v>
       </c>
       <c r="C217" s="1">
-        <v>135.2740860675748</v>
+        <v>135.2740964953671</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -17684,10 +17683,10 @@
         <v>45260</v>
       </c>
       <c r="B218" s="1">
-        <v>131.443603515625</v>
+        <v>131.4436340332031</v>
       </c>
       <c r="C218" s="1">
-        <v>132.8088786257778</v>
+        <v>132.8089196980957</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -17695,10 +17694,10 @@
         <v>45261</v>
       </c>
       <c r="B219" s="1">
-        <v>130.7790985107422</v>
+        <v>130.7791137695312</v>
       </c>
       <c r="C219" s="1">
-        <v>132.137471557048</v>
+        <v>132.1374971603298</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -17709,7 +17708,7 @@
         <v>128.2103424072266</v>
       </c>
       <c r="C220" s="1">
-        <v>129.5420343623391</v>
+        <v>129.542044348268</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -17717,10 +17716,10 @@
         <v>45265</v>
       </c>
       <c r="B221" s="1">
-        <v>129.9162445068359</v>
+        <v>129.916259765625</v>
       </c>
       <c r="C221" s="1">
-        <v>131.2656552829078</v>
+        <v>131.2656808189844</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -17728,10 +17727,10 @@
         <v>45266</v>
       </c>
       <c r="B222" s="1">
-        <v>128.9542236328125</v>
+        <v>128.9541931152344</v>
       </c>
       <c r="C222" s="1">
-        <v>130.2936421147018</v>
+        <v>130.2936213240098</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -17739,10 +17738,10 @@
         <v>45267</v>
       </c>
       <c r="B223" s="1">
-        <v>135.8075561523438</v>
+        <v>135.8075256347656</v>
       </c>
       <c r="C223" s="1">
-        <v>137.218158655823</v>
+        <v>137.218138398917</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -17753,7 +17752,7 @@
         <v>133.8834686279297</v>
       </c>
       <c r="C224" s="1">
-        <v>135.2740860675748</v>
+        <v>135.2740964953671</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -17761,10 +17760,10 @@
         <v>45271</v>
       </c>
       <c r="B225" s="1">
-        <v>132.1973876953125</v>
+        <v>132.1974029541016</v>
       </c>
       <c r="C225" s="1">
-        <v>133.5704921919963</v>
+        <v>133.5705179057445</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -17772,10 +17771,10 @@
         <v>45272</v>
       </c>
       <c r="B226" s="1">
-        <v>131.4337005615234</v>
+        <v>131.4336853027344</v>
       </c>
       <c r="C226" s="1">
-        <v>132.798872811922</v>
+        <v>132.7988676316291</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -17786,7 +17785,7 @@
         <v>131.4832916259766</v>
       </c>
       <c r="C227" s="1">
-        <v>132.8489789675943</v>
+        <v>132.8489892084437</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -17797,7 +17796,7 @@
         <v>130.8584594726562</v>
       </c>
       <c r="C228" s="1">
-        <v>132.2176568234023</v>
+        <v>132.2176670155854</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -17805,10 +17804,10 @@
         <v>45275</v>
       </c>
       <c r="B229" s="1">
-        <v>131.5130310058594</v>
+        <v>131.5130462646484</v>
       </c>
       <c r="C229" s="1">
-        <v>132.879027243719</v>
+        <v>132.8790529041646</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -17819,7 +17818,7 @@
         <v>134.6868133544922</v>
       </c>
       <c r="C230" s="1">
-        <v>136.0857749549083</v>
+        <v>136.0857854452707</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -17827,10 +17826,10 @@
         <v>45279</v>
       </c>
       <c r="B231" s="1">
-        <v>135.5298309326172</v>
+        <v>135.5298156738281</v>
       </c>
       <c r="C231" s="1">
-        <v>136.9375487667796</v>
+        <v>136.9375439055223</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -17838,10 +17837,10 @@
         <v>45280</v>
       </c>
       <c r="B232" s="1">
-        <v>137.2059783935547</v>
+        <v>137.2059936523438</v>
       </c>
       <c r="C232" s="1">
-        <v>138.631105993945</v>
+        <v>138.6311320977977</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -17852,7 +17851,7 @@
         <v>139.2689514160156</v>
       </c>
       <c r="C233" s="1">
-        <v>140.7155066526328</v>
+        <v>140.7155174998846</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -17863,7 +17862,7 @@
         <v>140.3301696777344</v>
       </c>
       <c r="C234" s="1">
-        <v>141.7877475494621</v>
+        <v>141.787758479369</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -17874,7 +17873,7 @@
         <v>140.3599395751953</v>
       </c>
       <c r="C235" s="1">
-        <v>141.8178266601441</v>
+        <v>141.8178375923698</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -17882,10 +17881,10 @@
         <v>45287</v>
       </c>
       <c r="B236" s="1">
-        <v>139.2193450927734</v>
+        <v>139.2193756103516</v>
       </c>
       <c r="C236" s="1">
-        <v>140.6653850796819</v>
+        <v>140.6654267576297</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -17893,10 +17892,10 @@
         <v>45288</v>
       </c>
       <c r="B237" s="1">
-        <v>139.0804901123047</v>
+        <v>139.0805053710938</v>
       </c>
       <c r="C237" s="1">
-        <v>140.5250878437995</v>
+        <v>140.5251140936524</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -17904,10 +17903,10 @@
         <v>45289</v>
       </c>
       <c r="B238" s="1">
-        <v>138.5449523925781</v>
+        <v>138.544921875</v>
       </c>
       <c r="C238" s="1">
-        <v>139.983987614375</v>
+        <v>139.9839675706769</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -17915,10 +17914,10 @@
         <v>45293</v>
       </c>
       <c r="B239" s="1">
-        <v>137.0373992919922</v>
+        <v>137.0373840332031</v>
       </c>
       <c r="C239" s="1">
-        <v>138.4607758992166</v>
+        <v>138.4607711553794</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -17926,10 +17925,10 @@
         <v>45294</v>
       </c>
       <c r="B240" s="1">
-        <v>137.78125</v>
+        <v>137.7812194824219</v>
       </c>
       <c r="C240" s="1">
-        <v>139.212352817022</v>
+        <v>139.2123327138413</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -17937,10 +17936,10 @@
         <v>45295</v>
       </c>
       <c r="B241" s="1">
-        <v>135.27197265625</v>
+        <v>135.2720031738281</v>
       </c>
       <c r="C241" s="1">
-        <v>136.6770121745625</v>
+        <v>136.6770535450609</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -17948,10 +17947,10 @@
         <v>45296</v>
       </c>
       <c r="B242" s="1">
-        <v>134.6174011230469</v>
+        <v>134.6173706054688</v>
       </c>
       <c r="C242" s="1">
-        <v>136.0156417542458</v>
+        <v>136.0156214046422</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -17959,10 +17958,10 @@
         <v>45299</v>
       </c>
       <c r="B243" s="1">
-        <v>137.701904296875</v>
+        <v>137.7018737792969</v>
       </c>
       <c r="C243" s="1">
-        <v>139.1321829679464</v>
+        <v>139.1321628585857</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -17970,10 +17969,10 @@
         <v>45300</v>
       </c>
       <c r="B244" s="1">
-        <v>139.7946014404297</v>
+        <v>139.7945861816406</v>
       </c>
       <c r="C244" s="1">
-        <v>141.2466164854802</v>
+        <v>141.2466119563935</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -17981,10 +17980,10 @@
         <v>45301</v>
       </c>
       <c r="B245" s="1">
-        <v>141.1136932373047</v>
+        <v>141.1137084960938</v>
       </c>
       <c r="C245" s="1">
-        <v>142.5794093918053</v>
+        <v>142.5794358000185</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -17992,10 +17991,10 @@
         <v>45302</v>
       </c>
       <c r="B246" s="1">
-        <v>140.9153442382812</v>
+        <v>140.9153289794922</v>
       </c>
       <c r="C246" s="1">
-        <v>142.3790001863949</v>
+        <v>142.3789957445995</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -18003,10 +18002,10 @@
         <v>45303</v>
       </c>
       <c r="B247" s="1">
-        <v>141.4806671142578</v>
+        <v>141.4806365966797</v>
       </c>
       <c r="C247" s="1">
-        <v>142.9501949437801</v>
+        <v>142.9501751287362</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -18017,7 +18016,7 @@
         <v>141.3219757080078</v>
       </c>
       <c r="C248" s="1">
-        <v>142.7898552456289</v>
+        <v>142.7898662527846</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -18028,7 +18027,7 @@
         <v>140.3103179931641</v>
       </c>
       <c r="C249" s="1">
-        <v>141.7676896699145</v>
+        <v>141.7677005982753</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -18036,10 +18035,10 @@
         <v>45309</v>
       </c>
       <c r="B250" s="1">
-        <v>142.3038635253906</v>
+        <v>142.3038330078125</v>
       </c>
       <c r="C250" s="1">
-        <v>143.7819417106612</v>
+        <v>143.7819219597336</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -18047,10 +18046,10 @@
         <v>45310</v>
       </c>
       <c r="B251" s="1">
-        <v>145.1800689697266</v>
+        <v>145.1801147460938</v>
       </c>
       <c r="C251" s="1">
-        <v>146.6880216532595</v>
+        <v>146.6880792127505</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -18058,10 +18057,10 @@
         <v>45313</v>
       </c>
       <c r="B252" s="1">
-        <v>144.7932891845703</v>
+        <v>144.7932739257812</v>
       </c>
       <c r="C252" s="1">
-        <v>146.2972244735732</v>
+        <v>146.2972203338196</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -18069,10 +18068,10 @@
         <v>45314</v>
       </c>
       <c r="B253" s="1">
-        <v>145.8346710205078</v>
+        <v>145.8346557617188</v>
       </c>
       <c r="C253" s="1">
-        <v>147.3494229081335</v>
+        <v>147.3494188494901</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -18083,7 +18082,7 @@
         <v>147.4810638427734</v>
       </c>
       <c r="C254" s="1">
-        <v>149.0129164418956</v>
+        <v>149.0129279287648</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -18091,10 +18090,10 @@
         <v>45316</v>
       </c>
       <c r="B255" s="1">
-        <v>150.6250610351562</v>
+        <v>150.6250915527344</v>
       </c>
       <c r="C255" s="1">
-        <v>152.1895696251242</v>
+        <v>152.1896121914299</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -18102,10 +18101,10 @@
         <v>45317</v>
       </c>
       <c r="B256" s="1">
-        <v>150.9424896240234</v>
+        <v>150.9424591064453</v>
       </c>
       <c r="C256" s="1">
-        <v>152.5102952732628</v>
+        <v>152.5102761951726</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -18116,7 +18115,7 @@
         <v>152.2516326904297</v>
       </c>
       <c r="C257" s="1">
-        <v>153.8330361138961</v>
+        <v>153.8330479723309</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -18124,10 +18123,10 @@
         <v>45321</v>
       </c>
       <c r="B258" s="1">
-        <v>150.2184448242188</v>
+        <v>150.2184600830078</v>
       </c>
       <c r="C258" s="1">
-        <v>151.7787299831689</v>
+        <v>151.7787571005246</v>
       </c>
     </row>
   </sheetData>

--- a/resultats.xlsx
+++ b/resultats.xlsx
@@ -473,7 +473,8 @@
     <col min="1" max="1" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1">
@@ -535,19 +536,19 @@
         <v>4019.81005859375</v>
       </c>
       <c r="C5" s="1">
-        <v>138.8828430175781</v>
+        <v>138.8828735351562</v>
       </c>
       <c r="D5" s="1">
         <v>202</v>
       </c>
       <c r="E5" s="1">
-        <v>236.3760986328125</v>
+        <v>236.3760528564453</v>
       </c>
       <c r="F5" s="1">
         <v>97.51999664306641</v>
       </c>
       <c r="G5" s="1">
-        <v>98.97199249267578</v>
+        <v>98.97200012207031</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -570,7 +571,7 @@
         <v>159</v>
       </c>
       <c r="G6" s="1">
-        <v>150.2184600830078</v>
+        <v>150.2184448242188</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="3" customFormat="1">
@@ -581,19 +582,19 @@
         <v>0.2251748572833444</v>
       </c>
       <c r="C7" s="3">
-        <v>0.3400260563100195</v>
+        <v>0.3400257618579476</v>
       </c>
       <c r="D7" s="3">
         <v>0.06237626783918626</v>
       </c>
       <c r="E7" s="3">
-        <v>0.6992863793661721</v>
+        <v>0.6992867084483964</v>
       </c>
       <c r="F7" s="3">
         <v>0.6304348387331982</v>
       </c>
       <c r="G7" s="3">
-        <v>0.517787571005246</v>
+        <v>0.5177872998316896</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="3" customFormat="1">
@@ -604,19 +605,19 @@
         <v>0.2212933175580829</v>
       </c>
       <c r="C8" s="3">
-        <v>0.3339117518080452</v>
+        <v>0.3339114632793259</v>
       </c>
       <c r="D8" s="3">
         <v>0.06137232945653404</v>
       </c>
       <c r="E8" s="3">
-        <v>0.6852667840002153</v>
+        <v>0.6852671052679318</v>
       </c>
       <c r="F8" s="3">
         <v>0.6180286426432327</v>
       </c>
       <c r="G8" s="3">
-        <v>0.5079244058973418</v>
+        <v>0.5079241406955288</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="3" customFormat="1">
@@ -627,19 +628,19 @@
         <v>0.0007932952126940571</v>
       </c>
       <c r="C9" s="3">
-        <v>0.001143316635864242</v>
+        <v>0.001143315777520084</v>
       </c>
       <c r="D9" s="3">
         <v>0.0002363600048310617</v>
       </c>
       <c r="E9" s="3">
-        <v>0.002071126508155384</v>
+        <v>0.002071127264636067</v>
       </c>
       <c r="F9" s="3">
         <v>0.001909557622930636</v>
       </c>
       <c r="G9" s="3">
-        <v>0.001629897379420586</v>
+        <v>0.001629896681515416</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="3" customFormat="1">
@@ -650,19 +651,19 @@
         <v>0.1253305867413214</v>
       </c>
       <c r="C10" s="3">
-        <v>0.2005365867859033</v>
+        <v>0.200536503864588</v>
       </c>
       <c r="D10" s="3">
         <v>0.0567447014935399</v>
       </c>
       <c r="E10" s="3">
-        <v>0.237017821350406</v>
+        <v>0.2370177575142819</v>
       </c>
       <c r="F10" s="3">
         <v>0.3161577817349202</v>
       </c>
       <c r="G10" s="3">
-        <v>0.295824069544639</v>
+        <v>0.2958242622337487</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="3" customFormat="1">
@@ -673,19 +674,19 @@
         <v>0.007895084861603466</v>
       </c>
       <c r="C11" s="3">
-        <v>0.01263261755726718</v>
+        <v>0.01263261233371531</v>
       </c>
       <c r="D11" s="3">
         <v>0.003574580199345286</v>
       </c>
       <c r="E11" s="3">
-        <v>0.01493071932341689</v>
+        <v>0.01493071530211906</v>
       </c>
       <c r="F11" s="3">
         <v>0.01991606822686756</v>
       </c>
       <c r="G11" s="3">
-        <v>0.01863516475814741</v>
+        <v>0.01863517689642038</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -696,19 +697,19 @@
         <v>1.765676865574927</v>
       </c>
       <c r="C12" s="1">
-        <v>1.665091428750285</v>
+        <v>1.665090678477167</v>
       </c>
       <c r="D12" s="1">
         <v>1.081551719212427</v>
       </c>
       <c r="E12" s="1">
-        <v>2.891203623828439</v>
+        <v>2.89120575797634</v>
       </c>
       <c r="F12" s="1">
         <v>1.954810788625198</v>
       </c>
       <c r="G12" s="1">
-        <v>1.716981335153654</v>
+        <v>1.71697932029046</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="3" customFormat="1">
@@ -719,19 +720,19 @@
         <v>-0.1027661709329137</v>
       </c>
       <c r="C13" s="3">
-        <v>-0.1493236401017953</v>
+        <v>-0.1493237187908421</v>
       </c>
       <c r="D13" s="3">
         <v>-0.02974119167021968</v>
       </c>
       <c r="E13" s="3">
-        <v>-0.129875900169687</v>
+        <v>-0.1298760094054953</v>
       </c>
       <c r="F13" s="3">
         <v>-0.1964396385244207</v>
       </c>
       <c r="G13" s="3">
-        <v>-0.1727306660931956</v>
+        <v>-0.1727305356292835</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -739,22 +740,22 @@
         <v>22</v>
       </c>
       <c r="B14" s="1">
-        <v>276.1600664370077</v>
+        <v>271.7601236992977</v>
       </c>
       <c r="C14" s="1">
-        <v>477.4879464885985</v>
+        <v>527.575947233816</v>
       </c>
       <c r="D14" s="1">
-        <v>135.4241270416449</v>
+        <v>134.5289025149724</v>
       </c>
       <c r="E14" s="1">
-        <v>1459.405947235744</v>
+        <v>1579.683081428831</v>
       </c>
       <c r="F14" s="1">
-        <v>1492.239514073</v>
+        <v>1362.957041121342</v>
       </c>
       <c r="G14" s="1">
-        <v>1010.627389295891</v>
+        <v>883.7252139249748</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -762,22 +763,22 @@
         <v>23</v>
       </c>
       <c r="B15" s="1">
-        <v>178.2326878503416</v>
+        <v>174.2002490692583</v>
       </c>
       <c r="C15" s="1">
-        <v>218.8578667831883</v>
+        <v>234.6869451343696</v>
       </c>
       <c r="D15" s="1">
-        <v>113.6232836619716</v>
+        <v>110.7064162516255</v>
       </c>
       <c r="E15" s="1">
-        <v>494.7682914898266</v>
+        <v>765.7157190491664</v>
       </c>
       <c r="F15" s="1">
-        <v>401.3814220466234</v>
+        <v>345.9887778212983</v>
       </c>
       <c r="G15" s="1">
-        <v>254.3858357059047</v>
+        <v>272.7870966957291</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -785,22 +786,22 @@
         <v>24</v>
       </c>
       <c r="B16" s="1">
-        <v>264.5203265010251</v>
+        <v>265.325688035945</v>
       </c>
       <c r="C16" s="1">
-        <v>441.9585686873706</v>
+        <v>471.2639343859741</v>
       </c>
       <c r="D16" s="1">
-        <v>132.3152773411375</v>
+        <v>132.6785372938336</v>
       </c>
       <c r="E16" s="1">
-        <v>1316.297161203467</v>
+        <v>1423.076123266681</v>
       </c>
       <c r="F16" s="1">
-        <v>1128.278748252805</v>
+        <v>1125.33808917952</v>
       </c>
       <c r="G16" s="1">
-        <v>828.0935053534004</v>
+        <v>848.8471749183246</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -808,22 +809,22 @@
         <v>25</v>
       </c>
       <c r="B17" s="1">
-        <v>404.2569374336622</v>
+        <v>397.4751929194269</v>
       </c>
       <c r="C17" s="1">
-        <v>892.8068078558273</v>
+        <v>995.2953608200739</v>
       </c>
       <c r="D17" s="1">
-        <v>162.5229752818519</v>
+        <v>159.3722271093831</v>
       </c>
       <c r="E17" s="1">
-        <v>3044.628573842618</v>
+        <v>3012.85158941961</v>
       </c>
       <c r="F17" s="1">
-        <v>3602.879418452111</v>
+        <v>3650.859046973546</v>
       </c>
       <c r="G17" s="1">
-        <v>2210.390721627754</v>
+        <v>1786.348095002214</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="3" customFormat="1">
@@ -880,19 +881,19 @@
         <v>1</v>
       </c>
       <c r="C21" s="1">
-        <v>0.7060172465660103</v>
+        <v>0.7060171764370482</v>
       </c>
       <c r="D21" s="1">
-        <v>0.004456046337864243</v>
+        <v>0.004456046337864237</v>
       </c>
       <c r="E21" s="1">
-        <v>0.6246286916963628</v>
+        <v>0.6246284424297324</v>
       </c>
       <c r="F21" s="1">
         <v>0.6045950866477746</v>
       </c>
       <c r="G21" s="1">
-        <v>0.6008773229065343</v>
+        <v>0.6008770952634304</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -900,22 +901,22 @@
         <v>7</v>
       </c>
       <c r="B22" s="1">
-        <v>0.7060172465660103</v>
+        <v>0.7060171764370482</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>-0.0561253848466664</v>
+        <v>-0.0561252797408004</v>
       </c>
       <c r="E22" s="1">
-        <v>0.5536257816599395</v>
+        <v>0.5536237316269575</v>
       </c>
       <c r="F22" s="1">
-        <v>0.4276414333842711</v>
+        <v>0.427640837707475</v>
       </c>
       <c r="G22" s="1">
-        <v>0.5177399329107535</v>
+        <v>0.5177399015053651</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -923,22 +924,22 @@
         <v>8</v>
       </c>
       <c r="B23" s="1">
-        <v>0.004456046337864243</v>
+        <v>0.004456046337864237</v>
       </c>
       <c r="C23" s="1">
-        <v>-0.0561253848466664</v>
+        <v>-0.0561252797408004</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="E23" s="1">
-        <v>-0.04384078424626962</v>
+        <v>-0.04384136641135974</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.005269283798744161</v>
+        <v>-0.005269283798744167</v>
       </c>
       <c r="G23" s="1">
-        <v>-0.01599772152909821</v>
+        <v>-0.01599646412747189</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -946,22 +947,22 @@
         <v>9</v>
       </c>
       <c r="B24" s="1">
-        <v>0.6246286916963628</v>
+        <v>0.6246284424297324</v>
       </c>
       <c r="C24" s="1">
-        <v>0.5536257816599395</v>
+        <v>0.5536237316269575</v>
       </c>
       <c r="D24" s="1">
-        <v>-0.04384078424626962</v>
+        <v>-0.04384136641135974</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1">
-        <v>0.5709360806035841</v>
+        <v>0.5709361436725379</v>
       </c>
       <c r="G24" s="1">
-        <v>0.5011065761627947</v>
+        <v>0.5011058313581164</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -972,19 +973,19 @@
         <v>0.6045950866477746</v>
       </c>
       <c r="C25" s="1">
-        <v>0.4276414333842711</v>
+        <v>0.427640837707475</v>
       </c>
       <c r="D25" s="1">
-        <v>-0.005269283798744161</v>
+        <v>-0.005269283798744167</v>
       </c>
       <c r="E25" s="1">
-        <v>0.5709360806035841</v>
+        <v>0.5709361436725379</v>
       </c>
       <c r="F25" s="1">
         <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>0.6003319856823502</v>
+        <v>0.6003312130372177</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -992,19 +993,19 @@
         <v>11</v>
       </c>
       <c r="B26" s="1">
-        <v>0.6008773229065343</v>
+        <v>0.6008770952634304</v>
       </c>
       <c r="C26" s="1">
-        <v>0.5177399329107535</v>
+        <v>0.5177399015053651</v>
       </c>
       <c r="D26" s="1">
-        <v>-0.01599772152909821</v>
+        <v>-0.01599646412747189</v>
       </c>
       <c r="E26" s="1">
-        <v>0.5011065761627947</v>
+        <v>0.5011058313581164</v>
       </c>
       <c r="F26" s="1">
-        <v>0.6003319856823502</v>
+        <v>0.6003312130372177</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -3895,7 +3896,7 @@
         <v>44949</v>
       </c>
       <c r="B2" s="1">
-        <v>138.8828430175781</v>
+        <v>138.8828735351562</v>
       </c>
       <c r="C2" s="1">
         <v>100</v>
@@ -3909,7 +3910,7 @@
         <v>140.2804565429688</v>
       </c>
       <c r="C3" s="1">
-        <v>101.0063255439073</v>
+        <v>101.0063033491734</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3920,7 +3921,7 @@
         <v>139.6210174560547</v>
       </c>
       <c r="C4" s="1">
-        <v>100.5315087324236</v>
+        <v>100.531486642024</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3928,10 +3929,10 @@
         <v>44952</v>
       </c>
       <c r="B5" s="1">
-        <v>141.6878509521484</v>
+        <v>141.6878662109375</v>
       </c>
       <c r="C5" s="1">
-        <v>102.0196936307066</v>
+        <v>102.0196822001031</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3939,10 +3940,10 @@
         <v>44953</v>
       </c>
       <c r="B6" s="1">
-        <v>143.6268005371094</v>
+        <v>143.6267852783203</v>
       </c>
       <c r="C6" s="1">
-        <v>103.415798104688</v>
+        <v>103.415764393702</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3950,10 +3951,10 @@
         <v>44956</v>
       </c>
       <c r="B7" s="1">
-        <v>140.7430267333984</v>
+        <v>140.7430572509766</v>
       </c>
       <c r="C7" s="1">
-        <v>101.3393905794288</v>
+        <v>101.3393902851164</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3961,10 +3962,10 @@
         <v>44957</v>
       </c>
       <c r="B8" s="1">
-        <v>142.0126800537109</v>
+        <v>142.0126495361328</v>
       </c>
       <c r="C8" s="1">
-        <v>102.2535807650026</v>
+        <v>102.2535363225937</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3975,7 +3976,7 @@
         <v>143.1346740722656</v>
       </c>
       <c r="C9" s="1">
-        <v>103.0614516252014</v>
+        <v>103.061428978882</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3983,10 +3984,10 @@
         <v>44959</v>
       </c>
       <c r="B10" s="1">
-        <v>148.4396362304688</v>
+        <v>148.4396057128906</v>
       </c>
       <c r="C10" s="1">
-        <v>106.881190653392</v>
+        <v>106.8811451941302</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3997,7 +3998,7 @@
         <v>152.0615234375</v>
       </c>
       <c r="C11" s="1">
-        <v>109.4890629638492</v>
+        <v>109.4890389051518</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4005,10 +4006,10 @@
         <v>44963</v>
       </c>
       <c r="B12" s="1">
-        <v>149.3352661132812</v>
+        <v>149.3352508544922</v>
       </c>
       <c r="C12" s="1">
-        <v>107.5260722408888</v>
+        <v>107.5260376267273</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4016,10 +4017,10 @@
         <v>44964</v>
       </c>
       <c r="B13" s="1">
-        <v>152.2091522216797</v>
+        <v>152.2091369628906</v>
       </c>
       <c r="C13" s="1">
-        <v>109.5953603156114</v>
+        <v>109.5953252467526</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4030,7 +4031,7 @@
         <v>149.5222473144531</v>
       </c>
       <c r="C14" s="1">
-        <v>107.6607045663145</v>
+        <v>107.6606809093734</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4041,7 +4042,7 @@
         <v>148.4888153076172</v>
       </c>
       <c r="C15" s="1">
-        <v>106.9166011303666</v>
+        <v>106.9165776369318</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4049,10 +4050,10 @@
         <v>44967</v>
       </c>
       <c r="B16" s="1">
-        <v>148.8535461425781</v>
+        <v>148.8535308837891</v>
       </c>
       <c r="C16" s="1">
-        <v>107.1792187633558</v>
+        <v>107.1791842254106</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -4060,10 +4061,10 @@
         <v>44970</v>
       </c>
       <c r="B17" s="1">
-        <v>151.6529998779297</v>
+        <v>151.6529693603516</v>
       </c>
       <c r="C17" s="1">
-        <v>109.1949131965388</v>
+        <v>109.1948672288688</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4071,10 +4072,10 @@
         <v>44971</v>
       </c>
       <c r="B18" s="1">
-        <v>151.0122680664062</v>
+        <v>151.0122375488281</v>
       </c>
       <c r="C18" s="1">
-        <v>108.7335662096814</v>
+        <v>108.733520343386</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4082,10 +4083,10 @@
         <v>44972</v>
       </c>
       <c r="B19" s="1">
-        <v>153.1118316650391</v>
+        <v>153.1118621826172</v>
       </c>
       <c r="C19" s="1">
-        <v>110.2453178076575</v>
+        <v>110.2453155563915</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4096,7 +4097,7 @@
         <v>151.5149993896484</v>
       </c>
       <c r="C20" s="1">
-        <v>109.0955485196047</v>
+        <v>109.0955245473766</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -4104,10 +4105,10 @@
         <v>44974</v>
       </c>
       <c r="B21" s="1">
-        <v>150.3715972900391</v>
+        <v>150.3715362548828</v>
       </c>
       <c r="C21" s="1">
-        <v>108.2722631700496</v>
+        <v>108.2721954315111</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4118,7 +4119,7 @@
         <v>146.3596649169922</v>
       </c>
       <c r="C22" s="1">
-        <v>105.3835461148126</v>
+        <v>105.3835229582453</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4126,10 +4127,10 @@
         <v>44979</v>
       </c>
       <c r="B23" s="1">
-        <v>146.7835235595703</v>
+        <v>146.7835540771484</v>
       </c>
       <c r="C23" s="1">
-        <v>105.6887376225386</v>
+        <v>105.6887363725177</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4137,10 +4138,10 @@
         <v>44980</v>
       </c>
       <c r="B24" s="1">
-        <v>147.2665405273438</v>
+        <v>147.2665557861328</v>
       </c>
       <c r="C24" s="1">
-        <v>106.0365249786142</v>
+        <v>106.0365126653679</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4148,10 +4149,10 @@
         <v>44981</v>
       </c>
       <c r="B25" s="1">
-        <v>144.6149444580078</v>
+        <v>144.6149291992188</v>
       </c>
       <c r="C25" s="1">
-        <v>104.1272926992891</v>
+        <v>104.1272588319621</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4159,10 +4160,10 @@
         <v>44984</v>
       </c>
       <c r="B26" s="1">
-        <v>145.8076629638672</v>
+        <v>145.8076477050781</v>
       </c>
       <c r="C26" s="1">
-        <v>104.9860874070763</v>
+        <v>104.9860533510411</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4170,10 +4171,10 @@
         <v>44985</v>
       </c>
       <c r="B27" s="1">
-        <v>145.3049621582031</v>
+        <v>145.3049468994141</v>
       </c>
       <c r="C27" s="1">
-        <v>104.6241270707658</v>
+        <v>104.6240930942663</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4181,10 +4182,10 @@
         <v>44986</v>
       </c>
       <c r="B28" s="1">
-        <v>143.2349090576172</v>
+        <v>143.2349243164062</v>
       </c>
       <c r="C28" s="1">
-        <v>103.1336239563358</v>
+        <v>103.1336122809616</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -4192,10 +4193,10 @@
         <v>44987</v>
       </c>
       <c r="B29" s="1">
-        <v>143.8263854980469</v>
+        <v>143.8264007568359</v>
       </c>
       <c r="C29" s="1">
-        <v>103.5595055321866</v>
+        <v>103.5594937632309</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -4203,10 +4204,10 @@
         <v>44988</v>
       </c>
       <c r="B30" s="1">
-        <v>148.8732452392578</v>
+        <v>148.8732604980469</v>
       </c>
       <c r="C30" s="1">
-        <v>107.1934027303972</v>
+        <v>107.1933901629431</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -4214,10 +4215,10 @@
         <v>44991</v>
       </c>
       <c r="B31" s="1">
-        <v>151.6332550048828</v>
+        <v>151.6332702636719</v>
       </c>
       <c r="C31" s="1">
-        <v>109.1806962690783</v>
+        <v>109.1806832649442</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -4225,10 +4226,10 @@
         <v>44992</v>
       </c>
       <c r="B32" s="1">
-        <v>149.4351196289062</v>
+        <v>149.4351348876953</v>
       </c>
       <c r="C32" s="1">
-        <v>107.5979699018636</v>
+        <v>107.5979572455116</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -4236,10 +4237,10 @@
         <v>44993</v>
       </c>
       <c r="B33" s="1">
-        <v>150.6869812011719</v>
+        <v>150.6869659423828</v>
       </c>
       <c r="C33" s="1">
-        <v>108.499349471194</v>
+        <v>108.4993146431684</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -4247,10 +4248,10 @@
         <v>44994</v>
       </c>
       <c r="B34" s="1">
-        <v>148.4395599365234</v>
+        <v>148.4395141601562</v>
       </c>
       <c r="C34" s="1">
-        <v>106.88113571936</v>
+        <v>106.8810792733064</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -4258,10 +4259,10 @@
         <v>44995</v>
       </c>
       <c r="B35" s="1">
-        <v>146.37939453125</v>
+        <v>146.3794097900391</v>
       </c>
       <c r="C35" s="1">
-        <v>105.3977520554667</v>
+        <v>105.3977398825818</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -4272,7 +4273,7 @@
         <v>148.3212585449219</v>
       </c>
       <c r="C36" s="1">
-        <v>106.7959550094673</v>
+        <v>106.7959315425429</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -4280,10 +4281,10 @@
         <v>44999</v>
       </c>
       <c r="B37" s="1">
-        <v>150.4109802246094</v>
+        <v>150.4109954833984</v>
       </c>
       <c r="C37" s="1">
-        <v>108.3006201173259</v>
+        <v>108.3006073065762</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -4291,10 +4292,10 @@
         <v>45000</v>
       </c>
       <c r="B38" s="1">
-        <v>150.8052673339844</v>
+        <v>150.8052978515625</v>
       </c>
       <c r="C38" s="1">
-        <v>108.5845191942804</v>
+        <v>108.5845173079518</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -4302,10 +4303,10 @@
         <v>45001</v>
       </c>
       <c r="B39" s="1">
-        <v>153.6244354248047</v>
+        <v>153.6244506835938</v>
       </c>
       <c r="C39" s="1">
-        <v>110.614408581311</v>
+        <v>110.6143952621385</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -4313,10 +4314,10 @@
         <v>45002</v>
       </c>
       <c r="B40" s="1">
-        <v>152.7865600585938</v>
+        <v>152.7865753173828</v>
       </c>
       <c r="C40" s="1">
-        <v>110.0111120559765</v>
+        <v>110.01109886937</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -4324,10 +4325,10 @@
         <v>45005</v>
       </c>
       <c r="B41" s="1">
-        <v>155.1522827148438</v>
+        <v>155.1522979736328</v>
       </c>
       <c r="C41" s="1">
-        <v>111.7145065177032</v>
+        <v>111.7144929567994</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -4335,10 +4336,10 @@
         <v>45006</v>
       </c>
       <c r="B42" s="1">
-        <v>157.0054168701172</v>
+        <v>157.0054626464844</v>
       </c>
       <c r="C42" s="1">
-        <v>113.0488211925827</v>
+        <v>113.0488293120898</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -4346,10 +4347,10 @@
         <v>45007</v>
       </c>
       <c r="B43" s="1">
-        <v>155.5761566162109</v>
+        <v>155.576171875</v>
       </c>
       <c r="C43" s="1">
-        <v>112.0197090122356</v>
+        <v>112.0196953842679</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -4360,7 +4361,7 @@
         <v>156.6604309082031</v>
       </c>
       <c r="C44" s="1">
-        <v>112.8004204870539</v>
+        <v>112.8003957007318</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -4368,10 +4369,10 @@
         <v>45009</v>
       </c>
       <c r="B45" s="1">
-        <v>157.9616088867188</v>
+        <v>157.9615783691406</v>
       </c>
       <c r="C45" s="1">
-        <v>113.7373094146164</v>
+        <v>113.737262448818</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -4382,7 +4383,7 @@
         <v>156.0197296142578</v>
       </c>
       <c r="C46" s="1">
-        <v>112.3390954738093</v>
+        <v>112.3390707888569</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -4393,7 +4394,7 @@
         <v>155.3987121582031</v>
       </c>
       <c r="C47" s="1">
-        <v>111.8919434407997</v>
+        <v>111.8919188541027</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -4401,10 +4402,10 @@
         <v>45014</v>
       </c>
       <c r="B48" s="1">
-        <v>158.4741821289062</v>
+        <v>158.4741668701172</v>
       </c>
       <c r="C48" s="1">
-        <v>114.1063782146571</v>
+        <v>114.106342154565</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -4415,7 +4416,7 @@
         <v>160.0414733886719</v>
       </c>
       <c r="C49" s="1">
-        <v>115.2348770455511</v>
+        <v>115.234851724291</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -4426,7 +4427,7 @@
         <v>162.5451812744141</v>
       </c>
       <c r="C50" s="1">
-        <v>117.0376251974054</v>
+        <v>117.0375994800166</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -4437,7 +4438,7 @@
         <v>163.7970581054688</v>
       </c>
       <c r="C51" s="1">
-        <v>117.9390157535422</v>
+        <v>117.9389898380853</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -4448,7 +4449,7 @@
         <v>163.2647705078125</v>
       </c>
       <c r="C52" s="1">
-        <v>117.5557519996537</v>
+        <v>117.5557261684136</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -4459,7 +4460,7 @@
         <v>161.4214782714844</v>
       </c>
       <c r="C53" s="1">
-        <v>116.2285238148917</v>
+        <v>116.2284982752915</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -4467,10 +4468,10 @@
         <v>45022</v>
       </c>
       <c r="B54" s="1">
-        <v>162.30859375</v>
+        <v>162.3086090087891</v>
       </c>
       <c r="C54" s="1">
-        <v>116.8672747644264</v>
+        <v>116.8672600712736</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -4481,7 +4482,7 @@
         <v>159.7161560058594</v>
       </c>
       <c r="C55" s="1">
-        <v>115.0006383334509</v>
+        <v>115.0006130636615</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -4489,10 +4490,10 @@
         <v>45027</v>
       </c>
       <c r="B56" s="1">
-        <v>158.5037384033203</v>
+        <v>158.5037536621094</v>
       </c>
       <c r="C56" s="1">
-        <v>114.1276596586223</v>
+        <v>114.1276455674618</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -4503,7 +4504,7 @@
         <v>157.8137359619141</v>
       </c>
       <c r="C57" s="1">
-        <v>113.6308362739521</v>
+        <v>113.6308113051576</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -4511,10 +4512,10 @@
         <v>45029</v>
       </c>
       <c r="B58" s="1">
-        <v>163.1957550048828</v>
+        <v>163.1957397460938</v>
       </c>
       <c r="C58" s="1">
-        <v>117.5060586743803</v>
+        <v>117.5060218672557</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -4522,10 +4523,10 @@
         <v>45030</v>
       </c>
       <c r="B59" s="1">
-        <v>162.8507537841797</v>
+        <v>162.8507843017578</v>
       </c>
       <c r="C59" s="1">
-        <v>117.2576469820451</v>
+        <v>117.2576431899174</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -4533,10 +4534,10 @@
         <v>45033</v>
       </c>
       <c r="B60" s="1">
-        <v>162.8704833984375</v>
+        <v>162.8704681396484</v>
       </c>
       <c r="C60" s="1">
-        <v>117.2718529226992</v>
+        <v>117.2718161670381</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -4544,10 +4545,10 @@
         <v>45034</v>
       </c>
       <c r="B61" s="1">
-        <v>164.0927734375</v>
+        <v>164.0927581787109</v>
       </c>
       <c r="C61" s="1">
-        <v>118.151940061258</v>
+        <v>118.15190311221</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -4555,10 +4556,10 @@
         <v>45035</v>
       </c>
       <c r="B62" s="1">
-        <v>165.2362213134766</v>
+        <v>165.2362060546875</v>
       </c>
       <c r="C62" s="1">
-        <v>118.9752583712323</v>
+        <v>118.9752212412715</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -4569,7 +4570,7 @@
         <v>164.2701873779297</v>
       </c>
       <c r="C63" s="1">
-        <v>118.2796836590811</v>
+        <v>118.2796576687672</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -4577,10 +4578,10 @@
         <v>45037</v>
       </c>
       <c r="B64" s="1">
-        <v>162.6634979248047</v>
+        <v>162.6634674072266</v>
       </c>
       <c r="C64" s="1">
-        <v>117.1228168941046</v>
+        <v>117.122769184388</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -4588,10 +4589,10 @@
         <v>45040</v>
       </c>
       <c r="B65" s="1">
-        <v>162.9690551757812</v>
+        <v>162.9690399169922</v>
       </c>
       <c r="C65" s="1">
-        <v>117.3428276919379</v>
+        <v>117.342790920681</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -4599,10 +4600,10 @@
         <v>45041</v>
       </c>
       <c r="B66" s="1">
-        <v>161.4313201904297</v>
+        <v>161.4313354492188</v>
       </c>
       <c r="C66" s="1">
-        <v>116.2356103050091</v>
+        <v>116.2355957506558</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -4613,7 +4614,7 @@
         <v>161.4214782714844</v>
       </c>
       <c r="C67" s="1">
-        <v>116.2285238148917</v>
+        <v>116.2284982752915</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -4621,10 +4622,10 @@
         <v>45043</v>
       </c>
       <c r="B68" s="1">
-        <v>166.0050811767578</v>
+        <v>166.0050659179688</v>
       </c>
       <c r="C68" s="1">
-        <v>119.5288615712935</v>
+        <v>119.5288243196861</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -4632,10 +4633,10 @@
         <v>45044</v>
       </c>
       <c r="B69" s="1">
-        <v>167.2569122314453</v>
+        <v>167.2569274902344</v>
       </c>
       <c r="C69" s="1">
-        <v>120.4302191670111</v>
+        <v>120.4302036909509</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -4646,7 +4647,7 @@
         <v>167.168212890625</v>
       </c>
       <c r="C70" s="1">
-        <v>120.3663528615027</v>
+        <v>120.3663264126723</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -4657,7 +4658,7 @@
         <v>166.1331939697266</v>
       </c>
       <c r="C71" s="1">
-        <v>119.6211067976909</v>
+        <v>119.6210805126179</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -4668,7 +4669,7 @@
         <v>165.0587768554688</v>
       </c>
       <c r="C72" s="1">
-        <v>118.8474927997964</v>
+        <v>118.8474666847143</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -4676,10 +4677,10 @@
         <v>45050</v>
       </c>
       <c r="B73" s="1">
-        <v>163.4224853515625</v>
+        <v>163.4224700927734</v>
       </c>
       <c r="C73" s="1">
-        <v>117.6693116304355</v>
+        <v>117.6692747874383</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -4690,7 +4691,7 @@
         <v>171.0913848876953</v>
       </c>
       <c r="C74" s="1">
-        <v>123.1911596640059</v>
+        <v>123.1911325944634</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -4698,10 +4699,10 @@
         <v>45054</v>
       </c>
       <c r="B75" s="1">
-        <v>171.0223693847656</v>
+        <v>171.0223846435547</v>
       </c>
       <c r="C75" s="1">
-        <v>123.1414663387325</v>
+        <v>123.1414502669134</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -4712,7 +4713,7 @@
         <v>169.3170776367188</v>
       </c>
       <c r="C76" s="1">
-        <v>121.9136028309045</v>
+        <v>121.9135760420874</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -4720,10 +4721,10 @@
         <v>45056</v>
       </c>
       <c r="B77" s="1">
-        <v>171.0815124511719</v>
+        <v>171.0814971923828</v>
       </c>
       <c r="C77" s="1">
-        <v>123.1840512002756</v>
+        <v>123.1840131454912</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -4731,10 +4732,10 @@
         <v>45057</v>
       </c>
       <c r="B78" s="1">
-        <v>171.268798828125</v>
+        <v>171.2687835693359</v>
       </c>
       <c r="C78" s="1">
-        <v>123.318903261829</v>
+        <v>123.3188651774127</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -4742,10 +4743,10 @@
         <v>45058</v>
       </c>
       <c r="B79" s="1">
-        <v>170.3409881591797</v>
+        <v>170.3409729003906</v>
       </c>
       <c r="C79" s="1">
-        <v>122.650850499669</v>
+        <v>122.650812562048</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -4753,10 +4754,10 @@
         <v>45061</v>
       </c>
       <c r="B80" s="1">
-        <v>169.8473968505859</v>
+        <v>169.8474273681641</v>
       </c>
       <c r="C80" s="1">
-        <v>122.2954492867695</v>
+        <v>122.2954443876549</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -4764,10 +4765,10 @@
         <v>45062</v>
       </c>
       <c r="B81" s="1">
-        <v>169.8473968505859</v>
+        <v>169.8474273681641</v>
       </c>
       <c r="C81" s="1">
-        <v>122.2954492867695</v>
+        <v>122.2954443876549</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -4775,10 +4776,10 @@
         <v>45063</v>
       </c>
       <c r="B82" s="1">
-        <v>170.4593963623047</v>
+        <v>170.4594268798828</v>
       </c>
       <c r="C82" s="1">
-        <v>122.7361081172064</v>
+        <v>122.7361031212631</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -4786,10 +4787,10 @@
         <v>45064</v>
       </c>
       <c r="B83" s="1">
-        <v>172.7888946533203</v>
+        <v>172.7888793945312</v>
       </c>
       <c r="C83" s="1">
-        <v>124.4134199005782</v>
+        <v>124.4133815756571</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -4797,10 +4798,10 @@
         <v>45065</v>
       </c>
       <c r="B84" s="1">
-        <v>172.8975372314453</v>
+        <v>172.8974761962891</v>
       </c>
       <c r="C84" s="1">
-        <v>124.49164596203</v>
+        <v>124.4915746595079</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -4811,7 +4812,7 @@
         <v>171.9498901367188</v>
       </c>
       <c r="C85" s="1">
-        <v>123.8093103515712</v>
+        <v>123.8092831461988</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -4819,10 +4820,10 @@
         <v>45069</v>
       </c>
       <c r="B86" s="1">
-        <v>169.343994140625</v>
+        <v>169.3440093994141</v>
       </c>
       <c r="C86" s="1">
-        <v>121.9329835573653</v>
+        <v>121.9329677510935</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -4830,10 +4831,10 @@
         <v>45070</v>
       </c>
       <c r="B87" s="1">
-        <v>169.6203918457031</v>
+        <v>169.6203460693359</v>
       </c>
       <c r="C87" s="1">
-        <v>122.1319985681994</v>
+        <v>122.1319387709809</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -4841,10 +4842,10 @@
         <v>45071</v>
       </c>
       <c r="B88" s="1">
-        <v>170.7555541992188</v>
+        <v>170.7555236816406</v>
       </c>
       <c r="C88" s="1">
-        <v>122.9493510423073</v>
+        <v>122.949302052291</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -4855,7 +4856,7 @@
         <v>173.1640014648438</v>
       </c>
       <c r="C89" s="1">
-        <v>124.6835085619084</v>
+        <v>124.683481164443</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -4863,10 +4864,10 @@
         <v>45076</v>
       </c>
       <c r="B90" s="1">
-        <v>175.0098419189453</v>
+        <v>175.0098571777344</v>
       </c>
       <c r="C90" s="1">
-        <v>126.0125715433365</v>
+        <v>126.012554840632</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -4874,10 +4875,10 @@
         <v>45077</v>
       </c>
       <c r="B91" s="1">
-        <v>174.9605102539062</v>
+        <v>174.9604949951172</v>
       </c>
       <c r="C91" s="1">
-        <v>125.977051198298</v>
+        <v>125.9770125297907</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -4885,10 +4886,10 @@
         <v>45078</v>
       </c>
       <c r="B92" s="1">
-        <v>177.7638244628906</v>
+        <v>177.7637939453125</v>
       </c>
       <c r="C92" s="1">
-        <v>127.995525293496</v>
+        <v>127.9954751946532</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -4896,10 +4897,10 @@
         <v>45079</v>
       </c>
       <c r="B93" s="1">
-        <v>178.6127166748047</v>
+        <v>178.6126708984375</v>
       </c>
       <c r="C93" s="1">
-        <v>128.6067542930397</v>
+        <v>128.6066930730838</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -4910,7 +4911,7 @@
         <v>177.2604064941406</v>
       </c>
       <c r="C94" s="1">
-        <v>127.6330485772855</v>
+        <v>127.6330205316998</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -4918,10 +4919,10 @@
         <v>45083</v>
       </c>
       <c r="B95" s="1">
-        <v>176.8951721191406</v>
+        <v>176.8952178955078</v>
       </c>
       <c r="C95" s="1">
-        <v>127.3700683796856</v>
+        <v>127.370073352298</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -4932,7 +4933,7 @@
         <v>175.5231475830078</v>
       </c>
       <c r="C96" s="1">
-        <v>126.3821677100837</v>
+        <v>126.3821399393616</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -4943,7 +4944,7 @@
         <v>178.2376251220703</v>
       </c>
       <c r="C97" s="1">
-        <v>128.3366766185159</v>
+        <v>128.3366484183177</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -4951,10 +4952,10 @@
         <v>45086</v>
       </c>
       <c r="B98" s="1">
-        <v>178.6225738525391</v>
+        <v>178.6226043701172</v>
       </c>
       <c r="C98" s="1">
-        <v>128.6138517699635</v>
+        <v>128.6138454824679</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -4962,10 +4963,10 @@
         <v>45089</v>
       </c>
       <c r="B99" s="1">
-        <v>181.4160003662109</v>
+        <v>181.4160308837891</v>
       </c>
       <c r="C99" s="1">
-        <v>130.6252064146249</v>
+        <v>130.6251996851622</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -4973,10 +4974,10 @@
         <v>45090</v>
       </c>
       <c r="B100" s="1">
-        <v>180.9422149658203</v>
+        <v>180.9422302246094</v>
       </c>
       <c r="C100" s="1">
-        <v>130.2840660764115</v>
+        <v>130.2840484351056</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -4984,10 +4985,10 @@
         <v>45091</v>
       </c>
       <c r="B101" s="1">
-        <v>181.5739440917969</v>
+        <v>181.5739593505859</v>
       </c>
       <c r="C101" s="1">
-        <v>130.7389308475025</v>
+        <v>130.7389131062463</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -4995,10 +4996,10 @@
         <v>45092</v>
       </c>
       <c r="B102" s="1">
-        <v>183.6073303222656</v>
+        <v>183.6073455810547</v>
       </c>
       <c r="C102" s="1">
-        <v>132.2030326661925</v>
+        <v>132.2030146032204</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -5009,7 +5010,7 @@
         <v>182.5314331054688</v>
       </c>
       <c r="C103" s="1">
-        <v>131.4283529480788</v>
+        <v>131.4283240685278</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -5020,7 +5021,7 @@
         <v>182.6202697753906</v>
       </c>
       <c r="C104" s="1">
-        <v>131.4923181348446</v>
+        <v>131.4922892412381</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -5028,10 +5029,10 @@
         <v>45098</v>
       </c>
       <c r="B105" s="1">
-        <v>181.5838317871094</v>
+        <v>181.5838470458984</v>
       </c>
       <c r="C105" s="1">
-        <v>130.7460502980391</v>
+        <v>130.7460325552186</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -5042,7 +5043,7 @@
         <v>184.5845489501953</v>
       </c>
       <c r="C106" s="1">
-        <v>132.9066607074229</v>
+        <v>132.9066315030343</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -5050,10 +5051,10 @@
         <v>45100</v>
       </c>
       <c r="B107" s="1">
-        <v>184.2686920166016</v>
+        <v>184.2686767578125</v>
       </c>
       <c r="C107" s="1">
-        <v>132.6792338152806</v>
+        <v>132.679193674062</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -5061,10 +5062,10 @@
         <v>45103</v>
       </c>
       <c r="B108" s="1">
-        <v>182.8769073486328</v>
+        <v>182.8769226074219</v>
       </c>
       <c r="C108" s="1">
-        <v>131.6771052314118</v>
+        <v>131.6770872840049</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -5072,10 +5073,10 @@
         <v>45104</v>
       </c>
       <c r="B109" s="1">
-        <v>185.6308746337891</v>
+        <v>185.630859375</v>
       </c>
       <c r="C109" s="1">
-        <v>133.660047994765</v>
+        <v>133.6600076380261</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -5083,10 +5084,10 @@
         <v>45105</v>
       </c>
       <c r="B110" s="1">
-        <v>186.8054656982422</v>
+        <v>186.8054809570312</v>
       </c>
       <c r="C110" s="1">
-        <v>134.5057903765684</v>
+        <v>134.5057718075973</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -5097,7 +5098,7 @@
         <v>187.1410980224609</v>
       </c>
       <c r="C111" s="1">
-        <v>134.747456169784</v>
+        <v>134.7474265609062</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -5105,10 +5106,10 @@
         <v>45107</v>
       </c>
       <c r="B112" s="1">
-        <v>191.4645385742188</v>
+        <v>191.4645233154297</v>
       </c>
       <c r="C112" s="1">
-        <v>137.8604688773439</v>
+        <v>137.8604275976211</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -5116,10 +5117,10 @@
         <v>45110</v>
       </c>
       <c r="B113" s="1">
-        <v>189.9740295410156</v>
+        <v>189.9740447998047</v>
       </c>
       <c r="C113" s="1">
-        <v>136.7872556561727</v>
+        <v>136.7872365858814</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -5127,10 +5128,10 @@
         <v>45112</v>
       </c>
       <c r="B114" s="1">
-        <v>188.858642578125</v>
+        <v>188.8586273193359</v>
       </c>
       <c r="C114" s="1">
-        <v>135.984142083138</v>
+        <v>135.9841012157118</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -5138,10 +5139,10 @@
         <v>45113</v>
       </c>
       <c r="B115" s="1">
-        <v>189.3324432373047</v>
+        <v>189.3324127197266</v>
       </c>
       <c r="C115" s="1">
-        <v>136.3252934081579</v>
+        <v>136.3252414789644</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -5149,10 +5150,10 @@
         <v>45114</v>
       </c>
       <c r="B116" s="1">
-        <v>188.2169952392578</v>
+        <v>188.2170104980469</v>
       </c>
       <c r="C116" s="1">
-        <v>135.5221358878977</v>
+        <v>135.5221170955988</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -5160,10 +5161,10 @@
         <v>45117</v>
       </c>
       <c r="B117" s="1">
-        <v>186.1737518310547</v>
+        <v>186.1737670898438</v>
       </c>
       <c r="C117" s="1">
-        <v>134.0509365922838</v>
+        <v>134.0509181232605</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -5171,10 +5172,10 @@
         <v>45118</v>
       </c>
       <c r="B118" s="1">
-        <v>185.6506042480469</v>
+        <v>185.6506195068359</v>
       </c>
       <c r="C118" s="1">
-        <v>133.6742539354191</v>
+        <v>133.6742355491666</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -5182,10 +5183,10 @@
         <v>45119</v>
       </c>
       <c r="B119" s="1">
-        <v>187.3188018798828</v>
+        <v>187.3187866210938</v>
       </c>
       <c r="C119" s="1">
-        <v>134.8754085169284</v>
+        <v>134.8753678931309</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -5193,10 +5194,10 @@
         <v>45120</v>
       </c>
       <c r="B120" s="1">
-        <v>188.0788116455078</v>
+        <v>188.0788269042969</v>
       </c>
       <c r="C120" s="1">
-        <v>135.422639369287</v>
+        <v>135.4226205988511</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -5207,7 +5208,7 @@
         <v>188.2268981933594</v>
       </c>
       <c r="C121" s="1">
-        <v>135.5292663252407</v>
+        <v>135.5292365445711</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -5215,10 +5216,10 @@
         <v>45124</v>
       </c>
       <c r="B122" s="1">
-        <v>191.4842681884766</v>
+        <v>191.4842834472656</v>
       </c>
       <c r="C122" s="1">
-        <v>137.8746748179981</v>
+        <v>137.8746555087615</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -5229,7 +5230,7 @@
         <v>191.2276306152344</v>
       </c>
       <c r="C123" s="1">
-        <v>137.6898877214308</v>
+        <v>137.6898574659947</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -5237,10 +5238,10 @@
         <v>45126</v>
       </c>
       <c r="B124" s="1">
-        <v>192.5799255371094</v>
+        <v>192.5799407958984</v>
       </c>
       <c r="C124" s="1">
-        <v>138.6635824503786</v>
+        <v>138.6635629677907</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -5251,7 +5252,7 @@
         <v>190.6353759765625</v>
       </c>
       <c r="C125" s="1">
-        <v>137.2634458184544</v>
+        <v>137.263415656723</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -5262,7 +5263,7 @@
         <v>189.4607543945312</v>
       </c>
       <c r="C126" s="1">
-        <v>136.4176814630383</v>
+        <v>136.4176514871518</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -5273,7 +5274,7 @@
         <v>190.2602996826172</v>
       </c>
       <c r="C127" s="1">
-        <v>136.9933791307371</v>
+        <v>136.993349028349</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -5284,7 +5285,7 @@
         <v>191.1190490722656</v>
       </c>
       <c r="C128" s="1">
-        <v>137.6117056072045</v>
+        <v>137.6116753689479</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -5295,7 +5296,7 @@
         <v>191.9877014160156</v>
       </c>
       <c r="C129" s="1">
-        <v>138.237162521015</v>
+        <v>138.2371321453229</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -5306,7 +5307,7 @@
         <v>190.7242126464844</v>
       </c>
       <c r="C130" s="1">
-        <v>137.3274110052203</v>
+        <v>137.3273808294334</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -5314,10 +5315,10 @@
         <v>45135</v>
       </c>
       <c r="B131" s="1">
-        <v>193.300537109375</v>
+        <v>193.3004913330078</v>
       </c>
       <c r="C131" s="1">
-        <v>139.1824453686546</v>
+        <v>139.1823818248378</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -5328,7 +5329,7 @@
         <v>193.9124908447266</v>
       </c>
       <c r="C132" s="1">
-        <v>139.6230712386723</v>
+        <v>139.6230405584461</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -5336,10 +5337,10 @@
         <v>45139</v>
       </c>
       <c r="B133" s="1">
-        <v>193.0833587646484</v>
+        <v>193.0833435058594</v>
       </c>
       <c r="C133" s="1">
-        <v>139.0260701533956</v>
+        <v>139.026028617548</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -5347,10 +5348,10 @@
         <v>45140</v>
       </c>
       <c r="B134" s="1">
-        <v>190.0924530029297</v>
+        <v>190.0924835205078</v>
       </c>
       <c r="C134" s="1">
-        <v>136.8725242605165</v>
+        <v>136.8725161582926</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -5358,10 +5359,10 @@
         <v>45141</v>
       </c>
       <c r="B135" s="1">
-        <v>188.7006988525391</v>
+        <v>188.70068359375</v>
       </c>
       <c r="C135" s="1">
-        <v>135.8704176502605</v>
+        <v>135.8703768078236</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -5369,10 +5370,10 @@
         <v>45142</v>
       </c>
       <c r="B136" s="1">
-        <v>179.6392974853516</v>
+        <v>179.6392822265625</v>
       </c>
       <c r="C136" s="1">
-        <v>129.3459246529213</v>
+        <v>129.345885244151</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -5380,10 +5381,10 @@
         <v>45145</v>
       </c>
       <c r="B137" s="1">
-        <v>176.5398559570312</v>
+        <v>176.5398254394531</v>
       </c>
       <c r="C137" s="1">
-        <v>127.1142296062351</v>
+        <v>127.1141797010447</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -5391,10 +5392,10 @@
         <v>45146</v>
       </c>
       <c r="B138" s="1">
-        <v>177.4775543212891</v>
+        <v>177.4775695800781</v>
       </c>
       <c r="C138" s="1">
-        <v>127.7894018189317</v>
+        <v>127.7893847257936</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -5402,10 +5403,10 @@
         <v>45147</v>
       </c>
       <c r="B139" s="1">
-        <v>175.8883666992188</v>
+        <v>175.8883514404297</v>
       </c>
       <c r="C139" s="1">
-        <v>126.6451369208772</v>
+        <v>126.6450981055674</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -5416,7 +5417,7 @@
         <v>175.6712188720703</v>
       </c>
       <c r="C140" s="1">
-        <v>126.4887836792309</v>
+        <v>126.4887558850815</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -5424,10 +5425,10 @@
         <v>45149</v>
       </c>
       <c r="B141" s="1">
-        <v>175.7304992675781</v>
+        <v>175.7305145263672</v>
       </c>
       <c r="C141" s="1">
-        <v>126.5314674220316</v>
+        <v>126.531450605307</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -5435,10 +5436,10 @@
         <v>45152</v>
       </c>
       <c r="B142" s="1">
-        <v>177.3811645507812</v>
+        <v>177.3811798095703</v>
       </c>
       <c r="C142" s="1">
-        <v>127.719998163006</v>
+        <v>127.7199810851183</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -5449,7 +5450,7 @@
         <v>175.3944549560547</v>
       </c>
       <c r="C143" s="1">
-        <v>126.2895049850436</v>
+        <v>126.289477234683</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -5457,10 +5458,10 @@
         <v>45154</v>
       </c>
       <c r="B144" s="1">
-        <v>174.5246429443359</v>
+        <v>174.5246276855469</v>
       </c>
       <c r="C144" s="1">
-        <v>125.663213073948</v>
+        <v>125.6631744744023</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -5471,7 +5472,7 @@
         <v>171.9844055175781</v>
       </c>
       <c r="C145" s="1">
-        <v>123.8341625076111</v>
+        <v>123.8341352967777</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -5482,7 +5483,7 @@
         <v>172.4687347412109</v>
       </c>
       <c r="C146" s="1">
-        <v>124.1828947290357</v>
+        <v>124.1828674415733</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -5490,10 +5491,10 @@
         <v>45159</v>
       </c>
       <c r="B147" s="1">
-        <v>173.8030853271484</v>
+        <v>173.8031005859375</v>
       </c>
       <c r="C147" s="1">
-        <v>125.1436689736763</v>
+        <v>125.1436524619011</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -5501,10 +5502,10 @@
         <v>45160</v>
       </c>
       <c r="B148" s="1">
-        <v>175.1769866943359</v>
+        <v>175.177001953125</v>
       </c>
       <c r="C148" s="1">
-        <v>126.1329210204634</v>
+        <v>126.1329042913138</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -5512,10 +5513,10 @@
         <v>45161</v>
       </c>
       <c r="B149" s="1">
-        <v>179.0219421386719</v>
+        <v>179.0219268798828</v>
       </c>
       <c r="C149" s="1">
-        <v>128.9014094534437</v>
+        <v>128.9013701423494</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -5526,7 +5527,7 @@
         <v>174.3368377685547</v>
       </c>
       <c r="C150" s="1">
-        <v>125.5279874609776</v>
+        <v>125.5279598779498</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -5534,10 +5535,10 @@
         <v>45163</v>
       </c>
       <c r="B151" s="1">
-        <v>176.5410308837891</v>
+        <v>176.5410003662109</v>
       </c>
       <c r="C151" s="1">
-        <v>127.1150755903266</v>
+        <v>127.1150256849503</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -5545,10 +5546,10 @@
         <v>45166</v>
       </c>
       <c r="B152" s="1">
-        <v>178.1027221679688</v>
+        <v>178.1027069091797</v>
       </c>
       <c r="C152" s="1">
-        <v>128.2395422632777</v>
+        <v>128.2395030976195</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -5556,10 +5557,10 @@
         <v>45167</v>
       </c>
       <c r="B153" s="1">
-        <v>181.9871826171875</v>
+        <v>181.9871520996094</v>
       </c>
       <c r="C153" s="1">
-        <v>131.0364755379854</v>
+        <v>131.0364247709361</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -5570,7 +5571,7 @@
         <v>185.4762878417969</v>
       </c>
       <c r="C154" s="1">
-        <v>133.5487406592919</v>
+        <v>133.5487113138152</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -5578,10 +5579,10 @@
         <v>45169</v>
       </c>
       <c r="B155" s="1">
-        <v>185.6937255859375</v>
+        <v>185.6937408447266</v>
       </c>
       <c r="C155" s="1">
-        <v>133.7053026502594</v>
+        <v>133.7052842571844</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -5592,7 +5593,7 @@
         <v>187.2653198242188</v>
       </c>
       <c r="C156" s="1">
-        <v>134.8368997605536</v>
+        <v>134.8368701320218</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -5600,10 +5601,10 @@
         <v>45174</v>
       </c>
       <c r="B157" s="1">
-        <v>187.5025329589844</v>
+        <v>187.5025177001953</v>
       </c>
       <c r="C157" s="1">
-        <v>135.0077006525943</v>
+        <v>135.0076599997275</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -5611,10 +5612,10 @@
         <v>45175</v>
       </c>
       <c r="B158" s="1">
-        <v>180.7911987304688</v>
+        <v>180.7911834716797</v>
       </c>
       <c r="C158" s="1">
-        <v>130.1753296536321</v>
+        <v>130.1752900626116</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -5622,10 +5623,10 @@
         <v>45176</v>
       </c>
       <c r="B159" s="1">
-        <v>175.503173828125</v>
+        <v>175.5031585693359</v>
       </c>
       <c r="C159" s="1">
-        <v>126.3677859805274</v>
+        <v>126.3677472261616</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -5633,10 +5634,10 @@
         <v>45177</v>
       </c>
       <c r="B160" s="1">
-        <v>176.1159820556641</v>
+        <v>176.115966796875</v>
       </c>
       <c r="C160" s="1">
-        <v>126.8090271117026</v>
+        <v>126.8089882603802</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -5644,10 +5645,10 @@
         <v>45180</v>
       </c>
       <c r="B161" s="1">
-        <v>177.2822875976562</v>
+        <v>177.2823181152344</v>
       </c>
       <c r="C161" s="1">
-        <v>127.6488036576397</v>
+        <v>127.6487975822</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -5655,10 +5656,10 @@
         <v>45181</v>
       </c>
       <c r="B162" s="1">
-        <v>174.2577972412109</v>
+        <v>174.2577819824219</v>
       </c>
       <c r="C162" s="1">
-        <v>125.4710758039101</v>
+        <v>125.4710372465839</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -5666,10 +5667,10 @@
         <v>45182</v>
       </c>
       <c r="B163" s="1">
-        <v>172.1919708251953</v>
+        <v>172.1919860839844</v>
       </c>
       <c r="C163" s="1">
-        <v>123.9836160348484</v>
+        <v>123.9835997779787</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -5677,10 +5678,10 @@
         <v>45183</v>
       </c>
       <c r="B164" s="1">
-        <v>173.7042388916016</v>
+        <v>173.7042694091797</v>
       </c>
       <c r="C164" s="1">
-        <v>125.0724964419228</v>
+        <v>125.0724909325907</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -5688,10 +5689,10 @@
         <v>45184</v>
       </c>
       <c r="B165" s="1">
-        <v>172.9826965332031</v>
+        <v>172.9827117919922</v>
       </c>
       <c r="C165" s="1">
-        <v>124.5529633284574</v>
+        <v>124.5529469464815</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -5702,7 +5703,7 @@
         <v>175.9084320068359</v>
       </c>
       <c r="C166" s="1">
-        <v>126.6595845712717</v>
+        <v>126.6595567395912</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -5710,10 +5711,10 @@
         <v>45188</v>
       </c>
       <c r="B167" s="1">
-        <v>176.9956817626953</v>
+        <v>176.9956970214844</v>
       </c>
       <c r="C167" s="1">
-        <v>127.4424384733349</v>
+        <v>127.4424214564371</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -5721,10 +5722,10 @@
         <v>45189</v>
       </c>
       <c r="B168" s="1">
-        <v>173.4571380615234</v>
+        <v>173.4571533203125</v>
       </c>
       <c r="C168" s="1">
-        <v>124.8945760993453</v>
+        <v>124.8945596423048</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -5732,10 +5733,10 @@
         <v>45190</v>
       </c>
       <c r="B169" s="1">
-        <v>171.9151916503906</v>
+        <v>171.9152069091797</v>
       </c>
       <c r="C169" s="1">
-        <v>123.7843263538547</v>
+        <v>123.7843101407761</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -5743,10 +5744,10 @@
         <v>45191</v>
       </c>
       <c r="B170" s="1">
-        <v>172.7652130126953</v>
+        <v>172.7652435302734</v>
       </c>
       <c r="C170" s="1">
-        <v>124.3963683770707</v>
+        <v>124.3963630163084</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -5754,10 +5755,10 @@
         <v>45194</v>
       </c>
       <c r="B171" s="1">
-        <v>174.0403137207031</v>
+        <v>174.0402984619141</v>
       </c>
       <c r="C171" s="1">
-        <v>125.3144808525234</v>
+        <v>125.3144423296068</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -5765,10 +5766,10 @@
         <v>45195</v>
       </c>
       <c r="B172" s="1">
-        <v>169.9680480957031</v>
+        <v>169.968017578125</v>
       </c>
       <c r="C172" s="1">
-        <v>122.3823219648453</v>
+        <v>122.3822730994257</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -5776,10 +5777,10 @@
         <v>45196</v>
       </c>
       <c r="B173" s="1">
-        <v>168.4557647705078</v>
+        <v>168.4557495117188</v>
       </c>
       <c r="C173" s="1">
-        <v>121.2934305709646</v>
+        <v>121.2933929316177</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -5787,10 +5788,10 @@
         <v>45197</v>
       </c>
       <c r="B174" s="1">
-        <v>168.7127380371094</v>
+        <v>168.7127532958984</v>
       </c>
       <c r="C174" s="1">
-        <v>121.4784593772722</v>
+        <v>121.4784436708758</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -5798,10 +5799,10 @@
         <v>45198</v>
       </c>
       <c r="B175" s="1">
-        <v>169.2267456054688</v>
+        <v>169.2266998291016</v>
       </c>
       <c r="C175" s="1">
-        <v>121.848560937113</v>
+        <v>121.8485012021761</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -5809,10 +5810,10 @@
         <v>45201</v>
       </c>
       <c r="B176" s="1">
-        <v>171.7373046875</v>
+        <v>171.7372894287109</v>
       </c>
       <c r="C176" s="1">
-        <v>123.6562421650337</v>
+        <v>123.6562040064919</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -5820,10 +5821,10 @@
         <v>45202</v>
       </c>
       <c r="B177" s="1">
-        <v>170.4029083251953</v>
+        <v>170.4029235839844</v>
       </c>
       <c r="C177" s="1">
-        <v>122.695434959974</v>
+        <v>122.6954189861641</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -5831,10 +5832,10 @@
         <v>45203</v>
       </c>
       <c r="B178" s="1">
-        <v>171.6483764648438</v>
+        <v>171.6483459472656</v>
       </c>
       <c r="C178" s="1">
-        <v>123.5922110574296</v>
+        <v>123.5921619261538</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -5845,7 +5846,7 @@
         <v>172.8838653564453</v>
       </c>
       <c r="C179" s="1">
-        <v>124.4818017835102</v>
+        <v>124.4817744303672</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -5856,7 +5857,7 @@
         <v>175.4339752197266</v>
       </c>
       <c r="C180" s="1">
-        <v>126.3179608135774</v>
+        <v>126.317933056964</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -5864,10 +5865,10 @@
         <v>45208</v>
       </c>
       <c r="B181" s="1">
-        <v>176.9166259765625</v>
+        <v>176.9165954589844</v>
       </c>
       <c r="C181" s="1">
-        <v>127.385515829461</v>
+        <v>127.3854658646593</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -5878,7 +5879,7 @@
         <v>176.3235626220703</v>
       </c>
       <c r="C182" s="1">
-        <v>126.9584916257463</v>
+        <v>126.9584637283851</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -5889,7 +5890,7 @@
         <v>177.7172088623047</v>
       </c>
       <c r="C183" s="1">
-        <v>127.9619605999939</v>
+        <v>127.9619324821344</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -5897,10 +5898,10 @@
         <v>45211</v>
       </c>
       <c r="B184" s="1">
-        <v>178.6166687011719</v>
+        <v>178.61669921875</v>
       </c>
       <c r="C184" s="1">
-        <v>128.6095998758931</v>
+        <v>128.6095935893317</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -5908,10 +5909,10 @@
         <v>45212</v>
       </c>
       <c r="B185" s="1">
-        <v>176.7782440185547</v>
+        <v>176.7782287597656</v>
       </c>
       <c r="C185" s="1">
-        <v>127.2858764823674</v>
+        <v>127.2858375262639</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -5922,7 +5923,7 @@
         <v>176.6497192382812</v>
       </c>
       <c r="C186" s="1">
-        <v>127.1933346121976</v>
+        <v>127.1933066632329</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -5930,10 +5931,10 @@
         <v>45216</v>
       </c>
       <c r="B187" s="1">
-        <v>175.097900390625</v>
+        <v>175.0979461669922</v>
       </c>
       <c r="C187" s="1">
-        <v>126.0759764029767</v>
+        <v>126.0759816599479</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -5941,10 +5942,10 @@
         <v>45217</v>
       </c>
       <c r="B188" s="1">
-        <v>173.8030853271484</v>
+        <v>173.8031005859375</v>
       </c>
       <c r="C188" s="1">
-        <v>125.1436689736763</v>
+        <v>125.1436524619011</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -5952,10 +5953,10 @@
         <v>45218</v>
       </c>
       <c r="B189" s="1">
-        <v>173.427490234375</v>
+        <v>173.4275207519531</v>
       </c>
       <c r="C189" s="1">
-        <v>124.8732287345418</v>
+        <v>124.8732232689961</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -5963,10 +5964,10 @@
         <v>45219</v>
       </c>
       <c r="B190" s="1">
-        <v>170.8773803710938</v>
+        <v>170.8773956298828</v>
       </c>
       <c r="C190" s="1">
-        <v>123.0370697044747</v>
+        <v>123.0370536555953</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -5974,10 +5975,10 @@
         <v>45222</v>
       </c>
       <c r="B191" s="1">
-        <v>170.9959869384766</v>
+        <v>170.9960021972656</v>
       </c>
       <c r="C191" s="1">
-        <v>123.1224701504951</v>
+        <v>123.1224540828502</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -5985,10 +5986,10 @@
         <v>45223</v>
       </c>
       <c r="B192" s="1">
-        <v>171.4308776855469</v>
+        <v>171.430908203125</v>
       </c>
       <c r="C192" s="1">
-        <v>123.4356051192365</v>
+        <v>123.4355999695885</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -5996,10 +5997,10 @@
         <v>45224</v>
       </c>
       <c r="B193" s="1">
-        <v>169.1179962158203</v>
+        <v>169.1180114746094</v>
       </c>
       <c r="C193" s="1">
-        <v>121.7702579680165</v>
+        <v>121.7702421975014</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -6007,10 +6008,10 @@
         <v>45225</v>
       </c>
       <c r="B194" s="1">
-        <v>164.9567718505859</v>
+        <v>164.9567565917969</v>
       </c>
       <c r="C194" s="1">
-        <v>118.7740459991215</v>
+        <v>118.7740089133743</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -6018,10 +6019,10 @@
         <v>45226</v>
       </c>
       <c r="B195" s="1">
-        <v>166.2713470458984</v>
+        <v>166.2713317871094</v>
       </c>
       <c r="C195" s="1">
-        <v>119.7205813426888</v>
+        <v>119.7205440489537</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -6029,10 +6030,10 @@
         <v>45229</v>
       </c>
       <c r="B196" s="1">
-        <v>168.3173828125</v>
+        <v>168.3173675537109</v>
       </c>
       <c r="C196" s="1">
-        <v>121.1937912238709</v>
+        <v>121.1937536064184</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -6040,10 +6041,10 @@
         <v>45230</v>
       </c>
       <c r="B197" s="1">
-        <v>168.7918090820312</v>
+        <v>168.7918395996094</v>
       </c>
       <c r="C197" s="1">
-        <v>121.5353930079525</v>
+        <v>121.5353882758496</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -6051,10 +6052,10 @@
         <v>45231</v>
       </c>
       <c r="B198" s="1">
-        <v>171.9547729492188</v>
+        <v>171.9547271728516</v>
       </c>
       <c r="C198" s="1">
-        <v>123.812826129614</v>
+        <v>123.8127659630571</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -6062,10 +6063,10 @@
         <v>45232</v>
       </c>
       <c r="B199" s="1">
-        <v>175.5130462646484</v>
+        <v>175.5130767822266</v>
       </c>
       <c r="C199" s="1">
-        <v>126.3748944442577</v>
+        <v>126.3748886487418</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -6073,10 +6074,10 @@
         <v>45233</v>
       </c>
       <c r="B200" s="1">
-        <v>174.6037139892578</v>
+        <v>174.6036834716797</v>
       </c>
       <c r="C200" s="1">
-        <v>125.7201467046283</v>
+        <v>125.7200971057682</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -6087,7 +6088,7 @@
         <v>177.1538238525391</v>
       </c>
       <c r="C201" s="1">
-        <v>127.5563057346954</v>
+        <v>127.5562777059729</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -6095,10 +6096,10 @@
         <v>45237</v>
       </c>
       <c r="B202" s="1">
-        <v>179.7138366699219</v>
+        <v>179.7138214111328</v>
       </c>
       <c r="C202" s="1">
-        <v>129.3995952021056</v>
+        <v>129.3995557815419</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -6106,10 +6107,10 @@
         <v>45238</v>
       </c>
       <c r="B203" s="1">
-        <v>180.7714233398438</v>
+        <v>180.7714385986328</v>
       </c>
       <c r="C203" s="1">
-        <v>130.1610907525589</v>
+        <v>130.1610731382751</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -6117,10 +6118,10 @@
         <v>45239</v>
       </c>
       <c r="B204" s="1">
-        <v>180.2969970703125</v>
+        <v>180.2969818115234</v>
       </c>
       <c r="C204" s="1">
-        <v>129.8194889684773</v>
+        <v>129.8194494556478</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -6131,7 +6132,7 @@
         <v>184.4834899902344</v>
       </c>
       <c r="C205" s="1">
-        <v>132.8338950887437</v>
+        <v>132.8338659003444</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -6142,7 +6143,7 @@
         <v>182.8999328613281</v>
       </c>
       <c r="C206" s="1">
-        <v>131.6936843222448</v>
+        <v>131.6936553843909</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -6150,10 +6151,10 @@
         <v>45244</v>
       </c>
       <c r="B207" s="1">
-        <v>185.5128021240234</v>
+        <v>185.5128173828125</v>
       </c>
       <c r="C207" s="1">
-        <v>133.575032086968</v>
+        <v>133.5750137225182</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -6161,10 +6162,10 @@
         <v>45245</v>
       </c>
       <c r="B208" s="1">
-        <v>186.0769195556641</v>
+        <v>186.0769348144531</v>
       </c>
       <c r="C208" s="1">
-        <v>133.9812143189729</v>
+        <v>133.9811958652701</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -6172,10 +6173,10 @@
         <v>45246</v>
       </c>
       <c r="B209" s="1">
-        <v>187.7594909667969</v>
+        <v>187.7594757080078</v>
       </c>
       <c r="C209" s="1">
-        <v>135.1927184720956</v>
+        <v>135.1926777785737</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -6183,10 +6184,10 @@
         <v>45247</v>
       </c>
       <c r="B210" s="1">
-        <v>187.7396697998047</v>
+        <v>187.7396392822266</v>
       </c>
       <c r="C210" s="1">
-        <v>135.1784466106032</v>
+        <v>135.1783949334134</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -6197,7 +6198,7 @@
         <v>189.4815673828125</v>
       </c>
       <c r="C211" s="1">
-        <v>136.4326674669456</v>
+        <v>136.4326374877662</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -6208,7 +6209,7 @@
         <v>188.6798858642578</v>
       </c>
       <c r="C212" s="1">
-        <v>135.8554316463532</v>
+        <v>135.8554017940133</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -6216,10 +6217,10 @@
         <v>45252</v>
       </c>
       <c r="B213" s="1">
-        <v>189.3430023193359</v>
+        <v>189.3429870605469</v>
       </c>
       <c r="C213" s="1">
-        <v>136.3328962781754</v>
+        <v>136.3328553341153</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -6230,7 +6231,7 @@
         <v>188.0167694091797</v>
       </c>
       <c r="C214" s="1">
-        <v>135.3779670145309</v>
+        <v>135.3779372671072</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -6241,7 +6242,7 @@
         <v>187.8386383056641</v>
       </c>
       <c r="C215" s="1">
-        <v>135.2497070368078</v>
+        <v>135.2496773175674</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -6249,10 +6250,10 @@
         <v>45258</v>
       </c>
       <c r="B216" s="1">
-        <v>188.4423675537109</v>
+        <v>188.4423370361328</v>
       </c>
       <c r="C216" s="1">
-        <v>135.6844110181847</v>
+        <v>135.6843592298163</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -6263,7 +6264,7 @@
         <v>187.4229431152344</v>
       </c>
       <c r="C217" s="1">
-        <v>134.950393470497</v>
+        <v>134.9503638170266</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -6271,10 +6272,10 @@
         <v>45260</v>
       </c>
       <c r="B218" s="1">
-        <v>187.9969787597656</v>
+        <v>187.9970092773438</v>
       </c>
       <c r="C218" s="1">
-        <v>135.3637171266513</v>
+        <v>135.3637093559667</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -6282,10 +6283,10 @@
         <v>45261</v>
       </c>
       <c r="B219" s="1">
-        <v>189.2737579345703</v>
+        <v>189.2737121582031</v>
       </c>
       <c r="C219" s="1">
-        <v>136.2830381508062</v>
+        <v>136.2829752440938</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -6293,10 +6294,10 @@
         <v>45264</v>
       </c>
       <c r="B220" s="1">
-        <v>187.4823303222656</v>
+        <v>187.4823455810547</v>
       </c>
       <c r="C220" s="1">
-        <v>134.9931541209423</v>
+        <v>134.9931354448798</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -6304,10 +6305,10 @@
         <v>45265</v>
       </c>
       <c r="B221" s="1">
-        <v>191.4312896728516</v>
+        <v>191.4313049316406</v>
       </c>
       <c r="C221" s="1">
-        <v>137.8365286262339</v>
+        <v>137.8365093253795</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -6315,10 +6316,10 @@
         <v>45266</v>
       </c>
       <c r="B222" s="1">
-        <v>190.3426361083984</v>
+        <v>190.3426513671875</v>
       </c>
       <c r="C222" s="1">
-        <v>137.0526639379834</v>
+        <v>137.0526448093724</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -6326,10 +6327,10 @@
         <v>45267</v>
       </c>
       <c r="B223" s="1">
-        <v>192.2725982666016</v>
+        <v>192.2725830078125</v>
       </c>
       <c r="C223" s="1">
-        <v>138.4422971830048</v>
+        <v>138.4422557754332</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -6337,10 +6338,10 @@
         <v>45268</v>
       </c>
       <c r="B224" s="1">
-        <v>193.6977844238281</v>
+        <v>193.6978149414062</v>
       </c>
       <c r="C224" s="1">
-        <v>139.4684758860475</v>
+        <v>139.4684672133994</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -6351,7 +6352,7 @@
         <v>191.1937866210938</v>
       </c>
       <c r="C225" s="1">
-        <v>137.6655189848718</v>
+        <v>137.6654887347904</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -6359,10 +6360,10 @@
         <v>45272</v>
       </c>
       <c r="B226" s="1">
-        <v>192.7080535888672</v>
+        <v>192.7080688476562</v>
       </c>
       <c r="C226" s="1">
-        <v>138.7558386635825</v>
+        <v>138.7558191607224</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -6373,7 +6374,7 @@
         <v>195.9246520996094</v>
       </c>
       <c r="C227" s="1">
-        <v>141.0718904096826</v>
+        <v>141.0718594110985</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -6384,7 +6385,7 @@
         <v>196.0730895996094</v>
       </c>
       <c r="C228" s="1">
-        <v>141.1787700621831</v>
+        <v>141.1787390401137</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -6395,7 +6396,7 @@
         <v>195.5386505126953</v>
       </c>
       <c r="C229" s="1">
-        <v>140.7939571685945</v>
+        <v>140.7939262310824</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -6406,7 +6407,7 @@
         <v>193.8759307861328</v>
       </c>
       <c r="C230" s="1">
-        <v>139.596746850577</v>
+        <v>139.5967161761351</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -6414,10 +6415,10 @@
         <v>45279</v>
       </c>
       <c r="B231" s="1">
-        <v>194.9151306152344</v>
+        <v>194.9151153564453</v>
       </c>
       <c r="C231" s="1">
-        <v>140.345003299338</v>
+        <v>140.3449614736732</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -6425,10 +6426,10 @@
         <v>45280</v>
       </c>
       <c r="B232" s="1">
-        <v>192.8268280029297</v>
+        <v>192.8268127441406</v>
       </c>
       <c r="C232" s="1">
-        <v>138.8413599644731</v>
+        <v>138.841318469213</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -6436,10 +6437,10 @@
         <v>45281</v>
       </c>
       <c r="B233" s="1">
-        <v>192.6783447265625</v>
+        <v>192.6783599853516</v>
       </c>
       <c r="C233" s="1">
-        <v>138.7344473515534</v>
+        <v>138.7344278533938</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -6447,10 +6448,10 @@
         <v>45282</v>
       </c>
       <c r="B234" s="1">
-        <v>191.6094818115234</v>
+        <v>191.6095123291016</v>
       </c>
       <c r="C234" s="1">
-        <v>137.9648325511826</v>
+        <v>137.9648242089391</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -6458,10 +6459,10 @@
         <v>45286</v>
       </c>
       <c r="B235" s="1">
-        <v>191.0651245117188</v>
+        <v>191.0651092529297</v>
       </c>
       <c r="C235" s="1">
-        <v>137.5728782334446</v>
+        <v>137.5728370169157</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -6472,7 +6473,7 @@
         <v>191.1640930175781</v>
       </c>
       <c r="C236" s="1">
-        <v>137.6441386596492</v>
+        <v>137.6441084142658</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -6483,7 +6484,7 @@
         <v>191.5896606445312</v>
       </c>
       <c r="C237" s="1">
-        <v>137.9505606896902</v>
+        <v>137.9505303769748</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -6494,7 +6495,7 @@
         <v>190.5504608154297</v>
       </c>
       <c r="C238" s="1">
-        <v>137.2023042409292</v>
+        <v>137.2022740926328</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -6505,7 +6506,7 @@
         <v>183.7313079833984</v>
       </c>
       <c r="C239" s="1">
-        <v>132.2923004680599</v>
+        <v>132.2922713986685</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -6513,10 +6514,10 @@
         <v>45294</v>
       </c>
       <c r="B240" s="1">
-        <v>182.3556213378906</v>
+        <v>182.3556060791016</v>
       </c>
       <c r="C240" s="1">
-        <v>131.301762964926</v>
+        <v>131.3017231263873</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -6524,10 +6525,10 @@
         <v>45295</v>
       </c>
       <c r="B241" s="1">
-        <v>180.0396575927734</v>
+        <v>180.0396423339844</v>
       </c>
       <c r="C241" s="1">
-        <v>129.6341964788164</v>
+        <v>129.6341570067024</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -6535,10 +6536,10 @@
         <v>45296</v>
       </c>
       <c r="B242" s="1">
-        <v>179.3171539306641</v>
+        <v>179.3171691894531</v>
       </c>
       <c r="C242" s="1">
-        <v>129.1139711965489</v>
+        <v>129.1139538123551</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -6546,10 +6547,10 @@
         <v>45299</v>
       </c>
       <c r="B243" s="1">
-        <v>183.6521148681641</v>
+        <v>183.6521301269531</v>
       </c>
       <c r="C243" s="1">
-        <v>132.2352789429286</v>
+        <v>132.2352608728708</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -6557,10 +6558,10 @@
         <v>45300</v>
       </c>
       <c r="B244" s="1">
-        <v>183.2364501953125</v>
+        <v>183.2364654541016</v>
       </c>
       <c r="C244" s="1">
-        <v>131.9359873502306</v>
+        <v>131.935969345938</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -6568,10 +6569,10 @@
         <v>45301</v>
       </c>
       <c r="B245" s="1">
-        <v>184.275634765625</v>
+        <v>184.2756500244141</v>
       </c>
       <c r="C245" s="1">
-        <v>132.6842328121851</v>
+        <v>132.684214643476</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -6579,10 +6580,10 @@
         <v>45302</v>
       </c>
       <c r="B246" s="1">
-        <v>183.6818237304688</v>
+        <v>183.6818084716797</v>
       </c>
       <c r="C246" s="1">
-        <v>132.2566702549576</v>
+        <v>132.2566302065915</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -6590,10 +6591,10 @@
         <v>45303</v>
       </c>
       <c r="B247" s="1">
-        <v>184.0084075927734</v>
+        <v>184.0084381103516</v>
       </c>
       <c r="C247" s="1">
-        <v>132.4918208719877</v>
+        <v>132.4918137323623</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -6601,10 +6602,10 @@
         <v>45307</v>
       </c>
       <c r="B248" s="1">
-        <v>181.7419738769531</v>
+        <v>181.7419891357422</v>
       </c>
       <c r="C248" s="1">
-        <v>130.8599175593996</v>
+        <v>130.8598997915584</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -6612,10 +6613,10 @@
         <v>45308</v>
       </c>
       <c r="B249" s="1">
-        <v>180.8017425537109</v>
+        <v>180.8017120361328</v>
       </c>
       <c r="C249" s="1">
-        <v>130.1829215368433</v>
+        <v>130.1828709573506</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -6623,10 +6624,10 @@
         <v>45309</v>
       </c>
       <c r="B250" s="1">
-        <v>186.6905670166016</v>
+        <v>186.6905517578125</v>
       </c>
       <c r="C250" s="1">
-        <v>134.4230597244992</v>
+        <v>134.4230192000991</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -6637,7 +6638,7 @@
         <v>189.5904235839844</v>
       </c>
       <c r="C251" s="1">
-        <v>136.5110473436869</v>
+        <v>136.5110173472845</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -6645,10 +6646,10 @@
         <v>45313</v>
       </c>
       <c r="B252" s="1">
-        <v>191.8964996337891</v>
+        <v>191.896484375</v>
       </c>
       <c r="C252" s="1">
-        <v>138.1714943792597</v>
+        <v>138.1714530311933</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -6656,10 +6657,10 @@
         <v>45314</v>
       </c>
       <c r="B253" s="1">
-        <v>193.1732025146484</v>
+        <v>193.1732177734375</v>
       </c>
       <c r="C253" s="1">
-        <v>139.0907604693827</v>
+        <v>139.0907408929283</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -6667,10 +6668,10 @@
         <v>45315</v>
       </c>
       <c r="B254" s="1">
-        <v>192.5002288818359</v>
+        <v>192.5001983642578</v>
       </c>
       <c r="C254" s="1">
-        <v>138.6061983606367</v>
+        <v>138.6061459302461</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -6681,7 +6682,7 @@
         <v>192.1736297607422</v>
       </c>
       <c r="C255" s="1">
-        <v>138.3710367568002</v>
+        <v>138.3710063516911</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -6692,7 +6693,7 @@
         <v>190.4415893554688</v>
       </c>
       <c r="C256" s="1">
-        <v>137.1239133773816</v>
+        <v>137.1238832463105</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -6703,7 +6704,7 @@
         <v>189.7586975097656</v>
       </c>
       <c r="C257" s="1">
-        <v>136.6322098444861</v>
+        <v>136.63217982146</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -6714,7 +6715,7 @@
         <v>186.1066284179688</v>
       </c>
       <c r="C258" s="1">
-        <v>134.002605631002</v>
+        <v>134.0025761857948</v>
       </c>
     </row>
   </sheetData>
@@ -9601,7 +9602,7 @@
         <v>44949</v>
       </c>
       <c r="B2" s="1">
-        <v>236.3760986328125</v>
+        <v>236.3760528564453</v>
       </c>
       <c r="C2" s="1">
         <v>100</v>
@@ -9612,10 +9613,10 @@
         <v>44950</v>
       </c>
       <c r="B3" s="1">
-        <v>235.8498840332031</v>
+        <v>235.8498992919922</v>
       </c>
       <c r="C3" s="1">
-        <v>99.77738248382431</v>
+        <v>99.77740826192209</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9623,10 +9624,10 @@
         <v>44951</v>
       </c>
       <c r="B4" s="1">
-        <v>234.4564514160156</v>
+        <v>234.4564666748047</v>
       </c>
       <c r="C4" s="1">
-        <v>99.18788438090822</v>
+        <v>99.18791004484434</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9637,7 +9638,7 @@
         <v>241.6574554443359</v>
       </c>
       <c r="C5" s="1">
-        <v>102.234302385931</v>
+        <v>102.2343221845312</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -9645,10 +9646,10 @@
         <v>44953</v>
       </c>
       <c r="B6" s="1">
-        <v>241.8133697509766</v>
+        <v>241.8133850097656</v>
       </c>
       <c r="C6" s="1">
-        <v>102.300262653294</v>
+        <v>102.3002889199705</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -9659,7 +9660,7 @@
         <v>236.5027465820312</v>
       </c>
       <c r="C7" s="1">
-        <v>100.0535789997175</v>
+        <v>100.0535983760008</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -9670,7 +9671,7 @@
         <v>241.4723358154297</v>
       </c>
       <c r="C8" s="1">
-        <v>102.155986672127</v>
+        <v>102.1560064555606</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -9678,10 +9679,10 @@
         <v>44958</v>
       </c>
       <c r="B9" s="1">
-        <v>246.2859802246094</v>
+        <v>246.2859954833984</v>
       </c>
       <c r="C9" s="1">
-        <v>104.192421166571</v>
+        <v>104.1924477996811</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9692,7 +9693,7 @@
         <v>257.8329467773438</v>
       </c>
       <c r="C10" s="1">
-        <v>109.0774186851533</v>
+        <v>109.077439808985</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9700,10 +9701,10 @@
         <v>44960</v>
       </c>
       <c r="B11" s="1">
-        <v>251.7427978515625</v>
+        <v>251.7427368164062</v>
       </c>
       <c r="C11" s="1">
-        <v>106.5009530606649</v>
+        <v>106.500947864331</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -9711,10 +9712,10 @@
         <v>44963</v>
       </c>
       <c r="B12" s="1">
-        <v>250.2031555175781</v>
+        <v>250.2031402587891</v>
       </c>
       <c r="C12" s="1">
-        <v>105.8496002619303</v>
+        <v>105.8496143053633</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -9722,10 +9723,10 @@
         <v>44964</v>
       </c>
       <c r="B13" s="1">
-        <v>260.7172241210938</v>
+        <v>260.7172546386719</v>
       </c>
       <c r="C13" s="1">
-        <v>110.2976255336597</v>
+        <v>110.2976598044005</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9733,10 +9734,10 @@
         <v>44965</v>
       </c>
       <c r="B14" s="1">
-        <v>259.9084777832031</v>
+        <v>259.908447265625</v>
       </c>
       <c r="C14" s="1">
-        <v>109.9554816610058</v>
+        <v>109.9554900442776</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9744,10 +9745,10 @@
         <v>44966</v>
       </c>
       <c r="B15" s="1">
-        <v>256.8779907226562</v>
+        <v>256.8778991699219</v>
       </c>
       <c r="C15" s="1">
-        <v>108.6734201166809</v>
+        <v>108.6734024304601</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -9758,7 +9759,7 @@
         <v>256.3713073730469</v>
       </c>
       <c r="C16" s="1">
-        <v>108.4590653860038</v>
+        <v>108.4590863900858</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9766,10 +9767,10 @@
         <v>44970</v>
       </c>
       <c r="B17" s="1">
-        <v>264.381103515625</v>
+        <v>264.3810424804688</v>
       </c>
       <c r="C17" s="1">
-        <v>111.847646629584</v>
+        <v>111.8476424686858</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -9780,7 +9781,7 @@
         <v>265.2093200683594</v>
       </c>
       <c r="C18" s="1">
-        <v>112.1980274665318</v>
+        <v>112.1980491946978</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9788,10 +9789,10 @@
         <v>44972</v>
       </c>
       <c r="B19" s="1">
-        <v>263.0895385742188</v>
+        <v>263.0895080566406</v>
       </c>
       <c r="C19" s="1">
-        <v>111.301244117284</v>
+        <v>111.3012527611749</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -9799,10 +9800,10 @@
         <v>44973</v>
       </c>
       <c r="B20" s="1">
-        <v>256.0854187011719</v>
+        <v>256.0853881835938</v>
       </c>
       <c r="C20" s="1">
-        <v>108.3381188632679</v>
+        <v>108.3381269333227</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -9810,10 +9811,10 @@
         <v>44974</v>
       </c>
       <c r="B21" s="1">
-        <v>252.0900115966797</v>
+        <v>252.0899963378906</v>
       </c>
       <c r="C21" s="1">
-        <v>106.6478434388061</v>
+        <v>106.6478576368261</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -9824,7 +9825,7 @@
         <v>246.82470703125</v>
       </c>
       <c r="C22" s="1">
-        <v>104.4203320297068</v>
+        <v>104.4203522516515</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -9835,7 +9836,7 @@
         <v>245.6915435791016</v>
       </c>
       <c r="C23" s="1">
-        <v>103.9409419988608</v>
+        <v>103.9409621279672</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -9846,7 +9847,7 @@
         <v>248.8761138916016</v>
       </c>
       <c r="C24" s="1">
-        <v>105.2881891744083</v>
+        <v>105.2882095644214</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -9854,10 +9855,10 @@
         <v>44981</v>
       </c>
       <c r="B25" s="1">
-        <v>243.4545288085938</v>
+        <v>243.4544982910156</v>
       </c>
       <c r="C25" s="1">
-        <v>102.9945625707178</v>
+        <v>102.9945696059445</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -9865,10 +9866,10 @@
         <v>44984</v>
       </c>
       <c r="B26" s="1">
-        <v>244.3727722167969</v>
+        <v>244.3727874755859</v>
       </c>
       <c r="C26" s="1">
-        <v>103.3830296845733</v>
+        <v>103.3830561609374</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -9876,10 +9877,10 @@
         <v>44985</v>
       </c>
       <c r="B27" s="1">
-        <v>243.6498565673828</v>
+        <v>243.6498718261719</v>
       </c>
       <c r="C27" s="1">
-        <v>103.0771968810051</v>
+        <v>103.0772232981418</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -9887,10 +9888,10 @@
         <v>44986</v>
       </c>
       <c r="B28" s="1">
-        <v>240.5727691650391</v>
+        <v>240.5727844238281</v>
       </c>
       <c r="C28" s="1">
-        <v>101.7754208469045</v>
+        <v>101.7754470119406</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -9898,10 +9899,10 @@
         <v>44987</v>
       </c>
       <c r="B29" s="1">
-        <v>245.3007965087891</v>
+        <v>245.3008270263672</v>
       </c>
       <c r="C29" s="1">
-        <v>103.7756346464793</v>
+        <v>103.7756676541773</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -9912,7 +9913,7 @@
         <v>249.3840789794922</v>
       </c>
       <c r="C30" s="1">
-        <v>105.5030861503837</v>
+        <v>105.5031065820136</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -9920,10 +9921,10 @@
         <v>44991</v>
       </c>
       <c r="B31" s="1">
-        <v>250.9275817871094</v>
+        <v>250.9275360107422</v>
       </c>
       <c r="C31" s="1">
-        <v>106.1560721403145</v>
+        <v>106.1560733324937</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -9931,10 +9932,10 @@
         <v>44992</v>
       </c>
       <c r="B32" s="1">
-        <v>248.2704620361328</v>
+        <v>248.2704772949219</v>
       </c>
       <c r="C32" s="1">
-        <v>105.0319653603375</v>
+        <v>105.0319921560329</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -9942,10 +9943,10 @@
         <v>44993</v>
       </c>
       <c r="B33" s="1">
-        <v>247.8308563232422</v>
+        <v>247.8308715820312</v>
       </c>
       <c r="C33" s="1">
-        <v>104.8459881336072</v>
+        <v>104.8460148932864</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -9956,7 +9957,7 @@
         <v>246.4828186035156</v>
       </c>
       <c r="C34" s="1">
-        <v>104.2756945516742</v>
+        <v>104.2757147456085</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -9967,7 +9968,7 @@
         <v>242.8390960693359</v>
       </c>
       <c r="C35" s="1">
-        <v>102.7342009085965</v>
+        <v>102.7342208040066</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -9975,10 +9976,10 @@
         <v>44998</v>
       </c>
       <c r="B36" s="1">
-        <v>248.0457763671875</v>
+        <v>248.0458068847656</v>
       </c>
       <c r="C36" s="1">
-        <v>104.9369110505977</v>
+        <v>104.9369442831874</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -9986,10 +9987,10 @@
         <v>44999</v>
       </c>
       <c r="B37" s="1">
-        <v>254.7568817138672</v>
+        <v>254.7568969726562</v>
       </c>
       <c r="C37" s="1">
-        <v>107.7760751562312</v>
+        <v>107.7761024833484</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -9997,10 +9998,10 @@
         <v>45000</v>
       </c>
       <c r="B38" s="1">
-        <v>259.2992553710938</v>
+        <v>259.2992858886719</v>
       </c>
       <c r="C38" s="1">
-        <v>109.697747306461</v>
+        <v>109.6977814610299</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -10008,10 +10009,10 @@
         <v>45001</v>
       </c>
       <c r="B39" s="1">
-        <v>269.8103332519531</v>
+        <v>269.8103942871094</v>
       </c>
       <c r="C39" s="1">
-        <v>114.144507339161</v>
+        <v>114.1445552654901</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -10019,10 +10020,10 @@
         <v>45002</v>
       </c>
       <c r="B40" s="1">
-        <v>272.965576171875</v>
+        <v>272.9656066894531</v>
       </c>
       <c r="C40" s="1">
-        <v>115.4793474258583</v>
+        <v>115.4793827000865</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -10033,7 +10034,7 @@
         <v>265.9321899414062</v>
       </c>
       <c r="C41" s="1">
-        <v>112.5038409041966</v>
+        <v>112.5038626915861</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -10041,10 +10042,10 @@
         <v>45006</v>
       </c>
       <c r="B42" s="1">
-        <v>267.4462890625</v>
+        <v>267.4463195800781</v>
       </c>
       <c r="C42" s="1">
-        <v>113.1443875287713</v>
+        <v>113.1444223508133</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -10052,10 +10053,10 @@
         <v>45007</v>
       </c>
       <c r="B43" s="1">
-        <v>265.9908142089844</v>
+        <v>265.9908447265625</v>
       </c>
       <c r="C43" s="1">
-        <v>112.5286421712948</v>
+        <v>112.5286768740921</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -10063,10 +10064,10 @@
         <v>45008</v>
       </c>
       <c r="B44" s="1">
-        <v>271.2366027832031</v>
+        <v>271.236572265625</v>
       </c>
       <c r="C44" s="1">
-        <v>114.7478972501966</v>
+        <v>114.7479065615632</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -10077,7 +10078,7 @@
         <v>274.0792541503906</v>
       </c>
       <c r="C45" s="1">
-        <v>115.9504940371092</v>
+        <v>115.9505164919743</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -10085,10 +10086,10 @@
         <v>45012</v>
       </c>
       <c r="B46" s="1">
-        <v>269.9861755371094</v>
+        <v>269.9862365722656</v>
       </c>
       <c r="C46" s="1">
-        <v>114.2188982298531</v>
+        <v>114.2189461705887</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -10099,7 +10100,7 @@
         <v>268.86279296875</v>
       </c>
       <c r="C47" s="1">
-        <v>113.7436460470576</v>
+        <v>113.7436680745466</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -10107,10 +10108,10 @@
         <v>45014</v>
       </c>
       <c r="B48" s="1">
-        <v>274.0206909179688</v>
+        <v>274.0206298828125</v>
       </c>
       <c r="C48" s="1">
-        <v>115.9257185912157</v>
+        <v>115.9257152200732</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -10118,10 +10119,10 @@
         <v>45015</v>
       </c>
       <c r="B49" s="1">
-        <v>277.478759765625</v>
+        <v>277.4787902832031</v>
       </c>
       <c r="C49" s="1">
-        <v>117.3886705849484</v>
+        <v>117.3887062289343</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -10129,10 +10130,10 @@
         <v>45016</v>
       </c>
       <c r="B50" s="1">
-        <v>281.6304016113281</v>
+        <v>281.6304626464844</v>
       </c>
       <c r="C50" s="1">
-        <v>119.145041838098</v>
+        <v>119.1450907328259</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -10140,10 +10141,10 @@
         <v>45019</v>
       </c>
       <c r="B51" s="1">
-        <v>280.5852355957031</v>
+        <v>280.5851745605469</v>
       </c>
       <c r="C51" s="1">
-        <v>118.7028795291039</v>
+        <v>118.7028766957837</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -10154,7 +10155,7 @@
         <v>280.5363464355469</v>
       </c>
       <c r="C52" s="1">
-        <v>118.6821967441527</v>
+        <v>118.6822197280368</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -10162,10 +10163,10 @@
         <v>45021</v>
       </c>
       <c r="B53" s="1">
-        <v>277.7620239257812</v>
+        <v>277.7620849609375</v>
       </c>
       <c r="C53" s="1">
-        <v>117.5085067958829</v>
+        <v>117.508555373681</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -10173,10 +10174,10 @@
         <v>45022</v>
       </c>
       <c r="B54" s="1">
-        <v>284.8541259765625</v>
+        <v>284.8540649414062</v>
       </c>
       <c r="C54" s="1">
-        <v>120.5088533164497</v>
+        <v>120.5088508328728</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -10184,10 +10185,10 @@
         <v>45026</v>
       </c>
       <c r="B55" s="1">
-        <v>282.6952819824219</v>
+        <v>282.6952209472656</v>
       </c>
       <c r="C55" s="1">
-        <v>119.5955443962047</v>
+        <v>119.5955417357572</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -10195,10 +10196,10 @@
         <v>45027</v>
       </c>
       <c r="B56" s="1">
-        <v>276.2869567871094</v>
+        <v>276.2869262695312</v>
       </c>
       <c r="C56" s="1">
-        <v>116.8844728317031</v>
+        <v>116.8844825568368</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -10206,10 +10207,10 @@
         <v>45028</v>
       </c>
       <c r="B57" s="1">
-        <v>276.931640625</v>
+        <v>276.9317016601562</v>
       </c>
       <c r="C57" s="1">
-        <v>117.1572093061687</v>
+        <v>117.1572578159349</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -10217,10 +10218,10 @@
         <v>45029</v>
       </c>
       <c r="B58" s="1">
-        <v>283.1347961425781</v>
+        <v>283.1348266601562</v>
       </c>
       <c r="C58" s="1">
-        <v>119.781482891128</v>
+        <v>119.7815189985037</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -10228,10 +10229,10 @@
         <v>45030</v>
       </c>
       <c r="B59" s="1">
-        <v>279.5204162597656</v>
+        <v>279.5204467773438</v>
       </c>
       <c r="C59" s="1">
-        <v>118.2524027922018</v>
+        <v>118.2524386034573</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -10242,7 +10243,7 @@
         <v>282.1188659667969</v>
       </c>
       <c r="C60" s="1">
-        <v>119.3516889391771</v>
+        <v>119.3517120527145</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -10250,10 +10251,10 @@
         <v>45034</v>
       </c>
       <c r="B61" s="1">
-        <v>281.6988525390625</v>
+        <v>281.6988220214844</v>
       </c>
       <c r="C61" s="1">
-        <v>119.1740003191501</v>
+        <v>119.1740104876716</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -10264,7 +10265,7 @@
         <v>281.7770080566406</v>
       </c>
       <c r="C62" s="1">
-        <v>119.2070643717468</v>
+        <v>119.2070874572764</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -10275,7 +10276,7 @@
         <v>279.4910888671875</v>
       </c>
       <c r="C63" s="1">
-        <v>118.2399957033515</v>
+        <v>118.2400186015994</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -10283,10 +10284,10 @@
         <v>45037</v>
       </c>
       <c r="B64" s="1">
-        <v>279.1492309570312</v>
+        <v>279.149169921875</v>
       </c>
       <c r="C64" s="1">
-        <v>118.0953711359213</v>
+        <v>118.0953681849517</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -10294,10 +10295,10 @@
         <v>45040</v>
       </c>
       <c r="B65" s="1">
-        <v>275.2515563964844</v>
+        <v>275.25146484375</v>
       </c>
       <c r="C65" s="1">
-        <v>116.4464419154583</v>
+        <v>116.4464257345537</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -10305,10 +10306,10 @@
         <v>45041</v>
       </c>
       <c r="B66" s="1">
-        <v>269.0484619140625</v>
+        <v>269.0484008789062</v>
       </c>
       <c r="C66" s="1">
-        <v>113.8221941517037</v>
+        <v>113.8221903731946</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -10316,10 +10317,10 @@
         <v>45042</v>
       </c>
       <c r="B67" s="1">
-        <v>288.5368957519531</v>
+        <v>288.536865234375</v>
       </c>
       <c r="C67" s="1">
-        <v>122.0668660752234</v>
+        <v>122.0668768039746</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -10327,10 +10328,10 @@
         <v>45043</v>
       </c>
       <c r="B68" s="1">
-        <v>297.7780456542969</v>
+        <v>297.778076171875</v>
       </c>
       <c r="C68" s="1">
-        <v>125.9763772126836</v>
+        <v>125.9764145197568</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -10338,10 +10339,10 @@
         <v>45044</v>
       </c>
       <c r="B69" s="1">
-        <v>300.1517944335938</v>
+        <v>300.1518859863281</v>
       </c>
       <c r="C69" s="1">
-        <v>126.9806025946179</v>
+        <v>126.9806659173782</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -10349,10 +10350,10 @@
         <v>45047</v>
       </c>
       <c r="B70" s="1">
-        <v>298.4911193847656</v>
+        <v>298.4911499023438</v>
       </c>
       <c r="C70" s="1">
-        <v>126.2780463469967</v>
+        <v>126.2780837124909</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -10360,10 +10361,10 @@
         <v>45048</v>
       </c>
       <c r="B71" s="1">
-        <v>298.3446044921875</v>
+        <v>298.3446350097656</v>
       </c>
       <c r="C71" s="1">
-        <v>126.2160625451548</v>
+        <v>126.2160998986453</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -10371,10 +10372,10 @@
         <v>45049</v>
       </c>
       <c r="B72" s="1">
-        <v>297.3579406738281</v>
+        <v>297.3579711914062</v>
       </c>
       <c r="C72" s="1">
-        <v>125.7986498608495</v>
+        <v>125.7986871335042</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -10382,10 +10383,10 @@
         <v>45050</v>
       </c>
       <c r="B73" s="1">
-        <v>298.3446044921875</v>
+        <v>298.3446350097656</v>
       </c>
       <c r="C73" s="1">
-        <v>126.2160625451548</v>
+        <v>126.2160998986453</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -10393,10 +10394,10 @@
         <v>45051</v>
       </c>
       <c r="B74" s="1">
-        <v>303.4634094238281</v>
+        <v>303.4633178710938</v>
       </c>
       <c r="C74" s="1">
-        <v>128.3815966077134</v>
+        <v>128.3815827381598</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -10404,10 +10405,10 @@
         <v>45054</v>
       </c>
       <c r="B75" s="1">
-        <v>301.5096435546875</v>
+        <v>301.5096740722656</v>
       </c>
       <c r="C75" s="1">
-        <v>127.5550469352037</v>
+        <v>127.5550845480007</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -10415,10 +10416,10 @@
         <v>45055</v>
       </c>
       <c r="B76" s="1">
-        <v>299.8977966308594</v>
+        <v>299.8978881835938</v>
       </c>
       <c r="C76" s="1">
-        <v>126.873147651329</v>
+        <v>126.8732109532797</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -10426,10 +10427,10 @@
         <v>45056</v>
       </c>
       <c r="B77" s="1">
-        <v>305.0849609375</v>
+        <v>305.0849914550781</v>
       </c>
       <c r="C77" s="1">
-        <v>129.0676014631327</v>
+        <v>129.0676393688496</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -10437,10 +10438,10 @@
         <v>45057</v>
       </c>
       <c r="B78" s="1">
-        <v>302.9359130859375</v>
+        <v>302.9358520507812</v>
       </c>
       <c r="C78" s="1">
-        <v>128.1584368462394</v>
+        <v>128.1584358440737</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -10448,10 +10449,10 @@
         <v>45058</v>
       </c>
       <c r="B79" s="1">
-        <v>301.8222351074219</v>
+        <v>301.822265625</v>
       </c>
       <c r="C79" s="1">
-        <v>127.6872902349885</v>
+        <v>127.6873278733955</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -10462,7 +10463,7 @@
         <v>302.3009033203125</v>
       </c>
       <c r="C80" s="1">
-        <v>127.889793032716</v>
+        <v>127.8898177997347</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -10470,10 +10471,10 @@
         <v>45062</v>
       </c>
       <c r="B81" s="1">
-        <v>304.5281677246094</v>
+        <v>304.5281372070312</v>
       </c>
       <c r="C81" s="1">
-        <v>128.8320475234108</v>
+        <v>128.8320595623008</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -10484,7 +10485,7 @@
         <v>307.4064331054688</v>
       </c>
       <c r="C82" s="1">
-        <v>130.049710983256</v>
+        <v>130.0497361685624</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -10492,10 +10493,10 @@
         <v>45064</v>
       </c>
       <c r="B83" s="1">
-        <v>311.8314514160156</v>
+        <v>311.8315124511719</v>
       </c>
       <c r="C83" s="1">
-        <v>131.9217354121813</v>
+        <v>131.9217867812319</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -10503,10 +10504,10 @@
         <v>45065</v>
       </c>
       <c r="B84" s="1">
-        <v>311.6553344726562</v>
+        <v>311.6553039550781</v>
       </c>
       <c r="C84" s="1">
-        <v>131.8472283260681</v>
+        <v>131.8472409488752</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -10514,10 +10515,10 @@
         <v>45068</v>
       </c>
       <c r="B85" s="1">
-        <v>314.4356384277344</v>
+        <v>314.4356689453125</v>
       </c>
       <c r="C85" s="1">
-        <v>133.0234487523968</v>
+        <v>133.0234874241994</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -10528,7 +10529,7 @@
         <v>308.6399536132812</v>
       </c>
       <c r="C86" s="1">
-        <v>130.5715575299022</v>
+        <v>130.571582816269</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -10536,10 +10537,10 @@
         <v>45070</v>
       </c>
       <c r="B87" s="1">
-        <v>307.2596130371094</v>
+        <v>307.2596435546875</v>
       </c>
       <c r="C87" s="1">
-        <v>129.9875980753907</v>
+        <v>129.9876361592732</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -10550,7 +10551,7 @@
         <v>319.0761108398438</v>
       </c>
       <c r="C88" s="1">
-        <v>134.9866220338537</v>
+        <v>134.9866481752377</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -10558,10 +10559,10 @@
         <v>45072</v>
       </c>
       <c r="B89" s="1">
-        <v>325.8997497558594</v>
+        <v>325.8997802734375</v>
       </c>
       <c r="C89" s="1">
-        <v>137.8733939856217</v>
+        <v>137.8734335966602</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -10569,10 +10570,10 @@
         <v>45076</v>
       </c>
       <c r="B90" s="1">
-        <v>324.2550048828125</v>
+        <v>324.2550659179688</v>
       </c>
       <c r="C90" s="1">
-        <v>137.1775770724228</v>
+        <v>137.1776294593148</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -10580,10 +10581,10 @@
         <v>45077</v>
       </c>
       <c r="B91" s="1">
-        <v>321.4943237304688</v>
+        <v>321.4942626953125</v>
       </c>
       <c r="C91" s="1">
-        <v>136.0096581633997</v>
+        <v>136.0096586816942</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -10591,10 +10592,10 @@
         <v>45078</v>
       </c>
       <c r="B92" s="1">
-        <v>325.5963134765625</v>
+        <v>325.5962524414062</v>
       </c>
       <c r="C92" s="1">
-        <v>137.7450238665395</v>
+        <v>137.7450247209034</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -10605,7 +10606,7 @@
         <v>328.3570251464844</v>
       </c>
       <c r="C93" s="1">
-        <v>138.912955686165</v>
+        <v>138.9129825879191</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -10616,7 +10617,7 @@
         <v>328.8857421875</v>
       </c>
       <c r="C94" s="1">
-        <v>139.1366318717326</v>
+        <v>139.1366588168038</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -10624,10 +10625,10 @@
         <v>45083</v>
       </c>
       <c r="B95" s="1">
-        <v>326.6731872558594</v>
+        <v>326.6731567382812</v>
       </c>
       <c r="C95" s="1">
-        <v>138.2006002913665</v>
+        <v>138.2006141445617</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -10635,10 +10636,10 @@
         <v>45084</v>
       </c>
       <c r="B96" s="1">
-        <v>316.5895080566406</v>
+        <v>316.5894775390625</v>
       </c>
       <c r="C96" s="1">
-        <v>133.9346532444602</v>
+        <v>133.9346662715161</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -10649,7 +10650,7 @@
         <v>318.4300231933594</v>
       </c>
       <c r="C97" s="1">
-        <v>134.7132916716803</v>
+        <v>134.7133177601314</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -10660,7 +10661,7 @@
         <v>319.9278564453125</v>
       </c>
       <c r="C98" s="1">
-        <v>135.3469569452069</v>
+        <v>135.3469831563731</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -10668,10 +10669,10 @@
         <v>45089</v>
       </c>
       <c r="B99" s="1">
-        <v>324.8816528320312</v>
+        <v>324.8816223144531</v>
       </c>
       <c r="C99" s="1">
-        <v>137.4426833809046</v>
+        <v>137.4426970873224</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -10679,10 +10680,10 @@
         <v>45090</v>
       </c>
       <c r="B100" s="1">
-        <v>327.2704162597656</v>
+        <v>327.2703857421875</v>
       </c>
       <c r="C100" s="1">
-        <v>138.453260779191</v>
+        <v>138.4532746813163</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -10693,7 +10694,7 @@
         <v>330.2563171386719</v>
       </c>
       <c r="C101" s="1">
-        <v>139.7164599334949</v>
+        <v>139.716486990855</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -10704,7 +10705,7 @@
         <v>340.7904357910156</v>
       </c>
       <c r="C102" s="1">
-        <v>144.1729674709628</v>
+        <v>144.1729953913659</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -10715,7 +10716,7 @@
         <v>335.1415405273438</v>
       </c>
       <c r="C103" s="1">
-        <v>141.7831762457311</v>
+        <v>141.7832037033295</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -10723,10 +10724,10 @@
         <v>45097</v>
       </c>
       <c r="B104" s="1">
-        <v>330.951416015625</v>
+        <v>330.9513854980469</v>
       </c>
       <c r="C104" s="1">
-        <v>140.0105247230289</v>
+        <v>140.0105389267324</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -10734,10 +10735,10 @@
         <v>45098</v>
       </c>
       <c r="B105" s="1">
-        <v>326.5557250976562</v>
+        <v>326.5556945800781</v>
       </c>
       <c r="C105" s="1">
-        <v>138.1509073829538</v>
+        <v>138.1509212265255</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -10745,10 +10746,10 @@
         <v>45099</v>
       </c>
       <c r="B106" s="1">
-        <v>332.5766296386719</v>
+        <v>332.5765686035156</v>
       </c>
       <c r="C106" s="1">
-        <v>140.6980788507292</v>
+        <v>140.6980802769789</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -10759,7 +10760,7 @@
         <v>327.9850158691406</v>
       </c>
       <c r="C107" s="1">
-        <v>138.7555754436212</v>
+        <v>138.7556023148973</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -10767,10 +10768,10 @@
         <v>45103</v>
       </c>
       <c r="B108" s="1">
-        <v>321.6997985839844</v>
+        <v>321.6998596191406</v>
       </c>
       <c r="C108" s="1">
-        <v>136.0965852489655</v>
+        <v>136.0966374265136</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -10778,10 +10779,10 @@
         <v>45104</v>
       </c>
       <c r="B109" s="1">
-        <v>327.5445251464844</v>
+        <v>327.5444946289062</v>
       </c>
       <c r="C109" s="1">
-        <v>138.569223809423</v>
+        <v>138.5692377340055</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -10789,10 +10790,10 @@
         <v>45105</v>
       </c>
       <c r="B110" s="1">
-        <v>328.7976379394531</v>
+        <v>328.797607421875</v>
       </c>
       <c r="C110" s="1">
-        <v>139.0993589627726</v>
+        <v>139.0993729900206</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -10803,7 +10804,7 @@
         <v>328.014404296875</v>
       </c>
       <c r="C111" s="1">
-        <v>138.7680083536761</v>
+        <v>138.7680352273599</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -10811,10 +10812,10 @@
         <v>45107</v>
       </c>
       <c r="B112" s="1">
-        <v>333.38916015625</v>
+        <v>333.3891296386719</v>
       </c>
       <c r="C112" s="1">
-        <v>141.0418236380735</v>
+        <v>141.0418380414974</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -10822,10 +10823,10 @@
         <v>45110</v>
       </c>
       <c r="B113" s="1">
-        <v>330.8926391601562</v>
+        <v>330.8927001953125</v>
       </c>
       <c r="C113" s="1">
-        <v>139.985658902919</v>
+        <v>139.9857118336216</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -10833,10 +10834,10 @@
         <v>45112</v>
       </c>
       <c r="B114" s="1">
-        <v>331.04931640625</v>
+        <v>331.0493774414062</v>
       </c>
       <c r="C114" s="1">
-        <v>140.0519419353406</v>
+        <v>140.0519948788795</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -10844,10 +10845,10 @@
         <v>45113</v>
       </c>
       <c r="B115" s="1">
-        <v>334.1037902832031</v>
+        <v>334.103759765625</v>
       </c>
       <c r="C115" s="1">
-        <v>141.344151213106</v>
+        <v>141.3441656750784</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -10855,10 +10856,10 @@
         <v>45114</v>
       </c>
       <c r="B116" s="1">
-        <v>330.1388549804688</v>
+        <v>330.1387939453125</v>
       </c>
       <c r="C116" s="1">
-        <v>139.6667670250822</v>
+        <v>139.6667682516091</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -10866,10 +10867,10 @@
         <v>45117</v>
       </c>
       <c r="B117" s="1">
-        <v>324.8620300292969</v>
+        <v>324.8619689941406</v>
       </c>
       <c r="C117" s="1">
-        <v>137.434381863599</v>
+        <v>137.4343826578042</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -10877,10 +10878,10 @@
         <v>45118</v>
       </c>
       <c r="B118" s="1">
-        <v>325.4886169433594</v>
+        <v>325.4885864257812</v>
       </c>
       <c r="C118" s="1">
-        <v>137.6994623508761</v>
+        <v>137.6994761070214</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -10891,7 +10892,7 @@
         <v>330.1192626953125</v>
       </c>
       <c r="C119" s="1">
-        <v>139.6584784183789</v>
+        <v>139.6585054645103</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -10899,10 +10900,10 @@
         <v>45120</v>
       </c>
       <c r="B120" s="1">
-        <v>335.464599609375</v>
+        <v>335.4645690917969</v>
       </c>
       <c r="C120" s="1">
-        <v>141.919847882119</v>
+        <v>141.9198624555803</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -10913,7 +10914,7 @@
         <v>337.9904479980469</v>
       </c>
       <c r="C121" s="1">
-        <v>142.9884197061237</v>
+        <v>142.9884473971285</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -10924,7 +10925,7 @@
         <v>338.4701538085938</v>
       </c>
       <c r="C122" s="1">
-        <v>143.1913614643308</v>
+        <v>143.1913891946371</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -10932,10 +10933,10 @@
         <v>45125</v>
       </c>
       <c r="B123" s="1">
-        <v>351.9411926269531</v>
+        <v>351.9411315917969</v>
       </c>
       <c r="C123" s="1">
-        <v>148.8903466393444</v>
+        <v>148.8903496521012</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -10946,7 +10947,7 @@
         <v>347.6238098144531</v>
       </c>
       <c r="C124" s="1">
-        <v>147.0638579048778</v>
+        <v>147.0638863851281</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -10957,7 +10958,7 @@
         <v>339.586181640625</v>
       </c>
       <c r="C125" s="1">
-        <v>143.6635021919621</v>
+        <v>143.6635300137027</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -10965,10 +10966,10 @@
         <v>45128</v>
       </c>
       <c r="B126" s="1">
-        <v>336.55126953125</v>
+        <v>336.5513610839844</v>
       </c>
       <c r="C126" s="1">
-        <v>142.3795686102976</v>
+        <v>142.3796349152074</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -10976,10 +10977,10 @@
         <v>45131</v>
       </c>
       <c r="B127" s="1">
-        <v>337.8630981445312</v>
+        <v>337.8631591796875</v>
       </c>
       <c r="C127" s="1">
-        <v>142.9345437625523</v>
+        <v>142.9345972643332</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -10987,10 +10988,10 @@
         <v>45132</v>
       </c>
       <c r="B128" s="1">
-        <v>343.60986328125</v>
+        <v>343.6099243164062</v>
       </c>
       <c r="C128" s="1">
-        <v>145.3657392894934</v>
+        <v>145.3657932620974</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -10998,10 +10999,10 @@
         <v>45133</v>
       </c>
       <c r="B129" s="1">
-        <v>330.6773071289062</v>
+        <v>330.6772766113281</v>
       </c>
       <c r="C129" s="1">
-        <v>139.8945616927969</v>
+        <v>139.8945758740431</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -11009,10 +11010,10 @@
         <v>45134</v>
       </c>
       <c r="B130" s="1">
-        <v>323.7753295898438</v>
+        <v>323.7753601074219</v>
       </c>
       <c r="C130" s="1">
-        <v>136.974648224818</v>
+        <v>136.9746876618062</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -11020,10 +11021,10 @@
         <v>45135</v>
       </c>
       <c r="B131" s="1">
-        <v>331.2647094726562</v>
+        <v>331.2646789550781</v>
       </c>
       <c r="C131" s="1">
-        <v>140.1430649666674</v>
+        <v>140.1430791960386</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -11031,10 +11032,10 @@
         <v>45138</v>
       </c>
       <c r="B132" s="1">
-        <v>328.8661193847656</v>
+        <v>328.8661804199219</v>
       </c>
       <c r="C132" s="1">
-        <v>139.128330354427</v>
+        <v>139.1283831191001</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -11045,7 +11046,7 @@
         <v>329.2773132324219</v>
       </c>
       <c r="C133" s="1">
-        <v>139.3022878103774</v>
+        <v>139.3023147875292</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -11053,10 +11054,10 @@
         <v>45140</v>
       </c>
       <c r="B134" s="1">
-        <v>320.6228942871094</v>
+        <v>320.6229248046875</v>
       </c>
       <c r="C134" s="1">
-        <v>135.6409959135362</v>
+        <v>135.6410350922505</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -11067,7 +11068,7 @@
         <v>319.8005981445312</v>
       </c>
       <c r="C135" s="1">
-        <v>135.2931197334425</v>
+        <v>135.2931459341826</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -11075,10 +11076,10 @@
         <v>45142</v>
       </c>
       <c r="B136" s="1">
-        <v>320.8970336914062</v>
+        <v>320.8970031738281</v>
       </c>
       <c r="C136" s="1">
-        <v>135.7569718543705</v>
+        <v>135.7569852343349</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -11086,10 +11087,10 @@
         <v>45145</v>
       </c>
       <c r="B137" s="1">
-        <v>323.1781005859375</v>
+        <v>323.1781311035156</v>
       </c>
       <c r="C137" s="1">
-        <v>136.7219877369935</v>
+        <v>136.7220271250517</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -11097,10 +11098,10 @@
         <v>45146</v>
       </c>
       <c r="B138" s="1">
-        <v>319.2033996582031</v>
+        <v>319.2033386230469</v>
       </c>
       <c r="C138" s="1">
-        <v>135.0404721562203</v>
+        <v>135.0404724868233</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -11108,10 +11109,10 @@
         <v>45147</v>
       </c>
       <c r="B139" s="1">
-        <v>315.463623046875</v>
+        <v>315.4635925292969</v>
       </c>
       <c r="C139" s="1">
-        <v>133.4583423922726</v>
+        <v>133.4583553270866</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -11119,10 +11120,10 @@
         <v>45148</v>
       </c>
       <c r="B140" s="1">
-        <v>316.14892578125</v>
+        <v>316.1488952636719</v>
       </c>
       <c r="C140" s="1">
-        <v>133.7482628784549</v>
+        <v>133.7482758694146</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -11130,10 +11131,10 @@
         <v>45149</v>
       </c>
       <c r="B141" s="1">
-        <v>314.2692260742188</v>
+        <v>314.2692565917969</v>
       </c>
       <c r="C141" s="1">
-        <v>132.9530472378283</v>
+        <v>132.9530858959969</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -11144,7 +11145,7 @@
         <v>317.2356567382812</v>
       </c>
       <c r="C142" s="1">
-        <v>134.2080094278382</v>
+        <v>134.2080354184369</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -11152,10 +11153,10 @@
         <v>45153</v>
       </c>
       <c r="B143" s="1">
-        <v>315.101318359375</v>
+        <v>315.1013488769531</v>
       </c>
       <c r="C143" s="1">
-        <v>133.3050677212735</v>
+        <v>133.3051064476142</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -11163,10 +11164,10 @@
         <v>45154</v>
       </c>
       <c r="B144" s="1">
-        <v>314.336181640625</v>
+        <v>314.3361511230469</v>
       </c>
       <c r="C144" s="1">
-        <v>132.9813730993657</v>
+        <v>132.9813859418102</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -11177,7 +11178,7 @@
         <v>310.8827819824219</v>
       </c>
       <c r="C145" s="1">
-        <v>131.5203964277912</v>
+        <v>131.5204218979093</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -11185,10 +11186,10 @@
         <v>45156</v>
       </c>
       <c r="B146" s="1">
-        <v>310.4903564453125</v>
+        <v>310.4903869628906</v>
       </c>
       <c r="C146" s="1">
-        <v>131.354378992281</v>
+        <v>131.3544173408531</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -11196,10 +11197,10 @@
         <v>45159</v>
       </c>
       <c r="B147" s="1">
-        <v>315.7881469726562</v>
+        <v>315.7881774902344</v>
       </c>
       <c r="C147" s="1">
-        <v>133.5956337375729</v>
+        <v>133.5956725201843</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -11207,10 +11208,10 @@
         <v>45160</v>
       </c>
       <c r="B148" s="1">
-        <v>316.357177734375</v>
+        <v>316.3572082519531</v>
       </c>
       <c r="C148" s="1">
-        <v>133.8363648288338</v>
+        <v>133.8364036580649</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -11218,10 +11219,10 @@
         <v>45161</v>
       </c>
       <c r="B149" s="1">
-        <v>320.811279296875</v>
+        <v>320.8112487792969</v>
       </c>
       <c r="C149" s="1">
-        <v>135.7206930617907</v>
+        <v>135.7207064347294</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -11229,10 +11230,10 @@
         <v>45162</v>
       </c>
       <c r="B150" s="1">
-        <v>313.9143371582031</v>
+        <v>313.9142150878906</v>
       </c>
       <c r="C150" s="1">
-        <v>132.8029098431982</v>
+        <v>132.8028839192671</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -11243,7 +11244,7 @@
         <v>316.8673400878906</v>
       </c>
       <c r="C151" s="1">
-        <v>134.0521913681779</v>
+        <v>134.0522173286009</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -11254,7 +11255,7 @@
         <v>317.57373046875</v>
       </c>
       <c r="C152" s="1">
-        <v>134.3510330805782</v>
+        <v>134.3510590988746</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -11262,10 +11263,10 @@
         <v>45167</v>
       </c>
       <c r="B153" s="1">
-        <v>322.194580078125</v>
+        <v>322.1945495605469</v>
       </c>
       <c r="C153" s="1">
-        <v>136.3059048447294</v>
+        <v>136.3059183309996</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -11276,7 +11277,7 @@
         <v>322.5673828125</v>
       </c>
       <c r="C154" s="1">
-        <v>136.463620762934</v>
+        <v>136.4636471903522</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -11287,7 +11288,7 @@
         <v>321.556884765625</v>
       </c>
       <c r="C155" s="1">
-        <v>136.0361248981999</v>
+        <v>136.0361512428297</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -11295,10 +11296,10 @@
         <v>45170</v>
       </c>
       <c r="B156" s="1">
-        <v>322.4397888183594</v>
+        <v>322.4398498535156</v>
       </c>
       <c r="C156" s="1">
-        <v>136.4096415345439</v>
+        <v>136.4096937727182</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -11309,7 +11310,7 @@
         <v>327.2372741699219</v>
       </c>
       <c r="C157" s="1">
-        <v>138.4392398650481</v>
+        <v>138.4392666750629</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -11317,10 +11318,10 @@
         <v>45175</v>
       </c>
       <c r="B158" s="1">
-        <v>326.5799865722656</v>
+        <v>326.5799560546875</v>
       </c>
       <c r="C158" s="1">
-        <v>138.1611713118153</v>
+        <v>138.1611851573748</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -11331,7 +11332,7 @@
         <v>323.6661682128906</v>
       </c>
       <c r="C159" s="1">
-        <v>136.9284670002422</v>
+        <v>136.9284935176821</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -11342,7 +11343,7 @@
         <v>327.9436340332031</v>
       </c>
       <c r="C160" s="1">
-        <v>138.738068666846</v>
+        <v>138.7380955347317</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -11350,10 +11351,10 @@
         <v>45180</v>
       </c>
       <c r="B161" s="1">
-        <v>331.5442199707031</v>
+        <v>331.544189453125</v>
       </c>
       <c r="C161" s="1">
-        <v>140.2613131735139</v>
+        <v>140.2613274257848</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -11361,10 +11362,10 @@
         <v>45181</v>
       </c>
       <c r="B162" s="1">
-        <v>325.4909057617188</v>
+        <v>325.490966796875</v>
       </c>
       <c r="C162" s="1">
-        <v>137.7004306460517</v>
+        <v>137.7004831341991</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -11375,7 +11376,7 @@
         <v>329.6997680664062</v>
       </c>
       <c r="C163" s="1">
-        <v>139.4810092785917</v>
+        <v>139.4810362903546</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -11383,10 +11384,10 @@
         <v>45183</v>
       </c>
       <c r="B164" s="1">
-        <v>332.2898254394531</v>
+        <v>332.289794921875</v>
       </c>
       <c r="C164" s="1">
-        <v>140.5767450099231</v>
+        <v>140.5767593232803</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -11394,10 +11395,10 @@
         <v>45184</v>
       </c>
       <c r="B165" s="1">
-        <v>323.9702453613281</v>
+        <v>323.9703674316406</v>
       </c>
       <c r="C165" s="1">
-        <v>137.0571082419736</v>
+        <v>137.0571864267455</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -11408,7 +11409,7 @@
         <v>322.8323059082031</v>
       </c>
       <c r="C166" s="1">
-        <v>136.5756977018611</v>
+        <v>136.5757241509841</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -11416,10 +11417,10 @@
         <v>45188</v>
       </c>
       <c r="B167" s="1">
-        <v>322.4300842285156</v>
+        <v>322.4300231933594</v>
       </c>
       <c r="C167" s="1">
-        <v>136.4055359629992</v>
+        <v>136.4055365579592</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -11427,10 +11428,10 @@
         <v>45189</v>
       </c>
       <c r="B168" s="1">
-        <v>314.6991577148438</v>
+        <v>314.6991271972656</v>
       </c>
       <c r="C168" s="1">
-        <v>133.1349318036163</v>
+        <v>133.1349446757989</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -11441,7 +11442,7 @@
         <v>313.4826354980469</v>
       </c>
       <c r="C169" s="1">
-        <v>132.6202764624743</v>
+        <v>132.6203021455941</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -11449,10 +11450,10 @@
         <v>45191</v>
       </c>
       <c r="B170" s="1">
-        <v>311.0102844238281</v>
+        <v>311.0103454589844</v>
       </c>
       <c r="C170" s="1">
-        <v>131.5743369243743</v>
+        <v>131.5743882261481</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -11460,10 +11461,10 @@
         <v>45194</v>
       </c>
       <c r="B171" s="1">
-        <v>311.5302734375</v>
+        <v>311.5303039550781</v>
       </c>
       <c r="C171" s="1">
-        <v>131.7943206776724</v>
+        <v>131.7943591114431</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -11471,10 +11472,10 @@
         <v>45195</v>
       </c>
       <c r="B172" s="1">
-        <v>306.2325134277344</v>
+        <v>306.232421875</v>
       </c>
       <c r="C172" s="1">
-        <v>129.5530788429828</v>
+        <v>129.5530652002974</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -11482,10 +11483,10 @@
         <v>45196</v>
       </c>
       <c r="B173" s="1">
-        <v>306.8702087402344</v>
+        <v>306.8701782226562</v>
       </c>
       <c r="C173" s="1">
-        <v>129.8228587895123</v>
+        <v>129.8228710202818</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -11493,10 +11494,10 @@
         <v>45197</v>
       </c>
       <c r="B174" s="1">
-        <v>307.7040405273438</v>
+        <v>307.7041625976562</v>
       </c>
       <c r="C174" s="1">
-        <v>130.175615177291</v>
+        <v>130.1756920293992</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -11504,10 +11505,10 @@
         <v>45198</v>
       </c>
       <c r="B175" s="1">
-        <v>309.7741394042969</v>
+        <v>309.7742004394531</v>
       </c>
       <c r="C175" s="1">
-        <v>131.0513800659267</v>
+        <v>131.0514312664251</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -11518,7 +11519,7 @@
         <v>315.7096252441406</v>
       </c>
       <c r="C176" s="1">
-        <v>133.562414757748</v>
+        <v>133.5624406233214</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -11529,7 +11530,7 @@
         <v>307.4588623046875</v>
       </c>
       <c r="C177" s="1">
-        <v>130.0718913980788</v>
+        <v>130.0719165876807</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -11537,10 +11538,10 @@
         <v>45203</v>
       </c>
       <c r="B178" s="1">
-        <v>312.9234008789062</v>
+        <v>312.9234313964844</v>
       </c>
       <c r="C178" s="1">
-        <v>132.383689674565</v>
+        <v>132.3837282224724</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -11548,10 +11549,10 @@
         <v>45204</v>
       </c>
       <c r="B179" s="1">
-        <v>313.3158264160156</v>
+        <v>313.3157958984375</v>
       </c>
       <c r="C179" s="1">
-        <v>132.5497071100753</v>
+        <v>132.5497198689238</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -11559,10 +11560,10 @@
         <v>45205</v>
       </c>
       <c r="B180" s="1">
-        <v>321.0663452148438</v>
+        <v>321.0663146972656</v>
       </c>
       <c r="C180" s="1">
-        <v>135.8285998761615</v>
+        <v>135.8286132699974</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -11570,10 +11571,10 @@
         <v>45208</v>
       </c>
       <c r="B181" s="1">
-        <v>323.5778503417969</v>
+        <v>323.577880859375</v>
       </c>
       <c r="C181" s="1">
-        <v>136.8911037170657</v>
+        <v>136.8911431378747</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -11581,10 +11582,10 @@
         <v>45209</v>
       </c>
       <c r="B182" s="1">
-        <v>322.1749877929688</v>
+        <v>322.1749572753906</v>
       </c>
       <c r="C182" s="1">
-        <v>136.2976162380261</v>
+        <v>136.2976297226912</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -11592,10 +11593,10 @@
         <v>45210</v>
       </c>
       <c r="B183" s="1">
-        <v>326.128662109375</v>
+        <v>326.1286315917969</v>
       </c>
       <c r="C183" s="1">
-        <v>137.9702364137858</v>
+        <v>137.970250222369</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -11603,10 +11604,10 @@
         <v>45211</v>
       </c>
       <c r="B184" s="1">
-        <v>324.8924865722656</v>
+        <v>324.8925170898438</v>
       </c>
       <c r="C184" s="1">
-        <v>137.4472666447359</v>
+        <v>137.4473061732509</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -11614,10 +11615,10 @@
         <v>45212</v>
       </c>
       <c r="B185" s="1">
-        <v>321.5274047851562</v>
+        <v>321.5274658203125</v>
       </c>
       <c r="C185" s="1">
-        <v>136.023653256338</v>
+        <v>136.0237054197622</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -11625,10 +11626,10 @@
         <v>45215</v>
       </c>
       <c r="B186" s="1">
-        <v>326.3445434570312</v>
+        <v>326.3445129394531</v>
       </c>
       <c r="C186" s="1">
-        <v>138.0615660147501</v>
+        <v>138.0615798410201</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -11639,7 +11640,7 @@
         <v>325.7754516601562</v>
       </c>
       <c r="C187" s="1">
-        <v>137.8208091022845</v>
+        <v>137.8208357925346</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -11647,10 +11648,10 @@
         <v>45217</v>
       </c>
       <c r="B188" s="1">
-        <v>323.8623352050781</v>
+        <v>323.8623657226562</v>
       </c>
       <c r="C188" s="1">
-        <v>137.0114563520938</v>
+        <v>137.0114957962102</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -11658,10 +11659,10 @@
         <v>45218</v>
       </c>
       <c r="B189" s="1">
-        <v>325.0494689941406</v>
+        <v>325.0494995117188</v>
       </c>
       <c r="C189" s="1">
-        <v>137.5136787831809</v>
+        <v>137.5137183245572</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -11672,7 +11673,7 @@
         <v>320.4875183105469</v>
       </c>
       <c r="C190" s="1">
-        <v>135.5837244815489</v>
+        <v>135.5837507385673</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -11680,10 +11681,10 @@
         <v>45222</v>
       </c>
       <c r="B191" s="1">
-        <v>323.0873107910156</v>
+        <v>323.0873413085938</v>
       </c>
       <c r="C191" s="1">
-        <v>136.6835786950273</v>
+        <v>136.6836180756472</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -11691,10 +11692,10 @@
         <v>45223</v>
       </c>
       <c r="B192" s="1">
-        <v>324.2744750976562</v>
+        <v>324.2744140625</v>
       </c>
       <c r="C192" s="1">
-        <v>137.1858140367167</v>
+        <v>137.1858147827845</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -11705,7 +11706,7 @@
         <v>334.2225341796875</v>
       </c>
       <c r="C193" s="1">
-        <v>141.3943863668171</v>
+        <v>141.3944137491228</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -11716,7 +11717,7 @@
         <v>321.6844482421875</v>
       </c>
       <c r="C194" s="1">
-        <v>136.0900912159877</v>
+        <v>136.0901175710685</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -11727,7 +11728,7 @@
         <v>323.5680541992188</v>
       </c>
       <c r="C195" s="1">
-        <v>136.886959413714</v>
+        <v>136.8869859231157</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -11735,10 +11736,10 @@
         <v>45229</v>
       </c>
       <c r="B196" s="1">
-        <v>330.9260864257812</v>
+        <v>330.9261779785156</v>
       </c>
       <c r="C196" s="1">
-        <v>139.9998089230853</v>
+        <v>139.999874767133</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -11746,10 +11747,10 @@
         <v>45230</v>
       </c>
       <c r="B197" s="1">
-        <v>331.7109375</v>
+        <v>331.7109069824219</v>
       </c>
       <c r="C197" s="1">
-        <v>140.3318437941059</v>
+        <v>140.3318580600357</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -11757,10 +11758,10 @@
         <v>45231</v>
       </c>
       <c r="B198" s="1">
-        <v>339.5203247070312</v>
+        <v>339.5202941894531</v>
       </c>
       <c r="C198" s="1">
-        <v>143.635641112109</v>
+        <v>143.6356560178492</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -11771,7 +11772,7 @@
         <v>341.727783203125</v>
       </c>
       <c r="C199" s="1">
-        <v>144.5695166218841</v>
+        <v>144.5695446190826</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -11782,7 +11783,7 @@
         <v>346.1229553222656</v>
       </c>
       <c r="C200" s="1">
-        <v>146.4289144817193</v>
+        <v>146.4289428390071</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -11790,10 +11791,10 @@
         <v>45236</v>
       </c>
       <c r="B201" s="1">
-        <v>349.7823486328125</v>
+        <v>349.7823791503906</v>
       </c>
       <c r="C201" s="1">
-        <v>147.9770377190994</v>
+        <v>147.9770792868001</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -11801,10 +11802,10 @@
         <v>45237</v>
       </c>
       <c r="B202" s="1">
-        <v>353.7066650390625</v>
+        <v>353.7066345214844</v>
       </c>
       <c r="C202" s="1">
-        <v>149.6372378954066</v>
+        <v>149.6372539634104</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -11812,10 +11813,10 @@
         <v>45238</v>
       </c>
       <c r="B203" s="1">
-        <v>356.3261108398438</v>
+        <v>356.3261413574219</v>
       </c>
       <c r="C203" s="1">
-        <v>150.7454065367929</v>
+        <v>150.7454486406134</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -11823,10 +11824,10 @@
         <v>45239</v>
       </c>
       <c r="B204" s="1">
-        <v>353.8636474609375</v>
+        <v>353.8636779785156</v>
       </c>
       <c r="C204" s="1">
-        <v>149.7036500338516</v>
+        <v>149.7036919359265</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -11834,10 +11835,10 @@
         <v>45240</v>
       </c>
       <c r="B205" s="1">
-        <v>362.6736755371094</v>
+        <v>362.6737060546875</v>
       </c>
       <c r="C205" s="1">
-        <v>153.4307730920325</v>
+        <v>153.4308157158985</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -11845,10 +11846,10 @@
         <v>45243</v>
       </c>
       <c r="B206" s="1">
-        <v>359.740234375</v>
+        <v>359.7402954101562</v>
       </c>
       <c r="C206" s="1">
-        <v>152.1897672631537</v>
+        <v>152.1898225572926</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -11856,10 +11857,10 @@
         <v>45244</v>
       </c>
       <c r="B207" s="1">
-        <v>363.2623291015625</v>
+        <v>363.2624206542969</v>
       </c>
       <c r="C207" s="1">
-        <v>153.679805700599</v>
+        <v>153.6798741939022</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -11867,10 +11868,10 @@
         <v>45245</v>
       </c>
       <c r="B208" s="1">
-        <v>363.4097900390625</v>
+        <v>363.4098205566406</v>
       </c>
       <c r="C208" s="1">
-        <v>153.7421897311135</v>
+        <v>153.7422324152882</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -11878,10 +11879,10 @@
         <v>45246</v>
       </c>
       <c r="B209" s="1">
-        <v>369.7996826171875</v>
+        <v>369.7997436523438</v>
       </c>
       <c r="C209" s="1">
-        <v>156.4454632918008</v>
+        <v>156.4455194100938</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -11889,10 +11890,10 @@
         <v>45247</v>
       </c>
       <c r="B210" s="1">
-        <v>363.5867614746094</v>
+        <v>363.5867309570312</v>
       </c>
       <c r="C210" s="1">
-        <v>153.8170583140922</v>
+        <v>153.8170751915563</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -11900,10 +11901,10 @@
         <v>45250</v>
       </c>
       <c r="B211" s="1">
-        <v>371.0482177734375</v>
+        <v>371.0481567382812</v>
       </c>
       <c r="C211" s="1">
-        <v>156.9736618547991</v>
+        <v>156.9736664329632</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -11914,7 +11915,7 @@
         <v>366.7522583007812</v>
       </c>
       <c r="C212" s="1">
-        <v>155.1562363631763</v>
+        <v>155.1562664105891</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -11925,7 +11926,7 @@
         <v>371.4512939453125</v>
       </c>
       <c r="C213" s="1">
-        <v>157.1441850905266</v>
+        <v>157.1442155229237</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -11933,10 +11934,10 @@
         <v>45254</v>
       </c>
       <c r="B214" s="1">
-        <v>371.0383911132812</v>
+        <v>371.0383605957031</v>
       </c>
       <c r="C214" s="1">
-        <v>156.9695046408451</v>
+        <v>156.969522128809</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -11944,10 +11945,10 @@
         <v>45257</v>
       </c>
       <c r="B215" s="1">
-        <v>372.1983947753906</v>
+        <v>372.1983642578125</v>
       </c>
       <c r="C215" s="1">
-        <v>157.4602495464505</v>
+        <v>157.4602671294516</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -11958,7 +11959,7 @@
         <v>376.2191467285156</v>
       </c>
       <c r="C216" s="1">
-        <v>159.1612472261571</v>
+        <v>159.1612780491766</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -11969,7 +11970,7 @@
         <v>372.434326171875</v>
       </c>
       <c r="C217" s="1">
-        <v>157.5600614131532</v>
+        <v>157.5600919260886</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -11980,7 +11981,7 @@
         <v>372.4933166503906</v>
       </c>
       <c r="C218" s="1">
-        <v>157.5850176074795</v>
+        <v>157.5850481252479</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -11991,7 +11992,7 @@
         <v>368.1678466796875</v>
       </c>
       <c r="C219" s="1">
-        <v>155.7551075633924</v>
+        <v>155.755137726782</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -12002,7 +12003,7 @@
         <v>362.8887939453125</v>
       </c>
       <c r="C220" s="1">
-        <v>153.5217799279382</v>
+        <v>153.5218096588237</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -12010,10 +12011,10 @@
         <v>45265</v>
       </c>
       <c r="B221" s="1">
-        <v>366.2114868164062</v>
+        <v>366.2115173339844</v>
       </c>
       <c r="C221" s="1">
-        <v>154.9274604896837</v>
+        <v>154.9275034033968</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -12021,10 +12022,10 @@
         <v>45266</v>
       </c>
       <c r="B222" s="1">
-        <v>362.5545654296875</v>
+        <v>362.5545043945312</v>
       </c>
       <c r="C222" s="1">
-        <v>153.3803830110933</v>
+        <v>153.3803868933863</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -12032,10 +12033,10 @@
         <v>45267</v>
       </c>
       <c r="B223" s="1">
-        <v>364.6681213378906</v>
+        <v>364.6680908203125</v>
       </c>
       <c r="C223" s="1">
-        <v>154.2745325974634</v>
+        <v>154.2745495635215</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -12043,10 +12044,10 @@
         <v>45268</v>
       </c>
       <c r="B224" s="1">
-        <v>367.8925170898438</v>
+        <v>367.892578125</v>
       </c>
       <c r="C224" s="1">
-        <v>155.6386281090667</v>
+        <v>155.6386840711088</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -12054,10 +12055,10 @@
         <v>45271</v>
       </c>
       <c r="B225" s="1">
-        <v>365.0121765136719</v>
+        <v>365.0121459960938</v>
       </c>
       <c r="C225" s="1">
-        <v>154.4200867282623</v>
+        <v>154.4201037225082</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -12065,10 +12066,10 @@
         <v>45272</v>
       </c>
       <c r="B226" s="1">
-        <v>368.0400085449219</v>
+        <v>368.0400390625</v>
       </c>
       <c r="C226" s="1">
-        <v>155.7010250501835</v>
+        <v>155.7010681137045</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -12079,7 +12080,7 @@
         <v>368.0301513671875</v>
       </c>
       <c r="C227" s="1">
-        <v>155.6968549256272</v>
+        <v>155.6968850777357</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -12087,10 +12088,10 @@
         <v>45274</v>
       </c>
       <c r="B228" s="1">
-        <v>359.7331237792969</v>
+        <v>359.7330932617188</v>
       </c>
       <c r="C228" s="1">
-        <v>152.1867590928081</v>
+        <v>152.1867756545499</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -12098,10 +12099,10 @@
         <v>45275</v>
       </c>
       <c r="B229" s="1">
-        <v>364.4518127441406</v>
+        <v>364.4518737792969</v>
       </c>
       <c r="C229" s="1">
-        <v>154.1830222480664</v>
+        <v>154.1830779282172</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -12112,7 +12113,7 @@
         <v>366.3392944335938</v>
       </c>
       <c r="C230" s="1">
-        <v>154.9815300922901</v>
+        <v>154.9815601058695</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -12120,10 +12121,10 @@
         <v>45279</v>
       </c>
       <c r="B231" s="1">
-        <v>366.93896484375</v>
+        <v>366.9389038085938</v>
       </c>
       <c r="C231" s="1">
-        <v>155.235223428302</v>
+        <v>155.2352276698017</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -12131,10 +12132,10 @@
         <v>45280</v>
       </c>
       <c r="B232" s="1">
-        <v>364.3437194824219</v>
+        <v>364.3436889648438</v>
       </c>
       <c r="C232" s="1">
-        <v>154.1372928945725</v>
+        <v>154.1373098340529</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -12145,7 +12146,7 @@
         <v>367.2142028808594</v>
       </c>
       <c r="C233" s="1">
-        <v>155.3516641508206</v>
+        <v>155.3516942360799</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -12156,7 +12157,7 @@
         <v>368.2366333007812</v>
       </c>
       <c r="C234" s="1">
-        <v>155.7842080610702</v>
+        <v>155.7842382300955</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -12164,10 +12165,10 @@
         <v>45286</v>
       </c>
       <c r="B235" s="1">
-        <v>368.3153076171875</v>
+        <v>368.3152770996094</v>
       </c>
       <c r="C235" s="1">
-        <v>155.8174915939068</v>
+        <v>155.8175088587729</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -12175,10 +12176,10 @@
         <v>45287</v>
       </c>
       <c r="B236" s="1">
-        <v>367.7352905273438</v>
+        <v>367.7352600097656</v>
       </c>
       <c r="C236" s="1">
-        <v>155.5721126858029</v>
+        <v>155.5721299031492</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -12189,7 +12190,7 @@
         <v>368.9248046875</v>
       </c>
       <c r="C237" s="1">
-        <v>156.0753421438727</v>
+        <v>156.0753723692787</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -12200,7 +12201,7 @@
         <v>369.6719360351562</v>
       </c>
       <c r="C238" s="1">
-        <v>156.391419510399</v>
+        <v>156.3914497970162</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -12208,10 +12209,10 @@
         <v>45293</v>
       </c>
       <c r="B239" s="1">
-        <v>364.5894775390625</v>
+        <v>364.5894470214844</v>
       </c>
       <c r="C239" s="1">
-        <v>154.2412619752292</v>
+        <v>154.2412789348441</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -12222,7 +12223,7 @@
         <v>364.3240356445312</v>
       </c>
       <c r="C240" s="1">
-        <v>154.1289655560622</v>
+        <v>154.1289954045347</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -12233,7 +12234,7 @@
         <v>361.7090759277344</v>
       </c>
       <c r="C241" s="1">
-        <v>153.0226947732201</v>
+        <v>153.0227244074533</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -12241,10 +12242,10 @@
         <v>45296</v>
       </c>
       <c r="B242" s="1">
-        <v>361.5222778320312</v>
+        <v>361.5223083496094</v>
       </c>
       <c r="C242" s="1">
-        <v>152.9436689762873</v>
+        <v>152.9437115058213</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -12252,10 +12253,10 @@
         <v>45299</v>
       </c>
       <c r="B243" s="1">
-        <v>368.3447570800781</v>
+        <v>368.3447265625</v>
       </c>
       <c r="C243" s="1">
-        <v>155.8299503251664</v>
+        <v>155.8299675924453</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -12266,7 +12267,7 @@
         <v>369.4261474609375</v>
       </c>
       <c r="C244" s="1">
-        <v>156.28743751914</v>
+        <v>156.2874677856202</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -12274,10 +12275,10 @@
         <v>45301</v>
       </c>
       <c r="B245" s="1">
-        <v>376.2879028320312</v>
+        <v>376.2879333496094</v>
       </c>
       <c r="C245" s="1">
-        <v>159.1903348132326</v>
+        <v>159.1903785524901</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -12288,7 +12289,7 @@
         <v>378.116455078125</v>
       </c>
       <c r="C246" s="1">
-        <v>159.9639122843348</v>
+        <v>159.9639432627978</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -12296,10 +12297,10 @@
         <v>45303</v>
       </c>
       <c r="B247" s="1">
-        <v>381.8914184570312</v>
+        <v>381.8914489746094</v>
       </c>
       <c r="C247" s="1">
-        <v>161.5609279727824</v>
+        <v>161.5609721711267</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -12307,10 +12308,10 @@
         <v>45307</v>
       </c>
       <c r="B248" s="1">
-        <v>383.660888671875</v>
+        <v>383.6609497070312</v>
       </c>
       <c r="C248" s="1">
-        <v>162.3095105177513</v>
+        <v>162.3095677716703</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -12321,7 +12322,7 @@
         <v>382.8744812011719</v>
       </c>
       <c r="C249" s="1">
-        <v>161.9768172060114</v>
+        <v>161.9768485742916</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -12329,10 +12330,10 @@
         <v>45309</v>
       </c>
       <c r="B250" s="1">
-        <v>387.1999816894531</v>
+        <v>387.199951171875</v>
       </c>
       <c r="C250" s="1">
-        <v>163.8067401607009</v>
+        <v>163.8067589727574</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -12343,7 +12344,7 @@
         <v>391.9186706542969</v>
       </c>
       <c r="C251" s="1">
-        <v>165.8030033159591</v>
+        <v>165.803035425215</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -12351,10 +12352,10 @@
         <v>45313</v>
       </c>
       <c r="B252" s="1">
-        <v>389.7952575683594</v>
+        <v>389.7952270507812</v>
       </c>
       <c r="C252" s="1">
-        <v>164.9046836050327</v>
+        <v>164.9047026297159</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -12365,7 +12366,7 @@
         <v>392.1447448730469</v>
       </c>
       <c r="C253" s="1">
-        <v>165.8986450581054</v>
+        <v>165.8986771858832</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -12373,10 +12374,10 @@
         <v>45315</v>
       </c>
       <c r="B254" s="1">
-        <v>395.7427673339844</v>
+        <v>395.7427978515625</v>
       </c>
       <c r="C254" s="1">
-        <v>167.4208050741766</v>
+        <v>167.4208504073393</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -12384,10 +12385,10 @@
         <v>45316</v>
       </c>
       <c r="B255" s="1">
-        <v>398.0137023925781</v>
+        <v>398.0136413574219</v>
       </c>
       <c r="C255" s="1">
-        <v>168.3815346368222</v>
+        <v>168.3815414242243</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -12398,7 +12399,7 @@
         <v>397.089599609375</v>
       </c>
       <c r="C256" s="1">
-        <v>167.9905886873171</v>
+        <v>167.9906212202187</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -12409,7 +12410,7 @@
         <v>402.7815551757812</v>
       </c>
       <c r="C257" s="1">
-        <v>170.3985967724527</v>
+        <v>170.3986297716869</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -12420,7 +12421,7 @@
         <v>401.6706848144531</v>
       </c>
       <c r="C258" s="1">
-        <v>169.9286379366172</v>
+        <v>169.9286708448396</v>
       </c>
     </row>
   </sheetData>
@@ -15307,7 +15308,7 @@
         <v>44949</v>
       </c>
       <c r="B2" s="1">
-        <v>98.97199249267578</v>
+        <v>98.97200012207031</v>
       </c>
       <c r="C2" s="1">
         <v>100</v>
@@ -15321,7 +15322,7 @@
         <v>96.89913177490234</v>
       </c>
       <c r="C3" s="1">
-        <v>97.905608783286</v>
+        <v>97.90560123609573</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -15329,10 +15330,10 @@
         <v>44951</v>
       </c>
       <c r="B4" s="1">
-        <v>94.43946075439453</v>
+        <v>94.439453125</v>
       </c>
       <c r="C4" s="1">
-        <v>95.42038952220076</v>
+        <v>95.42037445794776</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -15340,10 +15341,10 @@
         <v>44952</v>
       </c>
       <c r="B5" s="1">
-        <v>96.72059631347656</v>
+        <v>96.72060394287109</v>
       </c>
       <c r="C5" s="1">
-        <v>97.72521890032088</v>
+        <v>97.72521907567557</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -15351,10 +15352,10 @@
         <v>44953</v>
       </c>
       <c r="B6" s="1">
-        <v>98.55544281005859</v>
+        <v>98.55545043945312</v>
       </c>
       <c r="C6" s="1">
-        <v>99.57912367718775</v>
+        <v>99.57912370963159</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -15365,7 +15366,7 @@
         <v>96.14536285400391</v>
       </c>
       <c r="C7" s="1">
-        <v>97.14401057563728</v>
+        <v>97.14400308715588</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -15373,10 +15374,10 @@
         <v>44957</v>
       </c>
       <c r="B8" s="1">
-        <v>98.02977752685547</v>
+        <v>98.02978515625</v>
       </c>
       <c r="C8" s="1">
-        <v>99.04799838611915</v>
+        <v>99.04799845950552</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -15384,10 +15385,10 @@
         <v>44958</v>
       </c>
       <c r="B9" s="1">
-        <v>99.60675811767578</v>
+        <v>99.60675048828125</v>
       </c>
       <c r="C9" s="1">
-        <v>100.6413588420451</v>
+        <v>100.6413433753264</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -15395,10 +15396,10 @@
         <v>44959</v>
       </c>
       <c r="B10" s="1">
-        <v>106.8568267822266</v>
+        <v>106.856819152832</v>
       </c>
       <c r="C10" s="1">
-        <v>107.9667329018705</v>
+        <v>107.9667168704651</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -15406,10 +15407,10 @@
         <v>44960</v>
       </c>
       <c r="B11" s="1">
-        <v>103.9210968017578</v>
+        <v>103.9210891723633</v>
       </c>
       <c r="C11" s="1">
-        <v>105.0005099265313</v>
+        <v>105.0004941237813</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -15420,7 +15421,7 @@
         <v>102.0565032958984</v>
       </c>
       <c r="C12" s="1">
-        <v>103.1165491625835</v>
+        <v>103.1165412137006</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -15428,10 +15429,10 @@
         <v>44964</v>
       </c>
       <c r="B13" s="1">
-        <v>106.7576446533203</v>
+        <v>106.7576522827148</v>
       </c>
       <c r="C13" s="1">
-        <v>107.8665205828009</v>
+        <v>107.8665199763992</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -15439,10 +15440,10 @@
         <v>44965</v>
       </c>
       <c r="B14" s="1">
-        <v>98.55544281005859</v>
+        <v>98.55545043945312</v>
       </c>
       <c r="C14" s="1">
-        <v>99.57912367718775</v>
+        <v>99.57912370963159</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -15450,10 +15451,10 @@
         <v>44966</v>
       </c>
       <c r="B15" s="1">
-        <v>94.23118591308594</v>
+        <v>94.23119354248047</v>
       </c>
       <c r="C15" s="1">
-        <v>95.20995136079465</v>
+        <v>95.20995173004222</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -15461,10 +15462,10 @@
         <v>44967</v>
       </c>
       <c r="B16" s="1">
-        <v>93.79478454589844</v>
+        <v>93.79479217529297</v>
       </c>
       <c r="C16" s="1">
-        <v>94.76901715688862</v>
+        <v>94.76901756012623</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -15472,10 +15473,10 @@
         <v>44970</v>
       </c>
       <c r="B17" s="1">
-        <v>93.83446502685547</v>
+        <v>93.83445739746094</v>
       </c>
       <c r="C17" s="1">
-        <v>94.80910979315638</v>
+        <v>94.80909477602472</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -15483,10 +15484,10 @@
         <v>44971</v>
       </c>
       <c r="B18" s="1">
-        <v>93.90390014648438</v>
+        <v>93.90388488769531</v>
       </c>
       <c r="C18" s="1">
-        <v>94.87926612514499</v>
+        <v>94.87924339396589</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -15497,7 +15498,7 @@
         <v>96.14536285400391</v>
       </c>
       <c r="C19" s="1">
-        <v>97.14401057563728</v>
+        <v>97.14400308715588</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -15505,10 +15506,10 @@
         <v>44973</v>
       </c>
       <c r="B20" s="1">
-        <v>94.72708892822266</v>
+        <v>94.72708129882812</v>
       </c>
       <c r="C20" s="1">
-        <v>95.71100524750246</v>
+        <v>95.71099016084693</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -15516,10 +15517,10 @@
         <v>44974</v>
       </c>
       <c r="B21" s="1">
-        <v>93.57659149169922</v>
+        <v>93.57658386230469</v>
       </c>
       <c r="C21" s="1">
-        <v>94.54855776357554</v>
+        <v>94.5485427665289</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -15527,10 +15528,10 @@
         <v>44978</v>
       </c>
       <c r="B22" s="1">
-        <v>91.03757476806641</v>
+        <v>91.03758239746094</v>
       </c>
       <c r="C22" s="1">
-        <v>91.98316864723468</v>
+        <v>91.98316926522328</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -15538,10 +15539,10 @@
         <v>44979</v>
       </c>
       <c r="B23" s="1">
-        <v>90.89871978759766</v>
+        <v>90.89872741699219</v>
       </c>
       <c r="C23" s="1">
-        <v>91.84287140053731</v>
+        <v>91.84287202934092</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -15552,7 +15553,7 @@
         <v>90.14495849609375</v>
       </c>
       <c r="C24" s="1">
-        <v>91.08128090152853</v>
+        <v>91.08127388040108</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -15560,10 +15561,10 @@
         <v>44981</v>
       </c>
       <c r="B25" s="1">
-        <v>88.39937591552734</v>
+        <v>88.39938354492188</v>
       </c>
       <c r="C25" s="1">
-        <v>89.31756721182425</v>
+        <v>89.31756803529447</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -15571,10 +15572,10 @@
         <v>44984</v>
       </c>
       <c r="B26" s="1">
-        <v>89.13332366943359</v>
+        <v>89.13331604003906</v>
       </c>
       <c r="C26" s="1">
-        <v>90.0591383729389</v>
+        <v>90.05912372196542</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -15582,10 +15583,10 @@
         <v>44985</v>
       </c>
       <c r="B27" s="1">
-        <v>89.32175445556641</v>
+        <v>89.32176208496094</v>
       </c>
       <c r="C27" s="1">
-        <v>90.2495263618912</v>
+        <v>90.24952711352005</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -15593,10 +15594,10 @@
         <v>44986</v>
       </c>
       <c r="B28" s="1">
-        <v>89.61930847167969</v>
+        <v>89.61928558349609</v>
       </c>
       <c r="C28" s="1">
-        <v>90.55017102773976</v>
+        <v>90.55014092163567</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -15604,10 +15605,10 @@
         <v>44987</v>
       </c>
       <c r="B29" s="1">
-        <v>91.245849609375</v>
+        <v>91.24585723876953</v>
       </c>
       <c r="C29" s="1">
-        <v>92.19360680864081</v>
+        <v>92.19360741040749</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -15615,10 +15616,10 @@
         <v>44988</v>
       </c>
       <c r="B30" s="1">
-        <v>92.88233184814453</v>
+        <v>92.88231658935547</v>
       </c>
       <c r="C30" s="1">
-        <v>93.84708694736857</v>
+        <v>93.84706429575644</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -15626,10 +15627,10 @@
         <v>44991</v>
       </c>
       <c r="B31" s="1">
-        <v>94.35019683837891</v>
+        <v>94.35020446777344</v>
       </c>
       <c r="C31" s="1">
-        <v>95.33019843503817</v>
+        <v>95.33019879501633</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -15637,10 +15638,10 @@
         <v>44992</v>
       </c>
       <c r="B32" s="1">
-        <v>93.09062194824219</v>
+        <v>93.09060668945312</v>
       </c>
       <c r="C32" s="1">
-        <v>94.05754052605455</v>
+        <v>94.05751785821931</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -15651,7 +15652,7 @@
         <v>93.47740936279297</v>
       </c>
       <c r="C33" s="1">
-        <v>94.448345444506</v>
+        <v>94.44833816382369</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -15662,7 +15663,7 @@
         <v>91.56322479248047</v>
       </c>
       <c r="C34" s="1">
-        <v>92.51427852102343</v>
+        <v>92.51427138943137</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -15670,10 +15671,10 @@
         <v>44995</v>
       </c>
       <c r="B35" s="1">
-        <v>89.8870849609375</v>
+        <v>89.88707733154297</v>
       </c>
       <c r="C35" s="1">
-        <v>90.82072887194769</v>
+        <v>90.82071416226594</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -15681,10 +15682,10 @@
         <v>44998</v>
       </c>
       <c r="B36" s="1">
-        <v>90.36316680908203</v>
+        <v>90.36315155029297</v>
       </c>
       <c r="C36" s="1">
-        <v>91.30175571212146</v>
+        <v>91.30173325671974</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -15692,10 +15693,10 @@
         <v>44999</v>
       </c>
       <c r="B37" s="1">
-        <v>93.19970703125</v>
+        <v>93.19971466064453</v>
       </c>
       <c r="C37" s="1">
-        <v>94.1677586597512</v>
+        <v>94.16775910933765</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -15703,10 +15704,10 @@
         <v>45000</v>
       </c>
       <c r="B38" s="1">
-        <v>95.32215881347656</v>
+        <v>95.32216644287109</v>
       </c>
       <c r="C38" s="1">
-        <v>96.31225603599997</v>
+        <v>96.31225632027484</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -15714,10 +15715,10 @@
         <v>45001</v>
       </c>
       <c r="B39" s="1">
-        <v>99.49765014648438</v>
+        <v>99.49766540527344</v>
       </c>
       <c r="C39" s="1">
-        <v>100.5311175824287</v>
+        <v>100.5311252501261</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -15725,10 +15726,10 @@
         <v>45002</v>
       </c>
       <c r="B40" s="1">
-        <v>100.786994934082</v>
+        <v>100.7870025634766</v>
       </c>
       <c r="C40" s="1">
-        <v>101.833854604413</v>
+        <v>101.8338544630478</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -15736,10 +15737,10 @@
         <v>45005</v>
       </c>
       <c r="B41" s="1">
-        <v>100.3902816772461</v>
+        <v>100.390266418457</v>
       </c>
       <c r="C41" s="1">
-        <v>101.4330207454147</v>
+        <v>101.4329975090303</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -15750,7 +15751,7 @@
         <v>104.059944152832</v>
       </c>
       <c r="C42" s="1">
-        <v>105.1407994645887</v>
+        <v>105.1407913596637</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -15761,7 +15762,7 @@
         <v>102.5226516723633</v>
       </c>
       <c r="C43" s="1">
-        <v>103.5875393535704</v>
+        <v>103.5875313683806</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -15772,7 +15773,7 @@
         <v>104.734375</v>
       </c>
       <c r="C44" s="1">
-        <v>105.8222355256217</v>
+        <v>105.8222273681672</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -15780,10 +15781,10 @@
         <v>45009</v>
       </c>
       <c r="B45" s="1">
-        <v>104.57568359375</v>
+        <v>104.5756912231445</v>
       </c>
       <c r="C45" s="1">
-        <v>105.6618958151104</v>
+        <v>105.6618953786553</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -15794,7 +15795,7 @@
         <v>101.6201095581055</v>
       </c>
       <c r="C46" s="1">
-        <v>102.6756226673174</v>
+        <v>102.675614752424</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -15802,10 +15803,10 @@
         <v>45013</v>
       </c>
       <c r="B47" s="1">
-        <v>100.2018356323242</v>
+        <v>100.2018432617188</v>
       </c>
       <c r="C47" s="1">
-        <v>101.2426173391825</v>
+        <v>101.2426172433937</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -15816,7 +15817,7 @@
         <v>100.5588836669922</v>
       </c>
       <c r="C48" s="1">
-        <v>101.603373979193</v>
+        <v>101.6033661469553</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -15824,10 +15825,10 @@
         <v>45015</v>
       </c>
       <c r="B49" s="1">
-        <v>100.0629806518555</v>
+        <v>100.0629959106445</v>
       </c>
       <c r="C49" s="1">
-        <v>101.1023200924852</v>
+        <v>101.1023277161506</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -15835,10 +15836,10 @@
         <v>45016</v>
       </c>
       <c r="B50" s="1">
-        <v>102.8796920776367</v>
+        <v>102.8797149658203</v>
       </c>
       <c r="C50" s="1">
-        <v>103.9482882849409</v>
+        <v>103.9483033978603</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -15846,10 +15847,10 @@
         <v>45019</v>
       </c>
       <c r="B51" s="1">
-        <v>103.5045394897461</v>
+        <v>103.5045318603516</v>
       </c>
       <c r="C51" s="1">
-        <v>104.5796258950791</v>
+        <v>104.5796101247736</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -15857,10 +15858,10 @@
         <v>45020</v>
       </c>
       <c r="B52" s="1">
-        <v>103.8615951538086</v>
+        <v>103.861572265625</v>
       </c>
       <c r="C52" s="1">
-        <v>104.9403902437295</v>
+        <v>104.9403590283353</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -15871,7 +15872,7 @@
         <v>103.6136322021484</v>
       </c>
       <c r="C53" s="1">
-        <v>104.6898517374157</v>
+        <v>104.6898436672526</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -15879,10 +15880,10 @@
         <v>45022</v>
       </c>
       <c r="B54" s="1">
-        <v>107.53125</v>
+        <v>107.5312423706055</v>
       </c>
       <c r="C54" s="1">
-        <v>108.6481612542636</v>
+        <v>108.6481451703293</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -15893,7 +15894,7 @@
         <v>105.5674896240234</v>
       </c>
       <c r="C55" s="1">
-        <v>106.6640035885261</v>
+        <v>106.6639953661827</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -15901,10 +15902,10 @@
         <v>45027</v>
       </c>
       <c r="B56" s="1">
-        <v>104.4864120483398</v>
+        <v>104.4864196777344</v>
       </c>
       <c r="C56" s="1">
-        <v>105.5716970193079</v>
+        <v>105.5716965898059</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -15915,7 +15916,7 @@
         <v>103.7822418212891</v>
       </c>
       <c r="C57" s="1">
-        <v>104.8602126798339</v>
+        <v>104.8602045965383</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -15923,10 +15924,10 @@
         <v>45029</v>
       </c>
       <c r="B58" s="1">
-        <v>106.5493545532227</v>
+        <v>106.5493774414062</v>
       </c>
       <c r="C58" s="1">
-        <v>107.6560670041149</v>
+        <v>107.656081831215</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -15934,10 +15935,10 @@
         <v>45030</v>
       </c>
       <c r="B59" s="1">
-        <v>107.9775772094727</v>
+        <v>107.9775695800781</v>
       </c>
       <c r="C59" s="1">
-        <v>109.0991243987165</v>
+        <v>109.0991082800191</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -15945,10 +15946,10 @@
         <v>45033</v>
       </c>
       <c r="B60" s="1">
-        <v>105.1013336181641</v>
+        <v>105.1013488769531</v>
       </c>
       <c r="C60" s="1">
-        <v>106.1930056888992</v>
+        <v>106.1930129201421</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -15959,7 +15960,7 @@
         <v>103.6433868408203</v>
       </c>
       <c r="C61" s="1">
-        <v>104.7199154331365</v>
+        <v>104.7199073606559</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -15967,10 +15968,10 @@
         <v>45035</v>
       </c>
       <c r="B62" s="1">
-        <v>103.3260192871094</v>
+        <v>103.3260116577148</v>
       </c>
       <c r="C62" s="1">
-        <v>104.3992514293938</v>
+        <v>104.3992356729927</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -15978,10 +15979,10 @@
         <v>45036</v>
       </c>
       <c r="B63" s="1">
-        <v>104.4269180297852</v>
+        <v>104.4269104003906</v>
       </c>
       <c r="C63" s="1">
-        <v>105.511585045146</v>
+        <v>105.5115692029992</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -15989,10 +15990,10 @@
         <v>45037</v>
       </c>
       <c r="B64" s="1">
-        <v>104.5459365844727</v>
+        <v>104.5459289550781</v>
       </c>
       <c r="C64" s="1">
-        <v>105.6318398280295</v>
+        <v>105.6318239766126</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -16000,10 +16001,10 @@
         <v>45040</v>
       </c>
       <c r="B65" s="1">
-        <v>105.1013336181641</v>
+        <v>105.1013488769531</v>
       </c>
       <c r="C65" s="1">
-        <v>106.1930056888992</v>
+        <v>106.1930129201421</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -16014,7 +16015,7 @@
         <v>102.9987182617188</v>
       </c>
       <c r="C66" s="1">
-        <v>104.0685507764643</v>
+        <v>104.0685427541951</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -16025,7 +16026,7 @@
         <v>102.85986328125</v>
       </c>
       <c r="C67" s="1">
-        <v>103.928253529767</v>
+        <v>103.9282455183127</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -16033,10 +16034,10 @@
         <v>45043</v>
       </c>
       <c r="B68" s="1">
-        <v>106.7080612182617</v>
+        <v>106.7080383300781</v>
       </c>
       <c r="C68" s="1">
-        <v>107.8164221319061</v>
+        <v>107.8163906948089</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -16047,7 +16048,7 @@
         <v>106.4601058959961</v>
       </c>
       <c r="C69" s="1">
-        <v>107.5658913342322</v>
+        <v>107.5658830423656</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -16058,7 +16059,7 @@
         <v>106.3212585449219</v>
       </c>
       <c r="C70" s="1">
-        <v>107.4256017961748</v>
+        <v>107.4255935151226</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -16069,7 +16070,7 @@
         <v>104.456672668457</v>
       </c>
       <c r="C71" s="1">
-        <v>105.5416487408669</v>
+        <v>105.5416406050418</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -16077,10 +16078,10 @@
         <v>45049</v>
       </c>
       <c r="B72" s="1">
-        <v>104.5459365844727</v>
+        <v>104.5459289550781</v>
       </c>
       <c r="C72" s="1">
-        <v>105.6318398280295</v>
+        <v>105.6318239766126</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -16088,10 +16089,10 @@
         <v>45050</v>
       </c>
       <c r="B73" s="1">
-        <v>103.8318328857422</v>
+        <v>103.8318405151367</v>
       </c>
       <c r="C73" s="1">
-        <v>104.9103188393687</v>
+        <v>104.9103184608499</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -16099,10 +16100,10 @@
         <v>45051</v>
       </c>
       <c r="B74" s="1">
-        <v>104.7046127319336</v>
+        <v>104.7046051025391</v>
       </c>
       <c r="C74" s="1">
-        <v>105.7921641212609</v>
+        <v>105.7921482574852</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -16113,7 +16114,7 @@
         <v>106.8865814208984</v>
       </c>
       <c r="C75" s="1">
-        <v>107.9967965975913</v>
+        <v>107.9967882725078</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -16124,7 +16125,7 @@
         <v>106.4700241088867</v>
       </c>
       <c r="C76" s="1">
-        <v>107.5759125661392</v>
+        <v>107.5759042735001</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -16135,7 +16136,7 @@
         <v>110.8339614868164</v>
       </c>
       <c r="C77" s="1">
-        <v>111.9851775188</v>
+        <v>111.9851688862666</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -16143,10 +16144,10 @@
         <v>45057</v>
       </c>
       <c r="B78" s="1">
-        <v>115.6144409179688</v>
+        <v>115.6144485473633</v>
       </c>
       <c r="C78" s="1">
-        <v>116.8153110856332</v>
+        <v>116.8153097894015</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -16157,7 +16158,7 @@
         <v>116.546745300293</v>
       </c>
       <c r="C79" s="1">
-        <v>117.757299176247</v>
+        <v>117.7572900987615</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -16165,10 +16166,10 @@
         <v>45061</v>
       </c>
       <c r="B80" s="1">
-        <v>115.5549392700195</v>
+        <v>115.554931640625</v>
       </c>
       <c r="C80" s="1">
-        <v>116.7551914028314</v>
+        <v>116.7551746939555</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -16179,7 +16180,7 @@
         <v>118.5303497314453</v>
       </c>
       <c r="C81" s="1">
-        <v>119.7615070144384</v>
+        <v>119.7614977824557</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -16190,7 +16191,7 @@
         <v>119.8494491577148</v>
       </c>
       <c r="C82" s="1">
-        <v>121.0943077321436</v>
+        <v>121.0942983974201</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -16198,10 +16199,10 @@
         <v>45064</v>
       </c>
       <c r="B83" s="1">
-        <v>121.8231506347656</v>
+        <v>121.8231353759766</v>
       </c>
       <c r="C83" s="1">
-        <v>123.0885097557078</v>
+        <v>123.0884848499798</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -16212,7 +16213,7 @@
         <v>121.7537078857422</v>
       </c>
       <c r="C84" s="1">
-        <v>123.0183457150793</v>
+        <v>123.0183362320387</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -16223,7 +16224,7 @@
         <v>124.0249328613281</v>
       </c>
       <c r="C85" s="1">
-        <v>125.3131615699323</v>
+        <v>125.3131519099927</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -16234,7 +16235,7 @@
         <v>121.5553436279297</v>
       </c>
       <c r="C86" s="1">
-        <v>122.8179210769402</v>
+        <v>122.8179116093496</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -16242,10 +16243,10 @@
         <v>45070</v>
       </c>
       <c r="B87" s="1">
-        <v>119.9089660644531</v>
+        <v>119.9089584350586</v>
       </c>
       <c r="C87" s="1">
-        <v>121.1544428322252</v>
+        <v>121.1544257842269</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -16253,10 +16254,10 @@
         <v>45071</v>
       </c>
       <c r="B88" s="1">
-        <v>122.4678039550781</v>
+        <v>122.4678115844727</v>
       </c>
       <c r="C88" s="1">
-        <v>123.7398589951002</v>
+        <v>123.7398571650801</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -16264,10 +16265,10 @@
         <v>45072</v>
       </c>
       <c r="B89" s="1">
-        <v>123.5885391235352</v>
+        <v>123.5885467529297</v>
       </c>
       <c r="C89" s="1">
-        <v>124.8722350746663</v>
+        <v>124.8722331573554</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -16275,10 +16276,10 @@
         <v>45076</v>
       </c>
       <c r="B90" s="1">
-        <v>122.6562347412109</v>
+        <v>122.65625</v>
       </c>
       <c r="C90" s="1">
-        <v>123.9302469840524</v>
+        <v>123.9302528479953</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -16286,10 +16287,10 @@
         <v>45077</v>
       </c>
       <c r="B91" s="1">
-        <v>121.8628082275391</v>
+        <v>121.8628158569336</v>
       </c>
       <c r="C91" s="1">
-        <v>123.1285792660558</v>
+        <v>123.128577483157</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -16300,7 +16301,7 @@
         <v>122.7058410644531</v>
       </c>
       <c r="C92" s="1">
-        <v>123.9803685608671</v>
+        <v>123.9803590036676</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -16308,10 +16309,10 @@
         <v>45079</v>
       </c>
       <c r="B93" s="1">
-        <v>123.6480407714844</v>
+        <v>123.6480484008789</v>
       </c>
       <c r="C93" s="1">
-        <v>124.9323547574681</v>
+        <v>124.9323528355228</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -16319,10 +16320,10 @@
         <v>45082</v>
       </c>
       <c r="B94" s="1">
-        <v>124.9770736694336</v>
+        <v>124.9770660400391</v>
       </c>
       <c r="C94" s="1">
-        <v>126.2751921243601</v>
+        <v>126.2751746816216</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -16330,10 +16331,10 @@
         <v>45083</v>
       </c>
       <c r="B95" s="1">
-        <v>126.2664108276367</v>
+        <v>126.2664031982422</v>
       </c>
       <c r="C95" s="1">
-        <v>127.5779214377045</v>
+        <v>127.5779038945434</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -16341,10 +16342,10 @@
         <v>45084</v>
       </c>
       <c r="B96" s="1">
-        <v>121.4958267211914</v>
+        <v>121.4958419799805</v>
       </c>
       <c r="C96" s="1">
-        <v>122.7577859768585</v>
+        <v>122.7577919311822</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -16352,10 +16353,10 @@
         <v>45085</v>
       </c>
       <c r="B97" s="1">
-        <v>121.138786315918</v>
+        <v>121.1387939453125</v>
       </c>
       <c r="C97" s="1">
-        <v>122.397037045488</v>
+        <v>122.3970353189812</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -16363,10 +16364,10 @@
         <v>45086</v>
       </c>
       <c r="B98" s="1">
-        <v>121.2280578613281</v>
+        <v>121.2280502319336</v>
       </c>
       <c r="C98" s="1">
-        <v>122.4872358412905</v>
+        <v>122.4872186905519</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -16377,7 +16378,7 @@
         <v>122.6264953613281</v>
       </c>
       <c r="C99" s="1">
-        <v>123.9001987056114</v>
+        <v>123.900189154592</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -16385,10 +16386,10 @@
         <v>45090</v>
       </c>
       <c r="B100" s="1">
-        <v>122.8149337768555</v>
+        <v>122.81494140625</v>
       </c>
       <c r="C100" s="1">
-        <v>124.0905944032037</v>
+        <v>124.0905925461466</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -16396,10 +16397,10 @@
         <v>45091</v>
       </c>
       <c r="B101" s="1">
-        <v>122.6562347412109</v>
+        <v>122.65625</v>
       </c>
       <c r="C101" s="1">
-        <v>123.9302469840524</v>
+        <v>123.9302528479953</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -16407,10 +16408,10 @@
         <v>45092</v>
       </c>
       <c r="B102" s="1">
-        <v>124.0646057128906</v>
+        <v>124.0645980834961</v>
       </c>
       <c r="C102" s="1">
-        <v>125.3532464975602</v>
+        <v>125.3532291258912</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -16421,7 +16422,7 @@
         <v>122.5173950195312</v>
       </c>
       <c r="C103" s="1">
-        <v>123.7899651546349</v>
+        <v>123.789955612113</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -16429,10 +16430,10 @@
         <v>45097</v>
       </c>
       <c r="B104" s="1">
-        <v>122.0909118652344</v>
+        <v>122.0909271240234</v>
       </c>
       <c r="C104" s="1">
-        <v>123.3590521826359</v>
+        <v>123.3590580906101</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -16440,10 +16441,10 @@
         <v>45098</v>
       </c>
       <c r="B105" s="1">
-        <v>119.5618209838867</v>
+        <v>119.5618286132812</v>
       </c>
       <c r="C105" s="1">
-        <v>120.8036920068419</v>
+        <v>120.8036904031603</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -16451,10 +16452,10 @@
         <v>45099</v>
       </c>
       <c r="B106" s="1">
-        <v>122.140510559082</v>
+        <v>122.1405029296875</v>
       </c>
       <c r="C106" s="1">
-        <v>123.4091660508106</v>
+        <v>123.4091488290037</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -16465,7 +16466,7 @@
         <v>121.3371505737305</v>
       </c>
       <c r="C107" s="1">
-        <v>122.5974616836271</v>
+        <v>122.5974522330309</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -16473,10 +16474,10 @@
         <v>45103</v>
       </c>
       <c r="B108" s="1">
-        <v>117.3699264526367</v>
+        <v>117.3699340820312</v>
       </c>
       <c r="C108" s="1">
-        <v>118.5890305899646</v>
+        <v>118.5890291570032</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -16487,7 +16488,7 @@
         <v>117.3600158691406</v>
       </c>
       <c r="C109" s="1">
-        <v>118.5790170666975</v>
+        <v>118.5790079258688</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -16495,10 +16496,10 @@
         <v>45105</v>
       </c>
       <c r="B110" s="1">
-        <v>119.1948623657227</v>
+        <v>119.1948699951172</v>
       </c>
       <c r="C110" s="1">
-        <v>120.4329218435644</v>
+        <v>120.4329202684641</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -16506,10 +16507,10 @@
         <v>45106</v>
       </c>
       <c r="B111" s="1">
-        <v>118.1237030029297</v>
+        <v>118.1237182617188</v>
       </c>
       <c r="C111" s="1">
-        <v>119.3506365062532</v>
+        <v>119.3506427232218</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -16517,10 +16518,10 @@
         <v>45107</v>
       </c>
       <c r="B112" s="1">
-        <v>118.7187805175781</v>
+        <v>118.7187881469727</v>
       </c>
       <c r="C112" s="1">
-        <v>119.9518950033906</v>
+        <v>119.951893465371</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -16528,10 +16529,10 @@
         <v>45110</v>
       </c>
       <c r="B113" s="1">
-        <v>118.9171524047852</v>
+        <v>118.9171447753906</v>
       </c>
       <c r="C113" s="1">
-        <v>120.1523273501697</v>
+        <v>120.1523103794208</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -16542,7 +16543,7 @@
         <v>120.7519836425781</v>
       </c>
       <c r="C114" s="1">
-        <v>122.0062167097567</v>
+        <v>122.0062073047375</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -16553,7 +16554,7 @@
         <v>119.1254348754883</v>
       </c>
       <c r="C115" s="1">
-        <v>120.3627732202157</v>
+        <v>120.3627639418836</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -16561,10 +16562,10 @@
         <v>45114</v>
       </c>
       <c r="B116" s="1">
-        <v>118.5005950927734</v>
+        <v>118.500602722168</v>
       </c>
       <c r="C116" s="1">
-        <v>119.7314433187175</v>
+        <v>119.7314417976917</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -16575,7 +16576,7 @@
         <v>115.4954299926758</v>
       </c>
       <c r="C117" s="1">
-        <v>116.6950640113897</v>
+        <v>116.6950550157881</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -16583,10 +16584,10 @@
         <v>45118</v>
       </c>
       <c r="B118" s="1">
-        <v>116.1797790527344</v>
+        <v>116.1797714233398</v>
       </c>
       <c r="C118" s="1">
-        <v>117.3865213043296</v>
+        <v>117.3865045467867</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -16597,7 +16598,7 @@
         <v>117.9551010131836</v>
       </c>
       <c r="C119" s="1">
-        <v>119.1802832724749</v>
+        <v>119.1802740852967</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -16605,10 +16606,10 @@
         <v>45120</v>
       </c>
       <c r="B120" s="1">
-        <v>123.5191192626953</v>
+        <v>123.5191268920898</v>
       </c>
       <c r="C120" s="1">
-        <v>124.8020941599575</v>
+        <v>124.8020922480535</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -16619,7 +16620,7 @@
         <v>124.3918991088867</v>
       </c>
       <c r="C121" s="1">
-        <v>125.6839394418498</v>
+        <v>125.6839297533282</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -16627,10 +16628,10 @@
         <v>45124</v>
       </c>
       <c r="B122" s="1">
-        <v>123.6282043457031</v>
+        <v>123.6282119750977</v>
       </c>
       <c r="C122" s="1">
-        <v>124.9123122936542</v>
+        <v>124.9123103732539</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -16638,10 +16639,10 @@
         <v>45125</v>
       </c>
       <c r="B123" s="1">
-        <v>122.7455215454102</v>
+        <v>122.7455062866211</v>
       </c>
       <c r="C123" s="1">
-        <v>124.0204611971348</v>
+        <v>124.0204362195661</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -16649,10 +16650,10 @@
         <v>45126</v>
       </c>
       <c r="B124" s="1">
-        <v>121.0296936035156</v>
+        <v>121.0296859741211</v>
       </c>
       <c r="C124" s="1">
-        <v>122.2868112031514</v>
+        <v>122.2867940678628</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -16660,10 +16661,10 @@
         <v>45127</v>
       </c>
       <c r="B125" s="1">
-        <v>118.2228927612305</v>
+        <v>118.222900390625</v>
       </c>
       <c r="C125" s="1">
-        <v>119.4508565339627</v>
+        <v>119.4508550345663</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -16671,10 +16672,10 @@
         <v>45128</v>
       </c>
       <c r="B126" s="1">
-        <v>119.0361633300781</v>
+        <v>119.0361709594727</v>
       </c>
       <c r="C126" s="1">
-        <v>120.2725744244132</v>
+        <v>120.2725728616736</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -16685,7 +16686,7 @@
         <v>120.5337982177734</v>
       </c>
       <c r="C127" s="1">
-        <v>121.7857650250835</v>
+        <v>121.7857556370581</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -16693,10 +16694,10 @@
         <v>45132</v>
       </c>
       <c r="B128" s="1">
-        <v>121.2082214355469</v>
+        <v>121.2082138061523</v>
       </c>
       <c r="C128" s="1">
-        <v>122.4671933774766</v>
+        <v>122.467176228283</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -16704,10 +16705,10 @@
         <v>45133</v>
       </c>
       <c r="B129" s="1">
-        <v>128.2103424072266</v>
+        <v>128.2103271484375</v>
       </c>
       <c r="C129" s="1">
-        <v>129.542044348268</v>
+        <v>129.5420189450604</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -16715,10 +16716,10 @@
         <v>45134</v>
       </c>
       <c r="B130" s="1">
-        <v>128.3392944335938</v>
+        <v>128.3392791748047</v>
       </c>
       <c r="C130" s="1">
-        <v>129.6723357803383</v>
+        <v>129.672310367087</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -16726,10 +16727,10 @@
         <v>45135</v>
       </c>
       <c r="B131" s="1">
-        <v>131.4932098388672</v>
+        <v>131.4932250976562</v>
       </c>
       <c r="C131" s="1">
-        <v>132.8590104403507</v>
+        <v>132.8590156160074</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -16737,10 +16738,10 @@
         <v>45138</v>
       </c>
       <c r="B132" s="1">
-        <v>131.6320953369141</v>
+        <v>131.632080078125</v>
       </c>
       <c r="C132" s="1">
-        <v>132.9993385216077</v>
+        <v>132.9993128518898</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -16748,10 +16749,10 @@
         <v>45139</v>
       </c>
       <c r="B133" s="1">
-        <v>130.4716491699219</v>
+        <v>130.4716644287109</v>
       </c>
       <c r="C133" s="1">
-        <v>131.8268389712142</v>
+        <v>131.8268442264373</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -16759,10 +16760,10 @@
         <v>45140</v>
       </c>
       <c r="B134" s="1">
-        <v>127.3276519775391</v>
+        <v>127.3276443481445</v>
       </c>
       <c r="C134" s="1">
-        <v>128.6501855431088</v>
+        <v>128.6501679172906</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -16773,7 +16774,7 @@
         <v>127.3970718383789</v>
       </c>
       <c r="C135" s="1">
-        <v>128.7203264578175</v>
+        <v>128.7203165352318</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -16784,7 +16785,7 @@
         <v>127.0598449707031</v>
       </c>
       <c r="C136" s="1">
-        <v>128.3795968643411</v>
+        <v>128.379586968021</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -16795,7 +16796,7 @@
         <v>130.4518280029297</v>
       </c>
       <c r="C137" s="1">
-        <v>131.8068119246801</v>
+        <v>131.8068017641684</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -16803,10 +16804,10 @@
         <v>45146</v>
       </c>
       <c r="B138" s="1">
-        <v>130.3228607177734</v>
+        <v>130.3228759765625</v>
       </c>
       <c r="C138" s="1">
-        <v>131.67650507533</v>
+        <v>131.6765103421418</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -16817,7 +16818,7 @@
         <v>128.5971527099609</v>
       </c>
       <c r="C139" s="1">
-        <v>129.9328723926393</v>
+        <v>129.9328623765828</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -16825,10 +16826,10 @@
         <v>45148</v>
       </c>
       <c r="B140" s="1">
-        <v>128.6268920898438</v>
+        <v>128.6269073486328</v>
       </c>
       <c r="C140" s="1">
-        <v>129.9629206710803</v>
+        <v>129.9629260699861</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -16836,10 +16837,10 @@
         <v>45149</v>
       </c>
       <c r="B141" s="1">
-        <v>128.4979705810547</v>
+        <v>128.4979553222656</v>
       </c>
       <c r="C141" s="1">
-        <v>129.8326600735697</v>
+        <v>129.8326346479596</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -16847,10 +16848,10 @@
         <v>45152</v>
       </c>
       <c r="B142" s="1">
-        <v>130.2534790039062</v>
+        <v>130.2534637451172</v>
       </c>
       <c r="C142" s="1">
-        <v>131.6064027038209</v>
+        <v>131.6063771414793</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -16858,10 +16859,10 @@
         <v>45153</v>
       </c>
       <c r="B143" s="1">
-        <v>128.7161560058594</v>
+        <v>128.7161712646484</v>
       </c>
       <c r="C143" s="1">
-        <v>130.0531117582429</v>
+        <v>130.0531171501962</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -16869,10 +16870,10 @@
         <v>45154</v>
       </c>
       <c r="B144" s="1">
-        <v>127.64501953125</v>
+        <v>127.6450042724609</v>
       </c>
       <c r="C144" s="1">
-        <v>128.9708495468514</v>
+        <v>128.9708241876752</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -16883,7 +16884,7 @@
         <v>128.8550262451172</v>
       </c>
       <c r="C145" s="1">
-        <v>130.1934244222201</v>
+        <v>130.1934143860786</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -16894,7 +16895,7 @@
         <v>126.4151763916016</v>
       </c>
       <c r="C146" s="1">
-        <v>127.7282322076689</v>
+        <v>127.7282223615602</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -16905,7 +16906,7 @@
         <v>127.3177032470703</v>
       </c>
       <c r="C147" s="1">
-        <v>128.6401334766421</v>
+        <v>128.6401235602382</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -16913,10 +16914,10 @@
         <v>45160</v>
       </c>
       <c r="B148" s="1">
-        <v>128.0219268798828</v>
+        <v>128.0219116210938</v>
       </c>
       <c r="C148" s="1">
-        <v>129.3516717765956</v>
+        <v>129.3516463880631</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -16927,7 +16928,7 @@
         <v>131.2849273681641</v>
       </c>
       <c r="C149" s="1">
-        <v>132.6485645703046</v>
+        <v>132.6485543449052</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -16935,10 +16936,10 @@
         <v>45162</v>
       </c>
       <c r="B150" s="1">
-        <v>128.7161560058594</v>
+        <v>128.7161712646484</v>
       </c>
       <c r="C150" s="1">
-        <v>130.0531117582429</v>
+        <v>130.0531171501962</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -16946,10 +16947,10 @@
         <v>45163</v>
       </c>
       <c r="B151" s="1">
-        <v>128.8153533935547</v>
+        <v>128.8153381347656</v>
       </c>
       <c r="C151" s="1">
-        <v>130.1533394945923</v>
+        <v>130.1533140442621</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -16957,10 +16958,10 @@
         <v>45166</v>
       </c>
       <c r="B152" s="1">
-        <v>129.9360961914062</v>
+        <v>129.9360809326172</v>
       </c>
       <c r="C152" s="1">
-        <v>131.2857232827983</v>
+        <v>131.2856977451767</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -16968,10 +16969,10 @@
         <v>45167</v>
       </c>
       <c r="B153" s="1">
-        <v>133.4669189453125</v>
+        <v>133.4669036865234</v>
       </c>
       <c r="C153" s="1">
-        <v>134.8532201725548</v>
+        <v>134.8531943599278</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -16979,10 +16980,10 @@
         <v>45168</v>
       </c>
       <c r="B154" s="1">
-        <v>134.7661743164062</v>
+        <v>134.7661895751953</v>
       </c>
       <c r="C154" s="1">
-        <v>136.1659707178062</v>
+        <v>136.1659756385413</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -16993,7 +16994,7 @@
         <v>135.0537872314453</v>
       </c>
       <c r="C155" s="1">
-        <v>136.456571025828</v>
+        <v>136.4565605068831</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -17001,10 +17002,10 @@
         <v>45170</v>
       </c>
       <c r="B156" s="1">
-        <v>134.5479278564453</v>
+        <v>134.5479583740234</v>
       </c>
       <c r="C156" s="1">
-        <v>135.9454573640136</v>
+        <v>135.945477719026</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -17012,10 +17013,10 @@
         <v>45174</v>
       </c>
       <c r="B157" s="1">
-        <v>134.6570739746094</v>
+        <v>134.6570434570312</v>
       </c>
       <c r="C157" s="1">
-        <v>136.0557371668297</v>
+        <v>136.0556958442263</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -17023,10 +17024,10 @@
         <v>45175</v>
       </c>
       <c r="B158" s="1">
-        <v>133.3578186035156</v>
+        <v>133.3578033447266</v>
       </c>
       <c r="C158" s="1">
-        <v>134.7429866215783</v>
+        <v>134.7429608174488</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -17037,7 +17038,7 @@
         <v>134.1512298583984</v>
       </c>
       <c r="C159" s="1">
-        <v>135.5446389222951</v>
+        <v>135.5446284736478</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -17045,10 +17046,10 @@
         <v>45177</v>
       </c>
       <c r="B160" s="1">
-        <v>135.2620849609375</v>
+        <v>135.2620697021484</v>
       </c>
       <c r="C160" s="1">
-        <v>136.6670323131539</v>
+        <v>136.6670063607067</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -17059,7 +17060,7 @@
         <v>135.7976226806641</v>
       </c>
       <c r="C161" s="1">
-        <v>137.2081325842899</v>
+        <v>137.2081220074099</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -17067,10 +17068,10 @@
         <v>45181</v>
       </c>
       <c r="B162" s="1">
-        <v>134.2305603027344</v>
+        <v>134.2305908203125</v>
       </c>
       <c r="C162" s="1">
-        <v>135.6247933602709</v>
+        <v>135.6248137400021</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -17078,10 +17079,10 @@
         <v>45182</v>
       </c>
       <c r="B163" s="1">
-        <v>135.5893707275391</v>
+        <v>135.58935546875</v>
       </c>
       <c r="C163" s="1">
-        <v>136.9977175488036</v>
+        <v>136.997691570865</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -17092,7 +17093,7 @@
         <v>136.9679565429688</v>
       </c>
       <c r="C164" s="1">
-        <v>138.3906225320307</v>
+        <v>138.3906118639968</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -17100,10 +17101,10 @@
         <v>45184</v>
       </c>
       <c r="B165" s="1">
-        <v>136.273681640625</v>
+        <v>136.2736968994141</v>
       </c>
       <c r="C165" s="1">
-        <v>137.6891362985439</v>
+        <v>137.6891411018636</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -17111,10 +17112,10 @@
         <v>45187</v>
       </c>
       <c r="B166" s="1">
-        <v>137.0770721435547</v>
+        <v>137.0770568847656</v>
       </c>
       <c r="C166" s="1">
-        <v>138.5008715002871</v>
+        <v>138.5008454064758</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -17122,10 +17123,10 @@
         <v>45188</v>
       </c>
       <c r="B167" s="1">
-        <v>136.9084625244141</v>
+        <v>136.908447265625</v>
       </c>
       <c r="C167" s="1">
-        <v>138.3305105578689</v>
+        <v>138.3304844771901</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -17133,10 +17134,10 @@
         <v>45189</v>
       </c>
       <c r="B168" s="1">
-        <v>132.6437072753906</v>
+        <v>132.6436767578125</v>
       </c>
       <c r="C168" s="1">
-        <v>134.0214579242776</v>
+        <v>134.0214167584894</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -17144,10 +17145,10 @@
         <v>45190</v>
       </c>
       <c r="B169" s="1">
-        <v>129.3707580566406</v>
+        <v>129.3707427978516</v>
       </c>
       <c r="C169" s="1">
-        <v>130.7145130641019</v>
+        <v>130.7144875705129</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -17158,7 +17159,7 @@
         <v>129.1822967529297</v>
       </c>
       <c r="C170" s="1">
-        <v>130.5240942405899</v>
+        <v>130.5240841789582</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -17166,10 +17167,10 @@
         <v>45194</v>
       </c>
       <c r="B171" s="1">
-        <v>130.0352630615234</v>
+        <v>130.0352783203125</v>
       </c>
       <c r="C171" s="1">
-        <v>131.385920184588</v>
+        <v>131.3859254737999</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -17177,10 +17178,10 @@
         <v>45195</v>
       </c>
       <c r="B172" s="1">
-        <v>127.5160903930664</v>
+        <v>127.5160827636719</v>
       </c>
       <c r="C172" s="1">
-        <v>128.840581240701</v>
+        <v>128.8405636002059</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -17191,7 +17192,7 @@
         <v>129.4699249267578</v>
       </c>
       <c r="C173" s="1">
-        <v>130.8147099658916</v>
+        <v>130.8146998818574</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -17202,7 +17203,7 @@
         <v>131.2254180908203</v>
       </c>
       <c r="C174" s="1">
-        <v>132.5884371788629</v>
+        <v>132.5884269580984</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -17210,10 +17211,10 @@
         <v>45198</v>
       </c>
       <c r="B175" s="1">
-        <v>129.7873229980469</v>
+        <v>129.7873077392578</v>
       </c>
       <c r="C175" s="1">
-        <v>131.135404804194</v>
+        <v>131.1353792781599</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -17221,10 +17222,10 @@
         <v>45201</v>
       </c>
       <c r="B176" s="1">
-        <v>133.0701751708984</v>
+        <v>133.0701599121094</v>
       </c>
       <c r="C176" s="1">
-        <v>134.4523554789968</v>
+        <v>134.452329697271</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -17232,10 +17233,10 @@
         <v>45202</v>
       </c>
       <c r="B177" s="1">
-        <v>131.3444061279297</v>
+        <v>131.3444366455078</v>
       </c>
       <c r="C177" s="1">
-        <v>132.7086611271866</v>
+        <v>132.7086817317119</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -17243,10 +17244,10 @@
         <v>45203</v>
       </c>
       <c r="B178" s="1">
-        <v>134.1314086914062</v>
+        <v>134.1313934326172</v>
       </c>
       <c r="C178" s="1">
-        <v>135.5246118757611</v>
+        <v>135.5245860113789</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -17254,10 +17255,10 @@
         <v>45204</v>
       </c>
       <c r="B179" s="1">
-        <v>133.9628295898438</v>
+        <v>133.9627990722656</v>
       </c>
       <c r="C179" s="1">
-        <v>135.3542817679026</v>
+        <v>135.3542404993718</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -17268,7 +17269,7 @@
         <v>136.4522247314453</v>
       </c>
       <c r="C180" s="1">
-        <v>137.8695338901489</v>
+        <v>137.8695232622838</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -17279,7 +17280,7 @@
         <v>137.2853393554688</v>
       </c>
       <c r="C181" s="1">
-        <v>138.7113019530533</v>
+        <v>138.7112912602993</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -17290,7 +17291,7 @@
         <v>136.9282836914062</v>
       </c>
       <c r="C182" s="1">
-        <v>138.3505376044029</v>
+        <v>138.350526939459</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -17298,10 +17299,10 @@
         <v>45210</v>
       </c>
       <c r="B183" s="1">
-        <v>139.3978576660156</v>
+        <v>139.3979034423828</v>
       </c>
       <c r="C183" s="1">
-        <v>140.8457626801153</v>
+        <v>140.8457980746594</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -17309,10 +17310,10 @@
         <v>45211</v>
       </c>
       <c r="B184" s="1">
-        <v>137.8308410644531</v>
+        <v>137.8308258056641</v>
       </c>
       <c r="C184" s="1">
-        <v>139.2624697079358</v>
+        <v>139.2624435554156</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -17320,10 +17321,10 @@
         <v>45212</v>
       </c>
       <c r="B185" s="1">
-        <v>136.2340240478516</v>
+        <v>136.2340393066406</v>
       </c>
       <c r="C185" s="1">
-        <v>137.6490667881959</v>
+        <v>137.6490715946045</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -17331,10 +17332,10 @@
         <v>45215</v>
       </c>
       <c r="B186" s="1">
-        <v>137.9597778320312</v>
+        <v>137.9597473144531</v>
       </c>
       <c r="C186" s="1">
-        <v>139.3927457227262</v>
+        <v>139.3927041428849</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -17345,7 +17346,7 @@
         <v>138.5746765136719</v>
       </c>
       <c r="C187" s="1">
-        <v>140.0140312663977</v>
+        <v>140.0140204732211</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -17356,7 +17357,7 @@
         <v>136.8291320800781</v>
       </c>
       <c r="C188" s="1">
-        <v>138.2503561198931</v>
+        <v>138.2503454626718</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -17367,7 +17368,7 @@
         <v>136.6208343505859</v>
       </c>
       <c r="C189" s="1">
-        <v>138.0398948325672</v>
+        <v>138.0398841915696</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -17375,10 +17376,10 @@
         <v>45219</v>
       </c>
       <c r="B190" s="1">
-        <v>134.4884643554688</v>
+        <v>134.4884796142578</v>
       </c>
       <c r="C190" s="1">
-        <v>135.8853762244115</v>
+        <v>135.8853811667766</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -17386,10 +17387,10 @@
         <v>45222</v>
       </c>
       <c r="B191" s="1">
-        <v>135.3810729980469</v>
+        <v>135.3810882568359</v>
       </c>
       <c r="C191" s="1">
-        <v>136.7872562614777</v>
+        <v>136.7872611343201</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -17400,7 +17401,7 @@
         <v>137.6721343994141</v>
       </c>
       <c r="C192" s="1">
-        <v>139.1021145801447</v>
+        <v>139.1021038572644</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -17411,7 +17412,7 @@
         <v>124.5803451538086</v>
       </c>
       <c r="C193" s="1">
-        <v>125.8743428480819</v>
+        <v>125.8743331448828</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -17422,7 +17423,7 @@
         <v>121.2776336669922</v>
       </c>
       <c r="C194" s="1">
-        <v>122.5373265835454</v>
+        <v>122.5373171375849</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -17430,10 +17431,10 @@
         <v>45226</v>
       </c>
       <c r="B195" s="1">
-        <v>121.1685485839844</v>
+        <v>121.1685409545898</v>
       </c>
       <c r="C195" s="1">
-        <v>122.4271084498488</v>
+        <v>122.4270913037452</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -17441,10 +17442,10 @@
         <v>45229</v>
       </c>
       <c r="B196" s="1">
-        <v>123.4397735595703</v>
+        <v>123.4397811889648</v>
       </c>
       <c r="C196" s="1">
-        <v>124.7219243047019</v>
+        <v>124.7219223989779</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -17452,10 +17453,10 @@
         <v>45230</v>
       </c>
       <c r="B197" s="1">
-        <v>123.0628967285156</v>
+        <v>123.0628890991211</v>
       </c>
       <c r="C197" s="1">
-        <v>124.3411329095175</v>
+        <v>124.3411156158686</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -17463,10 +17464,10 @@
         <v>45231</v>
       </c>
       <c r="B198" s="1">
-        <v>125.4134521484375</v>
+        <v>125.413459777832</v>
       </c>
       <c r="C198" s="1">
-        <v>126.7161032023463</v>
+        <v>126.7161011428983</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -17474,10 +17475,10 @@
         <v>45232</v>
       </c>
       <c r="B199" s="1">
-        <v>126.444938659668</v>
+        <v>126.4449310302734</v>
       </c>
       <c r="C199" s="1">
-        <v>127.7583036120297</v>
+        <v>127.7582860549635</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -17488,7 +17489,7 @@
         <v>128.041748046875</v>
       </c>
       <c r="C200" s="1">
-        <v>129.3716988231296</v>
+        <v>129.371688850332</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -17499,7 +17500,7 @@
         <v>129.1822967529297</v>
       </c>
       <c r="C201" s="1">
-        <v>130.5240942405899</v>
+        <v>130.5240841789582</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -17510,7 +17511,7 @@
         <v>129.8964080810547</v>
       </c>
       <c r="C202" s="1">
-        <v>131.2456229378906</v>
+        <v>131.2456128206389</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -17518,10 +17519,10 @@
         <v>45238</v>
       </c>
       <c r="B203" s="1">
-        <v>130.7592620849609</v>
+        <v>130.75927734375</v>
       </c>
       <c r="C203" s="1">
-        <v>132.117439279236</v>
+        <v>132.1174445120578</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -17532,7 +17533,7 @@
         <v>129.1724090576172</v>
       </c>
       <c r="C204" s="1">
-        <v>130.5141038432427</v>
+        <v>130.5140937823811</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -17540,10 +17541,10 @@
         <v>45240</v>
       </c>
       <c r="B205" s="1">
-        <v>131.5031127929688</v>
+        <v>131.5031280517578</v>
       </c>
       <c r="C205" s="1">
-        <v>132.8690162549778</v>
+        <v>132.8690214298632</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -17554,7 +17555,7 @@
         <v>131.0072326660156</v>
       </c>
       <c r="C206" s="1">
-        <v>132.3679854941897</v>
+        <v>132.3679752904191</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -17565,7 +17566,7 @@
         <v>132.5246734619141</v>
       </c>
       <c r="C207" s="1">
-        <v>133.9011877241143</v>
+        <v>133.9011774021546</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -17573,10 +17574,10 @@
         <v>45245</v>
       </c>
       <c r="B208" s="1">
-        <v>133.5164642333984</v>
+        <v>133.5164947509766</v>
       </c>
       <c r="C208" s="1">
-        <v>134.90328008025</v>
+        <v>134.9033005156001</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -17584,10 +17585,10 @@
         <v>45246</v>
       </c>
       <c r="B209" s="1">
-        <v>135.8075256347656</v>
+        <v>135.8075714111328</v>
       </c>
       <c r="C209" s="1">
-        <v>137.218138398917</v>
+        <v>137.2181740731016</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -17598,7 +17599,7 @@
         <v>134.2008361816406</v>
       </c>
       <c r="C210" s="1">
-        <v>135.5947604991098</v>
+        <v>135.5947500465987</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -17609,7 +17610,7 @@
         <v>135.1331176757812</v>
       </c>
       <c r="C211" s="1">
-        <v>136.5367254638038</v>
+        <v>136.5367149386801</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -17617,10 +17618,10 @@
         <v>45251</v>
       </c>
       <c r="B212" s="1">
-        <v>135.8471984863281</v>
+        <v>135.8472442626953</v>
       </c>
       <c r="C212" s="1">
-        <v>137.2582233265449</v>
+        <v>137.2582589976395</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -17628,10 +17629,10 @@
         <v>45252</v>
       </c>
       <c r="B213" s="1">
-        <v>137.3547821044922</v>
+        <v>137.3547668457031</v>
       </c>
       <c r="C213" s="1">
-        <v>138.7814659936818</v>
+        <v>138.7814398782405</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -17639,10 +17640,10 @@
         <v>45254</v>
       </c>
       <c r="B214" s="1">
-        <v>135.5695037841797</v>
+        <v>135.5695343017578</v>
       </c>
       <c r="C214" s="1">
-        <v>136.97764425043</v>
+        <v>136.9776645258747</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -17650,10 +17651,10 @@
         <v>45257</v>
       </c>
       <c r="B215" s="1">
-        <v>135.2917938232422</v>
+        <v>135.2918243408203</v>
       </c>
       <c r="C215" s="1">
-        <v>136.6970497570352</v>
+        <v>136.69707005411</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -17661,10 +17662,10 @@
         <v>45258</v>
       </c>
       <c r="B216" s="1">
-        <v>136.0753479003906</v>
+        <v>136.0753173828125</v>
       </c>
       <c r="C216" s="1">
-        <v>137.4887424949645</v>
+        <v>137.4887010618959</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -17675,7 +17676,7 @@
         <v>133.8834686279297</v>
       </c>
       <c r="C217" s="1">
-        <v>135.2740964953671</v>
+        <v>135.2740860675748</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -17683,10 +17684,10 @@
         <v>45260</v>
       </c>
       <c r="B218" s="1">
-        <v>131.4436340332031</v>
+        <v>131.4436187744141</v>
       </c>
       <c r="C218" s="1">
-        <v>132.8089196980957</v>
+        <v>132.8088940430565</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -17697,7 +17698,7 @@
         <v>130.7791137695312</v>
       </c>
       <c r="C219" s="1">
-        <v>132.1374971603298</v>
+        <v>132.1374869743267</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -17705,10 +17706,10 @@
         <v>45264</v>
       </c>
       <c r="B220" s="1">
-        <v>128.2103424072266</v>
+        <v>128.2103271484375</v>
       </c>
       <c r="C220" s="1">
-        <v>129.542044348268</v>
+        <v>129.5420189450604</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -17716,10 +17717,10 @@
         <v>45265</v>
       </c>
       <c r="B221" s="1">
-        <v>129.916259765625</v>
+        <v>129.9162445068359</v>
       </c>
       <c r="C221" s="1">
-        <v>131.2656808189844</v>
+        <v>131.2656552829078</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -17730,7 +17731,7 @@
         <v>128.9541931152344</v>
       </c>
       <c r="C222" s="1">
-        <v>130.2936213240098</v>
+        <v>130.2936112801445</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -17738,10 +17739,10 @@
         <v>45267</v>
       </c>
       <c r="B223" s="1">
-        <v>135.8075256347656</v>
+        <v>135.8075714111328</v>
       </c>
       <c r="C223" s="1">
-        <v>137.218138398917</v>
+        <v>137.2181740731016</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -17752,7 +17753,7 @@
         <v>133.8834686279297</v>
       </c>
       <c r="C224" s="1">
-        <v>135.2740964953671</v>
+        <v>135.2740860675748</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -17760,10 +17761,10 @@
         <v>45271</v>
       </c>
       <c r="B225" s="1">
-        <v>132.1974029541016</v>
+        <v>132.1973724365234</v>
       </c>
       <c r="C225" s="1">
-        <v>133.5705179057445</v>
+        <v>133.5704767747176</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -17771,10 +17772,10 @@
         <v>45272</v>
       </c>
       <c r="B226" s="1">
-        <v>131.4336853027344</v>
+        <v>131.4337005615234</v>
       </c>
       <c r="C226" s="1">
-        <v>132.7988676316291</v>
+        <v>132.798872811922</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -17785,7 +17786,7 @@
         <v>131.4832916259766</v>
       </c>
       <c r="C227" s="1">
-        <v>132.8489892084437</v>
+        <v>132.8489789675943</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -17793,10 +17794,10 @@
         <v>45274</v>
       </c>
       <c r="B228" s="1">
-        <v>130.8584594726562</v>
+        <v>130.8584442138672</v>
       </c>
       <c r="C228" s="1">
-        <v>132.2176670155854</v>
+        <v>132.2176414061236</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -17807,7 +17808,7 @@
         <v>131.5130462646484</v>
       </c>
       <c r="C229" s="1">
-        <v>132.8790529041646</v>
+        <v>132.8790426609976</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -17815,10 +17816,10 @@
         <v>45278</v>
       </c>
       <c r="B230" s="1">
-        <v>134.6868133544922</v>
+        <v>134.6868286132812</v>
       </c>
       <c r="C230" s="1">
-        <v>136.0857854452707</v>
+        <v>136.085790372187</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -17826,10 +17827,10 @@
         <v>45279</v>
       </c>
       <c r="B231" s="1">
-        <v>135.5298156738281</v>
+        <v>135.5298461914062</v>
       </c>
       <c r="C231" s="1">
-        <v>136.9375439055223</v>
+        <v>136.9375641840583</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -17837,10 +17838,10 @@
         <v>45280</v>
       </c>
       <c r="B232" s="1">
-        <v>137.2059936523438</v>
+        <v>137.2059631347656</v>
       </c>
       <c r="C232" s="1">
-        <v>138.6311320977977</v>
+        <v>138.6310905766664</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -17848,10 +17849,10 @@
         <v>45281</v>
       </c>
       <c r="B233" s="1">
-        <v>139.2689514160156</v>
+        <v>139.2689361572266</v>
       </c>
       <c r="C233" s="1">
-        <v>140.7155174998846</v>
+        <v>140.7154912353542</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -17859,10 +17860,10 @@
         <v>45282</v>
       </c>
       <c r="B234" s="1">
-        <v>140.3301696777344</v>
+        <v>140.3301849365234</v>
       </c>
       <c r="C234" s="1">
-        <v>141.787758479369</v>
+        <v>141.7877629667408</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -17873,7 +17874,7 @@
         <v>140.3599395751953</v>
       </c>
       <c r="C235" s="1">
-        <v>141.8178375923698</v>
+        <v>141.8178266601441</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -17881,10 +17882,10 @@
         <v>45287</v>
       </c>
       <c r="B236" s="1">
-        <v>139.2193756103516</v>
+        <v>139.2193145751953</v>
       </c>
       <c r="C236" s="1">
-        <v>140.6654267576297</v>
+        <v>140.6653542451246</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -17892,10 +17893,10 @@
         <v>45288</v>
       </c>
       <c r="B237" s="1">
-        <v>139.0805053710938</v>
+        <v>139.0804901123047</v>
       </c>
       <c r="C237" s="1">
-        <v>140.5251140936524</v>
+        <v>140.5250878437995</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -17903,10 +17904,10 @@
         <v>45289</v>
       </c>
       <c r="B238" s="1">
-        <v>138.544921875</v>
+        <v>138.5449371337891</v>
       </c>
       <c r="C238" s="1">
-        <v>139.9839675706769</v>
+        <v>139.9839721970964</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -17917,7 +17918,7 @@
         <v>137.0373840332031</v>
       </c>
       <c r="C239" s="1">
-        <v>138.4607711553794</v>
+        <v>138.460760481938</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -17925,10 +17926,10 @@
         <v>45294</v>
       </c>
       <c r="B240" s="1">
-        <v>137.7812194824219</v>
+        <v>137.7812652587891</v>
       </c>
       <c r="C240" s="1">
-        <v>139.2123327138413</v>
+        <v>139.2123682343007</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -17936,10 +17937,10 @@
         <v>45295</v>
       </c>
       <c r="B241" s="1">
-        <v>135.2720031738281</v>
+        <v>135.2719879150391</v>
       </c>
       <c r="C241" s="1">
-        <v>136.6770535450609</v>
+        <v>136.6770275918411</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -17950,7 +17951,7 @@
         <v>134.6173706054688</v>
       </c>
       <c r="C242" s="1">
-        <v>136.0156214046422</v>
+        <v>136.0156109196885</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -17958,10 +17959,10 @@
         <v>45299</v>
       </c>
       <c r="B243" s="1">
-        <v>137.7018737792969</v>
+        <v>137.7018890380859</v>
       </c>
       <c r="C243" s="1">
-        <v>139.1321628585857</v>
+        <v>139.1321675506677</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -17969,10 +17970,10 @@
         <v>45300</v>
       </c>
       <c r="B244" s="1">
-        <v>139.7945861816406</v>
+        <v>139.7946166992188</v>
       </c>
       <c r="C244" s="1">
-        <v>141.2466119563935</v>
+        <v>141.2466319027589</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -17983,7 +17984,7 @@
         <v>141.1137084960938</v>
       </c>
       <c r="C245" s="1">
-        <v>142.5794358000185</v>
+        <v>142.579424809084</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -17994,7 +17995,7 @@
         <v>140.9153289794922</v>
       </c>
       <c r="C246" s="1">
-        <v>142.3789957445995</v>
+        <v>142.3789847691162</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -18002,10 +18003,10 @@
         <v>45303</v>
       </c>
       <c r="B247" s="1">
-        <v>141.4806365966797</v>
+        <v>141.4806671142578</v>
       </c>
       <c r="C247" s="1">
-        <v>142.9501751287362</v>
+        <v>142.9501949437801</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -18013,10 +18014,10 @@
         <v>45307</v>
       </c>
       <c r="B248" s="1">
-        <v>141.3219757080078</v>
+        <v>141.3219909667969</v>
       </c>
       <c r="C248" s="1">
-        <v>142.7898662527846</v>
+        <v>142.7898706629075</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -18027,7 +18028,7 @@
         <v>140.3103179931641</v>
       </c>
       <c r="C249" s="1">
-        <v>141.7677005982753</v>
+        <v>141.7676896699145</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -18035,10 +18036,10 @@
         <v>45309</v>
       </c>
       <c r="B250" s="1">
-        <v>142.3038330078125</v>
+        <v>142.3038635253906</v>
       </c>
       <c r="C250" s="1">
-        <v>143.7819219597336</v>
+        <v>143.7819417106612</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -18046,10 +18047,10 @@
         <v>45310</v>
       </c>
       <c r="B251" s="1">
-        <v>145.1801147460938</v>
+        <v>145.1800994873047</v>
       </c>
       <c r="C251" s="1">
-        <v>146.6880792127505</v>
+        <v>146.6880524878169</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -18057,10 +18058,10 @@
         <v>45313</v>
       </c>
       <c r="B252" s="1">
-        <v>144.7932739257812</v>
+        <v>144.7932891845703</v>
       </c>
       <c r="C252" s="1">
-        <v>146.2972203338196</v>
+        <v>146.2972244735732</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -18068,10 +18069,10 @@
         <v>45314</v>
       </c>
       <c r="B253" s="1">
-        <v>145.8346557617188</v>
+        <v>145.8346710205078</v>
       </c>
       <c r="C253" s="1">
-        <v>147.3494188494901</v>
+        <v>147.3494229081335</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -18082,7 +18083,7 @@
         <v>147.4810638427734</v>
       </c>
       <c r="C254" s="1">
-        <v>149.0129279287648</v>
+        <v>149.0129164418956</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -18090,10 +18091,10 @@
         <v>45316</v>
       </c>
       <c r="B255" s="1">
-        <v>150.6250915527344</v>
+        <v>150.6250762939453</v>
       </c>
       <c r="C255" s="1">
-        <v>152.1896121914299</v>
+        <v>152.1895850424029</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -18101,10 +18102,10 @@
         <v>45317</v>
       </c>
       <c r="B256" s="1">
-        <v>150.9424591064453</v>
+        <v>150.9424743652344</v>
       </c>
       <c r="C256" s="1">
-        <v>152.5102761951726</v>
+        <v>152.5102798559841</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -18115,7 +18116,7 @@
         <v>152.2516326904297</v>
       </c>
       <c r="C257" s="1">
-        <v>153.8330479723309</v>
+        <v>153.8330361138961</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -18123,10 +18124,10 @@
         <v>45321</v>
       </c>
       <c r="B258" s="1">
-        <v>150.2184600830078</v>
+        <v>150.2184448242188</v>
       </c>
       <c r="C258" s="1">
-        <v>151.7787571005246</v>
+        <v>151.7787299831689</v>
       </c>
     </row>
   </sheetData>
